--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="211">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260822--01</t>
-  </si>
-  <si>
-    <t>20260822--02</t>
-  </si>
-  <si>
-    <t>20260822--03</t>
-  </si>
-  <si>
     <t>20260823--01</t>
   </si>
   <si>
@@ -142,27 +133,30 @@
     <t>20260828--03</t>
   </si>
   <si>
-    <t>05:11</t>
-  </si>
-  <si>
-    <t>04:27</t>
+    <t>20260829--01</t>
+  </si>
+  <si>
+    <t>20260829--02</t>
+  </si>
+  <si>
+    <t>20260829--03</t>
+  </si>
+  <si>
+    <t>05:33</t>
+  </si>
+  <si>
+    <t>03:20</t>
+  </si>
+  <si>
+    <t>05:47</t>
+  </si>
+  <si>
+    <t>03:15</t>
   </si>
   <si>
     <t>05:55</t>
   </si>
   <si>
-    <t>05:33</t>
-  </si>
-  <si>
-    <t>03:21</t>
-  </si>
-  <si>
-    <t>05:47</t>
-  </si>
-  <si>
-    <t>03:15</t>
-  </si>
-  <si>
     <t>04:24</t>
   </si>
   <si>
@@ -202,6 +196,15 @@
     <t>04:15</t>
   </si>
   <si>
+    <t>05:13</t>
+  </si>
+  <si>
+    <t>05:56</t>
+  </si>
+  <si>
+    <t>04:58</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
@@ -217,13 +220,10 @@
     <t>02:41</t>
   </si>
   <si>
-    <t>01:19:29</t>
-  </si>
-  <si>
-    <t>21:17:00</t>
-  </si>
-  <si>
-    <t>22:53:18</t>
+    <t>04:41</t>
+  </si>
+  <si>
+    <t>01:09</t>
   </si>
   <si>
     <t>00:30:10</t>
@@ -256,7 +256,7 @@
     <t>22:01:58</t>
   </si>
   <si>
-    <t>23:38:55</t>
+    <t>23:38:56</t>
   </si>
   <si>
     <t>19:36:10</t>
@@ -271,7 +271,7 @@
     <t>18:46:54</t>
   </si>
   <si>
-    <t>20:22:57</t>
+    <t>20:22:58</t>
   </si>
   <si>
     <t>21:59:44</t>
@@ -280,7 +280,7 @@
     <t>23:36:55</t>
   </si>
   <si>
-    <t>19:33:24</t>
+    <t>19:33:25</t>
   </si>
   <si>
     <t>21:10:05</t>
@@ -289,13 +289,13 @@
     <t>22:47:08</t>
   </si>
   <si>
-    <t>01:21:54</t>
-  </si>
-  <si>
-    <t>21:19:35</t>
-  </si>
-  <si>
-    <t>22:55:32</t>
+    <t>18:43:52</t>
+  </si>
+  <si>
+    <t>20:20:23</t>
+  </si>
+  <si>
+    <t>21:57:20</t>
   </si>
   <si>
     <t>00:32:30</t>
@@ -355,19 +355,19 @@
     <t>19:35:43</t>
   </si>
   <si>
-    <t>21:12:19</t>
+    <t>21:12:20</t>
   </si>
   <si>
     <t>22:49:47</t>
   </si>
   <si>
-    <t>01:24:30</t>
-  </si>
-  <si>
-    <t>21:21:49</t>
-  </si>
-  <si>
-    <t>22:58:29</t>
+    <t>18:46:15</t>
+  </si>
+  <si>
+    <t>20:22:37</t>
+  </si>
+  <si>
+    <t>21:59:48</t>
   </si>
   <si>
     <t>00:35:16</t>
@@ -388,10 +388,10 @@
     <t>21:19:50</t>
   </si>
   <si>
-    <t>22:56:37</t>
-  </si>
-  <si>
-    <t>00:33:17</t>
+    <t>22:56:36</t>
+  </si>
+  <si>
+    <t>00:33:16</t>
   </si>
   <si>
     <t>20:30:26</t>
@@ -400,7 +400,7 @@
     <t>22:07:10</t>
   </si>
   <si>
-    <t>23:43:54</t>
+    <t>23:43:53</t>
   </si>
   <si>
     <t>19:40:59</t>
@@ -415,7 +415,7 @@
     <t>18:51:31</t>
   </si>
   <si>
-    <t>20:28:06</t>
+    <t>20:28:07</t>
   </si>
   <si>
     <t>22:04:53</t>
@@ -430,22 +430,22 @@
     <t>21:15:16</t>
   </si>
   <si>
-    <t>22:51:54</t>
-  </si>
-  <si>
-    <t>01:27:05</t>
-  </si>
-  <si>
-    <t>21:24:02</t>
-  </si>
-  <si>
-    <t>23:01:27</t>
+    <t>22:51:55</t>
+  </si>
+  <si>
+    <t>18:48:52</t>
+  </si>
+  <si>
+    <t>20:25:35</t>
+  </si>
+  <si>
+    <t>22:02:17</t>
   </si>
   <si>
     <t>00:38:03</t>
   </si>
   <si>
-    <t>20:34:16</t>
+    <t>20:34:15</t>
   </si>
   <si>
     <t>22:12:05</t>
@@ -499,19 +499,19 @@
     <t>19:41:18</t>
   </si>
   <si>
-    <t>21:18:12</t>
+    <t>21:18:13</t>
   </si>
   <si>
     <t>22:54:02</t>
   </si>
   <si>
-    <t>01:29:30</t>
-  </si>
-  <si>
-    <t>21:26:38</t>
-  </si>
-  <si>
-    <t>23:03:42</t>
+    <t>18:51:28</t>
+  </si>
+  <si>
+    <t>20:28:33</t>
+  </si>
+  <si>
+    <t>22:04:46</t>
   </si>
   <si>
     <t>00:40:23</t>
@@ -520,13 +520,13 @@
     <t>20:37:11</t>
   </si>
   <si>
-    <t>22:14:22</t>
+    <t>22:14:21</t>
   </si>
   <si>
     <t>23:51:09</t>
   </si>
   <si>
-    <t>01:27:10</t>
+    <t>01:27:09</t>
   </si>
   <si>
     <t>21:24:56</t>
@@ -562,16 +562,22 @@
     <t>22:10:02</t>
   </si>
   <si>
-    <t>23:45:58</t>
-  </si>
-  <si>
     <t>19:43:37</t>
   </si>
   <si>
     <t>21:20:27</t>
   </si>
   <si>
-    <t>22:56:40</t>
+    <t>22:56:41</t>
+  </si>
+  <si>
+    <t>18:53:52</t>
+  </si>
+  <si>
+    <t>20:30:47</t>
+  </si>
+  <si>
+    <t>22:07:14</t>
   </si>
   <si>
     <t>0°</t>
@@ -598,7 +604,7 @@
     <t>5°</t>
   </si>
   <si>
-    <t>01:29:39</t>
+    <t>18°</t>
   </si>
   <si>
     <t>20:26:32</t>
@@ -619,7 +625,13 @@
     <t>19:38:24</t>
   </si>
   <si>
-    <t>21:11:14</t>
+    <t>21:11:15</t>
+  </si>
+  <si>
+    <t>18:50:56</t>
+  </si>
+  <si>
+    <t>20:23:46</t>
   </si>
   <si>
     <t>B</t>
@@ -668,7 +680,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -683,7 +695,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -695,43 +773,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -743,25 +785,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -774,36 +804,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -844,7 +844,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -916,12 +916,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1403,55 +1397,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>194</v>
+        <v>70</v>
       </c>
       <c r="L2" s="4">
-        <v>-20.7</v>
+        <v>-25</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="O2" s="6">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="P2" s="7">
-        <v>44</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>91</v>
-      </c>
-      <c r="R2" s="9">
-        <v>32</v>
+        <v>0</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1459,54 +1453,54 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L3" s="4">
-        <v>-23.7</v>
+        <v>-19.6</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O3" s="10">
-        <v>26</v>
-      </c>
-      <c r="P3" s="11">
-        <v>25</v>
-      </c>
-      <c r="Q3" s="12">
-        <v>1</v>
-      </c>
-      <c r="R3" s="12">
+        <v>209</v>
+      </c>
+      <c r="O3" s="6">
+        <v>0</v>
+      </c>
+      <c r="P3" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>0</v>
+      </c>
+      <c r="R3" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1515,54 +1509,54 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="L4" s="4">
-        <v>-27.8</v>
+        <v>-26.9</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O4" s="10">
-        <v>30</v>
-      </c>
-      <c r="P4" s="11">
-        <v>26</v>
-      </c>
-      <c r="Q4" s="12">
-        <v>0</v>
-      </c>
-      <c r="R4" s="12">
+        <v>208</v>
+      </c>
+      <c r="O4" s="6">
+        <v>1</v>
+      </c>
+      <c r="P4" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>1</v>
+      </c>
+      <c r="R4" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1571,54 +1565,54 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L5" s="4">
-        <v>-25</v>
+        <v>-27.6</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O5" s="10">
-        <v>24</v>
-      </c>
-      <c r="P5" s="13">
-        <v>21</v>
-      </c>
-      <c r="Q5" s="12">
-        <v>0</v>
-      </c>
-      <c r="R5" s="12">
+        <v>208</v>
+      </c>
+      <c r="O5" s="6">
+        <v>1</v>
+      </c>
+      <c r="P5" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>1</v>
+      </c>
+      <c r="R5" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1630,51 +1624,51 @@
         <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L6" s="4">
-        <v>-19.6</v>
+        <v>-21.5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O6" s="14">
-        <v>0</v>
-      </c>
-      <c r="P6" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="12">
-        <v>0</v>
-      </c>
-      <c r="R6" s="12">
+        <v>209</v>
+      </c>
+      <c r="O6" s="6">
+        <v>11</v>
+      </c>
+      <c r="P6" s="8">
+        <v>11</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>0</v>
+      </c>
+      <c r="R6" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1683,54 +1677,54 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="L7" s="4">
-        <v>-26.9</v>
+        <v>-24.2</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O7" s="14">
-        <v>0</v>
-      </c>
-      <c r="P7" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="12">
-        <v>0</v>
-      </c>
-      <c r="R7" s="12">
+        <v>208</v>
+      </c>
+      <c r="O7" s="6">
+        <v>0</v>
+      </c>
+      <c r="P7" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>0</v>
+      </c>
+      <c r="R7" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1739,55 +1733,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L8" s="4">
-        <v>-27.6</v>
+        <v>-28.5</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O8" s="10">
-        <v>48</v>
-      </c>
-      <c r="P8" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="15">
-        <v>41</v>
-      </c>
-      <c r="R8" s="15">
-        <v>41</v>
+        <v>208</v>
+      </c>
+      <c r="O8" s="6">
+        <v>0</v>
+      </c>
+      <c r="P8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>0</v>
+      </c>
+      <c r="R8" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1795,55 +1789,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L9" s="4">
-        <v>-21.5</v>
+        <v>-25.7</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="O9" s="6">
-        <v>49</v>
-      </c>
-      <c r="P9" s="12">
-        <v>2</v>
-      </c>
-      <c r="Q9" s="16">
-        <v>36</v>
-      </c>
-      <c r="R9" s="17">
-        <v>9</v>
+        <v>0</v>
+      </c>
+      <c r="P9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>0</v>
+      </c>
+      <c r="R9" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1851,55 +1845,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>75</v>
+        <v>197</v>
       </c>
       <c r="L10" s="4">
-        <v>-24.2</v>
+        <v>-20</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O10" s="14">
-        <v>0</v>
-      </c>
-      <c r="P10" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="12">
-        <v>0</v>
-      </c>
-      <c r="R10" s="12">
-        <v>0</v>
+        <v>208</v>
+      </c>
+      <c r="O10" s="9">
+        <v>63</v>
+      </c>
+      <c r="P10" s="10">
+        <v>18</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>19</v>
+      </c>
+      <c r="R10" s="11">
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1910,52 +1904,52 @@
         <v>30</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="L11" s="4">
-        <v>-28.5</v>
+        <v>-27.5</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O11" s="14">
-        <v>0</v>
-      </c>
-      <c r="P11" s="12">
-        <v>0</v>
+        <v>208</v>
+      </c>
+      <c r="O11" s="9">
+        <v>81</v>
+      </c>
+      <c r="P11" s="8">
+        <v>8</v>
       </c>
       <c r="Q11" s="12">
-        <v>0</v>
-      </c>
-      <c r="R11" s="12">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="R11" s="13">
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1963,55 +1957,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>173</v>
+        <v>145</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L12" s="4">
-        <v>-25.7</v>
+        <v>-28.3</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O12" s="14">
-        <v>0</v>
-      </c>
-      <c r="P12" s="12">
-        <v>0</v>
+        <v>208</v>
+      </c>
+      <c r="O12" s="9">
+        <v>97</v>
+      </c>
+      <c r="P12" s="14">
+        <v>6</v>
       </c>
       <c r="Q12" s="12">
-        <v>0</v>
-      </c>
-      <c r="R12" s="12">
-        <v>0</v>
+        <v>35</v>
+      </c>
+      <c r="R12" s="15">
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2019,55 +2013,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="L13" s="4">
-        <v>-20</v>
+        <v>-14.7</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O13" s="6">
-        <v>95</v>
-      </c>
-      <c r="P13" s="13">
-        <v>20</v>
-      </c>
-      <c r="Q13" s="12">
-        <v>0</v>
-      </c>
-      <c r="R13" s="8">
-        <v>88</v>
+        <v>210</v>
+      </c>
+      <c r="O13" s="9">
+        <v>100</v>
+      </c>
+      <c r="P13" s="8">
+        <v>10</v>
+      </c>
+      <c r="Q13" s="10">
+        <v>19</v>
+      </c>
+      <c r="R13" s="16">
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2078,52 +2072,52 @@
         <v>30</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="L14" s="4">
-        <v>-27.5</v>
+        <v>-24.7</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O14" s="6">
-        <v>84</v>
-      </c>
-      <c r="P14" s="13">
-        <v>18</v>
-      </c>
-      <c r="Q14" s="11">
-        <v>26</v>
+        <v>208</v>
+      </c>
+      <c r="O14" s="9">
+        <v>78</v>
+      </c>
+      <c r="P14" s="8">
+        <v>9</v>
+      </c>
+      <c r="Q14" s="17">
+        <v>23</v>
       </c>
       <c r="R14" s="18">
-        <v>61</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2131,55 +2125,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="L15" s="4">
-        <v>-28.3</v>
+        <v>-29.2</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O15" s="6">
-        <v>73</v>
-      </c>
-      <c r="P15" s="19">
-        <v>13</v>
-      </c>
-      <c r="Q15" s="11">
-        <v>26</v>
-      </c>
-      <c r="R15" s="20">
-        <v>50</v>
+        <v>208</v>
+      </c>
+      <c r="O15" s="9">
+        <v>70</v>
+      </c>
+      <c r="P15" s="8">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="17">
+        <v>24</v>
+      </c>
+      <c r="R15" s="19">
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2187,55 +2181,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="L16" s="4">
-        <v>-14.6</v>
+        <v>-8.4</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O16" s="6">
-        <v>90</v>
-      </c>
-      <c r="P16" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="13">
-        <v>18</v>
-      </c>
-      <c r="R16" s="21">
-        <v>79</v>
+        <v>209</v>
+      </c>
+      <c r="O16" s="9">
+        <v>100</v>
+      </c>
+      <c r="P16" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="20">
+        <v>42</v>
+      </c>
+      <c r="R16" s="16">
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2243,55 +2237,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="L17" s="4">
-        <v>-24.7</v>
+        <v>-20.4</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O17" s="6">
-        <v>92</v>
-      </c>
-      <c r="P17" s="19">
-        <v>17</v>
-      </c>
-      <c r="Q17" s="15">
-        <v>41</v>
-      </c>
-      <c r="R17" s="22">
-        <v>84</v>
+        <v>210</v>
+      </c>
+      <c r="O17" s="9">
+        <v>71</v>
+      </c>
+      <c r="P17" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="21">
+        <v>59</v>
+      </c>
+      <c r="R17" s="12">
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2299,55 +2293,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="L18" s="4">
-        <v>-29.2</v>
+        <v>-28.1</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O18" s="6">
-        <v>89</v>
-      </c>
-      <c r="P18" s="19">
-        <v>13</v>
-      </c>
-      <c r="Q18" s="7">
-        <v>46</v>
-      </c>
-      <c r="R18" s="23">
-        <v>76</v>
+        <v>208</v>
+      </c>
+      <c r="O18" s="9">
+        <v>66</v>
+      </c>
+      <c r="P18" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="12">
+        <v>34</v>
+      </c>
+      <c r="R18" s="18">
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2355,55 +2349,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>179</v>
+        <v>121</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>198</v>
+        <v>87</v>
       </c>
       <c r="L19" s="4">
-        <v>-8.4</v>
+        <v>-29.1</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O19" s="6">
-        <v>99</v>
-      </c>
-      <c r="P19" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="21">
-        <v>79</v>
-      </c>
-      <c r="R19" s="18">
-        <v>60</v>
+        <v>209</v>
+      </c>
+      <c r="O19" s="9">
+        <v>77</v>
+      </c>
+      <c r="P19" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="17">
+        <v>24</v>
+      </c>
+      <c r="R19" s="11">
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2411,55 +2405,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="L20" s="4">
-        <v>-20.4</v>
+        <v>-15</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O20" s="6">
-        <v>100</v>
-      </c>
-      <c r="P20" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="24">
-        <v>68</v>
-      </c>
-      <c r="R20" s="22">
-        <v>86</v>
+        <v>210</v>
+      </c>
+      <c r="O20" s="9">
+        <v>79</v>
+      </c>
+      <c r="P20" s="22">
+        <v>70</v>
+      </c>
+      <c r="Q20" s="22">
+        <v>70</v>
+      </c>
+      <c r="R20" s="21">
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2467,55 +2461,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="L21" s="4">
+        <v>-25.2</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="O21" s="9">
         <v>57</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="L21" s="4">
-        <v>-28.1</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O21" s="6">
-        <v>99</v>
-      </c>
-      <c r="P21" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="7">
-        <v>47</v>
-      </c>
-      <c r="R21" s="25">
-        <v>98</v>
+      <c r="P21" s="23">
+        <v>48</v>
+      </c>
+      <c r="Q21" s="17">
+        <v>23</v>
+      </c>
+      <c r="R21" s="12">
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2523,55 +2517,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L22" s="4">
-        <v>-29.1</v>
+        <v>-29.8</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O22" s="6">
-        <v>100</v>
-      </c>
-      <c r="P22" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="26">
-        <v>54</v>
-      </c>
-      <c r="R22" s="25">
-        <v>99</v>
+        <v>208</v>
+      </c>
+      <c r="O22" s="9">
+        <v>45</v>
+      </c>
+      <c r="P22" s="19">
+        <v>28</v>
+      </c>
+      <c r="Q22" s="7">
+        <v>0</v>
+      </c>
+      <c r="R22" s="14">
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2579,55 +2573,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="L23" s="4">
-        <v>-15</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O23" s="6">
-        <v>85</v>
-      </c>
-      <c r="P23" s="9">
-        <v>29</v>
-      </c>
-      <c r="Q23" s="18">
-        <v>60</v>
-      </c>
-      <c r="R23" s="17">
-        <v>9</v>
+        <v>210</v>
+      </c>
+      <c r="O23" s="9">
+        <v>76</v>
+      </c>
+      <c r="P23" s="12">
+        <v>37</v>
+      </c>
+      <c r="Q23" s="19">
+        <v>30</v>
+      </c>
+      <c r="R23" s="18">
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2635,55 +2629,55 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D24" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="L24" s="4">
+        <v>-20.9</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="O24" s="9">
+        <v>74</v>
+      </c>
+      <c r="P24" s="8">
+        <v>9</v>
+      </c>
+      <c r="Q24" s="20">
+        <v>41</v>
+      </c>
+      <c r="R24" s="21">
         <v>62</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="L24" s="4">
-        <v>-25.2</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O24" s="6">
-        <v>59</v>
-      </c>
-      <c r="P24" s="19">
-        <v>17</v>
-      </c>
-      <c r="Q24" s="9">
-        <v>28</v>
-      </c>
-      <c r="R24" s="13">
-        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2691,55 +2685,55 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="L25" s="4">
-        <v>-29.8</v>
+        <v>-28.7</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O25" s="10">
-        <v>45</v>
-      </c>
-      <c r="P25" s="17">
-        <v>9</v>
-      </c>
-      <c r="Q25" s="17">
-        <v>11</v>
-      </c>
-      <c r="R25" s="13">
-        <v>22</v>
+        <v>208</v>
+      </c>
+      <c r="O25" s="9">
+        <v>94</v>
+      </c>
+      <c r="P25" s="14">
+        <v>5</v>
+      </c>
+      <c r="Q25" s="24">
+        <v>78</v>
+      </c>
+      <c r="R25" s="15">
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="204">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260823--01</t>
-  </si>
-  <si>
-    <t>20260823--02</t>
-  </si>
-  <si>
-    <t>20260823--03</t>
-  </si>
-  <si>
-    <t>20260823--04</t>
-  </si>
-  <si>
     <t>20260824--01</t>
   </si>
   <si>
@@ -142,67 +130,73 @@
     <t>20260829--03</t>
   </si>
   <si>
+    <t>20260830--01</t>
+  </si>
+  <si>
+    <t>20260830--02</t>
+  </si>
+  <si>
+    <t>03:15</t>
+  </si>
+  <si>
     <t>05:33</t>
   </si>
   <si>
-    <t>03:20</t>
-  </si>
-  <si>
-    <t>05:47</t>
-  </si>
-  <si>
-    <t>03:15</t>
+    <t>05:54</t>
+  </si>
+  <si>
+    <t>04:24</t>
+  </si>
+  <si>
+    <t>05:09</t>
+  </si>
+  <si>
+    <t>05:57</t>
+  </si>
+  <si>
+    <t>05:04</t>
+  </si>
+  <si>
+    <t>04:33</t>
+  </si>
+  <si>
+    <t>05:29</t>
+  </si>
+  <si>
+    <t>03:32</t>
+  </si>
+  <si>
+    <t>05:48</t>
+  </si>
+  <si>
+    <t>05:44</t>
+  </si>
+  <si>
+    <t>02:58</t>
+  </si>
+  <si>
+    <t>05:34</t>
+  </si>
+  <si>
+    <t>05:53</t>
+  </si>
+  <si>
+    <t>04:15</t>
+  </si>
+  <si>
+    <t>05:13</t>
+  </si>
+  <si>
+    <t>05:56</t>
+  </si>
+  <si>
+    <t>04:59</t>
   </si>
   <si>
     <t>05:55</t>
   </si>
   <si>
-    <t>04:24</t>
-  </si>
-  <si>
-    <t>05:10</t>
-  </si>
-  <si>
-    <t>05:57</t>
-  </si>
-  <si>
-    <t>05:04</t>
-  </si>
-  <si>
-    <t>04:33</t>
-  </si>
-  <si>
-    <t>05:29</t>
-  </si>
-  <si>
-    <t>03:32</t>
-  </si>
-  <si>
-    <t>05:48</t>
-  </si>
-  <si>
-    <t>05:44</t>
-  </si>
-  <si>
-    <t>02:58</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>05:53</t>
-  </si>
-  <si>
-    <t>04:15</t>
-  </si>
-  <si>
-    <t>05:13</t>
-  </si>
-  <si>
-    <t>05:56</t>
-  </si>
-  <si>
-    <t>04:58</t>
+    <t>05:26</t>
   </si>
   <si>
     <t>00:00</t>
@@ -211,7 +205,7 @@
     <t>01:07</t>
   </si>
   <si>
-    <t>03:04</t>
+    <t>03:05</t>
   </si>
   <si>
     <t>00:28</t>
@@ -226,304 +220,268 @@
     <t>01:09</t>
   </si>
   <si>
-    <t>00:30:10</t>
-  </si>
-  <si>
-    <t>20:28:00</t>
-  </si>
-  <si>
-    <t>22:04:02</t>
-  </si>
-  <si>
-    <t>23:40:49</t>
-  </si>
-  <si>
     <t>01:17:59</t>
   </si>
   <si>
     <t>21:14:45</t>
   </si>
   <si>
-    <t>22:51:25</t>
+    <t>22:51:24</t>
   </si>
   <si>
     <t>00:28:28</t>
   </si>
   <si>
-    <t>20:25:27</t>
-  </si>
-  <si>
-    <t>22:01:58</t>
-  </si>
-  <si>
-    <t>23:38:56</t>
-  </si>
-  <si>
-    <t>19:36:10</t>
+    <t>20:25:26</t>
+  </si>
+  <si>
+    <t>22:01:57</t>
+  </si>
+  <si>
+    <t>23:38:55</t>
+  </si>
+  <si>
+    <t>19:36:09</t>
+  </si>
+  <si>
+    <t>21:12:28</t>
+  </si>
+  <si>
+    <t>22:49:20</t>
+  </si>
+  <si>
+    <t>18:46:53</t>
+  </si>
+  <si>
+    <t>20:22:56</t>
+  </si>
+  <si>
+    <t>21:59:43</t>
+  </si>
+  <si>
+    <t>23:36:53</t>
+  </si>
+  <si>
+    <t>19:33:22</t>
+  </si>
+  <si>
+    <t>21:10:02</t>
+  </si>
+  <si>
+    <t>22:47:05</t>
+  </si>
+  <si>
+    <t>18:43:48</t>
+  </si>
+  <si>
+    <t>20:20:19</t>
+  </si>
+  <si>
+    <t>21:57:17</t>
+  </si>
+  <si>
+    <t>19:30:34</t>
+  </si>
+  <si>
+    <t>21:07:26</t>
+  </si>
+  <si>
+    <t>01:20:57</t>
+  </si>
+  <si>
+    <t>21:17:03</t>
+  </si>
+  <si>
+    <t>22:53:39</t>
+  </si>
+  <si>
+    <t>00:31:04</t>
+  </si>
+  <si>
+    <t>20:27:51</t>
+  </si>
+  <si>
+    <t>22:04:11</t>
+  </si>
+  <si>
+    <t>23:41:21</t>
+  </si>
+  <si>
+    <t>19:38:42</t>
+  </si>
+  <si>
+    <t>21:14:42</t>
+  </si>
+  <si>
+    <t>22:51:40</t>
+  </si>
+  <si>
+    <t>18:49:43</t>
+  </si>
+  <si>
+    <t>20:25:11</t>
+  </si>
+  <si>
+    <t>22:01:59</t>
+  </si>
+  <si>
+    <t>23:39:56</t>
+  </si>
+  <si>
+    <t>19:35:41</t>
+  </si>
+  <si>
+    <t>21:12:17</t>
+  </si>
+  <si>
+    <t>22:49:44</t>
+  </si>
+  <si>
+    <t>18:46:11</t>
+  </si>
+  <si>
+    <t>20:22:33</t>
+  </si>
+  <si>
+    <t>21:59:44</t>
+  </si>
+  <si>
+    <t>19:32:48</t>
+  </si>
+  <si>
+    <t>21:09:46</t>
+  </si>
+  <si>
+    <t>01:22:34</t>
+  </si>
+  <si>
+    <t>21:19:49</t>
+  </si>
+  <si>
+    <t>22:56:36</t>
+  </si>
+  <si>
+    <t>00:33:16</t>
+  </si>
+  <si>
+    <t>20:30:25</t>
+  </si>
+  <si>
+    <t>22:07:10</t>
+  </si>
+  <si>
+    <t>23:43:53</t>
+  </si>
+  <si>
+    <t>19:40:58</t>
+  </si>
+  <si>
+    <t>21:17:39</t>
+  </si>
+  <si>
+    <t>22:54:24</t>
+  </si>
+  <si>
+    <t>18:51:29</t>
+  </si>
+  <si>
+    <t>20:28:05</t>
+  </si>
+  <si>
+    <t>22:04:51</t>
+  </si>
+  <si>
+    <t>23:41:25</t>
+  </si>
+  <si>
+    <t>19:38:28</t>
+  </si>
+  <si>
+    <t>21:15:13</t>
+  </si>
+  <si>
+    <t>22:51:52</t>
+  </si>
+  <si>
+    <t>18:48:48</t>
+  </si>
+  <si>
+    <t>20:25:31</t>
+  </si>
+  <si>
+    <t>22:02:13</t>
+  </si>
+  <si>
+    <t>19:35:45</t>
   </si>
   <si>
     <t>21:12:29</t>
   </si>
   <si>
-    <t>22:49:21</t>
-  </si>
-  <si>
-    <t>18:46:54</t>
-  </si>
-  <si>
-    <t>20:22:58</t>
-  </si>
-  <si>
-    <t>21:59:44</t>
-  </si>
-  <si>
-    <t>23:36:55</t>
-  </si>
-  <si>
-    <t>19:33:25</t>
-  </si>
-  <si>
-    <t>21:10:05</t>
-  </si>
-  <si>
-    <t>22:47:08</t>
-  </si>
-  <si>
-    <t>18:43:52</t>
-  </si>
-  <si>
-    <t>20:20:23</t>
-  </si>
-  <si>
-    <t>21:57:20</t>
-  </si>
-  <si>
-    <t>00:32:30</t>
-  </si>
-  <si>
-    <t>20:30:55</t>
-  </si>
-  <si>
-    <t>22:06:18</t>
-  </si>
-  <si>
-    <t>23:43:05</t>
-  </si>
-  <si>
-    <t>01:20:57</t>
-  </si>
-  <si>
-    <t>21:17:04</t>
-  </si>
-  <si>
-    <t>22:53:39</t>
-  </si>
-  <si>
-    <t>00:31:05</t>
-  </si>
-  <si>
-    <t>20:27:51</t>
-  </si>
-  <si>
-    <t>22:04:12</t>
-  </si>
-  <si>
-    <t>23:41:22</t>
+    <t>01:24:12</t>
+  </si>
+  <si>
+    <t>21:22:36</t>
+  </si>
+  <si>
+    <t>22:59:33</t>
+  </si>
+  <si>
+    <t>00:35:28</t>
+  </si>
+  <si>
+    <t>20:33:00</t>
+  </si>
+  <si>
+    <t>22:10:08</t>
+  </si>
+  <si>
+    <t>23:46:25</t>
+  </si>
+  <si>
+    <t>19:43:15</t>
+  </si>
+  <si>
+    <t>21:20:36</t>
+  </si>
+  <si>
+    <t>22:57:09</t>
+  </si>
+  <si>
+    <t>18:53:15</t>
+  </si>
+  <si>
+    <t>20:30:59</t>
+  </si>
+  <si>
+    <t>22:07:43</t>
+  </si>
+  <si>
+    <t>23:42:54</t>
+  </si>
+  <si>
+    <t>19:41:15</t>
+  </si>
+  <si>
+    <t>21:18:10</t>
+  </si>
+  <si>
+    <t>22:53:59</t>
+  </si>
+  <si>
+    <t>18:51:24</t>
+  </si>
+  <si>
+    <t>20:28:29</t>
+  </si>
+  <si>
+    <t>22:04:43</t>
   </si>
   <si>
     <t>19:38:43</t>
   </si>
   <si>
-    <t>21:14:43</t>
-  </si>
-  <si>
-    <t>22:51:41</t>
-  </si>
-  <si>
-    <t>18:49:45</t>
-  </si>
-  <si>
-    <t>20:25:13</t>
-  </si>
-  <si>
-    <t>22:02:01</t>
-  </si>
-  <si>
-    <t>23:39:58</t>
-  </si>
-  <si>
-    <t>19:35:43</t>
-  </si>
-  <si>
-    <t>21:12:20</t>
-  </si>
-  <si>
-    <t>22:49:47</t>
-  </si>
-  <si>
-    <t>18:46:15</t>
-  </si>
-  <si>
-    <t>20:22:37</t>
-  </si>
-  <si>
-    <t>21:59:48</t>
-  </si>
-  <si>
-    <t>00:35:16</t>
-  </si>
-  <si>
-    <t>20:32:35</t>
-  </si>
-  <si>
-    <t>22:09:11</t>
-  </si>
-  <si>
-    <t>23:45:59</t>
-  </si>
-  <si>
-    <t>01:22:34</t>
-  </si>
-  <si>
-    <t>21:19:50</t>
-  </si>
-  <si>
-    <t>22:56:36</t>
-  </si>
-  <si>
-    <t>00:33:16</t>
-  </si>
-  <si>
-    <t>20:30:26</t>
-  </si>
-  <si>
-    <t>22:07:10</t>
-  </si>
-  <si>
-    <t>23:43:53</t>
-  </si>
-  <si>
-    <t>19:40:59</t>
-  </si>
-  <si>
-    <t>21:17:40</t>
-  </si>
-  <si>
-    <t>22:54:26</t>
-  </si>
-  <si>
-    <t>18:51:31</t>
-  </si>
-  <si>
-    <t>20:28:07</t>
-  </si>
-  <si>
-    <t>22:04:53</t>
-  </si>
-  <si>
-    <t>23:41:27</t>
-  </si>
-  <si>
-    <t>19:38:30</t>
-  </si>
-  <si>
-    <t>21:15:16</t>
-  </si>
-  <si>
-    <t>22:51:55</t>
-  </si>
-  <si>
-    <t>18:48:52</t>
-  </si>
-  <si>
-    <t>20:25:35</t>
-  </si>
-  <si>
-    <t>22:02:17</t>
-  </si>
-  <si>
-    <t>00:38:03</t>
-  </si>
-  <si>
-    <t>20:34:15</t>
-  </si>
-  <si>
-    <t>22:12:05</t>
-  </si>
-  <si>
-    <t>23:48:52</t>
-  </si>
-  <si>
-    <t>01:24:12</t>
-  </si>
-  <si>
-    <t>21:22:37</t>
-  </si>
-  <si>
-    <t>22:59:34</t>
-  </si>
-  <si>
-    <t>00:35:29</t>
-  </si>
-  <si>
-    <t>20:33:01</t>
-  </si>
-  <si>
-    <t>22:10:09</t>
-  </si>
-  <si>
-    <t>23:46:26</t>
-  </si>
-  <si>
-    <t>19:43:16</t>
-  </si>
-  <si>
-    <t>21:20:38</t>
-  </si>
-  <si>
-    <t>22:57:10</t>
-  </si>
-  <si>
-    <t>18:53:17</t>
-  </si>
-  <si>
-    <t>20:31:01</t>
-  </si>
-  <si>
-    <t>22:07:45</t>
-  </si>
-  <si>
-    <t>23:42:56</t>
-  </si>
-  <si>
-    <t>19:41:18</t>
-  </si>
-  <si>
-    <t>21:18:13</t>
-  </si>
-  <si>
-    <t>22:54:02</t>
-  </si>
-  <si>
-    <t>18:51:28</t>
-  </si>
-  <si>
-    <t>20:28:33</t>
-  </si>
-  <si>
-    <t>22:04:46</t>
-  </si>
-  <si>
-    <t>00:40:23</t>
-  </si>
-  <si>
-    <t>20:37:11</t>
-  </si>
-  <si>
-    <t>22:14:21</t>
-  </si>
-  <si>
-    <t>23:51:09</t>
+    <t>21:15:12</t>
   </si>
   <si>
     <t>01:27:09</t>
@@ -532,52 +490,61 @@
     <t>21:24:56</t>
   </si>
   <si>
-    <t>23:01:49</t>
+    <t>23:01:48</t>
   </si>
   <si>
     <t>00:38:05</t>
   </si>
   <si>
-    <t>20:35:26</t>
-  </si>
-  <si>
-    <t>22:12:23</t>
-  </si>
-  <si>
-    <t>19:45:50</t>
-  </si>
-  <si>
-    <t>21:22:52</t>
-  </si>
-  <si>
-    <t>22:59:30</t>
-  </si>
-  <si>
-    <t>18:56:09</t>
-  </si>
-  <si>
-    <t>20:33:17</t>
-  </si>
-  <si>
-    <t>22:10:02</t>
-  </si>
-  <si>
-    <t>19:43:37</t>
-  </si>
-  <si>
-    <t>21:20:27</t>
-  </si>
-  <si>
-    <t>22:56:41</t>
-  </si>
-  <si>
-    <t>18:53:52</t>
-  </si>
-  <si>
-    <t>20:30:47</t>
-  </si>
-  <si>
-    <t>22:07:14</t>
+    <t>20:35:25</t>
+  </si>
+  <si>
+    <t>22:12:22</t>
+  </si>
+  <si>
+    <t>23:48:51</t>
+  </si>
+  <si>
+    <t>19:45:49</t>
+  </si>
+  <si>
+    <t>21:22:51</t>
+  </si>
+  <si>
+    <t>22:59:29</t>
+  </si>
+  <si>
+    <t>18:56:07</t>
+  </si>
+  <si>
+    <t>20:33:15</t>
+  </si>
+  <si>
+    <t>22:10:00</t>
+  </si>
+  <si>
+    <t>23:45:56</t>
+  </si>
+  <si>
+    <t>19:43:34</t>
+  </si>
+  <si>
+    <t>21:20:24</t>
+  </si>
+  <si>
+    <t>22:56:38</t>
+  </si>
+  <si>
+    <t>18:53:48</t>
+  </si>
+  <si>
+    <t>20:30:43</t>
+  </si>
+  <si>
+    <t>19:40:57</t>
+  </si>
+  <si>
+    <t>21:17:33</t>
   </si>
   <si>
     <t>0°</t>
@@ -607,31 +574,43 @@
     <t>18°</t>
   </si>
   <si>
-    <t>20:26:32</t>
-  </si>
-  <si>
-    <t>19:39:50</t>
-  </si>
-  <si>
-    <t>21:12:42</t>
-  </si>
-  <si>
-    <t>18:52:49</t>
-  </si>
-  <si>
-    <t>20:25:41</t>
-  </si>
-  <si>
-    <t>19:38:24</t>
-  </si>
-  <si>
-    <t>21:11:15</t>
-  </si>
-  <si>
-    <t>18:50:56</t>
-  </si>
-  <si>
-    <t>20:23:46</t>
+    <t>29°</t>
+  </si>
+  <si>
+    <t>6°</t>
+  </si>
+  <si>
+    <t>20:26:31</t>
+  </si>
+  <si>
+    <t>19:39:49</t>
+  </si>
+  <si>
+    <t>21:12:41</t>
+  </si>
+  <si>
+    <t>18:52:48</t>
+  </si>
+  <si>
+    <t>20:25:39</t>
+  </si>
+  <si>
+    <t>19:38:22</t>
+  </si>
+  <si>
+    <t>21:11:12</t>
+  </si>
+  <si>
+    <t>18:50:52</t>
+  </si>
+  <si>
+    <t>20:23:42</t>
+  </si>
+  <si>
+    <t>19:36:03</t>
+  </si>
+  <si>
+    <t>21:08:52</t>
   </si>
   <si>
     <t>B</t>
@@ -640,10 +619,10 @@
     <t>A+B</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
   <si>
     <t>2</t>
@@ -680,7 +659,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -707,7 +686,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -719,13 +698,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -737,31 +764,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -773,37 +776,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FFF6F9FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -844,7 +829,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -916,6 +901,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1319,7 +1307,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1397,55 +1385,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L2" s="4">
-        <v>-25</v>
+        <v>-21.5</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="O2" s="6">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
-      <c r="Q2" s="7">
+      <c r="Q2" s="8">
+        <v>14</v>
+      </c>
+      <c r="R2" s="7">
         <v>0</v>
-      </c>
-      <c r="R2" s="7">
-        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1453,46 +1441,46 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="L3" s="4">
-        <v>-19.6</v>
+        <v>-24.2</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="O3" s="6">
-        <v>0</v>
+        <v>202</v>
+      </c>
+      <c r="O3" s="9">
+        <v>100</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
@@ -1500,8 +1488,8 @@
       <c r="Q3" s="7">
         <v>0</v>
       </c>
-      <c r="R3" s="7">
-        <v>0</v>
+      <c r="R3" s="10">
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1509,55 +1497,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L4" s="4">
-        <v>-26.9</v>
+        <v>-28.5</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O4" s="6">
-        <v>1</v>
+        <v>202</v>
+      </c>
+      <c r="O4" s="9">
+        <v>84</v>
       </c>
       <c r="P4" s="7">
         <v>0</v>
       </c>
       <c r="Q4" s="7">
-        <v>1</v>
-      </c>
-      <c r="R4" s="7">
         <v>0</v>
+      </c>
+      <c r="R4" s="11">
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1565,55 +1553,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L5" s="4">
-        <v>-27.6</v>
+        <v>-25.7</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="O5" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P5" s="7">
         <v>0</v>
       </c>
       <c r="Q5" s="7">
-        <v>1</v>
-      </c>
-      <c r="R5" s="7">
         <v>0</v>
+      </c>
+      <c r="R5" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1621,55 +1609,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="J6" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="L6" s="4">
-        <v>-21.5</v>
+        <v>-20</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="O6" s="6">
-        <v>11</v>
-      </c>
-      <c r="P6" s="8">
-        <v>11</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>0</v>
-      </c>
-      <c r="R6" s="7">
-        <v>0</v>
+        <v>202</v>
+      </c>
+      <c r="O6" s="9">
+        <v>100</v>
+      </c>
+      <c r="P6" s="13">
+        <v>10</v>
+      </c>
+      <c r="Q6" s="14">
+        <v>55</v>
+      </c>
+      <c r="R6" s="10">
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1677,55 +1665,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L7" s="4">
-        <v>-24.2</v>
+        <v>-27.5</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O7" s="6">
-        <v>0</v>
-      </c>
-      <c r="P7" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>0</v>
-      </c>
-      <c r="R7" s="7">
-        <v>0</v>
+        <v>202</v>
+      </c>
+      <c r="O7" s="9">
+        <v>100</v>
+      </c>
+      <c r="P7" s="8">
+        <v>17</v>
+      </c>
+      <c r="Q7" s="15">
+        <v>69</v>
+      </c>
+      <c r="R7" s="10">
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1733,55 +1721,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L8" s="4">
+        <v>-28.3</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="O8" s="9">
         <v>100</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="L8" s="4">
-        <v>-28.5</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O8" s="6">
-        <v>0</v>
-      </c>
-      <c r="P8" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="7">
-        <v>0</v>
-      </c>
-      <c r="R8" s="7">
-        <v>0</v>
+      <c r="P8" s="8">
+        <v>16</v>
+      </c>
+      <c r="Q8" s="16">
+        <v>61</v>
+      </c>
+      <c r="R8" s="11">
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1795,49 +1783,49 @@
         <v>47</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="L9" s="4">
-        <v>-25.7</v>
+        <v>-14.6</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O9" s="6">
-        <v>0</v>
-      </c>
-      <c r="P9" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="7">
-        <v>0</v>
-      </c>
-      <c r="R9" s="7">
-        <v>0</v>
+        <v>203</v>
+      </c>
+      <c r="O9" s="9">
+        <v>97</v>
+      </c>
+      <c r="P9" s="17">
+        <v>25</v>
+      </c>
+      <c r="Q9" s="16">
+        <v>61</v>
+      </c>
+      <c r="R9" s="18">
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1845,55 +1833,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="L10" s="4">
-        <v>-20</v>
+        <v>-24.7</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="O10" s="9">
-        <v>63</v>
-      </c>
-      <c r="P10" s="10">
-        <v>18</v>
-      </c>
-      <c r="Q10" s="10">
-        <v>19</v>
-      </c>
-      <c r="R10" s="11">
-        <v>63</v>
+        <v>60</v>
+      </c>
+      <c r="P10" s="19">
+        <v>40</v>
+      </c>
+      <c r="Q10" s="17">
+        <v>27</v>
+      </c>
+      <c r="R10" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1901,55 +1889,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L11" s="4">
-        <v>-27.5</v>
+        <v>-29.2</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="O11" s="9">
-        <v>81</v>
-      </c>
-      <c r="P11" s="8">
-        <v>8</v>
-      </c>
-      <c r="Q11" s="12">
-        <v>33</v>
+        <v>62</v>
+      </c>
+      <c r="P11" s="20">
+        <v>37</v>
+      </c>
+      <c r="Q11" s="17">
+        <v>23</v>
       </c>
       <c r="R11" s="13">
-        <v>74</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1957,55 +1945,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>63</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>80</v>
+        <v>191</v>
       </c>
       <c r="L12" s="4">
-        <v>-28.3</v>
+        <v>-8.4</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O12" s="9">
-        <v>97</v>
-      </c>
-      <c r="P12" s="14">
-        <v>6</v>
-      </c>
-      <c r="Q12" s="12">
-        <v>35</v>
-      </c>
-      <c r="R12" s="15">
-        <v>89</v>
+        <v>201</v>
+      </c>
+      <c r="O12" s="21">
+        <v>44</v>
+      </c>
+      <c r="P12" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>0</v>
+      </c>
+      <c r="R12" s="17">
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2013,55 +2001,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>64</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="L13" s="4">
-        <v>-14.7</v>
+        <v>-20.4</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="O13" s="9">
-        <v>100</v>
-      </c>
-      <c r="P13" s="8">
-        <v>10</v>
-      </c>
-      <c r="Q13" s="10">
-        <v>19</v>
-      </c>
-      <c r="R13" s="16">
-        <v>100</v>
+        <v>65</v>
+      </c>
+      <c r="P13" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="12">
+        <v>7</v>
+      </c>
+      <c r="R13" s="22">
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2069,55 +2057,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="I14" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>191</v>
-      </c>
       <c r="K14" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L14" s="4">
+        <v>-28.1</v>
+      </c>
+      <c r="M14" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="L14" s="4">
-        <v>-24.7</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>206</v>
-      </c>
       <c r="N14" s="1" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="O14" s="9">
-        <v>78</v>
-      </c>
-      <c r="P14" s="8">
-        <v>9</v>
-      </c>
-      <c r="Q14" s="17">
-        <v>23</v>
-      </c>
-      <c r="R14" s="18">
-        <v>43</v>
+        <v>100</v>
+      </c>
+      <c r="P14" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="23">
+        <v>19</v>
+      </c>
+      <c r="R14" s="10">
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2125,55 +2113,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="L15" s="4">
-        <v>-29.2</v>
+        <v>-29.1</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="O15" s="9">
-        <v>70</v>
-      </c>
-      <c r="P15" s="8">
-        <v>8</v>
-      </c>
-      <c r="Q15" s="17">
-        <v>24</v>
-      </c>
-      <c r="R15" s="19">
-        <v>30</v>
+        <v>100</v>
+      </c>
+      <c r="P15" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>13</v>
+      </c>
+      <c r="R15" s="10">
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2181,7 +2169,7 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>53</v>
@@ -2190,34 +2178,34 @@
         <v>65</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="K16" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="L16" s="4">
+        <v>-15</v>
+      </c>
+      <c r="M16" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="L16" s="4">
-        <v>-8.4</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="N16" s="1" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="O16" s="9">
         <v>100</v>
@@ -2225,10 +2213,10 @@
       <c r="P16" s="7">
         <v>0</v>
       </c>
-      <c r="Q16" s="20">
-        <v>42</v>
-      </c>
-      <c r="R16" s="16">
+      <c r="Q16" s="16">
+        <v>60</v>
+      </c>
+      <c r="R16" s="10">
         <v>100</v>
       </c>
     </row>
@@ -2237,55 +2225,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="L17" s="4">
-        <v>-20.4</v>
+        <v>-25.2</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="O17" s="9">
-        <v>71</v>
-      </c>
-      <c r="P17" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="21">
-        <v>59</v>
-      </c>
-      <c r="R17" s="12">
-        <v>37</v>
+        <v>98</v>
+      </c>
+      <c r="P17" s="8">
+        <v>14</v>
+      </c>
+      <c r="Q17" s="22">
+        <v>46</v>
+      </c>
+      <c r="R17" s="24">
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2293,55 +2281,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L18" s="4">
-        <v>-28.1</v>
+        <v>-29.8</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="O18" s="9">
-        <v>66</v>
-      </c>
-      <c r="P18" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="12">
-        <v>34</v>
-      </c>
-      <c r="R18" s="18">
-        <v>47</v>
+        <v>96</v>
+      </c>
+      <c r="P18" s="8">
+        <v>16</v>
+      </c>
+      <c r="Q18" s="14">
+        <v>54</v>
+      </c>
+      <c r="R18" s="24">
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2349,55 +2337,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>87</v>
+        <v>195</v>
       </c>
       <c r="L19" s="4">
-        <v>-29.1</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="O19" s="9">
-        <v>77</v>
-      </c>
-      <c r="P19" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="17">
-        <v>24</v>
-      </c>
-      <c r="R19" s="11">
-        <v>65</v>
+        <v>54</v>
+      </c>
+      <c r="P19" s="20">
+        <v>35</v>
+      </c>
+      <c r="Q19" s="20">
+        <v>37</v>
+      </c>
+      <c r="R19" s="8">
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2405,7 +2393,7 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>57</v>
@@ -2414,46 +2402,46 @@
         <v>67</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="L20" s="4">
-        <v>-15</v>
+        <v>-20.9</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="O20" s="9">
-        <v>79</v>
-      </c>
-      <c r="P20" s="22">
-        <v>70</v>
-      </c>
-      <c r="Q20" s="22">
-        <v>70</v>
-      </c>
-      <c r="R20" s="21">
-        <v>62</v>
+        <v>48</v>
+      </c>
+      <c r="P20" s="25">
+        <v>30</v>
+      </c>
+      <c r="Q20" s="17">
+        <v>24</v>
+      </c>
+      <c r="R20" s="13">
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2461,55 +2449,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>183</v>
+        <v>117</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>203</v>
+        <v>87</v>
       </c>
       <c r="L21" s="4">
-        <v>-25.2</v>
+        <v>-28.7</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O21" s="9">
-        <v>57</v>
-      </c>
-      <c r="P21" s="23">
-        <v>48</v>
-      </c>
-      <c r="Q21" s="17">
-        <v>23</v>
-      </c>
-      <c r="R21" s="12">
-        <v>35</v>
+        <v>202</v>
+      </c>
+      <c r="O21" s="21">
+        <v>43</v>
+      </c>
+      <c r="P21" s="8">
+        <v>17</v>
+      </c>
+      <c r="Q21" s="8">
+        <v>13</v>
+      </c>
+      <c r="R21" s="13">
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2517,55 +2505,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>59</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>90</v>
+        <v>197</v>
       </c>
       <c r="L22" s="4">
-        <v>-29.8</v>
+        <v>-15.4</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O22" s="9">
-        <v>45</v>
-      </c>
-      <c r="P22" s="19">
-        <v>28</v>
-      </c>
-      <c r="Q22" s="7">
+        <v>203</v>
+      </c>
+      <c r="O22" s="21">
+        <v>35</v>
+      </c>
+      <c r="P22" s="8">
+        <v>13</v>
+      </c>
+      <c r="Q22" s="23">
+        <v>22</v>
+      </c>
+      <c r="R22" s="7">
         <v>0</v>
-      </c>
-      <c r="R22" s="14">
-        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2573,226 +2561,114 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>60</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="L23" s="4">
-        <v>-8.699999999999999</v>
+        <v>-25.8</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O23" s="9">
-        <v>76</v>
+        <v>202</v>
+      </c>
+      <c r="O23" s="21">
+        <v>14</v>
       </c>
       <c r="P23" s="12">
-        <v>37</v>
-      </c>
-      <c r="Q23" s="19">
-        <v>30</v>
-      </c>
-      <c r="R23" s="18">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18">
-      <c r="A24" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="2">
-        <v>30</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="L24" s="4">
-        <v>-20.9</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O24" s="9">
-        <v>74</v>
-      </c>
-      <c r="P24" s="8">
-        <v>9</v>
-      </c>
-      <c r="Q24" s="20">
-        <v>41</v>
-      </c>
-      <c r="R24" s="21">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18">
-      <c r="A25" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="2">
-        <v>20</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="L25" s="4">
-        <v>-28.7</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O25" s="9">
-        <v>94</v>
-      </c>
-      <c r="P25" s="14">
-        <v>5</v>
-      </c>
-      <c r="Q25" s="24">
-        <v>78</v>
-      </c>
-      <c r="R25" s="15">
-        <v>92</v>
+        <v>4</v>
+      </c>
+      <c r="Q23" s="13">
+        <v>8</v>
+      </c>
+      <c r="R23" s="7">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A25">
+  <conditionalFormatting sqref="A2:A23">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B25">
+  <conditionalFormatting sqref="B2:B23">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C25">
+  <conditionalFormatting sqref="C2:C23">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D25">
+  <conditionalFormatting sqref="D2:D23">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E25">
+  <conditionalFormatting sqref="E2:E23">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F25">
+  <conditionalFormatting sqref="F2:F23">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G25">
+  <conditionalFormatting sqref="G2:G23">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H25">
+  <conditionalFormatting sqref="H2:H23">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I25">
+  <conditionalFormatting sqref="I2:I23">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J25">
+  <conditionalFormatting sqref="J2:J23">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K25">
+  <conditionalFormatting sqref="K2:K23">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L25">
+  <conditionalFormatting sqref="L2:L23">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2811,12 +2687,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M25">
+  <conditionalFormatting sqref="M2:M23">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N25">
+  <conditionalFormatting sqref="N2:N23">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2833,22 +2709,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O25">
+  <conditionalFormatting sqref="O2:O23">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P25">
+  <conditionalFormatting sqref="P2:P23">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q25">
+  <conditionalFormatting sqref="Q2:Q23">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R25">
+  <conditionalFormatting sqref="R2:R23">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="208">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260824--01</t>
-  </si>
-  <si>
-    <t>20260824--02</t>
-  </si>
-  <si>
-    <t>20260824--03</t>
-  </si>
-  <si>
     <t>20260825--01</t>
   </si>
   <si>
@@ -136,97 +127,103 @@
     <t>20260830--02</t>
   </si>
   <si>
+    <t>20260831--01</t>
+  </si>
+  <si>
+    <t>20260831--02</t>
+  </si>
+  <si>
+    <t>20260831--03</t>
+  </si>
+  <si>
+    <t>04:24</t>
+  </si>
+  <si>
+    <t>05:10</t>
+  </si>
+  <si>
+    <t>05:56</t>
+  </si>
+  <si>
+    <t>05:03</t>
+  </si>
+  <si>
+    <t>04:33</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>05:29</t>
+  </si>
+  <si>
+    <t>03:32</t>
+  </si>
+  <si>
+    <t>05:48</t>
+  </si>
+  <si>
+    <t>05:44</t>
+  </si>
+  <si>
+    <t>02:58</t>
+  </si>
+  <si>
+    <t>05:34</t>
+  </si>
+  <si>
+    <t>05:52</t>
+  </si>
+  <si>
+    <t>04:15</t>
+  </si>
+  <si>
+    <t>05:12</t>
+  </si>
+  <si>
+    <t>04:58</t>
+  </si>
+  <si>
+    <t>05:54</t>
+  </si>
+  <si>
+    <t>05:26</t>
+  </si>
+  <si>
+    <t>05:42</t>
+  </si>
+  <si>
+    <t>02:46</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>01:07</t>
+  </si>
+  <si>
+    <t>03:04</t>
+  </si>
+  <si>
+    <t>00:28</t>
+  </si>
+  <si>
+    <t>02:41</t>
+  </si>
+  <si>
+    <t>04:41</t>
+  </si>
+  <si>
+    <t>01:09</t>
+  </si>
+  <si>
     <t>03:15</t>
   </si>
   <si>
-    <t>05:33</t>
-  </si>
-  <si>
-    <t>05:54</t>
-  </si>
-  <si>
-    <t>04:24</t>
-  </si>
-  <si>
-    <t>05:09</t>
-  </si>
-  <si>
-    <t>05:57</t>
-  </si>
-  <si>
-    <t>05:04</t>
-  </si>
-  <si>
-    <t>04:33</t>
-  </si>
-  <si>
-    <t>05:29</t>
-  </si>
-  <si>
-    <t>03:32</t>
-  </si>
-  <si>
-    <t>05:48</t>
-  </si>
-  <si>
-    <t>05:44</t>
-  </si>
-  <si>
-    <t>02:58</t>
-  </si>
-  <si>
-    <t>05:34</t>
-  </si>
-  <si>
-    <t>05:53</t>
-  </si>
-  <si>
-    <t>04:15</t>
-  </si>
-  <si>
-    <t>05:13</t>
-  </si>
-  <si>
-    <t>05:56</t>
-  </si>
-  <si>
-    <t>04:59</t>
-  </si>
-  <si>
-    <t>05:55</t>
-  </si>
-  <si>
-    <t>05:26</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>01:07</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>00:28</t>
-  </si>
-  <si>
-    <t>02:41</t>
-  </si>
-  <si>
-    <t>04:41</t>
-  </si>
-  <si>
-    <t>01:09</t>
-  </si>
-  <si>
-    <t>01:17:59</t>
-  </si>
-  <si>
-    <t>21:14:45</t>
-  </si>
-  <si>
-    <t>22:51:24</t>
+    <t>05:15</t>
+  </si>
+  <si>
+    <t>01:15</t>
   </si>
   <si>
     <t>00:28:28</t>
@@ -241,64 +238,64 @@
     <t>23:38:55</t>
   </si>
   <si>
-    <t>19:36:09</t>
-  </si>
-  <si>
-    <t>21:12:28</t>
-  </si>
-  <si>
-    <t>22:49:20</t>
-  </si>
-  <si>
-    <t>18:46:53</t>
-  </si>
-  <si>
-    <t>20:22:56</t>
-  </si>
-  <si>
-    <t>21:59:43</t>
-  </si>
-  <si>
-    <t>23:36:53</t>
-  </si>
-  <si>
-    <t>19:33:22</t>
-  </si>
-  <si>
-    <t>21:10:02</t>
-  </si>
-  <si>
-    <t>22:47:05</t>
-  </si>
-  <si>
-    <t>18:43:48</t>
-  </si>
-  <si>
-    <t>20:20:19</t>
-  </si>
-  <si>
-    <t>21:57:17</t>
-  </si>
-  <si>
-    <t>19:30:34</t>
-  </si>
-  <si>
-    <t>21:07:26</t>
-  </si>
-  <si>
-    <t>01:20:57</t>
-  </si>
-  <si>
-    <t>21:17:03</t>
-  </si>
-  <si>
-    <t>22:53:39</t>
+    <t>19:36:08</t>
+  </si>
+  <si>
+    <t>21:12:27</t>
+  </si>
+  <si>
+    <t>22:49:19</t>
+  </si>
+  <si>
+    <t>18:46:51</t>
+  </si>
+  <si>
+    <t>20:22:54</t>
+  </si>
+  <si>
+    <t>21:59:41</t>
+  </si>
+  <si>
+    <t>23:36:52</t>
+  </si>
+  <si>
+    <t>19:33:20</t>
+  </si>
+  <si>
+    <t>21:10:00</t>
+  </si>
+  <si>
+    <t>22:47:03</t>
+  </si>
+  <si>
+    <t>18:43:45</t>
+  </si>
+  <si>
+    <t>20:20:16</t>
+  </si>
+  <si>
+    <t>21:57:13</t>
+  </si>
+  <si>
+    <t>19:30:30</t>
+  </si>
+  <si>
+    <t>21:07:22</t>
+  </si>
+  <si>
+    <t>18:40:41</t>
+  </si>
+  <si>
+    <t>20:17:27</t>
+  </si>
+  <si>
+    <t>21:54:38</t>
   </si>
   <si>
     <t>00:31:04</t>
   </si>
   <si>
-    <t>20:27:51</t>
+    <t>20:27:50</t>
   </si>
   <si>
     <t>22:04:11</t>
@@ -307,244 +304,250 @@
     <t>23:41:21</t>
   </si>
   <si>
-    <t>19:38:42</t>
-  </si>
-  <si>
-    <t>21:14:42</t>
-  </si>
-  <si>
-    <t>22:51:40</t>
-  </si>
-  <si>
-    <t>18:49:43</t>
-  </si>
-  <si>
-    <t>20:25:11</t>
-  </si>
-  <si>
-    <t>22:01:59</t>
-  </si>
-  <si>
-    <t>23:39:56</t>
+    <t>19:38:41</t>
+  </si>
+  <si>
+    <t>21:14:41</t>
+  </si>
+  <si>
+    <t>22:51:39</t>
+  </si>
+  <si>
+    <t>18:49:42</t>
+  </si>
+  <si>
+    <t>20:25:10</t>
+  </si>
+  <si>
+    <t>22:01:58</t>
+  </si>
+  <si>
+    <t>23:39:55</t>
+  </si>
+  <si>
+    <t>19:35:39</t>
+  </si>
+  <si>
+    <t>21:12:15</t>
+  </si>
+  <si>
+    <t>22:49:42</t>
+  </si>
+  <si>
+    <t>18:46:09</t>
+  </si>
+  <si>
+    <t>20:22:30</t>
+  </si>
+  <si>
+    <t>19:32:44</t>
+  </si>
+  <si>
+    <t>21:09:42</t>
+  </si>
+  <si>
+    <t>18:42:56</t>
+  </si>
+  <si>
+    <t>20:19:44</t>
+  </si>
+  <si>
+    <t>21:57:44</t>
+  </si>
+  <si>
+    <t>00:33:16</t>
+  </si>
+  <si>
+    <t>20:30:25</t>
+  </si>
+  <si>
+    <t>22:07:09</t>
+  </si>
+  <si>
+    <t>23:43:52</t>
+  </si>
+  <si>
+    <t>19:40:58</t>
+  </si>
+  <si>
+    <t>21:17:38</t>
+  </si>
+  <si>
+    <t>22:54:24</t>
+  </si>
+  <si>
+    <t>18:51:28</t>
+  </si>
+  <si>
+    <t>20:28:04</t>
+  </si>
+  <si>
+    <t>22:04:50</t>
+  </si>
+  <si>
+    <t>23:41:24</t>
+  </si>
+  <si>
+    <t>19:38:26</t>
+  </si>
+  <si>
+    <t>21:15:11</t>
+  </si>
+  <si>
+    <t>22:51:50</t>
+  </si>
+  <si>
+    <t>18:48:45</t>
+  </si>
+  <si>
+    <t>20:25:28</t>
+  </si>
+  <si>
+    <t>22:02:10</t>
   </si>
   <si>
     <t>19:35:41</t>
   </si>
   <si>
-    <t>21:12:17</t>
-  </si>
-  <si>
-    <t>22:49:44</t>
-  </si>
-  <si>
-    <t>18:46:11</t>
-  </si>
-  <si>
-    <t>20:22:33</t>
-  </si>
-  <si>
-    <t>21:59:44</t>
-  </si>
-  <si>
-    <t>19:32:48</t>
-  </si>
-  <si>
-    <t>21:09:46</t>
-  </si>
-  <si>
-    <t>01:22:34</t>
-  </si>
-  <si>
-    <t>21:19:49</t>
+    <t>21:12:25</t>
+  </si>
+  <si>
+    <t>18:45:50</t>
+  </si>
+  <si>
+    <t>20:22:35</t>
+  </si>
+  <si>
+    <t>21:59:07</t>
+  </si>
+  <si>
+    <t>00:35:28</t>
+  </si>
+  <si>
+    <t>20:33:00</t>
+  </si>
+  <si>
+    <t>22:10:07</t>
+  </si>
+  <si>
+    <t>23:46:24</t>
+  </si>
+  <si>
+    <t>19:43:14</t>
+  </si>
+  <si>
+    <t>21:20:36</t>
+  </si>
+  <si>
+    <t>22:57:08</t>
+  </si>
+  <si>
+    <t>18:53:14</t>
+  </si>
+  <si>
+    <t>20:30:58</t>
+  </si>
+  <si>
+    <t>22:07:42</t>
+  </si>
+  <si>
+    <t>23:42:53</t>
+  </si>
+  <si>
+    <t>19:41:13</t>
+  </si>
+  <si>
+    <t>21:18:07</t>
+  </si>
+  <si>
+    <t>22:53:57</t>
+  </si>
+  <si>
+    <t>18:51:21</t>
+  </si>
+  <si>
+    <t>20:28:26</t>
+  </si>
+  <si>
+    <t>22:04:39</t>
+  </si>
+  <si>
+    <t>19:38:38</t>
+  </si>
+  <si>
+    <t>21:15:08</t>
+  </si>
+  <si>
+    <t>18:48:44</t>
+  </si>
+  <si>
+    <t>22:00:30</t>
+  </si>
+  <si>
+    <t>00:38:05</t>
+  </si>
+  <si>
+    <t>20:35:25</t>
+  </si>
+  <si>
+    <t>22:12:22</t>
+  </si>
+  <si>
+    <t>23:48:51</t>
+  </si>
+  <si>
+    <t>19:45:48</t>
+  </si>
+  <si>
+    <t>21:22:50</t>
+  </si>
+  <si>
+    <t>22:59:28</t>
+  </si>
+  <si>
+    <t>18:56:05</t>
+  </si>
+  <si>
+    <t>20:33:14</t>
+  </si>
+  <si>
+    <t>22:09:58</t>
+  </si>
+  <si>
+    <t>23:45:55</t>
+  </si>
+  <si>
+    <t>19:43:32</t>
+  </si>
+  <si>
+    <t>21:20:22</t>
   </si>
   <si>
     <t>22:56:36</t>
   </si>
   <si>
-    <t>00:33:16</t>
-  </si>
-  <si>
-    <t>20:30:25</t>
-  </si>
-  <si>
-    <t>22:07:10</t>
-  </si>
-  <si>
-    <t>23:43:53</t>
-  </si>
-  <si>
-    <t>19:40:58</t>
-  </si>
-  <si>
-    <t>21:17:39</t>
-  </si>
-  <si>
-    <t>22:54:24</t>
-  </si>
-  <si>
-    <t>18:51:29</t>
-  </si>
-  <si>
-    <t>20:28:05</t>
-  </si>
-  <si>
-    <t>22:04:51</t>
-  </si>
-  <si>
-    <t>23:41:25</t>
-  </si>
-  <si>
-    <t>19:38:28</t>
-  </si>
-  <si>
-    <t>21:15:13</t>
-  </si>
-  <si>
-    <t>22:51:52</t>
-  </si>
-  <si>
-    <t>18:48:48</t>
-  </si>
-  <si>
-    <t>20:25:31</t>
-  </si>
-  <si>
-    <t>22:02:13</t>
-  </si>
-  <si>
-    <t>19:35:45</t>
-  </si>
-  <si>
-    <t>21:12:29</t>
-  </si>
-  <si>
-    <t>01:24:12</t>
-  </si>
-  <si>
-    <t>21:22:36</t>
-  </si>
-  <si>
-    <t>22:59:33</t>
-  </si>
-  <si>
-    <t>00:35:28</t>
-  </si>
-  <si>
-    <t>20:33:00</t>
-  </si>
-  <si>
-    <t>22:10:08</t>
-  </si>
-  <si>
-    <t>23:46:25</t>
-  </si>
-  <si>
-    <t>19:43:15</t>
-  </si>
-  <si>
-    <t>21:20:36</t>
-  </si>
-  <si>
-    <t>22:57:09</t>
-  </si>
-  <si>
-    <t>18:53:15</t>
-  </si>
-  <si>
-    <t>20:30:59</t>
-  </si>
-  <si>
-    <t>22:07:43</t>
-  </si>
-  <si>
-    <t>23:42:54</t>
-  </si>
-  <si>
-    <t>19:41:15</t>
-  </si>
-  <si>
-    <t>21:18:10</t>
-  </si>
-  <si>
-    <t>22:53:59</t>
-  </si>
-  <si>
-    <t>18:51:24</t>
-  </si>
-  <si>
-    <t>20:28:29</t>
-  </si>
-  <si>
-    <t>22:04:43</t>
-  </si>
-  <si>
-    <t>19:38:43</t>
-  </si>
-  <si>
-    <t>21:15:12</t>
-  </si>
-  <si>
-    <t>01:27:09</t>
-  </si>
-  <si>
-    <t>21:24:56</t>
-  </si>
-  <si>
-    <t>23:01:48</t>
-  </si>
-  <si>
-    <t>00:38:05</t>
-  </si>
-  <si>
-    <t>20:35:25</t>
-  </si>
-  <si>
-    <t>22:12:22</t>
-  </si>
-  <si>
-    <t>23:48:51</t>
-  </si>
-  <si>
-    <t>19:45:49</t>
-  </si>
-  <si>
-    <t>21:22:51</t>
-  </si>
-  <si>
-    <t>22:59:29</t>
-  </si>
-  <si>
-    <t>18:56:07</t>
-  </si>
-  <si>
-    <t>20:33:15</t>
-  </si>
-  <si>
-    <t>22:10:00</t>
-  </si>
-  <si>
-    <t>23:45:56</t>
-  </si>
-  <si>
-    <t>19:43:34</t>
-  </si>
-  <si>
-    <t>21:20:24</t>
-  </si>
-  <si>
-    <t>22:56:38</t>
-  </si>
-  <si>
-    <t>18:53:48</t>
-  </si>
-  <si>
-    <t>20:30:43</t>
-  </si>
-  <si>
-    <t>19:40:57</t>
-  </si>
-  <si>
-    <t>21:17:33</t>
+    <t>18:53:45</t>
+  </si>
+  <si>
+    <t>20:30:40</t>
+  </si>
+  <si>
+    <t>22:07:06</t>
+  </si>
+  <si>
+    <t>19:40:53</t>
+  </si>
+  <si>
+    <t>21:17:29</t>
+  </si>
+  <si>
+    <t>18:51:00</t>
+  </si>
+  <si>
+    <t>20:27:43</t>
+  </si>
+  <si>
+    <t>22:03:36</t>
   </si>
   <si>
     <t>0°</t>
@@ -580,37 +583,46 @@
     <t>6°</t>
   </si>
   <si>
+    <t>14°</t>
+  </si>
+  <si>
     <t>20:26:31</t>
   </si>
   <si>
-    <t>19:39:49</t>
-  </si>
-  <si>
-    <t>21:12:41</t>
-  </si>
-  <si>
-    <t>18:52:48</t>
-  </si>
-  <si>
-    <t>20:25:39</t>
-  </si>
-  <si>
-    <t>19:38:22</t>
-  </si>
-  <si>
-    <t>21:11:12</t>
-  </si>
-  <si>
-    <t>18:50:52</t>
-  </si>
-  <si>
-    <t>20:23:42</t>
-  </si>
-  <si>
-    <t>19:36:03</t>
-  </si>
-  <si>
-    <t>21:08:52</t>
+    <t>19:39:48</t>
+  </si>
+  <si>
+    <t>21:12:40</t>
+  </si>
+  <si>
+    <t>18:52:46</t>
+  </si>
+  <si>
+    <t>20:25:38</t>
+  </si>
+  <si>
+    <t>19:38:20</t>
+  </si>
+  <si>
+    <t>21:11:10</t>
+  </si>
+  <si>
+    <t>18:50:50</t>
+  </si>
+  <si>
+    <t>20:23:39</t>
+  </si>
+  <si>
+    <t>19:35:59</t>
+  </si>
+  <si>
+    <t>21:08:48</t>
+  </si>
+  <si>
+    <t>18:48:11</t>
+  </si>
+  <si>
+    <t>20:20:59</t>
   </si>
   <si>
     <t>B</t>
@@ -619,13 +631,13 @@
     <t>A+B</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
 </sst>
 </file>
@@ -659,7 +671,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -674,7 +686,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -686,13 +698,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -704,7 +710,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -716,79 +770,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -829,7 +817,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -892,18 +880,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1385,55 +1361,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>156</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L2" s="4">
-        <v>-21.5</v>
+        <v>-25.7</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="O2" s="6">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
       <c r="Q2" s="8">
-        <v>14</v>
-      </c>
-      <c r="R2" s="7">
-        <v>0</v>
+        <v>59</v>
+      </c>
+      <c r="R2" s="9">
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1441,55 +1417,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>41</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>157</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>69</v>
+        <v>190</v>
       </c>
       <c r="L3" s="4">
-        <v>-24.2</v>
+        <v>-20</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O3" s="9">
-        <v>100</v>
-      </c>
-      <c r="P3" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="7">
-        <v>0</v>
-      </c>
-      <c r="R3" s="10">
-        <v>100</v>
+        <v>205</v>
+      </c>
+      <c r="O3" s="6">
+        <v>99</v>
+      </c>
+      <c r="P3" s="10">
+        <v>8</v>
+      </c>
+      <c r="Q3" s="11">
+        <v>92</v>
+      </c>
+      <c r="R3" s="11">
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1503,49 +1479,49 @@
         <v>42</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>158</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L4" s="4">
-        <v>-28.5</v>
+        <v>-27.5</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O4" s="9">
-        <v>84</v>
-      </c>
-      <c r="P4" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="7">
-        <v>0</v>
-      </c>
-      <c r="R4" s="11">
-        <v>81</v>
+        <v>205</v>
+      </c>
+      <c r="O4" s="6">
+        <v>99</v>
+      </c>
+      <c r="P4" s="12">
+        <v>46</v>
+      </c>
+      <c r="Q4" s="13">
+        <v>97</v>
+      </c>
+      <c r="R4" s="14">
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1553,55 +1529,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>159</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L5" s="4">
-        <v>-25.7</v>
+        <v>-28.3</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="O5" s="6">
-        <v>5</v>
-      </c>
-      <c r="P5" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>0</v>
-      </c>
-      <c r="R5" s="12">
-        <v>4</v>
+        <v>97</v>
+      </c>
+      <c r="P5" s="14">
+        <v>49</v>
+      </c>
+      <c r="Q5" s="13">
+        <v>93</v>
+      </c>
+      <c r="R5" s="11">
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1609,7 +1585,7 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>44</v>
@@ -1618,46 +1594,46 @@
         <v>61</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>160</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L6" s="4">
-        <v>-20</v>
+        <v>-14.6</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O6" s="9">
-        <v>100</v>
-      </c>
-      <c r="P6" s="13">
-        <v>10</v>
-      </c>
-      <c r="Q6" s="14">
+        <v>206</v>
+      </c>
+      <c r="O6" s="6">
         <v>55</v>
       </c>
-      <c r="R6" s="10">
-        <v>100</v>
+      <c r="P6" s="15">
+        <v>19</v>
+      </c>
+      <c r="Q6" s="16">
+        <v>31</v>
+      </c>
+      <c r="R6" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1671,49 +1647,49 @@
         <v>45</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>161</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="L7" s="4">
-        <v>-27.5</v>
+        <v>-24.7</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O7" s="9">
-        <v>100</v>
-      </c>
-      <c r="P7" s="8">
-        <v>17</v>
-      </c>
-      <c r="Q7" s="15">
-        <v>69</v>
-      </c>
-      <c r="R7" s="10">
-        <v>100</v>
+        <v>205</v>
+      </c>
+      <c r="O7" s="6">
+        <v>95</v>
+      </c>
+      <c r="P7" s="17">
+        <v>14</v>
+      </c>
+      <c r="Q7" s="18">
+        <v>38</v>
+      </c>
+      <c r="R7" s="18">
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1721,55 +1697,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>162</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L8" s="4">
-        <v>-28.3</v>
+        <v>-29.2</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O8" s="9">
-        <v>100</v>
-      </c>
-      <c r="P8" s="8">
-        <v>16</v>
-      </c>
-      <c r="Q8" s="16">
-        <v>61</v>
-      </c>
-      <c r="R8" s="11">
-        <v>80</v>
+        <v>205</v>
+      </c>
+      <c r="O8" s="6">
+        <v>96</v>
+      </c>
+      <c r="P8" s="17">
+        <v>13</v>
+      </c>
+      <c r="Q8" s="18">
+        <v>40</v>
+      </c>
+      <c r="R8" s="12">
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1777,7 +1753,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>47</v>
@@ -1786,46 +1762,46 @@
         <v>62</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>163</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="L9" s="4">
-        <v>-14.6</v>
+        <v>-8.4</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O9" s="9">
-        <v>97</v>
+        <v>207</v>
+      </c>
+      <c r="O9" s="6">
+        <v>68</v>
       </c>
       <c r="P9" s="17">
-        <v>25</v>
-      </c>
-      <c r="Q9" s="16">
-        <v>61</v>
-      </c>
-      <c r="R9" s="18">
-        <v>92</v>
+        <v>15</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>0</v>
+      </c>
+      <c r="R9" s="8">
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1833,55 +1809,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>164</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="L10" s="4">
-        <v>-24.7</v>
+        <v>-20.4</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O10" s="9">
-        <v>60</v>
-      </c>
-      <c r="P10" s="19">
-        <v>40</v>
-      </c>
-      <c r="Q10" s="17">
-        <v>27</v>
-      </c>
-      <c r="R10" s="12">
-        <v>4</v>
+        <v>206</v>
+      </c>
+      <c r="O10" s="6">
+        <v>100</v>
+      </c>
+      <c r="P10" s="10">
+        <v>9</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>1</v>
+      </c>
+      <c r="R10" s="9">
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1889,55 +1865,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>165</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L11" s="4">
-        <v>-29.2</v>
+        <v>-28.1</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O11" s="9">
-        <v>62</v>
-      </c>
-      <c r="P11" s="20">
-        <v>37</v>
-      </c>
-      <c r="Q11" s="17">
-        <v>23</v>
-      </c>
-      <c r="R11" s="13">
-        <v>11</v>
+        <v>205</v>
+      </c>
+      <c r="O11" s="6">
+        <v>100</v>
+      </c>
+      <c r="P11" s="19">
+        <v>4</v>
+      </c>
+      <c r="Q11" s="19">
+        <v>5</v>
+      </c>
+      <c r="R11" s="9">
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1945,55 +1921,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>166</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>191</v>
+        <v>80</v>
       </c>
       <c r="L12" s="4">
-        <v>-8.4</v>
+        <v>-29.1</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O12" s="21">
-        <v>44</v>
+        <v>207</v>
+      </c>
+      <c r="O12" s="6">
+        <v>100</v>
       </c>
       <c r="P12" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="7">
-        <v>0</v>
-      </c>
-      <c r="R12" s="17">
-        <v>23</v>
+        <v>2</v>
+      </c>
+      <c r="Q12" s="17">
+        <v>16</v>
+      </c>
+      <c r="R12" s="9">
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2001,55 +1977,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>64</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>167</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="L13" s="4">
-        <v>-20.4</v>
+        <v>-15</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O13" s="9">
+        <v>206</v>
+      </c>
+      <c r="O13" s="6">
+        <v>100</v>
+      </c>
+      <c r="P13" s="15">
+        <v>21</v>
+      </c>
+      <c r="Q13" s="20">
         <v>65</v>
       </c>
-      <c r="P13" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="12">
-        <v>7</v>
-      </c>
-      <c r="R13" s="22">
-        <v>46</v>
+      <c r="R13" s="9">
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2057,55 +2033,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>168</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>80</v>
+        <v>196</v>
       </c>
       <c r="L14" s="4">
-        <v>-28.1</v>
+        <v>-25.2</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O14" s="9">
-        <v>100</v>
-      </c>
-      <c r="P14" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="23">
-        <v>19</v>
-      </c>
-      <c r="R14" s="10">
-        <v>100</v>
+        <v>205</v>
+      </c>
+      <c r="O14" s="6">
+        <v>84</v>
+      </c>
+      <c r="P14" s="17">
+        <v>14</v>
+      </c>
+      <c r="Q14" s="16">
+        <v>30</v>
+      </c>
+      <c r="R14" s="8">
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2113,55 +2089,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>169</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L15" s="4">
-        <v>-29.1</v>
+        <v>-29.8</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O15" s="9">
-        <v>100</v>
-      </c>
-      <c r="P15" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="8">
-        <v>13</v>
-      </c>
-      <c r="R15" s="10">
-        <v>100</v>
+        <v>205</v>
+      </c>
+      <c r="O15" s="6">
+        <v>78</v>
+      </c>
+      <c r="P15" s="17">
+        <v>16</v>
+      </c>
+      <c r="Q15" s="15">
+        <v>18</v>
+      </c>
+      <c r="R15" s="12">
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2169,25 +2145,25 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>65</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>170</v>
@@ -2196,28 +2172,28 @@
         <v>183</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="L16" s="4">
-        <v>-15</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O16" s="9">
-        <v>100</v>
-      </c>
-      <c r="P16" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="16">
-        <v>60</v>
-      </c>
-      <c r="R16" s="10">
-        <v>100</v>
+        <v>206</v>
+      </c>
+      <c r="O16" s="6">
+        <v>36</v>
+      </c>
+      <c r="P16" s="15">
+        <v>22</v>
+      </c>
+      <c r="Q16" s="17">
+        <v>16</v>
+      </c>
+      <c r="R16" s="17">
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2225,55 +2201,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>171</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="L17" s="4">
-        <v>-25.2</v>
+        <v>-20.9</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O17" s="9">
-        <v>98</v>
-      </c>
-      <c r="P17" s="8">
+        <v>206</v>
+      </c>
+      <c r="O17" s="6">
+        <v>35</v>
+      </c>
+      <c r="P17" s="15">
+        <v>19</v>
+      </c>
+      <c r="Q17" s="10">
+        <v>10</v>
+      </c>
+      <c r="R17" s="17">
         <v>14</v>
-      </c>
-      <c r="Q17" s="22">
-        <v>46</v>
-      </c>
-      <c r="R17" s="24">
-        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2281,55 +2257,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>172</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L18" s="4">
-        <v>-29.8</v>
+        <v>-28.7</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O18" s="9">
-        <v>96</v>
-      </c>
-      <c r="P18" s="8">
-        <v>16</v>
-      </c>
-      <c r="Q18" s="14">
-        <v>54</v>
-      </c>
-      <c r="R18" s="24">
-        <v>95</v>
+        <v>205</v>
+      </c>
+      <c r="O18" s="6">
+        <v>64</v>
+      </c>
+      <c r="P18" s="17">
+        <v>13</v>
+      </c>
+      <c r="Q18" s="7">
+        <v>2</v>
+      </c>
+      <c r="R18" s="20">
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2337,55 +2313,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>173</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="L19" s="4">
-        <v>-8.699999999999999</v>
+        <v>-15.4</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O19" s="9">
-        <v>54</v>
+        <v>206</v>
+      </c>
+      <c r="O19" s="6">
+        <v>81</v>
       </c>
       <c r="P19" s="20">
-        <v>35</v>
-      </c>
-      <c r="Q19" s="20">
-        <v>37</v>
-      </c>
-      <c r="R19" s="8">
-        <v>15</v>
+        <v>64</v>
+      </c>
+      <c r="Q19" s="19">
+        <v>7</v>
+      </c>
+      <c r="R19" s="12">
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2393,55 +2369,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>174</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="L20" s="4">
-        <v>-20.9</v>
+        <v>-25.8</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O20" s="9">
-        <v>48</v>
-      </c>
-      <c r="P20" s="25">
-        <v>30</v>
-      </c>
-      <c r="Q20" s="17">
-        <v>24</v>
-      </c>
-      <c r="R20" s="13">
-        <v>10</v>
+        <v>205</v>
+      </c>
+      <c r="O20" s="6">
+        <v>93</v>
+      </c>
+      <c r="P20" s="8">
+        <v>58</v>
+      </c>
+      <c r="Q20" s="19">
+        <v>3</v>
+      </c>
+      <c r="R20" s="21">
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2449,55 +2425,43 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>117</v>
+        <v>175</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>87</v>
+        <v>201</v>
       </c>
       <c r="L21" s="4">
-        <v>-28.7</v>
+        <v>-8.9</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O21" s="21">
-        <v>43</v>
-      </c>
-      <c r="P21" s="8">
-        <v>17</v>
-      </c>
-      <c r="Q21" s="8">
-        <v>13</v>
-      </c>
-      <c r="R21" s="13">
-        <v>9</v>
+        <v>206</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2505,55 +2469,43 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>154</v>
+        <v>71</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>186</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="L22" s="4">
-        <v>-15.4</v>
+        <v>-21.3</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O22" s="21">
-        <v>35</v>
-      </c>
-      <c r="P22" s="8">
-        <v>13</v>
-      </c>
-      <c r="Q22" s="23">
-        <v>22</v>
-      </c>
-      <c r="R22" s="7">
-        <v>0</v>
+        <v>206</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2561,55 +2513,43 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="E23" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>155</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>198</v>
+        <v>91</v>
       </c>
       <c r="L23" s="4">
-        <v>-25.8</v>
+        <v>-29.3</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O23" s="21">
-        <v>14</v>
-      </c>
-      <c r="P23" s="12">
-        <v>4</v>
-      </c>
-      <c r="Q23" s="13">
-        <v>8</v>
-      </c>
-      <c r="R23" s="7">
-        <v>1</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="197">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260825--01</t>
-  </si>
-  <si>
-    <t>20260825--02</t>
-  </si>
-  <si>
-    <t>20260825--03</t>
-  </si>
-  <si>
-    <t>20260825--04</t>
-  </si>
-  <si>
     <t>20260826--01</t>
   </si>
   <si>
@@ -136,76 +124,79 @@
     <t>20260831--03</t>
   </si>
   <si>
-    <t>04:24</t>
-  </si>
-  <si>
-    <t>05:10</t>
+    <t>20260901--01</t>
+  </si>
+  <si>
+    <t>20260901--02</t>
+  </si>
+  <si>
+    <t>04:33</t>
+  </si>
+  <si>
+    <t>05:54</t>
+  </si>
+  <si>
+    <t>05:28</t>
+  </si>
+  <si>
+    <t>03:31</t>
+  </si>
+  <si>
+    <t>05:47</t>
+  </si>
+  <si>
+    <t>05:43</t>
+  </si>
+  <si>
+    <t>02:58</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>05:52</t>
+  </si>
+  <si>
+    <t>04:15</t>
+  </si>
+  <si>
+    <t>05:13</t>
   </si>
   <si>
     <t>05:56</t>
   </si>
   <si>
-    <t>05:03</t>
-  </si>
-  <si>
-    <t>04:33</t>
-  </si>
-  <si>
-    <t>05:55</t>
-  </si>
-  <si>
-    <t>05:29</t>
-  </si>
-  <si>
-    <t>03:32</t>
-  </si>
-  <si>
-    <t>05:48</t>
-  </si>
-  <si>
-    <t>05:44</t>
-  </si>
-  <si>
-    <t>02:58</t>
-  </si>
-  <si>
-    <t>05:34</t>
-  </si>
-  <si>
-    <t>05:52</t>
-  </si>
-  <si>
-    <t>04:15</t>
-  </si>
-  <si>
-    <t>05:12</t>
-  </si>
-  <si>
-    <t>04:58</t>
-  </si>
-  <si>
-    <t>05:54</t>
+    <t>04:59</t>
   </si>
   <si>
     <t>05:26</t>
   </si>
   <si>
+    <t>05:49</t>
+  </si>
+  <si>
     <t>05:42</t>
   </si>
   <si>
-    <t>02:46</t>
+    <t>02:47</t>
+  </si>
+  <si>
+    <t>05:51</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>01:06</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:07</t>
-  </si>
-  <si>
     <t>03:04</t>
   </si>
   <si>
-    <t>00:28</t>
+    <t>00:27</t>
   </si>
   <si>
     <t>02:41</t>
@@ -223,345 +214,318 @@
     <t>05:15</t>
   </si>
   <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>00:28:28</t>
-  </si>
-  <si>
-    <t>20:25:26</t>
+    <t>01:16</t>
+  </si>
+  <si>
+    <t>03:20</t>
+  </si>
+  <si>
+    <t>19:36:07</t>
+  </si>
+  <si>
+    <t>21:12:26</t>
+  </si>
+  <si>
+    <t>22:49:19</t>
+  </si>
+  <si>
+    <t>18:46:50</t>
+  </si>
+  <si>
+    <t>20:22:53</t>
+  </si>
+  <si>
+    <t>21:59:40</t>
+  </si>
+  <si>
+    <t>23:36:51</t>
+  </si>
+  <si>
+    <t>19:33:18</t>
+  </si>
+  <si>
+    <t>21:09:58</t>
+  </si>
+  <si>
+    <t>22:47:01</t>
+  </si>
+  <si>
+    <t>18:43:42</t>
+  </si>
+  <si>
+    <t>20:20:13</t>
+  </si>
+  <si>
+    <t>21:57:10</t>
+  </si>
+  <si>
+    <t>19:30:25</t>
+  </si>
+  <si>
+    <t>21:07:16</t>
+  </si>
+  <si>
+    <t>18:40:34</t>
+  </si>
+  <si>
+    <t>20:17:20</t>
+  </si>
+  <si>
+    <t>21:54:31</t>
+  </si>
+  <si>
+    <t>19:27:21</t>
+  </si>
+  <si>
+    <t>21:04:23</t>
+  </si>
+  <si>
+    <t>19:38:41</t>
+  </si>
+  <si>
+    <t>21:14:41</t>
+  </si>
+  <si>
+    <t>22:51:39</t>
+  </si>
+  <si>
+    <t>18:49:41</t>
+  </si>
+  <si>
+    <t>20:25:09</t>
   </si>
   <si>
     <t>22:01:57</t>
   </si>
   <si>
-    <t>23:38:55</t>
-  </si>
-  <si>
-    <t>19:36:08</t>
-  </si>
-  <si>
-    <t>21:12:27</t>
-  </si>
-  <si>
-    <t>22:49:19</t>
-  </si>
-  <si>
-    <t>18:46:51</t>
-  </si>
-  <si>
-    <t>20:22:54</t>
-  </si>
-  <si>
-    <t>21:59:41</t>
-  </si>
-  <si>
-    <t>23:36:52</t>
-  </si>
-  <si>
-    <t>19:33:20</t>
-  </si>
-  <si>
-    <t>21:10:00</t>
-  </si>
-  <si>
-    <t>22:47:03</t>
-  </si>
-  <si>
-    <t>18:43:45</t>
-  </si>
-  <si>
-    <t>20:20:16</t>
-  </si>
-  <si>
-    <t>21:57:13</t>
-  </si>
-  <si>
-    <t>19:30:30</t>
-  </si>
-  <si>
-    <t>21:07:22</t>
-  </si>
-  <si>
-    <t>18:40:41</t>
-  </si>
-  <si>
-    <t>20:17:27</t>
-  </si>
-  <si>
-    <t>21:54:38</t>
-  </si>
-  <si>
-    <t>00:31:04</t>
-  </si>
-  <si>
-    <t>20:27:50</t>
-  </si>
-  <si>
-    <t>22:04:11</t>
-  </si>
-  <si>
-    <t>23:41:21</t>
-  </si>
-  <si>
-    <t>19:38:41</t>
-  </si>
-  <si>
-    <t>21:14:41</t>
-  </si>
-  <si>
-    <t>22:51:39</t>
-  </si>
-  <si>
-    <t>18:49:42</t>
-  </si>
-  <si>
-    <t>20:25:10</t>
-  </si>
-  <si>
-    <t>22:01:58</t>
-  </si>
-  <si>
-    <t>23:39:55</t>
-  </si>
-  <si>
-    <t>19:35:39</t>
-  </si>
-  <si>
-    <t>21:12:15</t>
-  </si>
-  <si>
-    <t>22:49:42</t>
-  </si>
-  <si>
-    <t>18:46:09</t>
-  </si>
-  <si>
-    <t>20:22:30</t>
-  </si>
-  <si>
-    <t>19:32:44</t>
-  </si>
-  <si>
-    <t>21:09:42</t>
-  </si>
-  <si>
-    <t>18:42:56</t>
-  </si>
-  <si>
-    <t>20:19:44</t>
-  </si>
-  <si>
-    <t>21:57:44</t>
-  </si>
-  <si>
-    <t>00:33:16</t>
-  </si>
-  <si>
-    <t>20:30:25</t>
-  </si>
-  <si>
-    <t>22:07:09</t>
-  </si>
-  <si>
-    <t>23:43:52</t>
-  </si>
-  <si>
-    <t>19:40:58</t>
+    <t>23:39:53</t>
+  </si>
+  <si>
+    <t>19:35:36</t>
+  </si>
+  <si>
+    <t>21:12:13</t>
+  </si>
+  <si>
+    <t>22:49:40</t>
+  </si>
+  <si>
+    <t>18:46:05</t>
+  </si>
+  <si>
+    <t>20:22:27</t>
+  </si>
+  <si>
+    <t>21:59:37</t>
+  </si>
+  <si>
+    <t>19:32:39</t>
+  </si>
+  <si>
+    <t>21:09:37</t>
+  </si>
+  <si>
+    <t>18:42:49</t>
+  </si>
+  <si>
+    <t>20:19:37</t>
+  </si>
+  <si>
+    <t>21:57:37</t>
+  </si>
+  <si>
+    <t>19:29:36</t>
+  </si>
+  <si>
+    <t>21:07:03</t>
+  </si>
+  <si>
+    <t>19:40:57</t>
   </si>
   <si>
     <t>21:17:38</t>
   </si>
   <si>
-    <t>22:54:24</t>
-  </si>
-  <si>
-    <t>18:51:28</t>
-  </si>
-  <si>
-    <t>20:28:04</t>
-  </si>
-  <si>
-    <t>22:04:50</t>
-  </si>
-  <si>
-    <t>23:41:24</t>
-  </si>
-  <si>
-    <t>19:38:26</t>
-  </si>
-  <si>
-    <t>21:15:11</t>
-  </si>
-  <si>
-    <t>22:51:50</t>
-  </si>
-  <si>
-    <t>18:48:45</t>
-  </si>
-  <si>
-    <t>20:25:28</t>
-  </si>
-  <si>
-    <t>22:02:10</t>
-  </si>
-  <si>
-    <t>19:35:41</t>
-  </si>
-  <si>
-    <t>21:12:25</t>
-  </si>
-  <si>
-    <t>18:45:50</t>
-  </si>
-  <si>
-    <t>20:22:35</t>
-  </si>
-  <si>
-    <t>21:59:07</t>
-  </si>
-  <si>
-    <t>00:35:28</t>
-  </si>
-  <si>
-    <t>20:33:00</t>
-  </si>
-  <si>
-    <t>22:10:07</t>
-  </si>
-  <si>
-    <t>23:46:24</t>
+    <t>22:54:23</t>
+  </si>
+  <si>
+    <t>18:51:27</t>
+  </si>
+  <si>
+    <t>20:28:02</t>
+  </si>
+  <si>
+    <t>22:04:48</t>
+  </si>
+  <si>
+    <t>23:41:22</t>
+  </si>
+  <si>
+    <t>19:38:24</t>
+  </si>
+  <si>
+    <t>21:15:09</t>
+  </si>
+  <si>
+    <t>22:51:47</t>
+  </si>
+  <si>
+    <t>18:48:41</t>
+  </si>
+  <si>
+    <t>20:25:24</t>
+  </si>
+  <si>
+    <t>22:02:06</t>
+  </si>
+  <si>
+    <t>21:12:20</t>
+  </si>
+  <si>
+    <t>18:45:43</t>
+  </si>
+  <si>
+    <t>20:22:28</t>
+  </si>
+  <si>
+    <t>21:59:00</t>
+  </si>
+  <si>
+    <t>19:32:31</t>
+  </si>
+  <si>
+    <t>21:09:08</t>
   </si>
   <si>
     <t>19:43:14</t>
   </si>
   <si>
-    <t>21:20:36</t>
-  </si>
-  <si>
-    <t>22:57:08</t>
-  </si>
-  <si>
-    <t>18:53:14</t>
-  </si>
-  <si>
-    <t>20:30:58</t>
-  </si>
-  <si>
-    <t>22:07:42</t>
-  </si>
-  <si>
-    <t>23:42:53</t>
-  </si>
-  <si>
-    <t>19:41:13</t>
-  </si>
-  <si>
-    <t>21:18:07</t>
-  </si>
-  <si>
-    <t>22:53:57</t>
-  </si>
-  <si>
-    <t>18:51:21</t>
-  </si>
-  <si>
-    <t>20:28:26</t>
-  </si>
-  <si>
-    <t>22:04:39</t>
-  </si>
-  <si>
-    <t>19:38:38</t>
-  </si>
-  <si>
-    <t>21:15:08</t>
-  </si>
-  <si>
-    <t>18:48:44</t>
-  </si>
-  <si>
-    <t>22:00:30</t>
-  </si>
-  <si>
-    <t>00:38:05</t>
-  </si>
-  <si>
-    <t>20:35:25</t>
-  </si>
-  <si>
-    <t>22:12:22</t>
-  </si>
-  <si>
-    <t>23:48:51</t>
+    <t>21:20:35</t>
+  </si>
+  <si>
+    <t>22:57:07</t>
+  </si>
+  <si>
+    <t>18:53:12</t>
+  </si>
+  <si>
+    <t>20:30:56</t>
+  </si>
+  <si>
+    <t>22:07:40</t>
+  </si>
+  <si>
+    <t>23:42:51</t>
+  </si>
+  <si>
+    <t>19:41:11</t>
+  </si>
+  <si>
+    <t>21:18:05</t>
+  </si>
+  <si>
+    <t>22:53:55</t>
+  </si>
+  <si>
+    <t>18:51:18</t>
+  </si>
+  <si>
+    <t>20:28:23</t>
+  </si>
+  <si>
+    <t>22:04:36</t>
+  </si>
+  <si>
+    <t>19:38:33</t>
+  </si>
+  <si>
+    <t>21:15:03</t>
+  </si>
+  <si>
+    <t>18:48:38</t>
+  </si>
+  <si>
+    <t>20:25:19</t>
+  </si>
+  <si>
+    <t>22:00:24</t>
+  </si>
+  <si>
+    <t>19:35:27</t>
+  </si>
+  <si>
+    <t>21:11:13</t>
   </si>
   <si>
     <t>19:45:48</t>
   </si>
   <si>
-    <t>21:22:50</t>
-  </si>
-  <si>
-    <t>22:59:28</t>
-  </si>
-  <si>
-    <t>18:56:05</t>
-  </si>
-  <si>
-    <t>20:33:14</t>
-  </si>
-  <si>
-    <t>22:09:58</t>
-  </si>
-  <si>
-    <t>23:45:55</t>
-  </si>
-  <si>
-    <t>19:43:32</t>
-  </si>
-  <si>
-    <t>21:20:22</t>
-  </si>
-  <si>
-    <t>22:56:36</t>
-  </si>
-  <si>
-    <t>18:53:45</t>
-  </si>
-  <si>
-    <t>20:30:40</t>
-  </si>
-  <si>
-    <t>22:07:06</t>
-  </si>
-  <si>
-    <t>19:40:53</t>
-  </si>
-  <si>
-    <t>21:17:29</t>
-  </si>
-  <si>
-    <t>18:51:00</t>
-  </si>
-  <si>
-    <t>20:27:43</t>
-  </si>
-  <si>
-    <t>22:03:36</t>
+    <t>21:22:49</t>
+  </si>
+  <si>
+    <t>22:59:27</t>
+  </si>
+  <si>
+    <t>18:56:04</t>
+  </si>
+  <si>
+    <t>20:33:12</t>
+  </si>
+  <si>
+    <t>22:09:57</t>
+  </si>
+  <si>
+    <t>23:45:53</t>
+  </si>
+  <si>
+    <t>19:43:30</t>
+  </si>
+  <si>
+    <t>21:20:20</t>
+  </si>
+  <si>
+    <t>22:56:33</t>
+  </si>
+  <si>
+    <t>18:53:42</t>
+  </si>
+  <si>
+    <t>20:30:37</t>
+  </si>
+  <si>
+    <t>22:07:03</t>
+  </si>
+  <si>
+    <t>19:40:48</t>
+  </si>
+  <si>
+    <t>21:17:23</t>
+  </si>
+  <si>
+    <t>18:50:53</t>
+  </si>
+  <si>
+    <t>20:27:36</t>
+  </si>
+  <si>
+    <t>22:03:29</t>
+  </si>
+  <si>
+    <t>19:37:42</t>
+  </si>
+  <si>
+    <t>21:13:53</t>
+  </si>
+  <si>
+    <t>15°</t>
+  </si>
+  <si>
+    <t>1°</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>4°</t>
-  </si>
-  <si>
-    <t>15°</t>
-  </si>
-  <si>
-    <t>1°</t>
-  </si>
-  <si>
     <t>12°</t>
   </si>
   <si>
@@ -583,58 +547,61 @@
     <t>6°</t>
   </si>
   <si>
-    <t>14°</t>
-  </si>
-  <si>
-    <t>20:26:31</t>
-  </si>
-  <si>
-    <t>19:39:48</t>
+    <t>28°</t>
+  </si>
+  <si>
+    <t>19:39:47</t>
   </si>
   <si>
     <t>21:12:40</t>
   </si>
   <si>
-    <t>18:52:46</t>
-  </si>
-  <si>
-    <t>20:25:38</t>
-  </si>
-  <si>
-    <t>19:38:20</t>
-  </si>
-  <si>
-    <t>21:11:10</t>
-  </si>
-  <si>
-    <t>18:50:50</t>
-  </si>
-  <si>
-    <t>20:23:39</t>
-  </si>
-  <si>
-    <t>19:35:59</t>
-  </si>
-  <si>
-    <t>21:08:48</t>
-  </si>
-  <si>
-    <t>18:48:11</t>
-  </si>
-  <si>
-    <t>20:20:59</t>
+    <t>18:52:45</t>
+  </si>
+  <si>
+    <t>20:25:36</t>
+  </si>
+  <si>
+    <t>19:38:17</t>
+  </si>
+  <si>
+    <t>21:11:08</t>
+  </si>
+  <si>
+    <t>18:50:46</t>
+  </si>
+  <si>
+    <t>20:23:36</t>
+  </si>
+  <si>
+    <t>19:35:54</t>
+  </si>
+  <si>
+    <t>21:08:43</t>
+  </si>
+  <si>
+    <t>18:48:04</t>
+  </si>
+  <si>
+    <t>20:20:53</t>
+  </si>
+  <si>
+    <t>19:32:56</t>
+  </si>
+  <si>
+    <t>21:05:44</t>
+  </si>
+  <si>
+    <t>A+B</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>A+B</t>
+    <t>2</t>
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>4</t>
@@ -671,7 +638,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -692,7 +659,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -704,13 +671,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -722,7 +725,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -734,25 +737,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -764,19 +749,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -817,7 +802,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -880,6 +865,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1283,7 +1277,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1364,52 +1358,52 @@
         <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="J2" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="L2" s="4">
-        <v>-25.7</v>
+        <v>-14.6</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="O2" s="6">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="P2" s="7">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="Q2" s="8">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="R2" s="9">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1417,55 +1411,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="J3" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="L3" s="4">
-        <v>-20</v>
+        <v>-24.7</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O3" s="6">
-        <v>99</v>
-      </c>
-      <c r="P3" s="10">
-        <v>8</v>
+        <v>195</v>
+      </c>
+      <c r="O3" s="10">
+        <v>30</v>
+      </c>
+      <c r="P3" s="7">
+        <v>28</v>
       </c>
       <c r="Q3" s="11">
-        <v>92</v>
-      </c>
-      <c r="R3" s="11">
-        <v>90</v>
+        <v>13</v>
+      </c>
+      <c r="R3" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1473,55 +1467,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
+        <v>24</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-29.2</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="O4" s="10">
         <v>30</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-27.5</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O4" s="6">
-        <v>99</v>
-      </c>
       <c r="P4" s="12">
-        <v>46</v>
-      </c>
-      <c r="Q4" s="13">
-        <v>97</v>
-      </c>
-      <c r="R4" s="14">
-        <v>50</v>
+        <v>23</v>
+      </c>
+      <c r="Q4" s="11">
+        <v>15</v>
+      </c>
+      <c r="R4" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1529,55 +1523,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>73</v>
+        <v>180</v>
       </c>
       <c r="L5" s="4">
-        <v>-28.3</v>
+        <v>-8.4</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="O5" s="6">
-        <v>97</v>
-      </c>
-      <c r="P5" s="14">
-        <v>49</v>
+        <v>79</v>
+      </c>
+      <c r="P5" s="9">
+        <v>0</v>
       </c>
       <c r="Q5" s="13">
-        <v>93</v>
-      </c>
-      <c r="R5" s="11">
-        <v>88</v>
+        <v>3</v>
+      </c>
+      <c r="R5" s="14">
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1585,55 +1579,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="L6" s="4">
-        <v>-14.6</v>
+        <v>-20.4</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="O6" s="6">
-        <v>55</v>
-      </c>
-      <c r="P6" s="15">
-        <v>19</v>
-      </c>
-      <c r="Q6" s="16">
-        <v>31</v>
-      </c>
-      <c r="R6" s="7">
-        <v>2</v>
+        <v>100</v>
+      </c>
+      <c r="P6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="13">
+        <v>5</v>
+      </c>
+      <c r="R6" s="15">
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1641,55 +1635,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>192</v>
+        <v>73</v>
       </c>
       <c r="L7" s="4">
-        <v>-24.7</v>
+        <v>-28.1</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="O7" s="6">
         <v>95</v>
       </c>
-      <c r="P7" s="17">
-        <v>14</v>
-      </c>
-      <c r="Q7" s="18">
-        <v>38</v>
-      </c>
-      <c r="R7" s="18">
-        <v>40</v>
+      <c r="P7" s="9">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="16">
+        <v>35</v>
+      </c>
+      <c r="R7" s="17">
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1697,55 +1691,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L8" s="4">
+        <v>-29.1</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="O8" s="6">
         <v>98</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="L8" s="4">
-        <v>-29.2</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O8" s="6">
+      <c r="P8" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="18">
+        <v>49</v>
+      </c>
+      <c r="R8" s="19">
         <v>96</v>
-      </c>
-      <c r="P8" s="17">
-        <v>13</v>
-      </c>
-      <c r="Q8" s="18">
-        <v>40</v>
-      </c>
-      <c r="R8" s="12">
-        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1753,55 +1747,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="J9" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>193</v>
-      </c>
       <c r="L9" s="4">
-        <v>-8.4</v>
+        <v>-15</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="O9" s="6">
-        <v>68</v>
-      </c>
-      <c r="P9" s="17">
-        <v>15</v>
-      </c>
-      <c r="Q9" s="7">
-        <v>0</v>
-      </c>
-      <c r="R9" s="8">
-        <v>59</v>
+        <v>98</v>
+      </c>
+      <c r="P9" s="20">
+        <v>22</v>
+      </c>
+      <c r="Q9" s="17">
+        <v>92</v>
+      </c>
+      <c r="R9" s="17">
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1809,54 +1803,54 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="J10" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="L10" s="4">
-        <v>-20.4</v>
+        <v>-25.2</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="O10" s="6">
         <v>100</v>
       </c>
-      <c r="P10" s="10">
-        <v>9</v>
-      </c>
-      <c r="Q10" s="7">
-        <v>1</v>
-      </c>
-      <c r="R10" s="9">
+      <c r="P10" s="7">
+        <v>28</v>
+      </c>
+      <c r="Q10" s="17">
+        <v>91</v>
+      </c>
+      <c r="R10" s="15">
         <v>100</v>
       </c>
     </row>
@@ -1865,54 +1859,54 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L11" s="4">
-        <v>-28.1</v>
+        <v>-29.8</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="O11" s="6">
         <v>100</v>
       </c>
-      <c r="P11" s="19">
-        <v>4</v>
-      </c>
-      <c r="Q11" s="19">
-        <v>5</v>
-      </c>
-      <c r="R11" s="9">
+      <c r="P11" s="21">
+        <v>39</v>
+      </c>
+      <c r="Q11" s="15">
+        <v>100</v>
+      </c>
+      <c r="R11" s="15">
         <v>100</v>
       </c>
     </row>
@@ -1921,55 +1915,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>80</v>
+        <v>184</v>
       </c>
       <c r="L12" s="4">
-        <v>-29.1</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="O12" s="6">
-        <v>100</v>
-      </c>
-      <c r="P12" s="7">
-        <v>2</v>
-      </c>
-      <c r="Q12" s="17">
-        <v>16</v>
-      </c>
-      <c r="R12" s="9">
-        <v>100</v>
+        <v>96</v>
+      </c>
+      <c r="P12" s="22">
+        <v>46</v>
+      </c>
+      <c r="Q12" s="12">
+        <v>26</v>
+      </c>
+      <c r="R12" s="17">
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1977,55 +1971,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="L13" s="4">
-        <v>-15</v>
+        <v>-20.9</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="O13" s="6">
-        <v>100</v>
-      </c>
-      <c r="P13" s="15">
-        <v>21</v>
-      </c>
-      <c r="Q13" s="20">
-        <v>65</v>
-      </c>
-      <c r="R13" s="9">
-        <v>100</v>
+        <v>80</v>
+      </c>
+      <c r="P13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="16">
+        <v>33</v>
+      </c>
+      <c r="R13" s="23">
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2033,55 +2027,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>196</v>
+        <v>80</v>
       </c>
       <c r="L14" s="4">
-        <v>-25.2</v>
+        <v>-28.7</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="O14" s="6">
-        <v>84</v>
-      </c>
-      <c r="P14" s="17">
-        <v>14</v>
-      </c>
-      <c r="Q14" s="16">
-        <v>30</v>
-      </c>
-      <c r="R14" s="8">
-        <v>60</v>
+        <v>69</v>
+      </c>
+      <c r="P14" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>59</v>
+      </c>
+      <c r="R14" s="12">
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2089,55 +2083,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>83</v>
+        <v>186</v>
       </c>
       <c r="L15" s="4">
-        <v>-29.8</v>
+        <v>-15.3</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="O15" s="6">
-        <v>78</v>
-      </c>
-      <c r="P15" s="17">
-        <v>16</v>
-      </c>
-      <c r="Q15" s="15">
-        <v>18</v>
-      </c>
-      <c r="R15" s="12">
-        <v>45</v>
+        <v>100</v>
+      </c>
+      <c r="P15" s="24">
+        <v>55</v>
+      </c>
+      <c r="Q15" s="9">
+        <v>2</v>
+      </c>
+      <c r="R15" s="15">
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2145,55 +2139,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="L16" s="4">
-        <v>-8.699999999999999</v>
+        <v>-25.7</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="O16" s="6">
-        <v>36</v>
-      </c>
-      <c r="P16" s="15">
-        <v>22</v>
-      </c>
-      <c r="Q16" s="17">
-        <v>16</v>
-      </c>
-      <c r="R16" s="17">
-        <v>14</v>
+        <v>99</v>
+      </c>
+      <c r="P16" s="16">
+        <v>37</v>
+      </c>
+      <c r="Q16" s="16">
+        <v>37</v>
+      </c>
+      <c r="R16" s="19">
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2201,55 +2195,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="I17" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>186</v>
-      </c>
       <c r="K17" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="L17" s="4">
-        <v>-20.9</v>
+        <v>-8.9</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="O17" s="6">
-        <v>35</v>
-      </c>
-      <c r="P17" s="15">
+        <v>47</v>
+      </c>
+      <c r="P17" s="22">
+        <v>44</v>
+      </c>
+      <c r="Q17" s="20">
         <v>19</v>
       </c>
-      <c r="Q17" s="10">
-        <v>10</v>
-      </c>
-      <c r="R17" s="17">
-        <v>14</v>
+      <c r="R17" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2257,55 +2251,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>86</v>
+        <v>189</v>
       </c>
       <c r="L18" s="4">
-        <v>-28.7</v>
+        <v>-21.3</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O18" s="6">
-        <v>64</v>
-      </c>
-      <c r="P18" s="17">
-        <v>13</v>
-      </c>
-      <c r="Q18" s="7">
-        <v>2</v>
-      </c>
-      <c r="R18" s="20">
-        <v>64</v>
+        <v>194</v>
+      </c>
+      <c r="O18" s="10">
+        <v>37</v>
+      </c>
+      <c r="P18" s="16">
+        <v>37</v>
+      </c>
+      <c r="Q18" s="11">
+        <v>15</v>
+      </c>
+      <c r="R18" s="11">
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2313,55 +2307,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>199</v>
+        <v>85</v>
       </c>
       <c r="L19" s="4">
-        <v>-15.4</v>
+        <v>-29.3</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O19" s="6">
-        <v>81</v>
-      </c>
-      <c r="P19" s="20">
-        <v>64</v>
-      </c>
-      <c r="Q19" s="19">
-        <v>7</v>
-      </c>
-      <c r="R19" s="12">
-        <v>44</v>
+        <v>196</v>
+      </c>
+      <c r="O19" s="10">
+        <v>43</v>
+      </c>
+      <c r="P19" s="16">
+        <v>37</v>
+      </c>
+      <c r="Q19" s="11">
+        <v>15</v>
+      </c>
+      <c r="R19" s="22">
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2369,55 +2363,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="L20" s="4">
-        <v>-25.8</v>
+        <v>-15.6</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="O20" s="6">
-        <v>93</v>
-      </c>
-      <c r="P20" s="8">
-        <v>58</v>
-      </c>
-      <c r="Q20" s="19">
-        <v>3</v>
-      </c>
-      <c r="R20" s="21">
-        <v>73</v>
+        <v>85</v>
+      </c>
+      <c r="P20" s="13">
+        <v>6</v>
+      </c>
+      <c r="Q20" s="20">
+        <v>22</v>
+      </c>
+      <c r="R20" s="14">
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2425,190 +2419,114 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="L21" s="4">
-        <v>-8.9</v>
+        <v>-26.2</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18">
-      <c r="A22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="2">
-        <v>27</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="L22" s="4">
-        <v>-21.3</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18">
-      <c r="A23" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="2">
-        <v>12</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="L23" s="4">
-        <v>-29.3</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>207</v>
+        <v>195</v>
+      </c>
+      <c r="O21" s="6">
+        <v>82</v>
+      </c>
+      <c r="P21" s="13">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="11">
+        <v>16</v>
+      </c>
+      <c r="R21" s="14">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A23">
+  <conditionalFormatting sqref="A2:A21">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B23">
+  <conditionalFormatting sqref="B2:B21">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C23">
+  <conditionalFormatting sqref="C2:C21">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D23">
+  <conditionalFormatting sqref="D2:D21">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E23">
+  <conditionalFormatting sqref="E2:E21">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F23">
+  <conditionalFormatting sqref="F2:F21">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G23">
+  <conditionalFormatting sqref="G2:G21">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H23">
+  <conditionalFormatting sqref="H2:H21">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I23">
+  <conditionalFormatting sqref="I2:I21">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J23">
+  <conditionalFormatting sqref="J2:J21">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K23">
+  <conditionalFormatting sqref="K2:K21">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L23">
+  <conditionalFormatting sqref="L2:L21">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2627,12 +2545,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M23">
+  <conditionalFormatting sqref="M2:M21">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N23">
+  <conditionalFormatting sqref="N2:N21">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2649,22 +2567,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O23">
+  <conditionalFormatting sqref="O2:O21">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P23">
+  <conditionalFormatting sqref="P2:P21">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q23">
+  <conditionalFormatting sqref="Q2:Q21">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R23">
+  <conditionalFormatting sqref="R2:R21">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="191">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260826--01</t>
-  </si>
-  <si>
-    <t>20260826--02</t>
-  </si>
-  <si>
-    <t>20260826--03</t>
-  </si>
-  <si>
     <t>20260827--01</t>
   </si>
   <si>
@@ -130,75 +121,72 @@
     <t>20260901--02</t>
   </si>
   <si>
-    <t>04:33</t>
+    <t>20260902--01</t>
+  </si>
+  <si>
+    <t>20260902--02</t>
+  </si>
+  <si>
+    <t>03:31</t>
+  </si>
+  <si>
+    <t>05:47</t>
+  </si>
+  <si>
+    <t>05:43</t>
+  </si>
+  <si>
+    <t>02:58</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>05:52</t>
+  </si>
+  <si>
+    <t>04:14</t>
+  </si>
+  <si>
+    <t>05:13</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>04:59</t>
   </si>
   <si>
     <t>05:54</t>
   </si>
   <si>
-    <t>05:28</t>
-  </si>
-  <si>
-    <t>03:31</t>
-  </si>
-  <si>
-    <t>05:47</t>
-  </si>
-  <si>
-    <t>05:43</t>
-  </si>
-  <si>
-    <t>02:58</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>05:52</t>
-  </si>
-  <si>
-    <t>04:15</t>
-  </si>
-  <si>
-    <t>05:13</t>
-  </si>
-  <si>
-    <t>05:56</t>
-  </si>
-  <si>
-    <t>04:59</t>
-  </si>
-  <si>
-    <t>05:26</t>
-  </si>
-  <si>
-    <t>05:49</t>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>05:48</t>
   </si>
   <si>
     <t>05:42</t>
   </si>
   <si>
-    <t>02:47</t>
-  </si>
-  <si>
-    <t>05:51</t>
+    <t>02:46</t>
   </si>
   <si>
     <t>04:10</t>
   </si>
   <si>
-    <t>01:06</t>
+    <t>04:56</t>
+  </si>
+  <si>
+    <t>03:04</t>
+  </si>
+  <si>
+    <t>00:27</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>03:04</t>
-  </si>
-  <si>
-    <t>00:27</t>
-  </si>
-  <si>
     <t>02:41</t>
   </si>
   <si>
@@ -214,382 +202,376 @@
     <t>05:15</t>
   </si>
   <si>
-    <t>01:16</t>
+    <t>01:15</t>
   </si>
   <si>
     <t>03:20</t>
   </si>
   <si>
-    <t>19:36:07</t>
-  </si>
-  <si>
-    <t>21:12:26</t>
-  </si>
-  <si>
-    <t>22:49:19</t>
-  </si>
-  <si>
-    <t>18:46:50</t>
-  </si>
-  <si>
-    <t>20:22:53</t>
+    <t>05:21</t>
+  </si>
+  <si>
+    <t>00:58</t>
+  </si>
+  <si>
+    <t>18:46:51</t>
+  </si>
+  <si>
+    <t>20:22:54</t>
+  </si>
+  <si>
+    <t>21:59:41</t>
+  </si>
+  <si>
+    <t>23:36:52</t>
+  </si>
+  <si>
+    <t>19:33:20</t>
+  </si>
+  <si>
+    <t>21:10:00</t>
+  </si>
+  <si>
+    <t>22:47:03</t>
+  </si>
+  <si>
+    <t>18:43:45</t>
+  </si>
+  <si>
+    <t>20:20:16</t>
+  </si>
+  <si>
+    <t>21:57:13</t>
+  </si>
+  <si>
+    <t>19:30:29</t>
+  </si>
+  <si>
+    <t>21:07:21</t>
+  </si>
+  <si>
+    <t>18:40:40</t>
+  </si>
+  <si>
+    <t>20:17:26</t>
+  </si>
+  <si>
+    <t>21:54:37</t>
+  </si>
+  <si>
+    <t>19:27:28</t>
+  </si>
+  <si>
+    <t>21:04:31</t>
+  </si>
+  <si>
+    <t>18:37:28</t>
+  </si>
+  <si>
+    <t>20:14:24</t>
+  </si>
+  <si>
+    <t>18:49:42</t>
+  </si>
+  <si>
+    <t>20:25:10</t>
+  </si>
+  <si>
+    <t>22:01:58</t>
+  </si>
+  <si>
+    <t>23:39:54</t>
+  </si>
+  <si>
+    <t>19:35:38</t>
+  </si>
+  <si>
+    <t>21:12:15</t>
+  </si>
+  <si>
+    <t>22:49:42</t>
+  </si>
+  <si>
+    <t>18:46:08</t>
+  </si>
+  <si>
+    <t>20:22:30</t>
   </si>
   <si>
     <t>21:59:40</t>
   </si>
   <si>
-    <t>23:36:51</t>
-  </si>
-  <si>
-    <t>19:33:18</t>
-  </si>
-  <si>
-    <t>21:09:58</t>
-  </si>
-  <si>
-    <t>22:47:01</t>
-  </si>
-  <si>
-    <t>18:43:42</t>
-  </si>
-  <si>
-    <t>20:20:13</t>
-  </si>
-  <si>
-    <t>21:57:10</t>
-  </si>
-  <si>
-    <t>19:30:25</t>
-  </si>
-  <si>
-    <t>21:07:16</t>
-  </si>
-  <si>
-    <t>18:40:34</t>
-  </si>
-  <si>
-    <t>20:17:20</t>
-  </si>
-  <si>
-    <t>21:54:31</t>
-  </si>
-  <si>
-    <t>19:27:21</t>
-  </si>
-  <si>
-    <t>21:04:23</t>
-  </si>
-  <si>
-    <t>19:38:41</t>
-  </si>
-  <si>
-    <t>21:14:41</t>
-  </si>
-  <si>
-    <t>22:51:39</t>
-  </si>
-  <si>
-    <t>18:49:41</t>
-  </si>
-  <si>
-    <t>20:25:09</t>
-  </si>
-  <si>
-    <t>22:01:57</t>
-  </si>
-  <si>
-    <t>23:39:53</t>
-  </si>
-  <si>
-    <t>19:35:36</t>
-  </si>
-  <si>
-    <t>21:12:13</t>
-  </si>
-  <si>
-    <t>22:49:40</t>
-  </si>
-  <si>
-    <t>18:46:05</t>
-  </si>
-  <si>
-    <t>20:22:27</t>
-  </si>
-  <si>
-    <t>21:59:37</t>
+    <t>19:32:43</t>
+  </si>
+  <si>
+    <t>21:09:42</t>
+  </si>
+  <si>
+    <t>18:42:55</t>
+  </si>
+  <si>
+    <t>20:19:43</t>
+  </si>
+  <si>
+    <t>21:57:43</t>
+  </si>
+  <si>
+    <t>19:29:43</t>
+  </si>
+  <si>
+    <t>21:07:11</t>
+  </si>
+  <si>
+    <t>18:39:42</t>
+  </si>
+  <si>
+    <t>20:16:52</t>
+  </si>
+  <si>
+    <t>18:51:27</t>
+  </si>
+  <si>
+    <t>20:28:03</t>
+  </si>
+  <si>
+    <t>22:04:49</t>
+  </si>
+  <si>
+    <t>23:41:23</t>
+  </si>
+  <si>
+    <t>19:38:25</t>
+  </si>
+  <si>
+    <t>21:15:11</t>
+  </si>
+  <si>
+    <t>22:51:49</t>
+  </si>
+  <si>
+    <t>18:48:44</t>
+  </si>
+  <si>
+    <t>20:25:27</t>
+  </si>
+  <si>
+    <t>22:02:09</t>
+  </si>
+  <si>
+    <t>19:35:40</t>
+  </si>
+  <si>
+    <t>21:12:24</t>
+  </si>
+  <si>
+    <t>18:45:49</t>
+  </si>
+  <si>
+    <t>20:22:34</t>
+  </si>
+  <si>
+    <t>21:59:06</t>
   </si>
   <si>
     <t>19:32:39</t>
   </si>
   <si>
-    <t>21:09:37</t>
-  </si>
-  <si>
-    <t>18:42:49</t>
-  </si>
-  <si>
-    <t>20:19:37</t>
-  </si>
-  <si>
-    <t>21:57:37</t>
-  </si>
-  <si>
-    <t>19:29:36</t>
-  </si>
-  <si>
-    <t>21:07:03</t>
-  </si>
-  <si>
-    <t>19:40:57</t>
-  </si>
-  <si>
-    <t>21:17:38</t>
-  </si>
-  <si>
-    <t>22:54:23</t>
-  </si>
-  <si>
-    <t>18:51:27</t>
-  </si>
-  <si>
-    <t>20:28:02</t>
-  </si>
-  <si>
-    <t>22:04:48</t>
-  </si>
-  <si>
-    <t>23:41:22</t>
-  </si>
-  <si>
-    <t>19:38:24</t>
-  </si>
-  <si>
-    <t>21:15:09</t>
-  </si>
-  <si>
-    <t>22:51:47</t>
-  </si>
-  <si>
-    <t>18:48:41</t>
-  </si>
-  <si>
-    <t>20:25:24</t>
-  </si>
-  <si>
-    <t>22:02:06</t>
-  </si>
-  <si>
-    <t>21:12:20</t>
-  </si>
-  <si>
-    <t>18:45:43</t>
-  </si>
-  <si>
-    <t>20:22:28</t>
-  </si>
-  <si>
-    <t>21:59:00</t>
-  </si>
-  <si>
-    <t>19:32:31</t>
-  </si>
-  <si>
-    <t>21:09:08</t>
-  </si>
-  <si>
-    <t>19:43:14</t>
-  </si>
-  <si>
-    <t>21:20:35</t>
-  </si>
-  <si>
-    <t>22:57:07</t>
-  </si>
-  <si>
-    <t>18:53:12</t>
-  </si>
-  <si>
-    <t>20:30:56</t>
-  </si>
-  <si>
-    <t>22:07:40</t>
-  </si>
-  <si>
-    <t>23:42:51</t>
-  </si>
-  <si>
-    <t>19:41:11</t>
-  </si>
-  <si>
-    <t>21:18:05</t>
-  </si>
-  <si>
-    <t>22:53:55</t>
-  </si>
-  <si>
-    <t>18:51:18</t>
-  </si>
-  <si>
-    <t>20:28:23</t>
-  </si>
-  <si>
-    <t>22:04:36</t>
-  </si>
-  <si>
-    <t>19:38:33</t>
-  </si>
-  <si>
-    <t>21:15:03</t>
-  </si>
-  <si>
-    <t>18:48:38</t>
-  </si>
-  <si>
-    <t>20:25:19</t>
-  </si>
-  <si>
-    <t>22:00:24</t>
-  </si>
-  <si>
-    <t>19:35:27</t>
-  </si>
-  <si>
-    <t>21:11:13</t>
-  </si>
-  <si>
-    <t>19:45:48</t>
-  </si>
-  <si>
-    <t>21:22:49</t>
-  </si>
-  <si>
-    <t>22:59:27</t>
-  </si>
-  <si>
-    <t>18:56:04</t>
-  </si>
-  <si>
-    <t>20:33:12</t>
-  </si>
-  <si>
-    <t>22:09:57</t>
-  </si>
-  <si>
-    <t>23:45:53</t>
-  </si>
-  <si>
-    <t>19:43:30</t>
-  </si>
-  <si>
-    <t>21:20:20</t>
-  </si>
-  <si>
-    <t>22:56:33</t>
-  </si>
-  <si>
-    <t>18:53:42</t>
-  </si>
-  <si>
-    <t>20:30:37</t>
-  </si>
-  <si>
-    <t>22:07:03</t>
-  </si>
-  <si>
-    <t>19:40:48</t>
-  </si>
-  <si>
-    <t>21:17:23</t>
-  </si>
-  <si>
-    <t>18:50:53</t>
-  </si>
-  <si>
-    <t>20:27:36</t>
-  </si>
-  <si>
-    <t>22:03:29</t>
-  </si>
-  <si>
-    <t>19:37:42</t>
-  </si>
-  <si>
-    <t>21:13:53</t>
+    <t>21:09:16</t>
+  </si>
+  <si>
+    <t>18:42:39</t>
+  </si>
+  <si>
+    <t>20:19:20</t>
+  </si>
+  <si>
+    <t>18:53:13</t>
+  </si>
+  <si>
+    <t>20:30:57</t>
+  </si>
+  <si>
+    <t>22:07:41</t>
+  </si>
+  <si>
+    <t>23:42:52</t>
+  </si>
+  <si>
+    <t>19:41:13</t>
+  </si>
+  <si>
+    <t>21:18:07</t>
+  </si>
+  <si>
+    <t>22:53:56</t>
+  </si>
+  <si>
+    <t>18:51:21</t>
+  </si>
+  <si>
+    <t>20:28:25</t>
+  </si>
+  <si>
+    <t>22:04:39</t>
+  </si>
+  <si>
+    <t>19:38:37</t>
+  </si>
+  <si>
+    <t>21:15:07</t>
+  </si>
+  <si>
+    <t>18:48:43</t>
+  </si>
+  <si>
+    <t>20:25:25</t>
+  </si>
+  <si>
+    <t>22:00:29</t>
+  </si>
+  <si>
+    <t>19:35:35</t>
+  </si>
+  <si>
+    <t>21:11:21</t>
+  </si>
+  <si>
+    <t>18:45:37</t>
+  </si>
+  <si>
+    <t>20:21:48</t>
+  </si>
+  <si>
+    <t>18:56:05</t>
+  </si>
+  <si>
+    <t>20:33:13</t>
+  </si>
+  <si>
+    <t>22:09:58</t>
+  </si>
+  <si>
+    <t>23:45:54</t>
+  </si>
+  <si>
+    <t>19:43:31</t>
+  </si>
+  <si>
+    <t>21:20:22</t>
+  </si>
+  <si>
+    <t>22:56:35</t>
+  </si>
+  <si>
+    <t>18:53:44</t>
+  </si>
+  <si>
+    <t>20:30:39</t>
+  </si>
+  <si>
+    <t>22:07:06</t>
+  </si>
+  <si>
+    <t>19:40:52</t>
+  </si>
+  <si>
+    <t>21:17:28</t>
+  </si>
+  <si>
+    <t>18:50:59</t>
+  </si>
+  <si>
+    <t>20:27:42</t>
+  </si>
+  <si>
+    <t>22:03:35</t>
+  </si>
+  <si>
+    <t>19:37:50</t>
+  </si>
+  <si>
+    <t>21:14:00</t>
+  </si>
+  <si>
+    <t>18:47:51</t>
+  </si>
+  <si>
+    <t>20:24:15</t>
+  </si>
+  <si>
+    <t>12°</t>
+  </si>
+  <si>
+    <t>13°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>25°</t>
+  </si>
+  <si>
+    <t>5°</t>
+  </si>
+  <si>
+    <t>18°</t>
+  </si>
+  <si>
+    <t>29°</t>
+  </si>
+  <si>
+    <t>6°</t>
+  </si>
+  <si>
+    <t>14°</t>
+  </si>
+  <si>
+    <t>28°</t>
   </si>
   <si>
     <t>15°</t>
   </si>
   <si>
-    <t>1°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>12°</t>
-  </si>
-  <si>
-    <t>13°</t>
-  </si>
-  <si>
-    <t>25°</t>
-  </si>
-  <si>
-    <t>5°</t>
-  </si>
-  <si>
-    <t>18°</t>
-  </si>
-  <si>
-    <t>29°</t>
-  </si>
-  <si>
-    <t>6°</t>
-  </si>
-  <si>
-    <t>28°</t>
-  </si>
-  <si>
-    <t>19:39:47</t>
-  </si>
-  <si>
-    <t>21:12:40</t>
-  </si>
-  <si>
-    <t>18:52:45</t>
-  </si>
-  <si>
-    <t>20:25:36</t>
-  </si>
-  <si>
-    <t>19:38:17</t>
-  </si>
-  <si>
-    <t>21:11:08</t>
-  </si>
-  <si>
-    <t>18:50:46</t>
-  </si>
-  <si>
-    <t>20:23:36</t>
-  </si>
-  <si>
-    <t>19:35:54</t>
-  </si>
-  <si>
-    <t>21:08:43</t>
-  </si>
-  <si>
-    <t>18:48:04</t>
-  </si>
-  <si>
-    <t>20:20:53</t>
-  </si>
-  <si>
-    <t>19:32:56</t>
-  </si>
-  <si>
-    <t>21:05:44</t>
+    <t>18:52:46</t>
+  </si>
+  <si>
+    <t>20:25:37</t>
+  </si>
+  <si>
+    <t>19:38:19</t>
+  </si>
+  <si>
+    <t>21:11:09</t>
+  </si>
+  <si>
+    <t>18:50:49</t>
+  </si>
+  <si>
+    <t>20:23:39</t>
+  </si>
+  <si>
+    <t>19:35:58</t>
+  </si>
+  <si>
+    <t>21:08:47</t>
+  </si>
+  <si>
+    <t>18:48:10</t>
+  </si>
+  <si>
+    <t>20:20:58</t>
+  </si>
+  <si>
+    <t>19:33:03</t>
+  </si>
+  <si>
+    <t>21:05:51</t>
+  </si>
+  <si>
+    <t>18:45:03</t>
+  </si>
+  <si>
+    <t>20:17:50</t>
   </si>
   <si>
     <t>A+B</t>
@@ -598,13 +580,13 @@
     <t>B</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
 </sst>
 </file>
@@ -638,7 +620,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -659,37 +641,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FFEEF3F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -701,37 +665,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -743,13 +677,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -762,6 +696,66 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -802,7 +796,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -874,6 +868,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1277,7 +1277,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1355,55 +1355,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="L2" s="4">
-        <v>-14.6</v>
+        <v>-8.4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="O2" s="6">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="P2" s="7">
-        <v>31</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>62</v>
-      </c>
-      <c r="R2" s="9">
         <v>1</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="8">
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1411,55 +1411,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="L3" s="4">
-        <v>-24.7</v>
+        <v>-20.4</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O3" s="10">
-        <v>30</v>
+        <v>189</v>
+      </c>
+      <c r="O3" s="6">
+        <v>94</v>
       </c>
       <c r="P3" s="7">
-        <v>28</v>
-      </c>
-      <c r="Q3" s="11">
-        <v>13</v>
+        <v>2</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>0</v>
       </c>
       <c r="R3" s="9">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1467,55 +1467,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L4" s="4">
-        <v>-29.2</v>
+        <v>-28.1</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O4" s="10">
-        <v>30</v>
-      </c>
-      <c r="P4" s="12">
-        <v>23</v>
+        <v>190</v>
+      </c>
+      <c r="O4" s="6">
+        <v>100</v>
+      </c>
+      <c r="P4" s="10">
+        <v>3</v>
       </c>
       <c r="Q4" s="11">
-        <v>15</v>
-      </c>
-      <c r="R4" s="9">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="R4" s="8">
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1523,55 +1523,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>180</v>
+        <v>69</v>
       </c>
       <c r="L5" s="4">
-        <v>-8.4</v>
+        <v>-29.1</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O5" s="6">
-        <v>79</v>
-      </c>
-      <c r="P5" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="13">
+        <v>100</v>
+      </c>
+      <c r="P5" s="10">
         <v>3</v>
       </c>
-      <c r="R5" s="14">
-        <v>78</v>
+      <c r="Q5" s="12">
+        <v>19</v>
+      </c>
+      <c r="R5" s="8">
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1579,54 +1579,54 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="L6" s="4">
-        <v>-20.4</v>
+        <v>-15</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="O6" s="6">
         <v>100</v>
       </c>
-      <c r="P6" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="13">
-        <v>5</v>
-      </c>
-      <c r="R6" s="15">
+      <c r="P6" s="13">
+        <v>12</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>100</v>
+      </c>
+      <c r="R6" s="8">
         <v>100</v>
       </c>
     </row>
@@ -1635,55 +1635,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>73</v>
+        <v>175</v>
       </c>
       <c r="L7" s="4">
-        <v>-28.1</v>
+        <v>-25.2</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="O7" s="6">
-        <v>95</v>
-      </c>
-      <c r="P7" s="9">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="16">
-        <v>35</v>
-      </c>
-      <c r="R7" s="17">
-        <v>89</v>
+        <v>100</v>
+      </c>
+      <c r="P7" s="14">
+        <v>76</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>100</v>
+      </c>
+      <c r="R7" s="8">
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1691,55 +1691,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L8" s="4">
-        <v>-29.1</v>
+        <v>-29.8</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="O8" s="6">
-        <v>98</v>
-      </c>
-      <c r="P8" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="18">
-        <v>49</v>
-      </c>
-      <c r="R8" s="19">
-        <v>96</v>
+        <v>100</v>
+      </c>
+      <c r="P8" s="15">
+        <v>71</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>100</v>
+      </c>
+      <c r="R8" s="8">
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1747,55 +1747,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="L9" s="4">
-        <v>-15</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="O9" s="6">
-        <v>98</v>
-      </c>
-      <c r="P9" s="20">
-        <v>22</v>
-      </c>
-      <c r="Q9" s="17">
-        <v>92</v>
-      </c>
-      <c r="R9" s="17">
-        <v>89</v>
+        <v>63</v>
+      </c>
+      <c r="P9" s="16">
+        <v>55</v>
+      </c>
+      <c r="Q9" s="12">
+        <v>21</v>
+      </c>
+      <c r="R9" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1803,55 +1803,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="L10" s="4">
-        <v>-25.2</v>
+        <v>-20.9</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="O10" s="6">
-        <v>100</v>
-      </c>
-      <c r="P10" s="7">
-        <v>28</v>
+        <v>57</v>
+      </c>
+      <c r="P10" s="16">
+        <v>57</v>
       </c>
       <c r="Q10" s="17">
-        <v>91</v>
-      </c>
-      <c r="R10" s="15">
-        <v>100</v>
+        <v>14</v>
+      </c>
+      <c r="R10" s="12">
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1859,54 +1859,54 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L11" s="4">
-        <v>-29.8</v>
+        <v>-28.7</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="O11" s="6">
         <v>100</v>
       </c>
-      <c r="P11" s="21">
+      <c r="P11" s="10">
+        <v>3</v>
+      </c>
+      <c r="Q11" s="18">
         <v>39</v>
       </c>
-      <c r="Q11" s="15">
-        <v>100</v>
-      </c>
-      <c r="R11" s="15">
+      <c r="R11" s="8">
         <v>100</v>
       </c>
     </row>
@@ -1915,55 +1915,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="L12" s="4">
-        <v>-8.699999999999999</v>
+        <v>-15.4</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="O12" s="6">
-        <v>96</v>
-      </c>
-      <c r="P12" s="22">
-        <v>46</v>
-      </c>
-      <c r="Q12" s="12">
-        <v>26</v>
-      </c>
-      <c r="R12" s="17">
-        <v>91</v>
+        <v>100</v>
+      </c>
+      <c r="P12" s="10">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>0</v>
+      </c>
+      <c r="R12" s="8">
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1971,55 +1971,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="L13" s="4">
-        <v>-20.9</v>
+        <v>-25.8</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="O13" s="6">
-        <v>80</v>
-      </c>
-      <c r="P13" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="16">
-        <v>33</v>
-      </c>
-      <c r="R13" s="23">
-        <v>68</v>
+        <v>95</v>
+      </c>
+      <c r="P13" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="13">
+        <v>10</v>
+      </c>
+      <c r="R13" s="19">
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2027,55 +2027,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>169</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="L14" s="4">
-        <v>-28.7</v>
+        <v>-8.9</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O14" s="6">
-        <v>69</v>
-      </c>
-      <c r="P14" s="9">
+        <v>189</v>
+      </c>
+      <c r="O14" s="20">
+        <v>20</v>
+      </c>
+      <c r="P14" s="10">
+        <v>7</v>
+      </c>
+      <c r="Q14" s="13">
+        <v>9</v>
+      </c>
+      <c r="R14" s="7">
         <v>0</v>
-      </c>
-      <c r="Q14" s="8">
-        <v>59</v>
-      </c>
-      <c r="R14" s="12">
-        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2083,55 +2083,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="K15" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="L15" s="4">
+        <v>-21.3</v>
+      </c>
+      <c r="M15" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="L15" s="4">
-        <v>-15.3</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>192</v>
-      </c>
       <c r="N15" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="O15" s="6">
-        <v>100</v>
-      </c>
-      <c r="P15" s="24">
-        <v>55</v>
-      </c>
-      <c r="Q15" s="9">
-        <v>2</v>
-      </c>
-      <c r="R15" s="15">
-        <v>100</v>
+        <v>189</v>
+      </c>
+      <c r="O15" s="21">
+        <v>0</v>
+      </c>
+      <c r="P15" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="7">
+        <v>0</v>
+      </c>
+      <c r="R15" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2139,55 +2139,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="K16" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L16" s="4">
+        <v>-29.3</v>
+      </c>
+      <c r="M16" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="L16" s="4">
-        <v>-25.7</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>193</v>
-      </c>
       <c r="N16" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O16" s="6">
-        <v>99</v>
-      </c>
-      <c r="P16" s="16">
-        <v>37</v>
-      </c>
-      <c r="Q16" s="16">
-        <v>37</v>
-      </c>
-      <c r="R16" s="19">
-        <v>96</v>
+        <v>188</v>
+      </c>
+      <c r="O16" s="21">
+        <v>0</v>
+      </c>
+      <c r="P16" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="7">
+        <v>0</v>
+      </c>
+      <c r="R16" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2195,55 +2195,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="L17" s="4">
-        <v>-8.9</v>
+        <v>-15.7</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="O17" s="6">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="P17" s="22">
-        <v>44</v>
-      </c>
-      <c r="Q17" s="20">
-        <v>19</v>
-      </c>
-      <c r="R17" s="9">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="Q17" s="23">
+        <v>62</v>
+      </c>
+      <c r="R17" s="10">
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2251,55 +2251,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="L18" s="4">
-        <v>-21.3</v>
+        <v>-26.2</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="O18" s="10">
-        <v>37</v>
-      </c>
-      <c r="P18" s="16">
-        <v>37</v>
-      </c>
-      <c r="Q18" s="11">
-        <v>15</v>
-      </c>
-      <c r="R18" s="11">
-        <v>15</v>
+        <v>190</v>
+      </c>
+      <c r="O18" s="6">
+        <v>91</v>
+      </c>
+      <c r="P18" s="24">
+        <v>23</v>
+      </c>
+      <c r="Q18" s="15">
+        <v>69</v>
+      </c>
+      <c r="R18" s="10">
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2307,55 +2307,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>169</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>85</v>
+        <v>184</v>
       </c>
       <c r="L19" s="4">
-        <v>-29.3</v>
+        <v>-9.1</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O19" s="10">
-        <v>43</v>
-      </c>
-      <c r="P19" s="16">
-        <v>37</v>
-      </c>
-      <c r="Q19" s="11">
-        <v>15</v>
-      </c>
-      <c r="R19" s="22">
-        <v>43</v>
+        <v>189</v>
+      </c>
+      <c r="O19" s="6">
+        <v>97</v>
+      </c>
+      <c r="P19" s="25">
+        <v>28</v>
+      </c>
+      <c r="Q19" s="26">
+        <v>44</v>
+      </c>
+      <c r="R19" s="9">
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2363,170 +2363,114 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="L20" s="4">
-        <v>-15.6</v>
+        <v>-21.7</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="O20" s="6">
-        <v>85</v>
-      </c>
-      <c r="P20" s="13">
-        <v>6</v>
-      </c>
-      <c r="Q20" s="20">
-        <v>22</v>
-      </c>
-      <c r="R20" s="14">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18">
-      <c r="A21" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="2">
-        <v>16</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="L21" s="4">
-        <v>-26.2</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O21" s="6">
-        <v>82</v>
-      </c>
-      <c r="P21" s="13">
-        <v>4</v>
-      </c>
-      <c r="Q21" s="11">
-        <v>16</v>
-      </c>
-      <c r="R21" s="14">
-        <v>80</v>
+        <v>100</v>
+      </c>
+      <c r="P20" s="25">
+        <v>32</v>
+      </c>
+      <c r="Q20" s="16">
+        <v>57</v>
+      </c>
+      <c r="R20" s="9">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A21">
+  <conditionalFormatting sqref="A2:A20">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B21">
+  <conditionalFormatting sqref="B2:B20">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C21">
+  <conditionalFormatting sqref="C2:C20">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D21">
+  <conditionalFormatting sqref="D2:D20">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E21">
+  <conditionalFormatting sqref="E2:E20">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F21">
+  <conditionalFormatting sqref="F2:F20">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G21">
+  <conditionalFormatting sqref="G2:G20">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H21">
+  <conditionalFormatting sqref="H2:H20">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I21">
+  <conditionalFormatting sqref="I2:I20">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J21">
+  <conditionalFormatting sqref="J2:J20">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K21">
+  <conditionalFormatting sqref="K2:K20">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L21">
+  <conditionalFormatting sqref="L2:L20">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2545,12 +2489,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M21">
+  <conditionalFormatting sqref="M2:M20">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N21">
+  <conditionalFormatting sqref="N2:N20">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2567,22 +2511,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O21">
+  <conditionalFormatting sqref="O2:O20">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P21">
+  <conditionalFormatting sqref="P2:P20">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q21">
+  <conditionalFormatting sqref="Q2:Q20">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R21">
+  <conditionalFormatting sqref="R2:R20">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="168">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260827--01</t>
-  </si>
-  <si>
-    <t>20260827--02</t>
-  </si>
-  <si>
-    <t>20260827--03</t>
-  </si>
-  <si>
-    <t>20260827--04</t>
-  </si>
-  <si>
     <t>20260828--01</t>
   </si>
   <si>
@@ -127,16 +115,7 @@
     <t>20260902--02</t>
   </si>
   <si>
-    <t>03:31</t>
-  </si>
-  <si>
-    <t>05:47</t>
-  </si>
-  <si>
-    <t>05:43</t>
-  </si>
-  <si>
-    <t>02:58</t>
+    <t>20260903--01</t>
   </si>
   <si>
     <t>05:35</t>
@@ -178,18 +157,15 @@
     <t>04:56</t>
   </si>
   <si>
-    <t>03:04</t>
-  </si>
-  <si>
-    <t>00:27</t>
+    <t>05:24</t>
+  </si>
+  <si>
+    <t>02:41</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>02:41</t>
-  </si>
-  <si>
     <t>04:41</t>
   </si>
   <si>
@@ -214,16 +190,7 @@
     <t>00:58</t>
   </si>
   <si>
-    <t>18:46:51</t>
-  </si>
-  <si>
-    <t>20:22:54</t>
-  </si>
-  <si>
-    <t>21:59:41</t>
-  </si>
-  <si>
-    <t>23:36:52</t>
+    <t>03:09</t>
   </si>
   <si>
     <t>19:33:20</t>
@@ -271,16 +238,7 @@
     <t>20:14:24</t>
   </si>
   <si>
-    <t>18:49:42</t>
-  </si>
-  <si>
-    <t>20:25:10</t>
-  </si>
-  <si>
-    <t>22:01:58</t>
-  </si>
-  <si>
-    <t>23:39:54</t>
+    <t>19:24:15</t>
   </si>
   <si>
     <t>19:35:38</t>
@@ -328,16 +286,7 @@
     <t>20:16:52</t>
   </si>
   <si>
-    <t>18:51:27</t>
-  </si>
-  <si>
-    <t>20:28:03</t>
-  </si>
-  <si>
-    <t>22:04:49</t>
-  </si>
-  <si>
-    <t>23:41:23</t>
+    <t>19:26:37</t>
   </si>
   <si>
     <t>19:38:25</t>
@@ -385,16 +334,7 @@
     <t>20:19:20</t>
   </si>
   <si>
-    <t>18:53:13</t>
-  </si>
-  <si>
-    <t>20:30:57</t>
-  </si>
-  <si>
-    <t>22:07:41</t>
-  </si>
-  <si>
-    <t>23:42:52</t>
+    <t>19:29:19</t>
   </si>
   <si>
     <t>19:41:13</t>
@@ -442,16 +382,7 @@
     <t>20:21:48</t>
   </si>
   <si>
-    <t>18:56:05</t>
-  </si>
-  <si>
-    <t>20:33:13</t>
-  </si>
-  <si>
-    <t>22:09:58</t>
-  </si>
-  <si>
-    <t>23:45:54</t>
+    <t>19:32:01</t>
   </si>
   <si>
     <t>19:43:31</t>
@@ -499,21 +430,21 @@
     <t>20:24:15</t>
   </si>
   <si>
-    <t>12°</t>
+    <t>19:34:21</t>
+  </si>
+  <si>
+    <t>25°</t>
+  </si>
+  <si>
+    <t>5°</t>
+  </si>
+  <si>
+    <t>0°</t>
   </si>
   <si>
     <t>13°</t>
   </si>
   <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>25°</t>
-  </si>
-  <si>
-    <t>5°</t>
-  </si>
-  <si>
     <t>18°</t>
   </si>
   <si>
@@ -532,10 +463,7 @@
     <t>15°</t>
   </si>
   <si>
-    <t>18:52:46</t>
-  </si>
-  <si>
-    <t>20:25:37</t>
+    <t>22°</t>
   </si>
   <si>
     <t>19:38:19</t>
@@ -574,19 +502,22 @@
     <t>20:17:50</t>
   </si>
   <si>
+    <t>19:29:46</t>
+  </si>
+  <si>
     <t>A+B</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
 </sst>
 </file>
@@ -641,7 +572,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -653,7 +596,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -665,97 +680,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1277,7 +1208,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1355,55 +1286,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>142</v>
-      </c>
       <c r="J2" s="3" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="L2" s="4">
-        <v>-8.4</v>
+        <v>-15</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="O2" s="6">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="P2" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>84</v>
       </c>
       <c r="R2" s="8">
-        <v>100</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1411,55 +1342,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>143</v>
-      </c>
       <c r="J3" s="3" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="L3" s="4">
-        <v>-20.4</v>
+        <v>-25.2</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="O3" s="6">
-        <v>94</v>
-      </c>
-      <c r="P3" s="7">
-        <v>2</v>
-      </c>
-      <c r="Q3" s="7">
-        <v>0</v>
-      </c>
-      <c r="R3" s="9">
-        <v>90</v>
+        <v>100</v>
+      </c>
+      <c r="P3" s="9">
+        <v>21</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>100</v>
+      </c>
+      <c r="R3" s="10">
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1467,54 +1398,54 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="J4" s="3" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="L4" s="4">
-        <v>-28.1</v>
+        <v>-29.8</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="O4" s="6">
         <v>100</v>
       </c>
-      <c r="P4" s="10">
-        <v>3</v>
-      </c>
-      <c r="Q4" s="11">
-        <v>33</v>
-      </c>
-      <c r="R4" s="8">
+      <c r="P4" s="11">
+        <v>37</v>
+      </c>
+      <c r="Q4" s="10">
+        <v>100</v>
+      </c>
+      <c r="R4" s="10">
         <v>100</v>
       </c>
     </row>
@@ -1523,55 +1454,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>145</v>
-      </c>
       <c r="J5" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="L5" s="4">
-        <v>-29.1</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>187</v>
-      </c>
       <c r="N5" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="O5" s="6">
-        <v>100</v>
-      </c>
-      <c r="P5" s="10">
+        <v>165</v>
+      </c>
+      <c r="O5" s="12">
         <v>3</v>
       </c>
-      <c r="Q5" s="12">
-        <v>19</v>
-      </c>
-      <c r="R5" s="8">
-        <v>100</v>
+      <c r="P5" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="13">
+        <v>0</v>
+      </c>
+      <c r="R5" s="13">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1579,55 +1510,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-20.9</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="O6" s="6">
         <v>89</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="L6" s="4">
-        <v>-15</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="O6" s="6">
-        <v>100</v>
-      </c>
       <c r="P6" s="13">
-        <v>12</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>100</v>
-      </c>
-      <c r="R6" s="8">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>18</v>
+      </c>
+      <c r="R6" s="14">
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1635,55 +1566,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>147</v>
-      </c>
       <c r="J7" s="3" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>175</v>
+        <v>64</v>
       </c>
       <c r="L7" s="4">
-        <v>-25.2</v>
+        <v>-28.7</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="O7" s="6">
         <v>100</v>
       </c>
-      <c r="P7" s="14">
-        <v>76</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>100</v>
-      </c>
-      <c r="R7" s="8">
-        <v>100</v>
+      <c r="P7" s="15">
+        <v>80</v>
+      </c>
+      <c r="Q7" s="16">
+        <v>26</v>
+      </c>
+      <c r="R7" s="17">
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1691,55 +1622,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="H8" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="J8" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="L8" s="4">
+        <v>-15.4</v>
+      </c>
+      <c r="M8" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L8" s="4">
-        <v>-29.8</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>187</v>
-      </c>
       <c r="N8" s="1" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="O8" s="6">
-        <v>100</v>
-      </c>
-      <c r="P8" s="15">
-        <v>71</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>100</v>
-      </c>
-      <c r="R8" s="8">
-        <v>100</v>
+        <v>94</v>
+      </c>
+      <c r="P8" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="13">
+        <v>1</v>
+      </c>
+      <c r="R8" s="18">
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1747,55 +1678,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="H9" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="L9" s="4">
-        <v>-8.699999999999999</v>
+        <v>-25.8</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="O9" s="6">
-        <v>63</v>
-      </c>
-      <c r="P9" s="16">
-        <v>55</v>
-      </c>
-      <c r="Q9" s="12">
-        <v>21</v>
-      </c>
-      <c r="R9" s="7">
+        <v>59</v>
+      </c>
+      <c r="P9" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="13">
         <v>1</v>
+      </c>
+      <c r="R9" s="19">
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1803,55 +1734,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="H10" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="L10" s="4">
-        <v>-20.9</v>
+        <v>-8.9</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="O10" s="6">
-        <v>57</v>
-      </c>
-      <c r="P10" s="16">
-        <v>57</v>
-      </c>
-      <c r="Q10" s="17">
-        <v>14</v>
-      </c>
-      <c r="R10" s="12">
-        <v>20</v>
+        <v>98</v>
+      </c>
+      <c r="P10" s="17">
+        <v>72</v>
+      </c>
+      <c r="Q10" s="16">
+        <v>26</v>
+      </c>
+      <c r="R10" s="20">
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1859,55 +1790,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="H11" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="I11" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="J11" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="L11" s="4">
+        <v>-21.3</v>
+      </c>
+      <c r="M11" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="L11" s="4">
-        <v>-28.7</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>187</v>
-      </c>
       <c r="N11" s="1" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="O11" s="6">
-        <v>100</v>
-      </c>
-      <c r="P11" s="10">
-        <v>3</v>
-      </c>
-      <c r="Q11" s="18">
-        <v>39</v>
-      </c>
-      <c r="R11" s="8">
-        <v>100</v>
+        <v>51</v>
+      </c>
+      <c r="P11" s="9">
+        <v>22</v>
+      </c>
+      <c r="Q11" s="21">
+        <v>13</v>
+      </c>
+      <c r="R11" s="22">
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1915,55 +1846,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="H12" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="I12" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="J12" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="L12" s="4">
+        <v>-29.3</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="N12" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="L12" s="4">
-        <v>-15.4</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="O12" s="6">
-        <v>100</v>
-      </c>
-      <c r="P12" s="10">
-        <v>4</v>
-      </c>
-      <c r="Q12" s="7">
-        <v>0</v>
-      </c>
-      <c r="R12" s="8">
-        <v>100</v>
+      <c r="O12" s="23">
+        <v>35</v>
+      </c>
+      <c r="P12" s="9">
+        <v>20</v>
+      </c>
+      <c r="Q12" s="24">
+        <v>6</v>
+      </c>
+      <c r="R12" s="9">
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1971,55 +1902,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
+        <v>29</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="L13" s="4">
+        <v>-15.7</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="O13" s="6">
+        <v>100</v>
+      </c>
+      <c r="P13" s="16">
         <v>23</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="L13" s="4">
-        <v>-25.8</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="O13" s="6">
-        <v>95</v>
-      </c>
-      <c r="P13" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="13">
-        <v>10</v>
-      </c>
-      <c r="R13" s="19">
-        <v>83</v>
+      <c r="Q13" s="25">
+        <v>50</v>
+      </c>
+      <c r="R13" s="22">
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2027,55 +1958,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="E14" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="H14" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="I14" s="1" t="s">
-        <v>154</v>
-      </c>
       <c r="J14" s="3" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="L14" s="4">
-        <v>-8.9</v>
+        <v>-26.2</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="O14" s="20">
+        <v>166</v>
+      </c>
+      <c r="O14" s="6">
+        <v>82</v>
+      </c>
+      <c r="P14" s="9">
         <v>20</v>
       </c>
-      <c r="P14" s="10">
-        <v>7</v>
-      </c>
-      <c r="Q14" s="13">
-        <v>9</v>
-      </c>
-      <c r="R14" s="7">
-        <v>0</v>
+      <c r="Q14" s="17">
+        <v>69</v>
+      </c>
+      <c r="R14" s="11">
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2083,55 +2014,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="H15" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I15" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="I15" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="L15" s="4">
-        <v>-21.3</v>
+        <v>-9.1</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="O15" s="21">
-        <v>0</v>
-      </c>
-      <c r="P15" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="7">
-        <v>0</v>
-      </c>
-      <c r="R15" s="7">
-        <v>0</v>
+        <v>165</v>
+      </c>
+      <c r="O15" s="6">
+        <v>87</v>
+      </c>
+      <c r="P15" s="25">
+        <v>52</v>
+      </c>
+      <c r="Q15" s="19">
+        <v>44</v>
+      </c>
+      <c r="R15" s="22">
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2139,55 +2070,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="H16" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="I16" s="1" t="s">
-        <v>156</v>
-      </c>
       <c r="J16" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="L16" s="4">
+        <v>-21.7</v>
+      </c>
+      <c r="M16" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="K16" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="L16" s="4">
-        <v>-29.3</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>187</v>
-      </c>
       <c r="N16" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="O16" s="21">
-        <v>0</v>
-      </c>
-      <c r="P16" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="7">
-        <v>0</v>
-      </c>
-      <c r="R16" s="7">
-        <v>0</v>
+        <v>165</v>
+      </c>
+      <c r="O16" s="6">
+        <v>98</v>
+      </c>
+      <c r="P16" s="20">
+        <v>59</v>
+      </c>
+      <c r="Q16" s="26">
+        <v>53</v>
+      </c>
+      <c r="R16" s="19">
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2195,282 +2126,114 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="H17" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I17" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="J17" s="3" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="L17" s="4">
-        <v>-15.7</v>
+        <v>-15.9</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="O17" s="6">
-        <v>89</v>
-      </c>
-      <c r="P17" s="22">
-        <v>50</v>
-      </c>
-      <c r="Q17" s="23">
+        <v>99</v>
+      </c>
+      <c r="P17" s="20">
         <v>62</v>
       </c>
-      <c r="R17" s="10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18">
-      <c r="A18" s="1" t="s">
+      <c r="Q17" s="17">
+        <v>70</v>
+      </c>
+      <c r="R17" s="11">
         <v>34</v>
-      </c>
-      <c r="B18" s="2">
-        <v>16</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="L18" s="4">
-        <v>-26.2</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="O18" s="6">
-        <v>91</v>
-      </c>
-      <c r="P18" s="24">
-        <v>23</v>
-      </c>
-      <c r="Q18" s="15">
-        <v>69</v>
-      </c>
-      <c r="R18" s="10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18">
-      <c r="A19" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="2">
-        <v>30</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="L19" s="4">
-        <v>-9.1</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="O19" s="6">
-        <v>97</v>
-      </c>
-      <c r="P19" s="25">
-        <v>28</v>
-      </c>
-      <c r="Q19" s="26">
-        <v>44</v>
-      </c>
-      <c r="R19" s="9">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18">
-      <c r="A20" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="2">
-        <v>19</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="L20" s="4">
-        <v>-21.7</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="O20" s="6">
-        <v>100</v>
-      </c>
-      <c r="P20" s="25">
-        <v>32</v>
-      </c>
-      <c r="Q20" s="16">
-        <v>57</v>
-      </c>
-      <c r="R20" s="9">
-        <v>90</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A20">
+  <conditionalFormatting sqref="A2:A17">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B20">
+  <conditionalFormatting sqref="B2:B17">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C20">
+  <conditionalFormatting sqref="C2:C17">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D20">
+  <conditionalFormatting sqref="D2:D17">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E20">
+  <conditionalFormatting sqref="E2:E17">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F20">
+  <conditionalFormatting sqref="F2:F17">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G20">
+  <conditionalFormatting sqref="G2:G17">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H20">
+  <conditionalFormatting sqref="H2:H17">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I20">
+  <conditionalFormatting sqref="I2:I17">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J20">
+  <conditionalFormatting sqref="J2:J17">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K20">
+  <conditionalFormatting sqref="K2:K17">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L20">
+  <conditionalFormatting sqref="L2:L17">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2489,12 +2252,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M20">
+  <conditionalFormatting sqref="M2:M17">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N20">
+  <conditionalFormatting sqref="N2:N17">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2511,22 +2274,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O20">
+  <conditionalFormatting sqref="O2:O17">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P20">
+  <conditionalFormatting sqref="P2:P17">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q20">
+  <conditionalFormatting sqref="Q2:Q17">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R20">
+  <conditionalFormatting sqref="R2:R17">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="161">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260828--01</t>
-  </si>
-  <si>
-    <t>20260828--02</t>
-  </si>
-  <si>
-    <t>20260828--03</t>
-  </si>
-  <si>
     <t>20260829--01</t>
   </si>
   <si>
@@ -118,39 +109,39 @@
     <t>20260903--01</t>
   </si>
   <si>
-    <t>05:35</t>
+    <t>20260904--01</t>
+  </si>
+  <si>
+    <t>20260904--02</t>
+  </si>
+  <si>
+    <t>05:13</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>04:59</t>
+  </si>
+  <si>
+    <t>05:54</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>05:48</t>
+  </si>
+  <si>
+    <t>05:42</t>
+  </si>
+  <si>
+    <t>02:46</t>
   </si>
   <si>
     <t>05:52</t>
   </si>
   <si>
-    <t>04:14</t>
-  </si>
-  <si>
-    <t>05:13</t>
-  </si>
-  <si>
-    <t>05:55</t>
-  </si>
-  <si>
-    <t>04:59</t>
-  </si>
-  <si>
-    <t>05:54</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>05:48</t>
-  </si>
-  <si>
-    <t>05:42</t>
-  </si>
-  <si>
-    <t>02:46</t>
-  </si>
-  <si>
     <t>04:10</t>
   </si>
   <si>
@@ -160,18 +151,18 @@
     <t>05:24</t>
   </si>
   <si>
-    <t>02:41</t>
+    <t>02:40</t>
+  </si>
+  <si>
+    <t>04:41</t>
+  </si>
+  <si>
+    <t>01:09</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>04:41</t>
-  </si>
-  <si>
-    <t>01:09</t>
-  </si>
-  <si>
     <t>03:15</t>
   </si>
   <si>
@@ -193,13 +184,10 @@
     <t>03:09</t>
   </si>
   <si>
-    <t>19:33:20</t>
-  </si>
-  <si>
-    <t>21:10:00</t>
-  </si>
-  <si>
-    <t>22:47:03</t>
+    <t>05:16</t>
+  </si>
+  <si>
+    <t>00:01</t>
   </si>
   <si>
     <t>18:43:45</t>
@@ -241,13 +229,10 @@
     <t>19:24:15</t>
   </si>
   <si>
-    <t>19:35:38</t>
-  </si>
-  <si>
-    <t>21:12:15</t>
-  </si>
-  <si>
-    <t>22:49:42</t>
+    <t>18:34:04</t>
+  </si>
+  <si>
+    <t>20:11:14</t>
   </si>
   <si>
     <t>18:46:08</t>
@@ -289,13 +274,10 @@
     <t>19:26:37</t>
   </si>
   <si>
-    <t>19:38:25</t>
-  </si>
-  <si>
-    <t>21:15:11</t>
-  </si>
-  <si>
-    <t>22:51:49</t>
+    <t>18:36:21</t>
+  </si>
+  <si>
+    <t>20:14:23</t>
   </si>
   <si>
     <t>18:48:44</t>
@@ -337,13 +319,10 @@
     <t>19:29:19</t>
   </si>
   <si>
-    <t>19:41:13</t>
-  </si>
-  <si>
-    <t>21:18:07</t>
-  </si>
-  <si>
-    <t>22:53:56</t>
+    <t>18:39:12</t>
+  </si>
+  <si>
+    <t>20:15:43</t>
   </si>
   <si>
     <t>18:51:21</t>
@@ -385,13 +364,10 @@
     <t>19:32:01</t>
   </si>
   <si>
-    <t>19:43:31</t>
-  </si>
-  <si>
-    <t>21:20:22</t>
-  </si>
-  <si>
-    <t>22:56:35</t>
+    <t>18:42:03</t>
+  </si>
+  <si>
+    <t>20:17:03</t>
   </si>
   <si>
     <t>18:53:44</t>
@@ -433,43 +409,43 @@
     <t>19:34:21</t>
   </si>
   <si>
-    <t>25°</t>
+    <t>18:44:20</t>
+  </si>
+  <si>
+    <t>20:20:11</t>
+  </si>
+  <si>
+    <t>13°</t>
+  </si>
+  <si>
+    <t>18°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>29°</t>
+  </si>
+  <si>
+    <t>6°</t>
+  </si>
+  <si>
+    <t>14°</t>
+  </si>
+  <si>
+    <t>28°</t>
   </si>
   <si>
     <t>5°</t>
   </si>
   <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>13°</t>
-  </si>
-  <si>
-    <t>18°</t>
-  </si>
-  <si>
-    <t>29°</t>
-  </si>
-  <si>
-    <t>6°</t>
-  </si>
-  <si>
-    <t>14°</t>
-  </si>
-  <si>
-    <t>28°</t>
-  </si>
-  <si>
     <t>15°</t>
   </si>
   <si>
     <t>22°</t>
   </si>
   <si>
-    <t>19:38:19</t>
-  </si>
-  <si>
-    <t>21:11:09</t>
+    <t>10°</t>
   </si>
   <si>
     <t>18:50:49</t>
@@ -503,6 +479,9 @@
   </si>
   <si>
     <t>19:29:46</t>
+  </si>
+  <si>
+    <t>18:41:37</t>
   </si>
   <si>
     <t>A+B</t>
@@ -551,7 +530,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -572,13 +551,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -590,7 +647,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -602,91 +677,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -727,7 +718,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -805,6 +796,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1208,7 +1205,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1286,55 +1283,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="L2" s="4">
-        <v>-15</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="O2" s="6">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="P2" s="7">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="Q2" s="8">
-        <v>84</v>
-      </c>
-      <c r="R2" s="8">
-        <v>84</v>
+        <v>13</v>
+      </c>
+      <c r="R2" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1342,55 +1339,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="L3" s="4">
-        <v>-25.2</v>
+        <v>-20.9</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="O3" s="6">
-        <v>100</v>
-      </c>
-      <c r="P3" s="9">
-        <v>21</v>
-      </c>
-      <c r="Q3" s="10">
-        <v>100</v>
-      </c>
-      <c r="R3" s="10">
-        <v>100</v>
+        <v>89</v>
+      </c>
+      <c r="P3" s="10">
+        <v>32</v>
+      </c>
+      <c r="Q3" s="9">
+        <v>0</v>
+      </c>
+      <c r="R3" s="11">
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1398,54 +1395,54 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L4" s="4">
-        <v>-29.8</v>
+        <v>-28.7</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="O4" s="6">
         <v>100</v>
       </c>
-      <c r="P4" s="11">
-        <v>37</v>
-      </c>
-      <c r="Q4" s="10">
-        <v>100</v>
-      </c>
-      <c r="R4" s="10">
+      <c r="P4" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="12">
+        <v>60</v>
+      </c>
+      <c r="R4" s="13">
         <v>100</v>
       </c>
     </row>
@@ -1454,55 +1451,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="L5" s="4">
-        <v>-8.699999999999999</v>
+        <v>-15.4</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O5" s="12">
-        <v>3</v>
-      </c>
-      <c r="P5" s="13">
+        <v>158</v>
+      </c>
+      <c r="O5" s="6">
+        <v>100</v>
+      </c>
+      <c r="P5" s="9">
         <v>0</v>
       </c>
-      <c r="Q5" s="13">
+      <c r="Q5" s="9">
         <v>0</v>
       </c>
       <c r="R5" s="13">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1510,55 +1507,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="L6" s="4">
-        <v>-20.9</v>
+        <v>-25.8</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="O6" s="6">
-        <v>89</v>
-      </c>
-      <c r="P6" s="13">
+        <v>100</v>
+      </c>
+      <c r="P6" s="9">
         <v>0</v>
       </c>
       <c r="Q6" s="9">
-        <v>18</v>
-      </c>
-      <c r="R6" s="14">
-        <v>89</v>
+        <v>0</v>
+      </c>
+      <c r="R6" s="13">
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1566,55 +1563,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="L7" s="4">
+        <v>-8.9</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="O7" s="6">
         <v>49</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="L7" s="4">
-        <v>-28.7</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="O7" s="6">
-        <v>100</v>
-      </c>
-      <c r="P7" s="15">
-        <v>80</v>
-      </c>
-      <c r="Q7" s="16">
-        <v>26</v>
-      </c>
-      <c r="R7" s="17">
-        <v>68</v>
+      <c r="P7" s="8">
+        <v>16</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>29</v>
+      </c>
+      <c r="R7" s="14">
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1622,55 +1619,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L8" s="4">
-        <v>-15.4</v>
+        <v>-21.3</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="O8" s="6">
-        <v>94</v>
-      </c>
-      <c r="P8" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="13">
-        <v>1</v>
-      </c>
-      <c r="R8" s="18">
-        <v>93</v>
+        <v>100</v>
+      </c>
+      <c r="P8" s="14">
+        <v>12</v>
+      </c>
+      <c r="Q8" s="15">
+        <v>73</v>
+      </c>
+      <c r="R8" s="16">
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1678,55 +1675,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>155</v>
+        <v>65</v>
       </c>
       <c r="L9" s="4">
-        <v>-25.8</v>
+        <v>-29.3</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="O9" s="6">
-        <v>59</v>
-      </c>
-      <c r="P9" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="13">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="P9" s="17">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="18">
+        <v>93</v>
       </c>
       <c r="R9" s="19">
-        <v>43</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1734,55 +1731,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="K10" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="L10" s="4">
+        <v>-15.7</v>
+      </c>
+      <c r="M10" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="L10" s="4">
-        <v>-8.9</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>163</v>
-      </c>
       <c r="N10" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O10" s="6">
-        <v>98</v>
-      </c>
-      <c r="P10" s="17">
-        <v>72</v>
-      </c>
-      <c r="Q10" s="16">
-        <v>26</v>
-      </c>
-      <c r="R10" s="20">
-        <v>60</v>
+        <v>158</v>
+      </c>
+      <c r="O10" s="20">
+        <v>45</v>
+      </c>
+      <c r="P10" s="21">
+        <v>45</v>
+      </c>
+      <c r="Q10" s="17">
+        <v>6</v>
+      </c>
+      <c r="R10" s="22">
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1790,55 +1787,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="K11" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="L11" s="4">
+        <v>-26.2</v>
+      </c>
+      <c r="M11" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="L11" s="4">
-        <v>-21.3</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>163</v>
-      </c>
       <c r="N11" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="O11" s="6">
-        <v>51</v>
-      </c>
-      <c r="P11" s="9">
-        <v>22</v>
-      </c>
-      <c r="Q11" s="21">
-        <v>13</v>
-      </c>
-      <c r="R11" s="22">
-        <v>42</v>
+        <v>76</v>
+      </c>
+      <c r="P11" s="8">
+        <v>14</v>
+      </c>
+      <c r="Q11" s="15">
+        <v>76</v>
+      </c>
+      <c r="R11" s="14">
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1846,55 +1843,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>69</v>
+        <v>152</v>
       </c>
       <c r="L12" s="4">
-        <v>-29.3</v>
+        <v>-9.1</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="O12" s="23">
-        <v>35</v>
-      </c>
-      <c r="P12" s="9">
-        <v>20</v>
-      </c>
-      <c r="Q12" s="24">
-        <v>6</v>
-      </c>
-      <c r="R12" s="9">
-        <v>22</v>
+        <v>158</v>
+      </c>
+      <c r="O12" s="6">
+        <v>89</v>
+      </c>
+      <c r="P12" s="14">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="23">
+        <v>41</v>
+      </c>
+      <c r="R12" s="24">
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1902,55 +1899,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
+        <v>19</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="L13" s="4">
+        <v>-21.7</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="O13" s="6">
+        <v>49</v>
+      </c>
+      <c r="P13" s="9">
+        <v>2</v>
+      </c>
+      <c r="Q13" s="25">
+        <v>24</v>
+      </c>
+      <c r="R13" s="10">
         <v>29</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="L13" s="4">
-        <v>-15.7</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O13" s="6">
-        <v>100</v>
-      </c>
-      <c r="P13" s="16">
-        <v>23</v>
-      </c>
-      <c r="Q13" s="25">
-        <v>50</v>
-      </c>
-      <c r="R13" s="22">
-        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1958,55 +1955,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="L14" s="4">
-        <v>-26.2</v>
+        <v>-15.9</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="O14" s="6">
-        <v>82</v>
-      </c>
-      <c r="P14" s="9">
-        <v>20</v>
-      </c>
-      <c r="Q14" s="17">
-        <v>69</v>
-      </c>
-      <c r="R14" s="11">
-        <v>34</v>
+        <v>88</v>
+      </c>
+      <c r="P14" s="26">
+        <v>88</v>
+      </c>
+      <c r="Q14" s="15">
+        <v>75</v>
+      </c>
+      <c r="R14" s="17">
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2014,55 +2011,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="L15" s="4">
-        <v>-9.1</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="O15" s="6">
-        <v>87</v>
-      </c>
-      <c r="P15" s="25">
-        <v>52</v>
-      </c>
-      <c r="Q15" s="19">
+        <v>49</v>
+      </c>
+      <c r="P15" s="23">
+        <v>42</v>
+      </c>
+      <c r="Q15" s="21">
         <v>44</v>
       </c>
       <c r="R15" s="22">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2070,170 +2067,114 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>161</v>
+        <v>69</v>
       </c>
       <c r="L16" s="4">
-        <v>-21.7</v>
+        <v>-22</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="O16" s="6">
-        <v>98</v>
-      </c>
-      <c r="P16" s="20">
-        <v>59</v>
-      </c>
-      <c r="Q16" s="26">
-        <v>53</v>
-      </c>
-      <c r="R16" s="19">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18">
-      <c r="A17" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="2">
-        <v>23</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="L17" s="4">
-        <v>-15.9</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O17" s="6">
-        <v>99</v>
-      </c>
-      <c r="P17" s="20">
-        <v>62</v>
-      </c>
-      <c r="Q17" s="17">
-        <v>70</v>
-      </c>
-      <c r="R17" s="11">
-        <v>34</v>
+      <c r="P16" s="27">
+        <v>37</v>
+      </c>
+      <c r="Q16" s="28">
+        <v>48</v>
+      </c>
+      <c r="R16" s="25">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A17">
+  <conditionalFormatting sqref="A2:A16">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B17">
+  <conditionalFormatting sqref="B2:B16">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C17">
+  <conditionalFormatting sqref="C2:C16">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D17">
+  <conditionalFormatting sqref="D2:D16">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E17">
+  <conditionalFormatting sqref="E2:E16">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F17">
+  <conditionalFormatting sqref="F2:F16">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G17">
+  <conditionalFormatting sqref="G2:G16">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H17">
+  <conditionalFormatting sqref="H2:H16">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I17">
+  <conditionalFormatting sqref="I2:I16">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J17">
+  <conditionalFormatting sqref="J2:J16">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K17">
+  <conditionalFormatting sqref="K2:K16">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L17">
+  <conditionalFormatting sqref="L2:L16">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2252,12 +2193,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M17">
+  <conditionalFormatting sqref="M2:M16">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N17">
+  <conditionalFormatting sqref="N2:N16">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2274,22 +2215,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O17">
+  <conditionalFormatting sqref="O2:O16">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P17">
+  <conditionalFormatting sqref="P2:P16">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q17">
+  <conditionalFormatting sqref="Q2:Q16">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R17">
+  <conditionalFormatting sqref="R2:R16">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="148">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260829--01</t>
-  </si>
-  <si>
-    <t>20260829--02</t>
-  </si>
-  <si>
-    <t>20260829--03</t>
-  </si>
-  <si>
     <t>20260830--01</t>
   </si>
   <si>
@@ -115,64 +106,61 @@
     <t>20260904--02</t>
   </si>
   <si>
-    <t>05:13</t>
+    <t>20260905--01</t>
+  </si>
+  <si>
+    <t>05:54</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>05:48</t>
+  </si>
+  <si>
+    <t>05:41</t>
+  </si>
+  <si>
+    <t>02:45</t>
+  </si>
+  <si>
+    <t>05:51</t>
+  </si>
+  <si>
+    <t>04:09</t>
   </si>
   <si>
     <t>05:55</t>
   </si>
   <si>
-    <t>04:59</t>
-  </si>
-  <si>
-    <t>05:54</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>05:48</t>
+    <t>04:55</t>
+  </si>
+  <si>
+    <t>05:24</t>
   </si>
   <si>
     <t>05:42</t>
   </si>
   <si>
-    <t>02:46</t>
-  </si>
-  <si>
-    <t>05:52</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>04:56</t>
-  </si>
-  <si>
-    <t>05:24</t>
-  </si>
-  <si>
-    <t>02:40</t>
-  </si>
-  <si>
-    <t>04:41</t>
-  </si>
-  <si>
-    <t>01:09</t>
+    <t>02:41</t>
+  </si>
+  <si>
+    <t>04:08</t>
+  </si>
+  <si>
+    <t>03:14</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>03:15</t>
-  </si>
-  <si>
-    <t>05:15</t>
+    <t>05:14</t>
   </si>
   <si>
     <t>01:15</t>
   </si>
   <si>
-    <t>03:20</t>
+    <t>03:19</t>
   </si>
   <si>
     <t>05:21</t>
@@ -184,19 +172,13 @@
     <t>03:09</t>
   </si>
   <si>
-    <t>05:16</t>
-  </si>
-  <si>
-    <t>00:01</t>
-  </si>
-  <si>
-    <t>18:43:45</t>
-  </si>
-  <si>
-    <t>20:20:16</t>
-  </si>
-  <si>
-    <t>21:57:13</t>
+    <t>05:17</t>
+  </si>
+  <si>
+    <t>00:03</t>
+  </si>
+  <si>
+    <t>02:42</t>
   </si>
   <si>
     <t>19:30:29</t>
@@ -205,283 +187,262 @@
     <t>21:07:21</t>
   </si>
   <si>
-    <t>18:40:40</t>
-  </si>
-  <si>
-    <t>20:17:26</t>
-  </si>
-  <si>
-    <t>21:54:37</t>
-  </si>
-  <si>
-    <t>19:27:28</t>
-  </si>
-  <si>
-    <t>21:04:31</t>
-  </si>
-  <si>
-    <t>18:37:28</t>
-  </si>
-  <si>
-    <t>20:14:24</t>
-  </si>
-  <si>
-    <t>19:24:15</t>
-  </si>
-  <si>
-    <t>18:34:04</t>
-  </si>
-  <si>
-    <t>20:11:14</t>
-  </si>
-  <si>
-    <t>18:46:08</t>
-  </si>
-  <si>
-    <t>20:22:30</t>
-  </si>
-  <si>
-    <t>21:59:40</t>
-  </si>
-  <si>
-    <t>19:32:43</t>
+    <t>18:40:38</t>
+  </si>
+  <si>
+    <t>20:17:25</t>
+  </si>
+  <si>
+    <t>21:54:35</t>
+  </si>
+  <si>
+    <t>19:27:25</t>
+  </si>
+  <si>
+    <t>21:04:27</t>
+  </si>
+  <si>
+    <t>18:37:21</t>
+  </si>
+  <si>
+    <t>20:14:17</t>
+  </si>
+  <si>
+    <t>19:24:04</t>
+  </si>
+  <si>
+    <t>18:33:48</t>
+  </si>
+  <si>
+    <t>20:10:58</t>
+  </si>
+  <si>
+    <t>19:20:30</t>
+  </si>
+  <si>
+    <t>19:32:44</t>
   </si>
   <si>
     <t>21:09:42</t>
   </si>
   <si>
-    <t>18:42:55</t>
-  </si>
-  <si>
-    <t>20:19:43</t>
-  </si>
-  <si>
-    <t>21:57:43</t>
-  </si>
-  <si>
-    <t>19:29:43</t>
-  </si>
-  <si>
-    <t>21:07:11</t>
-  </si>
-  <si>
-    <t>18:39:42</t>
-  </si>
-  <si>
-    <t>20:16:52</t>
-  </si>
-  <si>
-    <t>19:26:37</t>
-  </si>
-  <si>
-    <t>18:36:21</t>
-  </si>
-  <si>
-    <t>20:14:23</t>
-  </si>
-  <si>
-    <t>18:48:44</t>
-  </si>
-  <si>
-    <t>20:25:27</t>
-  </si>
-  <si>
-    <t>22:02:09</t>
-  </si>
-  <si>
-    <t>19:35:40</t>
+    <t>18:42:54</t>
+  </si>
+  <si>
+    <t>20:19:42</t>
+  </si>
+  <si>
+    <t>21:57:42</t>
+  </si>
+  <si>
+    <t>19:29:40</t>
+  </si>
+  <si>
+    <t>21:07:07</t>
+  </si>
+  <si>
+    <t>18:39:35</t>
+  </si>
+  <si>
+    <t>20:16:45</t>
+  </si>
+  <si>
+    <t>19:26:25</t>
+  </si>
+  <si>
+    <t>18:36:05</t>
+  </si>
+  <si>
+    <t>20:14:06</t>
+  </si>
+  <si>
+    <t>19:23:10</t>
+  </si>
+  <si>
+    <t>19:35:41</t>
   </si>
   <si>
     <t>21:12:24</t>
   </si>
   <si>
-    <t>18:45:49</t>
-  </si>
-  <si>
-    <t>20:22:34</t>
-  </si>
-  <si>
-    <t>21:59:06</t>
-  </si>
-  <si>
-    <t>19:32:39</t>
-  </si>
-  <si>
-    <t>21:09:16</t>
-  </si>
-  <si>
-    <t>18:42:39</t>
-  </si>
-  <si>
-    <t>20:19:20</t>
-  </si>
-  <si>
-    <t>19:29:19</t>
-  </si>
-  <si>
-    <t>18:39:12</t>
-  </si>
-  <si>
-    <t>20:15:43</t>
-  </si>
-  <si>
-    <t>18:51:21</t>
-  </si>
-  <si>
-    <t>20:28:25</t>
-  </si>
-  <si>
-    <t>22:04:39</t>
-  </si>
-  <si>
-    <t>19:38:37</t>
+    <t>18:45:48</t>
+  </si>
+  <si>
+    <t>20:22:33</t>
+  </si>
+  <si>
+    <t>21:59:05</t>
+  </si>
+  <si>
+    <t>19:32:35</t>
+  </si>
+  <si>
+    <t>21:09:12</t>
+  </si>
+  <si>
+    <t>18:42:32</t>
+  </si>
+  <si>
+    <t>20:19:13</t>
+  </si>
+  <si>
+    <t>19:29:07</t>
+  </si>
+  <si>
+    <t>18:38:56</t>
+  </si>
+  <si>
+    <t>20:15:26</t>
+  </si>
+  <si>
+    <t>19:25:14</t>
+  </si>
+  <si>
+    <t>19:38:38</t>
   </si>
   <si>
     <t>21:15:07</t>
   </si>
   <si>
-    <t>18:48:43</t>
-  </si>
-  <si>
-    <t>20:25:25</t>
-  </si>
-  <si>
-    <t>22:00:29</t>
-  </si>
-  <si>
-    <t>19:35:35</t>
-  </si>
-  <si>
-    <t>21:11:21</t>
-  </si>
-  <si>
-    <t>18:45:37</t>
-  </si>
-  <si>
-    <t>20:21:48</t>
-  </si>
-  <si>
-    <t>19:32:01</t>
-  </si>
-  <si>
-    <t>18:42:03</t>
-  </si>
-  <si>
-    <t>20:17:03</t>
-  </si>
-  <si>
-    <t>18:53:44</t>
-  </si>
-  <si>
-    <t>20:30:39</t>
-  </si>
-  <si>
-    <t>22:07:06</t>
+    <t>18:48:42</t>
+  </si>
+  <si>
+    <t>20:25:23</t>
+  </si>
+  <si>
+    <t>22:00:27</t>
+  </si>
+  <si>
+    <t>19:35:31</t>
+  </si>
+  <si>
+    <t>21:11:16</t>
+  </si>
+  <si>
+    <t>18:45:30</t>
+  </si>
+  <si>
+    <t>20:21:40</t>
+  </si>
+  <si>
+    <t>19:31:49</t>
+  </si>
+  <si>
+    <t>18:41:47</t>
+  </si>
+  <si>
+    <t>20:16:47</t>
+  </si>
+  <si>
+    <t>19:27:18</t>
   </si>
   <si>
     <t>19:40:52</t>
   </si>
   <si>
-    <t>21:17:28</t>
-  </si>
-  <si>
-    <t>18:50:59</t>
-  </si>
-  <si>
-    <t>20:27:42</t>
-  </si>
-  <si>
-    <t>22:03:35</t>
-  </si>
-  <si>
-    <t>19:37:50</t>
-  </si>
-  <si>
-    <t>21:14:00</t>
-  </si>
-  <si>
-    <t>18:47:51</t>
-  </si>
-  <si>
-    <t>20:24:15</t>
-  </si>
-  <si>
-    <t>19:34:21</t>
-  </si>
-  <si>
-    <t>18:44:20</t>
-  </si>
-  <si>
-    <t>20:20:11</t>
+    <t>21:17:27</t>
+  </si>
+  <si>
+    <t>18:50:57</t>
+  </si>
+  <si>
+    <t>20:27:40</t>
+  </si>
+  <si>
+    <t>22:03:33</t>
+  </si>
+  <si>
+    <t>19:37:45</t>
+  </si>
+  <si>
+    <t>21:13:56</t>
+  </si>
+  <si>
+    <t>18:47:44</t>
+  </si>
+  <si>
+    <t>20:24:08</t>
+  </si>
+  <si>
+    <t>19:34:10</t>
+  </si>
+  <si>
+    <t>18:44:03</t>
+  </si>
+  <si>
+    <t>20:19:54</t>
+  </si>
+  <si>
+    <t>19:29:58</t>
+  </si>
+  <si>
+    <t>29°</t>
+  </si>
+  <si>
+    <t>6°</t>
+  </si>
+  <si>
+    <t>14°</t>
+  </si>
+  <si>
+    <t>18°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>28°</t>
+  </si>
+  <si>
+    <t>5°</t>
+  </si>
+  <si>
+    <t>15°</t>
+  </si>
+  <si>
+    <t>22°</t>
   </si>
   <si>
     <t>13°</t>
   </si>
   <si>
-    <t>18°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>29°</t>
-  </si>
-  <si>
-    <t>6°</t>
-  </si>
-  <si>
-    <t>14°</t>
-  </si>
-  <si>
-    <t>28°</t>
-  </si>
-  <si>
-    <t>5°</t>
-  </si>
-  <si>
-    <t>15°</t>
-  </si>
-  <si>
-    <t>22°</t>
-  </si>
-  <si>
     <t>10°</t>
   </si>
   <si>
-    <t>18:50:49</t>
-  </si>
-  <si>
-    <t>20:23:39</t>
-  </si>
-  <si>
     <t>19:35:58</t>
   </si>
   <si>
     <t>21:08:47</t>
   </si>
   <si>
-    <t>18:48:10</t>
-  </si>
-  <si>
-    <t>20:20:58</t>
-  </si>
-  <si>
-    <t>19:33:03</t>
-  </si>
-  <si>
-    <t>21:05:51</t>
-  </si>
-  <si>
-    <t>18:45:03</t>
-  </si>
-  <si>
-    <t>20:17:50</t>
-  </si>
-  <si>
-    <t>19:29:46</t>
-  </si>
-  <si>
-    <t>18:41:37</t>
+    <t>18:48:08</t>
+  </si>
+  <si>
+    <t>20:20:57</t>
+  </si>
+  <si>
+    <t>19:32:59</t>
+  </si>
+  <si>
+    <t>21:05:47</t>
+  </si>
+  <si>
+    <t>18:44:56</t>
+  </si>
+  <si>
+    <t>20:17:43</t>
+  </si>
+  <si>
+    <t>19:29:34</t>
+  </si>
+  <si>
+    <t>18:41:22</t>
+  </si>
+  <si>
+    <t>20:14:09</t>
+  </si>
+  <si>
+    <t>19:25:52</t>
   </si>
   <si>
     <t>A+B</t>
@@ -530,7 +491,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -551,7 +512,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -563,19 +548,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -587,19 +566,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -617,67 +608,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -718,7 +649,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -787,21 +718,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1205,7 +1121,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1283,55 +1199,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="L2" s="4">
-        <v>-8.699999999999999</v>
+        <v>-15.4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="O2" s="6">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="P2" s="7">
-        <v>65</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>13</v>
-      </c>
-      <c r="R2" s="9">
         <v>0</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="8">
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1339,55 +1255,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="L3" s="4">
-        <v>-20.9</v>
+        <v>-25.8</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="O3" s="6">
-        <v>89</v>
-      </c>
-      <c r="P3" s="10">
-        <v>32</v>
-      </c>
-      <c r="Q3" s="9">
+        <v>83</v>
+      </c>
+      <c r="P3" s="7">
         <v>0</v>
       </c>
-      <c r="R3" s="11">
-        <v>84</v>
+      <c r="Q3" s="7">
+        <v>0</v>
+      </c>
+      <c r="R3" s="9">
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1395,55 +1311,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>60</v>
+        <v>133</v>
       </c>
       <c r="L4" s="4">
-        <v>-28.7</v>
+        <v>-8.9</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="O4" s="6">
-        <v>100</v>
-      </c>
-      <c r="P4" s="9">
+        <v>145</v>
+      </c>
+      <c r="O4" s="10">
+        <v>19</v>
+      </c>
+      <c r="P4" s="11">
+        <v>9</v>
+      </c>
+      <c r="Q4" s="7">
         <v>0</v>
       </c>
-      <c r="Q4" s="12">
-        <v>60</v>
-      </c>
-      <c r="R4" s="13">
-        <v>100</v>
+      <c r="R4" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1451,55 +1367,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-21.3</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="O5" s="6">
         <v>76</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="L5" s="4">
-        <v>-15.4</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="O5" s="6">
-        <v>100</v>
-      </c>
-      <c r="P5" s="9">
-        <v>0</v>
+      <c r="P5" s="12">
+        <v>13</v>
       </c>
       <c r="Q5" s="9">
-        <v>0</v>
-      </c>
-      <c r="R5" s="13">
-        <v>100</v>
+        <v>69</v>
+      </c>
+      <c r="R5" s="11">
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1507,55 +1423,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="K6" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-29.3</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="L6" s="4">
-        <v>-25.8</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="O6" s="6">
-        <v>100</v>
-      </c>
-      <c r="P6" s="9">
+        <v>55</v>
+      </c>
+      <c r="P6" s="7">
         <v>0</v>
       </c>
-      <c r="Q6" s="9">
-        <v>0</v>
-      </c>
-      <c r="R6" s="13">
-        <v>100</v>
+      <c r="Q6" s="13">
+        <v>32</v>
+      </c>
+      <c r="R6" s="14">
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1563,55 +1479,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="L7" s="4">
-        <v>-8.9</v>
+        <v>-15.6</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="O7" s="6">
-        <v>49</v>
-      </c>
-      <c r="P7" s="8">
-        <v>16</v>
-      </c>
-      <c r="Q7" s="10">
-        <v>29</v>
-      </c>
-      <c r="R7" s="14">
-        <v>9</v>
+        <v>58</v>
+      </c>
+      <c r="P7" s="15">
+        <v>58</v>
+      </c>
+      <c r="Q7" s="16">
+        <v>23</v>
+      </c>
+      <c r="R7" s="12">
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1619,55 +1535,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="L8" s="4">
-        <v>-21.3</v>
+        <v>-26.2</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="O8" s="6">
-        <v>100</v>
-      </c>
-      <c r="P8" s="14">
-        <v>12</v>
-      </c>
-      <c r="Q8" s="15">
-        <v>73</v>
-      </c>
-      <c r="R8" s="16">
-        <v>80</v>
+        <v>146</v>
+      </c>
+      <c r="O8" s="10">
+        <v>44</v>
+      </c>
+      <c r="P8" s="17">
+        <v>44</v>
+      </c>
+      <c r="Q8" s="17">
+        <v>44</v>
+      </c>
+      <c r="R8" s="18">
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1675,55 +1591,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>65</v>
+        <v>137</v>
       </c>
       <c r="L9" s="4">
-        <v>-29.3</v>
+        <v>-9.1</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="O9" s="6">
-        <v>97</v>
-      </c>
-      <c r="P9" s="17">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="18">
-        <v>93</v>
-      </c>
-      <c r="R9" s="19">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="P9" s="19">
+        <v>55</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>9</v>
+      </c>
+      <c r="R9" s="16">
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1731,55 +1647,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="L10" s="4">
-        <v>-15.7</v>
+        <v>-21.6</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="O10" s="20">
-        <v>45</v>
-      </c>
-      <c r="P10" s="21">
-        <v>45</v>
-      </c>
-      <c r="Q10" s="17">
-        <v>6</v>
-      </c>
-      <c r="R10" s="22">
-        <v>20</v>
+        <v>145</v>
+      </c>
+      <c r="O10" s="6">
+        <v>65</v>
+      </c>
+      <c r="P10" s="20">
+        <v>65</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>17</v>
+      </c>
+      <c r="R10" s="14">
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1787,55 +1703,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="L11" s="4">
-        <v>-26.2</v>
+        <v>-15.9</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="O11" s="6">
-        <v>76</v>
-      </c>
-      <c r="P11" s="8">
-        <v>14</v>
-      </c>
-      <c r="Q11" s="15">
-        <v>76</v>
-      </c>
-      <c r="R11" s="14">
-        <v>8</v>
+        <v>100</v>
+      </c>
+      <c r="P11" s="17">
+        <v>47</v>
+      </c>
+      <c r="Q11" s="21">
+        <v>80</v>
+      </c>
+      <c r="R11" s="8">
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1843,55 +1759,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="L12" s="4">
-        <v>-9.1</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="O12" s="6">
-        <v>89</v>
-      </c>
-      <c r="P12" s="14">
-        <v>8</v>
-      </c>
-      <c r="Q12" s="23">
-        <v>41</v>
-      </c>
-      <c r="R12" s="24">
-        <v>70</v>
+        <v>67</v>
+      </c>
+      <c r="P12" s="20">
+        <v>67</v>
+      </c>
+      <c r="Q12" s="14">
+        <v>48</v>
+      </c>
+      <c r="R12" s="22">
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1899,55 +1815,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="J13" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="L13" s="4">
-        <v>-21.7</v>
+        <v>-21.9</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="O13" s="6">
-        <v>49</v>
-      </c>
-      <c r="P13" s="9">
-        <v>2</v>
-      </c>
-      <c r="Q13" s="25">
-        <v>24</v>
-      </c>
-      <c r="R13" s="10">
-        <v>29</v>
+        <v>62</v>
+      </c>
+      <c r="P13" s="15">
+        <v>59</v>
+      </c>
+      <c r="Q13" s="23">
+        <v>39</v>
+      </c>
+      <c r="R13" s="12">
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1955,226 +1871,114 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="J14" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="K14" s="1" t="s">
-        <v>154</v>
-      </c>
       <c r="L14" s="4">
-        <v>-15.9</v>
+        <v>-16.1</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="O14" s="6">
-        <v>88</v>
-      </c>
-      <c r="P14" s="26">
-        <v>88</v>
-      </c>
-      <c r="Q14" s="15">
-        <v>75</v>
-      </c>
-      <c r="R14" s="17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
-      <c r="A15" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="2">
-        <v>27</v>
-      </c>
-      <c r="C15" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="P14" s="23">
         <v>39</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="L15" s="4">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="O15" s="6">
-        <v>49</v>
-      </c>
-      <c r="P15" s="23">
-        <v>42</v>
-      </c>
-      <c r="Q15" s="21">
-        <v>44</v>
-      </c>
-      <c r="R15" s="22">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
-      <c r="A16" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="2">
-        <v>12</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="L16" s="4">
-        <v>-22</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="O16" s="6">
-        <v>58</v>
-      </c>
-      <c r="P16" s="27">
-        <v>37</v>
-      </c>
-      <c r="Q16" s="28">
-        <v>48</v>
-      </c>
-      <c r="R16" s="25">
-        <v>24</v>
+      <c r="Q14" s="13">
+        <v>30</v>
+      </c>
+      <c r="R14" s="14">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A16">
+  <conditionalFormatting sqref="A2:A14">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B16">
+  <conditionalFormatting sqref="B2:B14">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C16">
+  <conditionalFormatting sqref="C2:C14">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D16">
+  <conditionalFormatting sqref="D2:D14">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E16">
+  <conditionalFormatting sqref="E2:E14">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F16">
+  <conditionalFormatting sqref="F2:F14">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G16">
+  <conditionalFormatting sqref="G2:G14">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H16">
+  <conditionalFormatting sqref="H2:H14">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I16">
+  <conditionalFormatting sqref="I2:I14">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J16">
+  <conditionalFormatting sqref="J2:J14">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K16">
+  <conditionalFormatting sqref="K2:K14">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L16">
+  <conditionalFormatting sqref="L2:L14">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2193,12 +1997,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M16">
+  <conditionalFormatting sqref="M2:M14">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N16">
+  <conditionalFormatting sqref="N2:N14">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2215,22 +2019,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O16">
+  <conditionalFormatting sqref="O2:O14">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P16">
+  <conditionalFormatting sqref="P2:P14">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q16">
+  <conditionalFormatting sqref="Q2:Q14">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R16">
+  <conditionalFormatting sqref="R2:R14">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="138">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260830--01</t>
-  </si>
-  <si>
-    <t>20260830--02</t>
-  </si>
-  <si>
     <t>20260831--01</t>
   </si>
   <si>
@@ -109,10 +103,7 @@
     <t>20260905--01</t>
   </si>
   <si>
-    <t>05:54</t>
-  </si>
-  <si>
-    <t>05:25</t>
+    <t>20260906--01</t>
   </si>
   <si>
     <t>05:48</t>
@@ -148,18 +139,15 @@
     <t>04:08</t>
   </si>
   <si>
-    <t>03:14</t>
+    <t>05:14</t>
+  </si>
+  <si>
+    <t>01:15</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>05:14</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
     <t>03:19</t>
   </si>
   <si>
@@ -181,12 +169,6 @@
     <t>02:42</t>
   </si>
   <si>
-    <t>19:30:29</t>
-  </si>
-  <si>
-    <t>21:07:21</t>
-  </si>
-  <si>
     <t>18:40:38</t>
   </si>
   <si>
@@ -220,10 +202,7 @@
     <t>19:20:30</t>
   </si>
   <si>
-    <t>19:32:44</t>
-  </si>
-  <si>
-    <t>21:09:42</t>
+    <t>18:30:00</t>
   </si>
   <si>
     <t>18:42:54</t>
@@ -259,10 +238,7 @@
     <t>19:23:10</t>
   </si>
   <si>
-    <t>19:35:41</t>
-  </si>
-  <si>
-    <t>21:12:24</t>
+    <t>18:32:28</t>
   </si>
   <si>
     <t>18:45:48</t>
@@ -298,10 +274,7 @@
     <t>19:25:14</t>
   </si>
   <si>
-    <t>19:38:38</t>
-  </si>
-  <si>
-    <t>21:15:07</t>
+    <t>18:34:56</t>
   </si>
   <si>
     <t>18:48:42</t>
@@ -337,10 +310,7 @@
     <t>19:27:18</t>
   </si>
   <si>
-    <t>19:40:52</t>
-  </si>
-  <si>
-    <t>21:17:27</t>
+    <t>18:37:23</t>
   </si>
   <si>
     <t>18:50:57</t>
@@ -376,10 +346,7 @@
     <t>19:29:58</t>
   </si>
   <si>
-    <t>29°</t>
-  </si>
-  <si>
-    <t>6°</t>
+    <t>18:39:51</t>
   </si>
   <si>
     <t>14°</t>
@@ -409,10 +376,7 @@
     <t>10°</t>
   </si>
   <si>
-    <t>19:35:58</t>
-  </si>
-  <si>
-    <t>21:08:47</t>
+    <t>9°</t>
   </si>
   <si>
     <t>18:48:08</t>
@@ -445,19 +409,25 @@
     <t>19:25:52</t>
   </si>
   <si>
+    <t>18:37:33</t>
+  </si>
+  <si>
     <t>A+B</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
 </sst>
 </file>
@@ -491,7 +461,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -506,109 +476,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -649,7 +631,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -718,6 +700,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1121,7 +1109,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1199,55 +1187,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>28</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="L2" s="4">
-        <v>-15.4</v>
+        <v>-8.9</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="O2" s="6">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="P2" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
-        <v>100</v>
+        <v>7</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>35</v>
+      </c>
+      <c r="R2" s="9">
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1255,55 +1243,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="K3" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L3" s="4">
+        <v>-21.3</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="L3" s="4">
-        <v>-25.8</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="N3" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="O3" s="6">
-        <v>83</v>
+        <v>135</v>
+      </c>
+      <c r="O3" s="10">
+        <v>34</v>
       </c>
       <c r="P3" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="7">
-        <v>0</v>
-      </c>
-      <c r="R3" s="9">
-        <v>72</v>
+        <v>6</v>
+      </c>
+      <c r="Q3" s="11">
+        <v>30</v>
+      </c>
+      <c r="R3" s="12">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1311,55 +1299,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="K4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-29.3</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="L4" s="4">
-        <v>-8.9</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="N4" s="1" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="O4" s="10">
-        <v>19</v>
-      </c>
-      <c r="P4" s="11">
-        <v>9</v>
-      </c>
-      <c r="Q4" s="7">
-        <v>0</v>
-      </c>
-      <c r="R4" s="7">
+        <v>79</v>
+      </c>
+      <c r="P4" s="12">
         <v>2</v>
+      </c>
+      <c r="Q4" s="13">
+        <v>25</v>
+      </c>
+      <c r="R4" s="14">
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1367,55 +1355,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>134</v>
-      </c>
       <c r="L5" s="4">
-        <v>-21.3</v>
+        <v>-15.6</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O5" s="6">
-        <v>76</v>
-      </c>
-      <c r="P5" s="12">
-        <v>13</v>
-      </c>
-      <c r="Q5" s="9">
-        <v>69</v>
-      </c>
-      <c r="R5" s="11">
-        <v>8</v>
+        <v>135</v>
+      </c>
+      <c r="O5" s="10">
+        <v>86</v>
+      </c>
+      <c r="P5" s="15">
+        <v>80</v>
+      </c>
+      <c r="Q5" s="11">
+        <v>28</v>
+      </c>
+      <c r="R5" s="16">
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1423,55 +1411,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="J6" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="L6" s="4">
-        <v>-29.3</v>
+        <v>-26.2</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="O6" s="6">
-        <v>55</v>
+        <v>137</v>
+      </c>
+      <c r="O6" s="10">
+        <v>65</v>
       </c>
       <c r="P6" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="13">
-        <v>32</v>
-      </c>
-      <c r="R6" s="14">
-        <v>50</v>
+        <v>7</v>
+      </c>
+      <c r="Q6" s="16">
+        <v>42</v>
+      </c>
+      <c r="R6" s="11">
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1479,55 +1467,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="J7" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="4">
+        <v>-9.1</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="L7" s="4">
-        <v>-15.6</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O7" s="6">
+      <c r="O7" s="10">
+        <v>75</v>
+      </c>
+      <c r="P7" s="17">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="18">
         <v>58</v>
       </c>
-      <c r="P7" s="15">
-        <v>58</v>
-      </c>
-      <c r="Q7" s="16">
-        <v>23</v>
-      </c>
-      <c r="R7" s="12">
-        <v>14</v>
+      <c r="R7" s="11">
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1535,55 +1523,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="J8" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>136</v>
-      </c>
       <c r="L8" s="4">
-        <v>-26.2</v>
+        <v>-21.6</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="O8" s="10">
-        <v>44</v>
-      </c>
-      <c r="P8" s="17">
-        <v>44</v>
-      </c>
-      <c r="Q8" s="17">
-        <v>44</v>
-      </c>
-      <c r="R8" s="18">
-        <v>20</v>
+        <v>80</v>
+      </c>
+      <c r="P8" s="19">
+        <v>15</v>
+      </c>
+      <c r="Q8" s="20">
+        <v>48</v>
+      </c>
+      <c r="R8" s="8">
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1591,55 +1579,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="L9" s="4">
-        <v>-9.1</v>
+        <v>-15.9</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O9" s="6">
-        <v>55</v>
-      </c>
-      <c r="P9" s="19">
-        <v>55</v>
-      </c>
-      <c r="Q9" s="11">
+        <v>135</v>
+      </c>
+      <c r="O9" s="10">
+        <v>100</v>
+      </c>
+      <c r="P9" s="17">
         <v>9</v>
       </c>
-      <c r="R9" s="16">
-        <v>25</v>
+      <c r="Q9" s="15">
+        <v>80</v>
+      </c>
+      <c r="R9" s="21">
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1647,55 +1635,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="L10" s="4">
-        <v>-21.6</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O10" s="6">
-        <v>65</v>
-      </c>
-      <c r="P10" s="20">
-        <v>65</v>
-      </c>
-      <c r="Q10" s="12">
-        <v>17</v>
-      </c>
-      <c r="R10" s="14">
-        <v>49</v>
+        <v>135</v>
+      </c>
+      <c r="O10" s="10">
+        <v>99</v>
+      </c>
+      <c r="P10" s="22">
+        <v>74</v>
+      </c>
+      <c r="Q10" s="23">
+        <v>53</v>
+      </c>
+      <c r="R10" s="24">
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1703,55 +1691,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="L11" s="4">
-        <v>-15.9</v>
+        <v>-21.9</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O11" s="6">
+        <v>136</v>
+      </c>
+      <c r="O11" s="10">
         <v>100</v>
       </c>
-      <c r="P11" s="17">
-        <v>47</v>
-      </c>
-      <c r="Q11" s="21">
-        <v>80</v>
-      </c>
-      <c r="R11" s="8">
-        <v>100</v>
+      <c r="P11" s="25">
+        <v>72</v>
+      </c>
+      <c r="Q11" s="18">
+        <v>62</v>
+      </c>
+      <c r="R11" s="21">
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1759,55 +1747,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="L12" s="4">
-        <v>-9.300000000000001</v>
+        <v>-16.1</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="O12" s="6">
-        <v>67</v>
-      </c>
-      <c r="P12" s="20">
-        <v>67</v>
-      </c>
-      <c r="Q12" s="14">
-        <v>48</v>
-      </c>
-      <c r="R12" s="22">
-        <v>4</v>
+        <v>19</v>
+      </c>
+      <c r="P12" s="7">
+        <v>6</v>
+      </c>
+      <c r="Q12" s="19">
+        <v>14</v>
+      </c>
+      <c r="R12" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1815,170 +1803,114 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="L13" s="4">
-        <v>-21.9</v>
+        <v>-9.4</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="O13" s="6">
-        <v>62</v>
-      </c>
-      <c r="P13" s="15">
-        <v>59</v>
-      </c>
-      <c r="Q13" s="23">
-        <v>39</v>
-      </c>
-      <c r="R13" s="12">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
-      <c r="A14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="2">
-        <v>16</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="L14" s="4">
-        <v>-16.1</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O14" s="6">
-        <v>74</v>
-      </c>
-      <c r="P14" s="23">
-        <v>39</v>
-      </c>
-      <c r="Q14" s="13">
-        <v>30</v>
-      </c>
-      <c r="R14" s="14">
-        <v>50</v>
+        <v>23</v>
+      </c>
+      <c r="P13" s="17">
+        <v>11</v>
+      </c>
+      <c r="Q13" s="12">
+        <v>0</v>
+      </c>
+      <c r="R13" s="13">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A14">
+  <conditionalFormatting sqref="A2:A13">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B14">
+  <conditionalFormatting sqref="B2:B13">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C14">
+  <conditionalFormatting sqref="C2:C13">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D14">
+  <conditionalFormatting sqref="D2:D13">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E14">
+  <conditionalFormatting sqref="E2:E13">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F14">
+  <conditionalFormatting sqref="F2:F13">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G14">
+  <conditionalFormatting sqref="G2:G13">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H14">
+  <conditionalFormatting sqref="H2:H13">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I14">
+  <conditionalFormatting sqref="I2:I13">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J14">
+  <conditionalFormatting sqref="J2:J13">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K14">
+  <conditionalFormatting sqref="K2:K13">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L14">
+  <conditionalFormatting sqref="L2:L13">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1997,12 +1929,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M14">
+  <conditionalFormatting sqref="M2:M13">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N14">
+  <conditionalFormatting sqref="N2:N13">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2019,22 +1951,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O14">
+  <conditionalFormatting sqref="O2:O13">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P14">
+  <conditionalFormatting sqref="P2:P13">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q14">
+  <conditionalFormatting sqref="Q2:Q13">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R14">
+  <conditionalFormatting sqref="R2:R13">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="111">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260831--01</t>
-  </si>
-  <si>
-    <t>20260831--02</t>
-  </si>
-  <si>
-    <t>20260831--03</t>
-  </si>
-  <si>
     <t>20260901--01</t>
   </si>
   <si>
@@ -106,264 +97,198 @@
     <t>20260906--01</t>
   </si>
   <si>
-    <t>05:48</t>
+    <t>05:51</t>
+  </si>
+  <si>
+    <t>04:08</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>04:55</t>
+  </si>
+  <si>
+    <t>05:23</t>
   </si>
   <si>
     <t>05:41</t>
   </si>
   <si>
-    <t>02:45</t>
-  </si>
-  <si>
-    <t>05:51</t>
-  </si>
-  <si>
-    <t>04:09</t>
-  </si>
-  <si>
-    <t>05:55</t>
-  </si>
-  <si>
-    <t>04:55</t>
-  </si>
-  <si>
-    <t>05:24</t>
-  </si>
-  <si>
-    <t>05:42</t>
+    <t>02:40</t>
+  </si>
+  <si>
+    <t>04:07</t>
+  </si>
+  <si>
+    <t>03:19</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>05:21</t>
+  </si>
+  <si>
+    <t>00:58</t>
+  </si>
+  <si>
+    <t>03:08</t>
+  </si>
+  <si>
+    <t>05:16</t>
+  </si>
+  <si>
+    <t>00:02</t>
   </si>
   <si>
     <t>02:41</t>
   </si>
   <si>
-    <t>04:08</t>
-  </si>
-  <si>
-    <t>05:14</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>03:19</t>
-  </si>
-  <si>
-    <t>05:21</t>
-  </si>
-  <si>
-    <t>00:58</t>
-  </si>
-  <si>
-    <t>03:09</t>
-  </si>
-  <si>
-    <t>05:17</t>
-  </si>
-  <si>
-    <t>00:03</t>
-  </si>
-  <si>
-    <t>02:42</t>
-  </si>
-  <si>
-    <t>18:40:38</t>
-  </si>
-  <si>
-    <t>20:17:25</t>
-  </si>
-  <si>
-    <t>21:54:35</t>
-  </si>
-  <si>
-    <t>19:27:25</t>
-  </si>
-  <si>
-    <t>21:04:27</t>
-  </si>
-  <si>
-    <t>18:37:21</t>
-  </si>
-  <si>
-    <t>20:14:17</t>
-  </si>
-  <si>
-    <t>19:24:04</t>
-  </si>
-  <si>
-    <t>18:33:48</t>
-  </si>
-  <si>
-    <t>20:10:58</t>
-  </si>
-  <si>
-    <t>19:20:30</t>
-  </si>
-  <si>
-    <t>18:30:00</t>
-  </si>
-  <si>
-    <t>18:42:54</t>
-  </si>
-  <si>
-    <t>20:19:42</t>
-  </si>
-  <si>
-    <t>21:57:42</t>
-  </si>
-  <si>
-    <t>19:29:40</t>
-  </si>
-  <si>
-    <t>21:07:07</t>
-  </si>
-  <si>
-    <t>18:39:35</t>
-  </si>
-  <si>
-    <t>20:16:45</t>
-  </si>
-  <si>
-    <t>19:26:25</t>
-  </si>
-  <si>
-    <t>18:36:05</t>
-  </si>
-  <si>
-    <t>20:14:06</t>
-  </si>
-  <si>
-    <t>19:23:10</t>
-  </si>
-  <si>
-    <t>18:32:28</t>
-  </si>
-  <si>
-    <t>18:45:48</t>
-  </si>
-  <si>
-    <t>20:22:33</t>
-  </si>
-  <si>
-    <t>21:59:05</t>
-  </si>
-  <si>
-    <t>19:32:35</t>
-  </si>
-  <si>
-    <t>21:09:12</t>
-  </si>
-  <si>
-    <t>18:42:32</t>
-  </si>
-  <si>
-    <t>20:19:13</t>
-  </si>
-  <si>
-    <t>19:29:07</t>
-  </si>
-  <si>
-    <t>18:38:56</t>
-  </si>
-  <si>
-    <t>20:15:26</t>
-  </si>
-  <si>
-    <t>19:25:14</t>
-  </si>
-  <si>
-    <t>18:34:56</t>
-  </si>
-  <si>
-    <t>18:48:42</t>
-  </si>
-  <si>
-    <t>20:25:23</t>
-  </si>
-  <si>
-    <t>22:00:27</t>
-  </si>
-  <si>
-    <t>19:35:31</t>
-  </si>
-  <si>
-    <t>21:11:16</t>
-  </si>
-  <si>
-    <t>18:45:30</t>
-  </si>
-  <si>
-    <t>20:21:40</t>
-  </si>
-  <si>
-    <t>19:31:49</t>
-  </si>
-  <si>
-    <t>18:41:47</t>
-  </si>
-  <si>
-    <t>20:16:47</t>
-  </si>
-  <si>
-    <t>19:27:18</t>
+    <t>19:27:26</t>
+  </si>
+  <si>
+    <t>21:04:28</t>
   </si>
   <si>
     <t>18:37:23</t>
   </si>
   <si>
-    <t>18:50:57</t>
-  </si>
-  <si>
-    <t>20:27:40</t>
-  </si>
-  <si>
-    <t>22:03:33</t>
-  </si>
-  <si>
-    <t>19:37:45</t>
-  </si>
-  <si>
-    <t>21:13:56</t>
-  </si>
-  <si>
-    <t>18:47:44</t>
-  </si>
-  <si>
-    <t>20:24:08</t>
-  </si>
-  <si>
-    <t>19:34:10</t>
-  </si>
-  <si>
-    <t>18:44:03</t>
-  </si>
-  <si>
-    <t>20:19:54</t>
-  </si>
-  <si>
-    <t>19:29:58</t>
-  </si>
-  <si>
-    <t>18:39:51</t>
+    <t>20:14:20</t>
+  </si>
+  <si>
+    <t>19:24:09</t>
+  </si>
+  <si>
+    <t>18:33:55</t>
+  </si>
+  <si>
+    <t>20:11:05</t>
+  </si>
+  <si>
+    <t>19:20:39</t>
+  </si>
+  <si>
+    <t>18:30:13</t>
+  </si>
+  <si>
+    <t>19:29:41</t>
+  </si>
+  <si>
+    <t>21:07:09</t>
+  </si>
+  <si>
+    <t>18:39:37</t>
+  </si>
+  <si>
+    <t>20:16:48</t>
+  </si>
+  <si>
+    <t>19:26:30</t>
+  </si>
+  <si>
+    <t>18:36:12</t>
+  </si>
+  <si>
+    <t>20:14:13</t>
+  </si>
+  <si>
+    <t>19:23:20</t>
+  </si>
+  <si>
+    <t>18:32:41</t>
+  </si>
+  <si>
+    <t>19:32:36</t>
+  </si>
+  <si>
+    <t>21:09:13</t>
+  </si>
+  <si>
+    <t>18:42:35</t>
+  </si>
+  <si>
+    <t>20:19:15</t>
+  </si>
+  <si>
+    <t>19:29:12</t>
+  </si>
+  <si>
+    <t>18:39:03</t>
+  </si>
+  <si>
+    <t>20:15:33</t>
+  </si>
+  <si>
+    <t>19:25:24</t>
+  </si>
+  <si>
+    <t>18:35:08</t>
+  </si>
+  <si>
+    <t>19:35:32</t>
+  </si>
+  <si>
+    <t>21:11:17</t>
+  </si>
+  <si>
+    <t>18:45:32</t>
+  </si>
+  <si>
+    <t>20:21:43</t>
+  </si>
+  <si>
+    <t>19:31:53</t>
+  </si>
+  <si>
+    <t>18:41:53</t>
+  </si>
+  <si>
+    <t>20:16:53</t>
+  </si>
+  <si>
+    <t>19:27:27</t>
+  </si>
+  <si>
+    <t>18:37:36</t>
+  </si>
+  <si>
+    <t>19:37:46</t>
+  </si>
+  <si>
+    <t>21:13:57</t>
+  </si>
+  <si>
+    <t>18:47:46</t>
+  </si>
+  <si>
+    <t>20:24:10</t>
+  </si>
+  <si>
+    <t>19:34:14</t>
+  </si>
+  <si>
+    <t>18:44:10</t>
+  </si>
+  <si>
+    <t>20:20:01</t>
+  </si>
+  <si>
+    <t>19:30:07</t>
+  </si>
+  <si>
+    <t>18:40:03</t>
+  </si>
+  <si>
+    <t>28°</t>
+  </si>
+  <si>
+    <t>5°</t>
   </si>
   <si>
     <t>14°</t>
   </si>
   <si>
-    <t>18°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>28°</t>
-  </si>
-  <si>
-    <t>5°</t>
-  </si>
-  <si>
     <t>15°</t>
   </si>
   <si>
@@ -379,37 +304,31 @@
     <t>9°</t>
   </si>
   <si>
-    <t>18:48:08</t>
-  </si>
-  <si>
-    <t>20:20:57</t>
-  </si>
-  <si>
-    <t>19:32:59</t>
-  </si>
-  <si>
-    <t>21:05:47</t>
-  </si>
-  <si>
-    <t>18:44:56</t>
-  </si>
-  <si>
-    <t>20:17:43</t>
-  </si>
-  <si>
-    <t>19:29:34</t>
-  </si>
-  <si>
-    <t>18:41:22</t>
-  </si>
-  <si>
-    <t>20:14:09</t>
-  </si>
-  <si>
-    <t>19:25:52</t>
-  </si>
-  <si>
-    <t>18:37:33</t>
+    <t>19:33:00</t>
+  </si>
+  <si>
+    <t>21:05:48</t>
+  </si>
+  <si>
+    <t>18:44:58</t>
+  </si>
+  <si>
+    <t>20:17:46</t>
+  </si>
+  <si>
+    <t>19:29:38</t>
+  </si>
+  <si>
+    <t>18:41:28</t>
+  </si>
+  <si>
+    <t>20:14:15</t>
+  </si>
+  <si>
+    <t>19:26:01</t>
+  </si>
+  <si>
+    <t>18:37:45</t>
   </si>
   <si>
     <t>A+B</t>
@@ -424,10 +343,10 @@
     <t>2</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
 </sst>
 </file>
@@ -461,7 +380,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -476,19 +395,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,43 +425,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FFF6F9FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,19 +473,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,25 +485,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -631,7 +532,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -697,15 +598,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1109,7 +1001,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1187,55 +1079,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>29</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-15.7</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="O2" s="6">
+        <v>52</v>
+      </c>
+      <c r="P2" s="7">
+        <v>23</v>
+      </c>
+      <c r="Q2" s="8">
         <v>28</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-8.9</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="O2" s="6">
-        <v>47</v>
-      </c>
-      <c r="P2" s="7">
-        <v>7</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>35</v>
-      </c>
       <c r="R2" s="9">
-        <v>47</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1243,55 +1135,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="L3" s="4">
-        <v>-21.3</v>
+        <v>-26.2</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="O3" s="10">
-        <v>34</v>
+        <v>109</v>
+      </c>
+      <c r="O3" s="6">
+        <v>59</v>
       </c>
       <c r="P3" s="7">
-        <v>6</v>
-      </c>
-      <c r="Q3" s="11">
-        <v>30</v>
-      </c>
-      <c r="R3" s="12">
-        <v>2</v>
+        <v>23</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>43</v>
+      </c>
+      <c r="R3" s="9">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1299,55 +1191,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-9.1</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="O4" s="6">
+        <v>93</v>
+      </c>
+      <c r="P4" s="11">
+        <v>48</v>
+      </c>
+      <c r="Q4" s="12">
         <v>77</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-29.3</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="O4" s="10">
-        <v>79</v>
-      </c>
-      <c r="P4" s="12">
-        <v>2</v>
-      </c>
-      <c r="Q4" s="13">
-        <v>25</v>
-      </c>
-      <c r="R4" s="14">
-        <v>65</v>
+      <c r="R4" s="13">
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1355,55 +1247,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="L5" s="4">
-        <v>-15.6</v>
+        <v>-21.7</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="O5" s="10">
-        <v>86</v>
-      </c>
-      <c r="P5" s="15">
-        <v>80</v>
+        <v>108</v>
+      </c>
+      <c r="O5" s="6">
+        <v>87</v>
+      </c>
+      <c r="P5" s="14">
+        <v>68</v>
       </c>
       <c r="Q5" s="11">
-        <v>28</v>
-      </c>
-      <c r="R5" s="16">
-        <v>39</v>
+        <v>51</v>
+      </c>
+      <c r="R5" s="11">
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1411,55 +1303,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="L6" s="4">
-        <v>-26.2</v>
+        <v>-15.9</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O6" s="10">
-        <v>65</v>
-      </c>
-      <c r="P6" s="7">
-        <v>7</v>
+        <v>108</v>
+      </c>
+      <c r="O6" s="6">
+        <v>100</v>
+      </c>
+      <c r="P6" s="15">
+        <v>58</v>
       </c>
       <c r="Q6" s="16">
-        <v>42</v>
-      </c>
-      <c r="R6" s="11">
-        <v>30</v>
+        <v>94</v>
+      </c>
+      <c r="R6" s="12">
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1467,55 +1359,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="L7" s="4">
-        <v>-9.1</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="O7" s="10">
-        <v>75</v>
+        <v>108</v>
+      </c>
+      <c r="O7" s="6">
+        <v>62</v>
       </c>
       <c r="P7" s="17">
+        <v>16</v>
+      </c>
+      <c r="Q7" s="18">
         <v>12</v>
       </c>
-      <c r="Q7" s="18">
-        <v>58</v>
-      </c>
-      <c r="R7" s="11">
-        <v>28</v>
+      <c r="R7" s="7">
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1523,55 +1415,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="I8" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="L8" s="4">
+        <v>-21.9</v>
+      </c>
+      <c r="M8" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="L8" s="4">
-        <v>-21.6</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="N8" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="O8" s="10">
-        <v>80</v>
-      </c>
-      <c r="P8" s="19">
-        <v>15</v>
-      </c>
-      <c r="Q8" s="20">
-        <v>48</v>
-      </c>
-      <c r="R8" s="8">
-        <v>33</v>
+        <v>110</v>
+      </c>
+      <c r="O8" s="6">
+        <v>51</v>
+      </c>
+      <c r="P8" s="9">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="19">
+        <v>18</v>
+      </c>
+      <c r="R8" s="7">
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1579,54 +1471,54 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="L9" s="4">
-        <v>-15.9</v>
+        <v>-16.1</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="O9" s="10">
+        <v>108</v>
+      </c>
+      <c r="O9" s="6">
         <v>100</v>
       </c>
-      <c r="P9" s="17">
-        <v>9</v>
-      </c>
-      <c r="Q9" s="15">
-        <v>80</v>
-      </c>
-      <c r="R9" s="21">
+      <c r="P9" s="18">
+        <v>11</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>0</v>
+      </c>
+      <c r="R9" s="20">
         <v>100</v>
       </c>
     </row>
@@ -1635,282 +1527,114 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="H10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="K10" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="L10" s="4">
+        <v>-9.5</v>
+      </c>
+      <c r="M10" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="L10" s="4">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="N10" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="O10" s="10">
-        <v>99</v>
+        <v>108</v>
+      </c>
+      <c r="O10" s="21">
+        <v>16</v>
       </c>
       <c r="P10" s="22">
-        <v>74</v>
-      </c>
-      <c r="Q10" s="23">
-        <v>53</v>
-      </c>
-      <c r="R10" s="24">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
-      <c r="A11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="2">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>0</v>
+      </c>
+      <c r="R10" s="18">
         <v>12</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="L11" s="4">
-        <v>-21.9</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="O11" s="10">
-        <v>100</v>
-      </c>
-      <c r="P11" s="25">
-        <v>72</v>
-      </c>
-      <c r="Q11" s="18">
-        <v>62</v>
-      </c>
-      <c r="R11" s="21">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
-      <c r="A12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="2">
-        <v>16</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="L12" s="4">
-        <v>-16.1</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="O12" s="6">
-        <v>19</v>
-      </c>
-      <c r="P12" s="7">
-        <v>6</v>
-      </c>
-      <c r="Q12" s="19">
-        <v>14</v>
-      </c>
-      <c r="R12" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18">
-      <c r="A13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="2">
-        <v>19</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="L13" s="4">
-        <v>-9.4</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="O13" s="6">
-        <v>23</v>
-      </c>
-      <c r="P13" s="17">
-        <v>11</v>
-      </c>
-      <c r="Q13" s="12">
-        <v>0</v>
-      </c>
-      <c r="R13" s="13">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A13">
+  <conditionalFormatting sqref="A2:A10">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B13">
+  <conditionalFormatting sqref="B2:B10">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C13">
+  <conditionalFormatting sqref="C2:C10">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D13">
+  <conditionalFormatting sqref="D2:D10">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E13">
+  <conditionalFormatting sqref="E2:E10">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F13">
+  <conditionalFormatting sqref="F2:F10">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G13">
+  <conditionalFormatting sqref="G2:G10">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H13">
+  <conditionalFormatting sqref="H2:H10">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I13">
+  <conditionalFormatting sqref="I2:I10">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J13">
+  <conditionalFormatting sqref="J2:J10">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K13">
+  <conditionalFormatting sqref="K2:K10">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L13">
+  <conditionalFormatting sqref="L2:L10">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1929,12 +1653,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M13">
+  <conditionalFormatting sqref="M2:M10">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N13">
+  <conditionalFormatting sqref="N2:N10">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1951,22 +1675,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O13">
+  <conditionalFormatting sqref="O2:O10">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P13">
+  <conditionalFormatting sqref="P2:P10">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q13">
+  <conditionalFormatting sqref="Q2:Q10">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R13">
+  <conditionalFormatting sqref="R2:R10">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="98">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260901--01</t>
-  </si>
-  <si>
-    <t>20260901--02</t>
-  </si>
-  <si>
     <t>20260902--01</t>
   </si>
   <si>
@@ -97,193 +91,169 @@
     <t>20260906--01</t>
   </si>
   <si>
-    <t>05:51</t>
-  </si>
-  <si>
-    <t>04:08</t>
+    <t>20260908--01</t>
   </si>
   <si>
     <t>05:55</t>
   </si>
   <si>
+    <t>04:54</t>
+  </si>
+  <si>
+    <t>05:23</t>
+  </si>
+  <si>
+    <t>05:41</t>
+  </si>
+  <si>
+    <t>02:38</t>
+  </si>
+  <si>
+    <t>04:07</t>
+  </si>
+  <si>
     <t>04:55</t>
   </si>
   <si>
-    <t>05:23</t>
-  </si>
-  <si>
-    <t>05:41</t>
+    <t>02:39</t>
+  </si>
+  <si>
+    <t>05:21</t>
+  </si>
+  <si>
+    <t>00:57</t>
+  </si>
+  <si>
+    <t>03:08</t>
+  </si>
+  <si>
+    <t>05:15</t>
+  </si>
+  <si>
+    <t>00:01</t>
   </si>
   <si>
     <t>02:40</t>
   </si>
   <si>
-    <t>04:07</t>
-  </si>
-  <si>
-    <t>03:19</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>05:21</t>
-  </si>
-  <si>
-    <t>00:58</t>
-  </si>
-  <si>
-    <t>03:08</t>
-  </si>
-  <si>
-    <t>05:16</t>
-  </si>
-  <si>
-    <t>00:02</t>
-  </si>
-  <si>
-    <t>02:41</t>
-  </si>
-  <si>
-    <t>19:27:26</t>
-  </si>
-  <si>
-    <t>21:04:28</t>
-  </si>
-  <si>
-    <t>18:37:23</t>
-  </si>
-  <si>
-    <t>20:14:20</t>
-  </si>
-  <si>
-    <t>19:24:09</t>
-  </si>
-  <si>
-    <t>18:33:55</t>
-  </si>
-  <si>
-    <t>20:11:05</t>
-  </si>
-  <si>
-    <t>19:20:39</t>
-  </si>
-  <si>
-    <t>18:30:13</t>
-  </si>
-  <si>
-    <t>19:29:41</t>
-  </si>
-  <si>
-    <t>21:07:09</t>
-  </si>
-  <si>
-    <t>18:39:37</t>
-  </si>
-  <si>
-    <t>20:16:48</t>
-  </si>
-  <si>
-    <t>19:26:30</t>
-  </si>
-  <si>
-    <t>18:36:12</t>
-  </si>
-  <si>
-    <t>20:14:13</t>
-  </si>
-  <si>
-    <t>19:23:20</t>
-  </si>
-  <si>
-    <t>18:32:41</t>
-  </si>
-  <si>
-    <t>19:32:36</t>
-  </si>
-  <si>
-    <t>21:09:13</t>
-  </si>
-  <si>
-    <t>18:42:35</t>
-  </si>
-  <si>
-    <t>20:19:15</t>
-  </si>
-  <si>
-    <t>19:29:12</t>
-  </si>
-  <si>
-    <t>18:39:03</t>
-  </si>
-  <si>
-    <t>20:15:33</t>
-  </si>
-  <si>
-    <t>19:25:24</t>
-  </si>
-  <si>
-    <t>18:35:08</t>
-  </si>
-  <si>
-    <t>19:35:32</t>
-  </si>
-  <si>
-    <t>21:11:17</t>
-  </si>
-  <si>
-    <t>18:45:32</t>
-  </si>
-  <si>
-    <t>20:21:43</t>
-  </si>
-  <si>
-    <t>19:31:53</t>
-  </si>
-  <si>
-    <t>18:41:53</t>
-  </si>
-  <si>
-    <t>20:16:53</t>
-  </si>
-  <si>
-    <t>19:27:27</t>
-  </si>
-  <si>
-    <t>18:37:36</t>
-  </si>
-  <si>
-    <t>19:37:46</t>
-  </si>
-  <si>
-    <t>21:13:57</t>
-  </si>
-  <si>
-    <t>18:47:46</t>
-  </si>
-  <si>
-    <t>20:24:10</t>
-  </si>
-  <si>
-    <t>19:34:14</t>
-  </si>
-  <si>
-    <t>18:44:10</t>
-  </si>
-  <si>
-    <t>20:20:01</t>
-  </si>
-  <si>
-    <t>19:30:07</t>
-  </si>
-  <si>
-    <t>18:40:03</t>
-  </si>
-  <si>
-    <t>28°</t>
-  </si>
-  <si>
-    <t>5°</t>
+    <t>18:37:25</t>
+  </si>
+  <si>
+    <t>20:14:22</t>
+  </si>
+  <si>
+    <t>19:24:13</t>
+  </si>
+  <si>
+    <t>18:34:02</t>
+  </si>
+  <si>
+    <t>20:11:12</t>
+  </si>
+  <si>
+    <t>19:20:50</t>
+  </si>
+  <si>
+    <t>18:30:28</t>
+  </si>
+  <si>
+    <t>18:26:48</t>
+  </si>
+  <si>
+    <t>18:39:39</t>
+  </si>
+  <si>
+    <t>20:16:50</t>
+  </si>
+  <si>
+    <t>19:26:34</t>
+  </si>
+  <si>
+    <t>18:36:19</t>
+  </si>
+  <si>
+    <t>20:14:21</t>
+  </si>
+  <si>
+    <t>19:23:31</t>
+  </si>
+  <si>
+    <t>18:32:56</t>
+  </si>
+  <si>
+    <t>18:29:57</t>
+  </si>
+  <si>
+    <t>18:42:36</t>
+  </si>
+  <si>
+    <t>20:19:17</t>
+  </si>
+  <si>
+    <t>19:29:16</t>
+  </si>
+  <si>
+    <t>18:39:09</t>
+  </si>
+  <si>
+    <t>20:15:40</t>
+  </si>
+  <si>
+    <t>19:25:34</t>
+  </si>
+  <si>
+    <t>18:35:23</t>
+  </si>
+  <si>
+    <t>18:31:17</t>
+  </si>
+  <si>
+    <t>18:45:34</t>
+  </si>
+  <si>
+    <t>20:21:44</t>
+  </si>
+  <si>
+    <t>19:31:57</t>
+  </si>
+  <si>
+    <t>18:42:00</t>
+  </si>
+  <si>
+    <t>20:16:59</t>
+  </si>
+  <si>
+    <t>19:27:38</t>
+  </si>
+  <si>
+    <t>18:37:51</t>
+  </si>
+  <si>
+    <t>18:32:36</t>
+  </si>
+  <si>
+    <t>18:47:48</t>
+  </si>
+  <si>
+    <t>20:24:12</t>
+  </si>
+  <si>
+    <t>19:34:18</t>
+  </si>
+  <si>
+    <t>18:44:16</t>
+  </si>
+  <si>
+    <t>20:20:07</t>
+  </si>
+  <si>
+    <t>19:30:18</t>
+  </si>
+  <si>
+    <t>18:40:18</t>
+  </si>
+  <si>
+    <t>18:35:44</t>
   </si>
   <si>
     <t>14°</t>
@@ -304,46 +274,37 @@
     <t>9°</t>
   </si>
   <si>
-    <t>19:33:00</t>
-  </si>
-  <si>
-    <t>21:05:48</t>
-  </si>
-  <si>
-    <t>18:44:58</t>
-  </si>
-  <si>
-    <t>20:17:46</t>
-  </si>
-  <si>
-    <t>19:29:38</t>
-  </si>
-  <si>
-    <t>18:41:28</t>
-  </si>
-  <si>
-    <t>20:14:15</t>
-  </si>
-  <si>
-    <t>19:26:01</t>
-  </si>
-  <si>
-    <t>18:37:45</t>
+    <t>4°</t>
+  </si>
+  <si>
+    <t>18:45:00</t>
+  </si>
+  <si>
+    <t>20:17:47</t>
+  </si>
+  <si>
+    <t>19:29:42</t>
+  </si>
+  <si>
+    <t>18:41:34</t>
+  </si>
+  <si>
+    <t>19:26:11</t>
+  </si>
+  <si>
+    <t>18:37:59</t>
+  </si>
+  <si>
+    <t>18:34:22</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t>4</t>
@@ -380,7 +341,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -407,7 +368,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -419,79 +428,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -532,7 +475,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -589,15 +532,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1001,7 +935,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1079,55 +1013,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-9.1</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="O2" s="6">
+        <v>73</v>
+      </c>
+      <c r="P2" s="7">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="8">
         <v>43</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-15.7</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="O2" s="6">
-        <v>52</v>
-      </c>
-      <c r="P2" s="7">
-        <v>23</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>28</v>
-      </c>
       <c r="R2" s="9">
-        <v>1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1135,55 +1069,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="L3" s="4">
-        <v>-26.2</v>
+        <v>-21.7</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="O3" s="6">
+        <v>86</v>
+      </c>
+      <c r="P3" s="10">
+        <v>13</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>26</v>
+      </c>
+      <c r="R3" s="11">
         <v>59</v>
-      </c>
-      <c r="P3" s="7">
-        <v>23</v>
-      </c>
-      <c r="Q3" s="10">
-        <v>43</v>
-      </c>
-      <c r="R3" s="9">
-        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1191,55 +1125,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-15.9</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="O4" s="6">
+        <v>100</v>
+      </c>
+      <c r="P4" s="12">
         <v>63</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-9.1</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="O4" s="6">
-        <v>93</v>
-      </c>
-      <c r="P4" s="11">
-        <v>48</v>
-      </c>
-      <c r="Q4" s="12">
-        <v>77</v>
+      <c r="Q4" s="11">
+        <v>62</v>
       </c>
       <c r="R4" s="13">
-        <v>56</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1247,55 +1181,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="L5" s="4">
-        <v>-21.7</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="O5" s="6">
-        <v>87</v>
-      </c>
-      <c r="P5" s="14">
-        <v>68</v>
-      </c>
-      <c r="Q5" s="11">
-        <v>51</v>
-      </c>
-      <c r="R5" s="11">
-        <v>51</v>
+        <v>88</v>
+      </c>
+      <c r="P5" s="11">
+        <v>59</v>
+      </c>
+      <c r="Q5" s="14">
+        <v>31</v>
+      </c>
+      <c r="R5" s="15">
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1303,55 +1237,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="L6" s="4">
-        <v>-15.9</v>
+        <v>-22</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="O6" s="6">
-        <v>100</v>
-      </c>
-      <c r="P6" s="15">
-        <v>58</v>
-      </c>
-      <c r="Q6" s="16">
+        <v>99</v>
+      </c>
+      <c r="P6" s="12">
+        <v>67</v>
+      </c>
+      <c r="Q6" s="11">
+        <v>59</v>
+      </c>
+      <c r="R6" s="13">
         <v>94</v>
-      </c>
-      <c r="R6" s="12">
-        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1359,55 +1293,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="L7" s="4">
-        <v>-9.300000000000001</v>
+        <v>-16.1</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="O7" s="6">
-        <v>62</v>
-      </c>
-      <c r="P7" s="17">
-        <v>16</v>
-      </c>
-      <c r="Q7" s="18">
-        <v>12</v>
-      </c>
-      <c r="R7" s="7">
-        <v>25</v>
+        <v>65</v>
+      </c>
+      <c r="P7" s="16">
+        <v>20</v>
+      </c>
+      <c r="Q7" s="17">
+        <v>0</v>
+      </c>
+      <c r="R7" s="10">
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1415,55 +1349,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="I8" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="K8" s="1" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="L8" s="4">
-        <v>-21.9</v>
+        <v>-9.5</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="O8" s="6">
-        <v>51</v>
-      </c>
-      <c r="P8" s="9">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="19">
-        <v>18</v>
-      </c>
-      <c r="R8" s="7">
-        <v>27</v>
+        <v>96</v>
+      </c>
+      <c r="O8" s="18">
+        <v>28</v>
+      </c>
+      <c r="P8" s="17">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="17">
+        <v>0</v>
+      </c>
+      <c r="R8" s="14">
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1471,170 +1405,114 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="I9" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="K9" s="1" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="L9" s="4">
-        <v>-16.1</v>
+        <v>-9.6</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="O9" s="6">
         <v>100</v>
       </c>
-      <c r="P9" s="18">
-        <v>11</v>
+      <c r="P9" s="7">
+        <v>27</v>
       </c>
       <c r="Q9" s="9">
-        <v>0</v>
-      </c>
-      <c r="R9" s="20">
+        <v>38</v>
+      </c>
+      <c r="R9" s="19">
         <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
-      <c r="A10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="2">
-        <v>19</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="L10" s="4">
-        <v>-9.5</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="O10" s="21">
-        <v>16</v>
-      </c>
-      <c r="P10" s="22">
-        <v>5</v>
-      </c>
-      <c r="Q10" s="9">
-        <v>0</v>
-      </c>
-      <c r="R10" s="18">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A10">
+  <conditionalFormatting sqref="A2:A9">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B10">
+  <conditionalFormatting sqref="B2:B9">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C10">
+  <conditionalFormatting sqref="C2:C9">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D10">
+  <conditionalFormatting sqref="D2:D9">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E10">
+  <conditionalFormatting sqref="E2:E9">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F10">
+  <conditionalFormatting sqref="F2:F9">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G10">
+  <conditionalFormatting sqref="G2:G9">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H10">
+  <conditionalFormatting sqref="H2:H9">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I10">
+  <conditionalFormatting sqref="I2:I9">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J10">
+  <conditionalFormatting sqref="J2:J9">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K10">
+  <conditionalFormatting sqref="K2:K9">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L10">
+  <conditionalFormatting sqref="L2:L9">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1653,12 +1531,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M10">
+  <conditionalFormatting sqref="M2:M9">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N10">
+  <conditionalFormatting sqref="N2:N9">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1675,22 +1553,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O10">
+  <conditionalFormatting sqref="O2:O9">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P10">
+  <conditionalFormatting sqref="P2:P9">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q10">
+  <conditionalFormatting sqref="Q2:Q9">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R10">
+  <conditionalFormatting sqref="R2:R9">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="80">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260902--01</t>
-  </si>
-  <si>
-    <t>20260902--02</t>
-  </si>
-  <si>
     <t>20260903--01</t>
   </si>
   <si>
@@ -94,37 +88,25 @@
     <t>20260908--01</t>
   </si>
   <si>
-    <t>05:55</t>
-  </si>
-  <si>
-    <t>04:54</t>
-  </si>
-  <si>
-    <t>05:23</t>
+    <t>05:24</t>
   </si>
   <si>
     <t>05:41</t>
   </si>
   <si>
+    <t>02:39</t>
+  </si>
+  <si>
+    <t>04:06</t>
+  </si>
+  <si>
+    <t>04:55</t>
+  </si>
+  <si>
     <t>02:38</t>
   </si>
   <si>
-    <t>04:07</t>
-  </si>
-  <si>
-    <t>04:55</t>
-  </si>
-  <si>
-    <t>02:39</t>
-  </si>
-  <si>
-    <t>05:21</t>
-  </si>
-  <si>
-    <t>00:57</t>
-  </si>
-  <si>
-    <t>03:08</t>
+    <t>03:09</t>
   </si>
   <si>
     <t>05:15</t>
@@ -136,166 +118,130 @@
     <t>02:40</t>
   </si>
   <si>
-    <t>18:37:25</t>
+    <t>19:24:13</t>
+  </si>
+  <si>
+    <t>18:34:03</t>
+  </si>
+  <si>
+    <t>20:11:13</t>
+  </si>
+  <si>
+    <t>19:20:53</t>
+  </si>
+  <si>
+    <t>18:30:32</t>
+  </si>
+  <si>
+    <t>18:26:57</t>
+  </si>
+  <si>
+    <t>19:26:34</t>
+  </si>
+  <si>
+    <t>18:36:20</t>
   </si>
   <si>
     <t>20:14:22</t>
   </si>
   <si>
-    <t>19:24:13</t>
-  </si>
-  <si>
-    <t>18:34:02</t>
-  </si>
-  <si>
-    <t>20:11:12</t>
-  </si>
-  <si>
-    <t>19:20:50</t>
-  </si>
-  <si>
-    <t>18:30:28</t>
-  </si>
-  <si>
-    <t>18:26:48</t>
-  </si>
-  <si>
-    <t>18:39:39</t>
-  </si>
-  <si>
-    <t>20:16:50</t>
-  </si>
-  <si>
-    <t>19:26:34</t>
-  </si>
-  <si>
-    <t>18:36:19</t>
-  </si>
-  <si>
-    <t>20:14:21</t>
-  </si>
-  <si>
-    <t>19:23:31</t>
-  </si>
-  <si>
-    <t>18:32:56</t>
-  </si>
-  <si>
-    <t>18:29:57</t>
-  </si>
-  <si>
-    <t>18:42:36</t>
-  </si>
-  <si>
-    <t>20:19:17</t>
+    <t>19:23:34</t>
+  </si>
+  <si>
+    <t>18:33:00</t>
+  </si>
+  <si>
+    <t>18:30:06</t>
   </si>
   <si>
     <t>19:29:16</t>
   </si>
   <si>
-    <t>18:39:09</t>
-  </si>
-  <si>
-    <t>20:15:40</t>
-  </si>
-  <si>
-    <t>19:25:34</t>
-  </si>
-  <si>
-    <t>18:35:23</t>
-  </si>
-  <si>
-    <t>18:31:17</t>
-  </si>
-  <si>
-    <t>18:45:34</t>
-  </si>
-  <si>
-    <t>20:21:44</t>
-  </si>
-  <si>
-    <t>19:31:57</t>
-  </si>
-  <si>
-    <t>18:42:00</t>
-  </si>
-  <si>
-    <t>20:16:59</t>
-  </si>
-  <si>
-    <t>19:27:38</t>
-  </si>
-  <si>
-    <t>18:37:51</t>
-  </si>
-  <si>
-    <t>18:32:36</t>
-  </si>
-  <si>
-    <t>18:47:48</t>
-  </si>
-  <si>
-    <t>20:24:12</t>
+    <t>18:39:11</t>
+  </si>
+  <si>
+    <t>20:15:41</t>
+  </si>
+  <si>
+    <t>19:25:37</t>
+  </si>
+  <si>
+    <t>18:35:28</t>
+  </si>
+  <si>
+    <t>18:31:25</t>
+  </si>
+  <si>
+    <t>19:31:58</t>
+  </si>
+  <si>
+    <t>18:42:01</t>
+  </si>
+  <si>
+    <t>20:17:01</t>
+  </si>
+  <si>
+    <t>19:27:40</t>
+  </si>
+  <si>
+    <t>18:37:55</t>
+  </si>
+  <si>
+    <t>18:32:44</t>
   </si>
   <si>
     <t>19:34:18</t>
   </si>
   <si>
-    <t>18:44:16</t>
-  </si>
-  <si>
-    <t>20:20:07</t>
-  </si>
-  <si>
-    <t>19:30:18</t>
-  </si>
-  <si>
-    <t>18:40:18</t>
-  </si>
-  <si>
-    <t>18:35:44</t>
-  </si>
-  <si>
-    <t>14°</t>
+    <t>18:44:18</t>
+  </si>
+  <si>
+    <t>20:20:09</t>
+  </si>
+  <si>
+    <t>19:30:20</t>
+  </si>
+  <si>
+    <t>18:40:22</t>
+  </si>
+  <si>
+    <t>18:35:53</t>
+  </si>
+  <si>
+    <t>22°</t>
+  </si>
+  <si>
+    <t>13°</t>
+  </si>
+  <si>
+    <t>10°</t>
   </si>
   <si>
     <t>15°</t>
   </si>
   <si>
-    <t>22°</t>
-  </si>
-  <si>
-    <t>13°</t>
-  </si>
-  <si>
-    <t>10°</t>
-  </si>
-  <si>
     <t>9°</t>
   </si>
   <si>
     <t>4°</t>
   </si>
   <si>
-    <t>18:45:00</t>
-  </si>
-  <si>
-    <t>20:17:47</t>
-  </si>
-  <si>
-    <t>19:29:42</t>
-  </si>
-  <si>
-    <t>18:41:34</t>
-  </si>
-  <si>
-    <t>19:26:11</t>
-  </si>
-  <si>
-    <t>18:37:59</t>
-  </si>
-  <si>
-    <t>18:34:22</t>
+    <t>19:29:43</t>
+  </si>
+  <si>
+    <t>18:41:35</t>
+  </si>
+  <si>
+    <t>20:14:23</t>
+  </si>
+  <si>
+    <t>19:26:14</t>
+  </si>
+  <si>
+    <t>18:38:03</t>
+  </si>
+  <si>
+    <t>18:34:30</t>
   </si>
   <si>
     <t>A+B</t>
@@ -341,7 +287,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -362,79 +308,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -475,7 +427,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -532,6 +484,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -935,7 +890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1013,55 +968,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>23</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="K2" s="1" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="L2" s="4">
-        <v>-9.1</v>
+        <v>-15.9</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="O2" s="6">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="P2" s="7">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="Q2" s="8">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="R2" s="9">
-        <v>40</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1069,55 +1024,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="G3" s="3" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="L3" s="4">
-        <v>-21.7</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="O3" s="6">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P3" s="10">
-        <v>13</v>
-      </c>
-      <c r="Q3" s="7">
-        <v>26</v>
+        <v>48</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>50</v>
       </c>
       <c r="R3" s="11">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1125,55 +1080,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="G4" s="3" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="K4" s="1" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="L4" s="4">
-        <v>-15.9</v>
+        <v>-22</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="O4" s="6">
         <v>100</v>
       </c>
       <c r="P4" s="12">
-        <v>63</v>
-      </c>
-      <c r="Q4" s="11">
-        <v>62</v>
-      </c>
-      <c r="R4" s="13">
-        <v>95</v>
+        <v>90</v>
+      </c>
+      <c r="Q4" s="13">
+        <v>85</v>
+      </c>
+      <c r="R4" s="14">
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1181,55 +1136,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
+        <v>16</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="D5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="G5" s="3" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="K5" s="1" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="L5" s="4">
-        <v>-9.300000000000001</v>
+        <v>-16.1</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="O5" s="6">
-        <v>88</v>
-      </c>
-      <c r="P5" s="11">
-        <v>59</v>
-      </c>
-      <c r="Q5" s="14">
-        <v>31</v>
-      </c>
-      <c r="R5" s="15">
-        <v>53</v>
+        <v>78</v>
+      </c>
+      <c r="O5" s="15">
+        <v>27</v>
+      </c>
+      <c r="P5" s="16">
+        <v>9</v>
+      </c>
+      <c r="Q5" s="17">
+        <v>0</v>
+      </c>
+      <c r="R5" s="18">
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1237,55 +1192,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="G6" s="3" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="K6" s="1" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="L6" s="4">
-        <v>-22</v>
+        <v>-9.5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="O6" s="6">
-        <v>99</v>
-      </c>
-      <c r="P6" s="12">
-        <v>67</v>
-      </c>
-      <c r="Q6" s="11">
-        <v>59</v>
-      </c>
-      <c r="R6" s="13">
-        <v>94</v>
+        <v>78</v>
+      </c>
+      <c r="O6" s="15">
+        <v>28</v>
+      </c>
+      <c r="P6" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="17">
+        <v>0</v>
+      </c>
+      <c r="R6" s="18">
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1293,226 +1248,114 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="G7" s="3" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="K7" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L7" s="4">
+        <v>-9.6</v>
+      </c>
+      <c r="M7" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="L7" s="4">
-        <v>-16.1</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="N7" s="1" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="O7" s="6">
-        <v>65</v>
-      </c>
-      <c r="P7" s="16">
-        <v>20</v>
-      </c>
-      <c r="Q7" s="17">
-        <v>0</v>
-      </c>
-      <c r="R7" s="10">
+        <v>77</v>
+      </c>
+      <c r="P7" s="19">
+        <v>27</v>
+      </c>
+      <c r="Q7" s="18">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:18">
-      <c r="A8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="2">
-        <v>19</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="L8" s="4">
-        <v>-9.5</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="O8" s="18">
-        <v>28</v>
-      </c>
-      <c r="P8" s="17">
-        <v>2</v>
-      </c>
-      <c r="Q8" s="17">
-        <v>0</v>
-      </c>
-      <c r="R8" s="14">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
-      <c r="A9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="2">
-        <v>12</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="R7" s="20">
         <v>63</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="L9" s="4">
-        <v>-9.6</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="O9" s="6">
-        <v>100</v>
-      </c>
-      <c r="P9" s="7">
-        <v>27</v>
-      </c>
-      <c r="Q9" s="9">
-        <v>38</v>
-      </c>
-      <c r="R9" s="19">
-        <v>100</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A9">
+  <conditionalFormatting sqref="A2:A7">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B9">
+  <conditionalFormatting sqref="B2:B7">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C9">
+  <conditionalFormatting sqref="C2:C7">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D9">
+  <conditionalFormatting sqref="D2:D7">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E9">
+  <conditionalFormatting sqref="E2:E7">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F9">
+  <conditionalFormatting sqref="F2:F7">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G9">
+  <conditionalFormatting sqref="G2:G7">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H9">
+  <conditionalFormatting sqref="H2:H7">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I9">
+  <conditionalFormatting sqref="I2:I7">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J9">
+  <conditionalFormatting sqref="J2:J7">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K9">
+  <conditionalFormatting sqref="K2:K7">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L9">
+  <conditionalFormatting sqref="L2:L7">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1531,12 +1374,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M9">
+  <conditionalFormatting sqref="M2:M7">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N9">
+  <conditionalFormatting sqref="N2:N7">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1553,22 +1396,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O9">
+  <conditionalFormatting sqref="O2:O7">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P9">
+  <conditionalFormatting sqref="P2:P7">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q9">
+  <conditionalFormatting sqref="Q2:Q7">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R9">
+  <conditionalFormatting sqref="R2:R7">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="68">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260903--01</t>
-  </si>
-  <si>
     <t>20260904--01</t>
   </si>
   <si>
@@ -88,13 +85,10 @@
     <t>20260908--01</t>
   </si>
   <si>
-    <t>05:24</t>
-  </si>
-  <si>
     <t>05:41</t>
   </si>
   <si>
-    <t>02:39</t>
+    <t>02:38</t>
   </si>
   <si>
     <t>04:06</t>
@@ -103,40 +97,28 @@
     <t>04:55</t>
   </si>
   <si>
-    <t>02:38</t>
-  </si>
-  <si>
-    <t>03:09</t>
-  </si>
-  <si>
     <t>05:15</t>
   </si>
   <si>
-    <t>00:01</t>
+    <t>00:00</t>
   </si>
   <si>
     <t>02:40</t>
   </si>
   <si>
-    <t>19:24:13</t>
-  </si>
-  <si>
     <t>18:34:03</t>
   </si>
   <si>
     <t>20:11:13</t>
   </si>
   <si>
-    <t>19:20:53</t>
-  </si>
-  <si>
-    <t>18:30:32</t>
-  </si>
-  <si>
-    <t>18:26:57</t>
-  </si>
-  <si>
-    <t>19:26:34</t>
+    <t>19:20:52</t>
+  </si>
+  <si>
+    <t>18:30:31</t>
+  </si>
+  <si>
+    <t>18:26:54</t>
   </si>
   <si>
     <t>18:36:20</t>
@@ -145,70 +127,58 @@
     <t>20:14:22</t>
   </si>
   <si>
-    <t>19:23:34</t>
-  </si>
-  <si>
-    <t>18:33:00</t>
-  </si>
-  <si>
-    <t>18:30:06</t>
-  </si>
-  <si>
-    <t>19:29:16</t>
-  </si>
-  <si>
-    <t>18:39:11</t>
+    <t>19:23:33</t>
+  </si>
+  <si>
+    <t>18:32:59</t>
+  </si>
+  <si>
+    <t>18:30:04</t>
+  </si>
+  <si>
+    <t>18:39:10</t>
   </si>
   <si>
     <t>20:15:41</t>
   </si>
   <si>
-    <t>19:25:37</t>
-  </si>
-  <si>
-    <t>18:35:28</t>
-  </si>
-  <si>
-    <t>18:31:25</t>
-  </si>
-  <si>
-    <t>19:31:58</t>
+    <t>19:25:36</t>
+  </si>
+  <si>
+    <t>18:35:26</t>
+  </si>
+  <si>
+    <t>18:31:23</t>
   </si>
   <si>
     <t>18:42:01</t>
   </si>
   <si>
-    <t>20:17:01</t>
-  </si>
-  <si>
-    <t>19:27:40</t>
-  </si>
-  <si>
-    <t>18:37:55</t>
-  </si>
-  <si>
-    <t>18:32:44</t>
-  </si>
-  <si>
-    <t>19:34:18</t>
-  </si>
-  <si>
-    <t>18:44:18</t>
-  </si>
-  <si>
-    <t>20:20:09</t>
-  </si>
-  <si>
-    <t>19:30:20</t>
-  </si>
-  <si>
-    <t>18:40:22</t>
-  </si>
-  <si>
-    <t>18:35:53</t>
-  </si>
-  <si>
-    <t>22°</t>
+    <t>20:17:00</t>
+  </si>
+  <si>
+    <t>19:27:39</t>
+  </si>
+  <si>
+    <t>18:37:54</t>
+  </si>
+  <si>
+    <t>18:32:42</t>
+  </si>
+  <si>
+    <t>18:44:17</t>
+  </si>
+  <si>
+    <t>20:20:08</t>
+  </si>
+  <si>
+    <t>19:30:19</t>
+  </si>
+  <si>
+    <t>18:40:21</t>
+  </si>
+  <si>
+    <t>18:35:50</t>
   </si>
   <si>
     <t>13°</t>
@@ -226,22 +196,16 @@
     <t>4°</t>
   </si>
   <si>
-    <t>19:29:43</t>
-  </si>
-  <si>
     <t>18:41:35</t>
   </si>
   <si>
-    <t>20:14:23</t>
-  </si>
-  <si>
-    <t>19:26:14</t>
-  </si>
-  <si>
-    <t>18:38:03</t>
-  </si>
-  <si>
-    <t>18:34:30</t>
+    <t>19:26:13</t>
+  </si>
+  <si>
+    <t>18:38:02</t>
+  </si>
+  <si>
+    <t>18:34:28</t>
   </si>
   <si>
     <t>A+B</t>
@@ -287,7 +251,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -308,13 +272,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -326,13 +308,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -344,49 +326,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -427,7 +367,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -475,18 +415,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -890,7 +818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -968,55 +896,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>26</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="D2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="F2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="H2" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="J2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-15.9</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="N2" s="1" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="O2" s="6">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="P2" s="7">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="Q2" s="8">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="R2" s="9">
-        <v>82</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1024,55 +952,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="F3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="H3" s="3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="L3" s="4">
-        <v>-9.300000000000001</v>
+        <v>-22</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="O3" s="6">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P3" s="10">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="Q3" s="10">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="R3" s="11">
-        <v>45</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1080,55 +1008,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="F4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="H4" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="J4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-16.1</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-22</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="O4" s="6">
-        <v>100</v>
-      </c>
-      <c r="P4" s="12">
-        <v>90</v>
-      </c>
-      <c r="Q4" s="13">
-        <v>85</v>
-      </c>
-      <c r="R4" s="14">
-        <v>37</v>
+        <v>78</v>
+      </c>
+      <c r="P4" s="9">
+        <v>11</v>
+      </c>
+      <c r="Q4" s="11">
+        <v>18</v>
+      </c>
+      <c r="R4" s="12">
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1136,55 +1064,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-9.5</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O5" s="6">
+        <v>67</v>
+      </c>
+      <c r="P5" s="13">
         <v>27</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L5" s="4">
-        <v>-16.1</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="O5" s="15">
-        <v>27</v>
-      </c>
-      <c r="P5" s="16">
-        <v>9</v>
-      </c>
-      <c r="Q5" s="17">
+      <c r="Q5" s="14">
         <v>0</v>
       </c>
-      <c r="R5" s="18">
-        <v>17</v>
+      <c r="R5" s="13">
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1192,170 +1120,114 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-9.6</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="O6" s="6">
+        <v>100</v>
+      </c>
+      <c r="P6" s="10">
         <v>38</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="L6" s="4">
-        <v>-9.5</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="O6" s="15">
-        <v>28</v>
-      </c>
-      <c r="P6" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="17">
-        <v>0</v>
-      </c>
-      <c r="R6" s="18">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
-      <c r="A7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="2">
-        <v>12</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="L7" s="4">
-        <v>-9.6</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="O7" s="6">
-        <v>77</v>
-      </c>
-      <c r="P7" s="19">
-        <v>27</v>
-      </c>
-      <c r="Q7" s="18">
-        <v>15</v>
-      </c>
-      <c r="R7" s="20">
-        <v>63</v>
+      <c r="Q6" s="15">
+        <v>90</v>
+      </c>
+      <c r="R6" s="16">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A7">
+  <conditionalFormatting sqref="A2:A6">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B7">
+  <conditionalFormatting sqref="B2:B6">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C7">
+  <conditionalFormatting sqref="C2:C6">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D7">
+  <conditionalFormatting sqref="D2:D6">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E7">
+  <conditionalFormatting sqref="E2:E6">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F7">
+  <conditionalFormatting sqref="F2:F6">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G7">
+  <conditionalFormatting sqref="G2:G6">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H7">
+  <conditionalFormatting sqref="H2:H6">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I7">
+  <conditionalFormatting sqref="I2:I6">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J7">
+  <conditionalFormatting sqref="J2:J6">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K7">
+  <conditionalFormatting sqref="K2:K6">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L7">
+  <conditionalFormatting sqref="L2:L6">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1374,12 +1246,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M7">
+  <conditionalFormatting sqref="M2:M6">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N7">
+  <conditionalFormatting sqref="N2:N6">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1396,22 +1268,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O7">
+  <conditionalFormatting sqref="O2:O6">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P7">
+  <conditionalFormatting sqref="P2:P6">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q7">
+  <conditionalFormatting sqref="Q2:Q6">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R7">
+  <conditionalFormatting sqref="R2:R6">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="50">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260904--01</t>
-  </si>
-  <si>
-    <t>20260904--02</t>
-  </si>
-  <si>
     <t>20260905--01</t>
   </si>
   <si>
@@ -85,46 +79,25 @@
     <t>20260908--01</t>
   </si>
   <si>
-    <t>05:41</t>
+    <t>04:06</t>
+  </si>
+  <si>
+    <t>04:55</t>
   </si>
   <si>
     <t>02:38</t>
   </si>
   <si>
-    <t>04:06</t>
-  </si>
-  <si>
-    <t>04:55</t>
-  </si>
-  <si>
-    <t>05:15</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
     <t>02:40</t>
   </si>
   <si>
-    <t>18:34:03</t>
-  </si>
-  <si>
-    <t>20:11:13</t>
-  </si>
-  <si>
     <t>19:20:52</t>
   </si>
   <si>
     <t>18:30:31</t>
   </si>
   <si>
-    <t>18:26:54</t>
-  </si>
-  <si>
-    <t>18:36:20</t>
-  </si>
-  <si>
-    <t>20:14:22</t>
+    <t>18:26:55</t>
   </si>
   <si>
     <t>19:23:33</t>
@@ -136,12 +109,6 @@
     <t>18:30:04</t>
   </si>
   <si>
-    <t>18:39:10</t>
-  </si>
-  <si>
-    <t>20:15:41</t>
-  </si>
-  <si>
     <t>19:25:36</t>
   </si>
   <si>
@@ -151,12 +118,6 @@
     <t>18:31:23</t>
   </si>
   <si>
-    <t>18:42:01</t>
-  </si>
-  <si>
-    <t>20:17:00</t>
-  </si>
-  <si>
     <t>19:27:39</t>
   </si>
   <si>
@@ -166,12 +127,6 @@
     <t>18:32:42</t>
   </si>
   <si>
-    <t>18:44:17</t>
-  </si>
-  <si>
-    <t>20:20:08</t>
-  </si>
-  <si>
     <t>19:30:19</t>
   </si>
   <si>
@@ -181,12 +136,6 @@
     <t>18:35:50</t>
   </si>
   <si>
-    <t>13°</t>
-  </si>
-  <si>
-    <t>10°</t>
-  </si>
-  <si>
     <t>15°</t>
   </si>
   <si>
@@ -194,9 +143,6 @@
   </si>
   <si>
     <t>4°</t>
-  </si>
-  <si>
-    <t>18:41:35</t>
   </si>
   <si>
     <t>19:26:13</t>
@@ -251,7 +197,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -266,31 +212,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -302,31 +230,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -367,7 +307,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -412,9 +352,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -818,7 +755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -896,55 +833,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>16</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-16.1</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O2" s="6">
+        <v>39</v>
+      </c>
+      <c r="P2" s="7">
         <v>26</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="O2" s="6">
-        <v>63</v>
-      </c>
-      <c r="P2" s="7">
-        <v>32</v>
-      </c>
       <c r="Q2" s="8">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="R2" s="9">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -952,55 +889,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="L3" s="4">
-        <v>-22</v>
+        <v>-9.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="O3" s="6">
-        <v>85</v>
-      </c>
-      <c r="P3" s="10">
-        <v>41</v>
-      </c>
-      <c r="Q3" s="10">
-        <v>42</v>
-      </c>
-      <c r="R3" s="11">
-        <v>20</v>
+        <v>48</v>
+      </c>
+      <c r="O3" s="10">
+        <v>60</v>
+      </c>
+      <c r="P3" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="11">
+        <v>4</v>
+      </c>
+      <c r="R3" s="12">
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1008,226 +945,114 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="K4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-9.6</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-16.1</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="N4" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="O4" s="6">
-        <v>78</v>
-      </c>
-      <c r="P4" s="9">
-        <v>11</v>
-      </c>
-      <c r="Q4" s="11">
-        <v>18</v>
-      </c>
-      <c r="R4" s="12">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
-      <c r="A5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="2">
-        <v>19</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L5" s="4">
-        <v>-9.5</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="O5" s="6">
-        <v>67</v>
-      </c>
-      <c r="P5" s="13">
-        <v>27</v>
-      </c>
-      <c r="Q5" s="14">
-        <v>0</v>
-      </c>
-      <c r="R5" s="13">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
-      <c r="A6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="2">
-        <v>12</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="L6" s="4">
-        <v>-9.6</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="O6" s="6">
+      <c r="O4" s="10">
         <v>100</v>
       </c>
-      <c r="P6" s="10">
-        <v>38</v>
-      </c>
-      <c r="Q6" s="15">
-        <v>90</v>
-      </c>
-      <c r="R6" s="16">
-        <v>100</v>
+      <c r="P4" s="13">
+        <v>80</v>
+      </c>
+      <c r="Q4" s="14">
+        <v>70</v>
+      </c>
+      <c r="R4" s="15">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A6">
+  <conditionalFormatting sqref="A2:A4">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B6">
+  <conditionalFormatting sqref="B2:B4">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C6">
+  <conditionalFormatting sqref="C2:C4">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D6">
+  <conditionalFormatting sqref="D2:D4">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E6">
+  <conditionalFormatting sqref="E2:E4">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
+  <conditionalFormatting sqref="F2:F4">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G6">
+  <conditionalFormatting sqref="G2:G4">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H6">
+  <conditionalFormatting sqref="H2:H4">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I6">
+  <conditionalFormatting sqref="I2:I4">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
+  <conditionalFormatting sqref="J2:J4">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
+  <conditionalFormatting sqref="K2:K4">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
+  <conditionalFormatting sqref="L2:L4">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1246,12 +1071,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M6">
+  <conditionalFormatting sqref="M2:M4">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N6">
+  <conditionalFormatting sqref="N2:N4">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1268,22 +1093,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O6">
+  <conditionalFormatting sqref="O2:O4">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P6">
+  <conditionalFormatting sqref="P2:P4">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q6">
+  <conditionalFormatting sqref="Q2:Q4">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R6">
+  <conditionalFormatting sqref="R2:R4">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="39">
   <si>
     <t>Datum</t>
   </si>
@@ -70,73 +70,46 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260905--01</t>
-  </si>
-  <si>
     <t>20260906--01</t>
   </si>
   <si>
     <t>20260908--01</t>
   </si>
   <si>
-    <t>04:06</t>
-  </si>
-  <si>
-    <t>04:55</t>
+    <t>04:54</t>
   </si>
   <si>
     <t>02:38</t>
   </si>
   <si>
-    <t>02:40</t>
-  </si>
-  <si>
-    <t>19:20:52</t>
-  </si>
-  <si>
-    <t>18:30:31</t>
-  </si>
-  <si>
-    <t>18:26:55</t>
-  </si>
-  <si>
-    <t>19:23:33</t>
-  </si>
-  <si>
-    <t>18:32:59</t>
-  </si>
-  <si>
-    <t>18:30:04</t>
-  </si>
-  <si>
-    <t>19:25:36</t>
-  </si>
-  <si>
-    <t>18:35:26</t>
-  </si>
-  <si>
-    <t>18:31:23</t>
-  </si>
-  <si>
-    <t>19:27:39</t>
+    <t>18:30:32</t>
+  </si>
+  <si>
+    <t>18:26:57</t>
+  </si>
+  <si>
+    <t>18:33:00</t>
+  </si>
+  <si>
+    <t>18:30:06</t>
+  </si>
+  <si>
+    <t>18:35:27</t>
+  </si>
+  <si>
+    <t>18:31:25</t>
   </si>
   <si>
     <t>18:37:54</t>
   </si>
   <si>
-    <t>18:32:42</t>
-  </si>
-  <si>
-    <t>19:30:19</t>
+    <t>18:32:44</t>
   </si>
   <si>
     <t>18:40:21</t>
   </si>
   <si>
-    <t>18:35:50</t>
-  </si>
-  <si>
-    <t>15°</t>
+    <t>18:35:53</t>
   </si>
   <si>
     <t>9°</t>
@@ -145,16 +118,10 @@
     <t>4°</t>
   </si>
   <si>
-    <t>19:26:13</t>
-  </si>
-  <si>
-    <t>18:38:02</t>
-  </si>
-  <si>
-    <t>18:34:28</t>
-  </si>
-  <si>
-    <t>A+B</t>
+    <t>18:38:03</t>
+  </si>
+  <si>
+    <t>18:34:30</t>
   </si>
   <si>
     <t>A</t>
@@ -197,7 +164,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -212,19 +179,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -242,31 +197,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -307,7 +250,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -340,18 +283,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -755,7 +686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -833,55 +764,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="L2" s="4">
+        <v>-9.5</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-16.1</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="O2" s="6">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="P2" s="7">
-        <v>26</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>20</v>
-      </c>
-      <c r="R2" s="9">
         <v>0</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -889,170 +820,114 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="L3" s="4">
+        <v>-9.6</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L3" s="4">
-        <v>-9.5</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="O3" s="10">
-        <v>60</v>
+      <c r="O3" s="8">
+        <v>78</v>
       </c>
       <c r="P3" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="11">
-        <v>4</v>
-      </c>
-      <c r="R3" s="12">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18">
-      <c r="A4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="2">
-        <v>12</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-9.6</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="O4" s="10">
-        <v>100</v>
-      </c>
-      <c r="P4" s="13">
-        <v>80</v>
-      </c>
-      <c r="Q4" s="14">
-        <v>70</v>
-      </c>
-      <c r="R4" s="15">
-        <v>89</v>
+        <v>31</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>15</v>
+      </c>
+      <c r="R3" s="11">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A4">
+  <conditionalFormatting sqref="A2:A3">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B4">
+  <conditionalFormatting sqref="B2:B3">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C4">
+  <conditionalFormatting sqref="C2:C3">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D4">
+  <conditionalFormatting sqref="D2:D3">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E4">
+  <conditionalFormatting sqref="E2:E3">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F4">
+  <conditionalFormatting sqref="F2:F3">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G4">
+  <conditionalFormatting sqref="G2:G3">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H4">
+  <conditionalFormatting sqref="H2:H3">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I4">
+  <conditionalFormatting sqref="I2:I3">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J4">
+  <conditionalFormatting sqref="J2:J3">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K4">
+  <conditionalFormatting sqref="K2:K3">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L4">
+  <conditionalFormatting sqref="L2:L3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1071,12 +946,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M4">
+  <conditionalFormatting sqref="M2:M3">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N4">
+  <conditionalFormatting sqref="N2:N3">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1093,22 +968,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O4">
+  <conditionalFormatting sqref="O2:O3">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P4">
+  <conditionalFormatting sqref="P2:P3">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q4">
+  <conditionalFormatting sqref="Q2:Q3">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R4">
+  <conditionalFormatting sqref="R2:R3">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
   <si>
     <t>Datum</t>
   </si>
@@ -70,64 +70,34 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260906--01</t>
-  </si>
-  <si>
     <t>20260908--01</t>
   </si>
   <si>
-    <t>04:54</t>
-  </si>
-  <si>
     <t>02:38</t>
   </si>
   <si>
-    <t>18:30:32</t>
-  </si>
-  <si>
-    <t>18:26:57</t>
-  </si>
-  <si>
-    <t>18:33:00</t>
-  </si>
-  <si>
-    <t>18:30:06</t>
-  </si>
-  <si>
-    <t>18:35:27</t>
-  </si>
-  <si>
-    <t>18:31:25</t>
-  </si>
-  <si>
-    <t>18:37:54</t>
-  </si>
-  <si>
-    <t>18:32:44</t>
-  </si>
-  <si>
-    <t>18:40:21</t>
-  </si>
-  <si>
-    <t>18:35:53</t>
-  </si>
-  <si>
-    <t>9°</t>
+    <t>18:26:55</t>
+  </si>
+  <si>
+    <t>18:30:05</t>
+  </si>
+  <si>
+    <t>18:31:24</t>
+  </si>
+  <si>
+    <t>18:32:43</t>
+  </si>
+  <si>
+    <t>18:35:51</t>
   </si>
   <si>
     <t>4°</t>
   </si>
   <si>
-    <t>18:38:03</t>
-  </si>
-  <si>
-    <t>18:34:30</t>
+    <t>18:34:28</t>
   </si>
   <si>
     <t>A</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>4</t>
@@ -164,7 +134,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -179,37 +149,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -250,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -277,12 +235,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -686,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -764,170 +716,114 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>12</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="H2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="J2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="L2" s="4">
+        <v>-9.6</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="O2" s="6">
+        <v>99</v>
+      </c>
+      <c r="P2" s="7">
+        <v>64</v>
+      </c>
+      <c r="Q2" s="8">
         <v>34</v>
       </c>
-      <c r="L2" s="4">
-        <v>-9.5</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="O2" s="6">
-        <v>6</v>
-      </c>
-      <c r="P2" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>0</v>
-      </c>
-      <c r="R2" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18">
-      <c r="A3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="2">
-        <v>12</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L3" s="4">
-        <v>-9.6</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="O3" s="8">
+      <c r="R2" s="9">
         <v>78</v>
-      </c>
-      <c r="P3" s="9">
-        <v>31</v>
-      </c>
-      <c r="Q3" s="10">
-        <v>15</v>
-      </c>
-      <c r="R3" s="11">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A3">
+  <conditionalFormatting sqref="A2">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B3">
+  <conditionalFormatting sqref="B2">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C3">
+  <conditionalFormatting sqref="C2">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D3">
+  <conditionalFormatting sqref="D2">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E3">
+  <conditionalFormatting sqref="E2">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F3">
+  <conditionalFormatting sqref="F2">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G3">
+  <conditionalFormatting sqref="G2">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H3">
+  <conditionalFormatting sqref="H2">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I3">
+  <conditionalFormatting sqref="I2">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J3">
+  <conditionalFormatting sqref="J2">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K3">
+  <conditionalFormatting sqref="K2">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L3">
+  <conditionalFormatting sqref="L2">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -946,12 +842,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M3">
+  <conditionalFormatting sqref="M2">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N3">
+  <conditionalFormatting sqref="N2">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -968,22 +864,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O3">
+  <conditionalFormatting sqref="O2">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P3">
+  <conditionalFormatting sqref="P2">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q3">
+  <conditionalFormatting sqref="Q2">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R3">
+  <conditionalFormatting sqref="R2">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -76,25 +76,25 @@
     <t>02:38</t>
   </si>
   <si>
-    <t>18:26:55</t>
-  </si>
-  <si>
-    <t>18:30:05</t>
-  </si>
-  <si>
-    <t>18:31:24</t>
-  </si>
-  <si>
-    <t>18:32:43</t>
-  </si>
-  <si>
-    <t>18:35:51</t>
+    <t>18:26:54</t>
+  </si>
+  <si>
+    <t>18:30:03</t>
+  </si>
+  <si>
+    <t>18:31:23</t>
+  </si>
+  <si>
+    <t>18:32:41</t>
+  </si>
+  <si>
+    <t>18:35:50</t>
   </si>
   <si>
     <t>4°</t>
   </si>
   <si>
-    <t>18:34:28</t>
+    <t>18:34:27</t>
   </si>
   <si>
     <t>A</t>
@@ -149,13 +149,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -167,7 +161,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -755,16 +755,16 @@
         <v>28</v>
       </c>
       <c r="O2" s="6">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="P2" s="7">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="Q2" s="8">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="R2" s="9">
-        <v>78</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
   <si>
     <t>Datum</t>
   </si>
@@ -68,39 +68,6 @@
   </si>
   <si>
     <t>Vysoká</t>
-  </si>
-  <si>
-    <t>20260908--01</t>
-  </si>
-  <si>
-    <t>02:38</t>
-  </si>
-  <si>
-    <t>18:26:54</t>
-  </si>
-  <si>
-    <t>18:30:03</t>
-  </si>
-  <si>
-    <t>18:31:23</t>
-  </si>
-  <si>
-    <t>18:32:41</t>
-  </si>
-  <si>
-    <t>18:35:50</t>
-  </si>
-  <si>
-    <t>4°</t>
-  </si>
-  <si>
-    <t>18:34:27</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
 </sst>
 </file>
@@ -110,7 +77,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0&quot;°&quot;"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -126,15 +93,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF333333"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -144,30 +104,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD7E4BC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -208,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -224,18 +160,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -638,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -711,119 +635,63 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
-      <c r="A2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="2">
-        <v>12</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-9.6</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="6">
-        <v>45</v>
-      </c>
-      <c r="P2" s="7">
-        <v>37</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>20</v>
-      </c>
-      <c r="R2" s="9">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2">
+  <conditionalFormatting sqref="A1:A2">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2">
+  <conditionalFormatting sqref="B1:B2">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2">
+  <conditionalFormatting sqref="C1:C2">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2">
+  <conditionalFormatting sqref="D1:D2">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2">
+  <conditionalFormatting sqref="E1:E2">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2">
+  <conditionalFormatting sqref="F1:F2">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2">
+  <conditionalFormatting sqref="G1:G2">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2">
+  <conditionalFormatting sqref="H1:H2">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2">
+  <conditionalFormatting sqref="I1:I2">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2">
+  <conditionalFormatting sqref="J1:J2">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2">
+  <conditionalFormatting sqref="K1:K2">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2">
+  <conditionalFormatting sqref="L1:L2">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -842,12 +710,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2">
+  <conditionalFormatting sqref="M1:M2">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2">
+  <conditionalFormatting sqref="N1:N2">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -864,22 +732,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2">
+  <conditionalFormatting sqref="O1:O2">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2">
+  <conditionalFormatting sqref="P1:P2">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2">
+  <conditionalFormatting sqref="Q1:Q2">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2">
+  <conditionalFormatting sqref="R1:R2">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
   <si>
     <t>Datum</t>
   </si>
@@ -68,6 +68,39 @@
   </si>
   <si>
     <t>Vysoká</t>
+  </si>
+  <si>
+    <t>20261001--01</t>
+  </si>
+  <si>
+    <t>03:59</t>
+  </si>
+  <si>
+    <t>03:40:41</t>
+  </si>
+  <si>
+    <t>03:43:24</t>
+  </si>
+  <si>
+    <t>03:45:23</t>
+  </si>
+  <si>
+    <t>03:47:23</t>
+  </si>
+  <si>
+    <t>03:50:06</t>
+  </si>
+  <si>
+    <t>9°</t>
+  </si>
+  <si>
+    <t>03:43:01</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
 </sst>
 </file>
@@ -77,7 +110,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0&quot;°&quot;"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,8 +126,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -104,6 +144,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD7E4BC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -144,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -160,6 +212,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -562,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -635,63 +693,119 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2" spans="1:18">
+      <c r="A2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="2">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-13.4</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" s="6">
+        <v>0</v>
+      </c>
+      <c r="P2" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="7">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A2">
+  <conditionalFormatting sqref="A2">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B2">
+  <conditionalFormatting sqref="B2">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C2">
+  <conditionalFormatting sqref="C2">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D2">
+  <conditionalFormatting sqref="D2">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E2">
+  <conditionalFormatting sqref="E2">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F2">
+  <conditionalFormatting sqref="F2">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G1:G2">
+  <conditionalFormatting sqref="G2">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1:H2">
+  <conditionalFormatting sqref="H2">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I2">
+  <conditionalFormatting sqref="I2">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J2">
+  <conditionalFormatting sqref="J2">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:K2">
+  <conditionalFormatting sqref="K2">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L1:L2">
+  <conditionalFormatting sqref="L2">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -710,12 +824,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M1:M2">
+  <conditionalFormatting sqref="M2">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N1:N2">
+  <conditionalFormatting sqref="N2">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -732,22 +846,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O1:O2">
+  <conditionalFormatting sqref="O2">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P1:P2">
+  <conditionalFormatting sqref="P2">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q1:Q2">
+  <conditionalFormatting sqref="Q2">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R2">
+  <conditionalFormatting sqref="R2">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
   <si>
     <t>Datum</t>
   </si>
@@ -73,34 +73,70 @@
     <t>20261001--01</t>
   </si>
   <si>
+    <t>20261002--01</t>
+  </si>
+  <si>
     <t>03:59</t>
   </si>
   <si>
+    <t>02:06</t>
+  </si>
+  <si>
+    <t>01:07</t>
+  </si>
+  <si>
     <t>03:40:41</t>
   </si>
   <si>
+    <t>02:49:07</t>
+  </si>
+  <si>
     <t>03:43:24</t>
   </si>
   <si>
+    <t>02:52:27</t>
+  </si>
+  <si>
     <t>03:45:23</t>
   </si>
   <si>
+    <t>02:53:30</t>
+  </si>
+  <si>
     <t>03:47:23</t>
   </si>
   <si>
+    <t>02:54:33</t>
+  </si>
+  <si>
     <t>03:50:06</t>
   </si>
   <si>
+    <t>02:57:54</t>
+  </si>
+  <si>
     <t>9°</t>
   </si>
   <si>
+    <t>11°</t>
+  </si>
+  <si>
     <t>03:43:01</t>
   </si>
   <si>
+    <t>02:53:26</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
+    <t>A+B</t>
+  </si>
+  <si>
     <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
 </sst>
 </file>
@@ -134,7 +170,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -149,13 +185,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -196,7 +256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -217,6 +277,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -620,7 +692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -701,111 +773,167 @@
         <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="L2" s="4">
         <v>-13.4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="N2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="O2" s="6">
+        <v>20</v>
+      </c>
+      <c r="P2" s="7">
+        <v>11</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>0</v>
+      </c>
+      <c r="R2" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="2">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="6">
-        <v>0</v>
-      </c>
-      <c r="P2" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>0</v>
-      </c>
-      <c r="R2" s="7">
-        <v>0</v>
+      <c r="H3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" s="4">
+        <v>-21.5</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O3" s="9">
+        <v>72</v>
+      </c>
+      <c r="P3" s="10">
+        <v>56</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>10</v>
+      </c>
+      <c r="R3" s="11">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2">
+  <conditionalFormatting sqref="A2:A3">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2">
+  <conditionalFormatting sqref="B2:B3">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2">
+  <conditionalFormatting sqref="C2:C3">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2">
+  <conditionalFormatting sqref="D2:D3">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2">
+  <conditionalFormatting sqref="E2:E3">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2">
+  <conditionalFormatting sqref="F2:F3">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2">
+  <conditionalFormatting sqref="G2:G3">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2">
+  <conditionalFormatting sqref="H2:H3">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2">
+  <conditionalFormatting sqref="I2:I3">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2">
+  <conditionalFormatting sqref="J2:J3">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2">
+  <conditionalFormatting sqref="K2:K3">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2">
+  <conditionalFormatting sqref="L2:L3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -824,12 +952,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2">
+  <conditionalFormatting sqref="M2:M3">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2">
+  <conditionalFormatting sqref="N2:N3">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -846,22 +974,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2">
+  <conditionalFormatting sqref="O2:O3">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2">
+  <conditionalFormatting sqref="P2:P3">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2">
+  <conditionalFormatting sqref="Q2:Q3">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2">
+  <conditionalFormatting sqref="R2:R3">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="52">
   <si>
     <t>Datum</t>
   </si>
@@ -76,43 +76,67 @@
     <t>20261002--01</t>
   </si>
   <si>
-    <t>03:59</t>
-  </si>
-  <si>
-    <t>02:06</t>
-  </si>
-  <si>
-    <t>01:07</t>
-  </si>
-  <si>
-    <t>03:40:41</t>
-  </si>
-  <si>
-    <t>02:49:07</t>
-  </si>
-  <si>
-    <t>03:43:24</t>
-  </si>
-  <si>
-    <t>02:52:27</t>
-  </si>
-  <si>
-    <t>03:45:23</t>
-  </si>
-  <si>
-    <t>02:53:30</t>
-  </si>
-  <si>
-    <t>03:47:23</t>
-  </si>
-  <si>
-    <t>02:54:33</t>
-  </si>
-  <si>
-    <t>03:50:06</t>
-  </si>
-  <si>
-    <t>02:57:54</t>
+    <t>20261003--01</t>
+  </si>
+  <si>
+    <t>03:57</t>
+  </si>
+  <si>
+    <t>02:02</t>
+  </si>
+  <si>
+    <t>05:15</t>
+  </si>
+  <si>
+    <t>01:03</t>
+  </si>
+  <si>
+    <t>04:00</t>
+  </si>
+  <si>
+    <t>03:40:17</t>
+  </si>
+  <si>
+    <t>02:48:36</t>
+  </si>
+  <si>
+    <t>03:32:09</t>
+  </si>
+  <si>
+    <t>03:43:00</t>
+  </si>
+  <si>
+    <t>02:51:57</t>
+  </si>
+  <si>
+    <t>03:34:31</t>
+  </si>
+  <si>
+    <t>03:44:58</t>
+  </si>
+  <si>
+    <t>02:52:58</t>
+  </si>
+  <si>
+    <t>03:37:08</t>
+  </si>
+  <si>
+    <t>03:46:57</t>
+  </si>
+  <si>
+    <t>02:53:59</t>
+  </si>
+  <si>
+    <t>03:39:46</t>
+  </si>
+  <si>
+    <t>03:49:42</t>
+  </si>
+  <si>
+    <t>02:57:22</t>
+  </si>
+  <si>
+    <t>03:42:10</t>
   </si>
   <si>
     <t>9°</t>
@@ -121,10 +145,16 @@
     <t>11°</t>
   </si>
   <si>
-    <t>03:43:01</t>
-  </si>
-  <si>
-    <t>02:53:26</t>
+    <t>17°</t>
+  </si>
+  <si>
+    <t>03:42:37</t>
+  </si>
+  <si>
+    <t>02:52:56</t>
+  </si>
+  <si>
+    <t>03:35:46</t>
   </si>
   <si>
     <t>A</t>
@@ -137,6 +167,9 @@
   </si>
   <si>
     <t>4</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
 </sst>
 </file>
@@ -185,13 +218,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -215,7 +242,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -692,7 +725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -773,52 +806,52 @@
         <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="L2" s="4">
-        <v>-13.4</v>
+        <v>-13.5</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="O2" s="6">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="P2" s="7">
-        <v>11</v>
-      </c>
-      <c r="Q2" s="8">
         <v>0</v>
       </c>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
       <c r="R2" s="7">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -829,111 +862,167 @@
         <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L3" s="4">
         <v>-21.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="N3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O3" s="8">
+        <v>79</v>
+      </c>
+      <c r="P3" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>0</v>
+      </c>
+      <c r="R3" s="9">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="2">
+        <v>22</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O3" s="9">
-        <v>72</v>
-      </c>
-      <c r="P3" s="10">
-        <v>56</v>
-      </c>
-      <c r="Q3" s="7">
-        <v>10</v>
-      </c>
-      <c r="R3" s="11">
-        <v>25</v>
+      <c r="J4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-15.1</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O4" s="8">
+        <v>81</v>
+      </c>
+      <c r="P4" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="10">
+        <v>11</v>
+      </c>
+      <c r="R4" s="11">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A3">
+  <conditionalFormatting sqref="A2:A4">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B3">
+  <conditionalFormatting sqref="B2:B4">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C3">
+  <conditionalFormatting sqref="C2:C4">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D3">
+  <conditionalFormatting sqref="D2:D4">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E3">
+  <conditionalFormatting sqref="E2:E4">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F3">
+  <conditionalFormatting sqref="F2:F4">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G3">
+  <conditionalFormatting sqref="G2:G4">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H3">
+  <conditionalFormatting sqref="H2:H4">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I3">
+  <conditionalFormatting sqref="I2:I4">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J3">
+  <conditionalFormatting sqref="J2:J4">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K3">
+  <conditionalFormatting sqref="K2:K4">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L3">
+  <conditionalFormatting sqref="L2:L4">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -952,12 +1041,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M3">
+  <conditionalFormatting sqref="M2:M4">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N3">
+  <conditionalFormatting sqref="N2:N4">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -974,22 +1063,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O3">
+  <conditionalFormatting sqref="O2:O4">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P3">
+  <conditionalFormatting sqref="P2:P4">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q3">
+  <conditionalFormatting sqref="Q2:Q4">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R3">
+  <conditionalFormatting sqref="R2:R4">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="72">
   <si>
     <t>Datum</t>
   </si>
@@ -79,6 +79,12 @@
     <t>20261003--01</t>
   </si>
   <si>
+    <t>20261004--01</t>
+  </si>
+  <si>
+    <t>20261004--02</t>
+  </si>
+  <si>
     <t>03:57</t>
   </si>
   <si>
@@ -88,12 +94,24 @@
     <t>05:15</t>
   </si>
   <si>
+    <t>04:37</t>
+  </si>
+  <si>
+    <t>05:54</t>
+  </si>
+  <si>
     <t>01:03</t>
   </si>
   <si>
     <t>04:00</t>
   </si>
   <si>
+    <t>01:25</t>
+  </si>
+  <si>
+    <t>05:53</t>
+  </si>
+  <si>
     <t>03:40:17</t>
   </si>
   <si>
@@ -103,6 +121,12 @@
     <t>03:32:09</t>
   </si>
   <si>
+    <t>02:40:04</t>
+  </si>
+  <si>
+    <t>04:16:13</t>
+  </si>
+  <si>
     <t>03:43:00</t>
   </si>
   <si>
@@ -112,6 +136,12 @@
     <t>03:34:31</t>
   </si>
   <si>
+    <t>02:42:35</t>
+  </si>
+  <si>
+    <t>04:18:26</t>
+  </si>
+  <si>
     <t>03:44:58</t>
   </si>
   <si>
@@ -121,6 +151,12 @@
     <t>03:37:08</t>
   </si>
   <si>
+    <t>02:44:53</t>
+  </si>
+  <si>
+    <t>04:21:23</t>
+  </si>
+  <si>
     <t>03:46:57</t>
   </si>
   <si>
@@ -130,6 +166,12 @@
     <t>03:39:46</t>
   </si>
   <si>
+    <t>02:47:12</t>
+  </si>
+  <si>
+    <t>04:24:20</t>
+  </si>
+  <si>
     <t>03:49:42</t>
   </si>
   <si>
@@ -139,6 +181,12 @@
     <t>03:42:10</t>
   </si>
   <si>
+    <t>02:49:45</t>
+  </si>
+  <si>
+    <t>04:26:35</t>
+  </si>
+  <si>
     <t>9°</t>
   </si>
   <si>
@@ -148,6 +196,12 @@
     <t>17°</t>
   </si>
   <si>
+    <t>16°</t>
+  </si>
+  <si>
+    <t>10°</t>
+  </si>
+  <si>
     <t>03:42:37</t>
   </si>
   <si>
@@ -155,6 +209,12 @@
   </si>
   <si>
     <t>03:35:46</t>
+  </si>
+  <si>
+    <t>02:45:47</t>
+  </si>
+  <si>
+    <t>04:18:27</t>
   </si>
   <si>
     <t>A</t>
@@ -203,7 +263,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -218,7 +278,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -230,25 +290,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -289,7 +385,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -322,6 +418,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -725,7 +839,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -806,43 +920,43 @@
         <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="L2" s="4">
         <v>-13.5</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="O2" s="6">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
@@ -850,8 +964,8 @@
       <c r="Q2" s="7">
         <v>0</v>
       </c>
-      <c r="R2" s="7">
-        <v>2</v>
+      <c r="R2" s="8">
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -862,52 +976,52 @@
         <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="L3" s="4">
         <v>-21.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="O3" s="8">
-        <v>79</v>
-      </c>
-      <c r="P3" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="7">
-        <v>0</v>
-      </c>
-      <c r="R3" s="9">
-        <v>56</v>
+        <v>70</v>
+      </c>
+      <c r="O3" s="6">
+        <v>100</v>
+      </c>
+      <c r="P3" s="9">
+        <v>46</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>98</v>
+      </c>
+      <c r="R3" s="11">
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -918,111 +1032,223 @@
         <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="L4" s="4">
         <v>-15.1</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="N4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O4" s="6">
+        <v>93</v>
+      </c>
+      <c r="P4" s="11">
+        <v>75</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>46</v>
+      </c>
+      <c r="R4" s="12">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="2">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-23.2</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O5" s="6">
+        <v>61</v>
+      </c>
+      <c r="P5" s="13">
+        <v>23</v>
+      </c>
+      <c r="Q5" s="14">
+        <v>35</v>
+      </c>
+      <c r="R5" s="15">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="2">
+        <v>30</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="O4" s="8">
-        <v>81</v>
-      </c>
-      <c r="P4" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="10">
-        <v>11</v>
-      </c>
-      <c r="R4" s="11">
-        <v>59</v>
+      <c r="I6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-8.5</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O6" s="6">
+        <v>62</v>
+      </c>
+      <c r="P6" s="16">
+        <v>18</v>
+      </c>
+      <c r="Q6" s="17">
+        <v>30</v>
+      </c>
+      <c r="R6" s="13">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A4">
+  <conditionalFormatting sqref="A2:A6">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B4">
+  <conditionalFormatting sqref="B2:B6">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C4">
+  <conditionalFormatting sqref="C2:C6">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D4">
+  <conditionalFormatting sqref="D2:D6">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E4">
+  <conditionalFormatting sqref="E2:E6">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F4">
+  <conditionalFormatting sqref="F2:F6">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G4">
+  <conditionalFormatting sqref="G2:G6">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H4">
+  <conditionalFormatting sqref="H2:H6">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I4">
+  <conditionalFormatting sqref="I2:I6">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J4">
+  <conditionalFormatting sqref="J2:J6">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K4">
+  <conditionalFormatting sqref="K2:K6">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L4">
+  <conditionalFormatting sqref="L2:L6">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1041,12 +1267,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M4">
+  <conditionalFormatting sqref="M2:M6">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N4">
+  <conditionalFormatting sqref="N2:N6">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1063,22 +1289,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O4">
+  <conditionalFormatting sqref="O2:O6">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P4">
+  <conditionalFormatting sqref="P2:P6">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q4">
+  <conditionalFormatting sqref="Q2:Q6">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R4">
+  <conditionalFormatting sqref="R2:R6">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
   <si>
     <t>Datum</t>
   </si>
@@ -85,106 +85,148 @@
     <t>20261004--02</t>
   </si>
   <si>
-    <t>03:57</t>
-  </si>
-  <si>
-    <t>02:02</t>
-  </si>
-  <si>
-    <t>05:15</t>
-  </si>
-  <si>
-    <t>04:37</t>
-  </si>
-  <si>
-    <t>05:54</t>
-  </si>
-  <si>
-    <t>01:03</t>
-  </si>
-  <si>
-    <t>04:00</t>
-  </si>
-  <si>
-    <t>01:25</t>
-  </si>
-  <si>
-    <t>05:53</t>
+    <t>20261005--01</t>
+  </si>
+  <si>
+    <t>20261005--02</t>
+  </si>
+  <si>
+    <t>03:59</t>
+  </si>
+  <si>
+    <t>02:06</t>
+  </si>
+  <si>
+    <t>05:17</t>
+  </si>
+  <si>
+    <t>04:39</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>03:33</t>
+  </si>
+  <si>
+    <t>05:47</t>
+  </si>
+  <si>
+    <t>01:07</t>
+  </si>
+  <si>
+    <t>04:03</t>
+  </si>
+  <si>
+    <t>01:28</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>03:34</t>
+  </si>
+  <si>
+    <t>03:40:31</t>
+  </si>
+  <si>
+    <t>02:48:57</t>
+  </si>
+  <si>
+    <t>03:32:38</t>
+  </si>
+  <si>
+    <t>02:40:43</t>
+  </si>
+  <si>
+    <t>04:16:53</t>
+  </si>
+  <si>
+    <t>01:48:49</t>
+  </si>
+  <si>
+    <t>03:24:42</t>
+  </si>
+  <si>
+    <t>03:43:14</t>
+  </si>
+  <si>
+    <t>02:52:17</t>
+  </si>
+  <si>
+    <t>03:35:00</t>
+  </si>
+  <si>
+    <t>02:43:14</t>
+  </si>
+  <si>
+    <t>04:19:06</t>
+  </si>
+  <si>
+    <t>01:51:39</t>
+  </si>
+  <si>
+    <t>03:26:57</t>
+  </si>
+  <si>
+    <t>03:45:13</t>
+  </si>
+  <si>
+    <t>02:53:20</t>
+  </si>
+  <si>
+    <t>03:37:38</t>
+  </si>
+  <si>
+    <t>02:45:33</t>
+  </si>
+  <si>
+    <t>04:22:04</t>
+  </si>
+  <si>
+    <t>01:53:25</t>
+  </si>
+  <si>
+    <t>03:29:51</t>
+  </si>
+  <si>
+    <t>03:47:13</t>
+  </si>
+  <si>
+    <t>02:54:23</t>
   </si>
   <si>
     <t>03:40:17</t>
   </si>
   <si>
-    <t>02:48:36</t>
-  </si>
-  <si>
-    <t>03:32:09</t>
-  </si>
-  <si>
-    <t>02:40:04</t>
-  </si>
-  <si>
-    <t>04:16:13</t>
-  </si>
-  <si>
-    <t>03:43:00</t>
-  </si>
-  <si>
-    <t>02:51:57</t>
-  </si>
-  <si>
-    <t>03:34:31</t>
-  </si>
-  <si>
-    <t>02:42:35</t>
-  </si>
-  <si>
-    <t>04:18:26</t>
-  </si>
-  <si>
-    <t>03:44:58</t>
-  </si>
-  <si>
-    <t>02:52:58</t>
-  </si>
-  <si>
-    <t>03:37:08</t>
-  </si>
-  <si>
-    <t>02:44:53</t>
-  </si>
-  <si>
-    <t>04:21:23</t>
-  </si>
-  <si>
-    <t>03:46:57</t>
-  </si>
-  <si>
-    <t>02:53:59</t>
-  </si>
-  <si>
-    <t>03:39:46</t>
-  </si>
-  <si>
-    <t>02:47:12</t>
-  </si>
-  <si>
-    <t>04:24:20</t>
-  </si>
-  <si>
-    <t>03:49:42</t>
-  </si>
-  <si>
-    <t>02:57:22</t>
-  </si>
-  <si>
-    <t>03:42:10</t>
-  </si>
-  <si>
-    <t>02:49:45</t>
-  </si>
-  <si>
-    <t>04:26:35</t>
+    <t>02:47:53</t>
+  </si>
+  <si>
+    <t>04:25:01</t>
+  </si>
+  <si>
+    <t>01:55:12</t>
+  </si>
+  <si>
+    <t>03:32:44</t>
+  </si>
+  <si>
+    <t>03:49:57</t>
+  </si>
+  <si>
+    <t>02:57:44</t>
+  </si>
+  <si>
+    <t>03:42:41</t>
+  </si>
+  <si>
+    <t>02:50:25</t>
+  </si>
+  <si>
+    <t>04:27:16</t>
+  </si>
+  <si>
+    <t>01:58:03</t>
   </si>
   <si>
     <t>9°</t>
@@ -202,19 +244,31 @@
     <t>10°</t>
   </si>
   <si>
-    <t>03:42:37</t>
-  </si>
-  <si>
-    <t>02:52:56</t>
-  </si>
-  <si>
-    <t>03:35:46</t>
-  </si>
-  <si>
-    <t>02:45:47</t>
-  </si>
-  <si>
-    <t>04:18:27</t>
+    <t>5°</t>
+  </si>
+  <si>
+    <t>26°</t>
+  </si>
+  <si>
+    <t>03:42:51</t>
+  </si>
+  <si>
+    <t>02:53:16</t>
+  </si>
+  <si>
+    <t>03:36:14</t>
+  </si>
+  <si>
+    <t>02:46:25</t>
+  </si>
+  <si>
+    <t>04:19:05</t>
+  </si>
+  <si>
+    <t>01:56:30</t>
+  </si>
+  <si>
+    <t>03:29:10</t>
   </si>
   <si>
     <t>A</t>
@@ -223,6 +277,9 @@
     <t>A+B</t>
   </si>
   <si>
+    <t>B</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
@@ -230,6 +287,9 @@
   </si>
   <si>
     <t>2</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
 </sst>
 </file>
@@ -263,7 +323,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -290,37 +350,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FFEEF3F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -332,19 +410,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -385,7 +469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -436,6 +520,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -839,7 +935,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -920,52 +1016,52 @@
         <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="L2" s="4">
-        <v>-13.5</v>
+        <v>-13.4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="O2" s="6">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
-      <c r="Q2" s="7">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
-        <v>60</v>
+      <c r="Q2" s="8">
+        <v>9</v>
+      </c>
+      <c r="R2" s="9">
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -976,52 +1072,52 @@
         <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="L3" s="4">
         <v>-21.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="O3" s="6">
         <v>100</v>
       </c>
-      <c r="P3" s="9">
-        <v>46</v>
-      </c>
-      <c r="Q3" s="10">
-        <v>98</v>
-      </c>
-      <c r="R3" s="11">
-        <v>77</v>
+      <c r="P3" s="10">
+        <v>23</v>
+      </c>
+      <c r="Q3" s="11">
+        <v>47</v>
+      </c>
+      <c r="R3" s="12">
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1032,52 +1128,52 @@
         <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="L4" s="4">
         <v>-15.1</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="O4" s="6">
-        <v>93</v>
-      </c>
-      <c r="P4" s="11">
-        <v>75</v>
-      </c>
-      <c r="Q4" s="9">
-        <v>46</v>
-      </c>
-      <c r="R4" s="12">
-        <v>79</v>
+        <v>56</v>
+      </c>
+      <c r="P4" s="13">
+        <v>55</v>
+      </c>
+      <c r="Q4" s="14">
+        <v>16</v>
+      </c>
+      <c r="R4" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1088,52 +1184,52 @@
         <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-23.1</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="O5" s="6">
+        <v>96</v>
+      </c>
+      <c r="P5" s="8">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="15">
         <v>60</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L5" s="4">
-        <v>-23.2</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="O5" s="6">
-        <v>61</v>
-      </c>
-      <c r="P5" s="13">
-        <v>23</v>
-      </c>
-      <c r="Q5" s="14">
-        <v>35</v>
-      </c>
-      <c r="R5" s="15">
-        <v>16</v>
+      <c r="R5" s="16">
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1144,111 +1240,223 @@
         <v>30</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-8.4</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="O6" s="6">
+        <v>99</v>
+      </c>
+      <c r="P6" s="17">
+        <v>35</v>
+      </c>
+      <c r="Q6" s="13">
+        <v>55</v>
+      </c>
+      <c r="R6" s="12">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="A7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="2">
+        <v>14</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L7" s="4">
+        <v>-30.5</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="O7" s="18">
+        <v>45</v>
+      </c>
+      <c r="P7" s="17">
+        <v>36</v>
+      </c>
+      <c r="Q7" s="19">
+        <v>41</v>
+      </c>
+      <c r="R7" s="20">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="2">
+        <v>28</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="D8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="L6" s="4">
-        <v>-8.5</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="O6" s="6">
-        <v>62</v>
-      </c>
-      <c r="P6" s="16">
-        <v>18</v>
-      </c>
-      <c r="Q6" s="17">
-        <v>30</v>
-      </c>
-      <c r="R6" s="13">
+      <c r="J8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L8" s="4">
+        <v>-16.8</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="O8" s="6">
+        <v>83</v>
+      </c>
+      <c r="P8" s="10">
         <v>24</v>
+      </c>
+      <c r="Q8" s="14">
+        <v>14</v>
+      </c>
+      <c r="R8" s="21">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A6">
+  <conditionalFormatting sqref="A2:A8">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B6">
+  <conditionalFormatting sqref="B2:B8">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C6">
+  <conditionalFormatting sqref="C2:C8">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D6">
+  <conditionalFormatting sqref="D2:D8">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E6">
+  <conditionalFormatting sqref="E2:E8">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
+  <conditionalFormatting sqref="F2:F8">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G6">
+  <conditionalFormatting sqref="G2:G8">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H6">
+  <conditionalFormatting sqref="H2:H8">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I6">
+  <conditionalFormatting sqref="I2:I8">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
+  <conditionalFormatting sqref="J2:J8">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
+  <conditionalFormatting sqref="K2:K8">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
+  <conditionalFormatting sqref="L2:L8">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1267,12 +1475,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M6">
+  <conditionalFormatting sqref="M2:M8">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N6">
+  <conditionalFormatting sqref="N2:N8">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1289,22 +1497,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O6">
+  <conditionalFormatting sqref="O2:O8">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P6">
+  <conditionalFormatting sqref="P2:P8">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q6">
+  <conditionalFormatting sqref="Q2:Q8">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R6">
+  <conditionalFormatting sqref="R2:R8">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="118">
   <si>
     <t>Datum</t>
   </si>
@@ -91,142 +91,211 @@
     <t>20261005--02</t>
   </si>
   <si>
-    <t>03:59</t>
-  </si>
-  <si>
-    <t>02:06</t>
-  </si>
-  <si>
-    <t>05:17</t>
-  </si>
-  <si>
-    <t>04:39</t>
+    <t>20261006--01</t>
+  </si>
+  <si>
+    <t>20261006--02</t>
+  </si>
+  <si>
+    <t>20261006--03</t>
+  </si>
+  <si>
+    <t>04:00</t>
+  </si>
+  <si>
+    <t>02:08</t>
+  </si>
+  <si>
+    <t>05:18</t>
+  </si>
+  <si>
+    <t>04:41</t>
   </si>
   <si>
     <t>05:55</t>
   </si>
   <si>
-    <t>03:33</t>
-  </si>
-  <si>
-    <t>05:47</t>
-  </si>
-  <si>
-    <t>01:07</t>
-  </si>
-  <si>
-    <t>04:03</t>
-  </si>
-  <si>
-    <t>01:28</t>
+    <t>03:34</t>
+  </si>
+  <si>
+    <t>05:48</t>
+  </si>
+  <si>
+    <t>00:16</t>
+  </si>
+  <si>
+    <t>05:33</t>
+  </si>
+  <si>
+    <t>05:53</t>
+  </si>
+  <si>
+    <t>01:09</t>
+  </si>
+  <si>
+    <t>04:04</t>
+  </si>
+  <si>
+    <t>01:30</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>03:34</t>
-  </si>
-  <si>
-    <t>03:40:31</t>
-  </si>
-  <si>
-    <t>02:48:57</t>
-  </si>
-  <si>
-    <t>03:32:38</t>
-  </si>
-  <si>
-    <t>02:40:43</t>
-  </si>
-  <si>
-    <t>04:16:53</t>
-  </si>
-  <si>
-    <t>01:48:49</t>
-  </si>
-  <si>
-    <t>03:24:42</t>
-  </si>
-  <si>
-    <t>03:43:14</t>
-  </si>
-  <si>
-    <t>02:52:17</t>
-  </si>
-  <si>
-    <t>03:35:00</t>
-  </si>
-  <si>
-    <t>02:43:14</t>
-  </si>
-  <si>
-    <t>04:19:06</t>
-  </si>
-  <si>
-    <t>01:51:39</t>
-  </si>
-  <si>
-    <t>03:26:57</t>
-  </si>
-  <si>
-    <t>03:45:13</t>
-  </si>
-  <si>
-    <t>02:53:20</t>
-  </si>
-  <si>
-    <t>03:37:38</t>
-  </si>
-  <si>
-    <t>02:45:33</t>
-  </si>
-  <si>
-    <t>04:22:04</t>
-  </si>
-  <si>
-    <t>01:53:25</t>
-  </si>
-  <si>
-    <t>03:29:51</t>
-  </si>
-  <si>
-    <t>03:47:13</t>
-  </si>
-  <si>
-    <t>02:54:23</t>
-  </si>
-  <si>
-    <t>03:40:17</t>
-  </si>
-  <si>
-    <t>02:47:53</t>
-  </si>
-  <si>
-    <t>04:25:01</t>
-  </si>
-  <si>
-    <t>01:55:12</t>
-  </si>
-  <si>
-    <t>03:32:44</t>
-  </si>
-  <si>
-    <t>03:49:57</t>
-  </si>
-  <si>
-    <t>02:57:44</t>
-  </si>
-  <si>
-    <t>03:42:41</t>
-  </si>
-  <si>
-    <t>02:50:25</t>
-  </si>
-  <si>
-    <t>04:27:16</t>
-  </si>
-  <si>
-    <t>01:58:03</t>
+    <t>03:36</t>
+  </si>
+  <si>
+    <t>01:11</t>
+  </si>
+  <si>
+    <t>05:16</t>
+  </si>
+  <si>
+    <t>03:40:34</t>
+  </si>
+  <si>
+    <t>02:49:02</t>
+  </si>
+  <si>
+    <t>03:32:47</t>
+  </si>
+  <si>
+    <t>02:40:55</t>
+  </si>
+  <si>
+    <t>04:17:06</t>
+  </si>
+  <si>
+    <t>01:49:07</t>
+  </si>
+  <si>
+    <t>03:25:00</t>
+  </si>
+  <si>
+    <t>00:57:23</t>
+  </si>
+  <si>
+    <t>02:32:53</t>
+  </si>
+  <si>
+    <t>04:09:22</t>
+  </si>
+  <si>
+    <t>03:43:17</t>
+  </si>
+  <si>
+    <t>02:52:22</t>
+  </si>
+  <si>
+    <t>03:35:09</t>
+  </si>
+  <si>
+    <t>02:43:26</t>
+  </si>
+  <si>
+    <t>04:19:20</t>
+  </si>
+  <si>
+    <t>01:51:56</t>
+  </si>
+  <si>
+    <t>03:27:15</t>
+  </si>
+  <si>
+    <t>01:01:38</t>
+  </si>
+  <si>
+    <t>02:35:11</t>
+  </si>
+  <si>
+    <t>04:11:36</t>
+  </si>
+  <si>
+    <t>03:45:16</t>
+  </si>
+  <si>
+    <t>02:53:25</t>
+  </si>
+  <si>
+    <t>03:37:48</t>
+  </si>
+  <si>
+    <t>02:45:46</t>
+  </si>
+  <si>
+    <t>04:22:17</t>
+  </si>
+  <si>
+    <t>01:53:43</t>
+  </si>
+  <si>
+    <t>03:30:08</t>
+  </si>
+  <si>
+    <t>02:37:57</t>
+  </si>
+  <si>
+    <t>04:14:32</t>
+  </si>
+  <si>
+    <t>03:47:17</t>
+  </si>
+  <si>
+    <t>02:54:30</t>
+  </si>
+  <si>
+    <t>03:40:27</t>
+  </si>
+  <si>
+    <t>02:48:07</t>
+  </si>
+  <si>
+    <t>04:25:15</t>
+  </si>
+  <si>
+    <t>01:55:30</t>
+  </si>
+  <si>
+    <t>03:33:03</t>
+  </si>
+  <si>
+    <t>01:01:54</t>
+  </si>
+  <si>
+    <t>02:40:44</t>
+  </si>
+  <si>
+    <t>04:17:29</t>
+  </si>
+  <si>
+    <t>03:50:01</t>
+  </si>
+  <si>
+    <t>02:57:51</t>
+  </si>
+  <si>
+    <t>03:42:50</t>
+  </si>
+  <si>
+    <t>02:50:39</t>
+  </si>
+  <si>
+    <t>04:27:30</t>
+  </si>
+  <si>
+    <t>01:58:21</t>
+  </si>
+  <si>
+    <t>03:35:19</t>
+  </si>
+  <si>
+    <t>01:05:55</t>
+  </si>
+  <si>
+    <t>02:43:03</t>
+  </si>
+  <si>
+    <t>04:19:44</t>
   </si>
   <si>
     <t>9°</t>
@@ -250,25 +319,37 @@
     <t>26°</t>
   </si>
   <si>
-    <t>03:42:51</t>
-  </si>
-  <si>
-    <t>02:53:16</t>
-  </si>
-  <si>
-    <t>03:36:14</t>
-  </si>
-  <si>
-    <t>02:46:25</t>
-  </si>
-  <si>
-    <t>04:19:05</t>
-  </si>
-  <si>
-    <t>01:56:30</t>
-  </si>
-  <si>
-    <t>03:29:10</t>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>14°</t>
+  </si>
+  <si>
+    <t>03:42:54</t>
+  </si>
+  <si>
+    <t>02:53:21</t>
+  </si>
+  <si>
+    <t>03:36:23</t>
+  </si>
+  <si>
+    <t>02:46:37</t>
+  </si>
+  <si>
+    <t>04:19:18</t>
+  </si>
+  <si>
+    <t>01:56:47</t>
+  </si>
+  <si>
+    <t>03:29:27</t>
+  </si>
+  <si>
+    <t>02:39:33</t>
+  </si>
+  <si>
+    <t>04:12:13</t>
   </si>
   <si>
     <t>A</t>
@@ -280,13 +361,10 @@
     <t>B</t>
   </si>
   <si>
-    <t>3</t>
+    <t>2</t>
   </si>
   <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>1</t>
@@ -323,7 +401,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -350,13 +428,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -368,13 +458,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,31 +476,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,13 +512,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -469,7 +553,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -532,6 +616,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -935,7 +1022,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1016,52 +1103,52 @@
         <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="L2" s="4">
         <v>-13.4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="O2" s="6">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
-      <c r="Q2" s="8">
-        <v>9</v>
-      </c>
-      <c r="R2" s="9">
-        <v>96</v>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="8">
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1072,51 +1159,51 @@
         <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="L3" s="4">
         <v>-21.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="O3" s="6">
         <v>100</v>
       </c>
-      <c r="P3" s="10">
-        <v>23</v>
-      </c>
-      <c r="Q3" s="11">
-        <v>47</v>
-      </c>
-      <c r="R3" s="12">
+      <c r="P3" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="9">
+        <v>91</v>
+      </c>
+      <c r="R3" s="10">
         <v>100</v>
       </c>
     </row>
@@ -1128,52 +1215,52 @@
         <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="L4" s="4">
-        <v>-15.1</v>
+        <v>-15</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="O4" s="6">
-        <v>56</v>
-      </c>
-      <c r="P4" s="13">
-        <v>55</v>
-      </c>
-      <c r="Q4" s="14">
-        <v>16</v>
-      </c>
-      <c r="R4" s="7">
-        <v>2</v>
+        <v>75</v>
+      </c>
+      <c r="P4" s="11">
+        <v>64</v>
+      </c>
+      <c r="Q4" s="12">
+        <v>26</v>
+      </c>
+      <c r="R4" s="13">
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1184,52 +1271,52 @@
         <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="L5" s="4">
         <v>-23.1</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="O5" s="6">
-        <v>96</v>
-      </c>
-      <c r="P5" s="8">
-        <v>12</v>
-      </c>
-      <c r="Q5" s="15">
-        <v>60</v>
-      </c>
-      <c r="R5" s="16">
-        <v>91</v>
+        <v>85</v>
+      </c>
+      <c r="P5" s="13">
+        <v>6</v>
+      </c>
+      <c r="Q5" s="14">
+        <v>31</v>
+      </c>
+      <c r="R5" s="15">
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1240,52 +1327,52 @@
         <v>30</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="L6" s="4">
         <v>-8.4</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="O6" s="6">
-        <v>99</v>
-      </c>
-      <c r="P6" s="17">
-        <v>35</v>
-      </c>
-      <c r="Q6" s="13">
-        <v>55</v>
-      </c>
-      <c r="R6" s="12">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="P6" s="16">
+        <v>20</v>
+      </c>
+      <c r="Q6" s="16">
+        <v>21</v>
+      </c>
+      <c r="R6" s="10">
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1296,52 +1383,52 @@
         <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="L7" s="4">
         <v>-30.5</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="O7" s="18">
-        <v>45</v>
+        <v>116</v>
+      </c>
+      <c r="O7" s="6">
+        <v>74</v>
       </c>
       <c r="P7" s="17">
-        <v>36</v>
-      </c>
-      <c r="Q7" s="19">
-        <v>41</v>
-      </c>
-      <c r="R7" s="20">
-        <v>29</v>
+        <v>17</v>
+      </c>
+      <c r="Q7" s="17">
+        <v>15</v>
+      </c>
+      <c r="R7" s="18">
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1352,111 +1439,279 @@
         <v>28</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="L8" s="4">
+        <v>-16.7</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="O8" s="6">
+        <v>52</v>
+      </c>
+      <c r="P8" s="12">
+        <v>23</v>
+      </c>
+      <c r="Q8" s="13">
+        <v>6</v>
+      </c>
+      <c r="R8" s="19">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="2">
+        <v>10</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L9" s="4">
+        <v>-37.1</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="O9" s="6">
+        <v>80</v>
+      </c>
+      <c r="P9" s="13">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="17">
+        <v>14</v>
+      </c>
+      <c r="R9" s="15">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="2">
+        <v>25</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="D10" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H8" s="3" t="s">
+      <c r="E10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="L10" s="4">
+        <v>-24.8</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="O10" s="6">
         <v>64</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="L8" s="4">
-        <v>-16.8</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="O8" s="6">
+      <c r="P10" s="13">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="20">
+        <v>10</v>
+      </c>
+      <c r="R10" s="21">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="2">
+        <v>29</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="P8" s="10">
-        <v>24</v>
-      </c>
-      <c r="Q8" s="14">
-        <v>14</v>
-      </c>
-      <c r="R8" s="21">
-        <v>67</v>
+      <c r="I11" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="L11" s="4">
+        <v>-10.1</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="O11" s="22">
+        <v>34</v>
+      </c>
+      <c r="P11" s="13">
+        <v>3</v>
+      </c>
+      <c r="Q11" s="13">
+        <v>3</v>
+      </c>
+      <c r="R11" s="16">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A8">
+  <conditionalFormatting sqref="A2:A11">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B8">
+  <conditionalFormatting sqref="B2:B11">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C8">
+  <conditionalFormatting sqref="C2:C11">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D8">
+  <conditionalFormatting sqref="D2:D11">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E8">
+  <conditionalFormatting sqref="E2:E11">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F8">
+  <conditionalFormatting sqref="F2:F11">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G8">
+  <conditionalFormatting sqref="G2:G11">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H8">
+  <conditionalFormatting sqref="H2:H11">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I8">
+  <conditionalFormatting sqref="I2:I11">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J8">
+  <conditionalFormatting sqref="J2:J11">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K8">
+  <conditionalFormatting sqref="K2:K11">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L8">
+  <conditionalFormatting sqref="L2:L11">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1475,12 +1730,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M8">
+  <conditionalFormatting sqref="M2:M11">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N8">
+  <conditionalFormatting sqref="N2:N11">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1497,22 +1752,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O8">
+  <conditionalFormatting sqref="O2:O11">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P8">
+  <conditionalFormatting sqref="P2:P11">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q8">
+  <conditionalFormatting sqref="Q2:Q11">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R8">
+  <conditionalFormatting sqref="R2:R11">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="136">
   <si>
     <t>Datum</t>
   </si>
@@ -100,40 +100,52 @@
     <t>20261006--03</t>
   </si>
   <si>
+    <t>20261007--01</t>
+  </si>
+  <si>
+    <t>20261007--02</t>
+  </si>
+  <si>
     <t>04:00</t>
   </si>
   <si>
-    <t>02:08</t>
+    <t>02:09</t>
   </si>
   <si>
     <t>05:18</t>
   </si>
   <si>
-    <t>04:41</t>
+    <t>04:40</t>
+  </si>
+  <si>
+    <t>05:56</t>
+  </si>
+  <si>
+    <t>03:36</t>
+  </si>
+  <si>
+    <t>05:48</t>
+  </si>
+  <si>
+    <t>00:19</t>
+  </si>
+  <si>
+    <t>05:33</t>
+  </si>
+  <si>
+    <t>05:53</t>
+  </si>
+  <si>
+    <t>05:06</t>
   </si>
   <si>
     <t>05:55</t>
   </si>
   <si>
-    <t>03:34</t>
-  </si>
-  <si>
-    <t>05:48</t>
-  </si>
-  <si>
-    <t>00:16</t>
-  </si>
-  <si>
-    <t>05:33</t>
-  </si>
-  <si>
-    <t>05:53</t>
-  </si>
-  <si>
     <t>01:09</t>
   </si>
   <si>
-    <t>04:04</t>
+    <t>04:05</t>
   </si>
   <si>
     <t>01:30</t>
@@ -142,160 +154,190 @@
     <t>00:00</t>
   </si>
   <si>
-    <t>03:36</t>
-  </si>
-  <si>
     <t>01:11</t>
   </si>
   <si>
-    <t>05:16</t>
-  </si>
-  <si>
-    <t>03:40:34</t>
-  </si>
-  <si>
-    <t>02:49:02</t>
-  </si>
-  <si>
-    <t>03:32:47</t>
+    <t>05:17</t>
+  </si>
+  <si>
+    <t>02:59</t>
+  </si>
+  <si>
+    <t>03:40:35</t>
+  </si>
+  <si>
+    <t>02:49:04</t>
+  </si>
+  <si>
+    <t>03:32:51</t>
+  </si>
+  <si>
+    <t>02:41:01</t>
+  </si>
+  <si>
+    <t>04:17:11</t>
+  </si>
+  <si>
+    <t>01:49:14</t>
+  </si>
+  <si>
+    <t>03:25:08</t>
+  </si>
+  <si>
+    <t>00:57:34</t>
+  </si>
+  <si>
+    <t>02:33:04</t>
+  </si>
+  <si>
+    <t>04:09:33</t>
+  </si>
+  <si>
+    <t>01:41:02</t>
+  </si>
+  <si>
+    <t>03:17:21</t>
+  </si>
+  <si>
+    <t>03:43:17</t>
+  </si>
+  <si>
+    <t>02:52:23</t>
+  </si>
+  <si>
+    <t>03:35:13</t>
+  </si>
+  <si>
+    <t>02:43:32</t>
+  </si>
+  <si>
+    <t>04:19:25</t>
+  </si>
+  <si>
+    <t>01:52:03</t>
+  </si>
+  <si>
+    <t>03:27:23</t>
+  </si>
+  <si>
+    <t>01:01:49</t>
+  </si>
+  <si>
+    <t>02:35:22</t>
+  </si>
+  <si>
+    <t>04:11:48</t>
+  </si>
+  <si>
+    <t>01:43:26</t>
+  </si>
+  <si>
+    <t>03:19:34</t>
+  </si>
+  <si>
+    <t>03:45:17</t>
+  </si>
+  <si>
+    <t>02:53:27</t>
+  </si>
+  <si>
+    <t>03:37:51</t>
+  </si>
+  <si>
+    <t>02:45:52</t>
+  </si>
+  <si>
+    <t>04:22:23</t>
+  </si>
+  <si>
+    <t>01:53:51</t>
+  </si>
+  <si>
+    <t>03:30:16</t>
+  </si>
+  <si>
+    <t>02:38:08</t>
+  </si>
+  <si>
+    <t>04:14:44</t>
+  </si>
+  <si>
+    <t>01:45:58</t>
+  </si>
+  <si>
+    <t>03:22:31</t>
+  </si>
+  <si>
+    <t>03:47:17</t>
+  </si>
+  <si>
+    <t>02:54:32</t>
+  </si>
+  <si>
+    <t>03:40:31</t>
+  </si>
+  <si>
+    <t>02:48:12</t>
+  </si>
+  <si>
+    <t>04:25:21</t>
+  </si>
+  <si>
+    <t>01:55:39</t>
+  </si>
+  <si>
+    <t>03:33:11</t>
+  </si>
+  <si>
+    <t>01:02:08</t>
   </si>
   <si>
     <t>02:40:55</t>
   </si>
   <si>
-    <t>04:17:06</t>
-  </si>
-  <si>
-    <t>01:49:07</t>
-  </si>
-  <si>
-    <t>03:25:00</t>
-  </si>
-  <si>
-    <t>00:57:23</t>
-  </si>
-  <si>
-    <t>02:32:53</t>
-  </si>
-  <si>
-    <t>04:09:22</t>
-  </si>
-  <si>
-    <t>03:43:17</t>
-  </si>
-  <si>
-    <t>02:52:22</t>
-  </si>
-  <si>
-    <t>03:35:09</t>
-  </si>
-  <si>
-    <t>02:43:26</t>
-  </si>
-  <si>
-    <t>04:19:20</t>
-  </si>
-  <si>
-    <t>01:51:56</t>
-  </si>
-  <si>
-    <t>03:27:15</t>
-  </si>
-  <si>
-    <t>01:01:38</t>
-  </si>
-  <si>
-    <t>02:35:11</t>
-  </si>
-  <si>
-    <t>04:11:36</t>
-  </si>
-  <si>
-    <t>03:45:16</t>
-  </si>
-  <si>
-    <t>02:53:25</t>
-  </si>
-  <si>
-    <t>03:37:48</t>
-  </si>
-  <si>
-    <t>02:45:46</t>
-  </si>
-  <si>
-    <t>04:22:17</t>
-  </si>
-  <si>
-    <t>01:53:43</t>
-  </si>
-  <si>
-    <t>03:30:08</t>
-  </si>
-  <si>
-    <t>02:37:57</t>
-  </si>
-  <si>
-    <t>04:14:32</t>
-  </si>
-  <si>
-    <t>03:47:17</t>
-  </si>
-  <si>
-    <t>02:54:30</t>
-  </si>
-  <si>
-    <t>03:40:27</t>
-  </si>
-  <si>
-    <t>02:48:07</t>
-  </si>
-  <si>
-    <t>04:25:15</t>
-  </si>
-  <si>
-    <t>01:55:30</t>
-  </si>
-  <si>
-    <t>03:33:03</t>
-  </si>
-  <si>
-    <t>01:01:54</t>
-  </si>
-  <si>
-    <t>02:40:44</t>
-  </si>
-  <si>
-    <t>04:17:29</t>
+    <t>04:17:41</t>
+  </si>
+  <si>
+    <t>01:48:32</t>
+  </si>
+  <si>
+    <t>03:25:29</t>
   </si>
   <si>
     <t>03:50:01</t>
   </si>
   <si>
-    <t>02:57:51</t>
-  </si>
-  <si>
-    <t>03:42:50</t>
-  </si>
-  <si>
-    <t>02:50:39</t>
-  </si>
-  <si>
-    <t>04:27:30</t>
-  </si>
-  <si>
-    <t>01:58:21</t>
-  </si>
-  <si>
-    <t>03:35:19</t>
-  </si>
-  <si>
-    <t>01:05:55</t>
-  </si>
-  <si>
-    <t>02:43:03</t>
-  </si>
-  <si>
-    <t>04:19:44</t>
+    <t>02:57:52</t>
+  </si>
+  <si>
+    <t>03:42:54</t>
+  </si>
+  <si>
+    <t>02:50:44</t>
+  </si>
+  <si>
+    <t>04:27:35</t>
+  </si>
+  <si>
+    <t>01:58:29</t>
+  </si>
+  <si>
+    <t>03:35:27</t>
+  </si>
+  <si>
+    <t>01:06:06</t>
+  </si>
+  <si>
+    <t>02:43:15</t>
+  </si>
+  <si>
+    <t>04:19:55</t>
+  </si>
+  <si>
+    <t>01:50:57</t>
+  </si>
+  <si>
+    <t>03:27:44</t>
   </si>
   <si>
     <t>9°</t>
@@ -307,9 +349,6 @@
     <t>17°</t>
   </si>
   <si>
-    <t>16°</t>
-  </si>
-  <si>
     <t>10°</t>
   </si>
   <si>
@@ -325,31 +364,43 @@
     <t>14°</t>
   </si>
   <si>
-    <t>03:42:54</t>
-  </si>
-  <si>
-    <t>02:53:21</t>
-  </si>
-  <si>
-    <t>03:36:23</t>
-  </si>
-  <si>
-    <t>02:46:37</t>
-  </si>
-  <si>
-    <t>04:19:18</t>
-  </si>
-  <si>
-    <t>01:56:47</t>
-  </si>
-  <si>
-    <t>03:29:27</t>
-  </si>
-  <si>
-    <t>02:39:33</t>
-  </si>
-  <si>
-    <t>04:12:13</t>
+    <t>4°</t>
+  </si>
+  <si>
+    <t>30°</t>
+  </si>
+  <si>
+    <t>03:42:55</t>
+  </si>
+  <si>
+    <t>02:53:23</t>
+  </si>
+  <si>
+    <t>03:36:26</t>
+  </si>
+  <si>
+    <t>02:46:42</t>
+  </si>
+  <si>
+    <t>04:19:23</t>
+  </si>
+  <si>
+    <t>01:56:55</t>
+  </si>
+  <si>
+    <t>03:29:35</t>
+  </si>
+  <si>
+    <t>02:39:44</t>
+  </si>
+  <si>
+    <t>04:12:24</t>
+  </si>
+  <si>
+    <t>01:49:50</t>
+  </si>
+  <si>
+    <t>03:22:30</t>
   </si>
   <si>
     <t>A</t>
@@ -368,6 +419,9 @@
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
 </sst>
 </file>
@@ -401,7 +455,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -416,7 +470,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,13 +482,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,7 +500,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,61 +542,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -553,7 +589,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -610,15 +646,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1022,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1103,43 +1130,43 @@
         <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="L2" s="4">
         <v>-13.4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="O2" s="6">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
@@ -1148,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="R2" s="8">
-        <v>61</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1159,49 +1186,49 @@
         <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="L3" s="4">
         <v>-21.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="O3" s="6">
+        <v>133</v>
+      </c>
+      <c r="O3" s="9">
         <v>100</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
       </c>
-      <c r="Q3" s="9">
-        <v>91</v>
+      <c r="Q3" s="8">
+        <v>45</v>
       </c>
       <c r="R3" s="10">
         <v>100</v>
@@ -1215,52 +1242,52 @@
         <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="L4" s="4">
         <v>-15</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="O4" s="6">
-        <v>75</v>
+        <v>132</v>
+      </c>
+      <c r="O4" s="9">
+        <v>60</v>
       </c>
       <c r="P4" s="11">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="Q4" s="12">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="R4" s="13">
-        <v>6</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1271,52 +1298,52 @@
         <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="L5" s="4">
         <v>-23.1</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="O5" s="6">
-        <v>85</v>
-      </c>
-      <c r="P5" s="13">
+        <v>132</v>
+      </c>
+      <c r="O5" s="14">
         <v>6</v>
       </c>
-      <c r="Q5" s="14">
-        <v>31</v>
-      </c>
-      <c r="R5" s="15">
-        <v>57</v>
+      <c r="P5" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>0</v>
+      </c>
+      <c r="R5" s="11">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1327,52 +1354,52 @@
         <v>30</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="L6" s="4">
-        <v>-8.4</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="O6" s="6">
-        <v>100</v>
-      </c>
-      <c r="P6" s="16">
-        <v>20</v>
-      </c>
-      <c r="Q6" s="16">
-        <v>21</v>
-      </c>
-      <c r="R6" s="10">
-        <v>100</v>
+        <v>134</v>
+      </c>
+      <c r="O6" s="9">
+        <v>57</v>
+      </c>
+      <c r="P6" s="11">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="15">
+        <v>36</v>
+      </c>
+      <c r="R6" s="16">
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1383,52 +1410,52 @@
         <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="L7" s="4">
         <v>-30.5</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="O7" s="6">
-        <v>74</v>
+        <v>133</v>
+      </c>
+      <c r="O7" s="9">
+        <v>89</v>
       </c>
       <c r="P7" s="17">
-        <v>17</v>
-      </c>
-      <c r="Q7" s="17">
-        <v>15</v>
-      </c>
-      <c r="R7" s="18">
-        <v>72</v>
+        <v>27</v>
+      </c>
+      <c r="Q7" s="15">
+        <v>37</v>
+      </c>
+      <c r="R7" s="17">
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1439,52 +1466,52 @@
         <v>28</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="L8" s="4">
         <v>-16.7</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="O8" s="6">
-        <v>52</v>
-      </c>
-      <c r="P8" s="12">
-        <v>23</v>
-      </c>
-      <c r="Q8" s="13">
-        <v>6</v>
-      </c>
-      <c r="R8" s="19">
-        <v>52</v>
+        <v>132</v>
+      </c>
+      <c r="O8" s="9">
+        <v>78</v>
+      </c>
+      <c r="P8" s="15">
+        <v>36</v>
+      </c>
+      <c r="Q8" s="17">
+        <v>24</v>
+      </c>
+      <c r="R8" s="11">
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1495,52 +1522,52 @@
         <v>10</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="L9" s="4">
         <v>-37.1</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="O9" s="6">
-        <v>80</v>
-      </c>
-      <c r="P9" s="13">
-        <v>5</v>
-      </c>
-      <c r="Q9" s="17">
-        <v>14</v>
+        <v>133</v>
+      </c>
+      <c r="O9" s="9">
+        <v>59</v>
+      </c>
+      <c r="P9" s="12">
+        <v>13</v>
+      </c>
+      <c r="Q9" s="18">
+        <v>20</v>
       </c>
       <c r="R9" s="15">
-        <v>53</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1551,52 +1578,52 @@
         <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="L10" s="4">
-        <v>-24.8</v>
+        <v>-24.7</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="O10" s="6">
-        <v>64</v>
-      </c>
-      <c r="P10" s="13">
-        <v>4</v>
-      </c>
-      <c r="Q10" s="20">
-        <v>10</v>
-      </c>
-      <c r="R10" s="21">
-        <v>38</v>
+        <v>132</v>
+      </c>
+      <c r="O10" s="9">
+        <v>62</v>
+      </c>
+      <c r="P10" s="12">
+        <v>14</v>
+      </c>
+      <c r="Q10" s="19">
+        <v>28</v>
+      </c>
+      <c r="R10" s="19">
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1607,111 +1634,223 @@
         <v>29</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="L11" s="4">
+        <v>-10</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="O11" s="9">
+        <v>58</v>
+      </c>
+      <c r="P11" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q11" s="13">
+        <v>42</v>
+      </c>
+      <c r="R11" s="15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="2">
+        <v>21</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="L12" s="4">
+        <v>-32.1</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="O12" s="9">
+        <v>78</v>
+      </c>
+      <c r="P12" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>45</v>
+      </c>
+      <c r="R12" s="8">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="A13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="2">
+        <v>30</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="I11" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="L11" s="4">
-        <v>-10.1</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="O11" s="22">
-        <v>34</v>
-      </c>
-      <c r="P11" s="13">
-        <v>3</v>
-      </c>
-      <c r="Q11" s="13">
-        <v>3</v>
-      </c>
-      <c r="R11" s="16">
-        <v>19</v>
+      <c r="H13" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="L13" s="4">
+        <v>-18.4</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="O13" s="9">
+        <v>81</v>
+      </c>
+      <c r="P13" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="13">
+        <v>39</v>
+      </c>
+      <c r="R13" s="17">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A11">
+  <conditionalFormatting sqref="A2:A13">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B11">
+  <conditionalFormatting sqref="B2:B13">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C11">
+  <conditionalFormatting sqref="C2:C13">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D11">
+  <conditionalFormatting sqref="D2:D13">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E11">
+  <conditionalFormatting sqref="E2:E13">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F11">
+  <conditionalFormatting sqref="F2:F13">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G11">
+  <conditionalFormatting sqref="G2:G13">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H11">
+  <conditionalFormatting sqref="H2:H13">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I11">
+  <conditionalFormatting sqref="I2:I13">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J11">
+  <conditionalFormatting sqref="J2:J13">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K11">
+  <conditionalFormatting sqref="K2:K13">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L11">
+  <conditionalFormatting sqref="L2:L13">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1730,12 +1869,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M11">
+  <conditionalFormatting sqref="M2:M13">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N11">
+  <conditionalFormatting sqref="N2:N13">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1752,22 +1891,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O11">
+  <conditionalFormatting sqref="O2:O13">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P11">
+  <conditionalFormatting sqref="P2:P13">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q11">
+  <conditionalFormatting sqref="Q2:Q13">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R11">
+  <conditionalFormatting sqref="R2:R13">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="153">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261001--01</t>
-  </si>
-  <si>
     <t>20261002--01</t>
   </si>
   <si>
@@ -106,7 +103,13 @@
     <t>20261007--02</t>
   </si>
   <si>
-    <t>04:00</t>
+    <t>20261008--01</t>
+  </si>
+  <si>
+    <t>20261008--02</t>
+  </si>
+  <si>
+    <t>20261008--03</t>
   </si>
   <si>
     <t>02:09</t>
@@ -115,19 +118,19 @@
     <t>05:18</t>
   </si>
   <si>
-    <t>04:40</t>
+    <t>04:41</t>
   </si>
   <si>
     <t>05:56</t>
   </si>
   <si>
-    <t>03:36</t>
-  </si>
-  <si>
-    <t>05:48</t>
-  </si>
-  <si>
-    <t>00:19</t>
+    <t>03:35</t>
+  </si>
+  <si>
+    <t>05:49</t>
+  </si>
+  <si>
+    <t>00:20</t>
   </si>
   <si>
     <t>05:33</t>
@@ -136,12 +139,21 @@
     <t>05:53</t>
   </si>
   <si>
-    <t>05:06</t>
+    <t>05:07</t>
   </si>
   <si>
     <t>05:55</t>
   </si>
   <si>
+    <t>04:23</t>
+  </si>
+  <si>
+    <t>05:52</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
     <t>01:09</t>
   </si>
   <si>
@@ -154,7 +166,10 @@
     <t>00:00</t>
   </si>
   <si>
-    <t>01:11</t>
+    <t>03:37</t>
+  </si>
+  <si>
+    <t>01:12</t>
   </si>
   <si>
     <t>05:17</t>
@@ -163,7 +178,10 @@
     <t>02:59</t>
   </si>
   <si>
-    <t>03:40:35</t>
+    <t>00:38</t>
+  </si>
+  <si>
+    <t>04:22</t>
   </si>
   <si>
     <t>02:49:04</t>
@@ -175,31 +193,37 @@
     <t>02:41:01</t>
   </si>
   <si>
-    <t>04:17:11</t>
-  </si>
-  <si>
-    <t>01:49:14</t>
-  </si>
-  <si>
-    <t>03:25:08</t>
-  </si>
-  <si>
-    <t>00:57:34</t>
-  </si>
-  <si>
-    <t>02:33:04</t>
-  </si>
-  <si>
-    <t>04:09:33</t>
-  </si>
-  <si>
-    <t>01:41:02</t>
-  </si>
-  <si>
-    <t>03:17:21</t>
-  </si>
-  <si>
-    <t>03:43:17</t>
+    <t>04:17:12</t>
+  </si>
+  <si>
+    <t>01:49:16</t>
+  </si>
+  <si>
+    <t>03:25:09</t>
+  </si>
+  <si>
+    <t>00:57:36</t>
+  </si>
+  <si>
+    <t>02:33:06</t>
+  </si>
+  <si>
+    <t>04:09:35</t>
+  </si>
+  <si>
+    <t>01:41:04</t>
+  </si>
+  <si>
+    <t>03:17:23</t>
+  </si>
+  <si>
+    <t>00:49:05</t>
+  </si>
+  <si>
+    <t>02:25:10</t>
+  </si>
+  <si>
+    <t>04:01:50</t>
   </si>
   <si>
     <t>02:52:23</t>
@@ -211,31 +235,37 @@
     <t>02:43:32</t>
   </si>
   <si>
-    <t>04:19:25</t>
-  </si>
-  <si>
-    <t>01:52:03</t>
-  </si>
-  <si>
-    <t>03:27:23</t>
-  </si>
-  <si>
-    <t>01:01:49</t>
-  </si>
-  <si>
-    <t>02:35:22</t>
-  </si>
-  <si>
-    <t>04:11:48</t>
-  </si>
-  <si>
-    <t>01:43:26</t>
-  </si>
-  <si>
-    <t>03:19:34</t>
-  </si>
-  <si>
-    <t>03:45:17</t>
+    <t>04:19:26</t>
+  </si>
+  <si>
+    <t>01:52:05</t>
+  </si>
+  <si>
+    <t>03:27:24</t>
+  </si>
+  <si>
+    <t>01:01:51</t>
+  </si>
+  <si>
+    <t>02:35:24</t>
+  </si>
+  <si>
+    <t>04:11:50</t>
+  </si>
+  <si>
+    <t>01:43:28</t>
+  </si>
+  <si>
+    <t>03:19:37</t>
+  </si>
+  <si>
+    <t>00:51:40</t>
+  </si>
+  <si>
+    <t>02:27:24</t>
+  </si>
+  <si>
+    <t>04:04:10</t>
   </si>
   <si>
     <t>02:53:27</t>
@@ -250,25 +280,31 @@
     <t>04:22:23</t>
   </si>
   <si>
-    <t>01:53:51</t>
-  </si>
-  <si>
-    <t>03:30:16</t>
-  </si>
-  <si>
-    <t>02:38:08</t>
-  </si>
-  <si>
-    <t>04:14:44</t>
-  </si>
-  <si>
-    <t>01:45:58</t>
-  </si>
-  <si>
-    <t>03:22:31</t>
-  </si>
-  <si>
-    <t>03:47:17</t>
+    <t>01:53:52</t>
+  </si>
+  <si>
+    <t>03:30:18</t>
+  </si>
+  <si>
+    <t>02:38:10</t>
+  </si>
+  <si>
+    <t>04:14:46</t>
+  </si>
+  <si>
+    <t>01:46:01</t>
+  </si>
+  <si>
+    <t>03:22:34</t>
+  </si>
+  <si>
+    <t>00:53:51</t>
+  </si>
+  <si>
+    <t>02:30:20</t>
+  </si>
+  <si>
+    <t>04:06:55</t>
   </si>
   <si>
     <t>02:54:32</t>
@@ -277,70 +313,82 @@
     <t>03:40:31</t>
   </si>
   <si>
-    <t>02:48:12</t>
-  </si>
-  <si>
-    <t>04:25:21</t>
-  </si>
-  <si>
-    <t>01:55:39</t>
-  </si>
-  <si>
-    <t>03:33:11</t>
-  </si>
-  <si>
-    <t>01:02:08</t>
-  </si>
-  <si>
-    <t>02:40:55</t>
-  </si>
-  <si>
-    <t>04:17:41</t>
-  </si>
-  <si>
-    <t>01:48:32</t>
-  </si>
-  <si>
-    <t>03:25:29</t>
-  </si>
-  <si>
-    <t>03:50:01</t>
-  </si>
-  <si>
-    <t>02:57:52</t>
+    <t>02:48:13</t>
+  </si>
+  <si>
+    <t>04:25:22</t>
+  </si>
+  <si>
+    <t>01:55:40</t>
+  </si>
+  <si>
+    <t>03:33:13</t>
+  </si>
+  <si>
+    <t>01:02:11</t>
+  </si>
+  <si>
+    <t>02:40:57</t>
+  </si>
+  <si>
+    <t>04:17:43</t>
+  </si>
+  <si>
+    <t>01:48:35</t>
+  </si>
+  <si>
+    <t>03:25:32</t>
+  </si>
+  <si>
+    <t>00:56:03</t>
+  </si>
+  <si>
+    <t>02:33:16</t>
+  </si>
+  <si>
+    <t>04:09:40</t>
+  </si>
+  <si>
+    <t>02:57:53</t>
   </si>
   <si>
     <t>03:42:54</t>
   </si>
   <si>
-    <t>02:50:44</t>
-  </si>
-  <si>
-    <t>04:27:35</t>
-  </si>
-  <si>
-    <t>01:58:29</t>
-  </si>
-  <si>
-    <t>03:35:27</t>
-  </si>
-  <si>
-    <t>01:06:06</t>
-  </si>
-  <si>
-    <t>02:43:15</t>
-  </si>
-  <si>
-    <t>04:19:55</t>
-  </si>
-  <si>
-    <t>01:50:57</t>
-  </si>
-  <si>
-    <t>03:27:44</t>
-  </si>
-  <si>
-    <t>9°</t>
+    <t>02:50:45</t>
+  </si>
+  <si>
+    <t>04:27:36</t>
+  </si>
+  <si>
+    <t>01:58:31</t>
+  </si>
+  <si>
+    <t>03:35:29</t>
+  </si>
+  <si>
+    <t>01:06:08</t>
+  </si>
+  <si>
+    <t>02:43:17</t>
+  </si>
+  <si>
+    <t>04:19:58</t>
+  </si>
+  <si>
+    <t>01:51:00</t>
+  </si>
+  <si>
+    <t>03:27:47</t>
+  </si>
+  <si>
+    <t>00:58:39</t>
+  </si>
+  <si>
+    <t>02:35:31</t>
+  </si>
+  <si>
+    <t>04:12:00</t>
   </si>
   <si>
     <t>11°</t>
@@ -370,52 +418,55 @@
     <t>30°</t>
   </si>
   <si>
-    <t>03:42:55</t>
-  </si>
-  <si>
     <t>02:53:23</t>
   </si>
   <si>
     <t>03:36:26</t>
   </si>
   <si>
-    <t>02:46:42</t>
-  </si>
-  <si>
-    <t>04:19:23</t>
-  </si>
-  <si>
-    <t>01:56:55</t>
-  </si>
-  <si>
-    <t>03:29:35</t>
-  </si>
-  <si>
-    <t>02:39:44</t>
-  </si>
-  <si>
-    <t>04:12:24</t>
-  </si>
-  <si>
-    <t>01:49:50</t>
-  </si>
-  <si>
-    <t>03:22:30</t>
+    <t>02:46:43</t>
+  </si>
+  <si>
+    <t>04:19:24</t>
+  </si>
+  <si>
+    <t>01:56:56</t>
+  </si>
+  <si>
+    <t>03:29:36</t>
+  </si>
+  <si>
+    <t>02:39:45</t>
+  </si>
+  <si>
+    <t>04:12:26</t>
+  </si>
+  <si>
+    <t>01:49:52</t>
+  </si>
+  <si>
+    <t>03:22:33</t>
+  </si>
+  <si>
+    <t>02:32:38</t>
+  </si>
+  <si>
+    <t>04:05:18</t>
+  </si>
+  <si>
+    <t>A+B</t>
   </si>
   <si>
     <t>A</t>
   </si>
   <si>
-    <t>A+B</t>
-  </si>
-  <si>
     <t>B</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
   <si>
     <t>1</t>
@@ -455,7 +506,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -470,7 +521,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,13 +539,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,25 +557,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,19 +611,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -589,7 +664,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -646,6 +721,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1049,7 +1136,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1127,55 +1214,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="L2" s="4">
-        <v>-13.4</v>
+        <v>-21.5</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="O2" s="6">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
-      <c r="Q2" s="7">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
-        <v>43</v>
+      <c r="Q2" s="8">
+        <v>47</v>
+      </c>
+      <c r="R2" s="9">
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1183,55 +1270,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="L3" s="4">
+        <v>-15</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="O3" s="6">
+        <v>46</v>
+      </c>
+      <c r="P3" s="10">
         <v>42</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="L3" s="4">
-        <v>-21.5</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O3" s="9">
-        <v>100</v>
-      </c>
-      <c r="P3" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>45</v>
-      </c>
-      <c r="R3" s="10">
-        <v>100</v>
+      <c r="Q3" s="11">
+        <v>5</v>
+      </c>
+      <c r="R3" s="11">
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1239,55 +1326,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="L4" s="4">
-        <v>-15</v>
+        <v>-23.1</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="O4" s="9">
-        <v>60</v>
-      </c>
-      <c r="P4" s="11">
-        <v>6</v>
-      </c>
-      <c r="Q4" s="12">
-        <v>17</v>
-      </c>
-      <c r="R4" s="13">
-        <v>41</v>
+        <v>150</v>
+      </c>
+      <c r="O4" s="6">
+        <v>49</v>
+      </c>
+      <c r="P4" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>0</v>
+      </c>
+      <c r="R4" s="12">
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1295,55 +1382,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="L5" s="4">
-        <v>-23.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="O5" s="14">
-        <v>6</v>
+        <v>151</v>
+      </c>
+      <c r="O5" s="6">
+        <v>54</v>
       </c>
       <c r="P5" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="7">
         <v>0</v>
       </c>
-      <c r="R5" s="11">
-        <v>4</v>
+      <c r="R5" s="13">
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1351,55 +1438,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="I6" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-30.5</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="O6" s="6">
         <v>100</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="L6" s="4">
-        <v>-8.300000000000001</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="O6" s="9">
-        <v>57</v>
-      </c>
-      <c r="P6" s="11">
-        <v>3</v>
-      </c>
-      <c r="Q6" s="15">
-        <v>36</v>
-      </c>
-      <c r="R6" s="16">
-        <v>12</v>
+      <c r="P6" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="14">
+        <v>67</v>
+      </c>
+      <c r="R6" s="9">
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1407,55 +1494,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="L7" s="4">
-        <v>-30.5</v>
+        <v>-16.7</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O7" s="9">
-        <v>89</v>
-      </c>
-      <c r="P7" s="17">
-        <v>27</v>
+        <v>150</v>
+      </c>
+      <c r="O7" s="6">
+        <v>79</v>
+      </c>
+      <c r="P7" s="11">
+        <v>3</v>
       </c>
       <c r="Q7" s="15">
-        <v>37</v>
-      </c>
-      <c r="R7" s="17">
-        <v>25</v>
+        <v>79</v>
+      </c>
+      <c r="R7" s="10">
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1463,55 +1550,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>124</v>
+        <v>62</v>
       </c>
       <c r="L8" s="4">
-        <v>-16.7</v>
+        <v>-37</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="O8" s="9">
-        <v>78</v>
-      </c>
-      <c r="P8" s="15">
-        <v>36</v>
-      </c>
-      <c r="Q8" s="17">
-        <v>24</v>
-      </c>
-      <c r="R8" s="11">
-        <v>5</v>
+        <v>149</v>
+      </c>
+      <c r="O8" s="16">
+        <v>34</v>
+      </c>
+      <c r="P8" s="17">
+        <v>27</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>0</v>
+      </c>
+      <c r="R8" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1519,55 +1606,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>56</v>
+        <v>140</v>
       </c>
       <c r="L9" s="4">
-        <v>-37.1</v>
+        <v>-24.7</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="O9" s="9">
-        <v>59</v>
-      </c>
-      <c r="P9" s="12">
-        <v>13</v>
-      </c>
-      <c r="Q9" s="18">
-        <v>20</v>
-      </c>
-      <c r="R9" s="15">
-        <v>36</v>
+        <v>150</v>
+      </c>
+      <c r="O9" s="16">
+        <v>39</v>
+      </c>
+      <c r="P9" s="18">
+        <v>29</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>0</v>
+      </c>
+      <c r="R9" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1575,55 +1662,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="L10" s="4">
-        <v>-24.7</v>
+        <v>-10</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="O10" s="9">
-        <v>62</v>
-      </c>
-      <c r="P10" s="12">
-        <v>14</v>
-      </c>
-      <c r="Q10" s="19">
-        <v>28</v>
-      </c>
-      <c r="R10" s="19">
-        <v>32</v>
+        <v>150</v>
+      </c>
+      <c r="O10" s="16">
+        <v>44</v>
+      </c>
+      <c r="P10" s="18">
+        <v>29</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>0</v>
+      </c>
+      <c r="R10" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1631,55 +1718,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="L11" s="4">
-        <v>-10</v>
+        <v>-32.1</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="O11" s="9">
-        <v>58</v>
-      </c>
-      <c r="P11" s="12">
-        <v>15</v>
-      </c>
-      <c r="Q11" s="13">
-        <v>42</v>
-      </c>
-      <c r="R11" s="15">
-        <v>33</v>
+        <v>152</v>
+      </c>
+      <c r="O11" s="16">
+        <v>31</v>
+      </c>
+      <c r="P11" s="19">
+        <v>19</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>6</v>
+      </c>
+      <c r="R11" s="11">
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1687,55 +1774,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="L12" s="4">
-        <v>-32.1</v>
+        <v>-18.4</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="O12" s="9">
-        <v>78</v>
-      </c>
-      <c r="P12" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>45</v>
-      </c>
-      <c r="R12" s="8">
-        <v>47</v>
+        <v>150</v>
+      </c>
+      <c r="O12" s="6">
+        <v>80</v>
+      </c>
+      <c r="P12" s="20">
+        <v>9</v>
+      </c>
+      <c r="Q12" s="12">
+        <v>50</v>
+      </c>
+      <c r="R12" s="21">
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1743,114 +1830,226 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
+        <v>17</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L13" s="4">
+        <v>-38.5</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="O13" s="6">
+        <v>90</v>
+      </c>
+      <c r="P13" s="17">
+        <v>23</v>
+      </c>
+      <c r="Q13" s="21">
+        <v>69</v>
+      </c>
+      <c r="R13" s="8">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="A14" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="B14" s="2">
+        <v>30</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="L14" s="4">
+        <v>-26.4</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="O14" s="6">
+        <v>84</v>
+      </c>
+      <c r="P14" s="22">
+        <v>17</v>
+      </c>
+      <c r="Q14" s="21">
         <v>72</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="R14" s="10">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="A15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="2">
+        <v>24</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="L13" s="4">
-        <v>-18.4</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="O13" s="9">
+      <c r="G15" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L15" s="4">
+        <v>-11.8</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="O15" s="6">
+        <v>90</v>
+      </c>
+      <c r="P15" s="10">
+        <v>40</v>
+      </c>
+      <c r="Q15" s="23">
+        <v>83</v>
+      </c>
+      <c r="R15" s="15">
         <v>81</v>
-      </c>
-      <c r="P13" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="13">
-        <v>39</v>
-      </c>
-      <c r="R13" s="17">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A13">
+  <conditionalFormatting sqref="A2:A15">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B13">
+  <conditionalFormatting sqref="B2:B15">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C13">
+  <conditionalFormatting sqref="C2:C15">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D13">
+  <conditionalFormatting sqref="D2:D15">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E13">
+  <conditionalFormatting sqref="E2:E15">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F13">
+  <conditionalFormatting sqref="F2:F15">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G13">
+  <conditionalFormatting sqref="G2:G15">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H13">
+  <conditionalFormatting sqref="H2:H15">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I13">
+  <conditionalFormatting sqref="I2:I15">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J13">
+  <conditionalFormatting sqref="J2:J15">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K13">
+  <conditionalFormatting sqref="K2:K15">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L13">
+  <conditionalFormatting sqref="L2:L15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1869,12 +2068,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M13">
+  <conditionalFormatting sqref="M2:M15">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N13">
+  <conditionalFormatting sqref="N2:N15">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1891,22 +2090,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O13">
+  <conditionalFormatting sqref="O2:O15">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P13">
+  <conditionalFormatting sqref="P2:P15">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q13">
+  <conditionalFormatting sqref="Q2:Q15">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R13">
+  <conditionalFormatting sqref="R2:R15">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="168">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261002--01</t>
-  </si>
-  <si>
     <t>20261003--01</t>
   </si>
   <si>
@@ -112,13 +109,19 @@
     <t>20261008--03</t>
   </si>
   <si>
-    <t>02:09</t>
+    <t>20261009--01</t>
+  </si>
+  <si>
+    <t>20261009--02</t>
+  </si>
+  <si>
+    <t>20261009--03</t>
   </si>
   <si>
     <t>05:18</t>
   </si>
   <si>
-    <t>04:41</t>
+    <t>04:40</t>
   </si>
   <si>
     <t>05:56</t>
@@ -130,7 +133,7 @@
     <t>05:49</t>
   </si>
   <si>
-    <t>00:20</t>
+    <t>00:19</t>
   </si>
   <si>
     <t>05:33</t>
@@ -142,9 +145,6 @@
     <t>05:07</t>
   </si>
   <si>
-    <t>05:55</t>
-  </si>
-  <si>
     <t>04:23</t>
   </si>
   <si>
@@ -154,10 +154,16 @@
     <t>05:30</t>
   </si>
   <si>
-    <t>01:09</t>
-  </si>
-  <si>
-    <t>04:05</t>
+    <t>03:02</t>
+  </si>
+  <si>
+    <t>05:42</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>04:04</t>
   </si>
   <si>
     <t>01:30</t>
@@ -172,10 +178,10 @@
     <t>01:12</t>
   </si>
   <si>
-    <t>05:17</t>
-  </si>
-  <si>
-    <t>02:59</t>
+    <t>05:16</t>
+  </si>
+  <si>
+    <t>03:00</t>
   </si>
   <si>
     <t>00:38</t>
@@ -184,91 +190,103 @@
     <t>04:22</t>
   </si>
   <si>
-    <t>02:49:04</t>
-  </si>
-  <si>
-    <t>03:32:51</t>
+    <t>02:08</t>
+  </si>
+  <si>
+    <t>03:32:50</t>
   </si>
   <si>
     <t>02:41:01</t>
   </si>
   <si>
-    <t>04:17:12</t>
-  </si>
-  <si>
-    <t>01:49:16</t>
-  </si>
-  <si>
-    <t>03:25:09</t>
-  </si>
-  <si>
-    <t>00:57:36</t>
-  </si>
-  <si>
-    <t>02:33:06</t>
-  </si>
-  <si>
-    <t>04:09:35</t>
-  </si>
-  <si>
-    <t>01:41:04</t>
-  </si>
-  <si>
-    <t>03:17:23</t>
-  </si>
-  <si>
-    <t>00:49:05</t>
-  </si>
-  <si>
-    <t>02:25:10</t>
-  </si>
-  <si>
-    <t>04:01:50</t>
-  </si>
-  <si>
-    <t>02:52:23</t>
-  </si>
-  <si>
-    <t>03:35:13</t>
+    <t>04:17:11</t>
+  </si>
+  <si>
+    <t>01:49:15</t>
+  </si>
+  <si>
+    <t>03:25:08</t>
+  </si>
+  <si>
+    <t>00:57:35</t>
+  </si>
+  <si>
+    <t>02:33:05</t>
+  </si>
+  <si>
+    <t>04:09:34</t>
+  </si>
+  <si>
+    <t>01:41:03</t>
+  </si>
+  <si>
+    <t>03:17:22</t>
+  </si>
+  <si>
+    <t>00:49:03</t>
+  </si>
+  <si>
+    <t>02:25:08</t>
+  </si>
+  <si>
+    <t>04:01:49</t>
+  </si>
+  <si>
+    <t>23:57:08</t>
+  </si>
+  <si>
+    <t>01:32:54</t>
+  </si>
+  <si>
+    <t>03:09:28</t>
+  </si>
+  <si>
+    <t>03:35:12</t>
   </si>
   <si>
     <t>02:43:32</t>
   </si>
   <si>
-    <t>04:19:26</t>
-  </si>
-  <si>
-    <t>01:52:05</t>
-  </si>
-  <si>
-    <t>03:27:24</t>
-  </si>
-  <si>
-    <t>01:01:51</t>
-  </si>
-  <si>
-    <t>02:35:24</t>
-  </si>
-  <si>
-    <t>04:11:50</t>
-  </si>
-  <si>
-    <t>01:43:28</t>
-  </si>
-  <si>
-    <t>03:19:37</t>
-  </si>
-  <si>
-    <t>00:51:40</t>
-  </si>
-  <si>
-    <t>02:27:24</t>
-  </si>
-  <si>
-    <t>04:04:10</t>
-  </si>
-  <si>
-    <t>02:53:27</t>
+    <t>04:19:25</t>
+  </si>
+  <si>
+    <t>01:52:04</t>
+  </si>
+  <si>
+    <t>03:27:23</t>
+  </si>
+  <si>
+    <t>01:01:50</t>
+  </si>
+  <si>
+    <t>02:35:23</t>
+  </si>
+  <si>
+    <t>04:11:48</t>
+  </si>
+  <si>
+    <t>01:43:27</t>
+  </si>
+  <si>
+    <t>03:19:35</t>
+  </si>
+  <si>
+    <t>00:51:38</t>
+  </si>
+  <si>
+    <t>02:27:22</t>
+  </si>
+  <si>
+    <t>04:04:08</t>
+  </si>
+  <si>
+    <t>00:00:07</t>
+  </si>
+  <si>
+    <t>01:35:10</t>
+  </si>
+  <si>
+    <t>03:11:44</t>
   </si>
   <si>
     <t>03:37:51</t>
@@ -280,76 +298,88 @@
     <t>04:22:23</t>
   </si>
   <si>
-    <t>01:53:52</t>
-  </si>
-  <si>
-    <t>03:30:18</t>
-  </si>
-  <si>
-    <t>02:38:10</t>
-  </si>
-  <si>
-    <t>04:14:46</t>
-  </si>
-  <si>
-    <t>01:46:01</t>
-  </si>
-  <si>
-    <t>03:22:34</t>
-  </si>
-  <si>
-    <t>00:53:51</t>
-  </si>
-  <si>
-    <t>02:30:20</t>
-  </si>
-  <si>
-    <t>04:06:55</t>
-  </si>
-  <si>
-    <t>02:54:32</t>
-  </si>
-  <si>
-    <t>03:40:31</t>
-  </si>
-  <si>
-    <t>02:48:13</t>
-  </si>
-  <si>
-    <t>04:25:22</t>
-  </si>
-  <si>
-    <t>01:55:40</t>
-  </si>
-  <si>
-    <t>03:33:13</t>
-  </si>
-  <si>
-    <t>01:02:11</t>
-  </si>
-  <si>
-    <t>02:40:57</t>
-  </si>
-  <si>
-    <t>04:17:43</t>
-  </si>
-  <si>
-    <t>01:48:35</t>
-  </si>
-  <si>
-    <t>03:25:32</t>
-  </si>
-  <si>
-    <t>00:56:03</t>
-  </si>
-  <si>
-    <t>02:33:16</t>
-  </si>
-  <si>
-    <t>04:09:40</t>
-  </si>
-  <si>
-    <t>02:57:53</t>
+    <t>01:53:51</t>
+  </si>
+  <si>
+    <t>03:30:17</t>
+  </si>
+  <si>
+    <t>02:38:09</t>
+  </si>
+  <si>
+    <t>04:14:45</t>
+  </si>
+  <si>
+    <t>01:46:00</t>
+  </si>
+  <si>
+    <t>03:22:33</t>
+  </si>
+  <si>
+    <t>00:53:49</t>
+  </si>
+  <si>
+    <t>02:30:18</t>
+  </si>
+  <si>
+    <t>04:06:53</t>
+  </si>
+  <si>
+    <t>00:01:38</t>
+  </si>
+  <si>
+    <t>01:38:01</t>
+  </si>
+  <si>
+    <t>03:14:36</t>
+  </si>
+  <si>
+    <t>03:40:30</t>
+  </si>
+  <si>
+    <t>02:48:12</t>
+  </si>
+  <si>
+    <t>04:25:21</t>
+  </si>
+  <si>
+    <t>01:55:39</t>
+  </si>
+  <si>
+    <t>03:33:12</t>
+  </si>
+  <si>
+    <t>01:02:09</t>
+  </si>
+  <si>
+    <t>02:40:56</t>
+  </si>
+  <si>
+    <t>04:17:41</t>
+  </si>
+  <si>
+    <t>01:48:34</t>
+  </si>
+  <si>
+    <t>03:25:31</t>
+  </si>
+  <si>
+    <t>00:56:01</t>
+  </si>
+  <si>
+    <t>02:33:14</t>
+  </si>
+  <si>
+    <t>04:09:38</t>
+  </si>
+  <si>
+    <t>00:03:09</t>
+  </si>
+  <si>
+    <t>01:40:52</t>
+  </si>
+  <si>
+    <t>03:17:29</t>
   </si>
   <si>
     <t>03:42:54</t>
@@ -361,37 +391,43 @@
     <t>04:27:36</t>
   </si>
   <si>
-    <t>01:58:31</t>
-  </si>
-  <si>
-    <t>03:35:29</t>
-  </si>
-  <si>
-    <t>01:06:08</t>
-  </si>
-  <si>
-    <t>02:43:17</t>
-  </si>
-  <si>
-    <t>04:19:58</t>
-  </si>
-  <si>
-    <t>01:51:00</t>
-  </si>
-  <si>
-    <t>03:27:47</t>
-  </si>
-  <si>
-    <t>00:58:39</t>
-  </si>
-  <si>
-    <t>02:35:31</t>
-  </si>
-  <si>
-    <t>04:12:00</t>
-  </si>
-  <si>
-    <t>11°</t>
+    <t>01:58:30</t>
+  </si>
+  <si>
+    <t>03:35:28</t>
+  </si>
+  <si>
+    <t>01:06:07</t>
+  </si>
+  <si>
+    <t>02:43:15</t>
+  </si>
+  <si>
+    <t>04:19:56</t>
+  </si>
+  <si>
+    <t>01:50:59</t>
+  </si>
+  <si>
+    <t>03:27:45</t>
+  </si>
+  <si>
+    <t>00:58:37</t>
+  </si>
+  <si>
+    <t>02:35:29</t>
+  </si>
+  <si>
+    <t>04:11:58</t>
+  </si>
+  <si>
+    <t>00:06:09</t>
+  </si>
+  <si>
+    <t>01:43:09</t>
+  </si>
+  <si>
+    <t>03:19:45</t>
   </si>
   <si>
     <t>17°</t>
@@ -418,40 +454,49 @@
     <t>30°</t>
   </si>
   <si>
-    <t>02:53:23</t>
+    <t>2°</t>
+  </si>
+  <si>
+    <t>25°</t>
   </si>
   <si>
     <t>03:36:26</t>
   </si>
   <si>
-    <t>02:46:43</t>
-  </si>
-  <si>
-    <t>04:19:24</t>
-  </si>
-  <si>
-    <t>01:56:56</t>
-  </si>
-  <si>
-    <t>03:29:36</t>
-  </si>
-  <si>
-    <t>02:39:45</t>
-  </si>
-  <si>
-    <t>04:12:26</t>
-  </si>
-  <si>
-    <t>01:49:52</t>
-  </si>
-  <si>
-    <t>03:22:33</t>
-  </si>
-  <si>
-    <t>02:32:38</t>
-  </si>
-  <si>
-    <t>04:05:18</t>
+    <t>02:46:42</t>
+  </si>
+  <si>
+    <t>04:19:23</t>
+  </si>
+  <si>
+    <t>01:56:55</t>
+  </si>
+  <si>
+    <t>03:29:35</t>
+  </si>
+  <si>
+    <t>02:39:44</t>
+  </si>
+  <si>
+    <t>04:12:25</t>
+  </si>
+  <si>
+    <t>01:49:51</t>
+  </si>
+  <si>
+    <t>03:22:31</t>
+  </si>
+  <si>
+    <t>02:32:36</t>
+  </si>
+  <si>
+    <t>04:05:16</t>
+  </si>
+  <si>
+    <t>01:42:40</t>
+  </si>
+  <si>
+    <t>03:15:21</t>
   </si>
   <si>
     <t>A+B</t>
@@ -463,13 +508,13 @@
     <t>B</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t>3</t>
@@ -506,7 +551,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -521,7 +566,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -533,7 +584,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -545,85 +650,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FFEEF3F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF6F9FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -664,7 +733,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -733,6 +802,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1136,7 +1217,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1214,55 +1295,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="L2" s="4">
-        <v>-21.5</v>
+        <v>-15</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="O2" s="6">
-        <v>91</v>
+        <v>33</v>
       </c>
       <c r="P2" s="7">
+        <v>67</v>
+      </c>
+      <c r="Q2" s="8">
         <v>0</v>
       </c>
-      <c r="Q2" s="8">
-        <v>47</v>
-      </c>
       <c r="R2" s="9">
-        <v>100</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1270,55 +1351,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="L3" s="4">
-        <v>-15</v>
+        <v>-23.1</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="O3" s="6">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="P3" s="10">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="Q3" s="11">
-        <v>5</v>
-      </c>
-      <c r="R3" s="11">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="R3" s="12">
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1326,55 +1407,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="L4" s="4">
-        <v>-23.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="O4" s="6">
+        <v>165</v>
+      </c>
+      <c r="O4" s="13">
         <v>49</v>
       </c>
-      <c r="P4" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="7">
-        <v>0</v>
-      </c>
-      <c r="R4" s="12">
-        <v>49</v>
+      <c r="P4" s="14">
+        <v>24</v>
+      </c>
+      <c r="Q4" s="15">
+        <v>14</v>
+      </c>
+      <c r="R4" s="16">
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1382,55 +1463,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="L5" s="4">
-        <v>-8.300000000000001</v>
+        <v>-30.5</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="O5" s="6">
+        <v>166</v>
+      </c>
+      <c r="O5" s="13">
+        <v>99</v>
+      </c>
+      <c r="P5" s="17">
+        <v>28</v>
+      </c>
+      <c r="Q5" s="18">
         <v>54</v>
       </c>
-      <c r="P5" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>0</v>
-      </c>
-      <c r="R5" s="13">
-        <v>54</v>
+      <c r="R5" s="7">
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1438,54 +1519,54 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="L6" s="4">
-        <v>-30.5</v>
+        <v>-16.7</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="O6" s="6">
+        <v>164</v>
+      </c>
+      <c r="O6" s="13">
         <v>100</v>
       </c>
-      <c r="P6" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="14">
-        <v>67</v>
-      </c>
-      <c r="R6" s="9">
+      <c r="P6" s="9">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="18">
+        <v>55</v>
+      </c>
+      <c r="R6" s="19">
         <v>100</v>
       </c>
     </row>
@@ -1494,55 +1575,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>139</v>
+        <v>64</v>
       </c>
       <c r="L7" s="4">
-        <v>-16.7</v>
+        <v>-37</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="O7" s="6">
-        <v>79</v>
-      </c>
-      <c r="P7" s="11">
+        <v>166</v>
+      </c>
+      <c r="O7" s="20">
+        <v>7</v>
+      </c>
+      <c r="P7" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>0</v>
+      </c>
+      <c r="R7" s="9">
         <v>3</v>
-      </c>
-      <c r="Q7" s="15">
-        <v>79</v>
-      </c>
-      <c r="R7" s="10">
-        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1550,55 +1631,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>62</v>
+        <v>153</v>
       </c>
       <c r="L8" s="4">
-        <v>-37</v>
+        <v>-24.7</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="O8" s="16">
-        <v>34</v>
-      </c>
-      <c r="P8" s="17">
-        <v>27</v>
-      </c>
-      <c r="Q8" s="7">
+        <v>164</v>
+      </c>
+      <c r="O8" s="20">
+        <v>7</v>
+      </c>
+      <c r="P8" s="8">
         <v>0</v>
       </c>
-      <c r="R8" s="7">
-        <v>1</v>
+      <c r="Q8" s="8">
+        <v>0</v>
+      </c>
+      <c r="R8" s="9">
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1606,55 +1687,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="L9" s="4">
-        <v>-24.7</v>
+        <v>-10</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="O9" s="16">
-        <v>39</v>
-      </c>
-      <c r="P9" s="18">
-        <v>29</v>
-      </c>
-      <c r="Q9" s="7">
+        <v>164</v>
+      </c>
+      <c r="O9" s="20">
+        <v>7</v>
+      </c>
+      <c r="P9" s="8">
         <v>0</v>
       </c>
-      <c r="R9" s="7">
-        <v>1</v>
+      <c r="Q9" s="8">
+        <v>0</v>
+      </c>
+      <c r="R9" s="9">
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1662,55 +1743,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="L10" s="4">
-        <v>-10</v>
+        <v>-32.1</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="O10" s="16">
-        <v>44</v>
-      </c>
-      <c r="P10" s="18">
-        <v>29</v>
-      </c>
-      <c r="Q10" s="7">
+        <v>167</v>
+      </c>
+      <c r="O10" s="20">
+        <v>2</v>
+      </c>
+      <c r="P10" s="8">
         <v>0</v>
       </c>
-      <c r="R10" s="7">
-        <v>1</v>
+      <c r="Q10" s="8">
+        <v>0</v>
+      </c>
+      <c r="R10" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1718,55 +1799,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="L11" s="4">
-        <v>-32.1</v>
+        <v>-18.4</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="O11" s="16">
-        <v>31</v>
-      </c>
-      <c r="P11" s="19">
+        <v>164</v>
+      </c>
+      <c r="O11" s="6">
+        <v>20</v>
+      </c>
+      <c r="P11" s="8">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>3</v>
+      </c>
+      <c r="R11" s="12">
         <v>19</v>
-      </c>
-      <c r="Q11" s="11">
-        <v>6</v>
-      </c>
-      <c r="R11" s="11">
-        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1774,55 +1855,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>143</v>
+        <v>69</v>
       </c>
       <c r="L12" s="4">
-        <v>-18.4</v>
+        <v>-38.5</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="O12" s="6">
-        <v>80</v>
-      </c>
-      <c r="P12" s="20">
-        <v>9</v>
-      </c>
-      <c r="Q12" s="12">
-        <v>50</v>
-      </c>
-      <c r="R12" s="21">
-        <v>68</v>
+        <v>167</v>
+      </c>
+      <c r="O12" s="13">
+        <v>96</v>
+      </c>
+      <c r="P12" s="21">
+        <v>46</v>
+      </c>
+      <c r="Q12" s="22">
+        <v>88</v>
+      </c>
+      <c r="R12" s="18">
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1830,55 +1911,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>67</v>
+        <v>157</v>
       </c>
       <c r="L13" s="4">
-        <v>-38.5</v>
+        <v>-26.4</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="O13" s="6">
-        <v>90</v>
-      </c>
-      <c r="P13" s="17">
-        <v>23</v>
-      </c>
-      <c r="Q13" s="21">
-        <v>69</v>
-      </c>
-      <c r="R13" s="8">
-        <v>47</v>
+        <v>164</v>
+      </c>
+      <c r="O13" s="13">
+        <v>96</v>
+      </c>
+      <c r="P13" s="23">
+        <v>61</v>
+      </c>
+      <c r="Q13" s="24">
+        <v>85</v>
+      </c>
+      <c r="R13" s="25">
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1886,55 +1967,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="L14" s="4">
-        <v>-26.4</v>
+        <v>-11.8</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="O14" s="6">
-        <v>84</v>
-      </c>
-      <c r="P14" s="22">
-        <v>17</v>
-      </c>
-      <c r="Q14" s="21">
-        <v>72</v>
-      </c>
-      <c r="R14" s="10">
-        <v>42</v>
+        <v>164</v>
+      </c>
+      <c r="O14" s="13">
+        <v>99</v>
+      </c>
+      <c r="P14" s="25">
+        <v>76</v>
+      </c>
+      <c r="Q14" s="22">
+        <v>89</v>
+      </c>
+      <c r="R14" s="19">
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1942,114 +2023,226 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="L15" s="4">
-        <v>-11.8</v>
+        <v>-43.2</v>
       </c>
       <c r="M15" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="O15" s="13">
+        <v>93</v>
+      </c>
+      <c r="P15" s="22">
+        <v>89</v>
+      </c>
+      <c r="Q15" s="25">
+        <v>77</v>
+      </c>
+      <c r="R15" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="A16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="2">
+        <v>27</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="N15" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="O15" s="6">
+      <c r="K16" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="L16" s="4">
+        <v>-33.7</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="O16" s="13">
+        <v>94</v>
+      </c>
+      <c r="P16" s="26">
+        <v>94</v>
+      </c>
+      <c r="Q16" s="27">
+        <v>80</v>
+      </c>
+      <c r="R16" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="2">
+        <v>28</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="P15" s="10">
-        <v>40</v>
-      </c>
-      <c r="Q15" s="23">
-        <v>83</v>
-      </c>
-      <c r="R15" s="15">
-        <v>81</v>
+      <c r="G17" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L17" s="4">
+        <v>-20.1</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="O17" s="13">
+        <v>98</v>
+      </c>
+      <c r="P17" s="19">
+        <v>98</v>
+      </c>
+      <c r="Q17" s="18">
+        <v>53</v>
+      </c>
+      <c r="R17" s="9">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A15">
+  <conditionalFormatting sqref="A2:A17">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B15">
+  <conditionalFormatting sqref="B2:B17">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C15">
+  <conditionalFormatting sqref="C2:C17">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D15">
+  <conditionalFormatting sqref="D2:D17">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E15">
+  <conditionalFormatting sqref="E2:E17">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F15">
+  <conditionalFormatting sqref="F2:F17">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G15">
+  <conditionalFormatting sqref="G2:G17">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H15">
+  <conditionalFormatting sqref="H2:H17">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I15">
+  <conditionalFormatting sqref="I2:I17">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J15">
+  <conditionalFormatting sqref="J2:J17">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K15">
+  <conditionalFormatting sqref="K2:K17">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L15">
+  <conditionalFormatting sqref="L2:L17">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2068,12 +2261,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M15">
+  <conditionalFormatting sqref="M2:M17">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N15">
+  <conditionalFormatting sqref="N2:N17">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2090,22 +2283,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O15">
+  <conditionalFormatting sqref="O2:O17">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P15">
+  <conditionalFormatting sqref="P2:P17">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q15">
+  <conditionalFormatting sqref="Q2:Q17">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R15">
+  <conditionalFormatting sqref="R2:R17">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="191">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261003--01</t>
-  </si>
-  <si>
     <t>20261004--01</t>
   </si>
   <si>
@@ -118,10 +115,19 @@
     <t>20261009--03</t>
   </si>
   <si>
-    <t>05:18</t>
-  </si>
-  <si>
-    <t>04:40</t>
+    <t>20261010--01</t>
+  </si>
+  <si>
+    <t>20261010--02</t>
+  </si>
+  <si>
+    <t>20261010--03</t>
+  </si>
+  <si>
+    <t>20261010--04</t>
+  </si>
+  <si>
+    <t>04:41</t>
   </si>
   <si>
     <t>05:56</t>
@@ -130,10 +136,10 @@
     <t>03:35</t>
   </si>
   <si>
-    <t>05:49</t>
-  </si>
-  <si>
-    <t>00:19</t>
+    <t>05:48</t>
+  </si>
+  <si>
+    <t>00:18</t>
   </si>
   <si>
     <t>05:33</t>
@@ -142,10 +148,13 @@
     <t>05:53</t>
   </si>
   <si>
-    <t>05:07</t>
-  </si>
-  <si>
-    <t>04:23</t>
+    <t>05:06</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>04:22</t>
   </si>
   <si>
     <t>05:52</t>
@@ -154,7 +163,7 @@
     <t>05:30</t>
   </si>
   <si>
-    <t>03:02</t>
+    <t>03:01</t>
   </si>
   <si>
     <t>05:42</t>
@@ -163,7 +172,13 @@
     <t>05:45</t>
   </si>
   <si>
-    <t>04:04</t>
+    <t>05:24</t>
+  </si>
+  <si>
+    <t>04:33</t>
+  </si>
+  <si>
+    <t>04:53</t>
   </si>
   <si>
     <t>01:30</t>
@@ -172,7 +187,7 @@
     <t>00:00</t>
   </si>
   <si>
-    <t>03:37</t>
+    <t>03:36</t>
   </si>
   <si>
     <t>01:12</t>
@@ -181,253 +196,301 @@
     <t>05:16</t>
   </si>
   <si>
-    <t>03:00</t>
+    <t>02:59</t>
   </si>
   <si>
     <t>00:38</t>
   </si>
   <si>
-    <t>04:22</t>
+    <t>04:21</t>
   </si>
   <si>
     <t>02:08</t>
   </si>
   <si>
-    <t>03:32:50</t>
-  </si>
-  <si>
-    <t>02:41:01</t>
-  </si>
-  <si>
-    <t>04:17:11</t>
-  </si>
-  <si>
-    <t>01:49:15</t>
-  </si>
-  <si>
-    <t>03:25:08</t>
-  </si>
-  <si>
-    <t>00:57:35</t>
-  </si>
-  <si>
-    <t>02:33:05</t>
-  </si>
-  <si>
-    <t>04:09:34</t>
-  </si>
-  <si>
-    <t>01:41:03</t>
-  </si>
-  <si>
-    <t>03:17:22</t>
-  </si>
-  <si>
-    <t>00:49:03</t>
-  </si>
-  <si>
-    <t>02:25:08</t>
-  </si>
-  <si>
-    <t>04:01:49</t>
-  </si>
-  <si>
-    <t>23:57:08</t>
-  </si>
-  <si>
-    <t>01:32:54</t>
-  </si>
-  <si>
-    <t>03:09:28</t>
-  </si>
-  <si>
-    <t>03:35:12</t>
-  </si>
-  <si>
-    <t>02:43:32</t>
-  </si>
-  <si>
-    <t>04:19:25</t>
-  </si>
-  <si>
-    <t>01:52:04</t>
-  </si>
-  <si>
-    <t>03:27:23</t>
-  </si>
-  <si>
-    <t>01:01:50</t>
-  </si>
-  <si>
-    <t>02:35:23</t>
-  </si>
-  <si>
-    <t>04:11:48</t>
-  </si>
-  <si>
-    <t>01:43:27</t>
-  </si>
-  <si>
-    <t>03:19:35</t>
-  </si>
-  <si>
-    <t>00:51:38</t>
-  </si>
-  <si>
-    <t>02:27:22</t>
-  </si>
-  <si>
-    <t>04:04:08</t>
-  </si>
-  <si>
-    <t>00:00:07</t>
-  </si>
-  <si>
-    <t>01:35:10</t>
-  </si>
-  <si>
-    <t>03:11:44</t>
-  </si>
-  <si>
-    <t>03:37:51</t>
-  </si>
-  <si>
-    <t>02:45:52</t>
-  </si>
-  <si>
-    <t>04:22:23</t>
-  </si>
-  <si>
-    <t>01:53:51</t>
-  </si>
-  <si>
-    <t>03:30:17</t>
-  </si>
-  <si>
-    <t>02:38:09</t>
-  </si>
-  <si>
-    <t>04:14:45</t>
-  </si>
-  <si>
-    <t>01:46:00</t>
-  </si>
-  <si>
-    <t>03:22:33</t>
-  </si>
-  <si>
-    <t>00:53:49</t>
-  </si>
-  <si>
-    <t>02:30:18</t>
-  </si>
-  <si>
-    <t>04:06:53</t>
-  </si>
-  <si>
-    <t>00:01:38</t>
-  </si>
-  <si>
-    <t>01:38:01</t>
-  </si>
-  <si>
-    <t>03:14:36</t>
-  </si>
-  <si>
-    <t>03:40:30</t>
+    <t>02:55</t>
+  </si>
+  <si>
+    <t>02:41:00</t>
+  </si>
+  <si>
+    <t>04:17:10</t>
+  </si>
+  <si>
+    <t>01:49:13</t>
+  </si>
+  <si>
+    <t>03:25:06</t>
+  </si>
+  <si>
+    <t>00:57:32</t>
+  </si>
+  <si>
+    <t>02:33:02</t>
+  </si>
+  <si>
+    <t>04:09:31</t>
+  </si>
+  <si>
+    <t>01:40:58</t>
+  </si>
+  <si>
+    <t>03:17:17</t>
+  </si>
+  <si>
+    <t>00:48:56</t>
+  </si>
+  <si>
+    <t>02:25:01</t>
+  </si>
+  <si>
+    <t>04:01:41</t>
+  </si>
+  <si>
+    <t>23:56:58</t>
+  </si>
+  <si>
+    <t>01:32:44</t>
+  </si>
+  <si>
+    <t>03:09:17</t>
+  </si>
+  <si>
+    <t>00:40:27</t>
+  </si>
+  <si>
+    <t>02:16:52</t>
+  </si>
+  <si>
+    <t>03:53:41</t>
+  </si>
+  <si>
+    <t>23:48:11</t>
+  </si>
+  <si>
+    <t>02:43:31</t>
+  </si>
+  <si>
+    <t>04:19:24</t>
+  </si>
+  <si>
+    <t>01:52:02</t>
+  </si>
+  <si>
+    <t>03:27:22</t>
+  </si>
+  <si>
+    <t>01:01:47</t>
+  </si>
+  <si>
+    <t>02:35:20</t>
+  </si>
+  <si>
+    <t>04:11:45</t>
+  </si>
+  <si>
+    <t>01:43:22</t>
+  </si>
+  <si>
+    <t>03:19:30</t>
+  </si>
+  <si>
+    <t>00:51:31</t>
+  </si>
+  <si>
+    <t>02:27:15</t>
+  </si>
+  <si>
+    <t>04:04:00</t>
+  </si>
+  <si>
+    <t>23:59:57</t>
+  </si>
+  <si>
+    <t>01:35:00</t>
+  </si>
+  <si>
+    <t>03:11:33</t>
+  </si>
+  <si>
+    <t>00:42:46</t>
+  </si>
+  <si>
+    <t>02:19:06</t>
+  </si>
+  <si>
+    <t>03:56:14</t>
+  </si>
+  <si>
+    <t>23:50:37</t>
+  </si>
+  <si>
+    <t>02:45:51</t>
+  </si>
+  <si>
+    <t>04:22:22</t>
+  </si>
+  <si>
+    <t>01:53:49</t>
+  </si>
+  <si>
+    <t>03:30:15</t>
+  </si>
+  <si>
+    <t>02:38:06</t>
+  </si>
+  <si>
+    <t>04:14:41</t>
+  </si>
+  <si>
+    <t>01:45:55</t>
+  </si>
+  <si>
+    <t>03:22:27</t>
+  </si>
+  <si>
+    <t>00:53:42</t>
+  </si>
+  <si>
+    <t>02:30:10</t>
+  </si>
+  <si>
+    <t>04:06:45</t>
+  </si>
+  <si>
+    <t>00:01:27</t>
+  </si>
+  <si>
+    <t>01:37:50</t>
+  </si>
+  <si>
+    <t>03:14:25</t>
+  </si>
+  <si>
+    <t>00:45:27</t>
+  </si>
+  <si>
+    <t>02:22:01</t>
+  </si>
+  <si>
+    <t>03:58:30</t>
+  </si>
+  <si>
+    <t>23:53:03</t>
   </si>
   <si>
     <t>02:48:12</t>
   </si>
   <si>
-    <t>04:25:21</t>
-  </si>
-  <si>
-    <t>01:55:39</t>
-  </si>
-  <si>
-    <t>03:33:12</t>
-  </si>
-  <si>
-    <t>01:02:09</t>
-  </si>
-  <si>
-    <t>02:40:56</t>
-  </si>
-  <si>
-    <t>04:17:41</t>
-  </si>
-  <si>
-    <t>01:48:34</t>
-  </si>
-  <si>
-    <t>03:25:31</t>
-  </si>
-  <si>
-    <t>00:56:01</t>
-  </si>
-  <si>
-    <t>02:33:14</t>
-  </si>
-  <si>
-    <t>04:09:38</t>
-  </si>
-  <si>
-    <t>00:03:09</t>
-  </si>
-  <si>
-    <t>01:40:52</t>
-  </si>
-  <si>
-    <t>03:17:29</t>
-  </si>
-  <si>
-    <t>03:42:54</t>
-  </si>
-  <si>
-    <t>02:50:45</t>
-  </si>
-  <si>
-    <t>04:27:36</t>
-  </si>
-  <si>
-    <t>01:58:30</t>
-  </si>
-  <si>
-    <t>03:35:28</t>
-  </si>
-  <si>
-    <t>01:06:07</t>
-  </si>
-  <si>
-    <t>02:43:15</t>
-  </si>
-  <si>
-    <t>04:19:56</t>
-  </si>
-  <si>
-    <t>01:50:59</t>
-  </si>
-  <si>
-    <t>03:27:45</t>
-  </si>
-  <si>
-    <t>00:58:37</t>
-  </si>
-  <si>
-    <t>02:35:29</t>
-  </si>
-  <si>
-    <t>04:11:58</t>
-  </si>
-  <si>
-    <t>00:06:09</t>
-  </si>
-  <si>
-    <t>01:43:09</t>
-  </si>
-  <si>
-    <t>03:19:45</t>
+    <t>04:25:20</t>
+  </si>
+  <si>
+    <t>01:55:37</t>
+  </si>
+  <si>
+    <t>03:33:10</t>
+  </si>
+  <si>
+    <t>01:02:05</t>
+  </si>
+  <si>
+    <t>02:40:53</t>
+  </si>
+  <si>
+    <t>04:17:38</t>
+  </si>
+  <si>
+    <t>01:48:28</t>
+  </si>
+  <si>
+    <t>03:25:25</t>
+  </si>
+  <si>
+    <t>00:55:53</t>
+  </si>
+  <si>
+    <t>02:33:07</t>
+  </si>
+  <si>
+    <t>04:09:30</t>
+  </si>
+  <si>
+    <t>00:02:58</t>
+  </si>
+  <si>
+    <t>01:40:42</t>
+  </si>
+  <si>
+    <t>03:17:18</t>
+  </si>
+  <si>
+    <t>00:48:10</t>
+  </si>
+  <si>
+    <t>02:24:58</t>
+  </si>
+  <si>
+    <t>04:00:47</t>
+  </si>
+  <si>
+    <t>23:55:30</t>
+  </si>
+  <si>
+    <t>02:50:44</t>
+  </si>
+  <si>
+    <t>04:27:35</t>
+  </si>
+  <si>
+    <t>01:58:28</t>
+  </si>
+  <si>
+    <t>03:35:26</t>
+  </si>
+  <si>
+    <t>01:06:04</t>
+  </si>
+  <si>
+    <t>02:43:12</t>
+  </si>
+  <si>
+    <t>04:19:53</t>
+  </si>
+  <si>
+    <t>01:50:54</t>
+  </si>
+  <si>
+    <t>03:27:40</t>
+  </si>
+  <si>
+    <t>00:58:29</t>
+  </si>
+  <si>
+    <t>02:35:21</t>
+  </si>
+  <si>
+    <t>04:11:50</t>
+  </si>
+  <si>
+    <t>00:05:59</t>
+  </si>
+  <si>
+    <t>01:42:58</t>
+  </si>
+  <si>
+    <t>03:19:34</t>
+  </si>
+  <si>
+    <t>00:50:30</t>
+  </si>
+  <si>
+    <t>02:27:12</t>
+  </si>
+  <si>
+    <t>04:03:20</t>
+  </si>
+  <si>
+    <t>23:57:58</t>
   </si>
   <si>
     <t>17°</t>
@@ -460,7 +523,7 @@
     <t>25°</t>
   </si>
   <si>
-    <t>03:36:26</t>
+    <t>9°</t>
   </si>
   <si>
     <t>02:46:42</t>
@@ -469,34 +532,40 @@
     <t>04:19:23</t>
   </si>
   <si>
-    <t>01:56:55</t>
-  </si>
-  <si>
-    <t>03:29:35</t>
-  </si>
-  <si>
-    <t>02:39:44</t>
-  </si>
-  <si>
-    <t>04:12:25</t>
-  </si>
-  <si>
-    <t>01:49:51</t>
-  </si>
-  <si>
-    <t>03:22:31</t>
-  </si>
-  <si>
-    <t>02:32:36</t>
-  </si>
-  <si>
-    <t>04:05:16</t>
-  </si>
-  <si>
-    <t>01:42:40</t>
-  </si>
-  <si>
-    <t>03:15:21</t>
+    <t>01:56:53</t>
+  </si>
+  <si>
+    <t>03:29:34</t>
+  </si>
+  <si>
+    <t>02:39:41</t>
+  </si>
+  <si>
+    <t>04:12:22</t>
+  </si>
+  <si>
+    <t>01:49:46</t>
+  </si>
+  <si>
+    <t>03:22:26</t>
+  </si>
+  <si>
+    <t>02:32:29</t>
+  </si>
+  <si>
+    <t>04:05:09</t>
+  </si>
+  <si>
+    <t>01:42:30</t>
+  </si>
+  <si>
+    <t>03:15:10</t>
+  </si>
+  <si>
+    <t>02:25:12</t>
+  </si>
+  <si>
+    <t>03:57:52</t>
   </si>
   <si>
     <t>A+B</t>
@@ -551,7 +620,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -566,7 +635,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,79 +713,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -662,25 +731,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -692,7 +749,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -733,7 +790,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -808,12 +865,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1217,7 +1268,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1295,55 +1346,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-23.1</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="O2" s="6">
         <v>49</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-15</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="O2" s="6">
-        <v>33</v>
-      </c>
       <c r="P2" s="7">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="Q2" s="8">
-        <v>0</v>
-      </c>
-      <c r="R2" s="9">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R2" s="8">
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1351,55 +1402,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="L3" s="4">
-        <v>-23.1</v>
+        <v>-8.4</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="O3" s="6">
-        <v>41</v>
-      </c>
-      <c r="P3" s="10">
-        <v>34</v>
-      </c>
-      <c r="Q3" s="11">
-        <v>10</v>
-      </c>
-      <c r="R3" s="12">
-        <v>19</v>
+        <v>59</v>
+      </c>
+      <c r="P3" s="9">
+        <v>55</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>8</v>
+      </c>
+      <c r="R3" s="7">
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1407,55 +1458,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="L4" s="4">
-        <v>-8.300000000000001</v>
+        <v>-30.5</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O4" s="13">
-        <v>49</v>
-      </c>
-      <c r="P4" s="14">
-        <v>24</v>
-      </c>
-      <c r="Q4" s="15">
+        <v>189</v>
+      </c>
+      <c r="O4" s="6">
+        <v>100</v>
+      </c>
+      <c r="P4" s="10">
         <v>14</v>
       </c>
-      <c r="R4" s="16">
-        <v>39</v>
+      <c r="Q4" s="10">
+        <v>17</v>
+      </c>
+      <c r="R4" s="11">
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1463,55 +1514,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="L5" s="4">
-        <v>-30.5</v>
+        <v>-16.7</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="O5" s="13">
-        <v>99</v>
-      </c>
-      <c r="P5" s="17">
-        <v>28</v>
-      </c>
-      <c r="Q5" s="18">
-        <v>54</v>
-      </c>
-      <c r="R5" s="7">
-        <v>66</v>
+        <v>187</v>
+      </c>
+      <c r="O5" s="6">
+        <v>96</v>
+      </c>
+      <c r="P5" s="10">
+        <v>15</v>
+      </c>
+      <c r="Q5" s="12">
+        <v>1</v>
+      </c>
+      <c r="R5" s="13">
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1519,55 +1570,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>152</v>
+        <v>69</v>
       </c>
       <c r="L6" s="4">
-        <v>-16.7</v>
+        <v>-37.1</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="O6" s="13">
-        <v>100</v>
-      </c>
-      <c r="P6" s="9">
-        <v>3</v>
-      </c>
-      <c r="Q6" s="18">
-        <v>55</v>
-      </c>
-      <c r="R6" s="19">
-        <v>100</v>
+        <v>189</v>
+      </c>
+      <c r="O6" s="14">
+        <v>5</v>
+      </c>
+      <c r="P6" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="12">
+        <v>0</v>
+      </c>
+      <c r="R6" s="12">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1575,55 +1626,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>64</v>
+        <v>174</v>
       </c>
       <c r="L7" s="4">
-        <v>-37</v>
+        <v>-24.7</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="O7" s="20">
+        <v>187</v>
+      </c>
+      <c r="O7" s="14">
         <v>7</v>
       </c>
-      <c r="P7" s="8">
+      <c r="P7" s="12">
         <v>0</v>
       </c>
-      <c r="Q7" s="8">
+      <c r="Q7" s="12">
         <v>0</v>
       </c>
-      <c r="R7" s="9">
-        <v>3</v>
+      <c r="R7" s="15">
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1631,55 +1682,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="L8" s="4">
-        <v>-24.7</v>
+        <v>-10.1</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="O8" s="20">
+        <v>187</v>
+      </c>
+      <c r="O8" s="14">
         <v>7</v>
       </c>
-      <c r="P8" s="8">
+      <c r="P8" s="12">
         <v>0</v>
       </c>
-      <c r="Q8" s="8">
+      <c r="Q8" s="12">
         <v>0</v>
       </c>
-      <c r="R8" s="9">
-        <v>4</v>
+      <c r="R8" s="15">
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1687,55 +1738,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="L9" s="4">
-        <v>-10</v>
+        <v>-32.1</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="O9" s="20">
-        <v>7</v>
-      </c>
-      <c r="P9" s="8">
+        <v>190</v>
+      </c>
+      <c r="O9" s="14">
         <v>0</v>
       </c>
-      <c r="Q9" s="8">
+      <c r="P9" s="12">
         <v>0</v>
       </c>
-      <c r="R9" s="9">
-        <v>6</v>
+      <c r="Q9" s="12">
+        <v>0</v>
+      </c>
+      <c r="R9" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1743,54 +1794,54 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="L10" s="4">
-        <v>-32.1</v>
+        <v>-18.4</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="O10" s="20">
-        <v>2</v>
-      </c>
-      <c r="P10" s="8">
+        <v>187</v>
+      </c>
+      <c r="O10" s="14">
         <v>0</v>
       </c>
-      <c r="Q10" s="8">
+      <c r="P10" s="12">
         <v>0</v>
       </c>
-      <c r="R10" s="8">
+      <c r="Q10" s="12">
+        <v>0</v>
+      </c>
+      <c r="R10" s="12">
         <v>0</v>
       </c>
     </row>
@@ -1799,55 +1850,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>156</v>
+        <v>74</v>
       </c>
       <c r="L11" s="4">
-        <v>-18.4</v>
+        <v>-38.5</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="O11" s="6">
-        <v>20</v>
-      </c>
-      <c r="P11" s="8">
-        <v>2</v>
-      </c>
-      <c r="Q11" s="9">
+        <v>190</v>
+      </c>
+      <c r="O11" s="14">
         <v>3</v>
       </c>
-      <c r="R11" s="12">
-        <v>19</v>
+      <c r="P11" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="12">
+        <v>0</v>
+      </c>
+      <c r="R11" s="15">
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1855,55 +1906,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>69</v>
+        <v>178</v>
       </c>
       <c r="L12" s="4">
-        <v>-38.5</v>
+        <v>-26.4</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="O12" s="13">
-        <v>96</v>
-      </c>
-      <c r="P12" s="21">
-        <v>46</v>
-      </c>
-      <c r="Q12" s="22">
-        <v>88</v>
-      </c>
-      <c r="R12" s="18">
-        <v>54</v>
+        <v>187</v>
+      </c>
+      <c r="O12" s="16">
+        <v>23</v>
+      </c>
+      <c r="P12" s="12">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="15">
+        <v>7</v>
+      </c>
+      <c r="R12" s="8">
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1911,55 +1962,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="L13" s="4">
-        <v>-26.4</v>
+        <v>-11.8</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="O13" s="13">
-        <v>96</v>
-      </c>
-      <c r="P13" s="23">
-        <v>61</v>
-      </c>
-      <c r="Q13" s="24">
-        <v>85</v>
-      </c>
-      <c r="R13" s="25">
-        <v>77</v>
+        <v>187</v>
+      </c>
+      <c r="O13" s="16">
+        <v>47</v>
+      </c>
+      <c r="P13" s="12">
+        <v>2</v>
+      </c>
+      <c r="Q13" s="17">
+        <v>20</v>
+      </c>
+      <c r="R13" s="15">
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1967,55 +2018,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="L14" s="4">
-        <v>-11.8</v>
+        <v>-43.2</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="O14" s="13">
-        <v>99</v>
-      </c>
-      <c r="P14" s="25">
+        <v>189</v>
+      </c>
+      <c r="O14" s="6">
         <v>76</v>
       </c>
-      <c r="Q14" s="22">
-        <v>89</v>
+      <c r="P14" s="18">
+        <v>67</v>
+      </c>
+      <c r="Q14" s="7">
+        <v>50</v>
       </c>
       <c r="R14" s="19">
-        <v>98</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2023,55 +2074,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="L15" s="4">
+        <v>-33.7</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="O15" s="6">
+        <v>73</v>
+      </c>
+      <c r="P15" s="20">
+        <v>73</v>
+      </c>
+      <c r="Q15" s="21">
         <v>46</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L15" s="4">
-        <v>-43.2</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="O15" s="13">
-        <v>93</v>
-      </c>
-      <c r="P15" s="22">
-        <v>89</v>
-      </c>
-      <c r="Q15" s="25">
-        <v>77</v>
-      </c>
-      <c r="R15" s="8">
-        <v>0</v>
+      <c r="R15" s="18">
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2079,55 +2130,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="L16" s="4">
-        <v>-33.7</v>
+        <v>-20.1</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="O16" s="13">
-        <v>94</v>
-      </c>
-      <c r="P16" s="26">
-        <v>94</v>
-      </c>
-      <c r="Q16" s="27">
-        <v>80</v>
-      </c>
-      <c r="R16" s="8">
-        <v>1</v>
+        <v>187</v>
+      </c>
+      <c r="O16" s="6">
+        <v>86</v>
+      </c>
+      <c r="P16" s="20">
+        <v>77</v>
+      </c>
+      <c r="Q16" s="7">
+        <v>52</v>
+      </c>
+      <c r="R16" s="21">
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2135,114 +2186,282 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="I17" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L17" s="4">
+        <v>-40</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="O17" s="6">
+        <v>89</v>
+      </c>
+      <c r="P17" s="22">
+        <v>59</v>
+      </c>
+      <c r="Q17" s="20">
+        <v>75</v>
+      </c>
+      <c r="R17" s="20">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
+      <c r="A18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="2">
+        <v>30</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="L17" s="4">
-        <v>-20.1</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="O17" s="13">
+      <c r="I18" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="L18" s="4">
+        <v>-28.1</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="O18" s="6">
         <v>98</v>
       </c>
-      <c r="P17" s="19">
-        <v>98</v>
-      </c>
-      <c r="Q17" s="18">
+      <c r="P18" s="23">
+        <v>79</v>
+      </c>
+      <c r="Q18" s="24">
+        <v>93</v>
+      </c>
+      <c r="R18" s="23">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
+      <c r="A19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="2">
+        <v>17</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="R17" s="9">
-        <v>6</v>
+      <c r="D19" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="L19" s="4">
+        <v>-13.5</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="O19" s="6">
+        <v>99</v>
+      </c>
+      <c r="P19" s="23">
+        <v>78</v>
+      </c>
+      <c r="Q19" s="24">
+        <v>95</v>
+      </c>
+      <c r="R19" s="13">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
+      <c r="A20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="2">
+        <v>19</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L20" s="4">
+        <v>-44.5</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="O20" s="6">
+        <v>94</v>
+      </c>
+      <c r="P20" s="19">
+        <v>69</v>
+      </c>
+      <c r="Q20" s="25">
+        <v>40</v>
+      </c>
+      <c r="R20" s="7">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A17">
+  <conditionalFormatting sqref="A2:A20">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B17">
+  <conditionalFormatting sqref="B2:B20">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C17">
+  <conditionalFormatting sqref="C2:C20">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D17">
+  <conditionalFormatting sqref="D2:D20">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E17">
+  <conditionalFormatting sqref="E2:E20">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F17">
+  <conditionalFormatting sqref="F2:F20">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G17">
+  <conditionalFormatting sqref="G2:G20">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H17">
+  <conditionalFormatting sqref="H2:H20">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I17">
+  <conditionalFormatting sqref="I2:I20">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J17">
+  <conditionalFormatting sqref="J2:J20">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K17">
+  <conditionalFormatting sqref="K2:K20">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L17">
+  <conditionalFormatting sqref="L2:L20">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2261,12 +2480,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M17">
+  <conditionalFormatting sqref="M2:M20">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N17">
+  <conditionalFormatting sqref="N2:N20">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2283,22 +2502,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O17">
+  <conditionalFormatting sqref="O2:O20">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P17">
+  <conditionalFormatting sqref="P2:P20">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q17">
+  <conditionalFormatting sqref="Q2:Q20">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R17">
+  <conditionalFormatting sqref="R2:R20">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="193">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261004--01</t>
-  </si>
-  <si>
-    <t>20261004--02</t>
-  </si>
-  <si>
     <t>20261005--01</t>
   </si>
   <si>
@@ -127,10 +121,13 @@
     <t>20261010--04</t>
   </si>
   <si>
-    <t>04:41</t>
-  </si>
-  <si>
-    <t>05:56</t>
+    <t>20261011--01</t>
+  </si>
+  <si>
+    <t>20261011--02</t>
+  </si>
+  <si>
+    <t>20261011--03</t>
   </si>
   <si>
     <t>03:35</t>
@@ -139,7 +136,7 @@
     <t>05:48</t>
   </si>
   <si>
-    <t>00:18</t>
+    <t>00:17</t>
   </si>
   <si>
     <t>05:33</t>
@@ -154,34 +151,40 @@
     <t>05:55</t>
   </si>
   <si>
-    <t>04:22</t>
+    <t>04:21</t>
+  </si>
+  <si>
+    <t>05:51</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>02:59</t>
+  </si>
+  <si>
+    <t>05:42</t>
+  </si>
+  <si>
+    <t>05:44</t>
+  </si>
+  <si>
+    <t>05:22</t>
+  </si>
+  <si>
+    <t>04:33</t>
+  </si>
+  <si>
+    <t>04:51</t>
   </si>
   <si>
     <t>05:52</t>
   </si>
   <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>03:01</t>
-  </si>
-  <si>
-    <t>05:42</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>05:24</t>
-  </si>
-  <si>
-    <t>04:33</t>
-  </si>
-  <si>
-    <t>04:53</t>
-  </si>
-  <si>
-    <t>01:30</t>
+    <t>05:11</t>
+  </si>
+  <si>
+    <t>03:56</t>
   </si>
   <si>
     <t>00:00</t>
@@ -196,318 +199,330 @@
     <t>05:16</t>
   </si>
   <si>
-    <t>02:59</t>
-  </si>
-  <si>
-    <t>00:38</t>
-  </si>
-  <si>
-    <t>04:21</t>
-  </si>
-  <si>
-    <t>02:08</t>
-  </si>
-  <si>
-    <t>02:55</t>
-  </si>
-  <si>
-    <t>02:41:00</t>
-  </si>
-  <si>
-    <t>04:17:10</t>
-  </si>
-  <si>
-    <t>01:49:13</t>
-  </si>
-  <si>
-    <t>03:25:06</t>
-  </si>
-  <si>
-    <t>00:57:32</t>
-  </si>
-  <si>
-    <t>02:33:02</t>
-  </si>
-  <si>
-    <t>04:09:31</t>
-  </si>
-  <si>
-    <t>01:40:58</t>
-  </si>
-  <si>
-    <t>03:17:17</t>
-  </si>
-  <si>
-    <t>00:48:56</t>
-  </si>
-  <si>
-    <t>02:25:01</t>
-  </si>
-  <si>
-    <t>04:01:41</t>
-  </si>
-  <si>
-    <t>23:56:58</t>
-  </si>
-  <si>
-    <t>01:32:44</t>
-  </si>
-  <si>
-    <t>03:09:17</t>
-  </si>
-  <si>
-    <t>00:40:27</t>
-  </si>
-  <si>
-    <t>02:16:52</t>
-  </si>
-  <si>
-    <t>03:53:41</t>
-  </si>
-  <si>
-    <t>23:48:11</t>
-  </si>
-  <si>
-    <t>02:43:31</t>
-  </si>
-  <si>
-    <t>04:19:24</t>
-  </si>
-  <si>
-    <t>01:52:02</t>
-  </si>
-  <si>
-    <t>03:27:22</t>
-  </si>
-  <si>
-    <t>01:01:47</t>
-  </si>
-  <si>
-    <t>02:35:20</t>
-  </si>
-  <si>
-    <t>04:11:45</t>
-  </si>
-  <si>
-    <t>01:43:22</t>
-  </si>
-  <si>
-    <t>03:19:30</t>
-  </si>
-  <si>
-    <t>00:51:31</t>
-  </si>
-  <si>
-    <t>02:27:15</t>
-  </si>
-  <si>
-    <t>04:04:00</t>
-  </si>
-  <si>
-    <t>23:59:57</t>
-  </si>
-  <si>
-    <t>01:35:00</t>
-  </si>
-  <si>
-    <t>03:11:33</t>
-  </si>
-  <si>
-    <t>00:42:46</t>
-  </si>
-  <si>
-    <t>02:19:06</t>
-  </si>
-  <si>
-    <t>03:56:14</t>
-  </si>
-  <si>
-    <t>23:50:37</t>
-  </si>
-  <si>
-    <t>02:45:51</t>
-  </si>
-  <si>
-    <t>04:22:22</t>
+    <t>00:37</t>
+  </si>
+  <si>
+    <t>04:20</t>
+  </si>
+  <si>
+    <t>02:06</t>
+  </si>
+  <si>
+    <t>02:53</t>
+  </si>
+  <si>
+    <t>00:44</t>
+  </si>
+  <si>
+    <t>01:49:12</t>
+  </si>
+  <si>
+    <t>03:25:05</t>
+  </si>
+  <si>
+    <t>00:57:28</t>
+  </si>
+  <si>
+    <t>02:32:58</t>
+  </si>
+  <si>
+    <t>04:09:26</t>
+  </si>
+  <si>
+    <t>01:40:49</t>
+  </si>
+  <si>
+    <t>03:17:07</t>
+  </si>
+  <si>
+    <t>00:48:40</t>
+  </si>
+  <si>
+    <t>02:24:44</t>
+  </si>
+  <si>
+    <t>04:01:23</t>
+  </si>
+  <si>
+    <t>23:56:32</t>
+  </si>
+  <si>
+    <t>01:32:18</t>
+  </si>
+  <si>
+    <t>03:08:50</t>
+  </si>
+  <si>
+    <t>00:39:49</t>
+  </si>
+  <si>
+    <t>02:16:13</t>
+  </si>
+  <si>
+    <t>03:53:01</t>
+  </si>
+  <si>
+    <t>23:47:19</t>
+  </si>
+  <si>
+    <t>01:23:32</t>
+  </si>
+  <si>
+    <t>03:00:14</t>
+  </si>
+  <si>
+    <t>22:54:50</t>
+  </si>
+  <si>
+    <t>01:52:01</t>
+  </si>
+  <si>
+    <t>03:27:21</t>
+  </si>
+  <si>
+    <t>01:01:43</t>
+  </si>
+  <si>
+    <t>02:35:16</t>
+  </si>
+  <si>
+    <t>04:11:41</t>
+  </si>
+  <si>
+    <t>01:43:13</t>
+  </si>
+  <si>
+    <t>03:19:21</t>
+  </si>
+  <si>
+    <t>00:51:15</t>
+  </si>
+  <si>
+    <t>02:26:58</t>
+  </si>
+  <si>
+    <t>04:03:42</t>
+  </si>
+  <si>
+    <t>23:59:32</t>
+  </si>
+  <si>
+    <t>01:34:33</t>
+  </si>
+  <si>
+    <t>03:11:06</t>
+  </si>
+  <si>
+    <t>00:42:09</t>
+  </si>
+  <si>
+    <t>02:18:27</t>
+  </si>
+  <si>
+    <t>03:55:34</t>
+  </si>
+  <si>
+    <t>23:49:46</t>
+  </si>
+  <si>
+    <t>01:25:45</t>
+  </si>
+  <si>
+    <t>03:02:37</t>
+  </si>
+  <si>
+    <t>22:57:32</t>
   </si>
   <si>
     <t>01:53:49</t>
   </si>
   <si>
-    <t>03:30:15</t>
-  </si>
-  <si>
-    <t>02:38:06</t>
-  </si>
-  <si>
-    <t>04:14:41</t>
-  </si>
-  <si>
-    <t>01:45:55</t>
-  </si>
-  <si>
-    <t>03:22:27</t>
-  </si>
-  <si>
-    <t>00:53:42</t>
-  </si>
-  <si>
-    <t>02:30:10</t>
-  </si>
-  <si>
-    <t>04:06:45</t>
-  </si>
-  <si>
-    <t>00:01:27</t>
-  </si>
-  <si>
-    <t>01:37:50</t>
-  </si>
-  <si>
-    <t>03:14:25</t>
-  </si>
-  <si>
-    <t>00:45:27</t>
-  </si>
-  <si>
-    <t>02:22:01</t>
-  </si>
-  <si>
-    <t>03:58:30</t>
-  </si>
-  <si>
-    <t>23:53:03</t>
-  </si>
-  <si>
-    <t>02:48:12</t>
-  </si>
-  <si>
-    <t>04:25:20</t>
-  </si>
-  <si>
-    <t>01:55:37</t>
-  </si>
-  <si>
-    <t>03:33:10</t>
-  </si>
-  <si>
-    <t>01:02:05</t>
-  </si>
-  <si>
-    <t>02:40:53</t>
-  </si>
-  <si>
-    <t>04:17:38</t>
-  </si>
-  <si>
-    <t>01:48:28</t>
-  </si>
-  <si>
-    <t>03:25:25</t>
-  </si>
-  <si>
-    <t>00:55:53</t>
-  </si>
-  <si>
-    <t>02:33:07</t>
-  </si>
-  <si>
-    <t>04:09:30</t>
-  </si>
-  <si>
-    <t>00:02:58</t>
-  </si>
-  <si>
-    <t>01:40:42</t>
-  </si>
-  <si>
-    <t>03:17:18</t>
-  </si>
-  <si>
-    <t>00:48:10</t>
-  </si>
-  <si>
-    <t>02:24:58</t>
-  </si>
-  <si>
-    <t>04:00:47</t>
-  </si>
-  <si>
-    <t>23:55:30</t>
-  </si>
-  <si>
-    <t>02:50:44</t>
-  </si>
-  <si>
-    <t>04:27:35</t>
-  </si>
-  <si>
-    <t>01:58:28</t>
-  </si>
-  <si>
-    <t>03:35:26</t>
-  </si>
-  <si>
-    <t>01:06:04</t>
-  </si>
-  <si>
-    <t>02:43:12</t>
-  </si>
-  <si>
-    <t>04:19:53</t>
-  </si>
-  <si>
-    <t>01:50:54</t>
-  </si>
-  <si>
-    <t>03:27:40</t>
-  </si>
-  <si>
-    <t>00:58:29</t>
-  </si>
-  <si>
-    <t>02:35:21</t>
-  </si>
-  <si>
-    <t>04:11:50</t>
-  </si>
-  <si>
-    <t>00:05:59</t>
-  </si>
-  <si>
-    <t>01:42:58</t>
-  </si>
-  <si>
-    <t>03:19:34</t>
-  </si>
-  <si>
-    <t>00:50:30</t>
-  </si>
-  <si>
-    <t>02:27:12</t>
-  </si>
-  <si>
-    <t>04:03:20</t>
-  </si>
-  <si>
-    <t>23:57:58</t>
+    <t>03:30:14</t>
+  </si>
+  <si>
+    <t>02:38:02</t>
+  </si>
+  <si>
+    <t>04:14:37</t>
+  </si>
+  <si>
+    <t>01:45:45</t>
+  </si>
+  <si>
+    <t>03:22:18</t>
+  </si>
+  <si>
+    <t>00:53:25</t>
+  </si>
+  <si>
+    <t>02:29:53</t>
+  </si>
+  <si>
+    <t>04:06:27</t>
+  </si>
+  <si>
+    <t>00:01:01</t>
+  </si>
+  <si>
+    <t>01:37:24</t>
+  </si>
+  <si>
+    <t>03:13:58</t>
+  </si>
+  <si>
+    <t>00:44:49</t>
+  </si>
+  <si>
+    <t>02:21:22</t>
+  </si>
+  <si>
+    <t>03:57:50</t>
+  </si>
+  <si>
+    <t>23:52:11</t>
+  </si>
+  <si>
+    <t>01:28:41</t>
+  </si>
+  <si>
+    <t>03:05:12</t>
+  </si>
+  <si>
+    <t>22:59:29</t>
+  </si>
+  <si>
+    <t>01:55:36</t>
+  </si>
+  <si>
+    <t>03:33:09</t>
+  </si>
+  <si>
+    <t>01:02:00</t>
+  </si>
+  <si>
+    <t>02:40:49</t>
+  </si>
+  <si>
+    <t>04:17:34</t>
+  </si>
+  <si>
+    <t>01:48:19</t>
+  </si>
+  <si>
+    <t>03:25:16</t>
+  </si>
+  <si>
+    <t>00:55:36</t>
+  </si>
+  <si>
+    <t>02:32:49</t>
+  </si>
+  <si>
+    <t>04:09:12</t>
+  </si>
+  <si>
+    <t>00:02:31</t>
+  </si>
+  <si>
+    <t>01:40:15</t>
+  </si>
+  <si>
+    <t>03:16:50</t>
+  </si>
+  <si>
+    <t>00:47:31</t>
+  </si>
+  <si>
+    <t>02:24:18</t>
+  </si>
+  <si>
+    <t>04:00:07</t>
+  </si>
+  <si>
+    <t>23:54:37</t>
+  </si>
+  <si>
+    <t>01:31:37</t>
+  </si>
+  <si>
+    <t>03:07:48</t>
+  </si>
+  <si>
+    <t>23:01:28</t>
+  </si>
+  <si>
+    <t>01:58:27</t>
+  </si>
+  <si>
+    <t>03:35:25</t>
+  </si>
+  <si>
+    <t>01:06:00</t>
+  </si>
+  <si>
+    <t>02:43:08</t>
+  </si>
+  <si>
+    <t>04:19:49</t>
+  </si>
+  <si>
+    <t>01:50:44</t>
+  </si>
+  <si>
+    <t>03:27:30</t>
+  </si>
+  <si>
+    <t>00:58:13</t>
+  </si>
+  <si>
+    <t>02:35:04</t>
+  </si>
+  <si>
+    <t>04:11:32</t>
+  </si>
+  <si>
+    <t>00:05:32</t>
+  </si>
+  <si>
+    <t>01:42:31</t>
+  </si>
+  <si>
+    <t>03:19:07</t>
+  </si>
+  <si>
+    <t>00:49:52</t>
+  </si>
+  <si>
+    <t>02:26:33</t>
+  </si>
+  <si>
+    <t>04:02:40</t>
+  </si>
+  <si>
+    <t>23:57:05</t>
+  </si>
+  <si>
+    <t>01:33:51</t>
+  </si>
+  <si>
+    <t>03:10:11</t>
+  </si>
+  <si>
+    <t>23:04:11</t>
+  </si>
+  <si>
+    <t>5°</t>
+  </si>
+  <si>
+    <t>26°</t>
+  </si>
+  <si>
+    <t>0°</t>
   </si>
   <si>
     <t>17°</t>
   </si>
   <si>
-    <t>10°</t>
-  </si>
-  <si>
-    <t>5°</t>
-  </si>
-  <si>
-    <t>26°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
     <t>14°</t>
   </si>
   <si>
@@ -526,64 +541,55 @@
     <t>9°</t>
   </si>
   <si>
-    <t>02:46:42</t>
-  </si>
-  <si>
-    <t>04:19:23</t>
-  </si>
-  <si>
-    <t>01:56:53</t>
-  </si>
-  <si>
-    <t>03:29:34</t>
-  </si>
-  <si>
-    <t>02:39:41</t>
-  </si>
-  <si>
-    <t>04:12:22</t>
-  </si>
-  <si>
-    <t>01:49:46</t>
-  </si>
-  <si>
-    <t>03:22:26</t>
-  </si>
-  <si>
-    <t>02:32:29</t>
-  </si>
-  <si>
-    <t>04:05:09</t>
-  </si>
-  <si>
-    <t>01:42:30</t>
-  </si>
-  <si>
-    <t>03:15:10</t>
-  </si>
-  <si>
-    <t>02:25:12</t>
-  </si>
-  <si>
-    <t>03:57:52</t>
+    <t>01:56:52</t>
+  </si>
+  <si>
+    <t>03:29:33</t>
+  </si>
+  <si>
+    <t>02:39:37</t>
+  </si>
+  <si>
+    <t>04:12:18</t>
+  </si>
+  <si>
+    <t>01:49:37</t>
+  </si>
+  <si>
+    <t>03:22:17</t>
+  </si>
+  <si>
+    <t>02:32:12</t>
+  </si>
+  <si>
+    <t>04:04:52</t>
+  </si>
+  <si>
+    <t>01:42:05</t>
+  </si>
+  <si>
+    <t>03:14:44</t>
+  </si>
+  <si>
+    <t>02:24:35</t>
+  </si>
+  <si>
+    <t>03:57:14</t>
+  </si>
+  <si>
+    <t>03:07:04</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
+    <t>4</t>
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
   <si>
     <t>3</t>
@@ -620,7 +626,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -641,7 +647,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -653,7 +683,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -665,31 +695,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -701,25 +707,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -731,7 +731,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -749,7 +767,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -790,7 +814,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -865,6 +889,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1268,7 +1301,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1346,55 +1379,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="L2" s="4">
-        <v>-23.1</v>
+        <v>-30.5</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="O2" s="6">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="P2" s="7">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="Q2" s="8">
-        <v>8</v>
-      </c>
-      <c r="R2" s="8">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="R2" s="9">
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1402,55 +1435,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="L3" s="4">
-        <v>-8.4</v>
+        <v>-16.7</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="O3" s="6">
-        <v>59</v>
-      </c>
-      <c r="P3" s="9">
-        <v>55</v>
+        <v>91</v>
+      </c>
+      <c r="P3" s="10">
+        <v>64</v>
       </c>
       <c r="Q3" s="8">
-        <v>8</v>
-      </c>
-      <c r="R3" s="7">
-        <v>49</v>
+        <v>1</v>
+      </c>
+      <c r="R3" s="9">
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1458,55 +1491,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>172</v>
+        <v>68</v>
       </c>
       <c r="L4" s="4">
-        <v>-30.5</v>
+        <v>-37.1</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="O4" s="6">
-        <v>100</v>
-      </c>
-      <c r="P4" s="10">
-        <v>14</v>
-      </c>
-      <c r="Q4" s="10">
-        <v>17</v>
-      </c>
-      <c r="R4" s="11">
-        <v>100</v>
+        <v>190</v>
+      </c>
+      <c r="O4" s="11">
+        <v>15</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>0</v>
+      </c>
+      <c r="R4" s="12">
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1514,55 +1547,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="L5" s="4">
-        <v>-16.7</v>
+        <v>-24.7</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="O5" s="6">
-        <v>96</v>
-      </c>
-      <c r="P5" s="10">
-        <v>15</v>
-      </c>
-      <c r="Q5" s="12">
-        <v>1</v>
+        <v>191</v>
+      </c>
+      <c r="O5" s="11">
+        <v>8</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>0</v>
       </c>
       <c r="R5" s="13">
-        <v>92</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1570,55 +1603,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>69</v>
+        <v>178</v>
       </c>
       <c r="L6" s="4">
-        <v>-37.1</v>
+        <v>-10.1</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="O6" s="14">
-        <v>5</v>
-      </c>
-      <c r="P6" s="12">
+        <v>191</v>
+      </c>
+      <c r="O6" s="11">
+        <v>15</v>
+      </c>
+      <c r="P6" s="8">
         <v>0</v>
       </c>
-      <c r="Q6" s="12">
+      <c r="Q6" s="8">
         <v>0</v>
       </c>
-      <c r="R6" s="12">
-        <v>2</v>
+      <c r="R6" s="14">
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1626,55 +1659,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="L7" s="4">
-        <v>-24.7</v>
+        <v>-32.1</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="O7" s="14">
-        <v>7</v>
-      </c>
-      <c r="P7" s="12">
+        <v>192</v>
+      </c>
+      <c r="O7" s="11">
+        <v>3</v>
+      </c>
+      <c r="P7" s="8">
         <v>0</v>
       </c>
-      <c r="Q7" s="12">
+      <c r="Q7" s="8">
         <v>0</v>
       </c>
-      <c r="R7" s="15">
-        <v>4</v>
+      <c r="R7" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1682,55 +1715,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="L8" s="4">
-        <v>-10.1</v>
+        <v>-18.4</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="O8" s="14">
-        <v>7</v>
-      </c>
-      <c r="P8" s="12">
+        <v>191</v>
+      </c>
+      <c r="O8" s="6">
+        <v>99</v>
+      </c>
+      <c r="P8" s="8">
         <v>0</v>
       </c>
-      <c r="Q8" s="12">
-        <v>0</v>
-      </c>
-      <c r="R8" s="15">
-        <v>3</v>
+      <c r="Q8" s="15">
+        <v>31</v>
+      </c>
+      <c r="R8" s="9">
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1738,55 +1771,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>176</v>
+        <v>73</v>
       </c>
       <c r="L9" s="4">
-        <v>-32.1</v>
+        <v>-38.6</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="O9" s="14">
+        <v>192</v>
+      </c>
+      <c r="O9" s="16">
+        <v>38</v>
+      </c>
+      <c r="P9" s="8">
         <v>0</v>
       </c>
-      <c r="P9" s="12">
+      <c r="Q9" s="8">
         <v>0</v>
       </c>
-      <c r="Q9" s="12">
-        <v>0</v>
-      </c>
-      <c r="R9" s="12">
-        <v>0</v>
+      <c r="R9" s="17">
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1794,55 +1827,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="L10" s="4">
-        <v>-18.4</v>
+        <v>-26.4</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="O10" s="14">
+        <v>191</v>
+      </c>
+      <c r="O10" s="6">
+        <v>83</v>
+      </c>
+      <c r="P10" s="8">
         <v>0</v>
       </c>
-      <c r="P10" s="12">
+      <c r="Q10" s="8">
         <v>0</v>
       </c>
-      <c r="Q10" s="12">
-        <v>0</v>
-      </c>
-      <c r="R10" s="12">
-        <v>0</v>
+      <c r="R10" s="18">
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1850,55 +1883,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>74</v>
+        <v>182</v>
       </c>
       <c r="L11" s="4">
-        <v>-38.5</v>
+        <v>-11.8</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="O11" s="14">
-        <v>3</v>
-      </c>
-      <c r="P11" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="12">
-        <v>0</v>
-      </c>
-      <c r="R11" s="15">
-        <v>3</v>
+        <v>191</v>
+      </c>
+      <c r="O11" s="6">
+        <v>89</v>
+      </c>
+      <c r="P11" s="19">
+        <v>20</v>
+      </c>
+      <c r="Q11" s="18">
+        <v>83</v>
+      </c>
+      <c r="R11" s="10">
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1906,55 +1939,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L12" s="4">
+        <v>-43.3</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="O12" s="6">
+        <v>67</v>
+      </c>
+      <c r="P12" s="20">
         <v>47</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="L12" s="4">
-        <v>-26.4</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="O12" s="16">
-        <v>23</v>
-      </c>
-      <c r="P12" s="12">
-        <v>1</v>
-      </c>
       <c r="Q12" s="15">
-        <v>7</v>
-      </c>
-      <c r="R12" s="8">
-        <v>11</v>
+        <v>32</v>
+      </c>
+      <c r="R12" s="19">
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1962,55 +1995,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="L13" s="4">
-        <v>-11.8</v>
+        <v>-33.8</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="O13" s="16">
-        <v>47</v>
-      </c>
-      <c r="P13" s="12">
-        <v>2</v>
-      </c>
-      <c r="Q13" s="17">
-        <v>20</v>
-      </c>
-      <c r="R13" s="15">
-        <v>5</v>
+        <v>192</v>
+      </c>
+      <c r="O13" s="6">
+        <v>67</v>
+      </c>
+      <c r="P13" s="21">
+        <v>57</v>
+      </c>
+      <c r="Q13" s="22">
+        <v>26</v>
+      </c>
+      <c r="R13" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2018,55 +2051,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>77</v>
+        <v>184</v>
       </c>
       <c r="L14" s="4">
-        <v>-43.2</v>
+        <v>-20.2</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O14" s="6">
         <v>76</v>
       </c>
-      <c r="P14" s="18">
-        <v>67</v>
-      </c>
-      <c r="Q14" s="7">
-        <v>50</v>
-      </c>
-      <c r="R14" s="19">
-        <v>70</v>
+      <c r="P14" s="23">
+        <v>58</v>
+      </c>
+      <c r="Q14" s="12">
+        <v>11</v>
+      </c>
+      <c r="R14" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2074,55 +2107,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>167</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>180</v>
+        <v>79</v>
       </c>
       <c r="L15" s="4">
-        <v>-33.7</v>
+        <v>-40.1</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O15" s="6">
-        <v>73</v>
-      </c>
-      <c r="P15" s="20">
-        <v>73</v>
-      </c>
-      <c r="Q15" s="21">
-        <v>46</v>
-      </c>
-      <c r="R15" s="18">
-        <v>66</v>
+        <v>97</v>
+      </c>
+      <c r="P15" s="24">
+        <v>90</v>
+      </c>
+      <c r="Q15" s="18">
+        <v>86</v>
+      </c>
+      <c r="R15" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2130,55 +2163,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F16" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="L16" s="4">
+        <v>-28.2</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="O16" s="6">
         <v>98</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="L16" s="4">
-        <v>-20.1</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="O16" s="6">
-        <v>86</v>
-      </c>
-      <c r="P16" s="20">
-        <v>77</v>
-      </c>
-      <c r="Q16" s="7">
-        <v>52</v>
-      </c>
-      <c r="R16" s="21">
-        <v>43</v>
+      <c r="P16" s="24">
+        <v>92</v>
+      </c>
+      <c r="Q16" s="25">
+        <v>82</v>
+      </c>
+      <c r="R16" s="19">
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2186,55 +2219,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F17" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="L17" s="4">
+        <v>-13.7</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="O17" s="6">
         <v>99</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="L17" s="4">
-        <v>-40</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="O17" s="6">
-        <v>89</v>
-      </c>
-      <c r="P17" s="22">
-        <v>59</v>
-      </c>
-      <c r="Q17" s="20">
+      <c r="P17" s="26">
+        <v>96</v>
+      </c>
+      <c r="Q17" s="27">
         <v>75</v>
       </c>
-      <c r="R17" s="20">
-        <v>75</v>
+      <c r="R17" s="14">
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2242,55 +2275,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F18" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L18" s="4">
+        <v>-44.5</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="O18" s="6">
         <v>100</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="L18" s="4">
-        <v>-28.1</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="O18" s="6">
-        <v>98</v>
-      </c>
-      <c r="P18" s="23">
-        <v>79</v>
-      </c>
-      <c r="Q18" s="24">
-        <v>93</v>
+      <c r="P18" s="28">
+        <v>48</v>
+      </c>
+      <c r="Q18" s="26">
+        <v>94</v>
       </c>
       <c r="R18" s="23">
-        <v>82</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2298,55 +2331,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>183</v>
+        <v>83</v>
       </c>
       <c r="L19" s="4">
-        <v>-13.5</v>
+        <v>-35.5</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="O19" s="6">
+        <v>100</v>
+      </c>
+      <c r="P19" s="27">
+        <v>74</v>
+      </c>
+      <c r="Q19" s="9">
         <v>99</v>
       </c>
-      <c r="P19" s="23">
-        <v>78</v>
-      </c>
-      <c r="Q19" s="24">
-        <v>95</v>
-      </c>
-      <c r="R19" s="13">
-        <v>88</v>
+      <c r="R19" s="10">
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2354,114 +2387,170 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="L20" s="4">
+        <v>-22</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="O20" s="6">
+        <v>99</v>
+      </c>
+      <c r="P20" s="25">
+        <v>82</v>
+      </c>
+      <c r="Q20" s="24">
+        <v>92</v>
+      </c>
+      <c r="R20" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
+      <c r="A21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="2">
+        <v>15</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="L20" s="4">
-        <v>-44.5</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="O20" s="6">
-        <v>94</v>
-      </c>
-      <c r="P20" s="19">
-        <v>69</v>
-      </c>
-      <c r="Q20" s="25">
-        <v>40</v>
-      </c>
-      <c r="R20" s="7">
-        <v>50</v>
+      <c r="D21" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L21" s="4">
+        <v>-46.6</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="O21" s="6">
+        <v>93</v>
+      </c>
+      <c r="P21" s="18">
+        <v>87</v>
+      </c>
+      <c r="Q21" s="27">
+        <v>75</v>
+      </c>
+      <c r="R21" s="17">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A20">
+  <conditionalFormatting sqref="A2:A21">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B20">
+  <conditionalFormatting sqref="B2:B21">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C20">
+  <conditionalFormatting sqref="C2:C21">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D20">
+  <conditionalFormatting sqref="D2:D21">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E20">
+  <conditionalFormatting sqref="E2:E21">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F20">
+  <conditionalFormatting sqref="F2:F21">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G20">
+  <conditionalFormatting sqref="G2:G21">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H20">
+  <conditionalFormatting sqref="H2:H21">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I20">
+  <conditionalFormatting sqref="I2:I21">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J20">
+  <conditionalFormatting sqref="J2:J21">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K20">
+  <conditionalFormatting sqref="K2:K21">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L20">
+  <conditionalFormatting sqref="L2:L21">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2480,12 +2569,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M20">
+  <conditionalFormatting sqref="M2:M21">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N20">
+  <conditionalFormatting sqref="N2:N21">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2502,22 +2591,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O20">
+  <conditionalFormatting sqref="O2:O21">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P20">
+  <conditionalFormatting sqref="P2:P21">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q20">
+  <conditionalFormatting sqref="Q2:Q21">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R20">
+  <conditionalFormatting sqref="R2:R21">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="213">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261005--01</t>
-  </si>
-  <si>
-    <t>20261005--02</t>
-  </si>
-  <si>
     <t>20261006--01</t>
   </si>
   <si>
@@ -130,70 +124,91 @@
     <t>20261011--03</t>
   </si>
   <si>
-    <t>03:35</t>
-  </si>
-  <si>
-    <t>05:48</t>
-  </si>
-  <si>
-    <t>00:17</t>
+    <t>20261012--01</t>
+  </si>
+  <si>
+    <t>20261012--02</t>
+  </si>
+  <si>
+    <t>20261012--03</t>
+  </si>
+  <si>
+    <t>20261012--04</t>
+  </si>
+  <si>
+    <t>20261012--05</t>
+  </si>
+  <si>
+    <t>00:16</t>
+  </si>
+  <si>
+    <t>05:32</t>
+  </si>
+  <si>
+    <t>05:53</t>
+  </si>
+  <si>
+    <t>05:06</t>
+  </si>
+  <si>
+    <t>05:56</t>
+  </si>
+  <si>
+    <t>04:22</t>
+  </si>
+  <si>
+    <t>05:51</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>02:59</t>
+  </si>
+  <si>
+    <t>05:42</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>05:23</t>
+  </si>
+  <si>
+    <t>05:52</t>
+  </si>
+  <si>
+    <t>04:33</t>
+  </si>
+  <si>
+    <t>04:51</t>
+  </si>
+  <si>
+    <t>05:11</t>
+  </si>
+  <si>
+    <t>03:57</t>
+  </si>
+  <si>
+    <t>05:47</t>
   </si>
   <si>
     <t>05:33</t>
   </si>
   <si>
-    <t>05:53</t>
-  </si>
-  <si>
-    <t>05:06</t>
-  </si>
-  <si>
-    <t>05:55</t>
-  </si>
-  <si>
-    <t>04:21</t>
-  </si>
-  <si>
-    <t>05:51</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>02:59</t>
-  </si>
-  <si>
-    <t>05:42</t>
-  </si>
-  <si>
-    <t>05:44</t>
-  </si>
-  <si>
-    <t>05:22</t>
-  </si>
-  <si>
-    <t>04:33</t>
-  </si>
-  <si>
-    <t>04:51</t>
-  </si>
-  <si>
-    <t>05:52</t>
-  </si>
-  <si>
-    <t>05:11</t>
-  </si>
-  <si>
-    <t>03:56</t>
+    <t>01:46</t>
+  </si>
+  <si>
+    <t>02:03</t>
+  </si>
+  <si>
+    <t>05:34</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>03:36</t>
-  </si>
-  <si>
-    <t>01:12</t>
+    <t>01:11</t>
   </si>
   <si>
     <t>05:16</t>
@@ -211,13 +226,10 @@
     <t>02:53</t>
   </si>
   <si>
-    <t>00:44</t>
-  </si>
-  <si>
-    <t>01:49:12</t>
-  </si>
-  <si>
-    <t>03:25:05</t>
+    <t>00:45</t>
+  </si>
+  <si>
+    <t>00:07</t>
   </si>
   <si>
     <t>00:57:28</t>
@@ -226,358 +238,406 @@
     <t>02:32:58</t>
   </si>
   <si>
-    <t>04:09:26</t>
-  </si>
-  <si>
-    <t>01:40:49</t>
-  </si>
-  <si>
-    <t>03:17:07</t>
-  </si>
-  <si>
-    <t>00:48:40</t>
+    <t>04:09:27</t>
+  </si>
+  <si>
+    <t>01:40:51</t>
+  </si>
+  <si>
+    <t>03:17:09</t>
+  </si>
+  <si>
+    <t>00:48:43</t>
+  </si>
+  <si>
+    <t>02:24:48</t>
+  </si>
+  <si>
+    <t>04:01:27</t>
+  </si>
+  <si>
+    <t>23:56:38</t>
+  </si>
+  <si>
+    <t>01:32:24</t>
+  </si>
+  <si>
+    <t>03:08:57</t>
+  </si>
+  <si>
+    <t>00:39:58</t>
+  </si>
+  <si>
+    <t>02:16:23</t>
+  </si>
+  <si>
+    <t>03:53:11</t>
+  </si>
+  <si>
+    <t>23:47:32</t>
+  </si>
+  <si>
+    <t>01:23:45</t>
+  </si>
+  <si>
+    <t>03:00:27</t>
+  </si>
+  <si>
+    <t>22:55:08</t>
+  </si>
+  <si>
+    <t>00:31:05</t>
+  </si>
+  <si>
+    <t>02:07:41</t>
+  </si>
+  <si>
+    <t>03:44:43</t>
+  </si>
+  <si>
+    <t>22:02:47</t>
+  </si>
+  <si>
+    <t>23:38:23</t>
+  </si>
+  <si>
+    <t>01:01:44</t>
+  </si>
+  <si>
+    <t>02:35:17</t>
+  </si>
+  <si>
+    <t>04:11:41</t>
+  </si>
+  <si>
+    <t>01:43:15</t>
+  </si>
+  <si>
+    <t>03:19:22</t>
+  </si>
+  <si>
+    <t>00:51:18</t>
+  </si>
+  <si>
+    <t>02:27:02</t>
+  </si>
+  <si>
+    <t>04:03:46</t>
+  </si>
+  <si>
+    <t>23:59:38</t>
+  </si>
+  <si>
+    <t>01:34:39</t>
+  </si>
+  <si>
+    <t>03:11:12</t>
+  </si>
+  <si>
+    <t>00:42:18</t>
+  </si>
+  <si>
+    <t>02:18:36</t>
+  </si>
+  <si>
+    <t>03:55:44</t>
+  </si>
+  <si>
+    <t>23:49:59</t>
+  </si>
+  <si>
+    <t>01:25:59</t>
+  </si>
+  <si>
+    <t>03:02:51</t>
+  </si>
+  <si>
+    <t>22:57:49</t>
+  </si>
+  <si>
+    <t>00:33:19</t>
+  </si>
+  <si>
+    <t>02:09:59</t>
+  </si>
+  <si>
+    <t>03:48:11</t>
+  </si>
+  <si>
+    <t>22:06:06</t>
+  </si>
+  <si>
+    <t>23:40:39</t>
+  </si>
+  <si>
+    <t>02:38:02</t>
+  </si>
+  <si>
+    <t>04:14:38</t>
+  </si>
+  <si>
+    <t>01:45:47</t>
+  </si>
+  <si>
+    <t>03:22:20</t>
+  </si>
+  <si>
+    <t>00:53:29</t>
+  </si>
+  <si>
+    <t>02:29:57</t>
+  </si>
+  <si>
+    <t>04:06:31</t>
+  </si>
+  <si>
+    <t>00:01:07</t>
+  </si>
+  <si>
+    <t>01:37:30</t>
+  </si>
+  <si>
+    <t>03:14:04</t>
+  </si>
+  <si>
+    <t>00:44:59</t>
+  </si>
+  <si>
+    <t>02:21:32</t>
+  </si>
+  <si>
+    <t>03:58:00</t>
+  </si>
+  <si>
+    <t>23:52:24</t>
+  </si>
+  <si>
+    <t>01:28:54</t>
+  </si>
+  <si>
+    <t>03:05:26</t>
+  </si>
+  <si>
+    <t>22:59:47</t>
+  </si>
+  <si>
+    <t>00:36:12</t>
+  </si>
+  <si>
+    <t>02:12:45</t>
+  </si>
+  <si>
+    <t>03:49:04</t>
+  </si>
+  <si>
+    <t>22:07:07</t>
+  </si>
+  <si>
+    <t>23:43:26</t>
+  </si>
+  <si>
+    <t>01:02:00</t>
+  </si>
+  <si>
+    <t>02:40:49</t>
+  </si>
+  <si>
+    <t>04:17:34</t>
+  </si>
+  <si>
+    <t>01:48:21</t>
+  </si>
+  <si>
+    <t>03:25:18</t>
+  </si>
+  <si>
+    <t>00:55:40</t>
+  </si>
+  <si>
+    <t>02:32:53</t>
+  </si>
+  <si>
+    <t>04:09:16</t>
+  </si>
+  <si>
+    <t>00:02:37</t>
+  </si>
+  <si>
+    <t>01:40:21</t>
+  </si>
+  <si>
+    <t>03:16:57</t>
+  </si>
+  <si>
+    <t>00:47:41</t>
+  </si>
+  <si>
+    <t>02:24:28</t>
+  </si>
+  <si>
+    <t>04:00:17</t>
+  </si>
+  <si>
+    <t>23:54:50</t>
+  </si>
+  <si>
+    <t>01:31:51</t>
+  </si>
+  <si>
+    <t>03:08:02</t>
+  </si>
+  <si>
+    <t>23:01:46</t>
+  </si>
+  <si>
+    <t>00:39:06</t>
+  </si>
+  <si>
+    <t>02:15:32</t>
+  </si>
+  <si>
+    <t>03:49:57</t>
+  </si>
+  <si>
+    <t>22:08:09</t>
+  </si>
+  <si>
+    <t>23:46:13</t>
+  </si>
+  <si>
+    <t>01:06:01</t>
+  </si>
+  <si>
+    <t>02:43:09</t>
+  </si>
+  <si>
+    <t>04:19:49</t>
+  </si>
+  <si>
+    <t>01:50:46</t>
+  </si>
+  <si>
+    <t>03:27:32</t>
+  </si>
+  <si>
+    <t>00:58:16</t>
+  </si>
+  <si>
+    <t>02:35:08</t>
+  </si>
+  <si>
+    <t>04:11:36</t>
+  </si>
+  <si>
+    <t>00:05:38</t>
+  </si>
+  <si>
+    <t>01:42:38</t>
+  </si>
+  <si>
+    <t>03:19:13</t>
+  </si>
+  <si>
+    <t>00:50:01</t>
+  </si>
+  <si>
+    <t>02:26:42</t>
+  </si>
+  <si>
+    <t>04:02:50</t>
+  </si>
+  <si>
+    <t>23:57:19</t>
+  </si>
+  <si>
+    <t>01:34:05</t>
+  </si>
+  <si>
+    <t>03:10:25</t>
+  </si>
+  <si>
+    <t>23:04:28</t>
+  </si>
+  <si>
+    <t>00:41:21</t>
+  </si>
+  <si>
+    <t>02:17:50</t>
+  </si>
+  <si>
+    <t>03:53:25</t>
+  </si>
+  <si>
+    <t>22:11:29</t>
+  </si>
+  <si>
+    <t>23:48:31</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>17°</t>
+  </si>
+  <si>
+    <t>14°</t>
+  </si>
+  <si>
+    <t>4°</t>
+  </si>
+  <si>
+    <t>30°</t>
+  </si>
+  <si>
+    <t>2°</t>
+  </si>
+  <si>
+    <t>25°</t>
+  </si>
+  <si>
+    <t>9°</t>
+  </si>
+  <si>
+    <t>10°</t>
+  </si>
+  <si>
+    <t>02:39:38</t>
+  </si>
+  <si>
+    <t>04:12:18</t>
+  </si>
+  <si>
+    <t>01:49:39</t>
+  </si>
+  <si>
+    <t>03:22:19</t>
+  </si>
+  <si>
+    <t>02:32:16</t>
+  </si>
+  <si>
+    <t>04:04:56</t>
+  </si>
+  <si>
+    <t>01:42:11</t>
+  </si>
+  <si>
+    <t>03:14:51</t>
   </si>
   <si>
     <t>02:24:44</t>
   </si>
   <si>
-    <t>04:01:23</t>
-  </si>
-  <si>
-    <t>23:56:32</t>
-  </si>
-  <si>
-    <t>01:32:18</t>
-  </si>
-  <si>
-    <t>03:08:50</t>
-  </si>
-  <si>
-    <t>00:39:49</t>
-  </si>
-  <si>
-    <t>02:16:13</t>
-  </si>
-  <si>
-    <t>03:53:01</t>
-  </si>
-  <si>
-    <t>23:47:19</t>
-  </si>
-  <si>
-    <t>01:23:32</t>
-  </si>
-  <si>
-    <t>03:00:14</t>
-  </si>
-  <si>
-    <t>22:54:50</t>
-  </si>
-  <si>
-    <t>01:52:01</t>
-  </si>
-  <si>
-    <t>03:27:21</t>
-  </si>
-  <si>
-    <t>01:01:43</t>
-  </si>
-  <si>
-    <t>02:35:16</t>
-  </si>
-  <si>
-    <t>04:11:41</t>
-  </si>
-  <si>
-    <t>01:43:13</t>
-  </si>
-  <si>
-    <t>03:19:21</t>
-  </si>
-  <si>
-    <t>00:51:15</t>
-  </si>
-  <si>
-    <t>02:26:58</t>
-  </si>
-  <si>
-    <t>04:03:42</t>
-  </si>
-  <si>
-    <t>23:59:32</t>
-  </si>
-  <si>
-    <t>01:34:33</t>
-  </si>
-  <si>
-    <t>03:11:06</t>
-  </si>
-  <si>
-    <t>00:42:09</t>
-  </si>
-  <si>
-    <t>02:18:27</t>
-  </si>
-  <si>
-    <t>03:55:34</t>
-  </si>
-  <si>
-    <t>23:49:46</t>
-  </si>
-  <si>
-    <t>01:25:45</t>
-  </si>
-  <si>
-    <t>03:02:37</t>
-  </si>
-  <si>
-    <t>22:57:32</t>
-  </si>
-  <si>
-    <t>01:53:49</t>
-  </si>
-  <si>
-    <t>03:30:14</t>
-  </si>
-  <si>
-    <t>02:38:02</t>
-  </si>
-  <si>
-    <t>04:14:37</t>
-  </si>
-  <si>
-    <t>01:45:45</t>
-  </si>
-  <si>
-    <t>03:22:18</t>
-  </si>
-  <si>
-    <t>00:53:25</t>
-  </si>
-  <si>
-    <t>02:29:53</t>
-  </si>
-  <si>
-    <t>04:06:27</t>
-  </si>
-  <si>
-    <t>00:01:01</t>
-  </si>
-  <si>
-    <t>01:37:24</t>
-  </si>
-  <si>
-    <t>03:13:58</t>
-  </si>
-  <si>
-    <t>00:44:49</t>
-  </si>
-  <si>
-    <t>02:21:22</t>
-  </si>
-  <si>
-    <t>03:57:50</t>
-  </si>
-  <si>
-    <t>23:52:11</t>
-  </si>
-  <si>
-    <t>01:28:41</t>
-  </si>
-  <si>
-    <t>03:05:12</t>
-  </si>
-  <si>
-    <t>22:59:29</t>
-  </si>
-  <si>
-    <t>01:55:36</t>
-  </si>
-  <si>
-    <t>03:33:09</t>
-  </si>
-  <si>
-    <t>01:02:00</t>
-  </si>
-  <si>
-    <t>02:40:49</t>
-  </si>
-  <si>
-    <t>04:17:34</t>
-  </si>
-  <si>
-    <t>01:48:19</t>
-  </si>
-  <si>
-    <t>03:25:16</t>
-  </si>
-  <si>
-    <t>00:55:36</t>
-  </si>
-  <si>
-    <t>02:32:49</t>
-  </si>
-  <si>
-    <t>04:09:12</t>
-  </si>
-  <si>
-    <t>00:02:31</t>
-  </si>
-  <si>
-    <t>01:40:15</t>
-  </si>
-  <si>
-    <t>03:16:50</t>
-  </si>
-  <si>
-    <t>00:47:31</t>
-  </si>
-  <si>
-    <t>02:24:18</t>
-  </si>
-  <si>
-    <t>04:00:07</t>
-  </si>
-  <si>
-    <t>23:54:37</t>
-  </si>
-  <si>
-    <t>01:31:37</t>
-  </si>
-  <si>
-    <t>03:07:48</t>
-  </si>
-  <si>
-    <t>23:01:28</t>
-  </si>
-  <si>
-    <t>01:58:27</t>
-  </si>
-  <si>
-    <t>03:35:25</t>
-  </si>
-  <si>
-    <t>01:06:00</t>
-  </si>
-  <si>
-    <t>02:43:08</t>
-  </si>
-  <si>
-    <t>04:19:49</t>
-  </si>
-  <si>
-    <t>01:50:44</t>
-  </si>
-  <si>
-    <t>03:27:30</t>
-  </si>
-  <si>
-    <t>00:58:13</t>
-  </si>
-  <si>
-    <t>02:35:04</t>
-  </si>
-  <si>
-    <t>04:11:32</t>
-  </si>
-  <si>
-    <t>00:05:32</t>
-  </si>
-  <si>
-    <t>01:42:31</t>
-  </si>
-  <si>
-    <t>03:19:07</t>
-  </si>
-  <si>
-    <t>00:49:52</t>
-  </si>
-  <si>
-    <t>02:26:33</t>
-  </si>
-  <si>
-    <t>04:02:40</t>
-  </si>
-  <si>
-    <t>23:57:05</t>
-  </si>
-  <si>
-    <t>01:33:51</t>
-  </si>
-  <si>
-    <t>03:10:11</t>
-  </si>
-  <si>
-    <t>23:04:11</t>
-  </si>
-  <si>
-    <t>5°</t>
-  </si>
-  <si>
-    <t>26°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>17°</t>
-  </si>
-  <si>
-    <t>14°</t>
-  </si>
-  <si>
-    <t>4°</t>
-  </si>
-  <si>
-    <t>30°</t>
-  </si>
-  <si>
-    <t>2°</t>
-  </si>
-  <si>
-    <t>25°</t>
-  </si>
-  <si>
-    <t>9°</t>
-  </si>
-  <si>
-    <t>01:56:52</t>
-  </si>
-  <si>
-    <t>03:29:33</t>
-  </si>
-  <si>
-    <t>02:39:37</t>
-  </si>
-  <si>
-    <t>04:12:18</t>
-  </si>
-  <si>
-    <t>01:49:37</t>
-  </si>
-  <si>
-    <t>03:22:17</t>
-  </si>
-  <si>
-    <t>02:32:12</t>
-  </si>
-  <si>
-    <t>04:04:52</t>
-  </si>
-  <si>
-    <t>01:42:05</t>
-  </si>
-  <si>
-    <t>03:14:44</t>
-  </si>
-  <si>
-    <t>02:24:35</t>
-  </si>
-  <si>
-    <t>03:57:14</t>
-  </si>
-  <si>
-    <t>03:07:04</t>
+    <t>03:57:24</t>
+  </si>
+  <si>
+    <t>03:07:17</t>
+  </si>
+  <si>
+    <t>02:17:10</t>
+  </si>
+  <si>
+    <t>03:49:50</t>
   </si>
   <si>
     <t>B</t>
@@ -626,7 +686,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -641,7 +701,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -653,19 +749,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -677,37 +773,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -719,13 +803,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FFEEF3F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -737,43 +821,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -814,7 +862,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -892,12 +940,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1301,7 +1343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1379,55 +1421,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>175</v>
+        <v>72</v>
       </c>
       <c r="L2" s="4">
-        <v>-30.5</v>
+        <v>-37.1</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="O2" s="6">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="P2" s="7">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
       </c>
       <c r="R2" s="9">
-        <v>100</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1435,55 +1477,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="L3" s="4">
-        <v>-16.7</v>
+        <v>-24.7</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="O3" s="6">
-        <v>91</v>
+        <v>23</v>
       </c>
       <c r="P3" s="10">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="Q3" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" s="9">
-        <v>100</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1491,55 +1533,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="L4" s="4">
-        <v>-37.1</v>
+        <v>-10.1</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="O4" s="11">
-        <v>15</v>
-      </c>
-      <c r="P4" s="8">
-        <v>0</v>
+        <v>211</v>
+      </c>
+      <c r="O4" s="6">
+        <v>42</v>
+      </c>
+      <c r="P4" s="11">
+        <v>100</v>
       </c>
       <c r="Q4" s="8">
         <v>0</v>
       </c>
       <c r="R4" s="12">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1547,55 +1589,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="L5" s="4">
-        <v>-24.7</v>
+        <v>-32.1</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O5" s="11">
-        <v>8</v>
+        <v>212</v>
+      </c>
+      <c r="O5" s="6">
+        <v>47</v>
       </c>
       <c r="P5" s="8">
         <v>0</v>
       </c>
-      <c r="Q5" s="8">
-        <v>0</v>
-      </c>
-      <c r="R5" s="13">
-        <v>5</v>
+      <c r="Q5" s="13">
+        <v>42</v>
+      </c>
+      <c r="R5" s="14">
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1603,55 +1645,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="L6" s="4">
-        <v>-10.1</v>
+        <v>-18.4</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O6" s="11">
-        <v>15</v>
+        <v>211</v>
+      </c>
+      <c r="O6" s="15">
+        <v>100</v>
       </c>
       <c r="P6" s="8">
         <v>0</v>
       </c>
-      <c r="Q6" s="8">
-        <v>0</v>
-      </c>
-      <c r="R6" s="14">
-        <v>13</v>
+      <c r="Q6" s="16">
+        <v>35</v>
+      </c>
+      <c r="R6" s="11">
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1659,46 +1701,46 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>179</v>
+        <v>77</v>
       </c>
       <c r="L7" s="4">
-        <v>-32.1</v>
+        <v>-38.5</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="O7" s="11">
-        <v>3</v>
+        <v>212</v>
+      </c>
+      <c r="O7" s="17">
+        <v>8</v>
       </c>
       <c r="P7" s="8">
         <v>0</v>
@@ -1706,8 +1748,8 @@
       <c r="Q7" s="8">
         <v>0</v>
       </c>
-      <c r="R7" s="8">
-        <v>2</v>
+      <c r="R7" s="12">
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1715,55 +1757,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="L8" s="4">
+        <v>-26.4</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="O8" s="15">
         <v>72</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="L8" s="4">
-        <v>-18.4</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O8" s="6">
-        <v>99</v>
       </c>
       <c r="P8" s="8">
         <v>0</v>
       </c>
-      <c r="Q8" s="15">
-        <v>31</v>
-      </c>
-      <c r="R8" s="9">
-        <v>98</v>
+      <c r="Q8" s="8">
+        <v>1</v>
+      </c>
+      <c r="R8" s="18">
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1771,55 +1813,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>73</v>
+        <v>200</v>
       </c>
       <c r="L9" s="4">
-        <v>-38.6</v>
+        <v>-11.8</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="O9" s="16">
-        <v>38</v>
-      </c>
-      <c r="P9" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>0</v>
-      </c>
-      <c r="R9" s="17">
-        <v>35</v>
+        <v>211</v>
+      </c>
+      <c r="O9" s="15">
+        <v>100</v>
+      </c>
+      <c r="P9" s="9">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="14">
+        <v>43</v>
+      </c>
+      <c r="R9" s="11">
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1827,55 +1869,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>181</v>
+        <v>80</v>
       </c>
       <c r="L10" s="4">
-        <v>-26.4</v>
+        <v>-43.3</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="O10" s="6">
-        <v>83</v>
-      </c>
-      <c r="P10" s="8">
-        <v>0</v>
+        <v>39</v>
+      </c>
+      <c r="P10" s="7">
+        <v>30</v>
       </c>
       <c r="Q10" s="8">
         <v>0</v>
       </c>
-      <c r="R10" s="18">
-        <v>83</v>
+      <c r="R10" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1883,55 +1925,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="L11" s="4">
-        <v>-11.8</v>
+        <v>-33.7</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="O11" s="6">
-        <v>89</v>
-      </c>
-      <c r="P11" s="19">
-        <v>20</v>
-      </c>
-      <c r="Q11" s="18">
-        <v>83</v>
-      </c>
-      <c r="R11" s="10">
-        <v>67</v>
+        <v>37</v>
+      </c>
+      <c r="P11" s="7">
+        <v>29</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>0</v>
+      </c>
+      <c r="R11" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1939,55 +1981,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>76</v>
+        <v>202</v>
       </c>
       <c r="L12" s="4">
-        <v>-43.3</v>
+        <v>-20.2</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="O12" s="6">
-        <v>67</v>
-      </c>
-      <c r="P12" s="20">
-        <v>47</v>
-      </c>
-      <c r="Q12" s="15">
-        <v>32</v>
-      </c>
-      <c r="R12" s="19">
-        <v>20</v>
+        <v>211</v>
+      </c>
+      <c r="O12" s="15">
+        <v>52</v>
+      </c>
+      <c r="P12" s="16">
+        <v>36</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>0</v>
+      </c>
+      <c r="R12" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1995,55 +2037,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
+        <v>23</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L13" s="4">
+        <v>-40</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="O13" s="15">
+        <v>87</v>
+      </c>
+      <c r="P13" s="19">
+        <v>78</v>
+      </c>
+      <c r="Q13" s="20">
+        <v>19</v>
+      </c>
+      <c r="R13" s="21">
         <v>27</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="L13" s="4">
-        <v>-33.8</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="O13" s="6">
-        <v>67</v>
-      </c>
-      <c r="P13" s="21">
-        <v>57</v>
-      </c>
-      <c r="Q13" s="22">
-        <v>26</v>
-      </c>
-      <c r="R13" s="8">
-        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2051,55 +2093,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>63</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="L14" s="4">
-        <v>-20.2</v>
+        <v>-28.1</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O14" s="6">
-        <v>76</v>
-      </c>
-      <c r="P14" s="23">
-        <v>58</v>
-      </c>
-      <c r="Q14" s="12">
-        <v>11</v>
-      </c>
-      <c r="R14" s="8">
-        <v>0</v>
+        <v>212</v>
+      </c>
+      <c r="O14" s="15">
+        <v>89</v>
+      </c>
+      <c r="P14" s="22">
+        <v>87</v>
+      </c>
+      <c r="Q14" s="14">
+        <v>46</v>
+      </c>
+      <c r="R14" s="20">
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2107,55 +2149,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="L15" s="4">
-        <v>-40.1</v>
+        <v>-13.7</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="O15" s="6">
-        <v>97</v>
-      </c>
-      <c r="P15" s="24">
+        <v>211</v>
+      </c>
+      <c r="O15" s="15">
+        <v>93</v>
+      </c>
+      <c r="P15" s="23">
         <v>90</v>
       </c>
-      <c r="Q15" s="18">
-        <v>86</v>
-      </c>
-      <c r="R15" s="8">
-        <v>1</v>
+      <c r="Q15" s="24">
+        <v>74</v>
+      </c>
+      <c r="R15" s="9">
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2163,55 +2205,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>185</v>
+        <v>86</v>
       </c>
       <c r="L16" s="4">
-        <v>-28.2</v>
+        <v>-44.5</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="O16" s="6">
-        <v>98</v>
-      </c>
-      <c r="P16" s="24">
-        <v>92</v>
-      </c>
-      <c r="Q16" s="25">
+        <v>212</v>
+      </c>
+      <c r="O16" s="15">
+        <v>93</v>
+      </c>
+      <c r="P16" s="19">
         <v>82</v>
       </c>
-      <c r="R16" s="19">
-        <v>21</v>
+      <c r="Q16" s="19">
+        <v>81</v>
+      </c>
+      <c r="R16" s="12">
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2219,55 +2261,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>186</v>
+        <v>87</v>
       </c>
       <c r="L17" s="4">
-        <v>-13.7</v>
+        <v>-35.5</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O17" s="6">
-        <v>99</v>
-      </c>
-      <c r="P17" s="26">
-        <v>96</v>
-      </c>
-      <c r="Q17" s="27">
+        <v>212</v>
+      </c>
+      <c r="O17" s="15">
+        <v>86</v>
+      </c>
+      <c r="P17" s="24">
         <v>75</v>
       </c>
-      <c r="R17" s="14">
-        <v>16</v>
+      <c r="Q17" s="20">
+        <v>21</v>
+      </c>
+      <c r="R17" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2275,55 +2317,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="L18" s="4">
+        <v>-22</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="O18" s="15">
+        <v>90</v>
+      </c>
+      <c r="P18" s="25">
         <v>53</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="L18" s="4">
-        <v>-44.5</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="O18" s="6">
-        <v>100</v>
-      </c>
-      <c r="P18" s="28">
-        <v>48</v>
-      </c>
-      <c r="Q18" s="26">
-        <v>94</v>
-      </c>
-      <c r="R18" s="23">
-        <v>58</v>
+      <c r="Q18" s="13">
+        <v>41</v>
+      </c>
+      <c r="R18" s="12">
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2331,55 +2373,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="L19" s="4">
-        <v>-35.5</v>
+        <v>-46.6</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="O19" s="6">
-        <v>100</v>
-      </c>
-      <c r="P19" s="27">
-        <v>74</v>
-      </c>
-      <c r="Q19" s="9">
-        <v>99</v>
-      </c>
-      <c r="R19" s="10">
-        <v>65</v>
+        <v>212</v>
+      </c>
+      <c r="O19" s="15">
+        <v>70</v>
+      </c>
+      <c r="P19" s="16">
+        <v>36</v>
+      </c>
+      <c r="Q19" s="10">
+        <v>58</v>
+      </c>
+      <c r="R19" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2387,55 +2429,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>187</v>
+        <v>90</v>
       </c>
       <c r="L20" s="4">
-        <v>-22</v>
+        <v>-41.5</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O20" s="6">
-        <v>99</v>
-      </c>
-      <c r="P20" s="25">
-        <v>82</v>
-      </c>
-      <c r="Q20" s="24">
-        <v>92</v>
-      </c>
-      <c r="R20" s="12">
-        <v>11</v>
+        <v>212</v>
+      </c>
+      <c r="O20" s="15">
+        <v>90</v>
+      </c>
+      <c r="P20" s="19">
+        <v>78</v>
+      </c>
+      <c r="Q20" s="18">
+        <v>70</v>
+      </c>
+      <c r="R20" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2443,114 +2485,282 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E21" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L21" s="4">
+        <v>-29.9</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="O21" s="15">
+        <v>94</v>
+      </c>
+      <c r="P21" s="23">
+        <v>89</v>
+      </c>
+      <c r="Q21" s="26">
+        <v>65</v>
+      </c>
+      <c r="R21" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
+      <c r="A22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="2">
+        <v>11</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="L22" s="4">
+        <v>-15.5</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="O22" s="15">
         <v>85</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="L21" s="4">
-        <v>-46.6</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="O21" s="6">
+      <c r="P22" s="19">
+        <v>78</v>
+      </c>
+      <c r="Q22" s="25">
+        <v>55</v>
+      </c>
+      <c r="R22" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="A23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="2">
+        <v>11</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="P21" s="18">
-        <v>87</v>
-      </c>
-      <c r="Q21" s="27">
-        <v>75</v>
-      </c>
-      <c r="R21" s="17">
-        <v>33</v>
+      <c r="F23" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="L23" s="4">
+        <v>-46.1</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="O23" s="15">
+        <v>99</v>
+      </c>
+      <c r="P23" s="22">
+        <v>84</v>
+      </c>
+      <c r="Q23" s="16">
+        <v>37</v>
+      </c>
+      <c r="R23" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
+      <c r="A24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="2">
+        <v>26</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L24" s="4">
+        <v>-45.7</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="O24" s="15">
+        <v>97</v>
+      </c>
+      <c r="P24" s="22">
+        <v>86</v>
+      </c>
+      <c r="Q24" s="13">
+        <v>40</v>
+      </c>
+      <c r="R24" s="8">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A21">
+  <conditionalFormatting sqref="A2:A24">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B21">
+  <conditionalFormatting sqref="B2:B24">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C21">
+  <conditionalFormatting sqref="C2:C24">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D21">
+  <conditionalFormatting sqref="D2:D24">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E21">
+  <conditionalFormatting sqref="E2:E24">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F21">
+  <conditionalFormatting sqref="F2:F24">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G21">
+  <conditionalFormatting sqref="G2:G24">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H21">
+  <conditionalFormatting sqref="H2:H24">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I21">
+  <conditionalFormatting sqref="I2:I24">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J21">
+  <conditionalFormatting sqref="J2:J24">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K21">
+  <conditionalFormatting sqref="K2:K24">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L21">
+  <conditionalFormatting sqref="L2:L24">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2569,12 +2779,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M21">
+  <conditionalFormatting sqref="M2:M24">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N21">
+  <conditionalFormatting sqref="N2:N24">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2591,22 +2801,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O21">
+  <conditionalFormatting sqref="O2:O24">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P21">
+  <conditionalFormatting sqref="P2:P24">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q21">
+  <conditionalFormatting sqref="Q2:Q24">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R21">
+  <conditionalFormatting sqref="R2:R24">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261006--01</t>
-  </si>
-  <si>
-    <t>20261006--02</t>
-  </si>
-  <si>
-    <t>20261006--03</t>
-  </si>
-  <si>
     <t>20261007--01</t>
   </si>
   <si>
@@ -139,19 +130,19 @@
     <t>20261012--05</t>
   </si>
   <si>
-    <t>00:16</t>
-  </si>
-  <si>
-    <t>05:32</t>
-  </si>
-  <si>
-    <t>05:53</t>
+    <t>20261013--01</t>
+  </si>
+  <si>
+    <t>20261013--02</t>
+  </si>
+  <si>
+    <t>20261013--03</t>
   </si>
   <si>
     <t>05:06</t>
   </si>
   <si>
-    <t>05:56</t>
+    <t>05:55</t>
   </si>
   <si>
     <t>04:22</t>
@@ -160,484 +151,493 @@
     <t>05:51</t>
   </si>
   <si>
-    <t>05:30</t>
+    <t>05:31</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>05:41</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>05:23</t>
+  </si>
+  <si>
+    <t>05:52</t>
+  </si>
+  <si>
+    <t>04:33</t>
+  </si>
+  <si>
+    <t>04:51</t>
+  </si>
+  <si>
+    <t>05:12</t>
+  </si>
+  <si>
+    <t>03:57</t>
+  </si>
+  <si>
+    <t>05:47</t>
+  </si>
+  <si>
+    <t>05:34</t>
+  </si>
+  <si>
+    <t>01:45</t>
+  </si>
+  <si>
+    <t>02:04</t>
+  </si>
+  <si>
+    <t>05:46</t>
+  </si>
+  <si>
+    <t>03:50</t>
+  </si>
+  <si>
+    <t>05:11</t>
+  </si>
+  <si>
+    <t>00:00</t>
   </si>
   <si>
     <t>02:59</t>
   </si>
   <si>
-    <t>05:42</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>05:23</t>
-  </si>
-  <si>
-    <t>05:52</t>
-  </si>
-  <si>
-    <t>04:33</t>
-  </si>
-  <si>
-    <t>04:51</t>
-  </si>
-  <si>
-    <t>05:11</t>
-  </si>
-  <si>
-    <t>03:57</t>
-  </si>
-  <si>
-    <t>05:47</t>
-  </si>
-  <si>
-    <t>05:33</t>
-  </si>
-  <si>
-    <t>01:46</t>
-  </si>
-  <si>
-    <t>02:03</t>
-  </si>
-  <si>
-    <t>05:34</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>01:11</t>
-  </si>
-  <si>
-    <t>05:16</t>
-  </si>
-  <si>
     <t>00:37</t>
   </si>
   <si>
-    <t>04:20</t>
-  </si>
-  <si>
-    <t>02:06</t>
-  </si>
-  <si>
-    <t>02:53</t>
-  </si>
-  <si>
-    <t>00:45</t>
+    <t>04:21</t>
+  </si>
+  <si>
+    <t>02:07</t>
+  </si>
+  <si>
+    <t>02:54</t>
+  </si>
+  <si>
+    <t>00:46</t>
   </si>
   <si>
     <t>00:07</t>
   </si>
   <si>
-    <t>00:57:28</t>
-  </si>
-  <si>
-    <t>02:32:58</t>
-  </si>
-  <si>
-    <t>04:09:27</t>
-  </si>
-  <si>
     <t>01:40:51</t>
   </si>
   <si>
     <t>03:17:09</t>
   </si>
   <si>
-    <t>00:48:43</t>
+    <t>00:48:44</t>
+  </si>
+  <si>
+    <t>02:24:49</t>
+  </si>
+  <si>
+    <t>04:01:28</t>
+  </si>
+  <si>
+    <t>23:56:41</t>
+  </si>
+  <si>
+    <t>01:32:26</t>
+  </si>
+  <si>
+    <t>03:08:59</t>
+  </si>
+  <si>
+    <t>00:40:02</t>
+  </si>
+  <si>
+    <t>02:16:27</t>
+  </si>
+  <si>
+    <t>03:53:15</t>
+  </si>
+  <si>
+    <t>23:47:38</t>
+  </si>
+  <si>
+    <t>01:23:51</t>
+  </si>
+  <si>
+    <t>03:00:33</t>
+  </si>
+  <si>
+    <t>22:55:16</t>
+  </si>
+  <si>
+    <t>00:31:13</t>
+  </si>
+  <si>
+    <t>02:07:49</t>
+  </si>
+  <si>
+    <t>03:44:52</t>
+  </si>
+  <si>
+    <t>22:02:57</t>
+  </si>
+  <si>
+    <t>23:38:33</t>
+  </si>
+  <si>
+    <t>01:15:02</t>
+  </si>
+  <si>
+    <t>02:51:55</t>
+  </si>
+  <si>
+    <t>22:45:53</t>
+  </si>
+  <si>
+    <t>01:43:15</t>
+  </si>
+  <si>
+    <t>03:19:23</t>
+  </si>
+  <si>
+    <t>00:51:19</t>
+  </si>
+  <si>
+    <t>02:27:03</t>
+  </si>
+  <si>
+    <t>04:03:47</t>
+  </si>
+  <si>
+    <t>23:59:40</t>
+  </si>
+  <si>
+    <t>01:34:42</t>
+  </si>
+  <si>
+    <t>03:11:15</t>
+  </si>
+  <si>
+    <t>00:42:22</t>
+  </si>
+  <si>
+    <t>02:18:40</t>
+  </si>
+  <si>
+    <t>03:55:48</t>
+  </si>
+  <si>
+    <t>23:50:05</t>
+  </si>
+  <si>
+    <t>01:26:05</t>
+  </si>
+  <si>
+    <t>03:02:56</t>
+  </si>
+  <si>
+    <t>22:57:57</t>
+  </si>
+  <si>
+    <t>00:33:27</t>
+  </si>
+  <si>
+    <t>02:10:07</t>
+  </si>
+  <si>
+    <t>03:48:20</t>
+  </si>
+  <si>
+    <t>22:06:16</t>
+  </si>
+  <si>
+    <t>23:40:50</t>
+  </si>
+  <si>
+    <t>01:17:17</t>
+  </si>
+  <si>
+    <t>02:54:39</t>
+  </si>
+  <si>
+    <t>22:48:14</t>
+  </si>
+  <si>
+    <t>01:45:48</t>
+  </si>
+  <si>
+    <t>03:22:20</t>
+  </si>
+  <si>
+    <t>00:53:30</t>
+  </si>
+  <si>
+    <t>02:29:58</t>
+  </si>
+  <si>
+    <t>04:06:33</t>
+  </si>
+  <si>
+    <t>00:01:10</t>
+  </si>
+  <si>
+    <t>01:37:32</t>
+  </si>
+  <si>
+    <t>03:14:07</t>
+  </si>
+  <si>
+    <t>00:45:03</t>
+  </si>
+  <si>
+    <t>02:21:36</t>
+  </si>
+  <si>
+    <t>03:58:04</t>
+  </si>
+  <si>
+    <t>23:52:30</t>
+  </si>
+  <si>
+    <t>01:29:00</t>
+  </si>
+  <si>
+    <t>03:05:32</t>
+  </si>
+  <si>
+    <t>22:59:55</t>
+  </si>
+  <si>
+    <t>00:36:20</t>
+  </si>
+  <si>
+    <t>02:12:54</t>
+  </si>
+  <si>
+    <t>03:49:13</t>
+  </si>
+  <si>
+    <t>22:07:18</t>
+  </si>
+  <si>
+    <t>23:43:36</t>
+  </si>
+  <si>
+    <t>01:20:09</t>
+  </si>
+  <si>
+    <t>02:56:34</t>
+  </si>
+  <si>
+    <t>22:50:49</t>
+  </si>
+  <si>
+    <t>01:48:21</t>
+  </si>
+  <si>
+    <t>03:25:18</t>
+  </si>
+  <si>
+    <t>00:55:41</t>
+  </si>
+  <si>
+    <t>02:32:54</t>
+  </si>
+  <si>
+    <t>04:09:18</t>
+  </si>
+  <si>
+    <t>00:02:40</t>
+  </si>
+  <si>
+    <t>01:40:23</t>
+  </si>
+  <si>
+    <t>03:17:00</t>
+  </si>
+  <si>
+    <t>00:47:45</t>
+  </si>
+  <si>
+    <t>02:24:32</t>
+  </si>
+  <si>
+    <t>04:00:21</t>
+  </si>
+  <si>
+    <t>23:54:56</t>
+  </si>
+  <si>
+    <t>01:31:57</t>
+  </si>
+  <si>
+    <t>03:08:08</t>
+  </si>
+  <si>
+    <t>23:01:54</t>
+  </si>
+  <si>
+    <t>00:39:14</t>
+  </si>
+  <si>
+    <t>02:15:41</t>
+  </si>
+  <si>
+    <t>03:50:05</t>
+  </si>
+  <si>
+    <t>22:08:20</t>
+  </si>
+  <si>
+    <t>23:46:24</t>
+  </si>
+  <si>
+    <t>01:23:03</t>
+  </si>
+  <si>
+    <t>02:58:29</t>
+  </si>
+  <si>
+    <t>22:53:25</t>
+  </si>
+  <si>
+    <t>01:50:46</t>
+  </si>
+  <si>
+    <t>03:27:32</t>
+  </si>
+  <si>
+    <t>00:58:18</t>
+  </si>
+  <si>
+    <t>02:35:09</t>
+  </si>
+  <si>
+    <t>04:11:37</t>
+  </si>
+  <si>
+    <t>00:05:41</t>
+  </si>
+  <si>
+    <t>01:42:40</t>
+  </si>
+  <si>
+    <t>03:19:16</t>
+  </si>
+  <si>
+    <t>00:50:05</t>
+  </si>
+  <si>
+    <t>02:26:46</t>
+  </si>
+  <si>
+    <t>04:02:54</t>
+  </si>
+  <si>
+    <t>23:57:24</t>
+  </si>
+  <si>
+    <t>01:34:11</t>
+  </si>
+  <si>
+    <t>03:10:31</t>
+  </si>
+  <si>
+    <t>23:04:36</t>
+  </si>
+  <si>
+    <t>00:41:29</t>
+  </si>
+  <si>
+    <t>02:17:59</t>
+  </si>
+  <si>
+    <t>03:53:33</t>
+  </si>
+  <si>
+    <t>22:11:40</t>
+  </si>
+  <si>
+    <t>23:48:42</t>
+  </si>
+  <si>
+    <t>01:25:18</t>
+  </si>
+  <si>
+    <t>03:01:14</t>
+  </si>
+  <si>
+    <t>22:55:48</t>
+  </si>
+  <si>
+    <t>4°</t>
+  </si>
+  <si>
+    <t>30°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>14°</t>
+  </si>
+  <si>
+    <t>17°</t>
+  </si>
+  <si>
+    <t>2°</t>
+  </si>
+  <si>
+    <t>25°</t>
+  </si>
+  <si>
+    <t>9°</t>
+  </si>
+  <si>
+    <t>3°</t>
+  </si>
+  <si>
+    <t>10°</t>
+  </si>
+  <si>
+    <t>5°</t>
+  </si>
+  <si>
+    <t>01:49:39</t>
+  </si>
+  <si>
+    <t>03:22:19</t>
+  </si>
+  <si>
+    <t>02:32:17</t>
+  </si>
+  <si>
+    <t>04:04:57</t>
+  </si>
+  <si>
+    <t>01:42:13</t>
+  </si>
+  <si>
+    <t>03:14:53</t>
   </si>
   <si>
     <t>02:24:48</t>
   </si>
   <si>
-    <t>04:01:27</t>
-  </si>
-  <si>
-    <t>23:56:38</t>
-  </si>
-  <si>
-    <t>01:32:24</t>
-  </si>
-  <si>
-    <t>03:08:57</t>
-  </si>
-  <si>
-    <t>00:39:58</t>
-  </si>
-  <si>
-    <t>02:16:23</t>
-  </si>
-  <si>
-    <t>03:53:11</t>
-  </si>
-  <si>
-    <t>23:47:32</t>
-  </si>
-  <si>
-    <t>01:23:45</t>
-  </si>
-  <si>
-    <t>03:00:27</t>
-  </si>
-  <si>
-    <t>22:55:08</t>
-  </si>
-  <si>
-    <t>00:31:05</t>
-  </si>
-  <si>
-    <t>02:07:41</t>
-  </si>
-  <si>
-    <t>03:44:43</t>
-  </si>
-  <si>
-    <t>22:02:47</t>
-  </si>
-  <si>
-    <t>23:38:23</t>
-  </si>
-  <si>
-    <t>01:01:44</t>
-  </si>
-  <si>
-    <t>02:35:17</t>
-  </si>
-  <si>
-    <t>04:11:41</t>
-  </si>
-  <si>
-    <t>01:43:15</t>
-  </si>
-  <si>
-    <t>03:19:22</t>
-  </si>
-  <si>
-    <t>00:51:18</t>
-  </si>
-  <si>
-    <t>02:27:02</t>
-  </si>
-  <si>
-    <t>04:03:46</t>
-  </si>
-  <si>
-    <t>23:59:38</t>
-  </si>
-  <si>
-    <t>01:34:39</t>
-  </si>
-  <si>
-    <t>03:11:12</t>
-  </si>
-  <si>
-    <t>00:42:18</t>
-  </si>
-  <si>
-    <t>02:18:36</t>
-  </si>
-  <si>
-    <t>03:55:44</t>
-  </si>
-  <si>
-    <t>23:49:59</t>
-  </si>
-  <si>
-    <t>01:25:59</t>
-  </si>
-  <si>
-    <t>03:02:51</t>
-  </si>
-  <si>
-    <t>22:57:49</t>
-  </si>
-  <si>
-    <t>00:33:19</t>
-  </si>
-  <si>
-    <t>02:09:59</t>
-  </si>
-  <si>
-    <t>03:48:11</t>
-  </si>
-  <si>
-    <t>22:06:06</t>
-  </si>
-  <si>
-    <t>23:40:39</t>
-  </si>
-  <si>
-    <t>02:38:02</t>
-  </si>
-  <si>
-    <t>04:14:38</t>
-  </si>
-  <si>
-    <t>01:45:47</t>
-  </si>
-  <si>
-    <t>03:22:20</t>
-  </si>
-  <si>
-    <t>00:53:29</t>
-  </si>
-  <si>
-    <t>02:29:57</t>
-  </si>
-  <si>
-    <t>04:06:31</t>
-  </si>
-  <si>
-    <t>00:01:07</t>
-  </si>
-  <si>
-    <t>01:37:30</t>
-  </si>
-  <si>
-    <t>03:14:04</t>
-  </si>
-  <si>
-    <t>00:44:59</t>
-  </si>
-  <si>
-    <t>02:21:32</t>
-  </si>
-  <si>
-    <t>03:58:00</t>
-  </si>
-  <si>
-    <t>23:52:24</t>
-  </si>
-  <si>
-    <t>01:28:54</t>
-  </si>
-  <si>
-    <t>03:05:26</t>
-  </si>
-  <si>
-    <t>22:59:47</t>
-  </si>
-  <si>
-    <t>00:36:12</t>
-  </si>
-  <si>
-    <t>02:12:45</t>
-  </si>
-  <si>
-    <t>03:49:04</t>
-  </si>
-  <si>
-    <t>22:07:07</t>
-  </si>
-  <si>
-    <t>23:43:26</t>
-  </si>
-  <si>
-    <t>01:02:00</t>
-  </si>
-  <si>
-    <t>02:40:49</t>
-  </si>
-  <si>
-    <t>04:17:34</t>
-  </si>
-  <si>
-    <t>01:48:21</t>
-  </si>
-  <si>
-    <t>03:25:18</t>
-  </si>
-  <si>
-    <t>00:55:40</t>
-  </si>
-  <si>
-    <t>02:32:53</t>
-  </si>
-  <si>
-    <t>04:09:16</t>
-  </si>
-  <si>
-    <t>00:02:37</t>
-  </si>
-  <si>
-    <t>01:40:21</t>
-  </si>
-  <si>
-    <t>03:16:57</t>
-  </si>
-  <si>
-    <t>00:47:41</t>
-  </si>
-  <si>
-    <t>02:24:28</t>
-  </si>
-  <si>
-    <t>04:00:17</t>
-  </si>
-  <si>
-    <t>23:54:50</t>
-  </si>
-  <si>
-    <t>01:31:51</t>
-  </si>
-  <si>
-    <t>03:08:02</t>
-  </si>
-  <si>
-    <t>23:01:46</t>
-  </si>
-  <si>
-    <t>00:39:06</t>
-  </si>
-  <si>
-    <t>02:15:32</t>
-  </si>
-  <si>
-    <t>03:49:57</t>
-  </si>
-  <si>
-    <t>22:08:09</t>
-  </si>
-  <si>
-    <t>23:46:13</t>
-  </si>
-  <si>
-    <t>01:06:01</t>
-  </si>
-  <si>
-    <t>02:43:09</t>
-  </si>
-  <si>
-    <t>04:19:49</t>
-  </si>
-  <si>
-    <t>01:50:46</t>
-  </si>
-  <si>
-    <t>03:27:32</t>
-  </si>
-  <si>
-    <t>00:58:16</t>
-  </si>
-  <si>
-    <t>02:35:08</t>
-  </si>
-  <si>
-    <t>04:11:36</t>
-  </si>
-  <si>
-    <t>00:05:38</t>
-  </si>
-  <si>
-    <t>01:42:38</t>
-  </si>
-  <si>
-    <t>03:19:13</t>
-  </si>
-  <si>
-    <t>00:50:01</t>
-  </si>
-  <si>
-    <t>02:26:42</t>
-  </si>
-  <si>
-    <t>04:02:50</t>
-  </si>
-  <si>
-    <t>23:57:19</t>
-  </si>
-  <si>
-    <t>01:34:05</t>
-  </si>
-  <si>
-    <t>03:10:25</t>
-  </si>
-  <si>
-    <t>23:04:28</t>
-  </si>
-  <si>
-    <t>00:41:21</t>
-  </si>
-  <si>
-    <t>02:17:50</t>
-  </si>
-  <si>
-    <t>03:53:25</t>
-  </si>
-  <si>
-    <t>22:11:29</t>
-  </si>
-  <si>
-    <t>23:48:31</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>17°</t>
-  </si>
-  <si>
-    <t>14°</t>
-  </si>
-  <si>
-    <t>4°</t>
-  </si>
-  <si>
-    <t>30°</t>
-  </si>
-  <si>
-    <t>2°</t>
-  </si>
-  <si>
-    <t>25°</t>
-  </si>
-  <si>
-    <t>9°</t>
-  </si>
-  <si>
-    <t>10°</t>
-  </si>
-  <si>
-    <t>02:39:38</t>
-  </si>
-  <si>
-    <t>04:12:18</t>
-  </si>
-  <si>
-    <t>01:49:39</t>
-  </si>
-  <si>
-    <t>03:22:19</t>
-  </si>
-  <si>
-    <t>02:32:16</t>
-  </si>
-  <si>
-    <t>04:04:56</t>
-  </si>
-  <si>
-    <t>01:42:11</t>
-  </si>
-  <si>
-    <t>03:14:51</t>
-  </si>
-  <si>
-    <t>02:24:44</t>
-  </si>
-  <si>
-    <t>03:57:24</t>
-  </si>
-  <si>
-    <t>03:07:17</t>
-  </si>
-  <si>
-    <t>02:17:10</t>
-  </si>
-  <si>
-    <t>03:49:50</t>
+    <t>03:57:27</t>
+  </si>
+  <si>
+    <t>03:07:22</t>
+  </si>
+  <si>
+    <t>02:17:18</t>
+  </si>
+  <si>
+    <t>03:49:58</t>
+  </si>
+  <si>
+    <t>02:59:55</t>
   </si>
   <si>
     <t>B</t>
@@ -646,13 +646,13 @@
     <t>A+B</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
 </sst>
 </file>
@@ -701,13 +701,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -719,7 +719,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -731,7 +755,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -743,85 +815,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1421,37 +1421,37 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>41</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>72</v>
+        <v>196</v>
       </c>
       <c r="L2" s="4">
-        <v>-37.1</v>
+        <v>-32.1</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>208</v>
@@ -1460,16 +1460,16 @@
         <v>210</v>
       </c>
       <c r="O2" s="6">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="P2" s="7">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
       </c>
-      <c r="R2" s="9">
-        <v>3</v>
+      <c r="R2" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1477,37 +1477,37 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L3" s="4">
-        <v>-24.7</v>
+        <v>-18.4</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>209</v>
@@ -1515,17 +1515,17 @@
       <c r="N3" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="O3" s="6">
-        <v>23</v>
+      <c r="O3" s="9">
+        <v>50</v>
       </c>
       <c r="P3" s="10">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
       </c>
-      <c r="R3" s="9">
-        <v>6</v>
+      <c r="R3" s="11">
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1533,55 +1533,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>196</v>
+        <v>72</v>
       </c>
       <c r="L4" s="4">
-        <v>-10.1</v>
+        <v>-38.5</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O4" s="6">
-        <v>42</v>
-      </c>
-      <c r="P4" s="11">
-        <v>100</v>
+        <v>210</v>
+      </c>
+      <c r="O4" s="9">
+        <v>71</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0</v>
       </c>
       <c r="Q4" s="8">
         <v>0</v>
       </c>
       <c r="R4" s="12">
-        <v>9</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1589,55 +1589,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L5" s="4">
-        <v>-32.1</v>
+        <v>-26.4</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O5" s="6">
-        <v>47</v>
+        <v>211</v>
+      </c>
+      <c r="O5" s="9">
+        <v>64</v>
       </c>
       <c r="P5" s="8">
         <v>0</v>
       </c>
       <c r="Q5" s="13">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="R5" s="14">
-        <v>43</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1645,37 +1645,37 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L6" s="4">
-        <v>-18.4</v>
+        <v>-11.8</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>209</v>
@@ -1683,17 +1683,17 @@
       <c r="N6" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="O6" s="15">
+      <c r="O6" s="9">
         <v>100</v>
       </c>
       <c r="P6" s="8">
         <v>0</v>
       </c>
-      <c r="Q6" s="16">
-        <v>35</v>
-      </c>
-      <c r="R6" s="11">
-        <v>99</v>
+      <c r="Q6" s="15">
+        <v>53</v>
+      </c>
+      <c r="R6" s="16">
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1701,37 +1701,37 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L7" s="4">
-        <v>-38.5</v>
+        <v>-43.3</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>208</v>
@@ -1739,17 +1739,17 @@
       <c r="N7" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="O7" s="17">
-        <v>8</v>
-      </c>
-      <c r="P7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>0</v>
-      </c>
-      <c r="R7" s="12">
-        <v>8</v>
+      <c r="O7" s="9">
+        <v>94</v>
+      </c>
+      <c r="P7" s="17">
+        <v>51</v>
+      </c>
+      <c r="Q7" s="18">
+        <v>20</v>
+      </c>
+      <c r="R7" s="19">
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1757,55 +1757,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L8" s="4">
-        <v>-26.4</v>
+        <v>-33.7</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O8" s="15">
+        <v>210</v>
+      </c>
+      <c r="O8" s="9">
         <v>72</v>
       </c>
-      <c r="P8" s="8">
+      <c r="P8" s="17">
+        <v>52</v>
+      </c>
+      <c r="Q8" s="8">
         <v>0</v>
       </c>
-      <c r="Q8" s="8">
-        <v>1</v>
-      </c>
-      <c r="R8" s="18">
-        <v>71</v>
+      <c r="R8" s="15">
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1813,37 +1813,37 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L9" s="4">
-        <v>-11.8</v>
+        <v>-20.2</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>209</v>
@@ -1851,17 +1851,17 @@
       <c r="N9" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="O9" s="15">
-        <v>100</v>
-      </c>
-      <c r="P9" s="9">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="14">
-        <v>43</v>
-      </c>
-      <c r="R9" s="11">
-        <v>100</v>
+      <c r="O9" s="9">
+        <v>49</v>
+      </c>
+      <c r="P9" s="20">
+        <v>45</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>0</v>
+      </c>
+      <c r="R9" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1869,37 +1869,37 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L10" s="4">
-        <v>-43.3</v>
+        <v>-40</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>208</v>
@@ -1907,14 +1907,14 @@
       <c r="N10" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="O10" s="6">
-        <v>39</v>
-      </c>
-      <c r="P10" s="7">
-        <v>30</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>0</v>
+      <c r="O10" s="9">
+        <v>100</v>
+      </c>
+      <c r="P10" s="19">
+        <v>79</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>96</v>
       </c>
       <c r="R10" s="8">
         <v>0</v>
@@ -1925,52 +1925,52 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L11" s="4">
-        <v>-33.7</v>
+        <v>-28.1</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>208</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O11" s="6">
-        <v>37</v>
-      </c>
-      <c r="P11" s="7">
-        <v>29</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>0</v>
+        <v>210</v>
+      </c>
+      <c r="O11" s="9">
+        <v>98</v>
+      </c>
+      <c r="P11" s="14">
+        <v>61</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>94</v>
       </c>
       <c r="R11" s="8">
         <v>0</v>
@@ -1981,37 +1981,37 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L12" s="4">
-        <v>-20.2</v>
+        <v>-13.7</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>209</v>
@@ -2019,17 +2019,17 @@
       <c r="N12" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="O12" s="15">
-        <v>52</v>
-      </c>
-      <c r="P12" s="16">
-        <v>36</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>0</v>
-      </c>
-      <c r="R12" s="8">
-        <v>0</v>
+      <c r="O12" s="9">
+        <v>98</v>
+      </c>
+      <c r="P12" s="21">
+        <v>88</v>
+      </c>
+      <c r="Q12" s="21">
+        <v>92</v>
+      </c>
+      <c r="R12" s="7">
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2037,55 +2037,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="L13" s="4">
-        <v>-40</v>
+        <v>-44.5</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>208</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O13" s="15">
-        <v>87</v>
-      </c>
-      <c r="P13" s="19">
-        <v>78</v>
-      </c>
-      <c r="Q13" s="20">
-        <v>19</v>
-      </c>
-      <c r="R13" s="21">
-        <v>27</v>
+        <v>210</v>
+      </c>
+      <c r="O13" s="9">
+        <v>57</v>
+      </c>
+      <c r="P13" s="15">
+        <v>55</v>
+      </c>
+      <c r="Q13" s="18">
+        <v>21</v>
+      </c>
+      <c r="R13" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2096,52 +2096,52 @@
         <v>30</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>203</v>
+        <v>82</v>
       </c>
       <c r="L14" s="4">
-        <v>-28.1</v>
+        <v>-35.5</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>208</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O14" s="15">
-        <v>89</v>
-      </c>
-      <c r="P14" s="22">
-        <v>87</v>
-      </c>
-      <c r="Q14" s="14">
-        <v>46</v>
-      </c>
-      <c r="R14" s="20">
-        <v>20</v>
+        <v>210</v>
+      </c>
+      <c r="O14" s="9">
+        <v>43</v>
+      </c>
+      <c r="P14" s="20">
+        <v>43</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>0</v>
+      </c>
+      <c r="R14" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2149,37 +2149,37 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>204</v>
       </c>
       <c r="L15" s="4">
-        <v>-13.7</v>
+        <v>-22</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>209</v>
@@ -2187,17 +2187,17 @@
       <c r="N15" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="O15" s="15">
-        <v>93</v>
-      </c>
-      <c r="P15" s="23">
-        <v>90</v>
-      </c>
-      <c r="Q15" s="24">
-        <v>74</v>
-      </c>
-      <c r="R15" s="9">
-        <v>5</v>
+      <c r="O15" s="22">
+        <v>18</v>
+      </c>
+      <c r="P15" s="13">
+        <v>15</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>0</v>
+      </c>
+      <c r="R15" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2205,55 +2205,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L16" s="4">
-        <v>-44.5</v>
+        <v>-46.6</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>208</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O16" s="15">
-        <v>93</v>
-      </c>
-      <c r="P16" s="19">
-        <v>82</v>
-      </c>
-      <c r="Q16" s="19">
-        <v>81</v>
-      </c>
-      <c r="R16" s="12">
-        <v>10</v>
+        <v>210</v>
+      </c>
+      <c r="O16" s="9">
+        <v>79</v>
+      </c>
+      <c r="P16" s="15">
+        <v>53</v>
+      </c>
+      <c r="Q16" s="15">
+        <v>55</v>
+      </c>
+      <c r="R16" s="23">
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2261,55 +2261,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="L17" s="4">
-        <v>-35.5</v>
+        <v>-41.5</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>208</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O17" s="15">
-        <v>86</v>
-      </c>
-      <c r="P17" s="24">
-        <v>75</v>
-      </c>
-      <c r="Q17" s="20">
-        <v>21</v>
-      </c>
-      <c r="R17" s="8">
-        <v>0</v>
+        <v>210</v>
+      </c>
+      <c r="O17" s="9">
+        <v>96</v>
+      </c>
+      <c r="P17" s="11">
+        <v>93</v>
+      </c>
+      <c r="Q17" s="10">
+        <v>41</v>
+      </c>
+      <c r="R17" s="13">
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2317,55 +2317,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="K18" s="1" t="s">
         <v>205</v>
       </c>
       <c r="L18" s="4">
-        <v>-22</v>
+        <v>-29.9</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O18" s="15">
-        <v>90</v>
-      </c>
-      <c r="P18" s="25">
-        <v>53</v>
-      </c>
-      <c r="Q18" s="13">
-        <v>41</v>
-      </c>
-      <c r="R18" s="12">
-        <v>11</v>
+        <v>210</v>
+      </c>
+      <c r="O18" s="9">
+        <v>95</v>
+      </c>
+      <c r="P18" s="11">
+        <v>93</v>
+      </c>
+      <c r="Q18" s="7">
+        <v>23</v>
+      </c>
+      <c r="R18" s="13">
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2373,55 +2373,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>89</v>
+        <v>206</v>
       </c>
       <c r="L19" s="4">
-        <v>-46.6</v>
+        <v>-15.5</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N19" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="O19" s="15">
-        <v>70</v>
-      </c>
-      <c r="P19" s="16">
-        <v>36</v>
-      </c>
-      <c r="Q19" s="10">
-        <v>58</v>
-      </c>
-      <c r="R19" s="8">
-        <v>1</v>
+      <c r="O19" s="9">
+        <v>95</v>
+      </c>
+      <c r="P19" s="11">
+        <v>93</v>
+      </c>
+      <c r="Q19" s="24">
+        <v>12</v>
+      </c>
+      <c r="R19" s="23">
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2429,37 +2429,37 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L20" s="4">
-        <v>-41.5</v>
+        <v>-46.1</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>208</v>
@@ -2467,17 +2467,17 @@
       <c r="N20" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="O20" s="15">
-        <v>90</v>
-      </c>
-      <c r="P20" s="19">
-        <v>78</v>
-      </c>
-      <c r="Q20" s="18">
-        <v>70</v>
+      <c r="O20" s="9">
+        <v>80</v>
+      </c>
+      <c r="P20" s="25">
+        <v>76</v>
+      </c>
+      <c r="Q20" s="23">
+        <v>5</v>
       </c>
       <c r="R20" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2485,55 +2485,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>206</v>
+        <v>89</v>
       </c>
       <c r="L21" s="4">
-        <v>-29.9</v>
+        <v>-45.7</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>208</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O21" s="15">
-        <v>94</v>
-      </c>
-      <c r="P21" s="23">
-        <v>89</v>
-      </c>
-      <c r="Q21" s="26">
-        <v>65</v>
-      </c>
-      <c r="R21" s="12">
-        <v>8</v>
+        <v>210</v>
+      </c>
+      <c r="O21" s="9">
+        <v>81</v>
+      </c>
+      <c r="P21" s="25">
+        <v>77</v>
+      </c>
+      <c r="Q21" s="23">
+        <v>4</v>
+      </c>
+      <c r="R21" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2541,55 +2541,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>207</v>
+        <v>90</v>
       </c>
       <c r="L22" s="4">
-        <v>-15.5</v>
+        <v>-37.1</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="N22" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="O22" s="15">
-        <v>85</v>
+      <c r="O22" s="9">
+        <v>82</v>
       </c>
       <c r="P22" s="19">
-        <v>78</v>
-      </c>
-      <c r="Q22" s="25">
-        <v>55</v>
-      </c>
-      <c r="R22" s="12">
-        <v>8</v>
+        <v>80</v>
+      </c>
+      <c r="Q22" s="8">
+        <v>0</v>
+      </c>
+      <c r="R22" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2597,37 +2597,37 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>93</v>
+        <v>207</v>
       </c>
       <c r="L23" s="4">
-        <v>-46.1</v>
+        <v>-23.8</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>208</v>
@@ -2635,17 +2635,17 @@
       <c r="N23" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="O23" s="15">
-        <v>99</v>
-      </c>
-      <c r="P23" s="22">
+      <c r="O23" s="9">
         <v>84</v>
       </c>
-      <c r="Q23" s="16">
-        <v>37</v>
-      </c>
-      <c r="R23" s="9">
-        <v>4</v>
+      <c r="P23" s="26">
+        <v>84</v>
+      </c>
+      <c r="Q23" s="8">
+        <v>0</v>
+      </c>
+      <c r="R23" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2653,55 +2653,55 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="E24" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L24" s="4">
-        <v>-45.7</v>
+        <v>-47.4</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>208</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O24" s="15">
-        <v>97</v>
-      </c>
-      <c r="P24" s="22">
-        <v>86</v>
-      </c>
-      <c r="Q24" s="13">
-        <v>40</v>
-      </c>
-      <c r="R24" s="8">
+        <v>210</v>
+      </c>
+      <c r="O24" s="9">
+        <v>59</v>
+      </c>
+      <c r="P24" s="8">
         <v>2</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>0</v>
+      </c>
+      <c r="R24" s="14">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="220">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261007--01</t>
-  </si>
-  <si>
-    <t>20261007--02</t>
-  </si>
-  <si>
     <t>20261008--01</t>
   </si>
   <si>
@@ -139,16 +133,22 @@
     <t>20261013--03</t>
   </si>
   <si>
-    <t>05:06</t>
-  </si>
-  <si>
-    <t>05:55</t>
+    <t>20261014--01</t>
+  </si>
+  <si>
+    <t>20261014--02</t>
+  </si>
+  <si>
+    <t>20261014--03</t>
+  </si>
+  <si>
+    <t>20261014--04</t>
   </si>
   <si>
     <t>04:22</t>
   </si>
   <si>
-    <t>05:51</t>
+    <t>05:52</t>
   </si>
   <si>
     <t>05:31</t>
@@ -157,7 +157,7 @@
     <t>03:00</t>
   </si>
   <si>
-    <t>05:41</t>
+    <t>05:42</t>
   </si>
   <si>
     <t>05:45</t>
@@ -166,48 +166,51 @@
     <t>05:23</t>
   </si>
   <si>
-    <t>05:52</t>
+    <t>04:34</t>
+  </si>
+  <si>
+    <t>04:52</t>
+  </si>
+  <si>
+    <t>05:12</t>
+  </si>
+  <si>
+    <t>03:58</t>
+  </si>
+  <si>
+    <t>05:47</t>
+  </si>
+  <si>
+    <t>05:34</t>
+  </si>
+  <si>
+    <t>01:44</t>
+  </si>
+  <si>
+    <t>02:06</t>
+  </si>
+  <si>
+    <t>05:46</t>
+  </si>
+  <si>
+    <t>03:49</t>
+  </si>
+  <si>
+    <t>05:50</t>
+  </si>
+  <si>
+    <t>04:46</t>
   </si>
   <si>
     <t>04:33</t>
   </si>
   <si>
-    <t>04:51</t>
-  </si>
-  <si>
-    <t>05:12</t>
-  </si>
-  <si>
-    <t>03:57</t>
-  </si>
-  <si>
-    <t>05:47</t>
-  </si>
-  <si>
-    <t>05:34</t>
-  </si>
-  <si>
-    <t>01:45</t>
-  </si>
-  <si>
-    <t>02:04</t>
-  </si>
-  <si>
-    <t>05:46</t>
-  </si>
-  <si>
-    <t>03:50</t>
-  </si>
-  <si>
-    <t>05:11</t>
+    <t>05:49</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>02:59</t>
-  </si>
-  <si>
     <t>00:37</t>
   </si>
   <si>
@@ -217,7 +220,7 @@
     <t>02:07</t>
   </si>
   <si>
-    <t>02:54</t>
+    <t>02:55</t>
   </si>
   <si>
     <t>00:46</t>
@@ -226,355 +229,379 @@
     <t>00:07</t>
   </si>
   <si>
-    <t>01:40:51</t>
-  </si>
-  <si>
-    <t>03:17:09</t>
-  </si>
-  <si>
-    <t>00:48:44</t>
-  </si>
-  <si>
-    <t>02:24:49</t>
-  </si>
-  <si>
-    <t>04:01:28</t>
-  </si>
-  <si>
-    <t>23:56:41</t>
-  </si>
-  <si>
-    <t>01:32:26</t>
-  </si>
-  <si>
-    <t>03:08:59</t>
-  </si>
-  <si>
-    <t>00:40:02</t>
-  </si>
-  <si>
-    <t>02:16:27</t>
-  </si>
-  <si>
-    <t>03:53:15</t>
-  </si>
-  <si>
-    <t>23:47:38</t>
-  </si>
-  <si>
-    <t>01:23:51</t>
-  </si>
-  <si>
-    <t>03:00:33</t>
-  </si>
-  <si>
-    <t>22:55:16</t>
-  </si>
-  <si>
-    <t>00:31:13</t>
-  </si>
-  <si>
-    <t>02:07:49</t>
-  </si>
-  <si>
-    <t>03:44:52</t>
-  </si>
-  <si>
-    <t>22:02:57</t>
-  </si>
-  <si>
-    <t>23:38:33</t>
-  </si>
-  <si>
-    <t>01:15:02</t>
-  </si>
-  <si>
-    <t>02:51:55</t>
-  </si>
-  <si>
-    <t>22:45:53</t>
-  </si>
-  <si>
-    <t>01:43:15</t>
-  </si>
-  <si>
-    <t>03:19:23</t>
-  </si>
-  <si>
-    <t>00:51:19</t>
+    <t>00:48:45</t>
+  </si>
+  <si>
+    <t>02:24:50</t>
+  </si>
+  <si>
+    <t>04:01:29</t>
+  </si>
+  <si>
+    <t>23:56:43</t>
+  </si>
+  <si>
+    <t>01:32:28</t>
+  </si>
+  <si>
+    <t>03:09:02</t>
+  </si>
+  <si>
+    <t>00:40:07</t>
+  </si>
+  <si>
+    <t>02:16:32</t>
+  </si>
+  <si>
+    <t>03:53:20</t>
+  </si>
+  <si>
+    <t>23:47:46</t>
+  </si>
+  <si>
+    <t>01:24:00</t>
+  </si>
+  <si>
+    <t>03:00:42</t>
+  </si>
+  <si>
+    <t>22:55:28</t>
+  </si>
+  <si>
+    <t>00:31:26</t>
+  </si>
+  <si>
+    <t>02:08:02</t>
+  </si>
+  <si>
+    <t>03:45:05</t>
+  </si>
+  <si>
+    <t>22:03:14</t>
+  </si>
+  <si>
+    <t>23:38:51</t>
+  </si>
+  <si>
+    <t>01:15:21</t>
+  </si>
+  <si>
+    <t>02:52:13</t>
+  </si>
+  <si>
+    <t>22:46:16</t>
+  </si>
+  <si>
+    <t>00:22:36</t>
+  </si>
+  <si>
+    <t>01:59:22</t>
+  </si>
+  <si>
+    <t>21:53:43</t>
+  </si>
+  <si>
+    <t>23:29:50</t>
+  </si>
+  <si>
+    <t>00:51:20</t>
   </si>
   <si>
     <t>02:27:03</t>
   </si>
   <si>
-    <t>04:03:47</t>
-  </si>
-  <si>
-    <t>23:59:40</t>
-  </si>
-  <si>
-    <t>01:34:42</t>
-  </si>
-  <si>
-    <t>03:11:15</t>
-  </si>
-  <si>
-    <t>00:42:22</t>
-  </si>
-  <si>
-    <t>02:18:40</t>
-  </si>
-  <si>
-    <t>03:55:48</t>
-  </si>
-  <si>
-    <t>23:50:05</t>
-  </si>
-  <si>
-    <t>01:26:05</t>
-  </si>
-  <si>
-    <t>03:02:56</t>
-  </si>
-  <si>
-    <t>22:57:57</t>
-  </si>
-  <si>
-    <t>00:33:27</t>
-  </si>
-  <si>
-    <t>02:10:07</t>
-  </si>
-  <si>
-    <t>03:48:20</t>
-  </si>
-  <si>
-    <t>22:06:16</t>
-  </si>
-  <si>
-    <t>23:40:50</t>
-  </si>
-  <si>
-    <t>01:17:17</t>
-  </si>
-  <si>
-    <t>02:54:39</t>
-  </si>
-  <si>
-    <t>22:48:14</t>
-  </si>
-  <si>
-    <t>01:45:48</t>
-  </si>
-  <si>
-    <t>03:22:20</t>
-  </si>
-  <si>
-    <t>00:53:30</t>
-  </si>
-  <si>
-    <t>02:29:58</t>
+    <t>04:03:48</t>
+  </si>
+  <si>
+    <t>23:59:42</t>
+  </si>
+  <si>
+    <t>01:34:44</t>
+  </si>
+  <si>
+    <t>03:11:17</t>
+  </si>
+  <si>
+    <t>00:42:27</t>
+  </si>
+  <si>
+    <t>02:18:45</t>
+  </si>
+  <si>
+    <t>03:55:53</t>
+  </si>
+  <si>
+    <t>23:50:13</t>
+  </si>
+  <si>
+    <t>01:26:13</t>
+  </si>
+  <si>
+    <t>03:03:05</t>
+  </si>
+  <si>
+    <t>22:58:09</t>
+  </si>
+  <si>
+    <t>00:33:40</t>
+  </si>
+  <si>
+    <t>02:10:20</t>
+  </si>
+  <si>
+    <t>03:48:34</t>
+  </si>
+  <si>
+    <t>22:06:32</t>
+  </si>
+  <si>
+    <t>23:41:08</t>
+  </si>
+  <si>
+    <t>01:17:35</t>
+  </si>
+  <si>
+    <t>02:54:58</t>
+  </si>
+  <si>
+    <t>22:48:38</t>
+  </si>
+  <si>
+    <t>00:24:50</t>
+  </si>
+  <si>
+    <t>02:01:51</t>
+  </si>
+  <si>
+    <t>21:56:14</t>
+  </si>
+  <si>
+    <t>23:32:04</t>
+  </si>
+  <si>
+    <t>00:53:31</t>
+  </si>
+  <si>
+    <t>02:29:59</t>
   </si>
   <si>
     <t>04:06:33</t>
   </si>
   <si>
-    <t>00:01:10</t>
-  </si>
-  <si>
-    <t>01:37:32</t>
-  </si>
-  <si>
-    <t>03:14:07</t>
-  </si>
-  <si>
-    <t>00:45:03</t>
-  </si>
-  <si>
-    <t>02:21:36</t>
-  </si>
-  <si>
-    <t>03:58:04</t>
-  </si>
-  <si>
-    <t>23:52:30</t>
-  </si>
-  <si>
-    <t>01:29:00</t>
-  </si>
-  <si>
-    <t>03:05:32</t>
-  </si>
-  <si>
-    <t>22:59:55</t>
-  </si>
-  <si>
-    <t>00:36:20</t>
-  </si>
-  <si>
-    <t>02:12:54</t>
-  </si>
-  <si>
-    <t>03:49:13</t>
-  </si>
-  <si>
-    <t>22:07:18</t>
-  </si>
-  <si>
-    <t>23:43:36</t>
-  </si>
-  <si>
-    <t>01:20:09</t>
-  </si>
-  <si>
-    <t>02:56:34</t>
-  </si>
-  <si>
-    <t>22:50:49</t>
-  </si>
-  <si>
-    <t>01:48:21</t>
-  </si>
-  <si>
-    <t>03:25:18</t>
-  </si>
-  <si>
-    <t>00:55:41</t>
-  </si>
-  <si>
-    <t>02:32:54</t>
-  </si>
-  <si>
-    <t>04:09:18</t>
-  </si>
-  <si>
-    <t>00:02:40</t>
-  </si>
-  <si>
-    <t>01:40:23</t>
-  </si>
-  <si>
-    <t>03:17:00</t>
-  </si>
-  <si>
-    <t>00:47:45</t>
-  </si>
-  <si>
-    <t>02:24:32</t>
-  </si>
-  <si>
-    <t>04:00:21</t>
-  </si>
-  <si>
-    <t>23:54:56</t>
-  </si>
-  <si>
-    <t>01:31:57</t>
-  </si>
-  <si>
-    <t>03:08:08</t>
-  </si>
-  <si>
-    <t>23:01:54</t>
-  </si>
-  <si>
-    <t>00:39:14</t>
-  </si>
-  <si>
-    <t>02:15:41</t>
-  </si>
-  <si>
-    <t>03:50:05</t>
-  </si>
-  <si>
-    <t>22:08:20</t>
-  </si>
-  <si>
-    <t>23:46:24</t>
-  </si>
-  <si>
-    <t>01:23:03</t>
-  </si>
-  <si>
-    <t>02:58:29</t>
-  </si>
-  <si>
-    <t>22:53:25</t>
-  </si>
-  <si>
-    <t>01:50:46</t>
-  </si>
-  <si>
-    <t>03:27:32</t>
+    <t>00:01:12</t>
+  </si>
+  <si>
+    <t>01:37:35</t>
+  </si>
+  <si>
+    <t>03:14:09</t>
+  </si>
+  <si>
+    <t>00:45:08</t>
+  </si>
+  <si>
+    <t>02:21:41</t>
+  </si>
+  <si>
+    <t>03:58:10</t>
+  </si>
+  <si>
+    <t>23:52:38</t>
+  </si>
+  <si>
+    <t>01:29:09</t>
+  </si>
+  <si>
+    <t>03:05:41</t>
+  </si>
+  <si>
+    <t>23:00:07</t>
+  </si>
+  <si>
+    <t>00:36:33</t>
+  </si>
+  <si>
+    <t>02:13:06</t>
+  </si>
+  <si>
+    <t>03:49:26</t>
+  </si>
+  <si>
+    <t>22:07:35</t>
+  </si>
+  <si>
+    <t>23:43:54</t>
+  </si>
+  <si>
+    <t>01:20:28</t>
+  </si>
+  <si>
+    <t>02:56:53</t>
+  </si>
+  <si>
+    <t>22:51:13</t>
+  </si>
+  <si>
+    <t>00:27:45</t>
+  </si>
+  <si>
+    <t>02:04:14</t>
+  </si>
+  <si>
+    <t>21:58:30</t>
+  </si>
+  <si>
+    <t>23:34:58</t>
+  </si>
+  <si>
+    <t>00:55:42</t>
+  </si>
+  <si>
+    <t>02:32:55</t>
+  </si>
+  <si>
+    <t>04:09:19</t>
+  </si>
+  <si>
+    <t>00:02:42</t>
+  </si>
+  <si>
+    <t>01:40:26</t>
+  </si>
+  <si>
+    <t>03:17:02</t>
+  </si>
+  <si>
+    <t>00:47:50</t>
+  </si>
+  <si>
+    <t>02:24:37</t>
+  </si>
+  <si>
+    <t>04:00:27</t>
+  </si>
+  <si>
+    <t>23:55:05</t>
+  </si>
+  <si>
+    <t>01:32:05</t>
+  </si>
+  <si>
+    <t>03:08:17</t>
+  </si>
+  <si>
+    <t>23:02:07</t>
+  </si>
+  <si>
+    <t>00:39:27</t>
+  </si>
+  <si>
+    <t>02:15:54</t>
+  </si>
+  <si>
+    <t>03:50:18</t>
+  </si>
+  <si>
+    <t>22:08:38</t>
+  </si>
+  <si>
+    <t>23:46:42</t>
+  </si>
+  <si>
+    <t>01:23:21</t>
+  </si>
+  <si>
+    <t>02:58:47</t>
+  </si>
+  <si>
+    <t>22:53:50</t>
+  </si>
+  <si>
+    <t>00:30:40</t>
+  </si>
+  <si>
+    <t>02:06:37</t>
+  </si>
+  <si>
+    <t>22:00:47</t>
+  </si>
+  <si>
+    <t>23:37:53</t>
   </si>
   <si>
     <t>00:58:18</t>
   </si>
   <si>
-    <t>02:35:09</t>
-  </si>
-  <si>
-    <t>04:11:37</t>
-  </si>
-  <si>
-    <t>00:05:41</t>
-  </si>
-  <si>
-    <t>01:42:40</t>
-  </si>
-  <si>
-    <t>03:19:16</t>
-  </si>
-  <si>
-    <t>00:50:05</t>
-  </si>
-  <si>
-    <t>02:26:46</t>
-  </si>
-  <si>
-    <t>04:02:54</t>
-  </si>
-  <si>
-    <t>23:57:24</t>
-  </si>
-  <si>
-    <t>01:34:11</t>
-  </si>
-  <si>
-    <t>03:10:31</t>
-  </si>
-  <si>
-    <t>23:04:36</t>
-  </si>
-  <si>
-    <t>00:41:29</t>
-  </si>
-  <si>
-    <t>02:17:59</t>
-  </si>
-  <si>
-    <t>03:53:33</t>
-  </si>
-  <si>
-    <t>22:11:40</t>
-  </si>
-  <si>
-    <t>23:48:42</t>
-  </si>
-  <si>
-    <t>01:25:18</t>
-  </si>
-  <si>
-    <t>03:01:14</t>
-  </si>
-  <si>
-    <t>22:55:48</t>
-  </si>
-  <si>
-    <t>4°</t>
-  </si>
-  <si>
-    <t>30°</t>
+    <t>02:35:10</t>
+  </si>
+  <si>
+    <t>04:11:38</t>
+  </si>
+  <si>
+    <t>00:05:43</t>
+  </si>
+  <si>
+    <t>01:42:43</t>
+  </si>
+  <si>
+    <t>03:19:18</t>
+  </si>
+  <si>
+    <t>00:50:10</t>
+  </si>
+  <si>
+    <t>02:26:52</t>
+  </si>
+  <si>
+    <t>04:03:00</t>
+  </si>
+  <si>
+    <t>23:57:33</t>
+  </si>
+  <si>
+    <t>01:34:20</t>
+  </si>
+  <si>
+    <t>03:10:40</t>
+  </si>
+  <si>
+    <t>23:04:49</t>
+  </si>
+  <si>
+    <t>00:41:42</t>
+  </si>
+  <si>
+    <t>02:18:12</t>
+  </si>
+  <si>
+    <t>03:53:47</t>
+  </si>
+  <si>
+    <t>22:11:58</t>
+  </si>
+  <si>
+    <t>23:49:00</t>
+  </si>
+  <si>
+    <t>01:25:36</t>
+  </si>
+  <si>
+    <t>03:01:32</t>
+  </si>
+  <si>
+    <t>22:56:12</t>
+  </si>
+  <si>
+    <t>00:32:54</t>
+  </si>
+  <si>
+    <t>02:09:06</t>
+  </si>
+  <si>
+    <t>22:03:19</t>
+  </si>
+  <si>
+    <t>23:40:07</t>
   </si>
   <si>
     <t>0°</t>
@@ -604,40 +631,34 @@
     <t>5°</t>
   </si>
   <si>
-    <t>01:49:39</t>
-  </si>
-  <si>
-    <t>03:22:19</t>
-  </si>
-  <si>
-    <t>02:32:17</t>
-  </si>
-  <si>
-    <t>04:04:57</t>
-  </si>
-  <si>
-    <t>01:42:13</t>
-  </si>
-  <si>
-    <t>03:14:53</t>
-  </si>
-  <si>
-    <t>02:24:48</t>
-  </si>
-  <si>
-    <t>03:57:27</t>
-  </si>
-  <si>
-    <t>03:07:22</t>
-  </si>
-  <si>
-    <t>02:17:18</t>
-  </si>
-  <si>
-    <t>03:49:58</t>
-  </si>
-  <si>
-    <t>02:59:55</t>
+    <t>02:32:18</t>
+  </si>
+  <si>
+    <t>04:04:58</t>
+  </si>
+  <si>
+    <t>01:42:15</t>
+  </si>
+  <si>
+    <t>03:14:55</t>
+  </si>
+  <si>
+    <t>02:24:53</t>
+  </si>
+  <si>
+    <t>03:57:32</t>
+  </si>
+  <si>
+    <t>03:07:31</t>
+  </si>
+  <si>
+    <t>02:17:31</t>
+  </si>
+  <si>
+    <t>03:50:11</t>
+  </si>
+  <si>
+    <t>03:00:13</t>
   </si>
   <si>
     <t>B</t>
@@ -701,25 +722,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -737,7 +746,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -749,55 +824,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -810,18 +843,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1343,7 +1364,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R24"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1421,55 +1442,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>196</v>
+        <v>71</v>
       </c>
       <c r="L2" s="4">
-        <v>-32.1</v>
+        <v>-38.5</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="O2" s="6">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="P2" s="7">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="8">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
-        <v>1</v>
+        <v>40</v>
+      </c>
+      <c r="R2" s="9">
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1480,52 +1501,52 @@
         <v>30</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="L3" s="4">
-        <v>-18.4</v>
+        <v>-26.4</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O3" s="9">
-        <v>50</v>
-      </c>
-      <c r="P3" s="10">
-        <v>41</v>
-      </c>
-      <c r="Q3" s="8">
+        <v>218</v>
+      </c>
+      <c r="O3" s="6">
+        <v>84</v>
+      </c>
+      <c r="P3" s="7">
         <v>0</v>
       </c>
+      <c r="Q3" s="10">
+        <v>78</v>
+      </c>
       <c r="R3" s="11">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1533,55 +1554,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>72</v>
+        <v>206</v>
       </c>
       <c r="L4" s="4">
-        <v>-38.5</v>
+        <v>-11.8</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O4" s="9">
-        <v>71</v>
-      </c>
-      <c r="P4" s="8">
+        <v>218</v>
+      </c>
+      <c r="O4" s="6">
+        <v>91</v>
+      </c>
+      <c r="P4" s="7">
         <v>0</v>
       </c>
-      <c r="Q4" s="8">
-        <v>0</v>
-      </c>
-      <c r="R4" s="12">
-        <v>68</v>
+      <c r="Q4" s="12">
+        <v>91</v>
+      </c>
+      <c r="R4" s="11">
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1589,55 +1610,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>64</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>198</v>
+        <v>74</v>
       </c>
       <c r="L5" s="4">
-        <v>-26.4</v>
+        <v>-43.3</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O5" s="9">
-        <v>64</v>
-      </c>
-      <c r="P5" s="8">
+        <v>219</v>
+      </c>
+      <c r="O5" s="6">
+        <v>47</v>
+      </c>
+      <c r="P5" s="13">
+        <v>45</v>
+      </c>
+      <c r="Q5" s="7">
         <v>0</v>
       </c>
-      <c r="Q5" s="13">
-        <v>15</v>
-      </c>
-      <c r="R5" s="14">
-        <v>62</v>
+      <c r="R5" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1645,55 +1666,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="L6" s="4">
-        <v>-11.8</v>
+        <v>-33.7</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O6" s="9">
-        <v>100</v>
-      </c>
-      <c r="P6" s="8">
+        <v>217</v>
+      </c>
+      <c r="O6" s="6">
+        <v>47</v>
+      </c>
+      <c r="P6" s="13">
+        <v>46</v>
+      </c>
+      <c r="Q6" s="7">
         <v>0</v>
       </c>
-      <c r="Q6" s="15">
-        <v>53</v>
-      </c>
-      <c r="R6" s="16">
-        <v>100</v>
+      <c r="R6" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1701,55 +1722,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>75</v>
+        <v>208</v>
       </c>
       <c r="L7" s="4">
-        <v>-43.3</v>
+        <v>-20.2</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O7" s="9">
-        <v>94</v>
-      </c>
-      <c r="P7" s="17">
-        <v>51</v>
-      </c>
-      <c r="Q7" s="18">
-        <v>20</v>
-      </c>
-      <c r="R7" s="19">
-        <v>79</v>
+        <v>218</v>
+      </c>
+      <c r="O7" s="6">
+        <v>49</v>
+      </c>
+      <c r="P7" s="14">
+        <v>49</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>0</v>
+      </c>
+      <c r="R7" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1757,55 +1778,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>200</v>
+        <v>77</v>
       </c>
       <c r="L8" s="4">
-        <v>-33.7</v>
+        <v>-40</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O8" s="9">
-        <v>72</v>
-      </c>
-      <c r="P8" s="17">
-        <v>52</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>0</v>
-      </c>
-      <c r="R8" s="15">
-        <v>55</v>
+        <v>217</v>
+      </c>
+      <c r="O8" s="6">
+        <v>100</v>
+      </c>
+      <c r="P8" s="15">
+        <v>83</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>100</v>
+      </c>
+      <c r="R8" s="16">
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1813,55 +1834,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F9" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="L9" s="4">
+        <v>-28.1</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="O9" s="6">
         <v>100</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="L9" s="4">
-        <v>-20.2</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O9" s="9">
-        <v>49</v>
-      </c>
-      <c r="P9" s="20">
-        <v>45</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>0</v>
-      </c>
-      <c r="R9" s="8">
-        <v>0</v>
+      <c r="P9" s="10">
+        <v>81</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>100</v>
+      </c>
+      <c r="R9" s="11">
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1869,55 +1890,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>78</v>
+        <v>210</v>
       </c>
       <c r="L10" s="4">
-        <v>-40</v>
+        <v>-13.6</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O10" s="9">
+        <v>218</v>
+      </c>
+      <c r="O10" s="6">
         <v>100</v>
       </c>
-      <c r="P10" s="19">
-        <v>79</v>
+      <c r="P10" s="17">
+        <v>74</v>
       </c>
       <c r="Q10" s="11">
-        <v>96</v>
-      </c>
-      <c r="R10" s="8">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="R10" s="11">
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1925,54 +1946,54 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
+        <v>19</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L11" s="4">
+        <v>-44.5</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="O11" s="18">
         <v>30</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="L11" s="4">
-        <v>-28.1</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O11" s="9">
-        <v>98</v>
-      </c>
-      <c r="P11" s="14">
-        <v>61</v>
-      </c>
-      <c r="Q11" s="11">
-        <v>94</v>
-      </c>
-      <c r="R11" s="8">
+      <c r="P11" s="19">
+        <v>19</v>
+      </c>
+      <c r="Q11" s="20">
+        <v>24</v>
+      </c>
+      <c r="R11" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1981,55 +2002,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>203</v>
+        <v>81</v>
       </c>
       <c r="L12" s="4">
-        <v>-13.7</v>
+        <v>-35.5</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O12" s="9">
-        <v>98</v>
+        <v>217</v>
+      </c>
+      <c r="O12" s="6">
+        <v>59</v>
       </c>
       <c r="P12" s="21">
-        <v>88</v>
-      </c>
-      <c r="Q12" s="21">
-        <v>92</v>
-      </c>
-      <c r="R12" s="7">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>2</v>
+      </c>
+      <c r="R12" s="22">
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2037,55 +2058,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>81</v>
+        <v>211</v>
       </c>
       <c r="L13" s="4">
-        <v>-44.5</v>
+        <v>-21.9</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O13" s="9">
-        <v>57</v>
-      </c>
-      <c r="P13" s="15">
-        <v>55</v>
-      </c>
-      <c r="Q13" s="18">
-        <v>21</v>
-      </c>
-      <c r="R13" s="8">
-        <v>0</v>
+        <v>218</v>
+      </c>
+      <c r="O13" s="6">
+        <v>100</v>
+      </c>
+      <c r="P13" s="14">
+        <v>49</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>96</v>
+      </c>
+      <c r="R13" s="21">
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2093,55 +2114,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L14" s="4">
-        <v>-35.5</v>
+        <v>-46.6</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O14" s="9">
-        <v>43</v>
-      </c>
-      <c r="P14" s="20">
-        <v>43</v>
-      </c>
-      <c r="Q14" s="8">
-        <v>0</v>
-      </c>
-      <c r="R14" s="8">
-        <v>0</v>
+        <v>217</v>
+      </c>
+      <c r="O14" s="6">
+        <v>97</v>
+      </c>
+      <c r="P14" s="10">
+        <v>80</v>
+      </c>
+      <c r="Q14" s="12">
+        <v>92</v>
+      </c>
+      <c r="R14" s="23">
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2149,55 +2170,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>204</v>
+        <v>84</v>
       </c>
       <c r="L15" s="4">
-        <v>-22</v>
+        <v>-41.5</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O15" s="22">
-        <v>18</v>
-      </c>
-      <c r="P15" s="13">
-        <v>15</v>
-      </c>
-      <c r="Q15" s="8">
-        <v>0</v>
-      </c>
-      <c r="R15" s="8">
-        <v>0</v>
+        <v>217</v>
+      </c>
+      <c r="O15" s="6">
+        <v>98</v>
+      </c>
+      <c r="P15" s="10">
+        <v>82</v>
+      </c>
+      <c r="Q15" s="9">
+        <v>96</v>
+      </c>
+      <c r="R15" s="23">
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2205,55 +2226,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>84</v>
+        <v>212</v>
       </c>
       <c r="L16" s="4">
-        <v>-46.6</v>
+        <v>-29.8</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O16" s="9">
-        <v>79</v>
-      </c>
-      <c r="P16" s="15">
-        <v>53</v>
-      </c>
-      <c r="Q16" s="15">
-        <v>55</v>
-      </c>
-      <c r="R16" s="23">
-        <v>6</v>
+        <v>217</v>
+      </c>
+      <c r="O16" s="6">
+        <v>96</v>
+      </c>
+      <c r="P16" s="17">
+        <v>74</v>
+      </c>
+      <c r="Q16" s="10">
+        <v>80</v>
+      </c>
+      <c r="R16" s="20">
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2261,55 +2282,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>85</v>
+        <v>213</v>
       </c>
       <c r="L17" s="4">
-        <v>-41.5</v>
+        <v>-15.5</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O17" s="9">
-        <v>96</v>
-      </c>
-      <c r="P17" s="11">
-        <v>93</v>
-      </c>
-      <c r="Q17" s="10">
-        <v>41</v>
-      </c>
-      <c r="R17" s="13">
-        <v>13</v>
+        <v>219</v>
+      </c>
+      <c r="O17" s="6">
+        <v>91</v>
+      </c>
+      <c r="P17" s="24">
+        <v>63</v>
+      </c>
+      <c r="Q17" s="16">
+        <v>60</v>
+      </c>
+      <c r="R17" s="25">
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2317,55 +2338,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>205</v>
+        <v>87</v>
       </c>
       <c r="L18" s="4">
-        <v>-29.9</v>
+        <v>-46.1</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O18" s="9">
-        <v>95</v>
-      </c>
-      <c r="P18" s="11">
-        <v>93</v>
+        <v>219</v>
+      </c>
+      <c r="O18" s="18">
+        <v>14</v>
+      </c>
+      <c r="P18" s="22">
+        <v>14</v>
       </c>
       <c r="Q18" s="7">
-        <v>23</v>
-      </c>
-      <c r="R18" s="13">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="R18" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2373,55 +2394,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>206</v>
+        <v>88</v>
       </c>
       <c r="L19" s="4">
-        <v>-15.5</v>
+        <v>-45.7</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O19" s="9">
-        <v>95</v>
-      </c>
-      <c r="P19" s="11">
-        <v>93</v>
-      </c>
-      <c r="Q19" s="24">
-        <v>12</v>
-      </c>
-      <c r="R19" s="23">
-        <v>6</v>
+        <v>217</v>
+      </c>
+      <c r="O19" s="18">
+        <v>23</v>
+      </c>
+      <c r="P19" s="20">
+        <v>23</v>
+      </c>
+      <c r="Q19" s="7">
+        <v>1</v>
+      </c>
+      <c r="R19" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2429,54 +2450,54 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L20" s="4">
-        <v>-46.1</v>
+        <v>-37.1</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O20" s="9">
-        <v>80</v>
-      </c>
-      <c r="P20" s="25">
-        <v>76</v>
-      </c>
-      <c r="Q20" s="23">
-        <v>5</v>
-      </c>
-      <c r="R20" s="8">
+        <v>217</v>
+      </c>
+      <c r="O20" s="18">
+        <v>30</v>
+      </c>
+      <c r="P20" s="20">
+        <v>25</v>
+      </c>
+      <c r="Q20" s="20">
+        <v>23</v>
+      </c>
+      <c r="R20" s="7">
         <v>0</v>
       </c>
     </row>
@@ -2485,54 +2506,54 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>89</v>
+        <v>214</v>
       </c>
       <c r="L21" s="4">
-        <v>-45.7</v>
+        <v>-23.7</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O21" s="9">
-        <v>81</v>
-      </c>
-      <c r="P21" s="25">
-        <v>77</v>
-      </c>
-      <c r="Q21" s="23">
-        <v>4</v>
-      </c>
-      <c r="R21" s="8">
+        <v>217</v>
+      </c>
+      <c r="O21" s="18">
+        <v>35</v>
+      </c>
+      <c r="P21" s="19">
+        <v>20</v>
+      </c>
+      <c r="Q21" s="22">
+        <v>15</v>
+      </c>
+      <c r="R21" s="7">
         <v>0</v>
       </c>
     </row>
@@ -2541,55 +2562,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L22" s="4">
-        <v>-37.1</v>
+        <v>-47.4</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O22" s="9">
-        <v>82</v>
-      </c>
-      <c r="P22" s="19">
-        <v>80</v>
-      </c>
-      <c r="Q22" s="8">
-        <v>0</v>
-      </c>
-      <c r="R22" s="8">
-        <v>0</v>
+        <v>217</v>
+      </c>
+      <c r="O22" s="6">
+        <v>75</v>
+      </c>
+      <c r="P22" s="20">
+        <v>23</v>
+      </c>
+      <c r="Q22" s="13">
+        <v>45</v>
+      </c>
+      <c r="R22" s="17">
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2597,55 +2618,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>60</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>207</v>
+        <v>92</v>
       </c>
       <c r="L23" s="4">
-        <v>-23.8</v>
+        <v>-42.9</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O23" s="9">
-        <v>84</v>
+        <v>217</v>
+      </c>
+      <c r="O23" s="6">
+        <v>61</v>
       </c>
       <c r="P23" s="26">
-        <v>84</v>
-      </c>
-      <c r="Q23" s="8">
-        <v>0</v>
-      </c>
-      <c r="R23" s="8">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="Q23" s="14">
+        <v>48</v>
+      </c>
+      <c r="R23" s="23">
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2653,114 +2674,226 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>61</v>
       </c>
       <c r="D24" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="L24" s="4">
+        <v>-31.7</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="O24" s="6">
+        <v>60</v>
+      </c>
+      <c r="P24" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>42</v>
+      </c>
+      <c r="R24" s="21">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
+      <c r="A25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="2">
+        <v>18</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="L24" s="4">
-        <v>-47.4</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O24" s="9">
-        <v>59</v>
-      </c>
-      <c r="P24" s="8">
-        <v>2</v>
-      </c>
-      <c r="Q24" s="8">
-        <v>0</v>
-      </c>
-      <c r="R24" s="14">
-        <v>59</v>
+      <c r="D25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L25" s="4">
+        <v>-46.4</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="O25" s="6">
+        <v>73</v>
+      </c>
+      <c r="P25" s="19">
+        <v>19</v>
+      </c>
+      <c r="Q25" s="19">
+        <v>18</v>
+      </c>
+      <c r="R25" s="16">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
+      <c r="A26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="2">
+        <v>30</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="L26" s="4">
+        <v>-46.8</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="O26" s="6">
+        <v>80</v>
+      </c>
+      <c r="P26" s="22">
+        <v>17</v>
+      </c>
+      <c r="Q26" s="8">
+        <v>39</v>
+      </c>
+      <c r="R26" s="20">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A24">
+  <conditionalFormatting sqref="A2:A26">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B24">
+  <conditionalFormatting sqref="B2:B26">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C24">
+  <conditionalFormatting sqref="C2:C26">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D24">
+  <conditionalFormatting sqref="D2:D26">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E24">
+  <conditionalFormatting sqref="E2:E26">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F24">
+  <conditionalFormatting sqref="F2:F26">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G24">
+  <conditionalFormatting sqref="G2:G26">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H24">
+  <conditionalFormatting sqref="H2:H26">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I24">
+  <conditionalFormatting sqref="I2:I26">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J24">
+  <conditionalFormatting sqref="J2:J26">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K24">
+  <conditionalFormatting sqref="K2:K26">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L24">
+  <conditionalFormatting sqref="L2:L26">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2779,12 +2912,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M24">
+  <conditionalFormatting sqref="M2:M26">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N24">
+  <conditionalFormatting sqref="N2:N26">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2801,22 +2934,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O24">
+  <conditionalFormatting sqref="O2:O26">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P24">
+  <conditionalFormatting sqref="P2:P26">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q24">
+  <conditionalFormatting sqref="Q2:Q26">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R24">
+  <conditionalFormatting sqref="R2:R26">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="209">
   <si>
     <t>Datum</t>
   </si>
@@ -70,24 +70,12 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261008--01</t>
-  </si>
-  <si>
-    <t>20261008--02</t>
-  </si>
-  <si>
-    <t>20261008--03</t>
-  </si>
-  <si>
     <t>20261009--01</t>
   </si>
   <si>
     <t>20261009--02</t>
   </si>
   <si>
-    <t>20261009--03</t>
-  </si>
-  <si>
     <t>20261010--01</t>
   </si>
   <si>
@@ -145,483 +133,468 @@
     <t>20261014--04</t>
   </si>
   <si>
-    <t>04:22</t>
+    <t>20261015--01</t>
+  </si>
+  <si>
+    <t>20261015--02</t>
+  </si>
+  <si>
+    <t>20261015--03</t>
+  </si>
+  <si>
+    <t>05:41</t>
+  </si>
+  <si>
+    <t>05:46</t>
+  </si>
+  <si>
+    <t>05:23</t>
   </si>
   <si>
     <t>05:52</t>
   </si>
   <si>
-    <t>05:31</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>05:42</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>05:23</t>
+    <t>04:33</t>
+  </si>
+  <si>
+    <t>04:51</t>
+  </si>
+  <si>
+    <t>05:11</t>
+  </si>
+  <si>
+    <t>03:57</t>
+  </si>
+  <si>
+    <t>05:33</t>
+  </si>
+  <si>
+    <t>01:45</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>05:34</t>
+  </si>
+  <si>
+    <t>03:49</t>
+  </si>
+  <si>
+    <t>05:12</t>
+  </si>
+  <si>
+    <t>05:51</t>
+  </si>
+  <si>
+    <t>04:46</t>
   </si>
   <si>
     <t>04:34</t>
   </si>
   <si>
-    <t>04:52</t>
-  </si>
-  <si>
-    <t>05:12</t>
-  </si>
-  <si>
-    <t>03:58</t>
-  </si>
-  <si>
-    <t>05:47</t>
-  </si>
-  <si>
-    <t>05:34</t>
-  </si>
-  <si>
-    <t>01:44</t>
-  </si>
-  <si>
-    <t>02:06</t>
-  </si>
-  <si>
-    <t>05:46</t>
-  </si>
-  <si>
-    <t>03:49</t>
-  </si>
-  <si>
-    <t>05:50</t>
-  </si>
-  <si>
-    <t>04:46</t>
-  </si>
-  <si>
-    <t>04:33</t>
-  </si>
-  <si>
     <t>05:49</t>
   </si>
   <si>
+    <t>05:18</t>
+  </si>
+  <si>
+    <t>03:24</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>00:37</t>
-  </si>
-  <si>
-    <t>04:21</t>
-  </si>
-  <si>
     <t>02:07</t>
   </si>
   <si>
-    <t>02:55</t>
+    <t>02:54</t>
   </si>
   <si>
     <t>00:46</t>
   </si>
   <si>
-    <t>00:07</t>
-  </si>
-  <si>
-    <t>00:48:45</t>
-  </si>
-  <si>
-    <t>02:24:50</t>
-  </si>
-  <si>
-    <t>04:01:29</t>
-  </si>
-  <si>
-    <t>23:56:43</t>
+    <t>00:08</t>
   </si>
   <si>
     <t>01:32:28</t>
   </si>
   <si>
-    <t>03:09:02</t>
-  </si>
-  <si>
-    <t>00:40:07</t>
-  </si>
-  <si>
-    <t>02:16:32</t>
-  </si>
-  <si>
-    <t>03:53:20</t>
-  </si>
-  <si>
-    <t>23:47:46</t>
-  </si>
-  <si>
-    <t>01:24:00</t>
-  </si>
-  <si>
-    <t>03:00:42</t>
-  </si>
-  <si>
-    <t>22:55:28</t>
-  </si>
-  <si>
-    <t>00:31:26</t>
-  </si>
-  <si>
-    <t>02:08:02</t>
-  </si>
-  <si>
-    <t>03:45:05</t>
-  </si>
-  <si>
-    <t>22:03:14</t>
-  </si>
-  <si>
-    <t>23:38:51</t>
-  </si>
-  <si>
-    <t>01:15:21</t>
-  </si>
-  <si>
-    <t>02:52:13</t>
-  </si>
-  <si>
-    <t>22:46:16</t>
-  </si>
-  <si>
-    <t>00:22:36</t>
-  </si>
-  <si>
-    <t>01:59:22</t>
-  </si>
-  <si>
-    <t>21:53:43</t>
-  </si>
-  <si>
-    <t>23:29:50</t>
-  </si>
-  <si>
-    <t>00:51:20</t>
-  </si>
-  <si>
-    <t>02:27:03</t>
-  </si>
-  <si>
-    <t>04:03:48</t>
-  </si>
-  <si>
-    <t>23:59:42</t>
+    <t>03:09:01</t>
+  </si>
+  <si>
+    <t>00:40:06</t>
+  </si>
+  <si>
+    <t>02:16:30</t>
+  </si>
+  <si>
+    <t>03:53:19</t>
+  </si>
+  <si>
+    <t>23:47:44</t>
+  </si>
+  <si>
+    <t>01:23:57</t>
+  </si>
+  <si>
+    <t>03:00:40</t>
+  </si>
+  <si>
+    <t>22:55:25</t>
+  </si>
+  <si>
+    <t>00:31:23</t>
+  </si>
+  <si>
+    <t>02:07:59</t>
+  </si>
+  <si>
+    <t>03:45:02</t>
+  </si>
+  <si>
+    <t>22:03:10</t>
+  </si>
+  <si>
+    <t>23:38:46</t>
+  </si>
+  <si>
+    <t>01:15:16</t>
+  </si>
+  <si>
+    <t>02:52:08</t>
+  </si>
+  <si>
+    <t>22:46:10</t>
+  </si>
+  <si>
+    <t>00:22:30</t>
+  </si>
+  <si>
+    <t>01:59:15</t>
+  </si>
+  <si>
+    <t>21:53:35</t>
+  </si>
+  <si>
+    <t>23:29:42</t>
+  </si>
+  <si>
+    <t>01:06:21</t>
+  </si>
+  <si>
+    <t>21:01:02</t>
+  </si>
+  <si>
+    <t>22:36:52</t>
   </si>
   <si>
     <t>01:34:44</t>
   </si>
   <si>
-    <t>03:11:17</t>
-  </si>
-  <si>
-    <t>00:42:27</t>
-  </si>
-  <si>
-    <t>02:18:45</t>
-  </si>
-  <si>
-    <t>03:55:53</t>
-  </si>
-  <si>
-    <t>23:50:13</t>
-  </si>
-  <si>
-    <t>01:26:13</t>
-  </si>
-  <si>
-    <t>03:03:05</t>
-  </si>
-  <si>
-    <t>22:58:09</t>
-  </si>
-  <si>
-    <t>00:33:40</t>
-  </si>
-  <si>
-    <t>02:10:20</t>
-  </si>
-  <si>
-    <t>03:48:34</t>
-  </si>
-  <si>
-    <t>22:06:32</t>
-  </si>
-  <si>
-    <t>23:41:08</t>
-  </si>
-  <si>
-    <t>01:17:35</t>
-  </si>
-  <si>
-    <t>02:54:58</t>
-  </si>
-  <si>
-    <t>22:48:38</t>
-  </si>
-  <si>
-    <t>00:24:50</t>
-  </si>
-  <si>
-    <t>02:01:51</t>
-  </si>
-  <si>
-    <t>21:56:14</t>
-  </si>
-  <si>
-    <t>23:32:04</t>
-  </si>
-  <si>
-    <t>00:53:31</t>
-  </si>
-  <si>
-    <t>02:29:59</t>
-  </si>
-  <si>
-    <t>04:06:33</t>
-  </si>
-  <si>
-    <t>00:01:12</t>
-  </si>
-  <si>
-    <t>01:37:35</t>
+    <t>03:11:16</t>
+  </si>
+  <si>
+    <t>00:42:25</t>
+  </si>
+  <si>
+    <t>02:18:44</t>
+  </si>
+  <si>
+    <t>03:55:52</t>
+  </si>
+  <si>
+    <t>23:50:11</t>
+  </si>
+  <si>
+    <t>01:26:11</t>
+  </si>
+  <si>
+    <t>03:03:03</t>
+  </si>
+  <si>
+    <t>22:58:06</t>
+  </si>
+  <si>
+    <t>00:33:37</t>
+  </si>
+  <si>
+    <t>02:10:17</t>
+  </si>
+  <si>
+    <t>03:48:30</t>
+  </si>
+  <si>
+    <t>22:06:28</t>
+  </si>
+  <si>
+    <t>23:41:03</t>
+  </si>
+  <si>
+    <t>01:17:30</t>
+  </si>
+  <si>
+    <t>02:54:53</t>
+  </si>
+  <si>
+    <t>22:48:31</t>
+  </si>
+  <si>
+    <t>00:24:43</t>
+  </si>
+  <si>
+    <t>02:01:44</t>
+  </si>
+  <si>
+    <t>21:56:05</t>
+  </si>
+  <si>
+    <t>23:31:55</t>
+  </si>
+  <si>
+    <t>01:08:42</t>
+  </si>
+  <si>
+    <t>21:03:53</t>
+  </si>
+  <si>
+    <t>22:39:07</t>
+  </si>
+  <si>
+    <t>01:37:34</t>
   </si>
   <si>
     <t>03:14:09</t>
   </si>
   <si>
-    <t>00:45:08</t>
-  </si>
-  <si>
-    <t>02:21:41</t>
-  </si>
-  <si>
-    <t>03:58:10</t>
-  </si>
-  <si>
-    <t>23:52:38</t>
-  </si>
-  <si>
-    <t>01:29:09</t>
-  </si>
-  <si>
-    <t>03:05:41</t>
-  </si>
-  <si>
-    <t>23:00:07</t>
-  </si>
-  <si>
-    <t>00:36:33</t>
-  </si>
-  <si>
-    <t>02:13:06</t>
-  </si>
-  <si>
-    <t>03:49:26</t>
-  </si>
-  <si>
-    <t>22:07:35</t>
-  </si>
-  <si>
-    <t>23:43:54</t>
-  </si>
-  <si>
-    <t>01:20:28</t>
-  </si>
-  <si>
-    <t>02:56:53</t>
-  </si>
-  <si>
-    <t>22:51:13</t>
-  </si>
-  <si>
-    <t>00:27:45</t>
-  </si>
-  <si>
-    <t>02:04:14</t>
-  </si>
-  <si>
-    <t>21:58:30</t>
-  </si>
-  <si>
-    <t>23:34:58</t>
-  </si>
-  <si>
-    <t>00:55:42</t>
-  </si>
-  <si>
-    <t>02:32:55</t>
-  </si>
-  <si>
-    <t>04:09:19</t>
-  </si>
-  <si>
-    <t>00:02:42</t>
-  </si>
-  <si>
-    <t>01:40:26</t>
+    <t>00:45:06</t>
+  </si>
+  <si>
+    <t>02:21:40</t>
+  </si>
+  <si>
+    <t>03:58:08</t>
+  </si>
+  <si>
+    <t>23:52:36</t>
+  </si>
+  <si>
+    <t>01:29:07</t>
+  </si>
+  <si>
+    <t>03:05:39</t>
+  </si>
+  <si>
+    <t>23:00:04</t>
+  </si>
+  <si>
+    <t>00:36:29</t>
+  </si>
+  <si>
+    <t>02:13:03</t>
+  </si>
+  <si>
+    <t>03:49:22</t>
+  </si>
+  <si>
+    <t>22:07:30</t>
+  </si>
+  <si>
+    <t>23:43:49</t>
+  </si>
+  <si>
+    <t>01:20:23</t>
+  </si>
+  <si>
+    <t>02:56:48</t>
+  </si>
+  <si>
+    <t>22:51:07</t>
+  </si>
+  <si>
+    <t>00:27:38</t>
+  </si>
+  <si>
+    <t>02:04:07</t>
+  </si>
+  <si>
+    <t>21:58:22</t>
+  </si>
+  <si>
+    <t>23:34:49</t>
+  </si>
+  <si>
+    <t>01:11:21</t>
+  </si>
+  <si>
+    <t>21:05:35</t>
+  </si>
+  <si>
+    <t>22:41:57</t>
+  </si>
+  <si>
+    <t>01:40:25</t>
   </si>
   <si>
     <t>03:17:02</t>
   </si>
   <si>
-    <t>00:47:50</t>
-  </si>
-  <si>
-    <t>02:24:37</t>
-  </si>
-  <si>
-    <t>04:00:27</t>
-  </si>
-  <si>
-    <t>23:55:05</t>
-  </si>
-  <si>
-    <t>01:32:05</t>
-  </si>
-  <si>
-    <t>03:08:17</t>
-  </si>
-  <si>
-    <t>23:02:07</t>
-  </si>
-  <si>
-    <t>00:39:27</t>
-  </si>
-  <si>
-    <t>02:15:54</t>
-  </si>
-  <si>
-    <t>03:50:18</t>
-  </si>
-  <si>
-    <t>22:08:38</t>
-  </si>
-  <si>
-    <t>23:46:42</t>
-  </si>
-  <si>
-    <t>01:23:21</t>
-  </si>
-  <si>
-    <t>02:58:47</t>
-  </si>
-  <si>
-    <t>22:53:50</t>
-  </si>
-  <si>
-    <t>00:30:40</t>
-  </si>
-  <si>
-    <t>02:06:37</t>
-  </si>
-  <si>
-    <t>22:00:47</t>
-  </si>
-  <si>
-    <t>23:37:53</t>
-  </si>
-  <si>
-    <t>00:58:18</t>
-  </si>
-  <si>
-    <t>02:35:10</t>
-  </si>
-  <si>
-    <t>04:11:38</t>
-  </si>
-  <si>
-    <t>00:05:43</t>
-  </si>
-  <si>
-    <t>01:42:43</t>
+    <t>00:47:48</t>
+  </si>
+  <si>
+    <t>02:24:36</t>
+  </si>
+  <si>
+    <t>04:00:25</t>
+  </si>
+  <si>
+    <t>23:55:02</t>
+  </si>
+  <si>
+    <t>01:32:03</t>
+  </si>
+  <si>
+    <t>03:08:14</t>
+  </si>
+  <si>
+    <t>23:02:03</t>
+  </si>
+  <si>
+    <t>00:39:23</t>
+  </si>
+  <si>
+    <t>02:15:50</t>
+  </si>
+  <si>
+    <t>03:50:15</t>
+  </si>
+  <si>
+    <t>22:08:33</t>
+  </si>
+  <si>
+    <t>23:46:37</t>
+  </si>
+  <si>
+    <t>01:23:16</t>
+  </si>
+  <si>
+    <t>02:58:42</t>
+  </si>
+  <si>
+    <t>22:53:43</t>
+  </si>
+  <si>
+    <t>00:30:34</t>
+  </si>
+  <si>
+    <t>02:06:30</t>
+  </si>
+  <si>
+    <t>22:00:39</t>
+  </si>
+  <si>
+    <t>23:37:44</t>
+  </si>
+  <si>
+    <t>01:14:00</t>
+  </si>
+  <si>
+    <t>21:07:17</t>
+  </si>
+  <si>
+    <t>22:44:48</t>
+  </si>
+  <si>
+    <t>01:42:42</t>
   </si>
   <si>
     <t>03:19:18</t>
   </si>
   <si>
-    <t>00:50:10</t>
-  </si>
-  <si>
-    <t>02:26:52</t>
-  </si>
-  <si>
-    <t>04:03:00</t>
-  </si>
-  <si>
-    <t>23:57:33</t>
-  </si>
-  <si>
-    <t>01:34:20</t>
-  </si>
-  <si>
-    <t>03:10:40</t>
-  </si>
-  <si>
-    <t>23:04:49</t>
-  </si>
-  <si>
-    <t>00:41:42</t>
-  </si>
-  <si>
-    <t>02:18:12</t>
-  </si>
-  <si>
-    <t>03:53:47</t>
-  </si>
-  <si>
-    <t>22:11:58</t>
-  </si>
-  <si>
-    <t>23:49:00</t>
-  </si>
-  <si>
-    <t>01:25:36</t>
-  </si>
-  <si>
-    <t>03:01:32</t>
-  </si>
-  <si>
-    <t>22:56:12</t>
-  </si>
-  <si>
-    <t>00:32:54</t>
-  </si>
-  <si>
-    <t>02:09:06</t>
-  </si>
-  <si>
-    <t>22:03:19</t>
-  </si>
-  <si>
-    <t>23:40:07</t>
+    <t>00:50:09</t>
+  </si>
+  <si>
+    <t>02:26:50</t>
+  </si>
+  <si>
+    <t>04:02:58</t>
+  </si>
+  <si>
+    <t>23:57:31</t>
+  </si>
+  <si>
+    <t>01:34:17</t>
+  </si>
+  <si>
+    <t>03:10:38</t>
+  </si>
+  <si>
+    <t>23:04:46</t>
+  </si>
+  <si>
+    <t>00:41:39</t>
+  </si>
+  <si>
+    <t>02:18:08</t>
+  </si>
+  <si>
+    <t>03:53:43</t>
+  </si>
+  <si>
+    <t>22:11:53</t>
+  </si>
+  <si>
+    <t>23:48:55</t>
+  </si>
+  <si>
+    <t>01:25:31</t>
+  </si>
+  <si>
+    <t>03:01:27</t>
+  </si>
+  <si>
+    <t>22:56:06</t>
+  </si>
+  <si>
+    <t>00:32:48</t>
+  </si>
+  <si>
+    <t>02:08:59</t>
+  </si>
+  <si>
+    <t>22:03:11</t>
+  </si>
+  <si>
+    <t>23:39:58</t>
+  </si>
+  <si>
+    <t>01:16:21</t>
+  </si>
+  <si>
+    <t>21:10:09</t>
+  </si>
+  <si>
+    <t>22:47:04</t>
+  </si>
+  <si>
+    <t>2°</t>
+  </si>
+  <si>
+    <t>25°</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
+    <t>9°</t>
+  </si>
+  <si>
+    <t>17°</t>
+  </si>
+  <si>
     <t>14°</t>
   </si>
   <si>
-    <t>17°</t>
-  </si>
-  <si>
-    <t>2°</t>
-  </si>
-  <si>
-    <t>25°</t>
-  </si>
-  <si>
-    <t>9°</t>
-  </si>
-  <si>
     <t>3°</t>
   </si>
   <si>
@@ -631,34 +604,28 @@
     <t>5°</t>
   </si>
   <si>
-    <t>02:32:18</t>
-  </si>
-  <si>
-    <t>04:04:58</t>
-  </si>
-  <si>
     <t>01:42:15</t>
   </si>
   <si>
     <t>03:14:55</t>
   </si>
   <si>
-    <t>02:24:53</t>
-  </si>
-  <si>
-    <t>03:57:32</t>
-  </si>
-  <si>
-    <t>03:07:31</t>
-  </si>
-  <si>
-    <t>02:17:31</t>
-  </si>
-  <si>
-    <t>03:50:11</t>
-  </si>
-  <si>
-    <t>03:00:13</t>
+    <t>02:24:51</t>
+  </si>
+  <si>
+    <t>03:57:31</t>
+  </si>
+  <si>
+    <t>03:07:28</t>
+  </si>
+  <si>
+    <t>02:17:27</t>
+  </si>
+  <si>
+    <t>03:50:07</t>
+  </si>
+  <si>
+    <t>03:00:08</t>
   </si>
   <si>
     <t>B</t>
@@ -707,7 +674,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -722,7 +689,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -734,13 +707,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -752,49 +791,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -806,43 +803,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -883,7 +844,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -958,9 +919,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1364,7 +1322,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1442,55 +1400,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="J2" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="L2" s="4">
-        <v>-38.5</v>
+        <v>-33.7</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="O2" s="6">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="P2" s="7">
+        <v>52</v>
+      </c>
+      <c r="Q2" s="8">
         <v>0</v>
       </c>
-      <c r="Q2" s="8">
-        <v>40</v>
-      </c>
-      <c r="R2" s="9">
-        <v>97</v>
+      <c r="R2" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1498,55 +1456,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="J3" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="4">
+        <v>-20.2</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="L3" s="4">
-        <v>-26.4</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>216</v>
-      </c>
       <c r="N3" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O3" s="6">
-        <v>84</v>
+        <v>207</v>
+      </c>
+      <c r="O3" s="9">
+        <v>53</v>
       </c>
       <c r="P3" s="7">
+        <v>50</v>
+      </c>
+      <c r="Q3" s="8">
         <v>0</v>
       </c>
-      <c r="Q3" s="10">
-        <v>78</v>
-      </c>
-      <c r="R3" s="11">
-        <v>100</v>
+      <c r="R3" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1554,52 +1512,52 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="K4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-40</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="L4" s="4">
-        <v>-11.8</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O4" s="6">
-        <v>91</v>
-      </c>
-      <c r="P4" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="12">
-        <v>91</v>
+      <c r="O4" s="9">
+        <v>100</v>
+      </c>
+      <c r="P4" s="10">
+        <v>68</v>
+      </c>
+      <c r="Q4" s="11">
+        <v>100</v>
       </c>
       <c r="R4" s="11">
         <v>100</v>
@@ -1610,55 +1568,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>74</v>
+        <v>198</v>
       </c>
       <c r="L5" s="4">
-        <v>-43.3</v>
+        <v>-28.1</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="O5" s="6">
-        <v>47</v>
-      </c>
-      <c r="P5" s="13">
-        <v>45</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>0</v>
-      </c>
-      <c r="R5" s="7">
-        <v>0</v>
+        <v>206</v>
+      </c>
+      <c r="O5" s="9">
+        <v>100</v>
+      </c>
+      <c r="P5" s="10">
+        <v>68</v>
+      </c>
+      <c r="Q5" s="11">
+        <v>100</v>
+      </c>
+      <c r="R5" s="11">
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1666,55 +1624,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>64</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-13.6</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="O6" s="9">
         <v>100</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="L6" s="4">
-        <v>-33.7</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O6" s="6">
-        <v>47</v>
-      </c>
-      <c r="P6" s="13">
-        <v>46</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>0</v>
-      </c>
-      <c r="R6" s="7">
-        <v>0</v>
+      <c r="P6" s="12">
+        <v>77</v>
+      </c>
+      <c r="Q6" s="11">
+        <v>100</v>
+      </c>
+      <c r="R6" s="11">
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1722,54 +1680,54 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>208</v>
+        <v>72</v>
       </c>
       <c r="L7" s="4">
-        <v>-20.2</v>
+        <v>-44.5</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="O7" s="6">
-        <v>49</v>
-      </c>
-      <c r="P7" s="14">
-        <v>49</v>
-      </c>
-      <c r="Q7" s="7">
+        <v>31</v>
+      </c>
+      <c r="P7" s="13">
+        <v>31</v>
+      </c>
+      <c r="Q7" s="8">
         <v>0</v>
       </c>
-      <c r="R7" s="7">
+      <c r="R7" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1778,55 +1736,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="L8" s="4">
-        <v>-40</v>
+        <v>-35.5</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="O8" s="6">
-        <v>100</v>
-      </c>
-      <c r="P8" s="15">
-        <v>83</v>
-      </c>
-      <c r="Q8" s="11">
-        <v>100</v>
-      </c>
-      <c r="R8" s="16">
-        <v>61</v>
+        <v>43</v>
+      </c>
+      <c r="P8" s="14">
+        <v>43</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>0</v>
+      </c>
+      <c r="R8" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1834,55 +1792,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="L9" s="4">
-        <v>-28.1</v>
+        <v>-21.9</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O9" s="6">
-        <v>100</v>
-      </c>
-      <c r="P9" s="10">
-        <v>81</v>
-      </c>
-      <c r="Q9" s="11">
-        <v>100</v>
-      </c>
-      <c r="R9" s="11">
-        <v>100</v>
+        <v>207</v>
+      </c>
+      <c r="O9" s="9">
+        <v>49</v>
+      </c>
+      <c r="P9" s="15">
+        <v>36</v>
+      </c>
+      <c r="Q9" s="13">
+        <v>32</v>
+      </c>
+      <c r="R9" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1890,55 +1848,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L10" s="4">
+        <v>-46.6</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="O10" s="9">
+        <v>65</v>
+      </c>
+      <c r="P10" s="16">
+        <v>23</v>
+      </c>
+      <c r="Q10" s="7">
         <v>50</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="L10" s="4">
-        <v>-13.6</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O10" s="6">
-        <v>100</v>
-      </c>
-      <c r="P10" s="17">
-        <v>74</v>
-      </c>
-      <c r="Q10" s="11">
-        <v>100</v>
-      </c>
-      <c r="R10" s="11">
-        <v>98</v>
+      <c r="R10" s="17">
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1946,55 +1904,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="L11" s="4">
-        <v>-44.5</v>
+        <v>-41.5</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O11" s="18">
-        <v>30</v>
-      </c>
-      <c r="P11" s="19">
-        <v>19</v>
-      </c>
-      <c r="Q11" s="20">
-        <v>24</v>
-      </c>
-      <c r="R11" s="7">
-        <v>0</v>
+        <v>206</v>
+      </c>
+      <c r="O11" s="9">
+        <v>58</v>
+      </c>
+      <c r="P11" s="16">
+        <v>26</v>
+      </c>
+      <c r="Q11" s="18">
+        <v>42</v>
+      </c>
+      <c r="R11" s="19">
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -2002,55 +1960,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="L12" s="4">
-        <v>-35.5</v>
+        <v>-29.8</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O12" s="6">
-        <v>59</v>
-      </c>
-      <c r="P12" s="21">
-        <v>37</v>
-      </c>
-      <c r="Q12" s="7">
-        <v>2</v>
-      </c>
-      <c r="R12" s="22">
-        <v>13</v>
+        <v>206</v>
+      </c>
+      <c r="O12" s="9">
+        <v>67</v>
+      </c>
+      <c r="P12" s="15">
+        <v>33</v>
+      </c>
+      <c r="Q12" s="20">
+        <v>54</v>
+      </c>
+      <c r="R12" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2058,55 +2016,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="L13" s="4">
-        <v>-21.9</v>
+        <v>-15.5</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O13" s="6">
-        <v>100</v>
-      </c>
-      <c r="P13" s="14">
-        <v>49</v>
-      </c>
-      <c r="Q13" s="9">
-        <v>96</v>
-      </c>
-      <c r="R13" s="21">
-        <v>35</v>
+        <v>208</v>
+      </c>
+      <c r="O13" s="9">
+        <v>55</v>
+      </c>
+      <c r="P13" s="18">
+        <v>38</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>0</v>
+      </c>
+      <c r="R13" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2114,55 +2072,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L14" s="4">
-        <v>-46.6</v>
+        <v>-46.1</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O14" s="6">
-        <v>97</v>
-      </c>
-      <c r="P14" s="10">
-        <v>80</v>
-      </c>
-      <c r="Q14" s="12">
-        <v>92</v>
-      </c>
-      <c r="R14" s="23">
-        <v>31</v>
+        <v>208</v>
+      </c>
+      <c r="O14" s="21">
+        <v>1</v>
+      </c>
+      <c r="P14" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>0</v>
+      </c>
+      <c r="R14" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2170,55 +2128,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L15" s="4">
-        <v>-41.5</v>
+        <v>-45.7</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O15" s="6">
-        <v>98</v>
-      </c>
-      <c r="P15" s="10">
-        <v>82</v>
-      </c>
-      <c r="Q15" s="9">
-        <v>96</v>
-      </c>
-      <c r="R15" s="23">
-        <v>31</v>
+        <v>206</v>
+      </c>
+      <c r="O15" s="21">
+        <v>1</v>
+      </c>
+      <c r="P15" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>0</v>
+      </c>
+      <c r="R15" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2226,55 +2184,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>212</v>
+        <v>81</v>
       </c>
       <c r="L16" s="4">
-        <v>-29.8</v>
+        <v>-37.1</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O16" s="6">
-        <v>96</v>
-      </c>
-      <c r="P16" s="17">
-        <v>74</v>
-      </c>
-      <c r="Q16" s="10">
-        <v>80</v>
-      </c>
-      <c r="R16" s="20">
-        <v>23</v>
+        <v>206</v>
+      </c>
+      <c r="O16" s="21">
+        <v>0</v>
+      </c>
+      <c r="P16" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>0</v>
+      </c>
+      <c r="R16" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2282,55 +2240,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="J17" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>213</v>
-      </c>
       <c r="L17" s="4">
-        <v>-15.5</v>
+        <v>-23.8</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="O17" s="6">
-        <v>91</v>
-      </c>
-      <c r="P17" s="24">
-        <v>63</v>
-      </c>
-      <c r="Q17" s="16">
-        <v>60</v>
-      </c>
-      <c r="R17" s="25">
-        <v>7</v>
+        <v>206</v>
+      </c>
+      <c r="O17" s="21">
+        <v>0</v>
+      </c>
+      <c r="P17" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>0</v>
+      </c>
+      <c r="R17" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2338,55 +2296,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="L18" s="4">
-        <v>-46.1</v>
+        <v>-47.4</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="O18" s="18">
-        <v>14</v>
-      </c>
-      <c r="P18" s="22">
-        <v>14</v>
-      </c>
-      <c r="Q18" s="7">
+        <v>206</v>
+      </c>
+      <c r="O18" s="9">
+        <v>78</v>
+      </c>
+      <c r="P18" s="8">
         <v>0</v>
       </c>
-      <c r="R18" s="7">
-        <v>0</v>
+      <c r="Q18" s="22">
+        <v>78</v>
+      </c>
+      <c r="R18" s="15">
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2394,55 +2352,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E19" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L19" s="4">
+        <v>-42.9</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="O19" s="9">
         <v>88</v>
       </c>
-      <c r="F19" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="K19" s="1" t="s">
+      <c r="P19" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="23">
         <v>88</v>
       </c>
-      <c r="L19" s="4">
-        <v>-45.7</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O19" s="18">
-        <v>23</v>
-      </c>
-      <c r="P19" s="20">
-        <v>23</v>
-      </c>
-      <c r="Q19" s="7">
-        <v>1</v>
-      </c>
-      <c r="R19" s="7">
-        <v>0</v>
+      <c r="R19" s="20">
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2450,55 +2408,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="I20" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="K20" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="L20" s="4">
-        <v>-37.1</v>
+        <v>-31.8</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O20" s="18">
-        <v>30</v>
-      </c>
-      <c r="P20" s="20">
-        <v>25</v>
-      </c>
-      <c r="Q20" s="20">
-        <v>23</v>
-      </c>
-      <c r="R20" s="7">
-        <v>0</v>
+        <v>206</v>
+      </c>
+      <c r="O20" s="9">
+        <v>95</v>
+      </c>
+      <c r="P20" s="24">
+        <v>19</v>
+      </c>
+      <c r="Q20" s="25">
+        <v>86</v>
+      </c>
+      <c r="R20" s="10">
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2506,55 +2464,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="J21" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L21" s="4">
+        <v>-46.4</v>
+      </c>
+      <c r="M21" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="L21" s="4">
-        <v>-23.7</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="N21" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O21" s="18">
-        <v>35</v>
-      </c>
-      <c r="P21" s="19">
-        <v>20</v>
-      </c>
-      <c r="Q21" s="22">
-        <v>15</v>
-      </c>
-      <c r="R21" s="7">
-        <v>0</v>
+        <v>206</v>
+      </c>
+      <c r="O21" s="9">
+        <v>98</v>
+      </c>
+      <c r="P21" s="25">
+        <v>85</v>
+      </c>
+      <c r="Q21" s="17">
+        <v>9</v>
+      </c>
+      <c r="R21" s="25">
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2562,55 +2520,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E22" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="L22" s="4">
+        <v>-46.8</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="O22" s="9">
         <v>91</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="L22" s="4">
-        <v>-47.4</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O22" s="6">
-        <v>75</v>
-      </c>
-      <c r="P22" s="20">
-        <v>23</v>
-      </c>
-      <c r="Q22" s="13">
-        <v>45</v>
-      </c>
-      <c r="R22" s="17">
-        <v>75</v>
+      <c r="P22" s="25">
+        <v>85</v>
+      </c>
+      <c r="Q22" s="8">
+        <v>2</v>
+      </c>
+      <c r="R22" s="22">
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2618,55 +2576,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>60</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L23" s="4">
-        <v>-42.9</v>
+        <v>-38.8</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O23" s="6">
-        <v>61</v>
-      </c>
-      <c r="P23" s="26">
-        <v>10</v>
-      </c>
-      <c r="Q23" s="14">
-        <v>48</v>
-      </c>
-      <c r="R23" s="23">
-        <v>30</v>
+        <v>206</v>
+      </c>
+      <c r="O23" s="9">
+        <v>80</v>
+      </c>
+      <c r="P23" s="22">
+        <v>78</v>
+      </c>
+      <c r="Q23" s="8">
+        <v>2</v>
+      </c>
+      <c r="R23" s="18">
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2674,54 +2632,54 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>61</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="L24" s="4">
-        <v>-31.7</v>
+        <v>-42.9</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O24" s="6">
-        <v>60</v>
-      </c>
-      <c r="P24" s="7">
-        <v>2</v>
-      </c>
-      <c r="Q24" s="8">
-        <v>42</v>
-      </c>
-      <c r="R24" s="21">
+        <v>208</v>
+      </c>
+      <c r="O24" s="9">
+        <v>85</v>
+      </c>
+      <c r="P24" s="13">
+        <v>28</v>
+      </c>
+      <c r="Q24" s="7">
+        <v>50</v>
+      </c>
+      <c r="R24" s="15">
         <v>35</v>
       </c>
     </row>
@@ -2730,170 +2688,114 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="E25" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="L25" s="4">
-        <v>-46.4</v>
+        <v>-48.1</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O25" s="6">
-        <v>73</v>
-      </c>
-      <c r="P25" s="19">
-        <v>19</v>
-      </c>
-      <c r="Q25" s="19">
-        <v>18</v>
-      </c>
-      <c r="R25" s="16">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18">
-      <c r="A26" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="2">
-        <v>30</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="L26" s="4">
-        <v>-46.8</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O26" s="6">
-        <v>80</v>
-      </c>
-      <c r="P26" s="22">
-        <v>17</v>
-      </c>
-      <c r="Q26" s="8">
-        <v>39</v>
-      </c>
-      <c r="R26" s="20">
-        <v>24</v>
+        <v>206</v>
+      </c>
+      <c r="O25" s="9">
+        <v>100</v>
+      </c>
+      <c r="P25" s="15">
+        <v>33</v>
+      </c>
+      <c r="Q25" s="20">
+        <v>56</v>
+      </c>
+      <c r="R25" s="15">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A26">
+  <conditionalFormatting sqref="A2:A25">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B26">
+  <conditionalFormatting sqref="B2:B25">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C26">
+  <conditionalFormatting sqref="C2:C25">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D26">
+  <conditionalFormatting sqref="D2:D25">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E26">
+  <conditionalFormatting sqref="E2:E25">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F26">
+  <conditionalFormatting sqref="F2:F25">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G26">
+  <conditionalFormatting sqref="G2:G25">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H26">
+  <conditionalFormatting sqref="H2:H25">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I26">
+  <conditionalFormatting sqref="I2:I25">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J26">
+  <conditionalFormatting sqref="J2:J25">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K26">
+  <conditionalFormatting sqref="K2:K25">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L26">
+  <conditionalFormatting sqref="L2:L25">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2912,12 +2814,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M26">
+  <conditionalFormatting sqref="M2:M25">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N26">
+  <conditionalFormatting sqref="N2:N25">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2934,22 +2836,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O26">
+  <conditionalFormatting sqref="O2:O25">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P26">
+  <conditionalFormatting sqref="P2:P25">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q26">
+  <conditionalFormatting sqref="Q2:Q25">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R26">
+  <conditionalFormatting sqref="R2:R25">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="218">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261009--01</t>
-  </si>
-  <si>
-    <t>20261009--02</t>
-  </si>
-  <si>
     <t>20261010--01</t>
   </si>
   <si>
@@ -142,376 +136,409 @@
     <t>20261015--03</t>
   </si>
   <si>
-    <t>05:41</t>
+    <t>20261016--01</t>
+  </si>
+  <si>
+    <t>20261016--02</t>
+  </si>
+  <si>
+    <t>20261016--03</t>
+  </si>
+  <si>
+    <t>20261016--04</t>
+  </si>
+  <si>
+    <t>05:23</t>
+  </si>
+  <si>
+    <t>05:52</t>
+  </si>
+  <si>
+    <t>04:33</t>
+  </si>
+  <si>
+    <t>04:52</t>
+  </si>
+  <si>
+    <t>05:12</t>
+  </si>
+  <si>
+    <t>03:57</t>
+  </si>
+  <si>
+    <t>05:47</t>
+  </si>
+  <si>
+    <t>05:34</t>
+  </si>
+  <si>
+    <t>01:45</t>
+  </si>
+  <si>
+    <t>02:04</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>03:50</t>
+  </si>
+  <si>
+    <t>05:50</t>
+  </si>
+  <si>
+    <t>04:47</t>
+  </si>
+  <si>
+    <t>05:48</t>
+  </si>
+  <si>
+    <t>05:18</t>
+  </si>
+  <si>
+    <t>03:24</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>05:36</t>
+  </si>
+  <si>
+    <t>02:44</t>
+  </si>
+  <si>
+    <t>05:25</t>
   </si>
   <si>
     <t>05:46</t>
   </si>
   <si>
-    <t>05:23</t>
-  </si>
-  <si>
-    <t>05:52</t>
-  </si>
-  <si>
-    <t>04:33</t>
-  </si>
-  <si>
-    <t>04:51</t>
-  </si>
-  <si>
-    <t>05:11</t>
-  </si>
-  <si>
-    <t>03:57</t>
-  </si>
-  <si>
-    <t>05:33</t>
-  </si>
-  <si>
-    <t>01:45</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>05:34</t>
-  </si>
-  <si>
-    <t>03:49</t>
-  </si>
-  <si>
-    <t>05:12</t>
-  </si>
-  <si>
-    <t>05:51</t>
-  </si>
-  <si>
-    <t>04:46</t>
-  </si>
-  <si>
-    <t>04:34</t>
-  </si>
-  <si>
-    <t>05:49</t>
-  </si>
-  <si>
-    <t>05:18</t>
-  </si>
-  <si>
-    <t>03:24</t>
-  </si>
-  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>02:07</t>
-  </si>
-  <si>
     <t>02:54</t>
   </si>
   <si>
     <t>00:46</t>
   </si>
   <si>
-    <t>00:08</t>
-  </si>
-  <si>
-    <t>01:32:28</t>
-  </si>
-  <si>
-    <t>03:09:01</t>
-  </si>
-  <si>
-    <t>00:40:06</t>
+    <t>00:07</t>
+  </si>
+  <si>
+    <t>00:40:05</t>
   </si>
   <si>
     <t>02:16:30</t>
   </si>
   <si>
-    <t>03:53:19</t>
-  </si>
-  <si>
-    <t>23:47:44</t>
-  </si>
-  <si>
-    <t>01:23:57</t>
-  </si>
-  <si>
-    <t>03:00:40</t>
-  </si>
-  <si>
-    <t>22:55:25</t>
-  </si>
-  <si>
-    <t>00:31:23</t>
-  </si>
-  <si>
-    <t>02:07:59</t>
-  </si>
-  <si>
-    <t>03:45:02</t>
-  </si>
-  <si>
-    <t>22:03:10</t>
-  </si>
-  <si>
-    <t>23:38:46</t>
-  </si>
-  <si>
-    <t>01:15:16</t>
-  </si>
-  <si>
-    <t>02:52:08</t>
-  </si>
-  <si>
-    <t>22:46:10</t>
-  </si>
-  <si>
-    <t>00:22:30</t>
-  </si>
-  <si>
-    <t>01:59:15</t>
-  </si>
-  <si>
-    <t>21:53:35</t>
-  </si>
-  <si>
-    <t>23:29:42</t>
-  </si>
-  <si>
-    <t>01:06:21</t>
-  </si>
-  <si>
-    <t>21:01:02</t>
-  </si>
-  <si>
-    <t>22:36:52</t>
-  </si>
-  <si>
-    <t>01:34:44</t>
-  </si>
-  <si>
-    <t>03:11:16</t>
+    <t>03:53:18</t>
+  </si>
+  <si>
+    <t>23:47:43</t>
+  </si>
+  <si>
+    <t>01:23:56</t>
+  </si>
+  <si>
+    <t>03:00:38</t>
+  </si>
+  <si>
+    <t>22:55:22</t>
+  </si>
+  <si>
+    <t>00:31:19</t>
+  </si>
+  <si>
+    <t>02:07:55</t>
+  </si>
+  <si>
+    <t>03:44:58</t>
+  </si>
+  <si>
+    <t>22:03:04</t>
+  </si>
+  <si>
+    <t>23:38:41</t>
+  </si>
+  <si>
+    <t>01:15:10</t>
+  </si>
+  <si>
+    <t>02:52:02</t>
+  </si>
+  <si>
+    <t>22:46:02</t>
+  </si>
+  <si>
+    <t>00:22:21</t>
+  </si>
+  <si>
+    <t>01:59:07</t>
+  </si>
+  <si>
+    <t>21:53:23</t>
+  </si>
+  <si>
+    <t>23:29:30</t>
+  </si>
+  <si>
+    <t>01:06:09</t>
+  </si>
+  <si>
+    <t>21:00:47</t>
+  </si>
+  <si>
+    <t>22:36:37</t>
+  </si>
+  <si>
+    <t>00:13:09</t>
+  </si>
+  <si>
+    <t>01:50:07</t>
+  </si>
+  <si>
+    <t>21:43:42</t>
+  </si>
+  <si>
+    <t>23:20:07</t>
   </si>
   <si>
     <t>00:42:25</t>
   </si>
   <si>
-    <t>02:18:44</t>
-  </si>
-  <si>
-    <t>03:55:52</t>
-  </si>
-  <si>
-    <t>23:50:11</t>
-  </si>
-  <si>
-    <t>01:26:11</t>
-  </si>
-  <si>
-    <t>03:03:03</t>
-  </si>
-  <si>
-    <t>22:58:06</t>
-  </si>
-  <si>
-    <t>00:33:37</t>
-  </si>
-  <si>
-    <t>02:10:17</t>
-  </si>
-  <si>
-    <t>03:48:30</t>
-  </si>
-  <si>
-    <t>22:06:28</t>
-  </si>
-  <si>
-    <t>23:41:03</t>
-  </si>
-  <si>
-    <t>01:17:30</t>
-  </si>
-  <si>
-    <t>02:54:53</t>
-  </si>
-  <si>
-    <t>22:48:31</t>
-  </si>
-  <si>
-    <t>00:24:43</t>
-  </si>
-  <si>
-    <t>02:01:44</t>
-  </si>
-  <si>
-    <t>21:56:05</t>
-  </si>
-  <si>
-    <t>23:31:55</t>
-  </si>
-  <si>
-    <t>01:08:42</t>
-  </si>
-  <si>
-    <t>21:03:53</t>
-  </si>
-  <si>
-    <t>22:39:07</t>
-  </si>
-  <si>
-    <t>01:37:34</t>
-  </si>
-  <si>
-    <t>03:14:09</t>
+    <t>02:18:43</t>
+  </si>
+  <si>
+    <t>03:55:51</t>
+  </si>
+  <si>
+    <t>23:50:09</t>
+  </si>
+  <si>
+    <t>01:26:09</t>
+  </si>
+  <si>
+    <t>03:03:01</t>
+  </si>
+  <si>
+    <t>22:58:03</t>
+  </si>
+  <si>
+    <t>00:33:33</t>
+  </si>
+  <si>
+    <t>02:10:13</t>
+  </si>
+  <si>
+    <t>03:48:26</t>
+  </si>
+  <si>
+    <t>22:06:23</t>
+  </si>
+  <si>
+    <t>23:40:57</t>
+  </si>
+  <si>
+    <t>01:17:25</t>
+  </si>
+  <si>
+    <t>02:54:47</t>
+  </si>
+  <si>
+    <t>22:48:23</t>
+  </si>
+  <si>
+    <t>00:24:35</t>
+  </si>
+  <si>
+    <t>02:01:35</t>
+  </si>
+  <si>
+    <t>21:55:54</t>
+  </si>
+  <si>
+    <t>23:31:44</t>
+  </si>
+  <si>
+    <t>01:08:30</t>
+  </si>
+  <si>
+    <t>21:03:38</t>
+  </si>
+  <si>
+    <t>22:38:52</t>
+  </si>
+  <si>
+    <t>00:15:26</t>
+  </si>
+  <si>
+    <t>01:53:12</t>
+  </si>
+  <si>
+    <t>21:46:00</t>
+  </si>
+  <si>
+    <t>23:22:21</t>
   </si>
   <si>
     <t>00:45:06</t>
   </si>
   <si>
-    <t>02:21:40</t>
+    <t>02:21:39</t>
   </si>
   <si>
     <t>03:58:08</t>
   </si>
   <si>
-    <t>23:52:36</t>
-  </si>
-  <si>
-    <t>01:29:07</t>
-  </si>
-  <si>
-    <t>03:05:39</t>
-  </si>
-  <si>
-    <t>23:00:04</t>
-  </si>
-  <si>
-    <t>00:36:29</t>
-  </si>
-  <si>
-    <t>02:13:03</t>
-  </si>
-  <si>
-    <t>03:49:22</t>
-  </si>
-  <si>
-    <t>22:07:30</t>
-  </si>
-  <si>
-    <t>23:43:49</t>
-  </si>
-  <si>
-    <t>01:20:23</t>
-  </si>
-  <si>
-    <t>02:56:48</t>
-  </si>
-  <si>
-    <t>22:51:07</t>
-  </si>
-  <si>
-    <t>00:27:38</t>
-  </si>
-  <si>
-    <t>02:04:07</t>
-  </si>
-  <si>
-    <t>21:58:22</t>
-  </si>
-  <si>
-    <t>23:34:49</t>
-  </si>
-  <si>
-    <t>01:11:21</t>
-  </si>
-  <si>
-    <t>21:05:35</t>
-  </si>
-  <si>
-    <t>22:41:57</t>
-  </si>
-  <si>
-    <t>01:40:25</t>
-  </si>
-  <si>
-    <t>03:17:02</t>
+    <t>23:52:35</t>
+  </si>
+  <si>
+    <t>01:29:05</t>
+  </si>
+  <si>
+    <t>03:05:37</t>
+  </si>
+  <si>
+    <t>23:00:01</t>
+  </si>
+  <si>
+    <t>00:36:26</t>
+  </si>
+  <si>
+    <t>02:12:59</t>
+  </si>
+  <si>
+    <t>03:49:18</t>
+  </si>
+  <si>
+    <t>22:07:25</t>
+  </si>
+  <si>
+    <t>23:43:44</t>
+  </si>
+  <si>
+    <t>01:20:17</t>
+  </si>
+  <si>
+    <t>02:56:42</t>
+  </si>
+  <si>
+    <t>22:50:58</t>
+  </si>
+  <si>
+    <t>00:27:30</t>
+  </si>
+  <si>
+    <t>02:03:58</t>
+  </si>
+  <si>
+    <t>21:58:10</t>
+  </si>
+  <si>
+    <t>23:34:38</t>
+  </si>
+  <si>
+    <t>01:11:09</t>
+  </si>
+  <si>
+    <t>21:05:20</t>
+  </si>
+  <si>
+    <t>22:41:42</t>
+  </si>
+  <si>
+    <t>00:18:14</t>
+  </si>
+  <si>
+    <t>01:54:34</t>
+  </si>
+  <si>
+    <t>21:48:42</t>
+  </si>
+  <si>
+    <t>23:25:13</t>
   </si>
   <si>
     <t>00:47:48</t>
   </si>
   <si>
-    <t>02:24:36</t>
-  </si>
-  <si>
-    <t>04:00:25</t>
-  </si>
-  <si>
-    <t>23:55:02</t>
-  </si>
-  <si>
-    <t>01:32:03</t>
-  </si>
-  <si>
-    <t>03:08:14</t>
-  </si>
-  <si>
-    <t>23:02:03</t>
-  </si>
-  <si>
-    <t>00:39:23</t>
-  </si>
-  <si>
-    <t>02:15:50</t>
-  </si>
-  <si>
-    <t>03:50:15</t>
-  </si>
-  <si>
-    <t>22:08:33</t>
-  </si>
-  <si>
-    <t>23:46:37</t>
-  </si>
-  <si>
-    <t>01:23:16</t>
-  </si>
-  <si>
-    <t>02:58:42</t>
-  </si>
-  <si>
-    <t>22:53:43</t>
-  </si>
-  <si>
-    <t>00:30:34</t>
-  </si>
-  <si>
-    <t>02:06:30</t>
-  </si>
-  <si>
-    <t>22:00:39</t>
-  </si>
-  <si>
-    <t>23:37:44</t>
-  </si>
-  <si>
-    <t>01:14:00</t>
-  </si>
-  <si>
-    <t>21:07:17</t>
-  </si>
-  <si>
-    <t>22:44:48</t>
-  </si>
-  <si>
-    <t>01:42:42</t>
-  </si>
-  <si>
-    <t>03:19:18</t>
-  </si>
-  <si>
-    <t>00:50:09</t>
+    <t>02:24:35</t>
+  </si>
+  <si>
+    <t>04:00:24</t>
+  </si>
+  <si>
+    <t>23:55:01</t>
+  </si>
+  <si>
+    <t>01:32:01</t>
+  </si>
+  <si>
+    <t>03:08:13</t>
+  </si>
+  <si>
+    <t>23:02:00</t>
+  </si>
+  <si>
+    <t>00:39:20</t>
+  </si>
+  <si>
+    <t>02:15:47</t>
+  </si>
+  <si>
+    <t>03:50:11</t>
+  </si>
+  <si>
+    <t>22:08:27</t>
+  </si>
+  <si>
+    <t>23:46:31</t>
+  </si>
+  <si>
+    <t>01:23:10</t>
+  </si>
+  <si>
+    <t>02:58:37</t>
+  </si>
+  <si>
+    <t>22:53:35</t>
+  </si>
+  <si>
+    <t>00:30:25</t>
+  </si>
+  <si>
+    <t>02:06:22</t>
+  </si>
+  <si>
+    <t>22:00:27</t>
+  </si>
+  <si>
+    <t>23:37:32</t>
+  </si>
+  <si>
+    <t>01:13:48</t>
+  </si>
+  <si>
+    <t>21:07:02</t>
+  </si>
+  <si>
+    <t>22:44:32</t>
+  </si>
+  <si>
+    <t>00:21:02</t>
+  </si>
+  <si>
+    <t>01:55:56</t>
+  </si>
+  <si>
+    <t>21:51:25</t>
+  </si>
+  <si>
+    <t>23:28:07</t>
+  </si>
+  <si>
+    <t>00:50:08</t>
   </si>
   <si>
     <t>02:26:50</t>
@@ -520,67 +547,73 @@
     <t>04:02:58</t>
   </si>
   <si>
-    <t>23:57:31</t>
-  </si>
-  <si>
-    <t>01:34:17</t>
-  </si>
-  <si>
-    <t>03:10:38</t>
-  </si>
-  <si>
-    <t>23:04:46</t>
-  </si>
-  <si>
-    <t>00:41:39</t>
-  </si>
-  <si>
-    <t>02:18:08</t>
-  </si>
-  <si>
-    <t>03:53:43</t>
-  </si>
-  <si>
-    <t>22:11:53</t>
-  </si>
-  <si>
-    <t>23:48:55</t>
-  </si>
-  <si>
-    <t>01:25:31</t>
-  </si>
-  <si>
-    <t>03:01:27</t>
-  </si>
-  <si>
-    <t>22:56:06</t>
-  </si>
-  <si>
-    <t>00:32:48</t>
-  </si>
-  <si>
-    <t>02:08:59</t>
-  </si>
-  <si>
-    <t>22:03:11</t>
-  </si>
-  <si>
-    <t>23:39:58</t>
-  </si>
-  <si>
-    <t>01:16:21</t>
-  </si>
-  <si>
-    <t>21:10:09</t>
-  </si>
-  <si>
-    <t>22:47:04</t>
-  </si>
-  <si>
-    <t>2°</t>
-  </si>
-  <si>
-    <t>25°</t>
+    <t>23:57:29</t>
+  </si>
+  <si>
+    <t>01:34:15</t>
+  </si>
+  <si>
+    <t>03:10:36</t>
+  </si>
+  <si>
+    <t>23:04:42</t>
+  </si>
+  <si>
+    <t>00:41:35</t>
+  </si>
+  <si>
+    <t>02:18:05</t>
+  </si>
+  <si>
+    <t>03:53:39</t>
+  </si>
+  <si>
+    <t>22:11:47</t>
+  </si>
+  <si>
+    <t>23:48:49</t>
+  </si>
+  <si>
+    <t>01:25:25</t>
+  </si>
+  <si>
+    <t>03:01:21</t>
+  </si>
+  <si>
+    <t>22:55:57</t>
+  </si>
+  <si>
+    <t>00:32:39</t>
+  </si>
+  <si>
+    <t>02:08:51</t>
+  </si>
+  <si>
+    <t>22:02:59</t>
+  </si>
+  <si>
+    <t>23:39:46</t>
+  </si>
+  <si>
+    <t>01:16:09</t>
+  </si>
+  <si>
+    <t>21:09:54</t>
+  </si>
+  <si>
+    <t>22:46:48</t>
+  </si>
+  <si>
+    <t>00:23:19</t>
+  </si>
+  <si>
+    <t>01:59:01</t>
+  </si>
+  <si>
+    <t>21:53:44</t>
+  </si>
+  <si>
+    <t>23:30:21</t>
   </si>
   <si>
     <t>0°</t>
@@ -604,28 +637,22 @@
     <t>5°</t>
   </si>
   <si>
-    <t>01:42:15</t>
-  </si>
-  <si>
-    <t>03:14:55</t>
-  </si>
-  <si>
     <t>02:24:51</t>
   </si>
   <si>
-    <t>03:57:31</t>
-  </si>
-  <si>
-    <t>03:07:28</t>
-  </si>
-  <si>
-    <t>02:17:27</t>
-  </si>
-  <si>
-    <t>03:50:07</t>
-  </si>
-  <si>
-    <t>03:00:08</t>
+    <t>03:57:30</t>
+  </si>
+  <si>
+    <t>03:07:27</t>
+  </si>
+  <si>
+    <t>02:17:24</t>
+  </si>
+  <si>
+    <t>03:50:04</t>
+  </si>
+  <si>
+    <t>03:00:03</t>
   </si>
   <si>
     <t>B</t>
@@ -674,7 +701,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -689,13 +716,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -707,19 +752,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -731,25 +770,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -761,31 +788,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -803,7 +806,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -844,7 +883,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -919,6 +958,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1322,7 +1367,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1400,55 +1445,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>196</v>
+        <v>70</v>
       </c>
       <c r="L2" s="4">
-        <v>-33.7</v>
+        <v>-40</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="O2" s="6">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="P2" s="7">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="Q2" s="8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R2" s="8">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1456,55 +1501,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="L3" s="4">
-        <v>-20.2</v>
+        <v>-28.1</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="O3" s="9">
-        <v>53</v>
+        <v>215</v>
+      </c>
+      <c r="O3" s="6">
+        <v>100</v>
       </c>
       <c r="P3" s="7">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="Q3" s="8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R3" s="8">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1512,54 +1557,54 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>69</v>
+        <v>208</v>
       </c>
       <c r="L4" s="4">
-        <v>-40</v>
+        <v>-13.6</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O4" s="9">
+        <v>216</v>
+      </c>
+      <c r="O4" s="6">
         <v>100</v>
       </c>
-      <c r="P4" s="10">
-        <v>68</v>
-      </c>
-      <c r="Q4" s="11">
+      <c r="P4" s="7">
+        <v>41</v>
+      </c>
+      <c r="Q4" s="8">
         <v>100</v>
       </c>
-      <c r="R4" s="11">
+      <c r="R4" s="8">
         <v>100</v>
       </c>
     </row>
@@ -1568,55 +1613,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>198</v>
+        <v>73</v>
       </c>
       <c r="L5" s="4">
-        <v>-28.1</v>
+        <v>-44.5</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="O5" s="9">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="P5" s="10">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="Q5" s="11">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="R5" s="11">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1624,55 +1669,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>199</v>
+        <v>74</v>
       </c>
       <c r="L6" s="4">
-        <v>-13.6</v>
+        <v>-35.5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="O6" s="9">
-        <v>100</v>
-      </c>
-      <c r="P6" s="12">
-        <v>77</v>
-      </c>
-      <c r="Q6" s="11">
-        <v>100</v>
+        <v>215</v>
+      </c>
+      <c r="O6" s="6">
+        <v>54</v>
+      </c>
+      <c r="P6" s="10">
+        <v>25</v>
+      </c>
+      <c r="Q6" s="12">
+        <v>45</v>
       </c>
       <c r="R6" s="11">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1680,55 +1725,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>72</v>
+        <v>209</v>
       </c>
       <c r="L7" s="4">
-        <v>-44.5</v>
+        <v>-21.9</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="O7" s="6">
-        <v>31</v>
+        <v>98</v>
       </c>
       <c r="P7" s="13">
-        <v>31</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>0</v>
-      </c>
-      <c r="R7" s="8">
-        <v>0</v>
+        <v>28</v>
+      </c>
+      <c r="Q7" s="14">
+        <v>75</v>
+      </c>
+      <c r="R7" s="15">
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1736,55 +1781,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L8" s="4">
-        <v>-35.5</v>
+        <v>-46.6</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="O8" s="6">
-        <v>43</v>
-      </c>
-      <c r="P8" s="14">
-        <v>43</v>
-      </c>
-      <c r="Q8" s="8">
+        <v>47</v>
+      </c>
+      <c r="P8" s="10">
+        <v>25</v>
+      </c>
+      <c r="Q8" s="16">
+        <v>14</v>
+      </c>
+      <c r="R8" s="11">
         <v>0</v>
-      </c>
-      <c r="R8" s="8">
-        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1792,55 +1837,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>200</v>
+        <v>77</v>
       </c>
       <c r="L9" s="4">
-        <v>-21.9</v>
+        <v>-41.5</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="O9" s="9">
-        <v>49</v>
-      </c>
-      <c r="P9" s="15">
-        <v>36</v>
-      </c>
-      <c r="Q9" s="13">
-        <v>32</v>
-      </c>
-      <c r="R9" s="8">
-        <v>0</v>
+        <v>215</v>
+      </c>
+      <c r="O9" s="6">
+        <v>55</v>
+      </c>
+      <c r="P9" s="12">
+        <v>45</v>
+      </c>
+      <c r="Q9" s="17">
+        <v>8</v>
+      </c>
+      <c r="R9" s="11">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1848,55 +1893,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="L10" s="4">
-        <v>-46.6</v>
+        <v>-29.9</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O10" s="9">
-        <v>65</v>
-      </c>
-      <c r="P10" s="16">
-        <v>23</v>
-      </c>
-      <c r="Q10" s="7">
-        <v>50</v>
-      </c>
-      <c r="R10" s="17">
-        <v>11</v>
+        <v>215</v>
+      </c>
+      <c r="O10" s="6">
+        <v>85</v>
+      </c>
+      <c r="P10" s="18">
+        <v>85</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>0</v>
+      </c>
+      <c r="R10" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1904,55 +1949,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>76</v>
+        <v>211</v>
       </c>
       <c r="L11" s="4">
-        <v>-41.5</v>
+        <v>-15.5</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O11" s="9">
-        <v>58</v>
-      </c>
-      <c r="P11" s="16">
-        <v>26</v>
-      </c>
-      <c r="Q11" s="18">
-        <v>42</v>
-      </c>
-      <c r="R11" s="19">
-        <v>3</v>
+        <v>217</v>
+      </c>
+      <c r="O11" s="6">
+        <v>89</v>
+      </c>
+      <c r="P11" s="19">
+        <v>89</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>0</v>
+      </c>
+      <c r="R11" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1960,54 +2005,54 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>201</v>
+        <v>80</v>
       </c>
       <c r="L12" s="4">
-        <v>-29.8</v>
+        <v>-46.1</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="O12" s="9">
-        <v>67</v>
-      </c>
-      <c r="P12" s="15">
-        <v>33</v>
-      </c>
-      <c r="Q12" s="20">
-        <v>54</v>
-      </c>
-      <c r="R12" s="8">
+        <v>23</v>
+      </c>
+      <c r="P12" s="16">
+        <v>16</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>0</v>
+      </c>
+      <c r="R12" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2016,7 +2061,7 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>51</v>
@@ -2025,46 +2070,46 @@
         <v>66</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>202</v>
+        <v>81</v>
       </c>
       <c r="L13" s="4">
-        <v>-15.5</v>
+        <v>-45.7</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="O13" s="9">
-        <v>55</v>
-      </c>
-      <c r="P13" s="18">
-        <v>38</v>
-      </c>
-      <c r="Q13" s="8">
+        <v>27</v>
+      </c>
+      <c r="P13" s="20">
+        <v>19</v>
+      </c>
+      <c r="Q13" s="11">
         <v>0</v>
       </c>
-      <c r="R13" s="8">
-        <v>0</v>
+      <c r="R13" s="11">
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2072,54 +2117,54 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L14" s="4">
-        <v>-46.1</v>
+        <v>-37.1</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O14" s="21">
-        <v>1</v>
-      </c>
-      <c r="P14" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="8">
+        <v>215</v>
+      </c>
+      <c r="O14" s="9">
+        <v>31</v>
+      </c>
+      <c r="P14" s="10">
+        <v>25</v>
+      </c>
+      <c r="Q14" s="11">
         <v>0</v>
       </c>
-      <c r="R14" s="8">
+      <c r="R14" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2128,54 +2173,54 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>80</v>
+        <v>212</v>
       </c>
       <c r="L15" s="4">
-        <v>-45.7</v>
+        <v>-23.8</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O15" s="21">
-        <v>1</v>
-      </c>
-      <c r="P15" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="8">
+        <v>215</v>
+      </c>
+      <c r="O15" s="9">
+        <v>28</v>
+      </c>
+      <c r="P15" s="20">
+        <v>22</v>
+      </c>
+      <c r="Q15" s="11">
         <v>0</v>
       </c>
-      <c r="R15" s="8">
+      <c r="R15" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2184,55 +2229,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L16" s="4">
-        <v>-37.1</v>
+        <v>-47.4</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O16" s="21">
-        <v>0</v>
-      </c>
-      <c r="P16" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="8">
-        <v>0</v>
-      </c>
-      <c r="R16" s="8">
-        <v>0</v>
+        <v>215</v>
+      </c>
+      <c r="O16" s="6">
+        <v>79</v>
+      </c>
+      <c r="P16" s="21">
+        <v>37</v>
+      </c>
+      <c r="Q16" s="22">
+        <v>52</v>
+      </c>
+      <c r="R16" s="17">
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2240,55 +2285,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
+        <v>30</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L17" s="4">
+        <v>-43</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="O17" s="6">
+        <v>92</v>
+      </c>
+      <c r="P17" s="12">
+        <v>47</v>
+      </c>
+      <c r="Q17" s="18">
+        <v>84</v>
+      </c>
+      <c r="R17" s="16">
         <v>15</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="L17" s="4">
-        <v>-23.8</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O17" s="21">
-        <v>0</v>
-      </c>
-      <c r="P17" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>0</v>
-      </c>
-      <c r="R17" s="8">
-        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2296,55 +2341,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="L18" s="4">
-        <v>-47.4</v>
+        <v>-31.8</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O18" s="9">
-        <v>78</v>
-      </c>
-      <c r="P18" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="22">
-        <v>78</v>
-      </c>
-      <c r="R18" s="15">
-        <v>34</v>
+        <v>215</v>
+      </c>
+      <c r="O18" s="6">
+        <v>99</v>
+      </c>
+      <c r="P18" s="23">
+        <v>59</v>
+      </c>
+      <c r="Q18" s="24">
+        <v>94</v>
+      </c>
+      <c r="R18" s="16">
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2352,55 +2397,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L19" s="4">
-        <v>-42.9</v>
+        <v>-46.4</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O19" s="9">
-        <v>88</v>
-      </c>
-      <c r="P19" s="8">
+        <v>215</v>
+      </c>
+      <c r="O19" s="6">
+        <v>94</v>
+      </c>
+      <c r="P19" s="21">
+        <v>34</v>
+      </c>
+      <c r="Q19" s="11">
         <v>0</v>
       </c>
-      <c r="Q19" s="23">
-        <v>88</v>
-      </c>
-      <c r="R19" s="20">
-        <v>53</v>
+      <c r="R19" s="19">
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2408,55 +2453,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="L20" s="4">
-        <v>-31.8</v>
+        <v>-46.8</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O20" s="9">
-        <v>95</v>
-      </c>
-      <c r="P20" s="24">
-        <v>19</v>
+        <v>215</v>
+      </c>
+      <c r="O20" s="6">
+        <v>93</v>
+      </c>
+      <c r="P20" s="22">
+        <v>51</v>
       </c>
       <c r="Q20" s="25">
-        <v>86</v>
-      </c>
-      <c r="R20" s="10">
-        <v>69</v>
+        <v>5</v>
+      </c>
+      <c r="R20" s="26">
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2464,55 +2509,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
+        <v>23</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="L21" s="4">
+        <v>-38.8</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="O21" s="6">
+        <v>72</v>
+      </c>
+      <c r="P21" s="7">
+        <v>42</v>
+      </c>
+      <c r="Q21" s="20">
         <v>18</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="L21" s="4">
-        <v>-46.4</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O21" s="9">
-        <v>98</v>
-      </c>
-      <c r="P21" s="25">
-        <v>85</v>
-      </c>
-      <c r="Q21" s="17">
-        <v>9</v>
-      </c>
-      <c r="R21" s="25">
-        <v>84</v>
+      <c r="R21" s="13">
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2520,55 +2565,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L22" s="4">
-        <v>-46.8</v>
+        <v>-42.8</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O22" s="9">
-        <v>91</v>
+        <v>217</v>
+      </c>
+      <c r="O22" s="6">
+        <v>100</v>
       </c>
       <c r="P22" s="25">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="Q22" s="8">
-        <v>2</v>
-      </c>
-      <c r="R22" s="22">
-        <v>82</v>
+        <v>100</v>
+      </c>
+      <c r="R22" s="21">
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2576,55 +2621,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="L23" s="4">
-        <v>-38.8</v>
+        <v>-48.1</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O23" s="9">
-        <v>80</v>
-      </c>
-      <c r="P23" s="22">
-        <v>78</v>
+        <v>215</v>
+      </c>
+      <c r="O23" s="6">
+        <v>100</v>
+      </c>
+      <c r="P23" s="11">
+        <v>0</v>
       </c>
       <c r="Q23" s="8">
-        <v>2</v>
-      </c>
-      <c r="R23" s="18">
-        <v>42</v>
+        <v>100</v>
+      </c>
+      <c r="R23" s="20">
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2632,55 +2677,55 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="L24" s="4">
-        <v>-42.9</v>
+        <v>-44.4</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O24" s="9">
-        <v>85</v>
-      </c>
-      <c r="P24" s="13">
-        <v>28</v>
-      </c>
-      <c r="Q24" s="7">
-        <v>50</v>
+        <v>215</v>
+      </c>
+      <c r="O24" s="6">
+        <v>95</v>
+      </c>
+      <c r="P24" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="19">
+        <v>92</v>
       </c>
       <c r="R24" s="15">
-        <v>35</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2688,114 +2733,226 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="L25" s="4">
+        <v>-33.6</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="O25" s="6">
+        <v>93</v>
+      </c>
+      <c r="P25" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="19">
+        <v>88</v>
+      </c>
+      <c r="R25" s="27">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
+      <c r="A26" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="L25" s="4">
-        <v>-48.1</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="O25" s="9">
-        <v>100</v>
-      </c>
-      <c r="P25" s="15">
-        <v>33</v>
-      </c>
-      <c r="Q25" s="20">
-        <v>56</v>
-      </c>
-      <c r="R25" s="15">
-        <v>35</v>
+      <c r="B26" s="2">
+        <v>24</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L26" s="4">
+        <v>-46.6</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="O26" s="6">
+        <v>48</v>
+      </c>
+      <c r="P26" s="10">
+        <v>26</v>
+      </c>
+      <c r="Q26" s="11">
+        <v>0</v>
+      </c>
+      <c r="R26" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
+      <c r="A27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="2">
+        <v>29</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="L27" s="4">
+        <v>-47.9</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="O27" s="6">
+        <v>73</v>
+      </c>
+      <c r="P27" s="10">
+        <v>26</v>
+      </c>
+      <c r="Q27" s="17">
+        <v>12</v>
+      </c>
+      <c r="R27" s="11">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A25">
+  <conditionalFormatting sqref="A2:A27">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B25">
+  <conditionalFormatting sqref="B2:B27">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C25">
+  <conditionalFormatting sqref="C2:C27">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D25">
+  <conditionalFormatting sqref="D2:D27">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E25">
+  <conditionalFormatting sqref="E2:E27">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F25">
+  <conditionalFormatting sqref="F2:F27">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G25">
+  <conditionalFormatting sqref="G2:G27">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H25">
+  <conditionalFormatting sqref="H2:H27">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I25">
+  <conditionalFormatting sqref="I2:I27">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J25">
+  <conditionalFormatting sqref="J2:J27">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K25">
+  <conditionalFormatting sqref="K2:K27">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L25">
+  <conditionalFormatting sqref="L2:L27">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2814,12 +2971,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M25">
+  <conditionalFormatting sqref="M2:M27">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N25">
+  <conditionalFormatting sqref="N2:N27">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2836,22 +2993,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O25">
+  <conditionalFormatting sqref="O2:O27">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P25">
+  <conditionalFormatting sqref="P2:P27">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q25">
+  <conditionalFormatting sqref="Q2:Q27">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R25">
+  <conditionalFormatting sqref="R2:R27">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="208">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261010--01</t>
-  </si>
-  <si>
-    <t>20261010--02</t>
-  </si>
-  <si>
-    <t>20261010--03</t>
-  </si>
-  <si>
-    <t>20261010--04</t>
-  </si>
-  <si>
     <t>20261011--01</t>
   </si>
   <si>
@@ -148,483 +136,471 @@
     <t>20261016--04</t>
   </si>
   <si>
+    <t>20261017--01</t>
+  </si>
+  <si>
+    <t>20261017--02</t>
+  </si>
+  <si>
+    <t>20261017--03</t>
+  </si>
+  <si>
+    <t>05:52</t>
+  </si>
+  <si>
+    <t>05:11</t>
+  </si>
+  <si>
+    <t>03:56</t>
+  </si>
+  <si>
+    <t>05:46</t>
+  </si>
+  <si>
+    <t>05:34</t>
+  </si>
+  <si>
+    <t>01:45</t>
+  </si>
+  <si>
+    <t>02:02</t>
+  </si>
+  <si>
+    <t>05:33</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>03:50</t>
+  </si>
+  <si>
+    <t>05:10</t>
+  </si>
+  <si>
+    <t>05:50</t>
+  </si>
+  <si>
+    <t>04:46</t>
+  </si>
+  <si>
+    <t>04:31</t>
+  </si>
+  <si>
+    <t>05:48</t>
+  </si>
+  <si>
+    <t>05:18</t>
+  </si>
+  <si>
+    <t>03:20</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>05:36</t>
+  </si>
+  <si>
+    <t>02:46</t>
+  </si>
+  <si>
     <t>05:23</t>
   </si>
   <si>
-    <t>05:52</t>
-  </si>
-  <si>
-    <t>04:33</t>
-  </si>
-  <si>
-    <t>04:52</t>
-  </si>
-  <si>
-    <t>05:12</t>
-  </si>
-  <si>
-    <t>03:57</t>
-  </si>
-  <si>
-    <t>05:47</t>
-  </si>
-  <si>
-    <t>05:34</t>
-  </si>
-  <si>
-    <t>01:45</t>
-  </si>
-  <si>
-    <t>02:04</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>03:50</t>
-  </si>
-  <si>
-    <t>05:50</t>
-  </si>
-  <si>
-    <t>04:47</t>
-  </si>
-  <si>
-    <t>05:48</t>
-  </si>
-  <si>
-    <t>05:18</t>
-  </si>
-  <si>
-    <t>03:24</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>05:36</t>
-  </si>
-  <si>
-    <t>02:44</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>05:46</t>
+    <t>04:14</t>
+  </si>
+  <si>
+    <t>04:54</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>02:54</t>
-  </si>
-  <si>
     <t>00:46</t>
   </si>
   <si>
     <t>00:07</t>
   </si>
   <si>
-    <t>00:40:05</t>
-  </si>
-  <si>
-    <t>02:16:30</t>
-  </si>
-  <si>
-    <t>03:53:18</t>
-  </si>
-  <si>
-    <t>23:47:43</t>
-  </si>
-  <si>
-    <t>01:23:56</t>
-  </si>
-  <si>
-    <t>03:00:38</t>
-  </si>
-  <si>
-    <t>22:55:22</t>
-  </si>
-  <si>
-    <t>00:31:19</t>
-  </si>
-  <si>
-    <t>02:07:55</t>
-  </si>
-  <si>
-    <t>03:44:58</t>
-  </si>
-  <si>
-    <t>22:03:04</t>
-  </si>
-  <si>
-    <t>23:38:41</t>
-  </si>
-  <si>
-    <t>01:15:10</t>
-  </si>
-  <si>
-    <t>02:52:02</t>
+    <t>01:23:55</t>
+  </si>
+  <si>
+    <t>03:00:37</t>
+  </si>
+  <si>
+    <t>22:55:18</t>
+  </si>
+  <si>
+    <t>00:31:15</t>
+  </si>
+  <si>
+    <t>02:07:51</t>
+  </si>
+  <si>
+    <t>03:44:53</t>
+  </si>
+  <si>
+    <t>22:02:55</t>
+  </si>
+  <si>
+    <t>23:38:30</t>
+  </si>
+  <si>
+    <t>01:14:59</t>
+  </si>
+  <si>
+    <t>02:51:51</t>
+  </si>
+  <si>
+    <t>22:45:43</t>
+  </si>
+  <si>
+    <t>00:22:02</t>
+  </si>
+  <si>
+    <t>01:58:46</t>
+  </si>
+  <si>
+    <t>21:52:53</t>
+  </si>
+  <si>
+    <t>23:28:59</t>
+  </si>
+  <si>
+    <t>01:05:37</t>
+  </si>
+  <si>
+    <t>21:00:04</t>
+  </si>
+  <si>
+    <t>22:35:52</t>
+  </si>
+  <si>
+    <t>00:12:23</t>
+  </si>
+  <si>
+    <t>01:49:19</t>
+  </si>
+  <si>
+    <t>21:42:40</t>
+  </si>
+  <si>
+    <t>23:19:04</t>
+  </si>
+  <si>
+    <t>00:55:51</t>
+  </si>
+  <si>
+    <t>20:49:26</t>
+  </si>
+  <si>
+    <t>22:25:39</t>
+  </si>
+  <si>
+    <t>01:26:08</t>
+  </si>
+  <si>
+    <t>03:03:00</t>
+  </si>
+  <si>
+    <t>22:57:59</t>
+  </si>
+  <si>
+    <t>00:33:29</t>
+  </si>
+  <si>
+    <t>02:10:08</t>
+  </si>
+  <si>
+    <t>03:48:21</t>
+  </si>
+  <si>
+    <t>22:06:14</t>
+  </si>
+  <si>
+    <t>23:40:47</t>
+  </si>
+  <si>
+    <t>01:17:14</t>
+  </si>
+  <si>
+    <t>02:54:35</t>
+  </si>
+  <si>
+    <t>22:48:05</t>
+  </si>
+  <si>
+    <t>00:24:15</t>
+  </si>
+  <si>
+    <t>02:01:15</t>
+  </si>
+  <si>
+    <t>21:55:25</t>
+  </si>
+  <si>
+    <t>23:31:13</t>
+  </si>
+  <si>
+    <t>01:07:58</t>
+  </si>
+  <si>
+    <t>21:02:56</t>
+  </si>
+  <si>
+    <t>22:38:07</t>
+  </si>
+  <si>
+    <t>00:14:40</t>
+  </si>
+  <si>
+    <t>01:52:24</t>
+  </si>
+  <si>
+    <t>21:44:59</t>
+  </si>
+  <si>
+    <t>23:21:18</t>
+  </si>
+  <si>
+    <t>00:58:28</t>
+  </si>
+  <si>
+    <t>20:51:52</t>
+  </si>
+  <si>
+    <t>22:27:52</t>
+  </si>
+  <si>
+    <t>01:29:04</t>
+  </si>
+  <si>
+    <t>03:05:35</t>
+  </si>
+  <si>
+    <t>22:59:57</t>
+  </si>
+  <si>
+    <t>00:36:21</t>
+  </si>
+  <si>
+    <t>02:12:54</t>
+  </si>
+  <si>
+    <t>03:49:13</t>
+  </si>
+  <si>
+    <t>22:07:15</t>
+  </si>
+  <si>
+    <t>23:43:33</t>
+  </si>
+  <si>
+    <t>01:20:06</t>
+  </si>
+  <si>
+    <t>02:56:30</t>
+  </si>
+  <si>
+    <t>22:50:39</t>
+  </si>
+  <si>
+    <t>00:27:10</t>
+  </si>
+  <si>
+    <t>02:03:38</t>
+  </si>
+  <si>
+    <t>21:57:40</t>
+  </si>
+  <si>
+    <t>23:34:06</t>
+  </si>
+  <si>
+    <t>01:10:37</t>
+  </si>
+  <si>
+    <t>21:04:36</t>
+  </si>
+  <si>
+    <t>22:40:56</t>
+  </si>
+  <si>
+    <t>00:17:28</t>
+  </si>
+  <si>
+    <t>01:53:47</t>
+  </si>
+  <si>
+    <t>21:47:40</t>
+  </si>
+  <si>
+    <t>23:24:11</t>
+  </si>
+  <si>
+    <t>01:00:35</t>
+  </si>
+  <si>
+    <t>20:54:19</t>
+  </si>
+  <si>
+    <t>22:30:46</t>
+  </si>
+  <si>
+    <t>01:32:00</t>
+  </si>
+  <si>
+    <t>03:08:11</t>
+  </si>
+  <si>
+    <t>23:01:55</t>
+  </si>
+  <si>
+    <t>00:39:15</t>
+  </si>
+  <si>
+    <t>02:15:42</t>
+  </si>
+  <si>
+    <t>03:50:06</t>
+  </si>
+  <si>
+    <t>22:08:16</t>
+  </si>
+  <si>
+    <t>23:46:20</t>
+  </si>
+  <si>
+    <t>01:22:59</t>
+  </si>
+  <si>
+    <t>02:58:25</t>
+  </si>
+  <si>
+    <t>22:53:15</t>
+  </si>
+  <si>
+    <t>00:30:05</t>
+  </si>
+  <si>
+    <t>02:06:01</t>
+  </si>
+  <si>
+    <t>21:59:56</t>
+  </si>
+  <si>
+    <t>23:37:01</t>
+  </si>
+  <si>
+    <t>01:13:16</t>
+  </si>
+  <si>
+    <t>21:06:16</t>
+  </si>
+  <si>
+    <t>22:43:47</t>
+  </si>
+  <si>
+    <t>00:20:16</t>
+  </si>
+  <si>
+    <t>01:55:10</t>
+  </si>
+  <si>
+    <t>21:50:22</t>
+  </si>
+  <si>
+    <t>23:27:04</t>
+  </si>
+  <si>
+    <t>01:02:42</t>
+  </si>
+  <si>
+    <t>20:56:46</t>
+  </si>
+  <si>
+    <t>22:33:40</t>
+  </si>
+  <si>
+    <t>01:34:14</t>
+  </si>
+  <si>
+    <t>03:10:35</t>
+  </si>
+  <si>
+    <t>23:04:38</t>
+  </si>
+  <si>
+    <t>00:41:30</t>
+  </si>
+  <si>
+    <t>02:18:00</t>
+  </si>
+  <si>
+    <t>03:53:34</t>
+  </si>
+  <si>
+    <t>22:11:37</t>
+  </si>
+  <si>
+    <t>23:48:38</t>
+  </si>
+  <si>
+    <t>01:25:14</t>
+  </si>
+  <si>
+    <t>03:01:10</t>
+  </si>
+  <si>
+    <t>22:55:38</t>
+  </si>
+  <si>
+    <t>00:32:19</t>
+  </si>
+  <si>
+    <t>02:08:30</t>
+  </si>
+  <si>
+    <t>22:02:28</t>
+  </si>
+  <si>
+    <t>23:39:15</t>
+  </si>
+  <si>
+    <t>01:15:37</t>
+  </si>
+  <si>
+    <t>21:09:09</t>
   </si>
   <si>
     <t>22:46:02</t>
   </si>
   <si>
-    <t>00:22:21</t>
-  </si>
-  <si>
-    <t>01:59:07</t>
-  </si>
-  <si>
-    <t>21:53:23</t>
-  </si>
-  <si>
-    <t>23:29:30</t>
-  </si>
-  <si>
-    <t>01:06:09</t>
-  </si>
-  <si>
-    <t>21:00:47</t>
-  </si>
-  <si>
-    <t>22:36:37</t>
-  </si>
-  <si>
-    <t>00:13:09</t>
-  </si>
-  <si>
-    <t>01:50:07</t>
-  </si>
-  <si>
-    <t>21:43:42</t>
-  </si>
-  <si>
-    <t>23:20:07</t>
-  </si>
-  <si>
-    <t>00:42:25</t>
-  </si>
-  <si>
-    <t>02:18:43</t>
-  </si>
-  <si>
-    <t>03:55:51</t>
-  </si>
-  <si>
-    <t>23:50:09</t>
-  </si>
-  <si>
-    <t>01:26:09</t>
-  </si>
-  <si>
-    <t>03:03:01</t>
-  </si>
-  <si>
-    <t>22:58:03</t>
-  </si>
-  <si>
-    <t>00:33:33</t>
-  </si>
-  <si>
-    <t>02:10:13</t>
-  </si>
-  <si>
-    <t>03:48:26</t>
-  </si>
-  <si>
-    <t>22:06:23</t>
-  </si>
-  <si>
-    <t>23:40:57</t>
-  </si>
-  <si>
-    <t>01:17:25</t>
-  </si>
-  <si>
-    <t>02:54:47</t>
-  </si>
-  <si>
-    <t>22:48:23</t>
-  </si>
-  <si>
-    <t>00:24:35</t>
-  </si>
-  <si>
-    <t>02:01:35</t>
-  </si>
-  <si>
-    <t>21:55:54</t>
-  </si>
-  <si>
-    <t>23:31:44</t>
-  </si>
-  <si>
-    <t>01:08:30</t>
-  </si>
-  <si>
-    <t>21:03:38</t>
-  </si>
-  <si>
-    <t>22:38:52</t>
-  </si>
-  <si>
-    <t>00:15:26</t>
-  </si>
-  <si>
-    <t>01:53:12</t>
-  </si>
-  <si>
-    <t>21:46:00</t>
-  </si>
-  <si>
-    <t>23:22:21</t>
-  </si>
-  <si>
-    <t>00:45:06</t>
-  </si>
-  <si>
-    <t>02:21:39</t>
-  </si>
-  <si>
-    <t>03:58:08</t>
-  </si>
-  <si>
-    <t>23:52:35</t>
-  </si>
-  <si>
-    <t>01:29:05</t>
-  </si>
-  <si>
-    <t>03:05:37</t>
-  </si>
-  <si>
-    <t>23:00:01</t>
-  </si>
-  <si>
-    <t>00:36:26</t>
-  </si>
-  <si>
-    <t>02:12:59</t>
-  </si>
-  <si>
-    <t>03:49:18</t>
-  </si>
-  <si>
-    <t>22:07:25</t>
-  </si>
-  <si>
-    <t>23:43:44</t>
-  </si>
-  <si>
-    <t>01:20:17</t>
-  </si>
-  <si>
-    <t>02:56:42</t>
-  </si>
-  <si>
-    <t>22:50:58</t>
-  </si>
-  <si>
-    <t>00:27:30</t>
-  </si>
-  <si>
-    <t>02:03:58</t>
-  </si>
-  <si>
-    <t>21:58:10</t>
-  </si>
-  <si>
-    <t>23:34:38</t>
-  </si>
-  <si>
-    <t>01:11:09</t>
-  </si>
-  <si>
-    <t>21:05:20</t>
-  </si>
-  <si>
-    <t>22:41:42</t>
-  </si>
-  <si>
-    <t>00:18:14</t>
-  </si>
-  <si>
-    <t>01:54:34</t>
-  </si>
-  <si>
-    <t>21:48:42</t>
-  </si>
-  <si>
-    <t>23:25:13</t>
-  </si>
-  <si>
-    <t>00:47:48</t>
-  </si>
-  <si>
-    <t>02:24:35</t>
-  </si>
-  <si>
-    <t>04:00:24</t>
-  </si>
-  <si>
-    <t>23:55:01</t>
-  </si>
-  <si>
-    <t>01:32:01</t>
-  </si>
-  <si>
-    <t>03:08:13</t>
-  </si>
-  <si>
-    <t>23:02:00</t>
-  </si>
-  <si>
-    <t>00:39:20</t>
-  </si>
-  <si>
-    <t>02:15:47</t>
-  </si>
-  <si>
-    <t>03:50:11</t>
-  </si>
-  <si>
-    <t>22:08:27</t>
-  </si>
-  <si>
-    <t>23:46:31</t>
-  </si>
-  <si>
-    <t>01:23:10</t>
-  </si>
-  <si>
-    <t>02:58:37</t>
-  </si>
-  <si>
-    <t>22:53:35</t>
-  </si>
-  <si>
-    <t>00:30:25</t>
-  </si>
-  <si>
-    <t>02:06:22</t>
-  </si>
-  <si>
-    <t>22:00:27</t>
-  </si>
-  <si>
-    <t>23:37:32</t>
-  </si>
-  <si>
-    <t>01:13:48</t>
-  </si>
-  <si>
-    <t>21:07:02</t>
-  </si>
-  <si>
-    <t>22:44:32</t>
-  </si>
-  <si>
-    <t>00:21:02</t>
-  </si>
-  <si>
-    <t>01:55:56</t>
-  </si>
-  <si>
-    <t>21:51:25</t>
-  </si>
-  <si>
-    <t>23:28:07</t>
-  </si>
-  <si>
-    <t>00:50:08</t>
-  </si>
-  <si>
-    <t>02:26:50</t>
-  </si>
-  <si>
-    <t>04:02:58</t>
-  </si>
-  <si>
-    <t>23:57:29</t>
-  </si>
-  <si>
-    <t>01:34:15</t>
-  </si>
-  <si>
-    <t>03:10:36</t>
-  </si>
-  <si>
-    <t>23:04:42</t>
-  </si>
-  <si>
-    <t>00:41:35</t>
-  </si>
-  <si>
-    <t>02:18:05</t>
-  </si>
-  <si>
-    <t>03:53:39</t>
-  </si>
-  <si>
-    <t>22:11:47</t>
-  </si>
-  <si>
-    <t>23:48:49</t>
-  </si>
-  <si>
-    <t>01:25:25</t>
-  </si>
-  <si>
-    <t>03:01:21</t>
-  </si>
-  <si>
-    <t>22:55:57</t>
-  </si>
-  <si>
-    <t>00:32:39</t>
-  </si>
-  <si>
-    <t>02:08:51</t>
-  </si>
-  <si>
-    <t>22:02:59</t>
-  </si>
-  <si>
-    <t>23:39:46</t>
-  </si>
-  <si>
-    <t>01:16:09</t>
-  </si>
-  <si>
-    <t>21:09:54</t>
-  </si>
-  <si>
-    <t>22:46:48</t>
-  </si>
-  <si>
-    <t>00:23:19</t>
-  </si>
-  <si>
-    <t>01:59:01</t>
-  </si>
-  <si>
-    <t>21:53:44</t>
-  </si>
-  <si>
-    <t>23:30:21</t>
+    <t>00:22:33</t>
+  </si>
+  <si>
+    <t>01:58:14</t>
+  </si>
+  <si>
+    <t>21:52:42</t>
+  </si>
+  <si>
+    <t>23:29:18</t>
+  </si>
+  <si>
+    <t>01:05:18</t>
+  </si>
+  <si>
+    <t>20:59:12</t>
+  </si>
+  <si>
+    <t>22:35:54</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>9°</t>
-  </si>
-  <si>
-    <t>17°</t>
-  </si>
-  <si>
     <t>14°</t>
   </si>
   <si>
@@ -637,22 +613,16 @@
     <t>5°</t>
   </si>
   <si>
-    <t>02:24:51</t>
-  </si>
-  <si>
-    <t>03:57:30</t>
-  </si>
-  <si>
-    <t>03:07:27</t>
-  </si>
-  <si>
-    <t>02:17:24</t>
-  </si>
-  <si>
-    <t>03:50:04</t>
-  </si>
-  <si>
-    <t>03:00:03</t>
+    <t>03:07:25</t>
+  </si>
+  <si>
+    <t>02:17:19</t>
+  </si>
+  <si>
+    <t>03:49:59</t>
+  </si>
+  <si>
+    <t>02:59:52</t>
   </si>
   <si>
     <t>B</t>
@@ -701,7 +671,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -722,13 +692,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -746,7 +722,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -758,25 +740,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FFEEF3F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -788,61 +794,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -883,7 +835,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -955,15 +907,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1367,7 +1310,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R27"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1445,55 +1388,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>66</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L2" s="4">
-        <v>-40</v>
+        <v>-35.5</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="O2" s="6">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="P2" s="7">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="Q2" s="8">
-        <v>100</v>
-      </c>
-      <c r="R2" s="8">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="R2" s="9">
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1501,55 +1444,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="L3" s="4">
-        <v>-28.1</v>
+        <v>-21.9</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O3" s="6">
-        <v>100</v>
-      </c>
-      <c r="P3" s="7">
-        <v>42</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>100</v>
+        <v>206</v>
+      </c>
+      <c r="O3" s="10">
+        <v>16</v>
+      </c>
+      <c r="P3" s="9">
+        <v>38</v>
+      </c>
+      <c r="Q3" s="11">
+        <v>25</v>
       </c>
       <c r="R3" s="8">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1557,55 +1500,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>208</v>
+        <v>71</v>
       </c>
       <c r="L4" s="4">
-        <v>-13.6</v>
+        <v>-46.6</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="O4" s="6">
-        <v>100</v>
-      </c>
-      <c r="P4" s="7">
-        <v>41</v>
-      </c>
-      <c r="Q4" s="8">
-        <v>100</v>
+        <v>49</v>
+      </c>
+      <c r="P4" s="12">
+        <v>19</v>
+      </c>
+      <c r="Q4" s="13">
+        <v>30</v>
       </c>
       <c r="R4" s="8">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1613,54 +1556,54 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>66</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L5" s="4">
-        <v>-44.5</v>
+        <v>-41.5</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O5" s="9">
-        <v>32</v>
-      </c>
-      <c r="P5" s="10">
-        <v>26</v>
-      </c>
-      <c r="Q5" s="11">
-        <v>2</v>
-      </c>
-      <c r="R5" s="11">
+        <v>205</v>
+      </c>
+      <c r="O5" s="6">
+        <v>56</v>
+      </c>
+      <c r="P5" s="14">
+        <v>47</v>
+      </c>
+      <c r="Q5" s="15">
+        <v>16</v>
+      </c>
+      <c r="R5" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1669,55 +1612,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>66</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="J6" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="L6" s="4">
-        <v>-35.5</v>
+        <v>-29.9</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="O6" s="6">
-        <v>54</v>
-      </c>
-      <c r="P6" s="10">
-        <v>25</v>
-      </c>
-      <c r="Q6" s="12">
-        <v>45</v>
-      </c>
-      <c r="R6" s="11">
+        <v>72</v>
+      </c>
+      <c r="P6" s="16">
+        <v>71</v>
+      </c>
+      <c r="Q6" s="8">
         <v>0</v>
+      </c>
+      <c r="R6" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1725,7 +1668,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>48</v>
@@ -1734,46 +1677,46 @@
         <v>68</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L7" s="4">
-        <v>-21.9</v>
+        <v>-15.5</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="O7" s="6">
-        <v>98</v>
-      </c>
-      <c r="P7" s="13">
-        <v>28</v>
-      </c>
-      <c r="Q7" s="14">
-        <v>75</v>
-      </c>
-      <c r="R7" s="15">
-        <v>54</v>
+        <v>91</v>
+      </c>
+      <c r="P7" s="17">
+        <v>89</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>0</v>
+      </c>
+      <c r="R7" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1781,7 +1724,7 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>49</v>
@@ -1790,45 +1733,45 @@
         <v>66</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L8" s="4">
-        <v>-46.6</v>
+        <v>-46.1</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O8" s="6">
-        <v>47</v>
-      </c>
-      <c r="P8" s="10">
-        <v>25</v>
-      </c>
-      <c r="Q8" s="16">
-        <v>14</v>
-      </c>
-      <c r="R8" s="11">
+        <v>207</v>
+      </c>
+      <c r="O8" s="18">
+        <v>0</v>
+      </c>
+      <c r="P8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>0</v>
+      </c>
+      <c r="R8" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1837,7 +1780,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>50</v>
@@ -1846,46 +1789,46 @@
         <v>66</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L9" s="4">
-        <v>-41.5</v>
+        <v>-45.7</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O9" s="6">
-        <v>55</v>
-      </c>
-      <c r="P9" s="12">
-        <v>45</v>
-      </c>
-      <c r="Q9" s="17">
-        <v>8</v>
-      </c>
-      <c r="R9" s="11">
-        <v>1</v>
+        <v>205</v>
+      </c>
+      <c r="O9" s="18">
+        <v>4</v>
+      </c>
+      <c r="P9" s="7">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>0</v>
+      </c>
+      <c r="R9" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1893,7 +1836,7 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>51</v>
@@ -1902,45 +1845,45 @@
         <v>66</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>210</v>
+        <v>77</v>
       </c>
       <c r="L10" s="4">
-        <v>-29.9</v>
+        <v>-37.1</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O10" s="6">
-        <v>85</v>
-      </c>
-      <c r="P10" s="18">
-        <v>85</v>
-      </c>
-      <c r="Q10" s="11">
+        <v>205</v>
+      </c>
+      <c r="O10" s="18">
+        <v>1</v>
+      </c>
+      <c r="P10" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="8">
         <v>0</v>
       </c>
-      <c r="R10" s="11">
+      <c r="R10" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1949,54 +1892,54 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="J11" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="L11" s="4">
+        <v>-23.8</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="N11" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="L11" s="4">
-        <v>-15.5</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O11" s="6">
-        <v>89</v>
-      </c>
-      <c r="P11" s="19">
-        <v>89</v>
-      </c>
-      <c r="Q11" s="11">
+      <c r="O11" s="18">
+        <v>1</v>
+      </c>
+      <c r="P11" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="8">
         <v>0</v>
       </c>
-      <c r="R11" s="11">
+      <c r="R11" s="8">
         <v>0</v>
       </c>
     </row>
@@ -2005,7 +1948,7 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>53</v>
@@ -2014,46 +1957,46 @@
         <v>66</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L12" s="4">
-        <v>-46.1</v>
+        <v>-47.4</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O12" s="9">
-        <v>23</v>
-      </c>
-      <c r="P12" s="16">
-        <v>16</v>
-      </c>
-      <c r="Q12" s="11">
-        <v>0</v>
-      </c>
-      <c r="R12" s="11">
-        <v>0</v>
+        <v>205</v>
+      </c>
+      <c r="O12" s="6">
+        <v>100</v>
+      </c>
+      <c r="P12" s="11">
+        <v>26</v>
+      </c>
+      <c r="Q12" s="19">
+        <v>97</v>
+      </c>
+      <c r="R12" s="20">
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2061,55 +2004,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>66</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L13" s="4">
-        <v>-45.7</v>
+        <v>-43</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O13" s="9">
-        <v>27</v>
-      </c>
-      <c r="P13" s="20">
-        <v>19</v>
-      </c>
-      <c r="Q13" s="11">
-        <v>0</v>
-      </c>
-      <c r="R13" s="11">
-        <v>2</v>
+        <v>205</v>
+      </c>
+      <c r="O13" s="6">
+        <v>100</v>
+      </c>
+      <c r="P13" s="14">
+        <v>45</v>
+      </c>
+      <c r="Q13" s="20">
+        <v>99</v>
+      </c>
+      <c r="R13" s="20">
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2117,55 +2060,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>66</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L14" s="4">
-        <v>-37.1</v>
+        <v>-31.8</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O14" s="9">
-        <v>31</v>
-      </c>
-      <c r="P14" s="10">
-        <v>25</v>
-      </c>
-      <c r="Q14" s="11">
-        <v>0</v>
-      </c>
-      <c r="R14" s="11">
-        <v>0</v>
+        <v>205</v>
+      </c>
+      <c r="O14" s="6">
+        <v>100</v>
+      </c>
+      <c r="P14" s="17">
+        <v>91</v>
+      </c>
+      <c r="Q14" s="17">
+        <v>92</v>
+      </c>
+      <c r="R14" s="20">
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2173,55 +2116,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>66</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>212</v>
+        <v>82</v>
       </c>
       <c r="L15" s="4">
-        <v>-23.8</v>
+        <v>-46.4</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O15" s="9">
-        <v>28</v>
-      </c>
-      <c r="P15" s="20">
-        <v>22</v>
-      </c>
-      <c r="Q15" s="11">
+        <v>205</v>
+      </c>
+      <c r="O15" s="6">
+        <v>52</v>
+      </c>
+      <c r="P15" s="21">
+        <v>49</v>
+      </c>
+      <c r="Q15" s="8">
         <v>0</v>
       </c>
-      <c r="R15" s="11">
-        <v>0</v>
+      <c r="R15" s="9">
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2229,55 +2172,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>66</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L16" s="4">
-        <v>-47.4</v>
+        <v>-46.8</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O16" s="6">
-        <v>79</v>
-      </c>
-      <c r="P16" s="21">
-        <v>37</v>
-      </c>
-      <c r="Q16" s="22">
-        <v>52</v>
-      </c>
-      <c r="R16" s="17">
-        <v>10</v>
+        <v>205</v>
+      </c>
+      <c r="O16" s="18">
+        <v>11</v>
+      </c>
+      <c r="P16" s="7">
+        <v>5</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>0</v>
+      </c>
+      <c r="R16" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2285,55 +2228,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>66</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L17" s="4">
-        <v>-43</v>
+        <v>-38.9</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O17" s="6">
-        <v>92</v>
+        <v>205</v>
+      </c>
+      <c r="O17" s="10">
+        <v>26</v>
       </c>
       <c r="P17" s="12">
-        <v>47</v>
-      </c>
-      <c r="Q17" s="18">
-        <v>84</v>
-      </c>
-      <c r="R17" s="16">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>0</v>
+      </c>
+      <c r="R17" s="7">
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2341,55 +2284,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>66</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L18" s="4">
-        <v>-31.8</v>
+        <v>-42.8</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="O18" s="6">
-        <v>99</v>
-      </c>
-      <c r="P18" s="23">
-        <v>59</v>
-      </c>
-      <c r="Q18" s="24">
-        <v>94</v>
-      </c>
-      <c r="R18" s="16">
-        <v>13</v>
+        <v>58</v>
+      </c>
+      <c r="P18" s="7">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="13">
+        <v>31</v>
+      </c>
+      <c r="R18" s="12">
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2397,55 +2340,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>66</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L19" s="4">
-        <v>-46.4</v>
+        <v>-48.1</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="O19" s="6">
-        <v>94</v>
-      </c>
-      <c r="P19" s="21">
-        <v>34</v>
-      </c>
-      <c r="Q19" s="11">
+        <v>56</v>
+      </c>
+      <c r="P19" s="8">
         <v>0</v>
       </c>
-      <c r="R19" s="19">
-        <v>92</v>
+      <c r="Q19" s="22">
+        <v>35</v>
+      </c>
+      <c r="R19" s="11">
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2453,55 +2396,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>66</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L20" s="4">
-        <v>-46.8</v>
+        <v>-44.5</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="O20" s="6">
-        <v>93</v>
-      </c>
-      <c r="P20" s="22">
-        <v>51</v>
-      </c>
-      <c r="Q20" s="25">
-        <v>5</v>
-      </c>
-      <c r="R20" s="26">
-        <v>78</v>
+        <v>54</v>
+      </c>
+      <c r="P20" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="14">
+        <v>44</v>
+      </c>
+      <c r="R20" s="23">
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2509,55 +2452,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>66</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L21" s="4">
-        <v>-38.8</v>
+        <v>-33.7</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="O21" s="6">
-        <v>72</v>
-      </c>
-      <c r="P21" s="7">
-        <v>42</v>
-      </c>
-      <c r="Q21" s="20">
-        <v>18</v>
-      </c>
-      <c r="R21" s="13">
-        <v>29</v>
+        <v>60</v>
+      </c>
+      <c r="P21" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="21">
+        <v>49</v>
+      </c>
+      <c r="R21" s="23">
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2565,55 +2508,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>66</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I22" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>200</v>
-      </c>
       <c r="K22" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L22" s="4">
-        <v>-42.8</v>
+        <v>-46.5</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="O22" s="6">
-        <v>100</v>
-      </c>
-      <c r="P22" s="25">
-        <v>5</v>
-      </c>
-      <c r="Q22" s="8">
-        <v>100</v>
-      </c>
-      <c r="R22" s="21">
-        <v>33</v>
+        <v>44</v>
+      </c>
+      <c r="P22" s="14">
+        <v>44</v>
+      </c>
+      <c r="Q22" s="13">
+        <v>31</v>
+      </c>
+      <c r="R22" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2621,55 +2564,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>66</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L23" s="4">
-        <v>-48.1</v>
+        <v>-47.9</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="O23" s="6">
-        <v>100</v>
-      </c>
-      <c r="P23" s="11">
+        <v>34</v>
+      </c>
+      <c r="P23" s="22">
+        <v>34</v>
+      </c>
+      <c r="Q23" s="22">
+        <v>34</v>
+      </c>
+      <c r="R23" s="8">
         <v>0</v>
-      </c>
-      <c r="Q23" s="8">
-        <v>100</v>
-      </c>
-      <c r="R23" s="20">
-        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2677,55 +2620,55 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>66</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L24" s="4">
-        <v>-44.4</v>
+        <v>-40.6</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="O24" s="6">
-        <v>95</v>
-      </c>
-      <c r="P24" s="11">
+        <v>32</v>
+      </c>
+      <c r="P24" s="13">
+        <v>32</v>
+      </c>
+      <c r="Q24" s="13">
+        <v>32</v>
+      </c>
+      <c r="R24" s="8">
         <v>0</v>
-      </c>
-      <c r="Q24" s="19">
-        <v>92</v>
-      </c>
-      <c r="R24" s="15">
-        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2733,55 +2676,55 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>66</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L25" s="4">
-        <v>-33.6</v>
+        <v>-42.5</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O25" s="6">
-        <v>93</v>
-      </c>
-      <c r="P25" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="19">
-        <v>88</v>
-      </c>
-      <c r="R25" s="27">
-        <v>65</v>
+        <v>205</v>
+      </c>
+      <c r="O25" s="10">
+        <v>44</v>
+      </c>
+      <c r="P25" s="12">
+        <v>22</v>
+      </c>
+      <c r="Q25" s="8">
+        <v>1</v>
+      </c>
+      <c r="R25" s="9">
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -2789,170 +2732,114 @@
         <v>42</v>
       </c>
       <c r="B26" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>66</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L26" s="4">
-        <v>-46.6</v>
+        <v>-48.7</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="O26" s="6">
-        <v>48</v>
-      </c>
-      <c r="P26" s="10">
-        <v>26</v>
-      </c>
-      <c r="Q26" s="11">
-        <v>0</v>
-      </c>
-      <c r="R26" s="25">
+        <v>80</v>
+      </c>
+      <c r="P26" s="12">
+        <v>21</v>
+      </c>
+      <c r="Q26" s="7">
         <v>6</v>
       </c>
-    </row>
-    <row r="27" spans="1:18">
-      <c r="A27" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="2">
-        <v>29</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="L27" s="4">
-        <v>-47.9</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O27" s="6">
-        <v>73</v>
-      </c>
-      <c r="P27" s="10">
-        <v>26</v>
-      </c>
-      <c r="Q27" s="17">
-        <v>12</v>
-      </c>
-      <c r="R27" s="11">
-        <v>1</v>
+      <c r="R26" s="24">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A27">
+  <conditionalFormatting sqref="A2:A26">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B27">
+  <conditionalFormatting sqref="B2:B26">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C27">
+  <conditionalFormatting sqref="C2:C26">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D27">
+  <conditionalFormatting sqref="D2:D26">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E27">
+  <conditionalFormatting sqref="E2:E26">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F27">
+  <conditionalFormatting sqref="F2:F26">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G27">
+  <conditionalFormatting sqref="G2:G26">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H27">
+  <conditionalFormatting sqref="H2:H26">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I27">
+  <conditionalFormatting sqref="I2:I26">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J27">
+  <conditionalFormatting sqref="J2:J26">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K27">
+  <conditionalFormatting sqref="K2:K26">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L27">
+  <conditionalFormatting sqref="L2:L26">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2971,12 +2858,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M27">
+  <conditionalFormatting sqref="M2:M26">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N27">
+  <conditionalFormatting sqref="N2:N26">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2993,22 +2880,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O27">
+  <conditionalFormatting sqref="O2:O26">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P27">
+  <conditionalFormatting sqref="P2:P26">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q27">
+  <conditionalFormatting sqref="Q2:Q26">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R27">
+  <conditionalFormatting sqref="R2:R26">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="210">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261011--01</t>
-  </si>
-  <si>
-    <t>20261011--02</t>
-  </si>
-  <si>
-    <t>20261011--03</t>
-  </si>
-  <si>
     <t>20261012--01</t>
   </si>
   <si>
@@ -145,30 +136,30 @@
     <t>20261017--03</t>
   </si>
   <si>
-    <t>05:52</t>
-  </si>
-  <si>
-    <t>05:11</t>
-  </si>
-  <si>
-    <t>03:56</t>
+    <t>20261018--01</t>
+  </si>
+  <si>
+    <t>20261018--02</t>
+  </si>
+  <si>
+    <t>20261018--03</t>
+  </si>
+  <si>
+    <t>20261018--04</t>
   </si>
   <si>
     <t>05:46</t>
   </si>
   <si>
-    <t>05:34</t>
-  </si>
-  <si>
-    <t>01:45</t>
+    <t>05:33</t>
+  </si>
+  <si>
+    <t>01:46</t>
   </si>
   <si>
     <t>02:02</t>
   </si>
   <si>
-    <t>05:33</t>
-  </si>
-  <si>
     <t>05:45</t>
   </si>
   <si>
@@ -181,19 +172,19 @@
     <t>05:50</t>
   </si>
   <si>
-    <t>04:46</t>
-  </si>
-  <si>
-    <t>04:31</t>
+    <t>04:47</t>
+  </si>
+  <si>
+    <t>04:32</t>
   </si>
   <si>
     <t>05:48</t>
   </si>
   <si>
-    <t>05:18</t>
-  </si>
-  <si>
-    <t>03:20</t>
+    <t>05:19</t>
+  </si>
+  <si>
+    <t>03:22</t>
   </si>
   <si>
     <t>05:40</t>
@@ -202,109 +193,112 @@
     <t>05:36</t>
   </si>
   <si>
-    <t>02:46</t>
-  </si>
-  <si>
-    <t>05:23</t>
+    <t>02:45</t>
+  </si>
+  <si>
+    <t>05:24</t>
   </si>
   <si>
     <t>04:14</t>
   </si>
   <si>
-    <t>04:54</t>
+    <t>04:56</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>04:06</t>
+  </si>
+  <si>
+    <t>05:44</t>
+  </si>
+  <si>
+    <t>05:26</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>00:46</t>
-  </si>
-  <si>
-    <t>00:07</t>
-  </si>
-  <si>
-    <t>01:23:55</t>
-  </si>
-  <si>
-    <t>03:00:37</t>
-  </si>
-  <si>
-    <t>22:55:18</t>
-  </si>
-  <si>
-    <t>00:31:15</t>
-  </si>
-  <si>
-    <t>02:07:51</t>
-  </si>
-  <si>
-    <t>03:44:53</t>
-  </si>
-  <si>
-    <t>22:02:55</t>
-  </si>
-  <si>
-    <t>23:38:30</t>
-  </si>
-  <si>
-    <t>01:14:59</t>
-  </si>
-  <si>
-    <t>02:51:51</t>
-  </si>
-  <si>
-    <t>22:45:43</t>
-  </si>
-  <si>
-    <t>00:22:02</t>
-  </si>
-  <si>
-    <t>01:58:46</t>
-  </si>
-  <si>
-    <t>21:52:53</t>
-  </si>
-  <si>
-    <t>23:28:59</t>
-  </si>
-  <si>
-    <t>01:05:37</t>
-  </si>
-  <si>
-    <t>21:00:04</t>
-  </si>
-  <si>
-    <t>22:35:52</t>
-  </si>
-  <si>
-    <t>00:12:23</t>
-  </si>
-  <si>
-    <t>01:49:19</t>
-  </si>
-  <si>
-    <t>21:42:40</t>
-  </si>
-  <si>
-    <t>23:19:04</t>
-  </si>
-  <si>
-    <t>00:55:51</t>
-  </si>
-  <si>
-    <t>20:49:26</t>
-  </si>
-  <si>
-    <t>22:25:39</t>
-  </si>
-  <si>
-    <t>01:26:08</t>
-  </si>
-  <si>
-    <t>03:03:00</t>
-  </si>
-  <si>
-    <t>22:57:59</t>
+    <t>00:08</t>
+  </si>
+  <si>
+    <t>00:31:14</t>
+  </si>
+  <si>
+    <t>02:07:50</t>
+  </si>
+  <si>
+    <t>03:44:52</t>
+  </si>
+  <si>
+    <t>22:02:56</t>
+  </si>
+  <si>
+    <t>23:38:31</t>
+  </si>
+  <si>
+    <t>01:15:00</t>
+  </si>
+  <si>
+    <t>02:51:52</t>
+  </si>
+  <si>
+    <t>22:45:47</t>
+  </si>
+  <si>
+    <t>00:22:06</t>
+  </si>
+  <si>
+    <t>01:58:51</t>
+  </si>
+  <si>
+    <t>21:53:02</t>
+  </si>
+  <si>
+    <t>23:29:08</t>
+  </si>
+  <si>
+    <t>01:05:47</t>
+  </si>
+  <si>
+    <t>21:00:19</t>
+  </si>
+  <si>
+    <t>22:36:07</t>
+  </si>
+  <si>
+    <t>00:12:40</t>
+  </si>
+  <si>
+    <t>01:49:36</t>
+  </si>
+  <si>
+    <t>21:43:04</t>
+  </si>
+  <si>
+    <t>23:19:28</t>
+  </si>
+  <si>
+    <t>00:56:16</t>
+  </si>
+  <si>
+    <t>20:50:00</t>
+  </si>
+  <si>
+    <t>22:26:14</t>
+  </si>
+  <si>
+    <t>00:02:54</t>
+  </si>
+  <si>
+    <t>19:56:57</t>
+  </si>
+  <si>
+    <t>21:32:55</t>
+  </si>
+  <si>
+    <t>23:09:30</t>
   </si>
   <si>
     <t>00:33:29</t>
@@ -313,73 +307,76 @@
     <t>02:10:08</t>
   </si>
   <si>
-    <t>03:48:21</t>
-  </si>
-  <si>
-    <t>22:06:14</t>
-  </si>
-  <si>
-    <t>23:40:47</t>
-  </si>
-  <si>
-    <t>01:17:14</t>
-  </si>
-  <si>
-    <t>02:54:35</t>
-  </si>
-  <si>
-    <t>22:48:05</t>
-  </si>
-  <si>
-    <t>00:24:15</t>
-  </si>
-  <si>
-    <t>02:01:15</t>
-  </si>
-  <si>
-    <t>21:55:25</t>
-  </si>
-  <si>
-    <t>23:31:13</t>
-  </si>
-  <si>
-    <t>01:07:58</t>
-  </si>
-  <si>
-    <t>21:02:56</t>
-  </si>
-  <si>
-    <t>22:38:07</t>
-  </si>
-  <si>
-    <t>00:14:40</t>
-  </si>
-  <si>
-    <t>01:52:24</t>
-  </si>
-  <si>
-    <t>21:44:59</t>
-  </si>
-  <si>
-    <t>23:21:18</t>
-  </si>
-  <si>
-    <t>00:58:28</t>
-  </si>
-  <si>
-    <t>20:51:52</t>
-  </si>
-  <si>
-    <t>22:27:52</t>
-  </si>
-  <si>
-    <t>01:29:04</t>
-  </si>
-  <si>
-    <t>03:05:35</t>
-  </si>
-  <si>
-    <t>22:59:57</t>
+    <t>03:48:20</t>
+  </si>
+  <si>
+    <t>22:06:15</t>
+  </si>
+  <si>
+    <t>23:40:48</t>
+  </si>
+  <si>
+    <t>01:17:15</t>
+  </si>
+  <si>
+    <t>02:54:36</t>
+  </si>
+  <si>
+    <t>22:48:09</t>
+  </si>
+  <si>
+    <t>00:24:19</t>
+  </si>
+  <si>
+    <t>02:01:19</t>
+  </si>
+  <si>
+    <t>21:55:33</t>
+  </si>
+  <si>
+    <t>23:31:22</t>
+  </si>
+  <si>
+    <t>01:08:07</t>
+  </si>
+  <si>
+    <t>21:03:10</t>
+  </si>
+  <si>
+    <t>22:38:22</t>
+  </si>
+  <si>
+    <t>00:14:56</t>
+  </si>
+  <si>
+    <t>01:52:41</t>
+  </si>
+  <si>
+    <t>21:45:23</t>
+  </si>
+  <si>
+    <t>23:21:42</t>
+  </si>
+  <si>
+    <t>00:58:53</t>
+  </si>
+  <si>
+    <t>20:52:25</t>
+  </si>
+  <si>
+    <t>22:28:27</t>
+  </si>
+  <si>
+    <t>00:05:19</t>
+  </si>
+  <si>
+    <t>19:59:35</t>
+  </si>
+  <si>
+    <t>21:35:09</t>
+  </si>
+  <si>
+    <t>23:11:48</t>
   </si>
   <si>
     <t>00:36:21</t>
@@ -391,219 +388,234 @@
     <t>03:49:13</t>
   </si>
   <si>
-    <t>22:07:15</t>
-  </si>
-  <si>
-    <t>23:43:33</t>
-  </si>
-  <si>
-    <t>01:20:06</t>
-  </si>
-  <si>
-    <t>02:56:30</t>
-  </si>
-  <si>
-    <t>22:50:39</t>
-  </si>
-  <si>
-    <t>00:27:10</t>
-  </si>
-  <si>
-    <t>02:03:38</t>
-  </si>
-  <si>
-    <t>21:57:40</t>
-  </si>
-  <si>
-    <t>23:34:06</t>
-  </si>
-  <si>
-    <t>01:10:37</t>
-  </si>
-  <si>
-    <t>21:04:36</t>
-  </si>
-  <si>
-    <t>22:40:56</t>
-  </si>
-  <si>
-    <t>00:17:28</t>
-  </si>
-  <si>
-    <t>01:53:47</t>
-  </si>
-  <si>
-    <t>21:47:40</t>
-  </si>
-  <si>
-    <t>23:24:11</t>
-  </si>
-  <si>
-    <t>01:00:35</t>
-  </si>
-  <si>
-    <t>20:54:19</t>
-  </si>
-  <si>
-    <t>22:30:46</t>
-  </si>
-  <si>
-    <t>01:32:00</t>
-  </si>
-  <si>
-    <t>03:08:11</t>
-  </si>
-  <si>
-    <t>23:01:55</t>
+    <t>22:07:16</t>
+  </si>
+  <si>
+    <t>23:43:34</t>
+  </si>
+  <si>
+    <t>01:20:07</t>
+  </si>
+  <si>
+    <t>02:56:31</t>
+  </si>
+  <si>
+    <t>22:50:43</t>
+  </si>
+  <si>
+    <t>00:27:14</t>
+  </si>
+  <si>
+    <t>02:03:42</t>
+  </si>
+  <si>
+    <t>21:57:49</t>
+  </si>
+  <si>
+    <t>23:34:16</t>
+  </si>
+  <si>
+    <t>01:10:47</t>
+  </si>
+  <si>
+    <t>21:04:51</t>
+  </si>
+  <si>
+    <t>22:41:12</t>
+  </si>
+  <si>
+    <t>00:17:44</t>
+  </si>
+  <si>
+    <t>01:54:03</t>
+  </si>
+  <si>
+    <t>21:48:04</t>
+  </si>
+  <si>
+    <t>23:24:35</t>
+  </si>
+  <si>
+    <t>01:01:00</t>
+  </si>
+  <si>
+    <t>20:54:53</t>
+  </si>
+  <si>
+    <t>22:31:20</t>
+  </si>
+  <si>
+    <t>00:07:49</t>
+  </si>
+  <si>
+    <t>20:01:38</t>
+  </si>
+  <si>
+    <t>21:38:01</t>
+  </si>
+  <si>
+    <t>23:14:31</t>
   </si>
   <si>
     <t>00:39:15</t>
   </si>
   <si>
-    <t>02:15:42</t>
+    <t>02:15:41</t>
   </si>
   <si>
     <t>03:50:06</t>
   </si>
   <si>
-    <t>22:08:16</t>
-  </si>
-  <si>
-    <t>23:46:20</t>
-  </si>
-  <si>
-    <t>01:22:59</t>
-  </si>
-  <si>
-    <t>02:58:25</t>
-  </si>
-  <si>
-    <t>22:53:15</t>
-  </si>
-  <si>
-    <t>00:30:05</t>
-  </si>
-  <si>
-    <t>02:06:01</t>
-  </si>
-  <si>
-    <t>21:59:56</t>
-  </si>
-  <si>
-    <t>23:37:01</t>
-  </si>
-  <si>
-    <t>01:13:16</t>
-  </si>
-  <si>
-    <t>21:06:16</t>
-  </si>
-  <si>
-    <t>22:43:47</t>
-  </si>
-  <si>
-    <t>00:20:16</t>
-  </si>
-  <si>
-    <t>01:55:10</t>
-  </si>
-  <si>
-    <t>21:50:22</t>
-  </si>
-  <si>
-    <t>23:27:04</t>
-  </si>
-  <si>
-    <t>01:02:42</t>
-  </si>
-  <si>
-    <t>20:56:46</t>
-  </si>
-  <si>
-    <t>22:33:40</t>
-  </si>
-  <si>
-    <t>01:34:14</t>
-  </si>
-  <si>
-    <t>03:10:35</t>
-  </si>
-  <si>
-    <t>23:04:38</t>
+    <t>22:08:17</t>
+  </si>
+  <si>
+    <t>23:46:21</t>
+  </si>
+  <si>
+    <t>01:23:00</t>
+  </si>
+  <si>
+    <t>02:58:26</t>
+  </si>
+  <si>
+    <t>22:53:19</t>
+  </si>
+  <si>
+    <t>00:30:09</t>
+  </si>
+  <si>
+    <t>02:06:06</t>
+  </si>
+  <si>
+    <t>22:00:05</t>
+  </si>
+  <si>
+    <t>23:37:10</t>
+  </si>
+  <si>
+    <t>01:13:26</t>
+  </si>
+  <si>
+    <t>21:06:32</t>
+  </si>
+  <si>
+    <t>22:44:02</t>
+  </si>
+  <si>
+    <t>00:20:32</t>
+  </si>
+  <si>
+    <t>01:55:26</t>
+  </si>
+  <si>
+    <t>21:50:47</t>
+  </si>
+  <si>
+    <t>23:27:28</t>
+  </si>
+  <si>
+    <t>01:03:07</t>
+  </si>
+  <si>
+    <t>20:57:21</t>
+  </si>
+  <si>
+    <t>22:34:15</t>
+  </si>
+  <si>
+    <t>00:10:19</t>
+  </si>
+  <si>
+    <t>20:03:41</t>
+  </si>
+  <si>
+    <t>21:40:53</t>
+  </si>
+  <si>
+    <t>23:17:14</t>
   </si>
   <si>
     <t>00:41:30</t>
   </si>
   <si>
-    <t>02:18:00</t>
+    <t>02:17:59</t>
   </si>
   <si>
     <t>03:53:34</t>
   </si>
   <si>
-    <t>22:11:37</t>
-  </si>
-  <si>
-    <t>23:48:38</t>
-  </si>
-  <si>
-    <t>01:25:14</t>
-  </si>
-  <si>
-    <t>03:01:10</t>
-  </si>
-  <si>
-    <t>22:55:38</t>
-  </si>
-  <si>
-    <t>00:32:19</t>
-  </si>
-  <si>
-    <t>02:08:30</t>
-  </si>
-  <si>
-    <t>22:02:28</t>
-  </si>
-  <si>
-    <t>23:39:15</t>
-  </si>
-  <si>
-    <t>01:15:37</t>
-  </si>
-  <si>
-    <t>21:09:09</t>
-  </si>
-  <si>
-    <t>22:46:02</t>
-  </si>
-  <si>
-    <t>00:22:33</t>
-  </si>
-  <si>
-    <t>01:58:14</t>
-  </si>
-  <si>
-    <t>21:52:42</t>
-  </si>
-  <si>
-    <t>23:29:18</t>
-  </si>
-  <si>
-    <t>01:05:18</t>
-  </si>
-  <si>
-    <t>20:59:12</t>
-  </si>
-  <si>
-    <t>22:35:54</t>
+    <t>22:11:38</t>
+  </si>
+  <si>
+    <t>23:48:39</t>
+  </si>
+  <si>
+    <t>01:25:15</t>
+  </si>
+  <si>
+    <t>03:01:11</t>
+  </si>
+  <si>
+    <t>22:55:42</t>
+  </si>
+  <si>
+    <t>00:32:23</t>
+  </si>
+  <si>
+    <t>02:08:35</t>
+  </si>
+  <si>
+    <t>22:02:37</t>
+  </si>
+  <si>
+    <t>23:39:24</t>
+  </si>
+  <si>
+    <t>01:15:47</t>
+  </si>
+  <si>
+    <t>21:09:24</t>
+  </si>
+  <si>
+    <t>22:46:18</t>
+  </si>
+  <si>
+    <t>00:22:49</t>
+  </si>
+  <si>
+    <t>01:58:31</t>
+  </si>
+  <si>
+    <t>21:53:06</t>
+  </si>
+  <si>
+    <t>23:29:43</t>
+  </si>
+  <si>
+    <t>01:05:44</t>
+  </si>
+  <si>
+    <t>20:59:46</t>
+  </si>
+  <si>
+    <t>22:36:29</t>
+  </si>
+  <si>
+    <t>00:12:43</t>
+  </si>
+  <si>
+    <t>20:06:20</t>
+  </si>
+  <si>
+    <t>21:43:08</t>
+  </si>
+  <si>
+    <t>23:19:32</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>14°</t>
-  </si>
-  <si>
     <t>3°</t>
   </si>
   <si>
@@ -613,16 +625,13 @@
     <t>5°</t>
   </si>
   <si>
-    <t>03:07:25</t>
-  </si>
-  <si>
     <t>02:17:19</t>
   </si>
   <si>
-    <t>03:49:59</t>
-  </si>
-  <si>
-    <t>02:59:52</t>
+    <t>03:49:58</t>
+  </si>
+  <si>
+    <t>02:59:53</t>
   </si>
   <si>
     <t>B</t>
@@ -632,9 +641,6 @@
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>4</t>
@@ -671,7 +677,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -686,7 +692,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -698,19 +734,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -728,73 +812,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -835,7 +853,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -907,6 +925,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1310,7 +1334,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:R27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1388,55 +1412,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>69</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>69</v>
       </c>
       <c r="L2" s="4">
-        <v>-35.5</v>
+        <v>-41.5</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="O2" s="6">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="P2" s="7">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="Q2" s="8">
+        <v>10</v>
+      </c>
+      <c r="R2" s="9">
         <v>0</v>
-      </c>
-      <c r="R2" s="9">
-        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1444,10 +1468,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>67</v>
@@ -1456,43 +1480,43 @@
         <v>70</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="L3" s="4">
-        <v>-21.9</v>
+        <v>-29.9</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O3" s="10">
-        <v>16</v>
-      </c>
-      <c r="P3" s="9">
-        <v>38</v>
-      </c>
-      <c r="Q3" s="11">
-        <v>25</v>
-      </c>
-      <c r="R3" s="8">
-        <v>1</v>
+        <v>78</v>
+      </c>
+      <c r="P3" s="11">
+        <v>46</v>
+      </c>
+      <c r="Q3" s="9">
+        <v>0</v>
+      </c>
+      <c r="R3" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1500,54 +1524,54 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="K4" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-15.5</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="O4" s="10">
         <v>71</v>
       </c>
-      <c r="L4" s="4">
-        <v>-46.6</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O4" s="6">
-        <v>49</v>
-      </c>
-      <c r="P4" s="12">
-        <v>19</v>
-      </c>
-      <c r="Q4" s="13">
-        <v>30</v>
-      </c>
-      <c r="R4" s="8">
+      <c r="P4" s="11">
+        <v>44</v>
+      </c>
+      <c r="Q4" s="12">
+        <v>5</v>
+      </c>
+      <c r="R4" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1556,55 +1580,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>72</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>72</v>
       </c>
       <c r="L5" s="4">
-        <v>-41.5</v>
+        <v>-46.1</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="O5" s="6">
-        <v>56</v>
-      </c>
-      <c r="P5" s="14">
-        <v>47</v>
-      </c>
-      <c r="Q5" s="15">
-        <v>16</v>
-      </c>
-      <c r="R5" s="8">
+        <v>34</v>
+      </c>
+      <c r="P5" s="13">
+        <v>31</v>
+      </c>
+      <c r="Q5" s="9">
         <v>0</v>
+      </c>
+      <c r="R5" s="9">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1612,55 +1636,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>73</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>200</v>
+        <v>73</v>
       </c>
       <c r="L6" s="4">
-        <v>-29.9</v>
+        <v>-45.7</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="O6" s="6">
-        <v>72</v>
-      </c>
-      <c r="P6" s="16">
-        <v>71</v>
-      </c>
-      <c r="Q6" s="8">
+        <v>36</v>
+      </c>
+      <c r="P6" s="14">
+        <v>34</v>
+      </c>
+      <c r="Q6" s="9">
         <v>0</v>
       </c>
-      <c r="R6" s="8">
-        <v>1</v>
+      <c r="R6" s="9">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1668,54 +1692,54 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>74</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>201</v>
+        <v>74</v>
       </c>
       <c r="L7" s="4">
-        <v>-15.5</v>
+        <v>-37.1</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O7" s="6">
-        <v>91</v>
-      </c>
-      <c r="P7" s="17">
-        <v>89</v>
-      </c>
-      <c r="Q7" s="8">
+        <v>32</v>
+      </c>
+      <c r="P7" s="13">
+        <v>32</v>
+      </c>
+      <c r="Q7" s="9">
         <v>0</v>
       </c>
-      <c r="R7" s="8">
+      <c r="R7" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1724,54 +1748,54 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>75</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>75</v>
+        <v>205</v>
       </c>
       <c r="L8" s="4">
-        <v>-46.1</v>
+        <v>-23.8</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="O8" s="18">
+        <v>208</v>
+      </c>
+      <c r="O8" s="6">
+        <v>14</v>
+      </c>
+      <c r="P8" s="15">
+        <v>14</v>
+      </c>
+      <c r="Q8" s="9">
         <v>0</v>
       </c>
-      <c r="P8" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>0</v>
-      </c>
-      <c r="R8" s="8">
+      <c r="R8" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1780,55 +1804,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>76</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>76</v>
       </c>
       <c r="L9" s="4">
-        <v>-45.7</v>
+        <v>-47.4</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O9" s="18">
+        <v>208</v>
+      </c>
+      <c r="O9" s="10">
+        <v>93</v>
+      </c>
+      <c r="P9" s="16">
+        <v>93</v>
+      </c>
+      <c r="Q9" s="17">
+        <v>87</v>
+      </c>
+      <c r="R9" s="12">
         <v>4</v>
-      </c>
-      <c r="P9" s="7">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>0</v>
-      </c>
-      <c r="R9" s="8">
-        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1836,55 +1860,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>77</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>77</v>
       </c>
       <c r="L10" s="4">
-        <v>-37.1</v>
+        <v>-43</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O10" s="18">
-        <v>1</v>
-      </c>
-      <c r="P10" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>0</v>
-      </c>
-      <c r="R10" s="8">
-        <v>0</v>
+        <v>208</v>
+      </c>
+      <c r="O10" s="10">
+        <v>100</v>
+      </c>
+      <c r="P10" s="18">
+        <v>100</v>
+      </c>
+      <c r="Q10" s="19">
+        <v>65</v>
+      </c>
+      <c r="R10" s="14">
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1892,54 +1916,54 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>78</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>202</v>
+        <v>78</v>
       </c>
       <c r="L11" s="4">
-        <v>-23.8</v>
+        <v>-31.8</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O11" s="18">
-        <v>1</v>
-      </c>
-      <c r="P11" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>0</v>
-      </c>
-      <c r="R11" s="8">
+        <v>208</v>
+      </c>
+      <c r="O11" s="10">
+        <v>100</v>
+      </c>
+      <c r="P11" s="18">
+        <v>100</v>
+      </c>
+      <c r="Q11" s="20">
+        <v>90</v>
+      </c>
+      <c r="R11" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1948,55 +1972,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>79</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>79</v>
       </c>
       <c r="L12" s="4">
-        <v>-47.4</v>
+        <v>-46.4</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O12" s="6">
-        <v>100</v>
-      </c>
-      <c r="P12" s="11">
-        <v>26</v>
-      </c>
-      <c r="Q12" s="19">
-        <v>97</v>
-      </c>
-      <c r="R12" s="20">
-        <v>100</v>
+        <v>208</v>
+      </c>
+      <c r="O12" s="10">
+        <v>69</v>
+      </c>
+      <c r="P12" s="15">
+        <v>15</v>
+      </c>
+      <c r="Q12" s="9">
+        <v>0</v>
+      </c>
+      <c r="R12" s="21">
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2010,49 +2034,49 @@
         <v>54</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>80</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>80</v>
       </c>
       <c r="L13" s="4">
-        <v>-43</v>
+        <v>-46.8</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O13" s="6">
-        <v>100</v>
-      </c>
-      <c r="P13" s="14">
-        <v>45</v>
-      </c>
-      <c r="Q13" s="20">
-        <v>99</v>
-      </c>
-      <c r="R13" s="20">
-        <v>100</v>
+        <v>208</v>
+      </c>
+      <c r="O13" s="10">
+        <v>67</v>
+      </c>
+      <c r="P13" s="15">
+        <v>13</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>0</v>
+      </c>
+      <c r="R13" s="21">
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2060,54 +2084,54 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>81</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>81</v>
       </c>
       <c r="L14" s="4">
-        <v>-31.8</v>
+        <v>-38.8</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O14" s="6">
+        <v>208</v>
+      </c>
+      <c r="O14" s="10">
         <v>100</v>
       </c>
-      <c r="P14" s="17">
-        <v>91</v>
-      </c>
-      <c r="Q14" s="17">
-        <v>92</v>
-      </c>
-      <c r="R14" s="20">
+      <c r="P14" s="15">
+        <v>13</v>
+      </c>
+      <c r="Q14" s="9">
+        <v>0</v>
+      </c>
+      <c r="R14" s="18">
         <v>100</v>
       </c>
     </row>
@@ -2116,55 +2140,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>82</v>
       </c>
       <c r="L15" s="4">
-        <v>-46.4</v>
+        <v>-42.8</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O15" s="6">
-        <v>52</v>
-      </c>
-      <c r="P15" s="21">
+        <v>209</v>
+      </c>
+      <c r="O15" s="10">
+        <v>99</v>
+      </c>
+      <c r="P15" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="22">
         <v>49</v>
       </c>
-      <c r="Q15" s="8">
-        <v>0</v>
-      </c>
-      <c r="R15" s="9">
-        <v>38</v>
+      <c r="R15" s="23">
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2172,55 +2196,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>83</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>83</v>
       </c>
       <c r="L16" s="4">
-        <v>-46.8</v>
+        <v>-48.1</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O16" s="18">
-        <v>11</v>
-      </c>
-      <c r="P16" s="7">
-        <v>5</v>
-      </c>
-      <c r="Q16" s="8">
+        <v>208</v>
+      </c>
+      <c r="O16" s="10">
+        <v>96</v>
+      </c>
+      <c r="P16" s="9">
         <v>0</v>
       </c>
-      <c r="R16" s="7">
-        <v>6</v>
+      <c r="Q16" s="22">
+        <v>50</v>
+      </c>
+      <c r="R16" s="19">
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2228,55 +2252,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>84</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>84</v>
       </c>
       <c r="L17" s="4">
-        <v>-38.9</v>
+        <v>-44.4</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="O17" s="10">
-        <v>26</v>
-      </c>
-      <c r="P17" s="12">
-        <v>20</v>
-      </c>
-      <c r="Q17" s="8">
+        <v>66</v>
+      </c>
+      <c r="P17" s="9">
         <v>0</v>
       </c>
-      <c r="R17" s="7">
-        <v>7</v>
+      <c r="Q17" s="22">
+        <v>52</v>
+      </c>
+      <c r="R17" s="14">
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2284,55 +2308,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>59</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>85</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="K18" s="1" t="s">
         <v>85</v>
       </c>
       <c r="L18" s="4">
-        <v>-42.8</v>
+        <v>-33.7</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="O18" s="6">
-        <v>58</v>
-      </c>
-      <c r="P18" s="7">
-        <v>5</v>
-      </c>
-      <c r="Q18" s="13">
-        <v>31</v>
-      </c>
-      <c r="R18" s="12">
-        <v>18</v>
+        <v>209</v>
+      </c>
+      <c r="O18" s="10">
+        <v>54</v>
+      </c>
+      <c r="P18" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="11">
+        <v>47</v>
+      </c>
+      <c r="R18" s="15">
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2340,55 +2364,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>60</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>86</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>86</v>
       </c>
       <c r="L19" s="4">
-        <v>-48.1</v>
+        <v>-46.6</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O19" s="6">
-        <v>56</v>
-      </c>
-      <c r="P19" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="22">
-        <v>35</v>
-      </c>
-      <c r="R19" s="11">
-        <v>24</v>
+        <v>208</v>
+      </c>
+      <c r="O19" s="10">
+        <v>91</v>
+      </c>
+      <c r="P19" s="9">
+        <v>2</v>
+      </c>
+      <c r="Q19" s="9">
+        <v>2</v>
+      </c>
+      <c r="R19" s="20">
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2396,55 +2420,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>87</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>87</v>
       </c>
       <c r="L20" s="4">
-        <v>-44.5</v>
+        <v>-47.9</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O20" s="6">
-        <v>54</v>
-      </c>
-      <c r="P20" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="14">
-        <v>44</v>
-      </c>
-      <c r="R20" s="23">
-        <v>12</v>
+        <v>208</v>
+      </c>
+      <c r="O20" s="10">
+        <v>100</v>
+      </c>
+      <c r="P20" s="15">
+        <v>14</v>
+      </c>
+      <c r="Q20" s="8">
+        <v>9</v>
+      </c>
+      <c r="R20" s="18">
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2452,55 +2476,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>88</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L21" s="4">
-        <v>-33.7</v>
+        <v>-40.6</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="O21" s="6">
-        <v>60</v>
-      </c>
-      <c r="P21" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q21" s="21">
-        <v>49</v>
-      </c>
-      <c r="R21" s="23">
-        <v>8</v>
+        <v>208</v>
+      </c>
+      <c r="O21" s="10">
+        <v>99</v>
+      </c>
+      <c r="P21" s="14">
+        <v>36</v>
+      </c>
+      <c r="Q21" s="13">
+        <v>31</v>
+      </c>
+      <c r="R21" s="18">
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2508,55 +2532,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>89</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>89</v>
       </c>
       <c r="L22" s="4">
-        <v>-46.5</v>
+        <v>-42.5</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O22" s="6">
-        <v>44</v>
-      </c>
-      <c r="P22" s="14">
-        <v>44</v>
-      </c>
-      <c r="Q22" s="13">
-        <v>31</v>
+        <v>208</v>
+      </c>
+      <c r="O22" s="10">
+        <v>98</v>
+      </c>
+      <c r="P22" s="22">
+        <v>48</v>
+      </c>
+      <c r="Q22" s="24">
+        <v>23</v>
       </c>
       <c r="R22" s="8">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2564,55 +2588,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>90</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>90</v>
       </c>
       <c r="L23" s="4">
-        <v>-47.9</v>
+        <v>-48.7</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O23" s="6">
-        <v>34</v>
-      </c>
-      <c r="P23" s="22">
-        <v>34</v>
-      </c>
-      <c r="Q23" s="22">
-        <v>34</v>
-      </c>
-      <c r="R23" s="8">
-        <v>0</v>
+        <v>208</v>
+      </c>
+      <c r="O23" s="10">
+        <v>99</v>
+      </c>
+      <c r="P23" s="21">
+        <v>53</v>
+      </c>
+      <c r="Q23" s="11">
+        <v>43</v>
+      </c>
+      <c r="R23" s="25">
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2620,55 +2644,55 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>91</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>91</v>
       </c>
       <c r="L24" s="4">
-        <v>-40.6</v>
+        <v>-45.9</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O24" s="6">
-        <v>32</v>
-      </c>
-      <c r="P24" s="13">
-        <v>32</v>
-      </c>
-      <c r="Q24" s="13">
-        <v>32</v>
-      </c>
-      <c r="R24" s="8">
-        <v>0</v>
+        <v>208</v>
+      </c>
+      <c r="O24" s="10">
+        <v>95</v>
+      </c>
+      <c r="P24" s="23">
+        <v>71</v>
+      </c>
+      <c r="Q24" s="14">
+        <v>36</v>
+      </c>
+      <c r="R24" s="14">
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2676,55 +2700,55 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>92</v>
       </c>
       <c r="L25" s="4">
-        <v>-42.5</v>
+        <v>-36.6</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="O25" s="10">
-        <v>44</v>
-      </c>
-      <c r="P25" s="12">
-        <v>22</v>
-      </c>
-      <c r="Q25" s="8">
-        <v>1</v>
-      </c>
-      <c r="R25" s="9">
-        <v>38</v>
+        <v>92</v>
+      </c>
+      <c r="P25" s="19">
+        <v>67</v>
+      </c>
+      <c r="Q25" s="9">
+        <v>0</v>
+      </c>
+      <c r="R25" s="19">
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -2732,114 +2756,170 @@
         <v>42</v>
       </c>
       <c r="B26" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>93</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>93</v>
       </c>
       <c r="L26" s="4">
-        <v>-48.7</v>
+        <v>-46.6</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O26" s="6">
-        <v>80</v>
-      </c>
-      <c r="P26" s="12">
-        <v>21</v>
-      </c>
-      <c r="Q26" s="7">
-        <v>6</v>
-      </c>
-      <c r="R26" s="24">
-        <v>80</v>
+        <v>208</v>
+      </c>
+      <c r="O26" s="10">
+        <v>93</v>
+      </c>
+      <c r="P26" s="21">
+        <v>57</v>
+      </c>
+      <c r="Q26" s="9">
+        <v>1</v>
+      </c>
+      <c r="R26" s="26">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
+      <c r="A27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="2">
+        <v>24</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L27" s="4">
+        <v>-48.9</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="O27" s="10">
+        <v>96</v>
+      </c>
+      <c r="P27" s="22">
+        <v>52</v>
+      </c>
+      <c r="Q27" s="25">
+        <v>19</v>
+      </c>
+      <c r="R27" s="23">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A26">
+  <conditionalFormatting sqref="A2:A27">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B26">
+  <conditionalFormatting sqref="B2:B27">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C26">
+  <conditionalFormatting sqref="C2:C27">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D26">
+  <conditionalFormatting sqref="D2:D27">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E26">
+  <conditionalFormatting sqref="E2:E27">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F26">
+  <conditionalFormatting sqref="F2:F27">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G26">
+  <conditionalFormatting sqref="G2:G27">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H26">
+  <conditionalFormatting sqref="H2:H27">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I26">
+  <conditionalFormatting sqref="I2:I27">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J26">
+  <conditionalFormatting sqref="J2:J27">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K26">
+  <conditionalFormatting sqref="K2:K27">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L26">
+  <conditionalFormatting sqref="L2:L27">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2858,12 +2938,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M26">
+  <conditionalFormatting sqref="M2:M27">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N26">
+  <conditionalFormatting sqref="N2:N27">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2880,22 +2960,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O26">
+  <conditionalFormatting sqref="O2:O27">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P26">
+  <conditionalFormatting sqref="P2:P27">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q26">
+  <conditionalFormatting sqref="Q2:Q27">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R26">
+  <conditionalFormatting sqref="R2:R27">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="197">
   <si>
     <t>Datum</t>
   </si>
@@ -70,21 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261012--01</t>
-  </si>
-  <si>
-    <t>20261012--02</t>
-  </si>
-  <si>
-    <t>20261012--03</t>
-  </si>
-  <si>
-    <t>20261012--04</t>
-  </si>
-  <si>
-    <t>20261012--05</t>
-  </si>
-  <si>
     <t>20261013--01</t>
   </si>
   <si>
@@ -148,16 +133,16 @@
     <t>20261018--04</t>
   </si>
   <si>
-    <t>05:46</t>
-  </si>
-  <si>
-    <t>05:33</t>
-  </si>
-  <si>
-    <t>01:46</t>
-  </si>
-  <si>
-    <t>02:02</t>
+    <t>20261019--01</t>
+  </si>
+  <si>
+    <t>20261019--02</t>
+  </si>
+  <si>
+    <t>20261019--03</t>
+  </si>
+  <si>
+    <t>20261019--04</t>
   </si>
   <si>
     <t>05:45</t>
@@ -172,7 +157,7 @@
     <t>05:50</t>
   </si>
   <si>
-    <t>04:47</t>
+    <t>04:46</t>
   </si>
   <si>
     <t>04:32</t>
@@ -181,28 +166,28 @@
     <t>05:48</t>
   </si>
   <si>
-    <t>05:19</t>
-  </si>
-  <si>
-    <t>03:22</t>
+    <t>05:18</t>
+  </si>
+  <si>
+    <t>03:21</t>
   </si>
   <si>
     <t>05:40</t>
   </si>
   <si>
-    <t>05:36</t>
-  </si>
-  <si>
-    <t>02:45</t>
+    <t>05:37</t>
+  </si>
+  <si>
+    <t>02:46</t>
   </si>
   <si>
     <t>05:24</t>
   </si>
   <si>
-    <t>04:14</t>
-  </si>
-  <si>
-    <t>04:56</t>
+    <t>04:13</t>
+  </si>
+  <si>
+    <t>04:55</t>
   </si>
   <si>
     <t>05:00</t>
@@ -214,30 +199,21 @@
     <t>05:44</t>
   </si>
   <si>
-    <t>05:26</t>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>02:28</t>
+  </si>
+  <si>
+    <t>05:34</t>
+  </si>
+  <si>
+    <t>03:28</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>00:08</t>
-  </si>
-  <si>
-    <t>00:31:14</t>
-  </si>
-  <si>
-    <t>02:07:50</t>
-  </si>
-  <si>
-    <t>03:44:52</t>
-  </si>
-  <si>
-    <t>22:02:56</t>
-  </si>
-  <si>
-    <t>23:38:31</t>
-  </si>
-  <si>
     <t>01:15:00</t>
   </si>
   <si>
@@ -247,397 +223,382 @@
     <t>22:45:47</t>
   </si>
   <si>
-    <t>00:22:06</t>
+    <t>00:22:07</t>
   </si>
   <si>
     <t>01:58:51</t>
   </si>
   <si>
-    <t>21:53:02</t>
-  </si>
-  <si>
-    <t>23:29:08</t>
-  </si>
-  <si>
-    <t>01:05:47</t>
-  </si>
-  <si>
-    <t>21:00:19</t>
-  </si>
-  <si>
-    <t>22:36:07</t>
-  </si>
-  <si>
-    <t>00:12:40</t>
-  </si>
-  <si>
-    <t>01:49:36</t>
-  </si>
-  <si>
-    <t>21:43:04</t>
-  </si>
-  <si>
-    <t>23:19:28</t>
-  </si>
-  <si>
-    <t>00:56:16</t>
+    <t>21:53:04</t>
+  </si>
+  <si>
+    <t>23:29:10</t>
+  </si>
+  <si>
+    <t>01:05:49</t>
+  </si>
+  <si>
+    <t>21:00:23</t>
+  </si>
+  <si>
+    <t>22:36:12</t>
+  </si>
+  <si>
+    <t>00:12:44</t>
+  </si>
+  <si>
+    <t>01:49:41</t>
+  </si>
+  <si>
+    <t>21:43:12</t>
+  </si>
+  <si>
+    <t>23:19:36</t>
+  </si>
+  <si>
+    <t>00:56:24</t>
+  </si>
+  <si>
+    <t>20:50:11</t>
+  </si>
+  <si>
+    <t>22:26:24</t>
+  </si>
+  <si>
+    <t>00:03:06</t>
+  </si>
+  <si>
+    <t>19:57:12</t>
+  </si>
+  <si>
+    <t>21:33:10</t>
+  </si>
+  <si>
+    <t>23:09:45</t>
+  </si>
+  <si>
+    <t>19:04:16</t>
+  </si>
+  <si>
+    <t>20:39:54</t>
+  </si>
+  <si>
+    <t>22:16:22</t>
+  </si>
+  <si>
+    <t>23:53:14</t>
+  </si>
+  <si>
+    <t>01:17:15</t>
+  </si>
+  <si>
+    <t>02:54:36</t>
+  </si>
+  <si>
+    <t>22:48:09</t>
+  </si>
+  <si>
+    <t>00:24:20</t>
+  </si>
+  <si>
+    <t>02:01:20</t>
+  </si>
+  <si>
+    <t>21:55:35</t>
+  </si>
+  <si>
+    <t>23:31:24</t>
+  </si>
+  <si>
+    <t>01:08:10</t>
+  </si>
+  <si>
+    <t>21:03:15</t>
+  </si>
+  <si>
+    <t>22:38:27</t>
+  </si>
+  <si>
+    <t>00:15:00</t>
+  </si>
+  <si>
+    <t>01:52:45</t>
+  </si>
+  <si>
+    <t>21:45:30</t>
+  </si>
+  <si>
+    <t>23:21:50</t>
+  </si>
+  <si>
+    <t>00:59:01</t>
+  </si>
+  <si>
+    <t>20:52:36</t>
+  </si>
+  <si>
+    <t>22:28:38</t>
+  </si>
+  <si>
+    <t>00:05:30</t>
+  </si>
+  <si>
+    <t>19:59:50</t>
+  </si>
+  <si>
+    <t>21:35:24</t>
+  </si>
+  <si>
+    <t>23:12:04</t>
+  </si>
+  <si>
+    <t>19:07:25</t>
+  </si>
+  <si>
+    <t>20:42:10</t>
+  </si>
+  <si>
+    <t>22:18:37</t>
+  </si>
+  <si>
+    <t>23:56:04</t>
+  </si>
+  <si>
+    <t>01:20:07</t>
+  </si>
+  <si>
+    <t>02:56:31</t>
+  </si>
+  <si>
+    <t>22:50:44</t>
+  </si>
+  <si>
+    <t>00:27:15</t>
+  </si>
+  <si>
+    <t>02:03:43</t>
+  </si>
+  <si>
+    <t>21:57:51</t>
+  </si>
+  <si>
+    <t>23:34:18</t>
+  </si>
+  <si>
+    <t>01:10:49</t>
+  </si>
+  <si>
+    <t>21:04:55</t>
+  </si>
+  <si>
+    <t>22:41:16</t>
+  </si>
+  <si>
+    <t>00:17:48</t>
+  </si>
+  <si>
+    <t>01:54:08</t>
+  </si>
+  <si>
+    <t>21:48:12</t>
+  </si>
+  <si>
+    <t>23:24:42</t>
+  </si>
+  <si>
+    <t>01:01:07</t>
+  </si>
+  <si>
+    <t>20:55:03</t>
+  </si>
+  <si>
+    <t>22:31:31</t>
+  </si>
+  <si>
+    <t>00:08:00</t>
+  </si>
+  <si>
+    <t>20:01:52</t>
+  </si>
+  <si>
+    <t>21:38:16</t>
+  </si>
+  <si>
+    <t>23:14:46</t>
+  </si>
+  <si>
+    <t>19:08:39</t>
+  </si>
+  <si>
+    <t>20:44:57</t>
+  </si>
+  <si>
+    <t>22:21:27</t>
+  </si>
+  <si>
+    <t>23:57:48</t>
+  </si>
+  <si>
+    <t>01:23:00</t>
+  </si>
+  <si>
+    <t>02:58:26</t>
+  </si>
+  <si>
+    <t>22:53:19</t>
+  </si>
+  <si>
+    <t>00:30:10</t>
+  </si>
+  <si>
+    <t>02:06:06</t>
+  </si>
+  <si>
+    <t>22:00:07</t>
+  </si>
+  <si>
+    <t>23:37:12</t>
+  </si>
+  <si>
+    <t>01:13:28</t>
+  </si>
+  <si>
+    <t>21:06:36</t>
+  </si>
+  <si>
+    <t>22:44:07</t>
+  </si>
+  <si>
+    <t>00:20:37</t>
+  </si>
+  <si>
+    <t>01:55:31</t>
+  </si>
+  <si>
+    <t>21:50:54</t>
+  </si>
+  <si>
+    <t>23:27:35</t>
+  </si>
+  <si>
+    <t>01:03:14</t>
+  </si>
+  <si>
+    <t>20:57:31</t>
+  </si>
+  <si>
+    <t>22:34:26</t>
+  </si>
+  <si>
+    <t>00:10:30</t>
+  </si>
+  <si>
+    <t>20:03:56</t>
+  </si>
+  <si>
+    <t>21:41:08</t>
+  </si>
+  <si>
+    <t>23:17:29</t>
+  </si>
+  <si>
+    <t>19:09:53</t>
+  </si>
+  <si>
+    <t>20:47:44</t>
+  </si>
+  <si>
+    <t>22:24:17</t>
+  </si>
+  <si>
+    <t>23:59:32</t>
+  </si>
+  <si>
+    <t>01:25:15</t>
+  </si>
+  <si>
+    <t>03:01:11</t>
+  </si>
+  <si>
+    <t>22:55:42</t>
+  </si>
+  <si>
+    <t>00:32:24</t>
+  </si>
+  <si>
+    <t>02:08:35</t>
+  </si>
+  <si>
+    <t>22:02:39</t>
+  </si>
+  <si>
+    <t>23:39:26</t>
+  </si>
+  <si>
+    <t>01:15:49</t>
+  </si>
+  <si>
+    <t>21:09:28</t>
+  </si>
+  <si>
+    <t>22:46:22</t>
+  </si>
+  <si>
+    <t>00:22:53</t>
+  </si>
+  <si>
+    <t>01:58:35</t>
+  </si>
+  <si>
+    <t>21:53:13</t>
+  </si>
+  <si>
+    <t>23:29:50</t>
+  </si>
+  <si>
+    <t>01:05:51</t>
+  </si>
+  <si>
+    <t>20:59:57</t>
+  </si>
+  <si>
+    <t>22:36:40</t>
+  </si>
+  <si>
+    <t>00:12:55</t>
+  </si>
+  <si>
+    <t>20:06:34</t>
+  </si>
+  <si>
+    <t>21:43:23</t>
+  </si>
+  <si>
+    <t>23:19:48</t>
+  </si>
+  <si>
+    <t>19:13:03</t>
   </si>
   <si>
     <t>20:50:00</t>
   </si>
   <si>
-    <t>22:26:14</t>
-  </si>
-  <si>
-    <t>00:02:54</t>
-  </si>
-  <si>
-    <t>19:56:57</t>
-  </si>
-  <si>
-    <t>21:32:55</t>
-  </si>
-  <si>
-    <t>23:09:30</t>
-  </si>
-  <si>
-    <t>00:33:29</t>
-  </si>
-  <si>
-    <t>02:10:08</t>
-  </si>
-  <si>
-    <t>03:48:20</t>
-  </si>
-  <si>
-    <t>22:06:15</t>
-  </si>
-  <si>
-    <t>23:40:48</t>
-  </si>
-  <si>
-    <t>01:17:15</t>
-  </si>
-  <si>
-    <t>02:54:36</t>
-  </si>
-  <si>
-    <t>22:48:09</t>
-  </si>
-  <si>
-    <t>00:24:19</t>
-  </si>
-  <si>
-    <t>02:01:19</t>
-  </si>
-  <si>
-    <t>21:55:33</t>
-  </si>
-  <si>
-    <t>23:31:22</t>
-  </si>
-  <si>
-    <t>01:08:07</t>
-  </si>
-  <si>
-    <t>21:03:10</t>
-  </si>
-  <si>
-    <t>22:38:22</t>
-  </si>
-  <si>
-    <t>00:14:56</t>
-  </si>
-  <si>
-    <t>01:52:41</t>
-  </si>
-  <si>
-    <t>21:45:23</t>
-  </si>
-  <si>
-    <t>23:21:42</t>
-  </si>
-  <si>
-    <t>00:58:53</t>
-  </si>
-  <si>
-    <t>20:52:25</t>
-  </si>
-  <si>
-    <t>22:28:27</t>
-  </si>
-  <si>
-    <t>00:05:19</t>
-  </si>
-  <si>
-    <t>19:59:35</t>
-  </si>
-  <si>
-    <t>21:35:09</t>
-  </si>
-  <si>
-    <t>23:11:48</t>
-  </si>
-  <si>
-    <t>00:36:21</t>
-  </si>
-  <si>
-    <t>02:12:54</t>
-  </si>
-  <si>
-    <t>03:49:13</t>
-  </si>
-  <si>
-    <t>22:07:16</t>
-  </si>
-  <si>
-    <t>23:43:34</t>
-  </si>
-  <si>
-    <t>01:20:07</t>
-  </si>
-  <si>
-    <t>02:56:31</t>
-  </si>
-  <si>
-    <t>22:50:43</t>
-  </si>
-  <si>
-    <t>00:27:14</t>
-  </si>
-  <si>
-    <t>02:03:42</t>
-  </si>
-  <si>
-    <t>21:57:49</t>
-  </si>
-  <si>
-    <t>23:34:16</t>
-  </si>
-  <si>
-    <t>01:10:47</t>
-  </si>
-  <si>
-    <t>21:04:51</t>
-  </si>
-  <si>
-    <t>22:41:12</t>
-  </si>
-  <si>
-    <t>00:17:44</t>
-  </si>
-  <si>
-    <t>01:54:03</t>
-  </si>
-  <si>
-    <t>21:48:04</t>
-  </si>
-  <si>
-    <t>23:24:35</t>
-  </si>
-  <si>
-    <t>01:01:00</t>
-  </si>
-  <si>
-    <t>20:54:53</t>
-  </si>
-  <si>
-    <t>22:31:20</t>
-  </si>
-  <si>
-    <t>00:07:49</t>
-  </si>
-  <si>
-    <t>20:01:38</t>
-  </si>
-  <si>
-    <t>21:38:01</t>
-  </si>
-  <si>
-    <t>23:14:31</t>
-  </si>
-  <si>
-    <t>00:39:15</t>
-  </si>
-  <si>
-    <t>02:15:41</t>
-  </si>
-  <si>
-    <t>03:50:06</t>
-  </si>
-  <si>
-    <t>22:08:17</t>
-  </si>
-  <si>
-    <t>23:46:21</t>
-  </si>
-  <si>
-    <t>01:23:00</t>
-  </si>
-  <si>
-    <t>02:58:26</t>
-  </si>
-  <si>
-    <t>22:53:19</t>
-  </si>
-  <si>
-    <t>00:30:09</t>
-  </si>
-  <si>
-    <t>02:06:06</t>
-  </si>
-  <si>
-    <t>22:00:05</t>
-  </si>
-  <si>
-    <t>23:37:10</t>
-  </si>
-  <si>
-    <t>01:13:26</t>
-  </si>
-  <si>
-    <t>21:06:32</t>
-  </si>
-  <si>
-    <t>22:44:02</t>
-  </si>
-  <si>
-    <t>00:20:32</t>
-  </si>
-  <si>
-    <t>01:55:26</t>
-  </si>
-  <si>
-    <t>21:50:47</t>
-  </si>
-  <si>
-    <t>23:27:28</t>
-  </si>
-  <si>
-    <t>01:03:07</t>
-  </si>
-  <si>
-    <t>20:57:21</t>
-  </si>
-  <si>
-    <t>22:34:15</t>
-  </si>
-  <si>
-    <t>00:10:19</t>
-  </si>
-  <si>
-    <t>20:03:41</t>
-  </si>
-  <si>
-    <t>21:40:53</t>
-  </si>
-  <si>
-    <t>23:17:14</t>
-  </si>
-  <si>
-    <t>00:41:30</t>
-  </si>
-  <si>
-    <t>02:17:59</t>
-  </si>
-  <si>
-    <t>03:53:34</t>
-  </si>
-  <si>
-    <t>22:11:38</t>
-  </si>
-  <si>
-    <t>23:48:39</t>
-  </si>
-  <si>
-    <t>01:25:15</t>
-  </si>
-  <si>
-    <t>03:01:11</t>
-  </si>
-  <si>
-    <t>22:55:42</t>
-  </si>
-  <si>
-    <t>00:32:23</t>
-  </si>
-  <si>
-    <t>02:08:35</t>
-  </si>
-  <si>
-    <t>22:02:37</t>
-  </si>
-  <si>
-    <t>23:39:24</t>
-  </si>
-  <si>
-    <t>01:15:47</t>
-  </si>
-  <si>
-    <t>21:09:24</t>
-  </si>
-  <si>
-    <t>22:46:18</t>
-  </si>
-  <si>
-    <t>00:22:49</t>
-  </si>
-  <si>
-    <t>01:58:31</t>
-  </si>
-  <si>
-    <t>21:53:06</t>
-  </si>
-  <si>
-    <t>23:29:43</t>
-  </si>
-  <si>
-    <t>01:05:44</t>
-  </si>
-  <si>
-    <t>20:59:46</t>
-  </si>
-  <si>
-    <t>22:36:29</t>
-  </si>
-  <si>
-    <t>00:12:43</t>
-  </si>
-  <si>
-    <t>20:06:20</t>
-  </si>
-  <si>
-    <t>21:43:08</t>
-  </si>
-  <si>
-    <t>23:19:32</t>
+    <t>22:26:33</t>
+  </si>
+  <si>
+    <t>00:02:22</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>3°</t>
-  </si>
-  <si>
-    <t>10°</t>
-  </si>
-  <si>
     <t>5°</t>
   </si>
   <si>
-    <t>02:17:19</t>
-  </si>
-  <si>
-    <t>03:49:58</t>
-  </si>
-  <si>
-    <t>02:59:53</t>
+    <t>02:59:52</t>
   </si>
   <si>
     <t>B</t>
-  </si>
-  <si>
-    <t>A+B</t>
   </si>
   <si>
     <t>3</t>
@@ -677,7 +638,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -692,13 +653,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -710,13 +671,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -728,7 +707,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -740,67 +767,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -812,7 +779,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -853,7 +820,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -931,6 +898,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1334,7 +1304,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R27"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1412,55 +1382,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L2" s="4">
-        <v>-41.5</v>
+        <v>-37.1</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="O2" s="6">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="P2" s="7">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="Q2" s="8">
-        <v>10</v>
-      </c>
-      <c r="R2" s="9">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="R2" s="8">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1468,55 +1438,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="F3" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="L3" s="4">
-        <v>-29.9</v>
+        <v>-23.8</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O3" s="10">
-        <v>78</v>
-      </c>
-      <c r="P3" s="11">
-        <v>46</v>
-      </c>
-      <c r="Q3" s="9">
+        <v>195</v>
+      </c>
+      <c r="O3" s="9">
+        <v>12</v>
+      </c>
+      <c r="P3" s="10">
+        <v>61</v>
+      </c>
+      <c r="Q3" s="11">
         <v>0</v>
       </c>
-      <c r="R3" s="9">
-        <v>0</v>
+      <c r="R3" s="11">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1524,55 +1494,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="F4" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-47.4</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="O4" s="6">
+        <v>100</v>
+      </c>
+      <c r="P4" s="12">
         <v>97</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-15.5</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="O4" s="10">
-        <v>71</v>
-      </c>
-      <c r="P4" s="11">
-        <v>44</v>
-      </c>
-      <c r="Q4" s="12">
-        <v>5</v>
-      </c>
-      <c r="R4" s="9">
-        <v>0</v>
+      <c r="Q4" s="13">
+        <v>100</v>
+      </c>
+      <c r="R4" s="12">
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1580,55 +1550,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="L5" s="4">
-        <v>-46.1</v>
+        <v>-43</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="O5" s="6">
-        <v>34</v>
-      </c>
-      <c r="P5" s="13">
-        <v>31</v>
-      </c>
-      <c r="Q5" s="9">
-        <v>0</v>
-      </c>
-      <c r="R5" s="9">
-        <v>2</v>
+        <v>97</v>
+      </c>
+      <c r="P5" s="12">
+        <v>94</v>
+      </c>
+      <c r="Q5" s="12">
+        <v>93</v>
+      </c>
+      <c r="R5" s="14">
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1636,55 +1606,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="L6" s="4">
-        <v>-45.7</v>
+        <v>-31.8</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="O6" s="6">
-        <v>36</v>
-      </c>
-      <c r="P6" s="14">
-        <v>34</v>
-      </c>
-      <c r="Q6" s="9">
+        <v>86</v>
+      </c>
+      <c r="P6" s="15">
+        <v>80</v>
+      </c>
+      <c r="Q6" s="16">
+        <v>50</v>
+      </c>
+      <c r="R6" s="11">
         <v>0</v>
-      </c>
-      <c r="R6" s="9">
-        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1692,55 +1662,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L7" s="4">
-        <v>-37.1</v>
+        <v>-46.4</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="O7" s="6">
-        <v>32</v>
-      </c>
-      <c r="P7" s="13">
-        <v>32</v>
-      </c>
-      <c r="Q7" s="9">
+        <v>66</v>
+      </c>
+      <c r="P7" s="8">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="11">
         <v>0</v>
       </c>
-      <c r="R7" s="9">
-        <v>0</v>
+      <c r="R7" s="16">
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1748,55 +1718,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>205</v>
+        <v>72</v>
       </c>
       <c r="L8" s="4">
-        <v>-23.8</v>
+        <v>-46.8</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="O8" s="6">
-        <v>14</v>
-      </c>
-      <c r="P8" s="15">
-        <v>14</v>
-      </c>
-      <c r="Q8" s="9">
+        <v>90</v>
+      </c>
+      <c r="P8" s="17">
+        <v>13</v>
+      </c>
+      <c r="Q8" s="11">
         <v>0</v>
       </c>
-      <c r="R8" s="9">
-        <v>0</v>
+      <c r="R8" s="18">
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1804,55 +1774,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L9" s="4">
-        <v>-47.4</v>
+        <v>-38.8</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O9" s="10">
-        <v>93</v>
-      </c>
-      <c r="P9" s="16">
-        <v>93</v>
-      </c>
-      <c r="Q9" s="17">
-        <v>87</v>
-      </c>
-      <c r="R9" s="12">
-        <v>4</v>
+        <v>195</v>
+      </c>
+      <c r="O9" s="6">
+        <v>63</v>
+      </c>
+      <c r="P9" s="19">
+        <v>6</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>0</v>
+      </c>
+      <c r="R9" s="7">
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1860,55 +1830,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L10" s="4">
-        <v>-43</v>
+        <v>-42.8</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O10" s="10">
-        <v>100</v>
-      </c>
-      <c r="P10" s="18">
-        <v>100</v>
-      </c>
-      <c r="Q10" s="19">
-        <v>65</v>
-      </c>
-      <c r="R10" s="14">
-        <v>36</v>
+        <v>196</v>
+      </c>
+      <c r="O10" s="6">
+        <v>91</v>
+      </c>
+      <c r="P10" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="20">
+        <v>88</v>
+      </c>
+      <c r="R10" s="7">
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1916,55 +1886,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L11" s="4">
-        <v>-31.8</v>
+        <v>-48.1</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O11" s="10">
-        <v>100</v>
-      </c>
-      <c r="P11" s="18">
-        <v>100</v>
-      </c>
-      <c r="Q11" s="20">
-        <v>90</v>
-      </c>
-      <c r="R11" s="9">
+        <v>195</v>
+      </c>
+      <c r="O11" s="6">
+        <v>81</v>
+      </c>
+      <c r="P11" s="11">
         <v>0</v>
+      </c>
+      <c r="Q11" s="21">
+        <v>68</v>
+      </c>
+      <c r="R11" s="7">
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1972,55 +1942,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="L12" s="4">
-        <v>-46.4</v>
+        <v>-44.4</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O12" s="10">
-        <v>69</v>
-      </c>
-      <c r="P12" s="15">
-        <v>15</v>
-      </c>
-      <c r="Q12" s="9">
+        <v>195</v>
+      </c>
+      <c r="O12" s="22">
+        <v>48</v>
+      </c>
+      <c r="P12" s="11">
         <v>0</v>
       </c>
-      <c r="R12" s="21">
-        <v>54</v>
+      <c r="Q12" s="19">
+        <v>4</v>
+      </c>
+      <c r="R12" s="16">
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2028,55 +1998,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L13" s="4">
-        <v>-46.8</v>
+        <v>-33.7</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O13" s="10">
-        <v>67</v>
-      </c>
-      <c r="P13" s="15">
-        <v>13</v>
-      </c>
-      <c r="Q13" s="9">
+        <v>196</v>
+      </c>
+      <c r="O13" s="6">
+        <v>75</v>
+      </c>
+      <c r="P13" s="11">
         <v>0</v>
       </c>
-      <c r="R13" s="21">
-        <v>54</v>
+      <c r="Q13" s="11">
+        <v>0</v>
+      </c>
+      <c r="R13" s="23">
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2084,55 +2054,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="L14" s="4">
-        <v>-38.8</v>
+        <v>-46.6</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O14" s="10">
-        <v>100</v>
-      </c>
-      <c r="P14" s="15">
-        <v>13</v>
-      </c>
-      <c r="Q14" s="9">
+        <v>195</v>
+      </c>
+      <c r="O14" s="6">
+        <v>70</v>
+      </c>
+      <c r="P14" s="11">
         <v>0</v>
       </c>
-      <c r="R14" s="18">
-        <v>100</v>
+      <c r="Q14" s="21">
+        <v>70</v>
+      </c>
+      <c r="R14" s="24">
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2140,55 +2110,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L15" s="4">
-        <v>-42.8</v>
+        <v>-47.9</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="O15" s="10">
-        <v>99</v>
-      </c>
-      <c r="P15" s="9">
+        <v>195</v>
+      </c>
+      <c r="O15" s="6">
+        <v>72</v>
+      </c>
+      <c r="P15" s="11">
         <v>0</v>
       </c>
-      <c r="Q15" s="22">
-        <v>49</v>
-      </c>
-      <c r="R15" s="23">
-        <v>70</v>
+      <c r="Q15" s="25">
+        <v>66</v>
+      </c>
+      <c r="R15" s="26">
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2196,55 +2166,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L16" s="4">
-        <v>-48.1</v>
+        <v>-40.5</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O16" s="10">
-        <v>96</v>
-      </c>
-      <c r="P16" s="9">
+        <v>195</v>
+      </c>
+      <c r="O16" s="6">
+        <v>74</v>
+      </c>
+      <c r="P16" s="11">
         <v>0</v>
       </c>
-      <c r="Q16" s="22">
-        <v>50</v>
-      </c>
-      <c r="R16" s="19">
-        <v>67</v>
+      <c r="Q16" s="7">
+        <v>55</v>
+      </c>
+      <c r="R16" s="26">
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2252,55 +2222,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L17" s="4">
-        <v>-44.4</v>
+        <v>-42.5</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O17" s="10">
-        <v>66</v>
-      </c>
-      <c r="P17" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="22">
-        <v>52</v>
-      </c>
-      <c r="R17" s="14">
-        <v>34</v>
+        <v>195</v>
+      </c>
+      <c r="O17" s="6">
+        <v>91</v>
+      </c>
+      <c r="P17" s="18">
+        <v>85</v>
+      </c>
+      <c r="Q17" s="15">
+        <v>82</v>
+      </c>
+      <c r="R17" s="24">
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2308,55 +2278,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="L18" s="4">
-        <v>-33.7</v>
+        <v>-48.7</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="O18" s="10">
-        <v>54</v>
-      </c>
-      <c r="P18" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="11">
-        <v>47</v>
-      </c>
-      <c r="R18" s="15">
-        <v>16</v>
+        <v>195</v>
+      </c>
+      <c r="O18" s="6">
+        <v>95</v>
+      </c>
+      <c r="P18" s="10">
+        <v>62</v>
+      </c>
+      <c r="Q18" s="20">
+        <v>88</v>
+      </c>
+      <c r="R18" s="19">
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2364,55 +2334,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="L19" s="4">
-        <v>-46.6</v>
+        <v>-45.9</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O19" s="10">
-        <v>91</v>
-      </c>
-      <c r="P19" s="9">
-        <v>2</v>
-      </c>
-      <c r="Q19" s="9">
-        <v>2</v>
-      </c>
-      <c r="R19" s="20">
-        <v>91</v>
+        <v>195</v>
+      </c>
+      <c r="O19" s="6">
+        <v>98</v>
+      </c>
+      <c r="P19" s="7">
+        <v>54</v>
+      </c>
+      <c r="Q19" s="20">
+        <v>88</v>
+      </c>
+      <c r="R19" s="16">
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2420,55 +2390,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="I20" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="K20" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="L20" s="4">
-        <v>-47.9</v>
+        <v>-36.6</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O20" s="10">
-        <v>100</v>
-      </c>
-      <c r="P20" s="15">
-        <v>14</v>
-      </c>
-      <c r="Q20" s="8">
-        <v>9</v>
-      </c>
-      <c r="R20" s="18">
-        <v>99</v>
+        <v>195</v>
+      </c>
+      <c r="O20" s="6">
+        <v>92</v>
+      </c>
+      <c r="P20" s="20">
+        <v>89</v>
+      </c>
+      <c r="Q20" s="27">
+        <v>33</v>
+      </c>
+      <c r="R20" s="7">
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2476,55 +2446,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L21" s="4">
-        <v>-40.6</v>
+        <v>-46.7</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O21" s="10">
-        <v>99</v>
-      </c>
-      <c r="P21" s="14">
-        <v>36</v>
-      </c>
-      <c r="Q21" s="13">
-        <v>31</v>
-      </c>
-      <c r="R21" s="18">
-        <v>98</v>
+        <v>195</v>
+      </c>
+      <c r="O21" s="6">
+        <v>94</v>
+      </c>
+      <c r="P21" s="20">
+        <v>90</v>
+      </c>
+      <c r="Q21" s="16">
+        <v>51</v>
+      </c>
+      <c r="R21" s="14">
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2532,55 +2502,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="L22" s="4">
-        <v>-42.5</v>
+        <v>-48.9</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O22" s="10">
-        <v>98</v>
-      </c>
-      <c r="P22" s="22">
-        <v>48</v>
-      </c>
-      <c r="Q22" s="24">
-        <v>23</v>
-      </c>
-      <c r="R22" s="8">
-        <v>10</v>
+        <v>195</v>
+      </c>
+      <c r="O22" s="6">
+        <v>99</v>
+      </c>
+      <c r="P22" s="20">
+        <v>90</v>
+      </c>
+      <c r="Q22" s="25">
+        <v>63</v>
+      </c>
+      <c r="R22" s="14">
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2588,55 +2558,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="I23" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="L23" s="4">
+        <v>-29.5</v>
+      </c>
+      <c r="M23" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="L23" s="4">
-        <v>-48.7</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>206</v>
-      </c>
       <c r="N23" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O23" s="10">
-        <v>99</v>
-      </c>
-      <c r="P23" s="21">
-        <v>53</v>
-      </c>
-      <c r="Q23" s="11">
-        <v>43</v>
-      </c>
-      <c r="R23" s="25">
-        <v>20</v>
+        <v>196</v>
+      </c>
+      <c r="O23" s="6">
+        <v>100</v>
+      </c>
+      <c r="P23" s="12">
+        <v>94</v>
+      </c>
+      <c r="Q23" s="8">
+        <v>10</v>
+      </c>
+      <c r="R23" s="12">
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2644,55 +2614,55 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>63</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="I24" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L24" s="4">
+        <v>-42.2</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="N24" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="L24" s="4">
-        <v>-45.9</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O24" s="10">
-        <v>95</v>
-      </c>
-      <c r="P24" s="23">
-        <v>71</v>
-      </c>
-      <c r="Q24" s="14">
-        <v>36</v>
-      </c>
-      <c r="R24" s="14">
-        <v>35</v>
+      <c r="O24" s="6">
+        <v>97</v>
+      </c>
+      <c r="P24" s="18">
+        <v>87</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>12</v>
+      </c>
+      <c r="R24" s="15">
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2700,55 +2670,55 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
+        <v>28</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="L25" s="4">
+        <v>-49.2</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="O25" s="6">
+        <v>88</v>
+      </c>
+      <c r="P25" s="23">
+        <v>74</v>
+      </c>
+      <c r="Q25" s="17">
         <v>16</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="L25" s="4">
-        <v>-36.6</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O25" s="10">
-        <v>92</v>
-      </c>
-      <c r="P25" s="19">
-        <v>67</v>
-      </c>
-      <c r="Q25" s="9">
-        <v>0</v>
-      </c>
-      <c r="R25" s="19">
-        <v>64</v>
+      <c r="R25" s="24">
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -2756,170 +2726,114 @@
         <v>42</v>
       </c>
       <c r="B26" s="2">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="E26" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="L26" s="4">
-        <v>-46.6</v>
+        <v>-47.2</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O26" s="10">
-        <v>93</v>
-      </c>
-      <c r="P26" s="21">
-        <v>57</v>
-      </c>
-      <c r="Q26" s="9">
-        <v>1</v>
-      </c>
-      <c r="R26" s="26">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18">
-      <c r="A27" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="2">
-        <v>24</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="L27" s="4">
-        <v>-48.9</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="O27" s="10">
-        <v>96</v>
-      </c>
-      <c r="P27" s="22">
-        <v>52</v>
-      </c>
-      <c r="Q27" s="25">
-        <v>19</v>
-      </c>
-      <c r="R27" s="23">
-        <v>68</v>
+        <v>196</v>
+      </c>
+      <c r="O26" s="6">
+        <v>78</v>
+      </c>
+      <c r="P26" s="7">
+        <v>55</v>
+      </c>
+      <c r="Q26" s="17">
+        <v>15</v>
+      </c>
+      <c r="R26" s="14">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A27">
+  <conditionalFormatting sqref="A2:A26">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B27">
+  <conditionalFormatting sqref="B2:B26">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C27">
+  <conditionalFormatting sqref="C2:C26">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D27">
+  <conditionalFormatting sqref="D2:D26">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E27">
+  <conditionalFormatting sqref="E2:E26">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F27">
+  <conditionalFormatting sqref="F2:F26">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G27">
+  <conditionalFormatting sqref="G2:G26">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H27">
+  <conditionalFormatting sqref="H2:H26">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I27">
+  <conditionalFormatting sqref="I2:I26">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J27">
+  <conditionalFormatting sqref="J2:J26">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K27">
+  <conditionalFormatting sqref="K2:K26">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L27">
+  <conditionalFormatting sqref="L2:L26">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2938,12 +2852,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M27">
+  <conditionalFormatting sqref="M2:M26">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N27">
+  <conditionalFormatting sqref="N2:N26">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2960,22 +2874,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O27">
+  <conditionalFormatting sqref="O2:O26">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P27">
+  <conditionalFormatting sqref="P2:P26">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q27">
+  <conditionalFormatting sqref="Q2:Q26">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R27">
+  <conditionalFormatting sqref="R2:R26">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261013--01</t>
-  </si>
-  <si>
-    <t>20261013--02</t>
-  </si>
-  <si>
-    <t>20261013--03</t>
-  </si>
-  <si>
     <t>20261014--01</t>
   </si>
   <si>
@@ -145,22 +136,22 @@
     <t>20261019--04</t>
   </si>
   <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>03:50</t>
-  </si>
-  <si>
-    <t>05:10</t>
-  </si>
-  <si>
-    <t>05:50</t>
-  </si>
-  <si>
-    <t>04:46</t>
-  </si>
-  <si>
-    <t>04:32</t>
+    <t>20261020--01</t>
+  </si>
+  <si>
+    <t>20261020--02</t>
+  </si>
+  <si>
+    <t>20261020--03</t>
+  </si>
+  <si>
+    <t>05:49</t>
+  </si>
+  <si>
+    <t>04:47</t>
+  </si>
+  <si>
+    <t>04:31</t>
   </si>
   <si>
     <t>05:48</t>
@@ -181,7 +172,10 @@
     <t>02:46</t>
   </si>
   <si>
-    <t>05:24</t>
+    <t>05:23</t>
+  </si>
+  <si>
+    <t>05:46</t>
   </si>
   <si>
     <t>04:13</t>
@@ -190,7 +184,7 @@
     <t>04:55</t>
   </si>
   <si>
-    <t>05:00</t>
+    <t>04:59</t>
   </si>
   <si>
     <t>04:06</t>
@@ -202,400 +196,406 @@
     <t>05:25</t>
   </si>
   <si>
-    <t>02:28</t>
-  </si>
-  <si>
-    <t>05:34</t>
-  </si>
-  <si>
-    <t>03:28</t>
+    <t>02:26</t>
+  </si>
+  <si>
+    <t>05:33</t>
+  </si>
+  <si>
+    <t>05:39</t>
+  </si>
+  <si>
+    <t>03:30</t>
+  </si>
+  <si>
+    <t>05:12</t>
+  </si>
+  <si>
+    <t>05:47</t>
+  </si>
+  <si>
+    <t>04:35</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:15:00</t>
-  </si>
-  <si>
-    <t>02:51:52</t>
-  </si>
-  <si>
-    <t>22:45:47</t>
-  </si>
-  <si>
-    <t>00:22:07</t>
+    <t>00:22:06</t>
   </si>
   <si>
     <t>01:58:51</t>
   </si>
   <si>
-    <t>21:53:04</t>
-  </si>
-  <si>
-    <t>23:29:10</t>
-  </si>
-  <si>
-    <t>01:05:49</t>
-  </si>
-  <si>
-    <t>21:00:23</t>
-  </si>
-  <si>
-    <t>22:36:12</t>
-  </si>
-  <si>
-    <t>00:12:44</t>
-  </si>
-  <si>
-    <t>01:49:41</t>
-  </si>
-  <si>
-    <t>21:43:12</t>
-  </si>
-  <si>
-    <t>23:19:36</t>
-  </si>
-  <si>
-    <t>00:56:24</t>
-  </si>
-  <si>
-    <t>20:50:11</t>
-  </si>
-  <si>
-    <t>22:26:24</t>
-  </si>
-  <si>
-    <t>00:03:06</t>
-  </si>
-  <si>
-    <t>19:57:12</t>
-  </si>
-  <si>
-    <t>21:33:10</t>
-  </si>
-  <si>
-    <t>23:09:45</t>
-  </si>
-  <si>
-    <t>19:04:16</t>
-  </si>
-  <si>
-    <t>20:39:54</t>
-  </si>
-  <si>
-    <t>22:16:22</t>
-  </si>
-  <si>
-    <t>23:53:14</t>
-  </si>
-  <si>
-    <t>01:17:15</t>
-  </si>
-  <si>
-    <t>02:54:36</t>
-  </si>
-  <si>
-    <t>22:48:09</t>
+    <t>21:53:03</t>
+  </si>
+  <si>
+    <t>23:29:09</t>
+  </si>
+  <si>
+    <t>01:05:47</t>
+  </si>
+  <si>
+    <t>21:00:20</t>
+  </si>
+  <si>
+    <t>22:36:08</t>
+  </si>
+  <si>
+    <t>00:12:40</t>
+  </si>
+  <si>
+    <t>01:49:37</t>
+  </si>
+  <si>
+    <t>21:43:05</t>
+  </si>
+  <si>
+    <t>23:19:30</t>
+  </si>
+  <si>
+    <t>00:56:17</t>
+  </si>
+  <si>
+    <t>20:50:02</t>
+  </si>
+  <si>
+    <t>22:26:15</t>
+  </si>
+  <si>
+    <t>00:02:56</t>
+  </si>
+  <si>
+    <t>19:56:58</t>
+  </si>
+  <si>
+    <t>21:32:57</t>
+  </si>
+  <si>
+    <t>23:09:32</t>
+  </si>
+  <si>
+    <t>19:03:58</t>
+  </si>
+  <si>
+    <t>20:39:36</t>
+  </si>
+  <si>
+    <t>22:16:04</t>
+  </si>
+  <si>
+    <t>23:52:55</t>
+  </si>
+  <si>
+    <t>19:46:13</t>
+  </si>
+  <si>
+    <t>21:22:32</t>
+  </si>
+  <si>
+    <t>22:59:15</t>
   </si>
   <si>
     <t>00:24:20</t>
   </si>
   <si>
-    <t>02:01:20</t>
-  </si>
-  <si>
-    <t>21:55:35</t>
-  </si>
-  <si>
-    <t>23:31:24</t>
-  </si>
-  <si>
-    <t>01:08:10</t>
-  </si>
-  <si>
-    <t>21:03:15</t>
-  </si>
-  <si>
-    <t>22:38:27</t>
-  </si>
-  <si>
-    <t>00:15:00</t>
-  </si>
-  <si>
-    <t>01:52:45</t>
-  </si>
-  <si>
-    <t>21:45:30</t>
-  </si>
-  <si>
-    <t>23:21:50</t>
-  </si>
-  <si>
-    <t>00:59:01</t>
-  </si>
-  <si>
-    <t>20:52:36</t>
-  </si>
-  <si>
-    <t>22:28:38</t>
-  </si>
-  <si>
-    <t>00:05:30</t>
-  </si>
-  <si>
-    <t>19:59:50</t>
-  </si>
-  <si>
-    <t>21:35:24</t>
-  </si>
-  <si>
-    <t>23:12:04</t>
-  </si>
-  <si>
-    <t>19:07:25</t>
-  </si>
-  <si>
-    <t>20:42:10</t>
-  </si>
-  <si>
-    <t>22:18:37</t>
-  </si>
-  <si>
-    <t>23:56:04</t>
-  </si>
-  <si>
-    <t>01:20:07</t>
-  </si>
-  <si>
-    <t>02:56:31</t>
-  </si>
-  <si>
-    <t>22:50:44</t>
-  </si>
-  <si>
-    <t>00:27:15</t>
-  </si>
-  <si>
-    <t>02:03:43</t>
-  </si>
-  <si>
-    <t>21:57:51</t>
-  </si>
-  <si>
-    <t>23:34:18</t>
-  </si>
-  <si>
-    <t>01:10:49</t>
-  </si>
-  <si>
-    <t>21:04:55</t>
-  </si>
-  <si>
-    <t>22:41:16</t>
-  </si>
-  <si>
-    <t>00:17:48</t>
-  </si>
-  <si>
-    <t>01:54:08</t>
-  </si>
-  <si>
-    <t>21:48:12</t>
-  </si>
-  <si>
-    <t>23:24:42</t>
-  </si>
-  <si>
-    <t>01:01:07</t>
-  </si>
-  <si>
-    <t>20:55:03</t>
-  </si>
-  <si>
-    <t>22:31:31</t>
-  </si>
-  <si>
-    <t>00:08:00</t>
-  </si>
-  <si>
-    <t>20:01:52</t>
-  </si>
-  <si>
-    <t>21:38:16</t>
-  </si>
-  <si>
-    <t>23:14:46</t>
-  </si>
-  <si>
-    <t>19:08:39</t>
-  </si>
-  <si>
-    <t>20:44:57</t>
-  </si>
-  <si>
-    <t>22:21:27</t>
-  </si>
-  <si>
-    <t>23:57:48</t>
-  </si>
-  <si>
-    <t>01:23:00</t>
-  </si>
-  <si>
-    <t>02:58:26</t>
-  </si>
-  <si>
-    <t>22:53:19</t>
-  </si>
-  <si>
-    <t>00:30:10</t>
+    <t>02:01:19</t>
+  </si>
+  <si>
+    <t>21:55:34</t>
+  </si>
+  <si>
+    <t>23:31:22</t>
+  </si>
+  <si>
+    <t>01:08:08</t>
+  </si>
+  <si>
+    <t>21:03:11</t>
+  </si>
+  <si>
+    <t>22:38:23</t>
+  </si>
+  <si>
+    <t>00:14:56</t>
+  </si>
+  <si>
+    <t>01:52:41</t>
+  </si>
+  <si>
+    <t>21:45:24</t>
+  </si>
+  <si>
+    <t>23:21:43</t>
+  </si>
+  <si>
+    <t>00:58:54</t>
+  </si>
+  <si>
+    <t>20:52:27</t>
+  </si>
+  <si>
+    <t>22:28:28</t>
+  </si>
+  <si>
+    <t>00:05:21</t>
+  </si>
+  <si>
+    <t>19:59:36</t>
+  </si>
+  <si>
+    <t>21:35:11</t>
+  </si>
+  <si>
+    <t>23:11:50</t>
+  </si>
+  <si>
+    <t>19:07:08</t>
+  </si>
+  <si>
+    <t>20:41:52</t>
+  </si>
+  <si>
+    <t>22:18:19</t>
+  </si>
+  <si>
+    <t>23:55:44</t>
+  </si>
+  <si>
+    <t>19:48:34</t>
+  </si>
+  <si>
+    <t>21:24:45</t>
+  </si>
+  <si>
+    <t>23:01:46</t>
+  </si>
+  <si>
+    <t>00:27:14</t>
+  </si>
+  <si>
+    <t>02:03:42</t>
+  </si>
+  <si>
+    <t>21:57:49</t>
+  </si>
+  <si>
+    <t>23:34:16</t>
+  </si>
+  <si>
+    <t>01:10:47</t>
+  </si>
+  <si>
+    <t>21:04:52</t>
+  </si>
+  <si>
+    <t>22:41:13</t>
+  </si>
+  <si>
+    <t>00:17:45</t>
+  </si>
+  <si>
+    <t>01:54:04</t>
+  </si>
+  <si>
+    <t>21:48:05</t>
+  </si>
+  <si>
+    <t>23:24:36</t>
+  </si>
+  <si>
+    <t>01:01:01</t>
+  </si>
+  <si>
+    <t>20:54:54</t>
+  </si>
+  <si>
+    <t>22:31:22</t>
+  </si>
+  <si>
+    <t>00:07:50</t>
+  </si>
+  <si>
+    <t>20:01:39</t>
+  </si>
+  <si>
+    <t>21:38:02</t>
+  </si>
+  <si>
+    <t>23:14:32</t>
+  </si>
+  <si>
+    <t>19:08:21</t>
+  </si>
+  <si>
+    <t>20:44:38</t>
+  </si>
+  <si>
+    <t>22:21:08</t>
+  </si>
+  <si>
+    <t>23:57:29</t>
+  </si>
+  <si>
+    <t>19:51:10</t>
+  </si>
+  <si>
+    <t>21:27:38</t>
+  </si>
+  <si>
+    <t>23:04:03</t>
+  </si>
+  <si>
+    <t>00:30:09</t>
   </si>
   <si>
     <t>02:06:06</t>
   </si>
   <si>
-    <t>22:00:07</t>
-  </si>
-  <si>
-    <t>23:37:12</t>
-  </si>
-  <si>
-    <t>01:13:28</t>
-  </si>
-  <si>
-    <t>21:06:36</t>
-  </si>
-  <si>
-    <t>22:44:07</t>
-  </si>
-  <si>
-    <t>00:20:37</t>
-  </si>
-  <si>
-    <t>01:55:31</t>
-  </si>
-  <si>
-    <t>21:50:54</t>
-  </si>
-  <si>
-    <t>23:27:35</t>
-  </si>
-  <si>
-    <t>01:03:14</t>
-  </si>
-  <si>
-    <t>20:57:31</t>
-  </si>
-  <si>
-    <t>22:34:26</t>
-  </si>
-  <si>
-    <t>00:10:30</t>
-  </si>
-  <si>
-    <t>20:03:56</t>
-  </si>
-  <si>
-    <t>21:41:08</t>
-  </si>
-  <si>
-    <t>23:17:29</t>
-  </si>
-  <si>
-    <t>19:09:53</t>
-  </si>
-  <si>
-    <t>20:47:44</t>
-  </si>
-  <si>
-    <t>22:24:17</t>
-  </si>
-  <si>
-    <t>23:59:32</t>
-  </si>
-  <si>
-    <t>01:25:15</t>
-  </si>
-  <si>
-    <t>03:01:11</t>
-  </si>
-  <si>
-    <t>22:55:42</t>
-  </si>
-  <si>
-    <t>00:32:24</t>
+    <t>22:00:05</t>
+  </si>
+  <si>
+    <t>23:37:10</t>
+  </si>
+  <si>
+    <t>01:13:26</t>
+  </si>
+  <si>
+    <t>21:06:32</t>
+  </si>
+  <si>
+    <t>22:44:03</t>
+  </si>
+  <si>
+    <t>00:20:33</t>
+  </si>
+  <si>
+    <t>01:55:27</t>
+  </si>
+  <si>
+    <t>21:50:47</t>
+  </si>
+  <si>
+    <t>23:27:29</t>
+  </si>
+  <si>
+    <t>01:03:07</t>
+  </si>
+  <si>
+    <t>20:57:22</t>
+  </si>
+  <si>
+    <t>22:34:16</t>
+  </si>
+  <si>
+    <t>00:10:20</t>
+  </si>
+  <si>
+    <t>20:03:42</t>
+  </si>
+  <si>
+    <t>21:40:55</t>
+  </si>
+  <si>
+    <t>23:17:15</t>
+  </si>
+  <si>
+    <t>19:09:34</t>
+  </si>
+  <si>
+    <t>20:47:25</t>
+  </si>
+  <si>
+    <t>22:23:58</t>
+  </si>
+  <si>
+    <t>23:59:14</t>
+  </si>
+  <si>
+    <t>19:53:46</t>
+  </si>
+  <si>
+    <t>21:30:32</t>
+  </si>
+  <si>
+    <t>23:06:21</t>
+  </si>
+  <si>
+    <t>00:32:23</t>
   </si>
   <si>
     <t>02:08:35</t>
   </si>
   <si>
-    <t>22:02:39</t>
-  </si>
-  <si>
-    <t>23:39:26</t>
-  </si>
-  <si>
-    <t>01:15:49</t>
-  </si>
-  <si>
-    <t>21:09:28</t>
-  </si>
-  <si>
-    <t>22:46:22</t>
-  </si>
-  <si>
-    <t>00:22:53</t>
-  </si>
-  <si>
-    <t>01:58:35</t>
-  </si>
-  <si>
-    <t>21:53:13</t>
-  </si>
-  <si>
-    <t>23:29:50</t>
-  </si>
-  <si>
-    <t>01:05:51</t>
-  </si>
-  <si>
-    <t>20:59:57</t>
-  </si>
-  <si>
-    <t>22:36:40</t>
-  </si>
-  <si>
-    <t>00:12:55</t>
-  </si>
-  <si>
-    <t>20:06:34</t>
-  </si>
-  <si>
-    <t>21:43:23</t>
-  </si>
-  <si>
-    <t>23:19:48</t>
-  </si>
-  <si>
-    <t>19:13:03</t>
-  </si>
-  <si>
-    <t>20:50:00</t>
-  </si>
-  <si>
-    <t>22:26:33</t>
-  </si>
-  <si>
-    <t>00:02:22</t>
+    <t>22:02:37</t>
+  </si>
+  <si>
+    <t>23:39:24</t>
+  </si>
+  <si>
+    <t>01:15:47</t>
+  </si>
+  <si>
+    <t>21:09:25</t>
+  </si>
+  <si>
+    <t>22:46:19</t>
+  </si>
+  <si>
+    <t>00:22:49</t>
+  </si>
+  <si>
+    <t>01:58:31</t>
+  </si>
+  <si>
+    <t>21:53:07</t>
+  </si>
+  <si>
+    <t>23:29:43</t>
+  </si>
+  <si>
+    <t>01:05:44</t>
+  </si>
+  <si>
+    <t>20:59:48</t>
+  </si>
+  <si>
+    <t>22:36:30</t>
+  </si>
+  <si>
+    <t>00:12:45</t>
+  </si>
+  <si>
+    <t>20:06:21</t>
+  </si>
+  <si>
+    <t>21:43:09</t>
+  </si>
+  <si>
+    <t>23:19:34</t>
+  </si>
+  <si>
+    <t>19:12:45</t>
+  </si>
+  <si>
+    <t>20:49:42</t>
+  </si>
+  <si>
+    <t>22:26:14</t>
+  </si>
+  <si>
+    <t>00:02:03</t>
+  </si>
+  <si>
+    <t>19:56:08</t>
+  </si>
+  <si>
+    <t>21:32:45</t>
+  </si>
+  <si>
+    <t>23:08:51</t>
   </si>
   <si>
     <t>0°</t>
-  </si>
-  <si>
-    <t>5°</t>
-  </si>
-  <si>
-    <t>02:59:52</t>
   </si>
   <si>
     <t>B</t>
@@ -638,7 +638,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -659,7 +659,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -671,115 +761,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -820,7 +808,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -895,12 +883,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1382,37 +1364,37 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L2" s="4">
-        <v>-37.1</v>
+        <v>-43</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>194</v>
@@ -1421,16 +1403,16 @@
         <v>195</v>
       </c>
       <c r="O2" s="6">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="P2" s="7">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="Q2" s="8">
-        <v>11</v>
-      </c>
-      <c r="R2" s="8">
-        <v>9</v>
+        <v>51</v>
+      </c>
+      <c r="R2" s="9">
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1438,37 +1420,37 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>193</v>
+        <v>69</v>
       </c>
       <c r="L3" s="4">
-        <v>-23.8</v>
+        <v>-31.8</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>194</v>
@@ -1476,17 +1458,17 @@
       <c r="N3" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="O3" s="9">
-        <v>12</v>
+      <c r="O3" s="6">
+        <v>100</v>
       </c>
       <c r="P3" s="10">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="Q3" s="11">
+        <v>23</v>
+      </c>
+      <c r="R3" s="12">
         <v>0</v>
-      </c>
-      <c r="R3" s="11">
-        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1494,37 +1476,37 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L4" s="4">
-        <v>-47.4</v>
+        <v>-46.4</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>194</v>
@@ -1533,16 +1515,16 @@
         <v>195</v>
       </c>
       <c r="O4" s="6">
-        <v>100</v>
-      </c>
-      <c r="P4" s="12">
-        <v>97</v>
-      </c>
-      <c r="Q4" s="13">
-        <v>100</v>
-      </c>
-      <c r="R4" s="12">
-        <v>95</v>
+        <v>76</v>
+      </c>
+      <c r="P4" s="13">
+        <v>31</v>
+      </c>
+      <c r="Q4" s="12">
+        <v>0</v>
+      </c>
+      <c r="R4" s="14">
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1556,31 +1538,31 @@
         <v>46</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L5" s="4">
-        <v>-43</v>
+        <v>-46.8</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>194</v>
@@ -1589,16 +1571,16 @@
         <v>195</v>
       </c>
       <c r="O5" s="6">
-        <v>97</v>
-      </c>
-      <c r="P5" s="12">
-        <v>94</v>
+        <v>57</v>
+      </c>
+      <c r="P5" s="15">
+        <v>21</v>
       </c>
       <c r="Q5" s="12">
-        <v>93</v>
-      </c>
-      <c r="R5" s="14">
-        <v>45</v>
+        <v>0</v>
+      </c>
+      <c r="R5" s="16">
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1606,37 +1588,37 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L6" s="4">
-        <v>-31.8</v>
+        <v>-38.8</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>194</v>
@@ -1645,16 +1627,16 @@
         <v>195</v>
       </c>
       <c r="O6" s="6">
-        <v>86</v>
-      </c>
-      <c r="P6" s="15">
-        <v>80</v>
-      </c>
-      <c r="Q6" s="16">
-        <v>50</v>
-      </c>
-      <c r="R6" s="11">
+        <v>77</v>
+      </c>
+      <c r="P6" s="17">
+        <v>14</v>
+      </c>
+      <c r="Q6" s="12">
         <v>0</v>
+      </c>
+      <c r="R6" s="10">
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1662,55 +1644,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L7" s="4">
-        <v>-46.4</v>
+        <v>-42.8</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>194</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O7" s="6">
-        <v>66</v>
-      </c>
-      <c r="P7" s="8">
-        <v>11</v>
-      </c>
-      <c r="Q7" s="11">
+        <v>88</v>
+      </c>
+      <c r="P7" s="12">
         <v>0</v>
       </c>
-      <c r="R7" s="16">
-        <v>49</v>
+      <c r="Q7" s="18">
+        <v>63</v>
+      </c>
+      <c r="R7" s="19">
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1718,37 +1700,37 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L8" s="4">
-        <v>-46.8</v>
+        <v>-48.1</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>194</v>
@@ -1757,16 +1739,16 @@
         <v>195</v>
       </c>
       <c r="O8" s="6">
-        <v>90</v>
-      </c>
-      <c r="P8" s="17">
-        <v>13</v>
-      </c>
-      <c r="Q8" s="11">
+        <v>100</v>
+      </c>
+      <c r="P8" s="12">
         <v>0</v>
       </c>
-      <c r="R8" s="18">
-        <v>85</v>
+      <c r="Q8" s="20">
+        <v>36</v>
+      </c>
+      <c r="R8" s="7">
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1774,37 +1756,37 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L9" s="4">
-        <v>-38.8</v>
+        <v>-44.4</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>194</v>
@@ -1813,16 +1795,16 @@
         <v>195</v>
       </c>
       <c r="O9" s="6">
-        <v>63</v>
-      </c>
-      <c r="P9" s="19">
-        <v>6</v>
-      </c>
-      <c r="Q9" s="11">
+        <v>95</v>
+      </c>
+      <c r="P9" s="12">
         <v>0</v>
       </c>
-      <c r="R9" s="7">
-        <v>55</v>
+      <c r="Q9" s="12">
+        <v>2</v>
+      </c>
+      <c r="R9" s="21">
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1830,37 +1812,37 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L10" s="4">
-        <v>-42.8</v>
+        <v>-33.7</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>194</v>
@@ -1869,16 +1851,16 @@
         <v>196</v>
       </c>
       <c r="O10" s="6">
-        <v>91</v>
-      </c>
-      <c r="P10" s="11">
+        <v>75</v>
+      </c>
+      <c r="P10" s="12">
         <v>0</v>
       </c>
-      <c r="Q10" s="20">
-        <v>88</v>
-      </c>
-      <c r="R10" s="7">
-        <v>53</v>
+      <c r="Q10" s="12">
+        <v>2</v>
+      </c>
+      <c r="R10" s="10">
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1886,37 +1868,37 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L11" s="4">
-        <v>-48.1</v>
+        <v>-46.6</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>194</v>
@@ -1925,16 +1907,16 @@
         <v>195</v>
       </c>
       <c r="O11" s="6">
-        <v>81</v>
-      </c>
-      <c r="P11" s="11">
+        <v>100</v>
+      </c>
+      <c r="P11" s="12">
         <v>0</v>
       </c>
-      <c r="Q11" s="21">
-        <v>68</v>
+      <c r="Q11" s="22">
+        <v>80</v>
       </c>
       <c r="R11" s="7">
-        <v>53</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1942,37 +1924,37 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L12" s="4">
-        <v>-44.4</v>
+        <v>-47.9</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>194</v>
@@ -1980,17 +1962,17 @@
       <c r="N12" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="O12" s="22">
-        <v>48</v>
-      </c>
-      <c r="P12" s="11">
+      <c r="O12" s="6">
+        <v>94</v>
+      </c>
+      <c r="P12" s="12">
         <v>0</v>
       </c>
-      <c r="Q12" s="19">
-        <v>4</v>
-      </c>
-      <c r="R12" s="16">
-        <v>48</v>
+      <c r="Q12" s="14">
+        <v>57</v>
+      </c>
+      <c r="R12" s="22">
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1998,55 +1980,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L13" s="4">
-        <v>-33.7</v>
+        <v>-40.6</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>194</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O13" s="6">
-        <v>75</v>
-      </c>
-      <c r="P13" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="11">
-        <v>0</v>
-      </c>
-      <c r="R13" s="23">
-        <v>75</v>
+        <v>74</v>
+      </c>
+      <c r="P13" s="23">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="10">
+        <v>70</v>
+      </c>
+      <c r="R13" s="14">
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2054,37 +2036,37 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="L14" s="4">
-        <v>-46.6</v>
+        <v>-42.5</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>194</v>
@@ -2093,16 +2075,16 @@
         <v>195</v>
       </c>
       <c r="O14" s="6">
-        <v>70</v>
-      </c>
-      <c r="P14" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="21">
-        <v>70</v>
-      </c>
-      <c r="R14" s="24">
-        <v>28</v>
+        <v>90</v>
+      </c>
+      <c r="P14" s="13">
+        <v>29</v>
+      </c>
+      <c r="Q14" s="9">
+        <v>42</v>
+      </c>
+      <c r="R14" s="15">
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2110,37 +2092,37 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="L15" s="4">
-        <v>-47.9</v>
+        <v>-48.7</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>194</v>
@@ -2149,16 +2131,16 @@
         <v>195</v>
       </c>
       <c r="O15" s="6">
-        <v>72</v>
-      </c>
-      <c r="P15" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="25">
-        <v>66</v>
-      </c>
-      <c r="R15" s="26">
-        <v>22</v>
+        <v>96</v>
+      </c>
+      <c r="P15" s="13">
+        <v>32</v>
+      </c>
+      <c r="Q15" s="14">
+        <v>53</v>
+      </c>
+      <c r="R15" s="24">
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2166,37 +2148,37 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L16" s="4">
-        <v>-40.5</v>
+        <v>-45.9</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>194</v>
@@ -2205,16 +2187,16 @@
         <v>195</v>
       </c>
       <c r="O16" s="6">
-        <v>74</v>
-      </c>
-      <c r="P16" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="7">
-        <v>55</v>
-      </c>
-      <c r="R16" s="26">
-        <v>20</v>
+        <v>97</v>
+      </c>
+      <c r="P16" s="13">
+        <v>31</v>
+      </c>
+      <c r="Q16" s="22">
+        <v>82</v>
+      </c>
+      <c r="R16" s="24">
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2222,37 +2204,37 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L17" s="4">
-        <v>-42.5</v>
+        <v>-36.6</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>194</v>
@@ -2261,16 +2243,16 @@
         <v>195</v>
       </c>
       <c r="O17" s="6">
-        <v>91</v>
-      </c>
-      <c r="P17" s="18">
-        <v>85</v>
-      </c>
-      <c r="Q17" s="15">
-        <v>82</v>
-      </c>
-      <c r="R17" s="24">
-        <v>30</v>
+        <v>70</v>
+      </c>
+      <c r="P17" s="15">
+        <v>21</v>
+      </c>
+      <c r="Q17" s="24">
+        <v>4</v>
+      </c>
+      <c r="R17" s="15">
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2278,37 +2260,37 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L18" s="4">
-        <v>-48.7</v>
+        <v>-46.6</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>194</v>
@@ -2317,16 +2299,16 @@
         <v>195</v>
       </c>
       <c r="O18" s="6">
-        <v>95</v>
-      </c>
-      <c r="P18" s="10">
-        <v>62</v>
-      </c>
-      <c r="Q18" s="20">
-        <v>88</v>
-      </c>
-      <c r="R18" s="19">
+        <v>64</v>
+      </c>
+      <c r="P18" s="15">
+        <v>21</v>
+      </c>
+      <c r="Q18" s="24">
         <v>4</v>
+      </c>
+      <c r="R18" s="15">
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2334,37 +2316,37 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="L19" s="4">
-        <v>-45.9</v>
+        <v>-48.9</v>
       </c>
       <c r="M19" s="3" t="s">
         <v>194</v>
@@ -2373,16 +2355,16 @@
         <v>195</v>
       </c>
       <c r="O19" s="6">
-        <v>98</v>
-      </c>
-      <c r="P19" s="7">
         <v>54</v>
       </c>
-      <c r="Q19" s="20">
-        <v>88</v>
-      </c>
-      <c r="R19" s="16">
-        <v>50</v>
+      <c r="P19" s="15">
+        <v>22</v>
+      </c>
+      <c r="Q19" s="24">
+        <v>3</v>
+      </c>
+      <c r="R19" s="17">
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2390,55 +2372,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L20" s="4">
-        <v>-36.6</v>
+        <v>-29.5</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>194</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O20" s="6">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="P20" s="20">
-        <v>89</v>
-      </c>
-      <c r="Q20" s="27">
-        <v>33</v>
-      </c>
-      <c r="R20" s="7">
-        <v>56</v>
+        <v>37</v>
+      </c>
+      <c r="Q20" s="12">
+        <v>0</v>
+      </c>
+      <c r="R20" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2446,37 +2428,37 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L21" s="4">
-        <v>-46.7</v>
+        <v>-42.1</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>194</v>
@@ -2485,16 +2467,16 @@
         <v>195</v>
       </c>
       <c r="O21" s="6">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="P21" s="20">
-        <v>90</v>
-      </c>
-      <c r="Q21" s="16">
-        <v>51</v>
-      </c>
-      <c r="R21" s="14">
-        <v>45</v>
+        <v>33</v>
+      </c>
+      <c r="Q21" s="12">
+        <v>0</v>
+      </c>
+      <c r="R21" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2502,37 +2484,37 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L22" s="4">
-        <v>-48.9</v>
+        <v>-49.2</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>194</v>
@@ -2541,16 +2523,16 @@
         <v>195</v>
       </c>
       <c r="O22" s="6">
-        <v>99</v>
-      </c>
-      <c r="P22" s="20">
-        <v>90</v>
-      </c>
-      <c r="Q22" s="25">
-        <v>63</v>
-      </c>
-      <c r="R22" s="14">
-        <v>47</v>
+        <v>57</v>
+      </c>
+      <c r="P22" s="23">
+        <v>10</v>
+      </c>
+      <c r="Q22" s="12">
+        <v>0</v>
+      </c>
+      <c r="R22" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2558,37 +2540,37 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L23" s="4">
-        <v>-29.5</v>
+        <v>-47.3</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>194</v>
@@ -2597,16 +2579,16 @@
         <v>196</v>
       </c>
       <c r="O23" s="6">
-        <v>100</v>
-      </c>
-      <c r="P23" s="12">
-        <v>94</v>
-      </c>
-      <c r="Q23" s="8">
-        <v>10</v>
+        <v>64</v>
+      </c>
+      <c r="P23" s="23">
+        <v>8</v>
+      </c>
+      <c r="Q23" s="12">
+        <v>0</v>
       </c>
       <c r="R23" s="12">
-        <v>97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2614,37 +2596,37 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L24" s="4">
-        <v>-42.2</v>
+        <v>-35.9</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>194</v>
@@ -2653,16 +2635,16 @@
         <v>195</v>
       </c>
       <c r="O24" s="6">
-        <v>97</v>
-      </c>
-      <c r="P24" s="18">
-        <v>87</v>
-      </c>
-      <c r="Q24" s="8">
-        <v>12</v>
-      </c>
-      <c r="R24" s="15">
-        <v>78</v>
+        <v>49</v>
+      </c>
+      <c r="P24" s="9">
+        <v>39</v>
+      </c>
+      <c r="Q24" s="12">
+        <v>0</v>
+      </c>
+      <c r="R24" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2670,37 +2652,37 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L25" s="4">
-        <v>-49.2</v>
+        <v>-46.6</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>194</v>
@@ -2708,17 +2690,17 @@
       <c r="N25" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="O25" s="6">
-        <v>88</v>
-      </c>
-      <c r="P25" s="23">
-        <v>74</v>
-      </c>
-      <c r="Q25" s="17">
-        <v>16</v>
-      </c>
-      <c r="R25" s="24">
+      <c r="O25" s="25">
+        <v>48</v>
+      </c>
+      <c r="P25" s="13">
         <v>32</v>
+      </c>
+      <c r="Q25" s="12">
+        <v>0</v>
+      </c>
+      <c r="R25" s="12">
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -2726,55 +2708,55 @@
         <v>42</v>
       </c>
       <c r="B26" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="L26" s="4">
-        <v>-47.2</v>
+        <v>-49.9</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>194</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O26" s="6">
-        <v>78</v>
-      </c>
-      <c r="P26" s="7">
-        <v>55</v>
-      </c>
-      <c r="Q26" s="17">
-        <v>15</v>
-      </c>
-      <c r="R26" s="14">
+        <v>195</v>
+      </c>
+      <c r="O26" s="25">
         <v>44</v>
+      </c>
+      <c r="P26" s="13">
+        <v>28</v>
+      </c>
+      <c r="Q26" s="12">
+        <v>0</v>
+      </c>
+      <c r="R26" s="12">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="191">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261014--01</t>
-  </si>
-  <si>
-    <t>20261014--02</t>
-  </si>
-  <si>
-    <t>20261014--03</t>
-  </si>
-  <si>
-    <t>20261014--04</t>
-  </si>
-  <si>
     <t>20261015--01</t>
   </si>
   <si>
@@ -145,457 +133,451 @@
     <t>20261020--03</t>
   </si>
   <si>
-    <t>05:49</t>
-  </si>
-  <si>
-    <t>04:47</t>
-  </si>
-  <si>
-    <t>04:31</t>
+    <t>20261021--01</t>
+  </si>
+  <si>
+    <t>20261021--02</t>
+  </si>
+  <si>
+    <t>20261021--03</t>
+  </si>
+  <si>
+    <t>05:18</t>
+  </si>
+  <si>
+    <t>03:20</t>
+  </si>
+  <si>
+    <t>05:39</t>
+  </si>
+  <si>
+    <t>05:36</t>
+  </si>
+  <si>
+    <t>02:45</t>
+  </si>
+  <si>
+    <t>05:23</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>04:13</t>
+  </si>
+  <si>
+    <t>04:55</t>
   </si>
   <si>
     <t>05:48</t>
   </si>
   <si>
-    <t>05:18</t>
-  </si>
-  <si>
-    <t>03:21</t>
+    <t>04:59</t>
+  </si>
+  <si>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>05:43</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>02:25</t>
+  </si>
+  <si>
+    <t>05:33</t>
   </si>
   <si>
     <t>05:40</t>
   </si>
   <si>
-    <t>05:37</t>
-  </si>
-  <si>
-    <t>02:46</t>
-  </si>
-  <si>
-    <t>05:23</t>
+    <t>03:29</t>
+  </si>
+  <si>
+    <t>05:12</t>
   </si>
   <si>
     <t>05:46</t>
   </si>
   <si>
-    <t>04:13</t>
-  </si>
-  <si>
-    <t>04:55</t>
-  </si>
-  <si>
-    <t>04:59</t>
-  </si>
-  <si>
-    <t>04:06</t>
-  </si>
-  <si>
-    <t>05:44</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>02:26</t>
-  </si>
-  <si>
-    <t>05:33</t>
-  </si>
-  <si>
-    <t>05:39</t>
-  </si>
-  <si>
-    <t>03:30</t>
-  </si>
-  <si>
-    <t>05:12</t>
-  </si>
-  <si>
-    <t>05:47</t>
-  </si>
-  <si>
     <t>04:35</t>
   </si>
   <si>
+    <t>04:34</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>00:22:06</t>
-  </si>
-  <si>
-    <t>01:58:51</t>
-  </si>
-  <si>
-    <t>21:53:03</t>
-  </si>
-  <si>
-    <t>23:29:09</t>
-  </si>
-  <si>
     <t>01:05:47</t>
   </si>
   <si>
-    <t>21:00:20</t>
-  </si>
-  <si>
-    <t>22:36:08</t>
+    <t>21:00:19</t>
+  </si>
+  <si>
+    <t>22:36:07</t>
+  </si>
+  <si>
+    <t>00:12:39</t>
+  </si>
+  <si>
+    <t>01:49:35</t>
+  </si>
+  <si>
+    <t>21:43:03</t>
+  </si>
+  <si>
+    <t>23:19:27</t>
+  </si>
+  <si>
+    <t>00:56:14</t>
+  </si>
+  <si>
+    <t>20:49:57</t>
+  </si>
+  <si>
+    <t>22:26:10</t>
+  </si>
+  <si>
+    <t>00:02:51</t>
+  </si>
+  <si>
+    <t>19:56:52</t>
+  </si>
+  <si>
+    <t>21:32:50</t>
+  </si>
+  <si>
+    <t>23:09:24</t>
+  </si>
+  <si>
+    <t>19:03:49</t>
+  </si>
+  <si>
+    <t>20:39:26</t>
+  </si>
+  <si>
+    <t>22:15:53</t>
+  </si>
+  <si>
+    <t>23:52:44</t>
+  </si>
+  <si>
+    <t>19:46:00</t>
+  </si>
+  <si>
+    <t>21:22:18</t>
+  </si>
+  <si>
+    <t>22:59:01</t>
+  </si>
+  <si>
+    <t>18:52:34</t>
+  </si>
+  <si>
+    <t>20:28:39</t>
+  </si>
+  <si>
+    <t>22:05:16</t>
+  </si>
+  <si>
+    <t>01:08:07</t>
+  </si>
+  <si>
+    <t>21:03:10</t>
+  </si>
+  <si>
+    <t>22:38:22</t>
+  </si>
+  <si>
+    <t>00:14:55</t>
+  </si>
+  <si>
+    <t>01:52:40</t>
+  </si>
+  <si>
+    <t>21:45:21</t>
+  </si>
+  <si>
+    <t>23:21:41</t>
+  </si>
+  <si>
+    <t>00:58:51</t>
+  </si>
+  <si>
+    <t>20:52:22</t>
+  </si>
+  <si>
+    <t>22:28:23</t>
+  </si>
+  <si>
+    <t>00:05:16</t>
+  </si>
+  <si>
+    <t>19:59:30</t>
+  </si>
+  <si>
+    <t>21:35:04</t>
+  </si>
+  <si>
+    <t>23:11:43</t>
+  </si>
+  <si>
+    <t>19:06:59</t>
+  </si>
+  <si>
+    <t>20:41:42</t>
+  </si>
+  <si>
+    <t>22:18:08</t>
+  </si>
+  <si>
+    <t>23:55:34</t>
+  </si>
+  <si>
+    <t>19:48:21</t>
+  </si>
+  <si>
+    <t>21:24:32</t>
+  </si>
+  <si>
+    <t>23:01:32</t>
+  </si>
+  <si>
+    <t>18:55:04</t>
+  </si>
+  <si>
+    <t>20:30:52</t>
+  </si>
+  <si>
+    <t>22:07:37</t>
+  </si>
+  <si>
+    <t>01:10:46</t>
+  </si>
+  <si>
+    <t>21:04:50</t>
+  </si>
+  <si>
+    <t>22:41:11</t>
+  </si>
+  <si>
+    <t>00:17:43</t>
+  </si>
+  <si>
+    <t>01:54:02</t>
+  </si>
+  <si>
+    <t>21:48:03</t>
+  </si>
+  <si>
+    <t>23:24:33</t>
+  </si>
+  <si>
+    <t>01:00:57</t>
+  </si>
+  <si>
+    <t>20:54:49</t>
+  </si>
+  <si>
+    <t>22:31:17</t>
+  </si>
+  <si>
+    <t>00:07:45</t>
+  </si>
+  <si>
+    <t>20:01:32</t>
+  </si>
+  <si>
+    <t>21:37:55</t>
+  </si>
+  <si>
+    <t>23:14:25</t>
+  </si>
+  <si>
+    <t>19:08:11</t>
+  </si>
+  <si>
+    <t>20:44:28</t>
+  </si>
+  <si>
+    <t>22:20:58</t>
+  </si>
+  <si>
+    <t>23:57:18</t>
+  </si>
+  <si>
+    <t>19:50:56</t>
+  </si>
+  <si>
+    <t>21:27:25</t>
+  </si>
+  <si>
+    <t>23:03:50</t>
+  </si>
+  <si>
+    <t>18:57:21</t>
+  </si>
+  <si>
+    <t>20:33:45</t>
+  </si>
+  <si>
+    <t>22:10:13</t>
+  </si>
+  <si>
+    <t>01:13:25</t>
+  </si>
+  <si>
+    <t>21:06:30</t>
+  </si>
+  <si>
+    <t>22:44:01</t>
+  </si>
+  <si>
+    <t>00:20:31</t>
+  </si>
+  <si>
+    <t>01:55:25</t>
+  </si>
+  <si>
+    <t>21:50:44</t>
+  </si>
+  <si>
+    <t>23:27:26</t>
+  </si>
+  <si>
+    <t>01:03:04</t>
+  </si>
+  <si>
+    <t>20:57:17</t>
+  </si>
+  <si>
+    <t>22:34:11</t>
+  </si>
+  <si>
+    <t>00:10:15</t>
+  </si>
+  <si>
+    <t>20:03:35</t>
+  </si>
+  <si>
+    <t>21:40:47</t>
+  </si>
+  <si>
+    <t>23:17:08</t>
+  </si>
+  <si>
+    <t>19:09:24</t>
+  </si>
+  <si>
+    <t>20:47:15</t>
+  </si>
+  <si>
+    <t>22:23:48</t>
+  </si>
+  <si>
+    <t>23:59:03</t>
+  </si>
+  <si>
+    <t>19:53:33</t>
+  </si>
+  <si>
+    <t>21:30:18</t>
+  </si>
+  <si>
+    <t>23:06:07</t>
+  </si>
+  <si>
+    <t>18:59:38</t>
+  </si>
+  <si>
+    <t>20:36:38</t>
+  </si>
+  <si>
+    <t>22:12:49</t>
+  </si>
+  <si>
+    <t>01:15:46</t>
+  </si>
+  <si>
+    <t>21:09:23</t>
+  </si>
+  <si>
+    <t>22:46:17</t>
+  </si>
+  <si>
+    <t>00:22:48</t>
+  </si>
+  <si>
+    <t>01:58:30</t>
+  </si>
+  <si>
+    <t>21:53:04</t>
+  </si>
+  <si>
+    <t>23:29:40</t>
+  </si>
+  <si>
+    <t>01:05:41</t>
+  </si>
+  <si>
+    <t>20:59:43</t>
+  </si>
+  <si>
+    <t>22:36:25</t>
   </si>
   <si>
     <t>00:12:40</t>
   </si>
   <si>
-    <t>01:49:37</t>
-  </si>
-  <si>
-    <t>21:43:05</t>
-  </si>
-  <si>
-    <t>23:19:30</t>
-  </si>
-  <si>
-    <t>00:56:17</t>
-  </si>
-  <si>
-    <t>20:50:02</t>
-  </si>
-  <si>
-    <t>22:26:15</t>
-  </si>
-  <si>
-    <t>00:02:56</t>
-  </si>
-  <si>
-    <t>19:56:58</t>
-  </si>
-  <si>
-    <t>21:32:57</t>
-  </si>
-  <si>
-    <t>23:09:32</t>
-  </si>
-  <si>
-    <t>19:03:58</t>
-  </si>
-  <si>
-    <t>20:39:36</t>
-  </si>
-  <si>
-    <t>22:16:04</t>
-  </si>
-  <si>
-    <t>23:52:55</t>
-  </si>
-  <si>
-    <t>19:46:13</t>
-  </si>
-  <si>
-    <t>21:22:32</t>
-  </si>
-  <si>
-    <t>22:59:15</t>
-  </si>
-  <si>
-    <t>00:24:20</t>
-  </si>
-  <si>
-    <t>02:01:19</t>
-  </si>
-  <si>
-    <t>21:55:34</t>
-  </si>
-  <si>
-    <t>23:31:22</t>
-  </si>
-  <si>
-    <t>01:08:08</t>
-  </si>
-  <si>
-    <t>21:03:11</t>
-  </si>
-  <si>
-    <t>22:38:23</t>
-  </si>
-  <si>
-    <t>00:14:56</t>
-  </si>
-  <si>
-    <t>01:52:41</t>
-  </si>
-  <si>
-    <t>21:45:24</t>
-  </si>
-  <si>
-    <t>23:21:43</t>
-  </si>
-  <si>
-    <t>00:58:54</t>
-  </si>
-  <si>
-    <t>20:52:27</t>
-  </si>
-  <si>
-    <t>22:28:28</t>
-  </si>
-  <si>
-    <t>00:05:21</t>
-  </si>
-  <si>
-    <t>19:59:36</t>
-  </si>
-  <si>
-    <t>21:35:11</t>
-  </si>
-  <si>
-    <t>23:11:50</t>
-  </si>
-  <si>
-    <t>19:07:08</t>
-  </si>
-  <si>
-    <t>20:41:52</t>
-  </si>
-  <si>
-    <t>22:18:19</t>
-  </si>
-  <si>
-    <t>23:55:44</t>
-  </si>
-  <si>
-    <t>19:48:34</t>
-  </si>
-  <si>
-    <t>21:24:45</t>
-  </si>
-  <si>
-    <t>23:01:46</t>
-  </si>
-  <si>
-    <t>00:27:14</t>
-  </si>
-  <si>
-    <t>02:03:42</t>
-  </si>
-  <si>
-    <t>21:57:49</t>
-  </si>
-  <si>
-    <t>23:34:16</t>
-  </si>
-  <si>
-    <t>01:10:47</t>
-  </si>
-  <si>
-    <t>21:04:52</t>
-  </si>
-  <si>
-    <t>22:41:13</t>
-  </si>
-  <si>
-    <t>00:17:45</t>
-  </si>
-  <si>
-    <t>01:54:04</t>
-  </si>
-  <si>
-    <t>21:48:05</t>
-  </si>
-  <si>
-    <t>23:24:36</t>
-  </si>
-  <si>
-    <t>01:01:01</t>
-  </si>
-  <si>
-    <t>20:54:54</t>
-  </si>
-  <si>
-    <t>22:31:22</t>
-  </si>
-  <si>
-    <t>00:07:50</t>
-  </si>
-  <si>
-    <t>20:01:39</t>
-  </si>
-  <si>
-    <t>21:38:02</t>
-  </si>
-  <si>
-    <t>23:14:32</t>
-  </si>
-  <si>
-    <t>19:08:21</t>
-  </si>
-  <si>
-    <t>20:44:38</t>
-  </si>
-  <si>
-    <t>22:21:08</t>
-  </si>
-  <si>
-    <t>23:57:29</t>
-  </si>
-  <si>
-    <t>19:51:10</t>
-  </si>
-  <si>
-    <t>21:27:38</t>
-  </si>
-  <si>
-    <t>23:04:03</t>
-  </si>
-  <si>
-    <t>00:30:09</t>
-  </si>
-  <si>
-    <t>02:06:06</t>
-  </si>
-  <si>
-    <t>22:00:05</t>
-  </si>
-  <si>
-    <t>23:37:10</t>
-  </si>
-  <si>
-    <t>01:13:26</t>
-  </si>
-  <si>
-    <t>21:06:32</t>
-  </si>
-  <si>
-    <t>22:44:03</t>
-  </si>
-  <si>
-    <t>00:20:33</t>
-  </si>
-  <si>
-    <t>01:55:27</t>
-  </si>
-  <si>
-    <t>21:50:47</t>
-  </si>
-  <si>
-    <t>23:27:29</t>
-  </si>
-  <si>
-    <t>01:03:07</t>
-  </si>
-  <si>
-    <t>20:57:22</t>
-  </si>
-  <si>
-    <t>22:34:16</t>
-  </si>
-  <si>
-    <t>00:10:20</t>
-  </si>
-  <si>
-    <t>20:03:42</t>
-  </si>
-  <si>
-    <t>21:40:55</t>
-  </si>
-  <si>
-    <t>23:17:15</t>
-  </si>
-  <si>
-    <t>19:09:34</t>
-  </si>
-  <si>
-    <t>20:47:25</t>
-  </si>
-  <si>
-    <t>22:23:58</t>
-  </si>
-  <si>
-    <t>23:59:14</t>
-  </si>
-  <si>
-    <t>19:53:46</t>
-  </si>
-  <si>
-    <t>21:30:32</t>
-  </si>
-  <si>
-    <t>23:06:21</t>
-  </si>
-  <si>
-    <t>00:32:23</t>
-  </si>
-  <si>
-    <t>02:08:35</t>
-  </si>
-  <si>
-    <t>22:02:37</t>
-  </si>
-  <si>
-    <t>23:39:24</t>
-  </si>
-  <si>
-    <t>01:15:47</t>
-  </si>
-  <si>
-    <t>21:09:25</t>
-  </si>
-  <si>
-    <t>22:46:19</t>
-  </si>
-  <si>
-    <t>00:22:49</t>
-  </si>
-  <si>
-    <t>01:58:31</t>
-  </si>
-  <si>
-    <t>21:53:07</t>
-  </si>
-  <si>
-    <t>23:29:43</t>
-  </si>
-  <si>
-    <t>01:05:44</t>
-  </si>
-  <si>
-    <t>20:59:48</t>
-  </si>
-  <si>
-    <t>22:36:30</t>
-  </si>
-  <si>
-    <t>00:12:45</t>
-  </si>
-  <si>
-    <t>20:06:21</t>
-  </si>
-  <si>
-    <t>21:43:09</t>
-  </si>
-  <si>
-    <t>23:19:34</t>
-  </si>
-  <si>
-    <t>19:12:45</t>
-  </si>
-  <si>
-    <t>20:49:42</t>
-  </si>
-  <si>
-    <t>22:26:14</t>
-  </si>
-  <si>
-    <t>00:02:03</t>
-  </si>
-  <si>
-    <t>19:56:08</t>
-  </si>
-  <si>
-    <t>21:32:45</t>
-  </si>
-  <si>
-    <t>23:08:51</t>
+    <t>20:06:14</t>
+  </si>
+  <si>
+    <t>21:43:02</t>
+  </si>
+  <si>
+    <t>23:19:26</t>
+  </si>
+  <si>
+    <t>19:12:35</t>
+  </si>
+  <si>
+    <t>20:49:32</t>
+  </si>
+  <si>
+    <t>22:26:03</t>
+  </si>
+  <si>
+    <t>00:01:53</t>
+  </si>
+  <si>
+    <t>19:55:54</t>
+  </si>
+  <si>
+    <t>21:32:32</t>
+  </si>
+  <si>
+    <t>23:08:38</t>
+  </si>
+  <si>
+    <t>19:02:09</t>
+  </si>
+  <si>
+    <t>20:38:52</t>
+  </si>
+  <si>
+    <t>22:15:10</t>
   </si>
   <si>
     <t>0°</t>
+  </si>
+  <si>
+    <t>2°</t>
+  </si>
+  <si>
+    <t>18:53:06</t>
   </si>
   <si>
     <t>B</t>
@@ -659,31 +641,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -695,43 +653,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -749,25 +677,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1286,7 +1268,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1364,55 +1346,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="L2" s="4">
-        <v>-43</v>
+        <v>-38.8</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="O2" s="6">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="P2" s="7">
-        <v>99</v>
+        <v>51</v>
       </c>
       <c r="Q2" s="8">
-        <v>51</v>
-      </c>
-      <c r="R2" s="9">
-        <v>40</v>
+        <v>0</v>
+      </c>
+      <c r="R2" s="7">
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1420,55 +1402,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L3" s="4">
-        <v>-31.8</v>
+        <v>-42.8</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="O3" s="6">
         <v>100</v>
       </c>
-      <c r="P3" s="10">
-        <v>71</v>
-      </c>
-      <c r="Q3" s="11">
-        <v>23</v>
-      </c>
-      <c r="R3" s="12">
+      <c r="P3" s="8">
         <v>0</v>
+      </c>
+      <c r="Q3" s="9">
+        <v>85</v>
+      </c>
+      <c r="R3" s="10">
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1476,55 +1458,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="F4" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L4" s="4">
-        <v>-46.4</v>
+        <v>-48.1</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="O4" s="6">
-        <v>76</v>
-      </c>
-      <c r="P4" s="13">
-        <v>31</v>
-      </c>
-      <c r="Q4" s="12">
+        <v>97</v>
+      </c>
+      <c r="P4" s="8">
         <v>0</v>
       </c>
-      <c r="R4" s="14">
-        <v>55</v>
+      <c r="Q4" s="11">
+        <v>37</v>
+      </c>
+      <c r="R4" s="12">
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1532,55 +1514,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L5" s="4">
-        <v>-46.8</v>
+        <v>-44.4</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="O5" s="6">
-        <v>57</v>
-      </c>
-      <c r="P5" s="15">
-        <v>21</v>
-      </c>
-      <c r="Q5" s="12">
+        <v>99</v>
+      </c>
+      <c r="P5" s="8">
         <v>0</v>
       </c>
-      <c r="R5" s="16">
-        <v>46</v>
+      <c r="Q5" s="13">
+        <v>13</v>
+      </c>
+      <c r="R5" s="10">
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1588,55 +1570,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="L6" s="4">
-        <v>-38.8</v>
+        <v>-33.7</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="O6" s="6">
-        <v>77</v>
-      </c>
-      <c r="P6" s="17">
-        <v>14</v>
-      </c>
-      <c r="Q6" s="12">
+        <v>55</v>
+      </c>
+      <c r="P6" s="8">
         <v>0</v>
       </c>
-      <c r="R6" s="10">
-        <v>68</v>
+      <c r="Q6" s="8">
+        <v>0</v>
+      </c>
+      <c r="R6" s="14">
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1644,55 +1626,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="L7" s="4">
-        <v>-42.8</v>
+        <v>-46.6</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="O7" s="6">
-        <v>88</v>
-      </c>
-      <c r="P7" s="12">
+        <v>100</v>
+      </c>
+      <c r="P7" s="8">
         <v>0</v>
       </c>
-      <c r="Q7" s="18">
-        <v>63</v>
-      </c>
-      <c r="R7" s="19">
-        <v>75</v>
+      <c r="Q7" s="12">
+        <v>94</v>
+      </c>
+      <c r="R7" s="15">
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1700,55 +1682,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L8" s="4">
+        <v>-47.9</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="O8" s="6">
+        <v>77</v>
+      </c>
+      <c r="P8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="16">
         <v>74</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="L8" s="4">
-        <v>-48.1</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O8" s="6">
-        <v>100</v>
-      </c>
-      <c r="P8" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="20">
-        <v>36</v>
-      </c>
-      <c r="R8" s="7">
-        <v>100</v>
+      <c r="R8" s="17">
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1756,55 +1738,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="L9" s="4">
-        <v>-44.4</v>
+        <v>-40.6</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="O9" s="6">
-        <v>95</v>
-      </c>
-      <c r="P9" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="12">
-        <v>2</v>
-      </c>
-      <c r="R9" s="21">
-        <v>95</v>
+        <v>98</v>
+      </c>
+      <c r="P9" s="13">
+        <v>14</v>
+      </c>
+      <c r="Q9" s="15">
+        <v>91</v>
+      </c>
+      <c r="R9" s="18">
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1812,55 +1794,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L10" s="4">
-        <v>-33.7</v>
+        <v>-42.5</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="O10" s="6">
-        <v>75</v>
-      </c>
-      <c r="P10" s="12">
-        <v>0</v>
+        <v>98</v>
+      </c>
+      <c r="P10" s="15">
+        <v>92</v>
       </c>
       <c r="Q10" s="12">
-        <v>2</v>
-      </c>
-      <c r="R10" s="10">
-        <v>69</v>
+        <v>95</v>
+      </c>
+      <c r="R10" s="19">
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1868,55 +1850,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L11" s="4">
-        <v>-46.6</v>
+        <v>-48.7</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="O11" s="6">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P11" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="22">
+        <v>95</v>
+      </c>
+      <c r="Q11" s="20">
         <v>80</v>
       </c>
-      <c r="R11" s="7">
-        <v>98</v>
+      <c r="R11" s="21">
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1924,55 +1906,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L12" s="4">
-        <v>-47.9</v>
+        <v>-45.9</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="O12" s="6">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="P12" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="14">
-        <v>57</v>
-      </c>
-      <c r="R12" s="22">
-        <v>82</v>
+        <v>95</v>
+      </c>
+      <c r="Q12" s="15">
+        <v>91</v>
+      </c>
+      <c r="R12" s="19">
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1983,52 +1965,52 @@
         <v>16</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="L13" s="4">
-        <v>-40.6</v>
+        <v>-36.6</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="O13" s="6">
-        <v>74</v>
-      </c>
-      <c r="P13" s="23">
-        <v>8</v>
-      </c>
-      <c r="Q13" s="10">
-        <v>70</v>
-      </c>
-      <c r="R13" s="14">
-        <v>53</v>
+        <v>71</v>
+      </c>
+      <c r="P13" s="22">
+        <v>46</v>
+      </c>
+      <c r="Q13" s="21">
+        <v>31</v>
+      </c>
+      <c r="R13" s="21">
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2036,55 +2018,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L14" s="4">
-        <v>-42.5</v>
+        <v>-46.6</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="O14" s="6">
-        <v>90</v>
-      </c>
-      <c r="P14" s="13">
-        <v>29</v>
-      </c>
-      <c r="Q14" s="9">
-        <v>42</v>
-      </c>
-      <c r="R14" s="15">
-        <v>20</v>
+        <v>82</v>
+      </c>
+      <c r="P14" s="7">
+        <v>51</v>
+      </c>
+      <c r="Q14" s="21">
+        <v>31</v>
+      </c>
+      <c r="R14" s="17">
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2092,55 +2074,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="L15" s="4">
-        <v>-48.7</v>
+        <v>-48.9</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="O15" s="6">
-        <v>96</v>
-      </c>
-      <c r="P15" s="13">
-        <v>32</v>
-      </c>
-      <c r="Q15" s="14">
-        <v>53</v>
-      </c>
-      <c r="R15" s="24">
-        <v>5</v>
+        <v>90</v>
+      </c>
+      <c r="P15" s="22">
+        <v>45</v>
+      </c>
+      <c r="Q15" s="23">
+        <v>19</v>
+      </c>
+      <c r="R15" s="15">
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2148,55 +2130,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L16" s="4">
-        <v>-45.9</v>
+        <v>-29.5</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="O16" s="6">
-        <v>97</v>
-      </c>
-      <c r="P16" s="13">
-        <v>31</v>
-      </c>
-      <c r="Q16" s="22">
-        <v>82</v>
-      </c>
-      <c r="R16" s="24">
-        <v>5</v>
+        <v>85</v>
+      </c>
+      <c r="P16" s="9">
+        <v>84</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>0</v>
+      </c>
+      <c r="R16" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2204,55 +2186,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L17" s="4">
-        <v>-36.6</v>
+        <v>-42.1</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="O17" s="6">
-        <v>70</v>
-      </c>
-      <c r="P17" s="15">
-        <v>21</v>
-      </c>
-      <c r="Q17" s="24">
-        <v>4</v>
-      </c>
-      <c r="R17" s="15">
-        <v>22</v>
+        <v>60</v>
+      </c>
+      <c r="P17" s="17">
+        <v>60</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>0</v>
+      </c>
+      <c r="R17" s="24">
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2260,55 +2242,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L18" s="4">
-        <v>-46.6</v>
+        <v>-49.2</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="O18" s="6">
-        <v>64</v>
-      </c>
-      <c r="P18" s="15">
-        <v>21</v>
-      </c>
-      <c r="Q18" s="24">
-        <v>4</v>
-      </c>
-      <c r="R18" s="15">
-        <v>20</v>
+        <v>89</v>
+      </c>
+      <c r="P18" s="14">
+        <v>57</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>0</v>
+      </c>
+      <c r="R18" s="14">
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2316,55 +2298,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>59</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="I19" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>193</v>
-      </c>
       <c r="K19" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="L19" s="4">
-        <v>-48.9</v>
+        <v>-47.3</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="O19" s="6">
-        <v>54</v>
-      </c>
-      <c r="P19" s="15">
-        <v>22</v>
-      </c>
-      <c r="Q19" s="24">
-        <v>3</v>
-      </c>
-      <c r="R19" s="17">
-        <v>16</v>
+        <v>76</v>
+      </c>
+      <c r="P19" s="22">
+        <v>44</v>
+      </c>
+      <c r="Q19" s="8">
+        <v>0</v>
+      </c>
+      <c r="R19" s="7">
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2372,55 +2354,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>60</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="L20" s="4">
-        <v>-29.5</v>
+        <v>-35.8</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="O20" s="6">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="P20" s="20">
-        <v>37</v>
-      </c>
-      <c r="Q20" s="12">
-        <v>0</v>
-      </c>
-      <c r="R20" s="12">
-        <v>0</v>
+        <v>78</v>
+      </c>
+      <c r="Q20" s="11">
+        <v>33</v>
+      </c>
+      <c r="R20" s="25">
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2428,55 +2410,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>61</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="L21" s="4">
-        <v>-42.1</v>
+        <v>-46.6</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="O21" s="6">
-        <v>62</v>
-      </c>
-      <c r="P21" s="20">
-        <v>33</v>
-      </c>
-      <c r="Q21" s="12">
-        <v>0</v>
-      </c>
-      <c r="R21" s="12">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="P21" s="16">
+        <v>73</v>
+      </c>
+      <c r="Q21" s="24">
+        <v>23</v>
+      </c>
+      <c r="R21" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2484,55 +2466,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="I22" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L22" s="4">
+        <v>-49.9</v>
+      </c>
+      <c r="M22" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="L22" s="4">
-        <v>-49.2</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="N22" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="O22" s="6">
-        <v>57</v>
-      </c>
-      <c r="P22" s="23">
-        <v>10</v>
-      </c>
-      <c r="Q22" s="12">
-        <v>0</v>
-      </c>
-      <c r="R22" s="12">
-        <v>0</v>
+        <v>69</v>
+      </c>
+      <c r="P22" s="17">
+        <v>60</v>
+      </c>
+      <c r="Q22" s="23">
+        <v>20</v>
+      </c>
+      <c r="R22" s="25">
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2540,55 +2522,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>63</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="I23" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="L23" s="4">
+        <v>-28.3</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="N23" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="L23" s="4">
-        <v>-47.3</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="O23" s="6">
-        <v>64</v>
-      </c>
-      <c r="P23" s="23">
-        <v>8</v>
-      </c>
-      <c r="Q23" s="12">
-        <v>0</v>
-      </c>
-      <c r="R23" s="12">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="P23" s="9">
+        <v>84</v>
+      </c>
+      <c r="Q23" s="19">
+        <v>40</v>
+      </c>
+      <c r="R23" s="20">
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2596,55 +2578,55 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="E24" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="L24" s="4">
+        <v>-41.6</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="O24" s="6">
+        <v>97</v>
+      </c>
+      <c r="P24" s="20">
+        <v>79</v>
+      </c>
+      <c r="Q24" s="17">
+        <v>61</v>
+      </c>
+      <c r="R24" s="18">
         <v>67</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="L24" s="4">
-        <v>-35.9</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O24" s="6">
-        <v>49</v>
-      </c>
-      <c r="P24" s="9">
-        <v>39</v>
-      </c>
-      <c r="Q24" s="12">
-        <v>0</v>
-      </c>
-      <c r="R24" s="12">
-        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2652,170 +2634,114 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L25" s="4">
-        <v>-46.6</v>
+        <v>-49.5</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O25" s="25">
-        <v>48</v>
-      </c>
-      <c r="P25" s="13">
-        <v>32</v>
-      </c>
-      <c r="Q25" s="12">
-        <v>0</v>
-      </c>
-      <c r="R25" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18">
-      <c r="A26" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="O25" s="6">
+        <v>93</v>
+      </c>
+      <c r="P25" s="18">
+        <v>66</v>
+      </c>
+      <c r="Q25" s="17">
+        <v>61</v>
+      </c>
+      <c r="R25" s="19">
         <v>42</v>
-      </c>
-      <c r="B26" s="2">
-        <v>18</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="L26" s="4">
-        <v>-49.9</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O26" s="25">
-        <v>44</v>
-      </c>
-      <c r="P26" s="13">
-        <v>28</v>
-      </c>
-      <c r="Q26" s="12">
-        <v>0</v>
-      </c>
-      <c r="R26" s="12">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A26">
+  <conditionalFormatting sqref="A2:A25">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B26">
+  <conditionalFormatting sqref="B2:B25">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C26">
+  <conditionalFormatting sqref="C2:C25">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D26">
+  <conditionalFormatting sqref="D2:D25">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E26">
+  <conditionalFormatting sqref="E2:E25">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F26">
+  <conditionalFormatting sqref="F2:F25">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G26">
+  <conditionalFormatting sqref="G2:G25">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H26">
+  <conditionalFormatting sqref="H2:H25">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I26">
+  <conditionalFormatting sqref="I2:I25">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J26">
+  <conditionalFormatting sqref="J2:J25">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K26">
+  <conditionalFormatting sqref="K2:K25">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L26">
+  <conditionalFormatting sqref="L2:L25">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2834,12 +2760,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M26">
+  <conditionalFormatting sqref="M2:M25">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N26">
+  <conditionalFormatting sqref="N2:N25">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2856,22 +2782,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O26">
+  <conditionalFormatting sqref="O2:O25">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P26">
+  <conditionalFormatting sqref="P2:P25">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q26">
+  <conditionalFormatting sqref="Q2:Q25">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R26">
+  <conditionalFormatting sqref="R2:R25">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="199">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261015--01</t>
-  </si>
-  <si>
-    <t>20261015--02</t>
-  </si>
-  <si>
-    <t>20261015--03</t>
-  </si>
-  <si>
     <t>20261016--01</t>
   </si>
   <si>
@@ -142,57 +133,60 @@
     <t>20261021--03</t>
   </si>
   <si>
-    <t>05:18</t>
-  </si>
-  <si>
-    <t>03:20</t>
+    <t>20261022--01</t>
+  </si>
+  <si>
+    <t>20261022--02</t>
+  </si>
+  <si>
+    <t>20261022--03</t>
+  </si>
+  <si>
+    <t>20261022--04</t>
+  </si>
+  <si>
+    <t>05:36</t>
+  </si>
+  <si>
+    <t>02:45</t>
+  </si>
+  <si>
+    <t>05:23</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>04:13</t>
+  </si>
+  <si>
+    <t>04:55</t>
+  </si>
+  <si>
+    <t>05:47</t>
+  </si>
+  <si>
+    <t>04:59</t>
+  </si>
+  <si>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>05:44</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>02:25</t>
+  </si>
+  <si>
+    <t>05:32</t>
   </si>
   <si>
     <t>05:39</t>
   </si>
   <si>
-    <t>05:36</t>
-  </si>
-  <si>
-    <t>02:45</t>
-  </si>
-  <si>
-    <t>05:23</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>04:13</t>
-  </si>
-  <si>
-    <t>04:55</t>
-  </si>
-  <si>
-    <t>05:48</t>
-  </si>
-  <si>
-    <t>04:59</t>
-  </si>
-  <si>
-    <t>04:05</t>
-  </si>
-  <si>
-    <t>05:43</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>02:25</t>
-  </si>
-  <si>
-    <t>05:33</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
     <t>03:29</t>
   </si>
   <si>
@@ -202,373 +196,397 @@
     <t>05:46</t>
   </si>
   <si>
+    <t>04:34</t>
+  </si>
+  <si>
     <t>04:35</t>
   </si>
   <si>
-    <t>04:34</t>
+    <t>05:11</t>
+  </si>
+  <si>
+    <t>03:28</t>
+  </si>
+  <si>
+    <t>02:24</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:05:47</t>
-  </si>
-  <si>
-    <t>21:00:19</t>
-  </si>
-  <si>
-    <t>22:36:07</t>
-  </si>
-  <si>
-    <t>00:12:39</t>
-  </si>
-  <si>
-    <t>01:49:35</t>
-  </si>
-  <si>
-    <t>21:43:03</t>
-  </si>
-  <si>
-    <t>23:19:27</t>
-  </si>
-  <si>
-    <t>00:56:14</t>
-  </si>
-  <si>
-    <t>20:49:57</t>
+    <t>00:12:40</t>
+  </si>
+  <si>
+    <t>01:49:36</t>
+  </si>
+  <si>
+    <t>21:43:05</t>
+  </si>
+  <si>
+    <t>23:19:29</t>
+  </si>
+  <si>
+    <t>00:56:16</t>
+  </si>
+  <si>
+    <t>20:50:00</t>
+  </si>
+  <si>
+    <t>22:26:13</t>
+  </si>
+  <si>
+    <t>00:02:54</t>
+  </si>
+  <si>
+    <t>19:56:56</t>
+  </si>
+  <si>
+    <t>21:32:54</t>
+  </si>
+  <si>
+    <t>23:09:29</t>
+  </si>
+  <si>
+    <t>19:03:55</t>
+  </si>
+  <si>
+    <t>20:39:32</t>
+  </si>
+  <si>
+    <t>22:16:00</t>
+  </si>
+  <si>
+    <t>23:52:51</t>
+  </si>
+  <si>
+    <t>19:46:08</t>
+  </si>
+  <si>
+    <t>21:22:27</t>
+  </si>
+  <si>
+    <t>22:59:10</t>
+  </si>
+  <si>
+    <t>18:52:44</t>
+  </si>
+  <si>
+    <t>20:28:50</t>
+  </si>
+  <si>
+    <t>22:05:26</t>
+  </si>
+  <si>
+    <t>17:59:21</t>
+  </si>
+  <si>
+    <t>19:35:09</t>
+  </si>
+  <si>
+    <t>21:11:40</t>
+  </si>
+  <si>
+    <t>22:48:35</t>
+  </si>
+  <si>
+    <t>00:14:56</t>
+  </si>
+  <si>
+    <t>01:52:41</t>
+  </si>
+  <si>
+    <t>21:45:23</t>
+  </si>
+  <si>
+    <t>23:21:43</t>
+  </si>
+  <si>
+    <t>00:58:53</t>
+  </si>
+  <si>
+    <t>20:52:25</t>
+  </si>
+  <si>
+    <t>22:28:27</t>
+  </si>
+  <si>
+    <t>00:05:19</t>
+  </si>
+  <si>
+    <t>19:59:34</t>
+  </si>
+  <si>
+    <t>21:35:08</t>
+  </si>
+  <si>
+    <t>23:11:47</t>
+  </si>
+  <si>
+    <t>19:07:05</t>
+  </si>
+  <si>
+    <t>20:41:49</t>
+  </si>
+  <si>
+    <t>22:18:15</t>
+  </si>
+  <si>
+    <t>23:55:40</t>
+  </si>
+  <si>
+    <t>19:48:29</t>
+  </si>
+  <si>
+    <t>21:24:40</t>
+  </si>
+  <si>
+    <t>23:01:41</t>
+  </si>
+  <si>
+    <t>18:55:14</t>
+  </si>
+  <si>
+    <t>20:31:03</t>
+  </si>
+  <si>
+    <t>22:07:48</t>
+  </si>
+  <si>
+    <t>18:02:10</t>
+  </si>
+  <si>
+    <t>19:37:24</t>
+  </si>
+  <si>
+    <t>21:13:56</t>
+  </si>
+  <si>
+    <t>22:51:46</t>
+  </si>
+  <si>
+    <t>00:17:44</t>
+  </si>
+  <si>
+    <t>01:54:03</t>
+  </si>
+  <si>
+    <t>21:48:04</t>
+  </si>
+  <si>
+    <t>23:24:35</t>
+  </si>
+  <si>
+    <t>01:01:00</t>
+  </si>
+  <si>
+    <t>20:54:52</t>
+  </si>
+  <si>
+    <t>22:31:20</t>
+  </si>
+  <si>
+    <t>00:07:48</t>
+  </si>
+  <si>
+    <t>20:01:37</t>
+  </si>
+  <si>
+    <t>21:38:00</t>
+  </si>
+  <si>
+    <t>23:14:30</t>
+  </si>
+  <si>
+    <t>19:08:17</t>
+  </si>
+  <si>
+    <t>20:44:34</t>
+  </si>
+  <si>
+    <t>22:21:05</t>
+  </si>
+  <si>
+    <t>23:57:25</t>
+  </si>
+  <si>
+    <t>19:51:05</t>
+  </si>
+  <si>
+    <t>21:27:33</t>
+  </si>
+  <si>
+    <t>23:03:58</t>
+  </si>
+  <si>
+    <t>18:57:31</t>
+  </si>
+  <si>
+    <t>20:33:56</t>
+  </si>
+  <si>
+    <t>22:10:24</t>
+  </si>
+  <si>
+    <t>18:03:54</t>
+  </si>
+  <si>
+    <t>19:40:13</t>
+  </si>
+  <si>
+    <t>21:16:42</t>
+  </si>
+  <si>
+    <t>22:52:58</t>
+  </si>
+  <si>
+    <t>00:20:32</t>
+  </si>
+  <si>
+    <t>01:55:26</t>
+  </si>
+  <si>
+    <t>21:50:46</t>
+  </si>
+  <si>
+    <t>23:27:28</t>
+  </si>
+  <si>
+    <t>01:03:06</t>
+  </si>
+  <si>
+    <t>20:57:20</t>
+  </si>
+  <si>
+    <t>22:34:14</t>
+  </si>
+  <si>
+    <t>00:10:18</t>
+  </si>
+  <si>
+    <t>20:03:39</t>
+  </si>
+  <si>
+    <t>21:40:52</t>
+  </si>
+  <si>
+    <t>23:17:12</t>
+  </si>
+  <si>
+    <t>19:09:30</t>
+  </si>
+  <si>
+    <t>20:47:21</t>
+  </si>
+  <si>
+    <t>22:23:54</t>
+  </si>
+  <si>
+    <t>23:59:09</t>
+  </si>
+  <si>
+    <t>19:53:41</t>
+  </si>
+  <si>
+    <t>21:30:26</t>
+  </si>
+  <si>
+    <t>23:06:15</t>
+  </si>
+  <si>
+    <t>18:59:49</t>
+  </si>
+  <si>
+    <t>20:36:49</t>
+  </si>
+  <si>
+    <t>22:12:59</t>
+  </si>
+  <si>
+    <t>18:05:38</t>
+  </si>
+  <si>
+    <t>19:43:03</t>
+  </si>
+  <si>
+    <t>21:19:28</t>
+  </si>
+  <si>
+    <t>22:54:10</t>
+  </si>
+  <si>
+    <t>00:22:49</t>
+  </si>
+  <si>
+    <t>01:58:31</t>
+  </si>
+  <si>
+    <t>21:53:05</t>
+  </si>
+  <si>
+    <t>23:29:42</t>
+  </si>
+  <si>
+    <t>01:05:43</t>
+  </si>
+  <si>
+    <t>20:59:46</t>
+  </si>
+  <si>
+    <t>22:36:28</t>
+  </si>
+  <si>
+    <t>00:12:43</t>
+  </si>
+  <si>
+    <t>20:06:18</t>
+  </si>
+  <si>
+    <t>21:43:06</t>
+  </si>
+  <si>
+    <t>23:19:31</t>
+  </si>
+  <si>
+    <t>19:12:41</t>
+  </si>
+  <si>
+    <t>20:49:38</t>
   </si>
   <si>
     <t>22:26:10</t>
   </si>
   <si>
-    <t>00:02:51</t>
-  </si>
-  <si>
-    <t>19:56:52</t>
-  </si>
-  <si>
-    <t>21:32:50</t>
-  </si>
-  <si>
-    <t>23:09:24</t>
-  </si>
-  <si>
-    <t>19:03:49</t>
-  </si>
-  <si>
-    <t>20:39:26</t>
-  </si>
-  <si>
-    <t>22:15:53</t>
-  </si>
-  <si>
-    <t>23:52:44</t>
-  </si>
-  <si>
-    <t>19:46:00</t>
-  </si>
-  <si>
-    <t>21:22:18</t>
-  </si>
-  <si>
-    <t>22:59:01</t>
-  </si>
-  <si>
-    <t>18:52:34</t>
-  </si>
-  <si>
-    <t>20:28:39</t>
-  </si>
-  <si>
-    <t>22:05:16</t>
-  </si>
-  <si>
-    <t>01:08:07</t>
-  </si>
-  <si>
-    <t>21:03:10</t>
-  </si>
-  <si>
-    <t>22:38:22</t>
-  </si>
-  <si>
-    <t>00:14:55</t>
-  </si>
-  <si>
-    <t>01:52:40</t>
-  </si>
-  <si>
-    <t>21:45:21</t>
-  </si>
-  <si>
-    <t>23:21:41</t>
-  </si>
-  <si>
-    <t>00:58:51</t>
-  </si>
-  <si>
-    <t>20:52:22</t>
-  </si>
-  <si>
-    <t>22:28:23</t>
-  </si>
-  <si>
-    <t>00:05:16</t>
-  </si>
-  <si>
-    <t>19:59:30</t>
-  </si>
-  <si>
-    <t>21:35:04</t>
-  </si>
-  <si>
-    <t>23:11:43</t>
-  </si>
-  <si>
-    <t>19:06:59</t>
-  </si>
-  <si>
-    <t>20:41:42</t>
-  </si>
-  <si>
-    <t>22:18:08</t>
-  </si>
-  <si>
-    <t>23:55:34</t>
-  </si>
-  <si>
-    <t>19:48:21</t>
-  </si>
-  <si>
-    <t>21:24:32</t>
-  </si>
-  <si>
-    <t>23:01:32</t>
-  </si>
-  <si>
-    <t>18:55:04</t>
-  </si>
-  <si>
-    <t>20:30:52</t>
-  </si>
-  <si>
-    <t>22:07:37</t>
-  </si>
-  <si>
-    <t>01:10:46</t>
-  </si>
-  <si>
-    <t>21:04:50</t>
-  </si>
-  <si>
-    <t>22:41:11</t>
-  </si>
-  <si>
-    <t>00:17:43</t>
-  </si>
-  <si>
-    <t>01:54:02</t>
-  </si>
-  <si>
-    <t>21:48:03</t>
-  </si>
-  <si>
-    <t>23:24:33</t>
-  </si>
-  <si>
-    <t>01:00:57</t>
-  </si>
-  <si>
-    <t>20:54:49</t>
-  </si>
-  <si>
-    <t>22:31:17</t>
-  </si>
-  <si>
-    <t>00:07:45</t>
-  </si>
-  <si>
-    <t>20:01:32</t>
-  </si>
-  <si>
-    <t>21:37:55</t>
-  </si>
-  <si>
-    <t>23:14:25</t>
-  </si>
-  <si>
-    <t>19:08:11</t>
-  </si>
-  <si>
-    <t>20:44:28</t>
-  </si>
-  <si>
-    <t>22:20:58</t>
-  </si>
-  <si>
-    <t>23:57:18</t>
-  </si>
-  <si>
-    <t>19:50:56</t>
-  </si>
-  <si>
-    <t>21:27:25</t>
-  </si>
-  <si>
-    <t>23:03:50</t>
-  </si>
-  <si>
-    <t>18:57:21</t>
-  </si>
-  <si>
-    <t>20:33:45</t>
-  </si>
-  <si>
-    <t>22:10:13</t>
-  </si>
-  <si>
-    <t>01:13:25</t>
-  </si>
-  <si>
-    <t>21:06:30</t>
-  </si>
-  <si>
-    <t>22:44:01</t>
-  </si>
-  <si>
-    <t>00:20:31</t>
-  </si>
-  <si>
-    <t>01:55:25</t>
-  </si>
-  <si>
-    <t>21:50:44</t>
-  </si>
-  <si>
-    <t>23:27:26</t>
-  </si>
-  <si>
-    <t>01:03:04</t>
-  </si>
-  <si>
-    <t>20:57:17</t>
-  </si>
-  <si>
-    <t>22:34:11</t>
-  </si>
-  <si>
-    <t>00:10:15</t>
-  </si>
-  <si>
-    <t>20:03:35</t>
-  </si>
-  <si>
-    <t>21:40:47</t>
-  </si>
-  <si>
-    <t>23:17:08</t>
-  </si>
-  <si>
-    <t>19:09:24</t>
-  </si>
-  <si>
-    <t>20:47:15</t>
-  </si>
-  <si>
-    <t>22:23:48</t>
-  </si>
-  <si>
-    <t>23:59:03</t>
-  </si>
-  <si>
-    <t>19:53:33</t>
-  </si>
-  <si>
-    <t>21:30:18</t>
-  </si>
-  <si>
-    <t>23:06:07</t>
-  </si>
-  <si>
-    <t>18:59:38</t>
-  </si>
-  <si>
-    <t>20:36:38</t>
-  </si>
-  <si>
-    <t>22:12:49</t>
-  </si>
-  <si>
-    <t>01:15:46</t>
-  </si>
-  <si>
-    <t>21:09:23</t>
-  </si>
-  <si>
-    <t>22:46:17</t>
-  </si>
-  <si>
-    <t>00:22:48</t>
-  </si>
-  <si>
-    <t>01:58:30</t>
-  </si>
-  <si>
-    <t>21:53:04</t>
-  </si>
-  <si>
-    <t>23:29:40</t>
-  </si>
-  <si>
-    <t>01:05:41</t>
-  </si>
-  <si>
-    <t>20:59:43</t>
-  </si>
-  <si>
-    <t>22:36:25</t>
-  </si>
-  <si>
-    <t>00:12:40</t>
-  </si>
-  <si>
-    <t>20:06:14</t>
-  </si>
-  <si>
-    <t>21:43:02</t>
-  </si>
-  <si>
-    <t>23:19:26</t>
-  </si>
-  <si>
-    <t>19:12:35</t>
-  </si>
-  <si>
-    <t>20:49:32</t>
-  </si>
-  <si>
-    <t>22:26:03</t>
-  </si>
-  <si>
-    <t>00:01:53</t>
-  </si>
-  <si>
-    <t>19:55:54</t>
-  </si>
-  <si>
-    <t>21:32:32</t>
-  </si>
-  <si>
-    <t>23:08:38</t>
-  </si>
-  <si>
-    <t>19:02:09</t>
-  </si>
-  <si>
-    <t>20:38:52</t>
-  </si>
-  <si>
-    <t>22:15:10</t>
+    <t>00:01:59</t>
+  </si>
+  <si>
+    <t>19:56:02</t>
+  </si>
+  <si>
+    <t>21:32:40</t>
+  </si>
+  <si>
+    <t>23:08:46</t>
+  </si>
+  <si>
+    <t>19:02:19</t>
+  </si>
+  <si>
+    <t>20:39:02</t>
+  </si>
+  <si>
+    <t>22:15:21</t>
+  </si>
+  <si>
+    <t>18:08:28</t>
+  </si>
+  <si>
+    <t>19:45:18</t>
+  </si>
+  <si>
+    <t>21:21:45</t>
+  </si>
+  <si>
+    <t>22:57:21</t>
   </si>
   <si>
     <t>0°</t>
@@ -577,7 +595,13 @@
     <t>2°</t>
   </si>
   <si>
-    <t>18:53:06</t>
+    <t>10°</t>
+  </si>
+  <si>
+    <t>18:53:16</t>
+  </si>
+  <si>
+    <t>18:02:07</t>
   </si>
   <si>
     <t>B</t>
@@ -641,13 +665,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -659,67 +701,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFEEF3F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -737,7 +725,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -749,7 +761,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1268,7 +1292,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1346,55 +1370,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L2" s="4">
-        <v>-38.8</v>
+        <v>-44.4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="O2" s="6">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="P2" s="7">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="8">
-        <v>0</v>
-      </c>
-      <c r="R2" s="7">
-        <v>49</v>
+        <v>18</v>
+      </c>
+      <c r="R2" s="9">
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1402,55 +1426,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L3" s="4">
-        <v>-42.8</v>
+        <v>-33.7</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="O3" s="6">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="P3" s="8">
+        <v>19</v>
+      </c>
+      <c r="Q3" s="7">
         <v>0</v>
       </c>
-      <c r="Q3" s="9">
-        <v>85</v>
-      </c>
       <c r="R3" s="10">
-        <v>100</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1458,55 +1482,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L4" s="4">
-        <v>-48.1</v>
+        <v>-46.6</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="O4" s="6">
-        <v>97</v>
-      </c>
-      <c r="P4" s="8">
+        <v>95</v>
+      </c>
+      <c r="P4" s="7">
         <v>0</v>
       </c>
       <c r="Q4" s="11">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="R4" s="12">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1514,55 +1538,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L5" s="4">
-        <v>-44.4</v>
+        <v>-47.9</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="O5" s="6">
-        <v>99</v>
-      </c>
-      <c r="P5" s="8">
+        <v>96</v>
+      </c>
+      <c r="P5" s="7">
         <v>0</v>
       </c>
       <c r="Q5" s="13">
-        <v>13</v>
-      </c>
-      <c r="R5" s="10">
-        <v>98</v>
+        <v>90</v>
+      </c>
+      <c r="R5" s="13">
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1570,55 +1594,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L6" s="4">
-        <v>-33.7</v>
+        <v>-40.6</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="O6" s="6">
-        <v>55</v>
-      </c>
-      <c r="P6" s="8">
+        <v>95</v>
+      </c>
+      <c r="P6" s="7">
         <v>0</v>
       </c>
-      <c r="Q6" s="8">
-        <v>0</v>
+      <c r="Q6" s="13">
+        <v>91</v>
       </c>
       <c r="R6" s="14">
-        <v>55</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1626,55 +1650,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L7" s="4">
+        <v>-42.5</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="O7" s="6">
+        <v>99</v>
+      </c>
+      <c r="P7" s="12">
+        <v>84</v>
+      </c>
+      <c r="Q7" s="11">
         <v>94</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="L7" s="4">
-        <v>-46.6</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="O7" s="6">
-        <v>100</v>
-      </c>
-      <c r="P7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="12">
-        <v>94</v>
-      </c>
       <c r="R7" s="15">
-        <v>92</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1682,55 +1706,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L8" s="4">
-        <v>-47.9</v>
+        <v>-48.7</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="O8" s="6">
-        <v>77</v>
-      </c>
-      <c r="P8" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="16">
-        <v>74</v>
-      </c>
-      <c r="R8" s="17">
-        <v>58</v>
+        <v>99</v>
+      </c>
+      <c r="P8" s="13">
+        <v>88</v>
+      </c>
+      <c r="Q8" s="13">
+        <v>92</v>
+      </c>
+      <c r="R8" s="16">
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1738,55 +1762,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L9" s="4">
-        <v>-40.6</v>
+        <v>-45.9</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="O9" s="6">
-        <v>98</v>
-      </c>
-      <c r="P9" s="13">
-        <v>14</v>
-      </c>
-      <c r="Q9" s="15">
-        <v>91</v>
+        <v>97</v>
+      </c>
+      <c r="P9" s="17">
+        <v>81</v>
+      </c>
+      <c r="Q9" s="13">
+        <v>90</v>
       </c>
       <c r="R9" s="18">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1794,54 +1818,54 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L10" s="4">
-        <v>-42.5</v>
+        <v>-36.6</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="O10" s="6">
-        <v>98</v>
-      </c>
-      <c r="P10" s="15">
-        <v>92</v>
-      </c>
-      <c r="Q10" s="12">
-        <v>95</v>
-      </c>
-      <c r="R10" s="19">
+        <v>81</v>
+      </c>
+      <c r="P10" s="19">
+        <v>35</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>0</v>
+      </c>
+      <c r="R10" s="20">
         <v>40</v>
       </c>
     </row>
@@ -1850,55 +1874,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L11" s="4">
-        <v>-48.7</v>
+        <v>-46.6</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="O11" s="6">
-        <v>96</v>
-      </c>
-      <c r="P11" s="12">
-        <v>95</v>
-      </c>
-      <c r="Q11" s="20">
-        <v>80</v>
-      </c>
-      <c r="R11" s="21">
-        <v>30</v>
+        <v>75</v>
+      </c>
+      <c r="P11" s="19">
+        <v>34</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>0</v>
+      </c>
+      <c r="R11" s="19">
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1906,55 +1930,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L12" s="4">
-        <v>-45.9</v>
+        <v>-48.9</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="O12" s="6">
-        <v>99</v>
-      </c>
-      <c r="P12" s="12">
-        <v>95</v>
-      </c>
-      <c r="Q12" s="15">
-        <v>91</v>
+        <v>73</v>
+      </c>
+      <c r="P12" s="15">
+        <v>32</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>0</v>
       </c>
       <c r="R12" s="19">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1962,54 +1986,54 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L13" s="4">
-        <v>-36.6</v>
+        <v>-29.5</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="O13" s="6">
-        <v>71</v>
-      </c>
-      <c r="P13" s="22">
-        <v>46</v>
-      </c>
-      <c r="Q13" s="21">
-        <v>31</v>
-      </c>
-      <c r="R13" s="21">
+        <v>70</v>
+      </c>
+      <c r="P13" s="15">
+        <v>32</v>
+      </c>
+      <c r="Q13" s="7">
+        <v>1</v>
+      </c>
+      <c r="R13" s="15">
         <v>29</v>
       </c>
     </row>
@@ -2018,55 +2042,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L14" s="4">
-        <v>-46.6</v>
+        <v>-42.1</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="O14" s="6">
-        <v>82</v>
-      </c>
-      <c r="P14" s="7">
-        <v>51</v>
-      </c>
-      <c r="Q14" s="21">
-        <v>31</v>
-      </c>
-      <c r="R14" s="17">
-        <v>59</v>
+        <v>76</v>
+      </c>
+      <c r="P14" s="21">
+        <v>50</v>
+      </c>
+      <c r="Q14" s="20">
+        <v>41</v>
+      </c>
+      <c r="R14" s="22">
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2074,55 +2098,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L15" s="4">
-        <v>-48.9</v>
+        <v>-49.2</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="O15" s="6">
-        <v>90</v>
-      </c>
-      <c r="P15" s="22">
-        <v>45</v>
-      </c>
-      <c r="Q15" s="23">
-        <v>19</v>
-      </c>
-      <c r="R15" s="15">
-        <v>89</v>
+        <v>95</v>
+      </c>
+      <c r="P15" s="9">
+        <v>71</v>
+      </c>
+      <c r="Q15" s="18">
+        <v>73</v>
+      </c>
+      <c r="R15" s="23">
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2130,55 +2154,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L16" s="4">
-        <v>-29.5</v>
+        <v>-47.3</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="O16" s="6">
-        <v>85</v>
-      </c>
-      <c r="P16" s="9">
-        <v>84</v>
-      </c>
-      <c r="Q16" s="8">
-        <v>0</v>
-      </c>
-      <c r="R16" s="8">
-        <v>0</v>
+        <v>96</v>
+      </c>
+      <c r="P16" s="24">
+        <v>60</v>
+      </c>
+      <c r="Q16" s="14">
+        <v>65</v>
+      </c>
+      <c r="R16" s="20">
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2186,55 +2210,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L17" s="4">
-        <v>-42.1</v>
+        <v>-35.9</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="O17" s="6">
-        <v>60</v>
-      </c>
-      <c r="P17" s="17">
-        <v>60</v>
-      </c>
-      <c r="Q17" s="8">
+        <v>70</v>
+      </c>
+      <c r="P17" s="9">
+        <v>68</v>
+      </c>
+      <c r="Q17" s="7">
         <v>0</v>
       </c>
-      <c r="R17" s="24">
-        <v>24</v>
+      <c r="R17" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2242,55 +2266,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L18" s="4">
-        <v>-49.2</v>
+        <v>-46.6</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="O18" s="6">
-        <v>89</v>
-      </c>
-      <c r="P18" s="14">
-        <v>57</v>
-      </c>
-      <c r="Q18" s="8">
+        <v>72</v>
+      </c>
+      <c r="P18" s="9">
+        <v>72</v>
+      </c>
+      <c r="Q18" s="7">
         <v>0</v>
       </c>
-      <c r="R18" s="14">
-        <v>56</v>
+      <c r="R18" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2298,55 +2322,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L19" s="4">
-        <v>-47.3</v>
+        <v>-49.9</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="O19" s="6">
-        <v>76</v>
-      </c>
-      <c r="P19" s="22">
-        <v>44</v>
-      </c>
-      <c r="Q19" s="8">
+        <v>75</v>
+      </c>
+      <c r="P19" s="18">
+        <v>75</v>
+      </c>
+      <c r="Q19" s="7">
         <v>0</v>
       </c>
       <c r="R19" s="7">
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2354,55 +2378,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>83</v>
+        <v>194</v>
       </c>
       <c r="L20" s="4">
-        <v>-35.8</v>
+        <v>-28.4</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="O20" s="6">
-        <v>89</v>
-      </c>
-      <c r="P20" s="20">
-        <v>78</v>
-      </c>
-      <c r="Q20" s="11">
-        <v>33</v>
-      </c>
-      <c r="R20" s="25">
-        <v>11</v>
+        <v>100</v>
+      </c>
+      <c r="P20" s="25">
+        <v>100</v>
+      </c>
+      <c r="Q20" s="13">
+        <v>91</v>
+      </c>
+      <c r="R20" s="12">
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2413,52 +2437,52 @@
         <v>29</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L21" s="4">
-        <v>-46.6</v>
+        <v>-41.6</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="O21" s="6">
-        <v>75</v>
-      </c>
-      <c r="P21" s="16">
-        <v>73</v>
-      </c>
-      <c r="Q21" s="24">
-        <v>23</v>
-      </c>
-      <c r="R21" s="8">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="P21" s="11">
+        <v>96</v>
+      </c>
+      <c r="Q21" s="13">
+        <v>89</v>
+      </c>
+      <c r="R21" s="25">
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2466,55 +2490,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L22" s="4">
-        <v>-49.9</v>
+        <v>-49.5</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="O22" s="6">
-        <v>69</v>
-      </c>
-      <c r="P22" s="17">
-        <v>60</v>
-      </c>
-      <c r="Q22" s="23">
-        <v>20</v>
+        <v>100</v>
+      </c>
+      <c r="P22" s="12">
+        <v>87</v>
+      </c>
+      <c r="Q22" s="11">
+        <v>94</v>
       </c>
       <c r="R22" s="25">
-        <v>8</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2522,55 +2546,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>63</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="L23" s="4">
-        <v>-28.3</v>
+        <v>-20.4</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="O23" s="6">
-        <v>100</v>
-      </c>
-      <c r="P23" s="9">
-        <v>84</v>
-      </c>
-      <c r="Q23" s="19">
-        <v>40</v>
-      </c>
-      <c r="R23" s="20">
-        <v>79</v>
+        <v>97</v>
+      </c>
+      <c r="P23" s="21">
+        <v>52</v>
+      </c>
+      <c r="Q23" s="12">
+        <v>83</v>
+      </c>
+      <c r="R23" s="9">
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2578,55 +2602,55 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L24" s="4">
-        <v>-41.6</v>
+        <v>-35</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="O24" s="6">
         <v>97</v>
       </c>
-      <c r="P24" s="20">
-        <v>79</v>
-      </c>
-      <c r="Q24" s="17">
-        <v>61</v>
-      </c>
-      <c r="R24" s="18">
-        <v>67</v>
+      <c r="P24" s="10">
+        <v>53</v>
+      </c>
+      <c r="Q24" s="12">
+        <v>85</v>
+      </c>
+      <c r="R24" s="14">
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2634,114 +2658,170 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="L25" s="4">
+        <v>-46.3</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="O25" s="6">
+        <v>97</v>
+      </c>
+      <c r="P25" s="20">
+        <v>39</v>
+      </c>
+      <c r="Q25" s="12">
+        <v>85</v>
+      </c>
+      <c r="R25" s="10">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
+      <c r="A26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="2">
+        <v>12</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="L25" s="4">
-        <v>-49.5</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="O25" s="6">
-        <v>93</v>
-      </c>
-      <c r="P25" s="18">
-        <v>66</v>
-      </c>
-      <c r="Q25" s="17">
-        <v>61</v>
-      </c>
-      <c r="R25" s="19">
-        <v>42</v>
+      <c r="D26" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="L26" s="4">
+        <v>-50.7</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="O26" s="6">
+        <v>96</v>
+      </c>
+      <c r="P26" s="19">
+        <v>36</v>
+      </c>
+      <c r="Q26" s="12">
+        <v>85</v>
+      </c>
+      <c r="R26" s="10">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A25">
+  <conditionalFormatting sqref="A2:A26">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B25">
+  <conditionalFormatting sqref="B2:B26">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C25">
+  <conditionalFormatting sqref="C2:C26">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D25">
+  <conditionalFormatting sqref="D2:D26">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E25">
+  <conditionalFormatting sqref="E2:E26">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F25">
+  <conditionalFormatting sqref="F2:F26">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G25">
+  <conditionalFormatting sqref="G2:G26">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H25">
+  <conditionalFormatting sqref="H2:H26">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I25">
+  <conditionalFormatting sqref="I2:I26">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J25">
+  <conditionalFormatting sqref="J2:J26">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K25">
+  <conditionalFormatting sqref="K2:K26">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L25">
+  <conditionalFormatting sqref="L2:L26">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2760,12 +2840,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M25">
+  <conditionalFormatting sqref="M2:M26">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N25">
+  <conditionalFormatting sqref="N2:N26">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2782,22 +2862,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O25">
+  <conditionalFormatting sqref="O2:O26">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P25">
+  <conditionalFormatting sqref="P2:P26">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q25">
+  <conditionalFormatting sqref="Q2:Q26">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R25">
+  <conditionalFormatting sqref="R2:R26">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="191">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261016--01</t>
-  </si>
-  <si>
-    <t>20261016--02</t>
-  </si>
-  <si>
-    <t>20261016--03</t>
-  </si>
-  <si>
-    <t>20261016--04</t>
-  </si>
-  <si>
     <t>20261017--01</t>
   </si>
   <si>
@@ -145,87 +133,72 @@
     <t>20261022--04</t>
   </si>
   <si>
-    <t>05:36</t>
-  </si>
-  <si>
-    <t>02:45</t>
+    <t>20261023--01</t>
+  </si>
+  <si>
+    <t>20261023--02</t>
+  </si>
+  <si>
+    <t>20261023--03</t>
+  </si>
+  <si>
+    <t>04:13</t>
+  </si>
+  <si>
+    <t>04:55</t>
+  </si>
+  <si>
+    <t>05:47</t>
+  </si>
+  <si>
+    <t>04:59</t>
+  </si>
+  <si>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>05:43</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>02:24</t>
+  </si>
+  <si>
+    <t>05:32</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>03:29</t>
+  </si>
+  <si>
+    <t>05:11</t>
+  </si>
+  <si>
+    <t>05:46</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>03:27</t>
+  </si>
+  <si>
+    <t>05:39</t>
+  </si>
+  <si>
+    <t>02:25</t>
   </si>
   <si>
     <t>05:23</t>
   </si>
   <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>04:13</t>
-  </si>
-  <si>
-    <t>04:55</t>
-  </si>
-  <si>
-    <t>05:47</t>
-  </si>
-  <si>
-    <t>04:59</t>
-  </si>
-  <si>
-    <t>04:05</t>
-  </si>
-  <si>
-    <t>05:44</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>02:25</t>
-  </si>
-  <si>
-    <t>05:32</t>
-  </si>
-  <si>
-    <t>05:39</t>
-  </si>
-  <si>
-    <t>03:29</t>
-  </si>
-  <si>
-    <t>05:12</t>
-  </si>
-  <si>
-    <t>05:46</t>
-  </si>
-  <si>
-    <t>04:34</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>05:11</t>
-  </si>
-  <si>
-    <t>03:28</t>
-  </si>
-  <si>
-    <t>02:24</t>
-  </si>
-  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>00:12:40</t>
-  </si>
-  <si>
-    <t>01:49:36</t>
-  </si>
-  <si>
-    <t>21:43:05</t>
-  </si>
-  <si>
-    <t>23:19:29</t>
-  </si>
-  <si>
     <t>00:56:16</t>
   </si>
   <si>
@@ -247,58 +220,55 @@
     <t>23:09:29</t>
   </si>
   <si>
-    <t>19:03:55</t>
+    <t>19:03:54</t>
   </si>
   <si>
     <t>20:39:32</t>
   </si>
   <si>
-    <t>22:16:00</t>
-  </si>
-  <si>
-    <t>23:52:51</t>
-  </si>
-  <si>
-    <t>19:46:08</t>
-  </si>
-  <si>
-    <t>21:22:27</t>
-  </si>
-  <si>
-    <t>22:59:10</t>
-  </si>
-  <si>
-    <t>18:52:44</t>
-  </si>
-  <si>
-    <t>20:28:50</t>
-  </si>
-  <si>
-    <t>22:05:26</t>
-  </si>
-  <si>
-    <t>17:59:21</t>
-  </si>
-  <si>
-    <t>19:35:09</t>
-  </si>
-  <si>
-    <t>21:11:40</t>
-  </si>
-  <si>
-    <t>22:48:35</t>
-  </si>
-  <si>
-    <t>00:14:56</t>
-  </si>
-  <si>
-    <t>01:52:41</t>
-  </si>
-  <si>
-    <t>21:45:23</t>
-  </si>
-  <si>
-    <t>23:21:43</t>
+    <t>22:15:59</t>
+  </si>
+  <si>
+    <t>23:52:50</t>
+  </si>
+  <si>
+    <t>19:46:07</t>
+  </si>
+  <si>
+    <t>21:22:26</t>
+  </si>
+  <si>
+    <t>22:59:09</t>
+  </si>
+  <si>
+    <t>18:52:42</t>
+  </si>
+  <si>
+    <t>20:28:48</t>
+  </si>
+  <si>
+    <t>22:05:25</t>
+  </si>
+  <si>
+    <t>17:59:19</t>
+  </si>
+  <si>
+    <t>19:35:07</t>
+  </si>
+  <si>
+    <t>21:11:37</t>
+  </si>
+  <si>
+    <t>22:48:32</t>
+  </si>
+  <si>
+    <t>18:41:23</t>
+  </si>
+  <si>
+    <t>20:17:45</t>
+  </si>
+  <si>
+    <t>21:54:31</t>
   </si>
   <si>
     <t>00:58:53</t>
@@ -325,55 +295,52 @@
     <t>19:07:05</t>
   </si>
   <si>
-    <t>20:41:49</t>
-  </si>
-  <si>
-    <t>22:18:15</t>
+    <t>20:41:48</t>
+  </si>
+  <si>
+    <t>22:18:14</t>
   </si>
   <si>
     <t>23:55:40</t>
   </si>
   <si>
-    <t>19:48:29</t>
-  </si>
-  <si>
-    <t>21:24:40</t>
-  </si>
-  <si>
-    <t>23:01:41</t>
-  </si>
-  <si>
-    <t>18:55:14</t>
-  </si>
-  <si>
-    <t>20:31:03</t>
-  </si>
-  <si>
-    <t>22:07:48</t>
-  </si>
-  <si>
-    <t>18:02:10</t>
-  </si>
-  <si>
-    <t>19:37:24</t>
-  </si>
-  <si>
-    <t>21:13:56</t>
-  </si>
-  <si>
-    <t>22:51:46</t>
-  </si>
-  <si>
-    <t>00:17:44</t>
-  </si>
-  <si>
-    <t>01:54:03</t>
-  </si>
-  <si>
-    <t>21:48:04</t>
-  </si>
-  <si>
-    <t>23:24:35</t>
+    <t>19:48:28</t>
+  </si>
+  <si>
+    <t>21:24:39</t>
+  </si>
+  <si>
+    <t>23:01:39</t>
+  </si>
+  <si>
+    <t>18:55:12</t>
+  </si>
+  <si>
+    <t>20:31:01</t>
+  </si>
+  <si>
+    <t>22:07:46</t>
+  </si>
+  <si>
+    <t>18:02:08</t>
+  </si>
+  <si>
+    <t>19:37:21</t>
+  </si>
+  <si>
+    <t>21:13:53</t>
+  </si>
+  <si>
+    <t>22:51:43</t>
+  </si>
+  <si>
+    <t>18:43:41</t>
+  </si>
+  <si>
+    <t>20:19:59</t>
+  </si>
+  <si>
+    <t>21:57:09</t>
   </si>
   <si>
     <t>01:01:00</t>
@@ -388,13 +355,13 @@
     <t>00:07:48</t>
   </si>
   <si>
-    <t>20:01:37</t>
-  </si>
-  <si>
-    <t>21:38:00</t>
-  </si>
-  <si>
-    <t>23:14:30</t>
+    <t>20:01:36</t>
+  </si>
+  <si>
+    <t>21:37:59</t>
+  </si>
+  <si>
+    <t>23:14:29</t>
   </si>
   <si>
     <t>19:08:17</t>
@@ -403,52 +370,49 @@
     <t>20:44:34</t>
   </si>
   <si>
-    <t>22:21:05</t>
-  </si>
-  <si>
-    <t>23:57:25</t>
-  </si>
-  <si>
-    <t>19:51:05</t>
-  </si>
-  <si>
-    <t>21:27:33</t>
-  </si>
-  <si>
-    <t>23:03:58</t>
-  </si>
-  <si>
-    <t>18:57:31</t>
-  </si>
-  <si>
-    <t>20:33:56</t>
-  </si>
-  <si>
-    <t>22:10:24</t>
-  </si>
-  <si>
-    <t>18:03:54</t>
-  </si>
-  <si>
-    <t>19:40:13</t>
-  </si>
-  <si>
-    <t>21:16:42</t>
-  </si>
-  <si>
-    <t>22:52:58</t>
-  </si>
-  <si>
-    <t>00:20:32</t>
-  </si>
-  <si>
-    <t>01:55:26</t>
-  </si>
-  <si>
-    <t>21:50:46</t>
-  </si>
-  <si>
-    <t>23:27:28</t>
+    <t>22:21:04</t>
+  </si>
+  <si>
+    <t>23:57:24</t>
+  </si>
+  <si>
+    <t>19:51:03</t>
+  </si>
+  <si>
+    <t>21:27:32</t>
+  </si>
+  <si>
+    <t>23:03:57</t>
+  </si>
+  <si>
+    <t>18:57:29</t>
+  </si>
+  <si>
+    <t>20:33:54</t>
+  </si>
+  <si>
+    <t>22:10:22</t>
+  </si>
+  <si>
+    <t>18:03:51</t>
+  </si>
+  <si>
+    <t>19:40:11</t>
+  </si>
+  <si>
+    <t>21:16:39</t>
+  </si>
+  <si>
+    <t>22:52:55</t>
+  </si>
+  <si>
+    <t>18:46:23</t>
+  </si>
+  <si>
+    <t>20:22:51</t>
+  </si>
+  <si>
+    <t>21:59:12</t>
   </si>
   <si>
     <t>01:03:06</t>
@@ -466,16 +430,16 @@
     <t>20:03:39</t>
   </si>
   <si>
-    <t>21:40:52</t>
+    <t>21:40:51</t>
   </si>
   <si>
     <t>23:17:12</t>
   </si>
   <si>
-    <t>19:09:30</t>
-  </si>
-  <si>
-    <t>20:47:21</t>
+    <t>19:09:29</t>
+  </si>
+  <si>
+    <t>20:47:20</t>
   </si>
   <si>
     <t>22:23:54</t>
@@ -484,46 +448,43 @@
     <t>23:59:09</t>
   </si>
   <si>
-    <t>19:53:41</t>
-  </si>
-  <si>
-    <t>21:30:26</t>
-  </si>
-  <si>
-    <t>23:06:15</t>
-  </si>
-  <si>
-    <t>18:59:49</t>
-  </si>
-  <si>
-    <t>20:36:49</t>
-  </si>
-  <si>
-    <t>22:12:59</t>
-  </si>
-  <si>
-    <t>18:05:38</t>
-  </si>
-  <si>
-    <t>19:43:03</t>
-  </si>
-  <si>
-    <t>21:19:28</t>
-  </si>
-  <si>
-    <t>22:54:10</t>
-  </si>
-  <si>
-    <t>00:22:49</t>
-  </si>
-  <si>
-    <t>01:58:31</t>
-  </si>
-  <si>
-    <t>21:53:05</t>
-  </si>
-  <si>
-    <t>23:29:42</t>
+    <t>19:53:39</t>
+  </si>
+  <si>
+    <t>21:30:25</t>
+  </si>
+  <si>
+    <t>23:06:14</t>
+  </si>
+  <si>
+    <t>18:59:47</t>
+  </si>
+  <si>
+    <t>20:36:47</t>
+  </si>
+  <si>
+    <t>22:12:57</t>
+  </si>
+  <si>
+    <t>18:05:35</t>
+  </si>
+  <si>
+    <t>19:43:00</t>
+  </si>
+  <si>
+    <t>21:19:25</t>
+  </si>
+  <si>
+    <t>22:54:08</t>
+  </si>
+  <si>
+    <t>18:49:04</t>
+  </si>
+  <si>
+    <t>20:25:42</t>
+  </si>
+  <si>
+    <t>22:01:14</t>
   </si>
   <si>
     <t>01:05:43</t>
@@ -547,46 +508,55 @@
     <t>23:19:31</t>
   </si>
   <si>
-    <t>19:12:41</t>
-  </si>
-  <si>
-    <t>20:49:38</t>
-  </si>
-  <si>
-    <t>22:26:10</t>
-  </si>
-  <si>
-    <t>00:01:59</t>
-  </si>
-  <si>
-    <t>19:56:02</t>
-  </si>
-  <si>
-    <t>21:32:40</t>
-  </si>
-  <si>
-    <t>23:08:46</t>
-  </si>
-  <si>
-    <t>19:02:19</t>
-  </si>
-  <si>
-    <t>20:39:02</t>
-  </si>
-  <si>
-    <t>22:15:21</t>
-  </si>
-  <si>
-    <t>18:08:28</t>
-  </si>
-  <si>
-    <t>19:45:18</t>
-  </si>
-  <si>
-    <t>21:21:45</t>
-  </si>
-  <si>
-    <t>22:57:21</t>
+    <t>19:12:40</t>
+  </si>
+  <si>
+    <t>20:49:37</t>
+  </si>
+  <si>
+    <t>22:26:09</t>
+  </si>
+  <si>
+    <t>00:01:58</t>
+  </si>
+  <si>
+    <t>19:56:01</t>
+  </si>
+  <si>
+    <t>21:32:39</t>
+  </si>
+  <si>
+    <t>23:08:45</t>
+  </si>
+  <si>
+    <t>19:02:17</t>
+  </si>
+  <si>
+    <t>20:39:00</t>
+  </si>
+  <si>
+    <t>22:15:19</t>
+  </si>
+  <si>
+    <t>18:08:25</t>
+  </si>
+  <si>
+    <t>19:45:15</t>
+  </si>
+  <si>
+    <t>21:21:42</t>
+  </si>
+  <si>
+    <t>22:57:18</t>
+  </si>
+  <si>
+    <t>18:51:23</t>
+  </si>
+  <si>
+    <t>20:27:56</t>
+  </si>
+  <si>
+    <t>22:03:53</t>
   </si>
   <si>
     <t>0°</t>
@@ -598,10 +568,16 @@
     <t>10°</t>
   </si>
   <si>
-    <t>18:53:16</t>
-  </si>
-  <si>
-    <t>18:02:07</t>
+    <t>8°</t>
+  </si>
+  <si>
+    <t>18:53:14</t>
+  </si>
+  <si>
+    <t>18:02:05</t>
+  </si>
+  <si>
+    <t>18:43:19</t>
   </si>
   <si>
     <t>B</t>
@@ -644,7 +620,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -665,7 +641,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -677,55 +725,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -737,25 +737,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -767,13 +755,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -814,7 +796,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -889,6 +871,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1292,7 +1277,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1370,55 +1355,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="L2" s="4">
-        <v>-44.4</v>
+        <v>-40.6</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="O2" s="6">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="P2" s="7">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q2" s="8">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="R2" s="9">
-        <v>69</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1426,55 +1411,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="L3" s="4">
-        <v>-33.7</v>
+        <v>-42.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="O3" s="6">
-        <v>70</v>
-      </c>
-      <c r="P3" s="8">
-        <v>19</v>
-      </c>
-      <c r="Q3" s="7">
-        <v>0</v>
-      </c>
-      <c r="R3" s="10">
-        <v>54</v>
+        <v>99</v>
+      </c>
+      <c r="P3" s="10">
+        <v>97</v>
+      </c>
+      <c r="Q3" s="11">
+        <v>72</v>
+      </c>
+      <c r="R3" s="12">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1482,55 +1467,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="L4" s="4">
-        <v>-46.6</v>
+        <v>-48.7</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="O4" s="6">
-        <v>95</v>
-      </c>
-      <c r="P4" s="7">
-        <v>0</v>
+        <v>99</v>
+      </c>
+      <c r="P4" s="13">
+        <v>98</v>
       </c>
       <c r="Q4" s="11">
-        <v>94</v>
-      </c>
-      <c r="R4" s="12">
-        <v>86</v>
+        <v>71</v>
+      </c>
+      <c r="R4" s="14">
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1538,55 +1523,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L5" s="4">
-        <v>-47.9</v>
+        <v>-45.9</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="O5" s="6">
-        <v>96</v>
-      </c>
-      <c r="P5" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="13">
-        <v>90</v>
-      </c>
-      <c r="R5" s="13">
-        <v>89</v>
+        <v>99</v>
+      </c>
+      <c r="P5" s="15">
+        <v>91</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>39</v>
+      </c>
+      <c r="R5" s="11">
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1597,52 +1582,52 @@
         <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="F6" s="3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="L6" s="4">
-        <v>-40.6</v>
+        <v>-36.6</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="O6" s="6">
-        <v>95</v>
-      </c>
-      <c r="P6" s="7">
+        <v>73</v>
+      </c>
+      <c r="P6" s="14">
+        <v>32</v>
+      </c>
+      <c r="Q6" s="16">
         <v>0</v>
       </c>
-      <c r="Q6" s="13">
-        <v>91</v>
-      </c>
-      <c r="R6" s="14">
-        <v>66</v>
+      <c r="R6" s="17">
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1650,55 +1635,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="L7" s="4">
-        <v>-42.5</v>
+        <v>-46.6</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="O7" s="6">
-        <v>99</v>
-      </c>
-      <c r="P7" s="12">
-        <v>84</v>
-      </c>
-      <c r="Q7" s="11">
-        <v>94</v>
-      </c>
-      <c r="R7" s="15">
-        <v>32</v>
+        <v>69</v>
+      </c>
+      <c r="P7" s="18">
+        <v>24</v>
+      </c>
+      <c r="Q7" s="16">
+        <v>0</v>
+      </c>
+      <c r="R7" s="9">
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1706,55 +1691,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="L8" s="4">
-        <v>-48.7</v>
+        <v>-48.9</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="O8" s="6">
-        <v>99</v>
-      </c>
-      <c r="P8" s="13">
-        <v>88</v>
-      </c>
-      <c r="Q8" s="13">
-        <v>92</v>
-      </c>
-      <c r="R8" s="16">
-        <v>44</v>
+        <v>57</v>
+      </c>
+      <c r="P8" s="12">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="16">
+        <v>0</v>
+      </c>
+      <c r="R8" s="8">
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1762,55 +1747,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F9" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L9" s="4">
+        <v>-29.5</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="O9" s="6">
         <v>98</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L9" s="4">
-        <v>-45.9</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O9" s="6">
-        <v>97</v>
-      </c>
-      <c r="P9" s="17">
-        <v>81</v>
-      </c>
-      <c r="Q9" s="13">
-        <v>90</v>
-      </c>
-      <c r="R9" s="18">
-        <v>73</v>
+      <c r="P9" s="9">
+        <v>38</v>
+      </c>
+      <c r="Q9" s="16">
+        <v>1</v>
+      </c>
+      <c r="R9" s="10">
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1818,55 +1803,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="L10" s="4">
-        <v>-36.6</v>
+        <v>-42.1</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="O10" s="6">
-        <v>81</v>
-      </c>
-      <c r="P10" s="19">
-        <v>35</v>
-      </c>
-      <c r="Q10" s="7">
-        <v>0</v>
-      </c>
-      <c r="R10" s="20">
-        <v>40</v>
+        <v>93</v>
+      </c>
+      <c r="P10" s="9">
+        <v>39</v>
+      </c>
+      <c r="Q10" s="16">
+        <v>2</v>
+      </c>
+      <c r="R10" s="19">
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1874,55 +1859,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="L11" s="4">
-        <v>-46.6</v>
+        <v>-49.2</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="O11" s="6">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="P11" s="19">
-        <v>34</v>
-      </c>
-      <c r="Q11" s="7">
+        <v>81</v>
+      </c>
+      <c r="Q11" s="16">
         <v>0</v>
       </c>
-      <c r="R11" s="19">
-        <v>34</v>
+      <c r="R11" s="20">
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1930,55 +1915,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="L12" s="4">
-        <v>-48.9</v>
+        <v>-47.3</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="O12" s="6">
-        <v>73</v>
-      </c>
-      <c r="P12" s="15">
-        <v>32</v>
-      </c>
-      <c r="Q12" s="7">
+        <v>82</v>
+      </c>
+      <c r="P12" s="19">
+        <v>80</v>
+      </c>
+      <c r="Q12" s="16">
         <v>0</v>
       </c>
-      <c r="R12" s="19">
-        <v>33</v>
+      <c r="R12" s="16">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1986,55 +1971,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="L13" s="4">
-        <v>-29.5</v>
+        <v>-35.9</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="O13" s="6">
-        <v>70</v>
-      </c>
-      <c r="P13" s="15">
-        <v>32</v>
-      </c>
-      <c r="Q13" s="7">
-        <v>1</v>
-      </c>
-      <c r="R13" s="15">
-        <v>29</v>
+        <v>100</v>
+      </c>
+      <c r="P13" s="10">
+        <v>93</v>
+      </c>
+      <c r="Q13" s="21">
+        <v>49</v>
+      </c>
+      <c r="R13" s="22">
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2042,55 +2027,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L14" s="4">
-        <v>-42.1</v>
+        <v>-46.6</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="O14" s="6">
-        <v>76</v>
-      </c>
-      <c r="P14" s="21">
-        <v>50</v>
-      </c>
-      <c r="Q14" s="20">
-        <v>41</v>
-      </c>
-      <c r="R14" s="22">
-        <v>26</v>
+        <v>100</v>
+      </c>
+      <c r="P14" s="15">
+        <v>92</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>56</v>
+      </c>
+      <c r="R14" s="10">
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2098,55 +2083,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L15" s="4">
-        <v>-49.2</v>
+        <v>-49.9</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="O15" s="6">
+        <v>100</v>
+      </c>
+      <c r="P15" s="7">
+        <v>85</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>53</v>
+      </c>
+      <c r="R15" s="10">
         <v>95</v>
-      </c>
-      <c r="P15" s="9">
-        <v>71</v>
-      </c>
-      <c r="Q15" s="18">
-        <v>73</v>
-      </c>
-      <c r="R15" s="23">
-        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2154,55 +2139,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>80</v>
+        <v>185</v>
       </c>
       <c r="L16" s="4">
-        <v>-47.3</v>
+        <v>-28.4</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="O16" s="6">
-        <v>96</v>
-      </c>
-      <c r="P16" s="24">
-        <v>60</v>
-      </c>
-      <c r="Q16" s="14">
-        <v>65</v>
-      </c>
-      <c r="R16" s="20">
-        <v>42</v>
+        <v>100</v>
+      </c>
+      <c r="P16" s="10">
+        <v>93</v>
+      </c>
+      <c r="Q16" s="10">
+        <v>97</v>
+      </c>
+      <c r="R16" s="19">
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2210,55 +2195,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="I17" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>191</v>
-      </c>
       <c r="K17" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="L17" s="4">
-        <v>-35.9</v>
+        <v>-41.6</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="O17" s="6">
-        <v>70</v>
-      </c>
-      <c r="P17" s="9">
-        <v>68</v>
-      </c>
-      <c r="Q17" s="7">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="P17" s="10">
+        <v>96</v>
+      </c>
+      <c r="Q17" s="13">
+        <v>98</v>
       </c>
       <c r="R17" s="7">
-        <v>0</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2266,55 +2251,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="L18" s="4">
-        <v>-46.6</v>
+        <v>-49.5</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="O18" s="6">
-        <v>72</v>
-      </c>
-      <c r="P18" s="9">
-        <v>72</v>
-      </c>
-      <c r="Q18" s="7">
-        <v>0</v>
-      </c>
-      <c r="R18" s="7">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="P18" s="10">
+        <v>95</v>
+      </c>
+      <c r="Q18" s="10">
+        <v>96</v>
+      </c>
+      <c r="R18" s="8">
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2322,55 +2307,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="E19" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="I19" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>191</v>
-      </c>
       <c r="K19" s="1" t="s">
-        <v>83</v>
+        <v>186</v>
       </c>
       <c r="L19" s="4">
-        <v>-49.9</v>
+        <v>-20.4</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O19" s="6">
-        <v>75</v>
-      </c>
-      <c r="P19" s="18">
-        <v>75</v>
-      </c>
-      <c r="Q19" s="7">
-        <v>0</v>
-      </c>
-      <c r="R19" s="7">
-        <v>0</v>
+        <v>190</v>
+      </c>
+      <c r="O19" s="23">
+        <v>42</v>
+      </c>
+      <c r="P19" s="9">
+        <v>42</v>
+      </c>
+      <c r="Q19" s="20">
+        <v>22</v>
+      </c>
+      <c r="R19" s="24">
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2378,55 +2363,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>194</v>
+        <v>79</v>
       </c>
       <c r="L20" s="4">
-        <v>-28.4</v>
+        <v>-35</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O20" s="6">
-        <v>100</v>
-      </c>
-      <c r="P20" s="25">
-        <v>100</v>
-      </c>
-      <c r="Q20" s="13">
-        <v>91</v>
-      </c>
-      <c r="R20" s="12">
-        <v>85</v>
+        <v>189</v>
+      </c>
+      <c r="O20" s="23">
+        <v>20</v>
+      </c>
+      <c r="P20" s="20">
+        <v>20</v>
+      </c>
+      <c r="Q20" s="20">
+        <v>20</v>
+      </c>
+      <c r="R20" s="25">
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2434,55 +2419,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="L21" s="4">
-        <v>-41.6</v>
+        <v>-46.3</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O21" s="6">
-        <v>100</v>
-      </c>
-      <c r="P21" s="11">
-        <v>96</v>
-      </c>
-      <c r="Q21" s="13">
-        <v>89</v>
-      </c>
-      <c r="R21" s="25">
-        <v>98</v>
+        <v>189</v>
+      </c>
+      <c r="O21" s="26">
+        <v>10</v>
+      </c>
+      <c r="P21" s="24">
+        <v>10</v>
+      </c>
+      <c r="Q21" s="24">
+        <v>10</v>
+      </c>
+      <c r="R21" s="12">
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2490,55 +2475,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="L22" s="4">
-        <v>-49.5</v>
+        <v>-50.7</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O22" s="6">
-        <v>100</v>
+        <v>190</v>
+      </c>
+      <c r="O22" s="26">
+        <v>10</v>
       </c>
       <c r="P22" s="12">
-        <v>87</v>
-      </c>
-      <c r="Q22" s="11">
-        <v>94</v>
-      </c>
-      <c r="R22" s="25">
-        <v>98</v>
+        <v>4</v>
+      </c>
+      <c r="Q22" s="24">
+        <v>10</v>
+      </c>
+      <c r="R22" s="12">
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2546,55 +2531,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I23" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="K23" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>195</v>
-      </c>
       <c r="L23" s="4">
-        <v>-20.4</v>
+        <v>-27.3</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="O23" s="6">
-        <v>97</v>
-      </c>
-      <c r="P23" s="21">
-        <v>52</v>
-      </c>
-      <c r="Q23" s="12">
-        <v>83</v>
+        <v>189</v>
+      </c>
+      <c r="O23" s="23">
+        <v>44</v>
+      </c>
+      <c r="P23" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="18">
+        <v>24</v>
       </c>
       <c r="R23" s="9">
-        <v>70</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2602,55 +2587,55 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="I24" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L24" s="4">
+        <v>-40.9</v>
+      </c>
+      <c r="M24" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="L24" s="4">
-        <v>-35</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="N24" s="1" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="O24" s="6">
-        <v>97</v>
-      </c>
-      <c r="P24" s="10">
         <v>53</v>
       </c>
-      <c r="Q24" s="12">
-        <v>85</v>
-      </c>
-      <c r="R24" s="14">
-        <v>65</v>
+      <c r="P24" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="25">
+        <v>17</v>
+      </c>
+      <c r="R24" s="8">
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2658,170 +2643,114 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L25" s="4">
+        <v>-49.7</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="O25" s="6">
         <v>55</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="L25" s="4">
-        <v>-46.3</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O25" s="6">
-        <v>97</v>
-      </c>
-      <c r="P25" s="20">
-        <v>39</v>
-      </c>
-      <c r="Q25" s="12">
-        <v>85</v>
-      </c>
-      <c r="R25" s="10">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18">
-      <c r="A26" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="2">
-        <v>12</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="L26" s="4">
-        <v>-50.7</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="O26" s="6">
-        <v>96</v>
-      </c>
-      <c r="P26" s="19">
-        <v>36</v>
-      </c>
-      <c r="Q26" s="12">
-        <v>85</v>
-      </c>
-      <c r="R26" s="10">
+      <c r="P25" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="24">
+        <v>8</v>
+      </c>
+      <c r="R25" s="8">
         <v>55</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A26">
+  <conditionalFormatting sqref="A2:A25">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B26">
+  <conditionalFormatting sqref="B2:B25">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C26">
+  <conditionalFormatting sqref="C2:C25">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D26">
+  <conditionalFormatting sqref="D2:D25">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E26">
+  <conditionalFormatting sqref="E2:E25">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F26">
+  <conditionalFormatting sqref="F2:F25">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G26">
+  <conditionalFormatting sqref="G2:G25">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H26">
+  <conditionalFormatting sqref="H2:H25">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I26">
+  <conditionalFormatting sqref="I2:I25">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J26">
+  <conditionalFormatting sqref="J2:J25">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K26">
+  <conditionalFormatting sqref="K2:K25">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L26">
+  <conditionalFormatting sqref="L2:L25">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2840,12 +2769,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M26">
+  <conditionalFormatting sqref="M2:M25">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N26">
+  <conditionalFormatting sqref="N2:N25">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2862,22 +2791,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O26">
+  <conditionalFormatting sqref="O2:O25">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P26">
+  <conditionalFormatting sqref="P2:P25">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q26">
+  <conditionalFormatting sqref="Q2:Q25">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R26">
+  <conditionalFormatting sqref="R2:R25">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="186">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261017--01</t>
-  </si>
-  <si>
-    <t>20261017--02</t>
-  </si>
-  <si>
-    <t>20261017--03</t>
-  </si>
-  <si>
     <t>20261018--01</t>
   </si>
   <si>
@@ -142,72 +133,69 @@
     <t>20261023--03</t>
   </si>
   <si>
-    <t>04:13</t>
+    <t>20261024--01</t>
+  </si>
+  <si>
+    <t>20261024--02</t>
+  </si>
+  <si>
+    <t>04:59</t>
+  </si>
+  <si>
+    <t>04:04</t>
+  </si>
+  <si>
+    <t>05:43</t>
+  </si>
+  <si>
+    <t>05:24</t>
+  </si>
+  <si>
+    <t>02:24</t>
+  </si>
+  <si>
+    <t>05:32</t>
+  </si>
+  <si>
+    <t>05:39</t>
+  </si>
+  <si>
+    <t>03:28</t>
+  </si>
+  <si>
+    <t>05:11</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>04:34</t>
+  </si>
+  <si>
+    <t>03:27</t>
+  </si>
+  <si>
+    <t>02:25</t>
+  </si>
+  <si>
+    <t>05:23</t>
+  </si>
+  <si>
+    <t>05:42</t>
+  </si>
+  <si>
+    <t>04:05</t>
   </si>
   <si>
     <t>04:55</t>
   </si>
   <si>
-    <t>05:47</t>
-  </si>
-  <si>
-    <t>04:59</t>
-  </si>
-  <si>
-    <t>04:05</t>
-  </si>
-  <si>
-    <t>05:43</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>02:24</t>
-  </si>
-  <si>
-    <t>05:32</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>03:29</t>
-  </si>
-  <si>
-    <t>05:11</t>
-  </si>
-  <si>
-    <t>05:46</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>03:27</t>
-  </si>
-  <si>
-    <t>05:39</t>
-  </si>
-  <si>
-    <t>02:25</t>
-  </si>
-  <si>
-    <t>05:23</t>
-  </si>
-  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>00:56:16</t>
-  </si>
-  <si>
-    <t>20:50:00</t>
-  </si>
-  <si>
-    <t>22:26:13</t>
-  </si>
-  <si>
     <t>00:02:54</t>
   </si>
   <si>
@@ -217,67 +205,64 @@
     <t>21:32:54</t>
   </si>
   <si>
-    <t>23:09:29</t>
-  </si>
-  <si>
-    <t>19:03:54</t>
-  </si>
-  <si>
-    <t>20:39:32</t>
-  </si>
-  <si>
-    <t>22:15:59</t>
-  </si>
-  <si>
-    <t>23:52:50</t>
-  </si>
-  <si>
-    <t>19:46:07</t>
-  </si>
-  <si>
-    <t>21:22:26</t>
-  </si>
-  <si>
-    <t>22:59:09</t>
-  </si>
-  <si>
-    <t>18:52:42</t>
-  </si>
-  <si>
-    <t>20:28:48</t>
-  </si>
-  <si>
-    <t>22:05:25</t>
-  </si>
-  <si>
-    <t>17:59:19</t>
-  </si>
-  <si>
-    <t>19:35:07</t>
-  </si>
-  <si>
-    <t>21:11:37</t>
-  </si>
-  <si>
-    <t>22:48:32</t>
-  </si>
-  <si>
-    <t>18:41:23</t>
-  </si>
-  <si>
-    <t>20:17:45</t>
-  </si>
-  <si>
-    <t>21:54:31</t>
-  </si>
-  <si>
-    <t>00:58:53</t>
-  </si>
-  <si>
-    <t>20:52:25</t>
-  </si>
-  <si>
-    <t>22:28:27</t>
+    <t>23:09:28</t>
+  </si>
+  <si>
+    <t>19:03:53</t>
+  </si>
+  <si>
+    <t>20:39:31</t>
+  </si>
+  <si>
+    <t>22:15:58</t>
+  </si>
+  <si>
+    <t>23:52:49</t>
+  </si>
+  <si>
+    <t>19:46:05</t>
+  </si>
+  <si>
+    <t>21:22:23</t>
+  </si>
+  <si>
+    <t>22:59:06</t>
+  </si>
+  <si>
+    <t>18:52:39</t>
+  </si>
+  <si>
+    <t>20:28:44</t>
+  </si>
+  <si>
+    <t>22:05:21</t>
+  </si>
+  <si>
+    <t>17:59:14</t>
+  </si>
+  <si>
+    <t>19:35:01</t>
+  </si>
+  <si>
+    <t>21:11:31</t>
+  </si>
+  <si>
+    <t>22:48:26</t>
+  </si>
+  <si>
+    <t>18:41:16</t>
+  </si>
+  <si>
+    <t>20:17:38</t>
+  </si>
+  <si>
+    <t>21:54:23</t>
+  </si>
+  <si>
+    <t>19:23:39</t>
+  </si>
+  <si>
+    <t>21:00:18</t>
   </si>
   <si>
     <t>00:05:19</t>
@@ -292,64 +277,61 @@
     <t>23:11:47</t>
   </si>
   <si>
-    <t>19:07:05</t>
-  </si>
-  <si>
-    <t>20:41:48</t>
-  </si>
-  <si>
-    <t>22:18:14</t>
-  </si>
-  <si>
-    <t>23:55:40</t>
-  </si>
-  <si>
-    <t>19:48:28</t>
-  </si>
-  <si>
-    <t>21:24:39</t>
-  </si>
-  <si>
-    <t>23:01:39</t>
-  </si>
-  <si>
-    <t>18:55:12</t>
-  </si>
-  <si>
-    <t>20:31:01</t>
-  </si>
-  <si>
-    <t>22:07:46</t>
-  </si>
-  <si>
-    <t>18:02:08</t>
-  </si>
-  <si>
-    <t>19:37:21</t>
-  </si>
-  <si>
-    <t>21:13:53</t>
-  </si>
-  <si>
-    <t>22:51:43</t>
-  </si>
-  <si>
-    <t>18:43:41</t>
-  </si>
-  <si>
-    <t>20:19:59</t>
-  </si>
-  <si>
-    <t>21:57:09</t>
-  </si>
-  <si>
-    <t>01:01:00</t>
-  </si>
-  <si>
-    <t>20:54:52</t>
-  </si>
-  <si>
-    <t>22:31:20</t>
+    <t>19:07:04</t>
+  </si>
+  <si>
+    <t>20:41:47</t>
+  </si>
+  <si>
+    <t>22:18:13</t>
+  </si>
+  <si>
+    <t>23:55:39</t>
+  </si>
+  <si>
+    <t>19:48:26</t>
+  </si>
+  <si>
+    <t>21:24:37</t>
+  </si>
+  <si>
+    <t>23:01:37</t>
+  </si>
+  <si>
+    <t>18:55:09</t>
+  </si>
+  <si>
+    <t>20:30:58</t>
+  </si>
+  <si>
+    <t>22:07:42</t>
+  </si>
+  <si>
+    <t>18:02:03</t>
+  </si>
+  <si>
+    <t>19:37:16</t>
+  </si>
+  <si>
+    <t>21:13:48</t>
+  </si>
+  <si>
+    <t>22:51:37</t>
+  </si>
+  <si>
+    <t>18:43:34</t>
+  </si>
+  <si>
+    <t>20:19:52</t>
+  </si>
+  <si>
+    <t>21:57:02</t>
+  </si>
+  <si>
+    <t>19:25:53</t>
+  </si>
+  <si>
+    <t>21:02:43</t>
   </si>
   <si>
     <t>00:07:48</t>
@@ -364,199 +346,199 @@
     <t>23:14:29</t>
   </si>
   <si>
-    <t>19:08:17</t>
-  </si>
-  <si>
-    <t>20:44:34</t>
-  </si>
-  <si>
-    <t>22:21:04</t>
-  </si>
-  <si>
-    <t>23:57:24</t>
-  </si>
-  <si>
-    <t>19:51:03</t>
-  </si>
-  <si>
-    <t>21:27:32</t>
-  </si>
-  <si>
-    <t>23:03:57</t>
-  </si>
-  <si>
-    <t>18:57:29</t>
-  </si>
-  <si>
-    <t>20:33:54</t>
-  </si>
-  <si>
-    <t>22:10:22</t>
-  </si>
-  <si>
-    <t>18:03:51</t>
-  </si>
-  <si>
-    <t>19:40:11</t>
-  </si>
-  <si>
-    <t>21:16:39</t>
-  </si>
-  <si>
-    <t>22:52:55</t>
-  </si>
-  <si>
-    <t>18:46:23</t>
-  </si>
-  <si>
-    <t>20:22:51</t>
-  </si>
-  <si>
-    <t>21:59:12</t>
-  </si>
-  <si>
-    <t>01:03:06</t>
-  </si>
-  <si>
-    <t>20:57:20</t>
-  </si>
-  <si>
-    <t>22:34:14</t>
+    <t>19:08:16</t>
+  </si>
+  <si>
+    <t>20:44:33</t>
+  </si>
+  <si>
+    <t>22:21:03</t>
+  </si>
+  <si>
+    <t>23:57:23</t>
+  </si>
+  <si>
+    <t>19:51:01</t>
+  </si>
+  <si>
+    <t>21:27:30</t>
+  </si>
+  <si>
+    <t>23:03:54</t>
+  </si>
+  <si>
+    <t>18:57:26</t>
+  </si>
+  <si>
+    <t>20:33:50</t>
+  </si>
+  <si>
+    <t>22:10:18</t>
+  </si>
+  <si>
+    <t>18:03:46</t>
+  </si>
+  <si>
+    <t>19:40:05</t>
+  </si>
+  <si>
+    <t>21:16:34</t>
+  </si>
+  <si>
+    <t>22:52:50</t>
+  </si>
+  <si>
+    <t>18:46:15</t>
+  </si>
+  <si>
+    <t>20:22:43</t>
+  </si>
+  <si>
+    <t>21:59:04</t>
+  </si>
+  <si>
+    <t>19:28:45</t>
+  </si>
+  <si>
+    <t>21:05:10</t>
   </si>
   <si>
     <t>00:10:18</t>
   </si>
   <si>
-    <t>20:03:39</t>
+    <t>20:03:38</t>
   </si>
   <si>
     <t>21:40:51</t>
   </si>
   <si>
-    <t>23:17:12</t>
-  </si>
-  <si>
-    <t>19:09:29</t>
-  </si>
-  <si>
-    <t>20:47:20</t>
-  </si>
-  <si>
-    <t>22:23:54</t>
-  </si>
-  <si>
-    <t>23:59:09</t>
-  </si>
-  <si>
-    <t>19:53:39</t>
-  </si>
-  <si>
-    <t>21:30:25</t>
-  </si>
-  <si>
-    <t>23:06:14</t>
-  </si>
-  <si>
-    <t>18:59:47</t>
-  </si>
-  <si>
-    <t>20:36:47</t>
-  </si>
-  <si>
-    <t>22:12:57</t>
-  </si>
-  <si>
-    <t>18:05:35</t>
-  </si>
-  <si>
-    <t>19:43:00</t>
-  </si>
-  <si>
-    <t>21:19:25</t>
-  </si>
-  <si>
-    <t>22:54:08</t>
-  </si>
-  <si>
-    <t>18:49:04</t>
-  </si>
-  <si>
-    <t>20:25:42</t>
-  </si>
-  <si>
-    <t>22:01:14</t>
-  </si>
-  <si>
-    <t>01:05:43</t>
-  </si>
-  <si>
-    <t>20:59:46</t>
-  </si>
-  <si>
-    <t>22:36:28</t>
-  </si>
-  <si>
-    <t>00:12:43</t>
-  </si>
-  <si>
-    <t>20:06:18</t>
-  </si>
-  <si>
-    <t>21:43:06</t>
-  </si>
-  <si>
-    <t>23:19:31</t>
-  </si>
-  <si>
-    <t>19:12:40</t>
-  </si>
-  <si>
-    <t>20:49:37</t>
-  </si>
-  <si>
-    <t>22:26:09</t>
-  </si>
-  <si>
-    <t>00:01:58</t>
-  </si>
-  <si>
-    <t>19:56:01</t>
-  </si>
-  <si>
-    <t>21:32:39</t>
-  </si>
-  <si>
-    <t>23:08:45</t>
-  </si>
-  <si>
-    <t>19:02:17</t>
-  </si>
-  <si>
-    <t>20:39:00</t>
-  </si>
-  <si>
-    <t>22:15:19</t>
-  </si>
-  <si>
-    <t>18:08:25</t>
-  </si>
-  <si>
-    <t>19:45:15</t>
-  </si>
-  <si>
-    <t>21:21:42</t>
-  </si>
-  <si>
-    <t>22:57:18</t>
-  </si>
-  <si>
-    <t>18:51:23</t>
-  </si>
-  <si>
-    <t>20:27:56</t>
-  </si>
-  <si>
-    <t>22:03:53</t>
+    <t>23:17:11</t>
+  </si>
+  <si>
+    <t>19:09:28</t>
+  </si>
+  <si>
+    <t>20:47:19</t>
+  </si>
+  <si>
+    <t>22:23:52</t>
+  </si>
+  <si>
+    <t>23:59:07</t>
+  </si>
+  <si>
+    <t>19:53:37</t>
+  </si>
+  <si>
+    <t>21:30:22</t>
+  </si>
+  <si>
+    <t>23:06:12</t>
+  </si>
+  <si>
+    <t>18:59:43</t>
+  </si>
+  <si>
+    <t>20:36:43</t>
+  </si>
+  <si>
+    <t>22:12:53</t>
+  </si>
+  <si>
+    <t>18:05:30</t>
+  </si>
+  <si>
+    <t>19:42:55</t>
+  </si>
+  <si>
+    <t>21:19:20</t>
+  </si>
+  <si>
+    <t>22:54:02</t>
+  </si>
+  <si>
+    <t>18:48:57</t>
+  </si>
+  <si>
+    <t>20:25:34</t>
+  </si>
+  <si>
+    <t>22:01:07</t>
+  </si>
+  <si>
+    <t>19:31:38</t>
+  </si>
+  <si>
+    <t>21:07:38</t>
+  </si>
+  <si>
+    <t>00:12:42</t>
+  </si>
+  <si>
+    <t>20:06:17</t>
+  </si>
+  <si>
+    <t>21:43:05</t>
+  </si>
+  <si>
+    <t>23:19:30</t>
+  </si>
+  <si>
+    <t>19:12:39</t>
+  </si>
+  <si>
+    <t>20:49:36</t>
+  </si>
+  <si>
+    <t>22:26:08</t>
+  </si>
+  <si>
+    <t>00:01:57</t>
+  </si>
+  <si>
+    <t>19:55:59</t>
+  </si>
+  <si>
+    <t>21:32:36</t>
+  </si>
+  <si>
+    <t>23:08:42</t>
+  </si>
+  <si>
+    <t>19:02:14</t>
+  </si>
+  <si>
+    <t>20:38:57</t>
+  </si>
+  <si>
+    <t>22:15:15</t>
+  </si>
+  <si>
+    <t>18:08:20</t>
+  </si>
+  <si>
+    <t>19:45:10</t>
+  </si>
+  <si>
+    <t>21:21:36</t>
+  </si>
+  <si>
+    <t>22:57:13</t>
+  </si>
+  <si>
+    <t>18:51:15</t>
+  </si>
+  <si>
+    <t>20:27:48</t>
+  </si>
+  <si>
+    <t>22:03:45</t>
+  </si>
+  <si>
+    <t>19:33:52</t>
+  </si>
+  <si>
+    <t>21:10:03</t>
   </si>
   <si>
     <t>0°</t>
@@ -571,13 +553,16 @@
     <t>8°</t>
   </si>
   <si>
-    <t>18:53:14</t>
-  </si>
-  <si>
-    <t>18:02:05</t>
-  </si>
-  <si>
-    <t>18:43:19</t>
+    <t>18:53:11</t>
+  </si>
+  <si>
+    <t>18:02:00</t>
+  </si>
+  <si>
+    <t>18:43:12</t>
+  </si>
+  <si>
+    <t>19:24:13</t>
   </si>
   <si>
     <t>B</t>
@@ -620,7 +605,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -641,7 +626,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -653,19 +668,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -677,31 +680,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFEEF3F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -713,49 +698,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -796,7 +757,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -862,18 +823,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1277,7 +1226,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1355,55 +1304,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="F2" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L2" s="4">
-        <v>-40.6</v>
+        <v>-45.9</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="O2" s="6">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="P2" s="7">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="Q2" s="8">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="R2" s="9">
-        <v>38</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1411,55 +1360,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L3" s="4">
-        <v>-42.5</v>
+        <v>-36.6</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="O3" s="6">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="P3" s="10">
-        <v>97</v>
+        <v>17</v>
       </c>
       <c r="Q3" s="11">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="R3" s="12">
-        <v>3</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1467,55 +1416,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L4" s="4">
-        <v>-48.7</v>
+        <v>-46.6</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="O4" s="6">
-        <v>99</v>
-      </c>
-      <c r="P4" s="13">
-        <v>98</v>
+        <v>77</v>
+      </c>
+      <c r="P4" s="8">
+        <v>34</v>
       </c>
       <c r="Q4" s="11">
-        <v>71</v>
-      </c>
-      <c r="R4" s="14">
-        <v>28</v>
+        <v>0</v>
+      </c>
+      <c r="R4" s="13">
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1523,55 +1472,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L5" s="4">
-        <v>-45.9</v>
+        <v>-48.9</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="O5" s="6">
-        <v>99</v>
+        <v>184</v>
+      </c>
+      <c r="O5" s="14">
+        <v>33</v>
       </c>
       <c r="P5" s="15">
-        <v>91</v>
-      </c>
-      <c r="Q5" s="9">
-        <v>39</v>
-      </c>
-      <c r="R5" s="11">
-        <v>72</v>
+        <v>7</v>
+      </c>
+      <c r="Q5" s="11">
+        <v>0</v>
+      </c>
+      <c r="R5" s="12">
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1579,55 +1528,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L6" s="4">
-        <v>-36.6</v>
+        <v>-29.5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="O6" s="6">
-        <v>73</v>
-      </c>
-      <c r="P6" s="14">
-        <v>32</v>
-      </c>
-      <c r="Q6" s="16">
+        <v>93</v>
+      </c>
+      <c r="P6" s="9">
+        <v>93</v>
+      </c>
+      <c r="Q6" s="11">
         <v>0</v>
       </c>
-      <c r="R6" s="17">
-        <v>34</v>
+      <c r="R6" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1635,55 +1584,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L7" s="4">
-        <v>-46.6</v>
+        <v>-42.1</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="O7" s="6">
-        <v>69</v>
-      </c>
-      <c r="P7" s="18">
-        <v>24</v>
-      </c>
-      <c r="Q7" s="16">
+        <v>93</v>
+      </c>
+      <c r="P7" s="9">
+        <v>93</v>
+      </c>
+      <c r="Q7" s="11">
         <v>0</v>
       </c>
-      <c r="R7" s="9">
-        <v>41</v>
+      <c r="R7" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1691,55 +1640,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L8" s="4">
-        <v>-48.9</v>
+        <v>-49.2</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="O8" s="6">
-        <v>57</v>
-      </c>
-      <c r="P8" s="12">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="16">
+        <v>93</v>
+      </c>
+      <c r="P8" s="9">
+        <v>93</v>
+      </c>
+      <c r="Q8" s="11">
         <v>0</v>
       </c>
-      <c r="R8" s="8">
-        <v>54</v>
+      <c r="R8" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1747,55 +1696,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F9" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L9" s="4">
+        <v>-47.3</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="O9" s="6">
         <v>92</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="L9" s="4">
-        <v>-29.5</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="O9" s="6">
-        <v>98</v>
-      </c>
-      <c r="P9" s="9">
-        <v>38</v>
-      </c>
-      <c r="Q9" s="16">
-        <v>1</v>
-      </c>
-      <c r="R9" s="10">
-        <v>94</v>
+      <c r="P9" s="16">
+        <v>92</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>0</v>
+      </c>
+      <c r="R9" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1803,55 +1752,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L10" s="4">
-        <v>-42.1</v>
+        <v>-35.9</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="O10" s="6">
-        <v>93</v>
-      </c>
-      <c r="P10" s="9">
-        <v>39</v>
-      </c>
-      <c r="Q10" s="16">
-        <v>2</v>
-      </c>
-      <c r="R10" s="19">
-        <v>79</v>
+        <v>64</v>
+      </c>
+      <c r="P10" s="12">
+        <v>30</v>
+      </c>
+      <c r="Q10" s="17">
+        <v>11</v>
+      </c>
+      <c r="R10" s="12">
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1859,55 +1808,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L11" s="4">
-        <v>-49.2</v>
+        <v>-46.6</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="O11" s="6">
-        <v>83</v>
-      </c>
-      <c r="P11" s="19">
-        <v>81</v>
-      </c>
-      <c r="Q11" s="16">
-        <v>0</v>
-      </c>
-      <c r="R11" s="20">
-        <v>19</v>
+        <v>184</v>
+      </c>
+      <c r="O11" s="14">
+        <v>41</v>
+      </c>
+      <c r="P11" s="10">
+        <v>16</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>2</v>
+      </c>
+      <c r="R11" s="12">
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1915,55 +1864,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L12" s="4">
-        <v>-47.3</v>
+        <v>-49.9</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="O12" s="6">
-        <v>82</v>
-      </c>
-      <c r="P12" s="19">
-        <v>80</v>
-      </c>
-      <c r="Q12" s="16">
-        <v>0</v>
-      </c>
-      <c r="R12" s="16">
-        <v>0</v>
+        <v>184</v>
+      </c>
+      <c r="O12" s="14">
+        <v>48</v>
+      </c>
+      <c r="P12" s="10">
+        <v>15</v>
+      </c>
+      <c r="Q12" s="15">
+        <v>6</v>
+      </c>
+      <c r="R12" s="18">
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1971,55 +1920,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
       <c r="L13" s="4">
-        <v>-35.9</v>
+        <v>-28.4</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="O13" s="6">
         <v>100</v>
       </c>
-      <c r="P13" s="10">
-        <v>93</v>
-      </c>
-      <c r="Q13" s="21">
-        <v>49</v>
-      </c>
-      <c r="R13" s="22">
-        <v>73</v>
+      <c r="P13" s="9">
+        <v>94</v>
+      </c>
+      <c r="Q13" s="7">
+        <v>100</v>
+      </c>
+      <c r="R13" s="7">
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2030,52 +1979,52 @@
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L14" s="4">
-        <v>-46.6</v>
+        <v>-41.6</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="O14" s="6">
         <v>100</v>
       </c>
-      <c r="P14" s="15">
+      <c r="P14" s="16">
         <v>92</v>
       </c>
-      <c r="Q14" s="8">
-        <v>56</v>
-      </c>
-      <c r="R14" s="10">
-        <v>94</v>
+      <c r="Q14" s="7">
+        <v>100</v>
+      </c>
+      <c r="R14" s="7">
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2083,55 +2032,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L15" s="4">
-        <v>-49.9</v>
+        <v>-49.5</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="O15" s="6">
         <v>100</v>
       </c>
-      <c r="P15" s="7">
-        <v>85</v>
-      </c>
-      <c r="Q15" s="8">
-        <v>53</v>
-      </c>
-      <c r="R15" s="10">
-        <v>95</v>
+      <c r="P15" s="9">
+        <v>93</v>
+      </c>
+      <c r="Q15" s="7">
+        <v>100</v>
+      </c>
+      <c r="R15" s="7">
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2139,55 +2088,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="K16" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="L16" s="4">
+        <v>-20.4</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="N16" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="L16" s="4">
-        <v>-28.4</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="O16" s="6">
-        <v>100</v>
-      </c>
-      <c r="P16" s="10">
-        <v>93</v>
-      </c>
-      <c r="Q16" s="10">
-        <v>97</v>
-      </c>
-      <c r="R16" s="19">
-        <v>78</v>
+      <c r="O16" s="14">
+        <v>32</v>
+      </c>
+      <c r="P16" s="11">
+        <v>2</v>
+      </c>
+      <c r="Q16" s="12">
+        <v>32</v>
+      </c>
+      <c r="R16" s="12">
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2195,55 +2144,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L17" s="4">
-        <v>-41.6</v>
+        <v>-35</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="O17" s="6">
-        <v>100</v>
-      </c>
-      <c r="P17" s="10">
-        <v>96</v>
-      </c>
-      <c r="Q17" s="13">
-        <v>98</v>
-      </c>
-      <c r="R17" s="7">
-        <v>85</v>
+        <v>184</v>
+      </c>
+      <c r="O17" s="14">
+        <v>30</v>
+      </c>
+      <c r="P17" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="17">
+        <v>8</v>
+      </c>
+      <c r="R17" s="12">
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2251,55 +2200,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L18" s="4">
-        <v>-49.5</v>
+        <v>-46.3</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="O18" s="6">
-        <v>100</v>
-      </c>
-      <c r="P18" s="10">
-        <v>95</v>
-      </c>
-      <c r="Q18" s="10">
-        <v>96</v>
-      </c>
-      <c r="R18" s="8">
-        <v>57</v>
+        <v>184</v>
+      </c>
+      <c r="O18" s="14">
+        <v>30</v>
+      </c>
+      <c r="P18" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="15">
+        <v>5</v>
+      </c>
+      <c r="R18" s="19">
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2307,55 +2256,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J19" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="L19" s="4">
+        <v>-50.7</v>
+      </c>
+      <c r="M19" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="L19" s="4">
-        <v>-20.4</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>188</v>
-      </c>
       <c r="N19" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="O19" s="23">
-        <v>42</v>
-      </c>
-      <c r="P19" s="9">
-        <v>42</v>
-      </c>
-      <c r="Q19" s="20">
-        <v>22</v>
-      </c>
-      <c r="R19" s="24">
-        <v>10</v>
+        <v>185</v>
+      </c>
+      <c r="O19" s="14">
+        <v>28</v>
+      </c>
+      <c r="P19" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="11">
+        <v>0</v>
+      </c>
+      <c r="R19" s="18">
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2363,55 +2312,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="J20" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="K20" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="L20" s="4">
-        <v>-35</v>
+        <v>-27.3</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="O20" s="23">
-        <v>20</v>
+        <v>184</v>
+      </c>
+      <c r="O20" s="6">
+        <v>95</v>
       </c>
       <c r="P20" s="20">
-        <v>20</v>
-      </c>
-      <c r="Q20" s="20">
-        <v>20</v>
-      </c>
-      <c r="R20" s="25">
-        <v>15</v>
+        <v>47</v>
+      </c>
+      <c r="Q20" s="21">
+        <v>82</v>
+      </c>
+      <c r="R20" s="17">
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2419,55 +2368,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L21" s="4">
-        <v>-46.3</v>
+        <v>-40.9</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="O21" s="26">
-        <v>10</v>
-      </c>
-      <c r="P21" s="24">
-        <v>10</v>
-      </c>
-      <c r="Q21" s="24">
-        <v>10</v>
-      </c>
-      <c r="R21" s="12">
-        <v>5</v>
+        <v>184</v>
+      </c>
+      <c r="O21" s="6">
+        <v>94</v>
+      </c>
+      <c r="P21" s="8">
+        <v>36</v>
+      </c>
+      <c r="Q21" s="22">
+        <v>69</v>
+      </c>
+      <c r="R21" s="15">
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2475,55 +2424,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L22" s="4">
-        <v>-50.7</v>
+        <v>-49.7</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="O22" s="26">
-        <v>10</v>
-      </c>
-      <c r="P22" s="12">
-        <v>4</v>
-      </c>
-      <c r="Q22" s="24">
-        <v>10</v>
-      </c>
-      <c r="R22" s="12">
-        <v>5</v>
+        <v>184</v>
+      </c>
+      <c r="O22" s="6">
+        <v>94</v>
+      </c>
+      <c r="P22" s="19">
+        <v>21</v>
+      </c>
+      <c r="Q22" s="13">
+        <v>55</v>
+      </c>
+      <c r="R22" s="15">
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2531,55 +2480,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="E23" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="J23" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="L23" s="4">
+        <v>-33.9</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="N23" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="K23" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="L23" s="4">
-        <v>-27.3</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="O23" s="23">
-        <v>44</v>
-      </c>
-      <c r="P23" s="16">
+      <c r="O23" s="14">
+        <v>36</v>
+      </c>
+      <c r="P23" s="8">
+        <v>35</v>
+      </c>
+      <c r="Q23" s="17">
+        <v>12</v>
+      </c>
+      <c r="R23" s="11">
         <v>0</v>
-      </c>
-      <c r="Q23" s="18">
-        <v>24</v>
-      </c>
-      <c r="R23" s="9">
-        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2587,170 +2536,114 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L24" s="4">
-        <v>-40.9</v>
+        <v>-45.9</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="O24" s="6">
-        <v>53</v>
-      </c>
-      <c r="P24" s="16">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="25">
+        <v>184</v>
+      </c>
+      <c r="O24" s="14">
+        <v>19</v>
+      </c>
+      <c r="P24" s="10">
         <v>17</v>
       </c>
-      <c r="R24" s="8">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18">
-      <c r="A25" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="2">
-        <v>16</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="L25" s="4">
-        <v>-49.7</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="O25" s="6">
-        <v>55</v>
-      </c>
-      <c r="P25" s="16">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="24">
+      <c r="Q24" s="17">
         <v>8</v>
       </c>
-      <c r="R25" s="8">
-        <v>55</v>
+      <c r="R24" s="19">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A25">
+  <conditionalFormatting sqref="A2:A24">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B25">
+  <conditionalFormatting sqref="B2:B24">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C25">
+  <conditionalFormatting sqref="C2:C24">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D25">
+  <conditionalFormatting sqref="D2:D24">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E25">
+  <conditionalFormatting sqref="E2:E24">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F25">
+  <conditionalFormatting sqref="F2:F24">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G25">
+  <conditionalFormatting sqref="G2:G24">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H25">
+  <conditionalFormatting sqref="H2:H24">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I25">
+  <conditionalFormatting sqref="I2:I24">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J25">
+  <conditionalFormatting sqref="J2:J24">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K25">
+  <conditionalFormatting sqref="K2:K24">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L25">
+  <conditionalFormatting sqref="L2:L24">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2769,12 +2662,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M25">
+  <conditionalFormatting sqref="M2:M24">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N25">
+  <conditionalFormatting sqref="N2:N24">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2791,22 +2684,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O25">
+  <conditionalFormatting sqref="O2:O24">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P25">
+  <conditionalFormatting sqref="P2:P24">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q25">
+  <conditionalFormatting sqref="Q2:Q24">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R25">
+  <conditionalFormatting sqref="R2:R24">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="195">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261018--01</t>
-  </si>
-  <si>
-    <t>20261018--02</t>
-  </si>
-  <si>
-    <t>20261018--03</t>
-  </si>
-  <si>
-    <t>20261018--04</t>
-  </si>
-  <si>
     <t>20261019--01</t>
   </si>
   <si>
@@ -139,76 +127,79 @@
     <t>20261024--02</t>
   </si>
   <si>
-    <t>04:59</t>
-  </si>
-  <si>
-    <t>04:04</t>
+    <t>20261024--03</t>
+  </si>
+  <si>
+    <t>20261025--01</t>
+  </si>
+  <si>
+    <t>20261025--02</t>
+  </si>
+  <si>
+    <t>20261025--03</t>
+  </si>
+  <si>
+    <t>02:24</t>
+  </si>
+  <si>
+    <t>05:32</t>
+  </si>
+  <si>
+    <t>05:39</t>
+  </si>
+  <si>
+    <t>03:28</t>
+  </si>
+  <si>
+    <t>05:11</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>04:34</t>
+  </si>
+  <si>
+    <t>03:27</t>
+  </si>
+  <si>
+    <t>05:38</t>
+  </si>
+  <si>
+    <t>05:22</t>
+  </si>
+  <si>
+    <t>05:42</t>
+  </si>
+  <si>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>04:55</t>
   </si>
   <si>
     <t>05:43</t>
   </si>
   <si>
-    <t>05:24</t>
-  </si>
-  <si>
-    <t>02:24</t>
-  </si>
-  <si>
-    <t>05:32</t>
-  </si>
-  <si>
-    <t>05:39</t>
-  </si>
-  <si>
-    <t>03:28</t>
-  </si>
-  <si>
-    <t>05:11</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>04:34</t>
-  </si>
-  <si>
-    <t>03:27</t>
-  </si>
-  <si>
-    <t>02:25</t>
-  </si>
-  <si>
     <t>05:23</t>
   </si>
   <si>
-    <t>05:42</t>
-  </si>
-  <si>
-    <t>04:05</t>
-  </si>
-  <si>
-    <t>04:55</t>
-  </si>
-  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>00:02:54</t>
-  </si>
-  <si>
-    <t>19:56:56</t>
-  </si>
-  <si>
-    <t>21:32:54</t>
-  </si>
-  <si>
-    <t>23:09:28</t>
-  </si>
-  <si>
-    <t>19:03:53</t>
+    <t>01:46</t>
+  </si>
+  <si>
+    <t>03:38</t>
+  </si>
+  <si>
+    <t>00:39</t>
+  </si>
+  <si>
+    <t>19:03:54</t>
   </si>
   <si>
     <t>20:39:31</t>
@@ -223,7 +214,7 @@
     <t>19:46:05</t>
   </si>
   <si>
-    <t>21:22:23</t>
+    <t>21:22:24</t>
   </si>
   <si>
     <t>22:59:06</t>
@@ -238,7 +229,7 @@
     <t>22:05:21</t>
   </si>
   <si>
-    <t>17:59:14</t>
+    <t>17:59:13</t>
   </si>
   <si>
     <t>19:35:01</t>
@@ -250,31 +241,31 @@
     <t>22:48:26</t>
   </si>
   <si>
-    <t>18:41:16</t>
-  </si>
-  <si>
-    <t>20:17:38</t>
-  </si>
-  <si>
-    <t>21:54:23</t>
-  </si>
-  <si>
-    <t>19:23:39</t>
-  </si>
-  <si>
-    <t>21:00:18</t>
-  </si>
-  <si>
-    <t>00:05:19</t>
-  </si>
-  <si>
-    <t>19:59:34</t>
-  </si>
-  <si>
-    <t>21:35:08</t>
-  </si>
-  <si>
-    <t>23:11:47</t>
+    <t>18:41:14</t>
+  </si>
+  <si>
+    <t>20:17:36</t>
+  </si>
+  <si>
+    <t>21:54:22</t>
+  </si>
+  <si>
+    <t>17:47:26</t>
+  </si>
+  <si>
+    <t>19:23:37</t>
+  </si>
+  <si>
+    <t>21:00:16</t>
+  </si>
+  <si>
+    <t>16:53:38</t>
+  </si>
+  <si>
+    <t>18:29:34</t>
+  </si>
+  <si>
+    <t>20:06:06</t>
   </si>
   <si>
     <t>19:07:04</t>
@@ -307,43 +298,43 @@
     <t>22:07:42</t>
   </si>
   <si>
-    <t>18:02:03</t>
+    <t>18:02:02</t>
   </si>
   <si>
     <t>19:37:16</t>
   </si>
   <si>
-    <t>21:13:48</t>
+    <t>21:13:47</t>
   </si>
   <si>
     <t>22:51:37</t>
   </si>
   <si>
-    <t>18:43:34</t>
-  </si>
-  <si>
-    <t>20:19:52</t>
-  </si>
-  <si>
-    <t>21:57:02</t>
-  </si>
-  <si>
-    <t>19:25:53</t>
-  </si>
-  <si>
-    <t>21:02:43</t>
-  </si>
-  <si>
-    <t>00:07:48</t>
-  </si>
-  <si>
-    <t>20:01:36</t>
-  </si>
-  <si>
-    <t>21:37:59</t>
-  </si>
-  <si>
-    <t>23:14:29</t>
+    <t>18:43:33</t>
+  </si>
+  <si>
+    <t>20:19:51</t>
+  </si>
+  <si>
+    <t>21:57:00</t>
+  </si>
+  <si>
+    <t>17:49:51</t>
+  </si>
+  <si>
+    <t>19:25:51</t>
+  </si>
+  <si>
+    <t>21:02:41</t>
+  </si>
+  <si>
+    <t>16:56:17</t>
+  </si>
+  <si>
+    <t>18:31:48</t>
+  </si>
+  <si>
+    <t>20:08:25</t>
   </si>
   <si>
     <t>19:08:16</t>
@@ -367,7 +358,7 @@
     <t>23:03:54</t>
   </si>
   <si>
-    <t>18:57:26</t>
+    <t>18:57:25</t>
   </si>
   <si>
     <t>20:33:50</t>
@@ -376,43 +367,43 @@
     <t>22:10:18</t>
   </si>
   <si>
-    <t>18:03:46</t>
+    <t>18:03:45</t>
   </si>
   <si>
     <t>19:40:05</t>
   </si>
   <si>
-    <t>21:16:34</t>
-  </si>
-  <si>
-    <t>22:52:50</t>
-  </si>
-  <si>
-    <t>18:46:15</t>
-  </si>
-  <si>
-    <t>20:22:43</t>
-  </si>
-  <si>
-    <t>21:59:04</t>
-  </si>
-  <si>
-    <t>19:28:45</t>
-  </si>
-  <si>
-    <t>21:05:10</t>
-  </si>
-  <si>
-    <t>00:10:18</t>
-  </si>
-  <si>
-    <t>20:03:38</t>
-  </si>
-  <si>
-    <t>21:40:51</t>
-  </si>
-  <si>
-    <t>23:17:11</t>
+    <t>21:16:33</t>
+  </si>
+  <si>
+    <t>22:52:49</t>
+  </si>
+  <si>
+    <t>18:46:14</t>
+  </si>
+  <si>
+    <t>20:22:42</t>
+  </si>
+  <si>
+    <t>21:59:03</t>
+  </si>
+  <si>
+    <t>17:52:19</t>
+  </si>
+  <si>
+    <t>19:28:43</t>
+  </si>
+  <si>
+    <t>21:05:08</t>
+  </si>
+  <si>
+    <t>16:58:19</t>
+  </si>
+  <si>
+    <t>18:34:39</t>
+  </si>
+  <si>
+    <t>20:11:06</t>
   </si>
   <si>
     <t>19:09:28</t>
@@ -445,43 +436,43 @@
     <t>22:12:53</t>
   </si>
   <si>
-    <t>18:05:30</t>
-  </si>
-  <si>
-    <t>19:42:55</t>
-  </si>
-  <si>
-    <t>21:19:20</t>
-  </si>
-  <si>
-    <t>22:54:02</t>
-  </si>
-  <si>
-    <t>18:48:57</t>
-  </si>
-  <si>
-    <t>20:25:34</t>
-  </si>
-  <si>
-    <t>22:01:07</t>
-  </si>
-  <si>
-    <t>19:31:38</t>
-  </si>
-  <si>
-    <t>21:07:38</t>
-  </si>
-  <si>
-    <t>00:12:42</t>
-  </si>
-  <si>
-    <t>20:06:17</t>
-  </si>
-  <si>
-    <t>21:43:05</t>
-  </si>
-  <si>
-    <t>23:19:30</t>
+    <t>18:05:29</t>
+  </si>
+  <si>
+    <t>19:42:54</t>
+  </si>
+  <si>
+    <t>21:19:19</t>
+  </si>
+  <si>
+    <t>22:54:01</t>
+  </si>
+  <si>
+    <t>18:48:55</t>
+  </si>
+  <si>
+    <t>20:25:33</t>
+  </si>
+  <si>
+    <t>22:01:05</t>
+  </si>
+  <si>
+    <t>17:54:46</t>
+  </si>
+  <si>
+    <t>19:31:36</t>
+  </si>
+  <si>
+    <t>21:07:36</t>
+  </si>
+  <si>
+    <t>17:00:22</t>
+  </si>
+  <si>
+    <t>18:37:31</t>
+  </si>
+  <si>
+    <t>20:13:48</t>
   </si>
   <si>
     <t>19:12:39</t>
@@ -505,40 +496,52 @@
     <t>23:08:42</t>
   </si>
   <si>
-    <t>19:02:14</t>
-  </si>
-  <si>
-    <t>20:38:57</t>
-  </si>
-  <si>
-    <t>22:15:15</t>
-  </si>
-  <si>
-    <t>18:08:20</t>
-  </si>
-  <si>
-    <t>19:45:10</t>
+    <t>19:02:13</t>
+  </si>
+  <si>
+    <t>20:38:56</t>
+  </si>
+  <si>
+    <t>22:15:14</t>
+  </si>
+  <si>
+    <t>18:08:19</t>
+  </si>
+  <si>
+    <t>19:45:09</t>
   </si>
   <si>
     <t>21:21:36</t>
   </si>
   <si>
-    <t>22:57:13</t>
-  </si>
-  <si>
-    <t>18:51:15</t>
-  </si>
-  <si>
-    <t>20:27:48</t>
-  </si>
-  <si>
-    <t>22:03:45</t>
-  </si>
-  <si>
-    <t>19:33:52</t>
-  </si>
-  <si>
-    <t>21:10:03</t>
+    <t>22:57:12</t>
+  </si>
+  <si>
+    <t>18:51:14</t>
+  </si>
+  <si>
+    <t>20:27:47</t>
+  </si>
+  <si>
+    <t>22:03:43</t>
+  </si>
+  <si>
+    <t>17:57:11</t>
+  </si>
+  <si>
+    <t>19:33:50</t>
+  </si>
+  <si>
+    <t>21:10:01</t>
+  </si>
+  <si>
+    <t>17:03:00</t>
+  </si>
+  <si>
+    <t>18:39:45</t>
+  </si>
+  <si>
+    <t>20:16:06</t>
   </si>
   <si>
     <t>0°</t>
@@ -553,25 +556,49 @@
     <t>8°</t>
   </si>
   <si>
-    <t>18:53:11</t>
-  </si>
-  <si>
-    <t>18:02:00</t>
-  </si>
-  <si>
-    <t>18:43:12</t>
-  </si>
-  <si>
-    <t>19:24:13</t>
+    <t>19°</t>
+  </si>
+  <si>
+    <t>12°</t>
+  </si>
+  <si>
+    <t>14°</t>
+  </si>
+  <si>
+    <t>18:53:10</t>
+  </si>
+  <si>
+    <t>18:01:59</t>
+  </si>
+  <si>
+    <t>18:43:11</t>
+  </si>
+  <si>
+    <t>17:51:37</t>
+  </si>
+  <si>
+    <t>19:24:11</t>
+  </si>
+  <si>
+    <t>16:59:55</t>
+  </si>
+  <si>
+    <t>18:32:27</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
+    <t>A+B</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
-    <t>4</t>
+    <t>2</t>
   </si>
 </sst>
 </file>
@@ -605,7 +632,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -620,7 +647,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -632,25 +725,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
+        <fgColor rgb="FFEEF3F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -662,25 +737,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -692,31 +755,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
+        <fgColor rgb="FFF6F9FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -757,7 +796,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -823,6 +862,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1304,55 +1349,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>41</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L2" s="4">
-        <v>-45.9</v>
+        <v>-29.5</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="O2" s="6">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="P2" s="7">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="Q2" s="8">
-        <v>37</v>
-      </c>
-      <c r="R2" s="9">
-        <v>95</v>
+        <v>0</v>
+      </c>
+      <c r="R2" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1360,55 +1405,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L3" s="4">
-        <v>-36.6</v>
+        <v>-42.1</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="O3" s="6">
+        <v>193</v>
+      </c>
+      <c r="O3" s="9">
         <v>50</v>
       </c>
       <c r="P3" s="10">
-        <v>17</v>
-      </c>
-      <c r="Q3" s="11">
+        <v>50</v>
+      </c>
+      <c r="Q3" s="8">
         <v>0</v>
       </c>
-      <c r="R3" s="12">
-        <v>32</v>
+      <c r="R3" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1416,55 +1461,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L4" s="4">
-        <v>-46.6</v>
+        <v>-49.2</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="O4" s="6">
-        <v>77</v>
-      </c>
-      <c r="P4" s="8">
-        <v>34</v>
-      </c>
-      <c r="Q4" s="11">
+        <v>193</v>
+      </c>
+      <c r="O4" s="9">
+        <v>87</v>
+      </c>
+      <c r="P4" s="11">
+        <v>84</v>
+      </c>
+      <c r="Q4" s="8">
         <v>0</v>
       </c>
-      <c r="R4" s="13">
-        <v>54</v>
+      <c r="R4" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1472,55 +1517,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L5" s="4">
-        <v>-48.9</v>
+        <v>-47.3</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="O5" s="14">
-        <v>33</v>
-      </c>
-      <c r="P5" s="15">
-        <v>7</v>
-      </c>
-      <c r="Q5" s="11">
+        <v>192</v>
+      </c>
+      <c r="O5" s="9">
+        <v>80</v>
+      </c>
+      <c r="P5" s="12">
+        <v>78</v>
+      </c>
+      <c r="Q5" s="8">
         <v>0</v>
       </c>
-      <c r="R5" s="12">
-        <v>30</v>
+      <c r="R5" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1528,55 +1573,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L6" s="4">
-        <v>-29.5</v>
+        <v>-35.9</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="O6" s="6">
-        <v>93</v>
-      </c>
-      <c r="P6" s="9">
-        <v>93</v>
-      </c>
-      <c r="Q6" s="11">
-        <v>0</v>
-      </c>
-      <c r="R6" s="11">
-        <v>0</v>
+        <v>193</v>
+      </c>
+      <c r="O6" s="9">
+        <v>97</v>
+      </c>
+      <c r="P6" s="7">
+        <v>40</v>
+      </c>
+      <c r="Q6" s="13">
+        <v>3</v>
+      </c>
+      <c r="R6" s="14">
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1584,55 +1629,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L7" s="4">
-        <v>-42.1</v>
+        <v>-46.6</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="O7" s="6">
-        <v>93</v>
-      </c>
-      <c r="P7" s="9">
-        <v>93</v>
-      </c>
-      <c r="Q7" s="11">
-        <v>0</v>
-      </c>
-      <c r="R7" s="11">
-        <v>0</v>
+        <v>193</v>
+      </c>
+      <c r="O7" s="9">
+        <v>68</v>
+      </c>
+      <c r="P7" s="7">
+        <v>42</v>
+      </c>
+      <c r="Q7" s="15">
+        <v>16</v>
+      </c>
+      <c r="R7" s="13">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1640,55 +1685,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L8" s="4">
-        <v>-49.2</v>
+        <v>-49.9</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="O8" s="6">
-        <v>93</v>
-      </c>
-      <c r="P8" s="9">
-        <v>93</v>
-      </c>
-      <c r="Q8" s="11">
-        <v>0</v>
-      </c>
-      <c r="R8" s="11">
-        <v>0</v>
+        <v>193</v>
+      </c>
+      <c r="O8" s="9">
+        <v>83</v>
+      </c>
+      <c r="P8" s="16">
+        <v>34</v>
+      </c>
+      <c r="Q8" s="13">
+        <v>5</v>
+      </c>
+      <c r="R8" s="17">
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1696,55 +1741,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>67</v>
+        <v>183</v>
       </c>
       <c r="L9" s="4">
-        <v>-47.3</v>
+        <v>-28.4</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="O9" s="6">
-        <v>92</v>
-      </c>
-      <c r="P9" s="16">
-        <v>92</v>
-      </c>
-      <c r="Q9" s="11">
-        <v>0</v>
-      </c>
-      <c r="R9" s="11">
-        <v>0</v>
+        <v>193</v>
+      </c>
+      <c r="O9" s="9">
+        <v>100</v>
+      </c>
+      <c r="P9" s="18">
+        <v>98</v>
+      </c>
+      <c r="Q9" s="18">
+        <v>100</v>
+      </c>
+      <c r="R9" s="18">
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1752,55 +1797,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L10" s="4">
-        <v>-35.9</v>
+        <v>-41.6</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="O10" s="6">
-        <v>64</v>
-      </c>
-      <c r="P10" s="12">
-        <v>30</v>
-      </c>
-      <c r="Q10" s="17">
-        <v>11</v>
-      </c>
-      <c r="R10" s="12">
-        <v>28</v>
+        <v>193</v>
+      </c>
+      <c r="O10" s="9">
+        <v>100</v>
+      </c>
+      <c r="P10" s="18">
+        <v>98</v>
+      </c>
+      <c r="Q10" s="18">
+        <v>100</v>
+      </c>
+      <c r="R10" s="18">
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1808,55 +1853,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L11" s="4">
+        <v>-49.5</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="O11" s="9">
+        <v>100</v>
+      </c>
+      <c r="P11" s="19">
         <v>92</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="L11" s="4">
-        <v>-46.6</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="O11" s="14">
-        <v>41</v>
-      </c>
-      <c r="P11" s="10">
-        <v>16</v>
-      </c>
-      <c r="Q11" s="11">
-        <v>2</v>
-      </c>
-      <c r="R11" s="12">
-        <v>29</v>
+      <c r="Q11" s="18">
+        <v>100</v>
+      </c>
+      <c r="R11" s="18">
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1864,55 +1909,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>70</v>
+        <v>184</v>
       </c>
       <c r="L12" s="4">
-        <v>-49.9</v>
+        <v>-20.4</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="O12" s="14">
-        <v>48</v>
-      </c>
-      <c r="P12" s="10">
-        <v>15</v>
-      </c>
-      <c r="Q12" s="15">
-        <v>6</v>
-      </c>
-      <c r="R12" s="18">
-        <v>26</v>
+        <v>192</v>
+      </c>
+      <c r="O12" s="6">
+        <v>44</v>
+      </c>
+      <c r="P12" s="8">
+        <v>2</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>42</v>
+      </c>
+      <c r="R12" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1920,55 +1965,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>176</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="L13" s="4">
-        <v>-28.4</v>
+        <v>-35</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="O13" s="6">
-        <v>100</v>
-      </c>
-      <c r="P13" s="9">
-        <v>94</v>
-      </c>
-      <c r="Q13" s="7">
-        <v>100</v>
-      </c>
-      <c r="R13" s="7">
-        <v>100</v>
+        <v>193</v>
+      </c>
+      <c r="O13" s="9">
+        <v>64</v>
+      </c>
+      <c r="P13" s="13">
+        <v>5</v>
+      </c>
+      <c r="Q13" s="17">
+        <v>55</v>
+      </c>
+      <c r="R13" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1976,55 +2021,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L14" s="4">
-        <v>-41.6</v>
+        <v>-46.3</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="O14" s="6">
-        <v>100</v>
-      </c>
-      <c r="P14" s="16">
-        <v>92</v>
-      </c>
-      <c r="Q14" s="7">
-        <v>100</v>
-      </c>
-      <c r="R14" s="7">
-        <v>100</v>
+        <v>193</v>
+      </c>
+      <c r="O14" s="9">
+        <v>90</v>
+      </c>
+      <c r="P14" s="7">
+        <v>39</v>
+      </c>
+      <c r="Q14" s="17">
+        <v>54</v>
+      </c>
+      <c r="R14" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2032,55 +2077,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L15" s="4">
-        <v>-49.5</v>
+        <v>-50.7</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="O15" s="6">
-        <v>100</v>
-      </c>
-      <c r="P15" s="9">
-        <v>93</v>
-      </c>
-      <c r="Q15" s="7">
-        <v>100</v>
-      </c>
-      <c r="R15" s="7">
-        <v>100</v>
+        <v>192</v>
+      </c>
+      <c r="O15" s="9">
+        <v>90</v>
+      </c>
+      <c r="P15" s="14">
+        <v>46</v>
+      </c>
+      <c r="Q15" s="17">
+        <v>55</v>
+      </c>
+      <c r="R15" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2088,55 +2133,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="L16" s="4">
+        <v>-27.3</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="O16" s="9">
         <v>53</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="L16" s="4">
-        <v>-20.4</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="O16" s="14">
-        <v>32</v>
-      </c>
-      <c r="P16" s="11">
-        <v>2</v>
-      </c>
-      <c r="Q16" s="12">
-        <v>32</v>
-      </c>
-      <c r="R16" s="12">
-        <v>28</v>
+      <c r="P16" s="16">
+        <v>35</v>
+      </c>
+      <c r="Q16" s="17">
+        <v>53</v>
+      </c>
+      <c r="R16" s="20">
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2144,55 +2189,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L17" s="4">
-        <v>-35</v>
+        <v>-40.9</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="O17" s="14">
-        <v>30</v>
-      </c>
-      <c r="P17" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="17">
-        <v>8</v>
-      </c>
-      <c r="R17" s="12">
-        <v>30</v>
+        <v>193</v>
+      </c>
+      <c r="O17" s="9">
+        <v>92</v>
+      </c>
+      <c r="P17" s="10">
+        <v>52</v>
+      </c>
+      <c r="Q17" s="21">
+        <v>73</v>
+      </c>
+      <c r="R17" s="14">
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2200,55 +2245,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L18" s="4">
-        <v>-46.3</v>
+        <v>-49.7</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="O18" s="14">
-        <v>30</v>
-      </c>
-      <c r="P18" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="15">
-        <v>5</v>
-      </c>
-      <c r="R18" s="19">
-        <v>18</v>
+        <v>193</v>
+      </c>
+      <c r="O18" s="9">
+        <v>83</v>
+      </c>
+      <c r="P18" s="16">
+        <v>35</v>
+      </c>
+      <c r="Q18" s="10">
+        <v>49</v>
+      </c>
+      <c r="R18" s="22">
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2256,55 +2301,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>77</v>
+        <v>186</v>
       </c>
       <c r="L19" s="4">
-        <v>-50.7</v>
+        <v>-19.2</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="O19" s="14">
-        <v>28</v>
-      </c>
-      <c r="P19" s="11">
+        <v>194</v>
+      </c>
+      <c r="O19" s="9">
+        <v>50</v>
+      </c>
+      <c r="P19" s="14">
+        <v>44</v>
+      </c>
+      <c r="Q19" s="20">
+        <v>29</v>
+      </c>
+      <c r="R19" s="8">
         <v>0</v>
-      </c>
-      <c r="Q19" s="11">
-        <v>0</v>
-      </c>
-      <c r="R19" s="18">
-        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2312,55 +2357,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="L20" s="4">
-        <v>-27.3</v>
+        <v>-33.9</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="O20" s="6">
-        <v>95</v>
-      </c>
-      <c r="P20" s="20">
-        <v>47</v>
-      </c>
-      <c r="Q20" s="21">
-        <v>82</v>
-      </c>
-      <c r="R20" s="17">
-        <v>10</v>
+        <v>14</v>
+      </c>
+      <c r="P20" s="15">
+        <v>14</v>
+      </c>
+      <c r="Q20" s="23">
+        <v>12</v>
+      </c>
+      <c r="R20" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2368,55 +2413,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L21" s="4">
-        <v>-40.9</v>
+        <v>-45.9</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="O21" s="6">
-        <v>94</v>
-      </c>
-      <c r="P21" s="8">
-        <v>36</v>
-      </c>
-      <c r="Q21" s="22">
-        <v>69</v>
-      </c>
-      <c r="R21" s="15">
-        <v>6</v>
+        <v>193</v>
+      </c>
+      <c r="O21" s="9">
+        <v>48</v>
+      </c>
+      <c r="P21" s="10">
+        <v>48</v>
+      </c>
+      <c r="Q21" s="16">
+        <v>34</v>
+      </c>
+      <c r="R21" s="7">
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2427,52 +2472,52 @@
         <v>16</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>80</v>
+        <v>188</v>
       </c>
       <c r="L22" s="4">
-        <v>-49.7</v>
+        <v>-11</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="O22" s="6">
-        <v>94</v>
-      </c>
-      <c r="P22" s="19">
-        <v>21</v>
-      </c>
-      <c r="Q22" s="13">
-        <v>55</v>
-      </c>
-      <c r="R22" s="15">
-        <v>6</v>
+        <v>194</v>
+      </c>
+      <c r="O22" s="9">
+        <v>100</v>
+      </c>
+      <c r="P22" s="22">
+        <v>65</v>
+      </c>
+      <c r="Q22" s="24">
+        <v>93</v>
+      </c>
+      <c r="R22" s="11">
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2480,55 +2525,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="L23" s="4">
-        <v>-33.9</v>
+        <v>-26.1</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="O23" s="14">
-        <v>36</v>
-      </c>
-      <c r="P23" s="8">
-        <v>35</v>
-      </c>
-      <c r="Q23" s="17">
-        <v>12</v>
-      </c>
-      <c r="R23" s="11">
-        <v>0</v>
+        <v>194</v>
+      </c>
+      <c r="O23" s="9">
+        <v>100</v>
+      </c>
+      <c r="P23" s="19">
+        <v>89</v>
+      </c>
+      <c r="Q23" s="18">
+        <v>99</v>
+      </c>
+      <c r="R23" s="18">
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2536,55 +2581,55 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L24" s="4">
-        <v>-45.9</v>
+        <v>-40.1</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="O24" s="14">
-        <v>19</v>
-      </c>
-      <c r="P24" s="10">
-        <v>17</v>
-      </c>
-      <c r="Q24" s="17">
-        <v>8</v>
-      </c>
-      <c r="R24" s="19">
-        <v>19</v>
+        <v>193</v>
+      </c>
+      <c r="O24" s="9">
+        <v>100</v>
+      </c>
+      <c r="P24" s="11">
+        <v>86</v>
+      </c>
+      <c r="Q24" s="18">
+        <v>100</v>
+      </c>
+      <c r="R24" s="18">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="194">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261019--01</t>
-  </si>
-  <si>
-    <t>20261019--02</t>
-  </si>
-  <si>
-    <t>20261019--03</t>
-  </si>
-  <si>
-    <t>20261019--04</t>
-  </si>
-  <si>
     <t>20261020--01</t>
   </si>
   <si>
@@ -139,409 +127,406 @@
     <t>20261025--03</t>
   </si>
   <si>
-    <t>02:24</t>
+    <t>20261026--01</t>
+  </si>
+  <si>
+    <t>20261026--02</t>
+  </si>
+  <si>
+    <t>20261026--03</t>
+  </si>
+  <si>
+    <t>05:10</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>04:34</t>
+  </si>
+  <si>
+    <t>03:26</t>
+  </si>
+  <si>
+    <t>05:38</t>
   </si>
   <si>
     <t>05:32</t>
   </si>
   <si>
-    <t>05:39</t>
-  </si>
-  <si>
-    <t>03:28</t>
-  </si>
-  <si>
-    <t>05:11</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>04:34</t>
-  </si>
-  <si>
-    <t>03:27</t>
-  </si>
-  <si>
-    <t>05:38</t>
+    <t>02:22</t>
+  </si>
+  <si>
+    <t>05:23</t>
+  </si>
+  <si>
+    <t>05:42</t>
+  </si>
+  <si>
+    <t>04:04</t>
+  </si>
+  <si>
+    <t>04:55</t>
+  </si>
+  <si>
+    <t>04:54</t>
+  </si>
+  <si>
+    <t>04:06</t>
   </si>
   <si>
     <t>05:22</t>
   </si>
   <si>
-    <t>05:42</t>
-  </si>
-  <si>
-    <t>04:05</t>
-  </si>
-  <si>
-    <t>04:55</t>
-  </si>
-  <si>
-    <t>05:43</t>
-  </si>
-  <si>
-    <t>05:23</t>
+    <t>05:31</t>
+  </si>
+  <si>
+    <t>03:25</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:46</t>
+    <t>01:45</t>
   </si>
   <si>
     <t>03:38</t>
   </si>
   <si>
-    <t>00:39</t>
-  </si>
-  <si>
-    <t>19:03:54</t>
-  </si>
-  <si>
-    <t>20:39:31</t>
-  </si>
-  <si>
-    <t>22:15:58</t>
-  </si>
-  <si>
-    <t>23:52:49</t>
-  </si>
-  <si>
-    <t>19:46:05</t>
-  </si>
-  <si>
-    <t>21:22:24</t>
-  </si>
-  <si>
-    <t>22:59:06</t>
-  </si>
-  <si>
-    <t>18:52:39</t>
-  </si>
-  <si>
-    <t>20:28:44</t>
-  </si>
-  <si>
-    <t>22:05:21</t>
-  </si>
-  <si>
-    <t>17:59:13</t>
-  </si>
-  <si>
-    <t>19:35:01</t>
-  </si>
-  <si>
-    <t>21:11:31</t>
-  </si>
-  <si>
-    <t>22:48:26</t>
-  </si>
-  <si>
-    <t>18:41:14</t>
-  </si>
-  <si>
-    <t>20:17:36</t>
-  </si>
-  <si>
-    <t>21:54:22</t>
-  </si>
-  <si>
-    <t>17:47:26</t>
-  </si>
-  <si>
-    <t>19:23:37</t>
-  </si>
-  <si>
-    <t>21:00:16</t>
-  </si>
-  <si>
-    <t>16:53:38</t>
-  </si>
-  <si>
-    <t>18:29:34</t>
-  </si>
-  <si>
-    <t>20:06:06</t>
-  </si>
-  <si>
-    <t>19:07:04</t>
-  </si>
-  <si>
-    <t>20:41:47</t>
-  </si>
-  <si>
-    <t>22:18:13</t>
-  </si>
-  <si>
-    <t>23:55:39</t>
-  </si>
-  <si>
-    <t>19:48:26</t>
-  </si>
-  <si>
-    <t>21:24:37</t>
-  </si>
-  <si>
-    <t>23:01:37</t>
-  </si>
-  <si>
-    <t>18:55:09</t>
-  </si>
-  <si>
-    <t>20:30:58</t>
-  </si>
-  <si>
-    <t>22:07:42</t>
-  </si>
-  <si>
-    <t>18:02:02</t>
-  </si>
-  <si>
-    <t>19:37:16</t>
-  </si>
-  <si>
-    <t>21:13:47</t>
-  </si>
-  <si>
-    <t>22:51:37</t>
-  </si>
-  <si>
-    <t>18:43:33</t>
-  </si>
-  <si>
-    <t>20:19:51</t>
-  </si>
-  <si>
-    <t>21:57:00</t>
-  </si>
-  <si>
-    <t>17:49:51</t>
-  </si>
-  <si>
-    <t>19:25:51</t>
-  </si>
-  <si>
-    <t>21:02:41</t>
-  </si>
-  <si>
-    <t>16:56:17</t>
-  </si>
-  <si>
-    <t>18:31:48</t>
-  </si>
-  <si>
-    <t>20:08:25</t>
-  </si>
-  <si>
-    <t>19:08:16</t>
-  </si>
-  <si>
-    <t>20:44:33</t>
-  </si>
-  <si>
-    <t>22:21:03</t>
-  </si>
-  <si>
-    <t>23:57:23</t>
-  </si>
-  <si>
-    <t>19:51:01</t>
-  </si>
-  <si>
-    <t>21:27:30</t>
-  </si>
-  <si>
-    <t>23:03:54</t>
-  </si>
-  <si>
-    <t>18:57:25</t>
-  </si>
-  <si>
-    <t>20:33:50</t>
-  </si>
-  <si>
-    <t>22:10:18</t>
-  </si>
-  <si>
-    <t>18:03:45</t>
-  </si>
-  <si>
-    <t>19:40:05</t>
-  </si>
-  <si>
-    <t>21:16:33</t>
-  </si>
-  <si>
-    <t>22:52:49</t>
-  </si>
-  <si>
-    <t>18:46:14</t>
-  </si>
-  <si>
-    <t>20:22:42</t>
-  </si>
-  <si>
-    <t>21:59:03</t>
-  </si>
-  <si>
-    <t>17:52:19</t>
-  </si>
-  <si>
-    <t>19:28:43</t>
-  </si>
-  <si>
-    <t>21:05:08</t>
-  </si>
-  <si>
-    <t>16:58:19</t>
-  </si>
-  <si>
-    <t>18:34:39</t>
-  </si>
-  <si>
-    <t>20:11:06</t>
-  </si>
-  <si>
-    <t>19:09:28</t>
-  </si>
-  <si>
-    <t>20:47:19</t>
-  </si>
-  <si>
-    <t>22:23:52</t>
-  </si>
-  <si>
-    <t>23:59:07</t>
-  </si>
-  <si>
-    <t>19:53:37</t>
-  </si>
-  <si>
-    <t>21:30:22</t>
-  </si>
-  <si>
-    <t>23:06:12</t>
-  </si>
-  <si>
-    <t>18:59:43</t>
-  </si>
-  <si>
-    <t>20:36:43</t>
-  </si>
-  <si>
-    <t>22:12:53</t>
-  </si>
-  <si>
-    <t>18:05:29</t>
-  </si>
-  <si>
-    <t>19:42:54</t>
-  </si>
-  <si>
-    <t>21:19:19</t>
-  </si>
-  <si>
-    <t>22:54:01</t>
-  </si>
-  <si>
-    <t>18:48:55</t>
-  </si>
-  <si>
-    <t>20:25:33</t>
-  </si>
-  <si>
-    <t>22:01:05</t>
-  </si>
-  <si>
-    <t>17:54:46</t>
-  </si>
-  <si>
-    <t>19:31:36</t>
-  </si>
-  <si>
-    <t>21:07:36</t>
-  </si>
-  <si>
-    <t>17:00:22</t>
-  </si>
-  <si>
-    <t>18:37:31</t>
-  </si>
-  <si>
-    <t>20:13:48</t>
-  </si>
-  <si>
-    <t>19:12:39</t>
-  </si>
-  <si>
-    <t>20:49:36</t>
-  </si>
-  <si>
-    <t>22:26:08</t>
-  </si>
-  <si>
-    <t>00:01:57</t>
-  </si>
-  <si>
-    <t>19:55:59</t>
-  </si>
-  <si>
-    <t>21:32:36</t>
-  </si>
-  <si>
-    <t>23:08:42</t>
-  </si>
-  <si>
-    <t>19:02:13</t>
-  </si>
-  <si>
-    <t>20:38:56</t>
-  </si>
-  <si>
-    <t>22:15:14</t>
-  </si>
-  <si>
-    <t>18:08:19</t>
-  </si>
-  <si>
-    <t>19:45:09</t>
-  </si>
-  <si>
-    <t>21:21:36</t>
-  </si>
-  <si>
-    <t>22:57:12</t>
-  </si>
-  <si>
-    <t>18:51:14</t>
-  </si>
-  <si>
-    <t>20:27:47</t>
-  </si>
-  <si>
-    <t>22:03:43</t>
-  </si>
-  <si>
-    <t>17:57:11</t>
-  </si>
-  <si>
-    <t>19:33:50</t>
-  </si>
-  <si>
-    <t>21:10:01</t>
-  </si>
-  <si>
-    <t>17:03:00</t>
-  </si>
-  <si>
-    <t>18:39:45</t>
-  </si>
-  <si>
-    <t>20:16:06</t>
+    <t>00:38</t>
+  </si>
+  <si>
+    <t>02:50</t>
+  </si>
+  <si>
+    <t>19:46:09</t>
+  </si>
+  <si>
+    <t>21:22:27</t>
+  </si>
+  <si>
+    <t>22:59:10</t>
+  </si>
+  <si>
+    <t>18:52:45</t>
+  </si>
+  <si>
+    <t>20:28:51</t>
+  </si>
+  <si>
+    <t>22:05:27</t>
+  </si>
+  <si>
+    <t>17:59:23</t>
+  </si>
+  <si>
+    <t>19:35:11</t>
+  </si>
+  <si>
+    <t>21:11:41</t>
+  </si>
+  <si>
+    <t>22:48:36</t>
+  </si>
+  <si>
+    <t>18:41:28</t>
+  </si>
+  <si>
+    <t>20:17:51</t>
+  </si>
+  <si>
+    <t>21:54:36</t>
+  </si>
+  <si>
+    <t>17:47:45</t>
+  </si>
+  <si>
+    <t>19:23:56</t>
+  </si>
+  <si>
+    <t>21:00:35</t>
+  </si>
+  <si>
+    <t>16:54:02</t>
+  </si>
+  <si>
+    <t>18:29:59</t>
+  </si>
+  <si>
+    <t>20:06:31</t>
+  </si>
+  <si>
+    <t>17:35:58</t>
+  </si>
+  <si>
+    <t>19:12:24</t>
+  </si>
+  <si>
+    <t>20:49:13</t>
+  </si>
+  <si>
+    <t>19:48:30</t>
+  </si>
+  <si>
+    <t>21:24:41</t>
+  </si>
+  <si>
+    <t>23:01:41</t>
+  </si>
+  <si>
+    <t>18:55:15</t>
+  </si>
+  <si>
+    <t>20:31:04</t>
+  </si>
+  <si>
+    <t>22:07:49</t>
+  </si>
+  <si>
+    <t>18:02:12</t>
+  </si>
+  <si>
+    <t>19:37:25</t>
+  </si>
+  <si>
+    <t>21:13:57</t>
+  </si>
+  <si>
+    <t>22:51:48</t>
+  </si>
+  <si>
+    <t>18:43:46</t>
+  </si>
+  <si>
+    <t>20:20:05</t>
+  </si>
+  <si>
+    <t>21:57:15</t>
+  </si>
+  <si>
+    <t>17:50:10</t>
+  </si>
+  <si>
+    <t>19:26:10</t>
+  </si>
+  <si>
+    <t>21:03:01</t>
+  </si>
+  <si>
+    <t>16:56:40</t>
+  </si>
+  <si>
+    <t>18:32:13</t>
+  </si>
+  <si>
+    <t>20:08:50</t>
+  </si>
+  <si>
+    <t>17:38:15</t>
+  </si>
+  <si>
+    <t>19:14:39</t>
+  </si>
+  <si>
+    <t>20:52:03</t>
+  </si>
+  <si>
+    <t>19:51:05</t>
+  </si>
+  <si>
+    <t>21:27:33</t>
+  </si>
+  <si>
+    <t>23:03:58</t>
+  </si>
+  <si>
+    <t>18:57:31</t>
+  </si>
+  <si>
+    <t>20:33:56</t>
+  </si>
+  <si>
+    <t>22:10:24</t>
+  </si>
+  <si>
+    <t>18:03:55</t>
+  </si>
+  <si>
+    <t>19:40:14</t>
+  </si>
+  <si>
+    <t>21:16:43</t>
+  </si>
+  <si>
+    <t>22:52:59</t>
+  </si>
+  <si>
+    <t>18:46:28</t>
+  </si>
+  <si>
+    <t>20:22:56</t>
+  </si>
+  <si>
+    <t>21:59:17</t>
+  </si>
+  <si>
+    <t>17:52:37</t>
+  </si>
+  <si>
+    <t>19:29:02</t>
+  </si>
+  <si>
+    <t>21:05:28</t>
+  </si>
+  <si>
+    <t>16:58:43</t>
+  </si>
+  <si>
+    <t>18:35:04</t>
+  </si>
+  <si>
+    <t>20:11:31</t>
+  </si>
+  <si>
+    <t>17:41:00</t>
+  </si>
+  <si>
+    <t>19:17:28</t>
+  </si>
+  <si>
+    <t>20:53:46</t>
+  </si>
+  <si>
+    <t>19:53:40</t>
+  </si>
+  <si>
+    <t>21:30:26</t>
+  </si>
+  <si>
+    <t>23:06:15</t>
+  </si>
+  <si>
+    <t>18:59:49</t>
+  </si>
+  <si>
+    <t>20:36:49</t>
+  </si>
+  <si>
+    <t>22:12:59</t>
+  </si>
+  <si>
+    <t>18:05:38</t>
+  </si>
+  <si>
+    <t>19:43:03</t>
+  </si>
+  <si>
+    <t>21:19:29</t>
+  </si>
+  <si>
+    <t>22:54:10</t>
+  </si>
+  <si>
+    <t>18:49:09</t>
+  </si>
+  <si>
+    <t>20:25:47</t>
+  </si>
+  <si>
+    <t>22:01:19</t>
+  </si>
+  <si>
+    <t>17:55:05</t>
+  </si>
+  <si>
+    <t>19:31:55</t>
+  </si>
+  <si>
+    <t>21:07:55</t>
+  </si>
+  <si>
+    <t>17:00:46</t>
+  </si>
+  <si>
+    <t>18:37:55</t>
+  </si>
+  <si>
+    <t>20:14:12</t>
+  </si>
+  <si>
+    <t>17:43:46</t>
+  </si>
+  <si>
+    <t>19:20:17</t>
+  </si>
+  <si>
+    <t>20:55:28</t>
+  </si>
+  <si>
+    <t>19:56:02</t>
+  </si>
+  <si>
+    <t>21:32:39</t>
+  </si>
+  <si>
+    <t>23:08:46</t>
+  </si>
+  <si>
+    <t>19:02:19</t>
+  </si>
+  <si>
+    <t>20:39:02</t>
+  </si>
+  <si>
+    <t>22:15:21</t>
+  </si>
+  <si>
+    <t>18:08:28</t>
+  </si>
+  <si>
+    <t>19:45:18</t>
+  </si>
+  <si>
+    <t>21:21:45</t>
+  </si>
+  <si>
+    <t>22:57:22</t>
+  </si>
+  <si>
+    <t>18:51:28</t>
+  </si>
+  <si>
+    <t>20:28:01</t>
+  </si>
+  <si>
+    <t>22:03:57</t>
+  </si>
+  <si>
+    <t>17:57:30</t>
+  </si>
+  <si>
+    <t>19:34:09</t>
+  </si>
+  <si>
+    <t>21:10:20</t>
+  </si>
+  <si>
+    <t>17:03:24</t>
+  </si>
+  <si>
+    <t>18:40:09</t>
+  </si>
+  <si>
+    <t>20:16:30</t>
+  </si>
+  <si>
+    <t>17:46:03</t>
+  </si>
+  <si>
+    <t>19:22:31</t>
+  </si>
+  <si>
+    <t>20:58:18</t>
   </si>
   <si>
     <t>0°</t>
@@ -565,25 +550,37 @@
     <t>14°</t>
   </si>
   <si>
-    <t>18:53:10</t>
-  </si>
-  <si>
-    <t>18:01:59</t>
-  </si>
-  <si>
-    <t>18:43:11</t>
-  </si>
-  <si>
-    <t>17:51:37</t>
-  </si>
-  <si>
-    <t>19:24:11</t>
-  </si>
-  <si>
-    <t>16:59:55</t>
-  </si>
-  <si>
-    <t>18:32:27</t>
+    <t>26°</t>
+  </si>
+  <si>
+    <t>5°</t>
+  </si>
+  <si>
+    <t>18:53:16</t>
+  </si>
+  <si>
+    <t>18:02:08</t>
+  </si>
+  <si>
+    <t>18:43:24</t>
+  </si>
+  <si>
+    <t>17:51:55</t>
+  </si>
+  <si>
+    <t>19:24:29</t>
+  </si>
+  <si>
+    <t>17:00:18</t>
+  </si>
+  <si>
+    <t>18:32:51</t>
+  </si>
+  <si>
+    <t>17:41:05</t>
+  </si>
+  <si>
+    <t>19:13:38</t>
   </si>
   <si>
     <t>B</t>
@@ -592,10 +589,10 @@
     <t>A+B</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t>2</t>
@@ -632,7 +629,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -647,13 +644,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -665,19 +668,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -695,7 +686,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -707,7 +698,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -719,19 +740,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -743,19 +764,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -796,7 +817,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -868,6 +889,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1271,7 +1304,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R24"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1349,55 +1382,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>61</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>61</v>
       </c>
       <c r="L2" s="4">
-        <v>-29.5</v>
+        <v>-35.9</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O2" s="6">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="P2" s="7">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="Q2" s="8">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
-        <v>0</v>
+        <v>97</v>
+      </c>
+      <c r="R2" s="9">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1405,55 +1438,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>62</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>62</v>
       </c>
       <c r="L3" s="4">
-        <v>-42.1</v>
+        <v>-46.6</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O3" s="9">
-        <v>50</v>
+        <v>191</v>
+      </c>
+      <c r="O3" s="6">
+        <v>86</v>
       </c>
       <c r="P3" s="10">
-        <v>50</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>0</v>
-      </c>
-      <c r="R3" s="8">
-        <v>0</v>
+        <v>28</v>
+      </c>
+      <c r="Q3" s="11">
+        <v>78</v>
+      </c>
+      <c r="R3" s="12">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1461,55 +1494,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>63</v>
       </c>
       <c r="L4" s="4">
-        <v>-49.2</v>
+        <v>-49.9</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O4" s="9">
-        <v>87</v>
-      </c>
-      <c r="P4" s="11">
-        <v>84</v>
-      </c>
-      <c r="Q4" s="8">
-        <v>0</v>
-      </c>
-      <c r="R4" s="8">
-        <v>0</v>
+        <v>191</v>
+      </c>
+      <c r="O4" s="6">
+        <v>78</v>
+      </c>
+      <c r="P4" s="7">
+        <v>19</v>
+      </c>
+      <c r="Q4" s="13">
+        <v>67</v>
+      </c>
+      <c r="R4" s="14">
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1517,55 +1550,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>64</v>
+        <v>180</v>
       </c>
       <c r="L5" s="4">
-        <v>-47.3</v>
+        <v>-28.4</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="O5" s="9">
-        <v>80</v>
-      </c>
-      <c r="P5" s="12">
-        <v>78</v>
+        <v>191</v>
+      </c>
+      <c r="O5" s="6">
+        <v>100</v>
+      </c>
+      <c r="P5" s="15">
+        <v>90</v>
       </c>
       <c r="Q5" s="8">
-        <v>0</v>
-      </c>
-      <c r="R5" s="8">
-        <v>0</v>
+        <v>95</v>
+      </c>
+      <c r="R5" s="16">
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1573,55 +1606,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>65</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>65</v>
       </c>
       <c r="L6" s="4">
-        <v>-35.9</v>
+        <v>-41.6</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O6" s="9">
-        <v>97</v>
-      </c>
-      <c r="P6" s="7">
-        <v>40</v>
-      </c>
-      <c r="Q6" s="13">
-        <v>3</v>
-      </c>
-      <c r="R6" s="14">
-        <v>45</v>
+        <v>191</v>
+      </c>
+      <c r="O6" s="6">
+        <v>100</v>
+      </c>
+      <c r="P6" s="16">
+        <v>100</v>
+      </c>
+      <c r="Q6" s="16">
+        <v>100</v>
+      </c>
+      <c r="R6" s="16">
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1629,55 +1662,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>66</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>66</v>
       </c>
       <c r="L7" s="4">
-        <v>-46.6</v>
+        <v>-49.5</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O7" s="9">
-        <v>68</v>
-      </c>
-      <c r="P7" s="7">
-        <v>42</v>
-      </c>
-      <c r="Q7" s="15">
-        <v>16</v>
-      </c>
-      <c r="R7" s="13">
-        <v>3</v>
+        <v>191</v>
+      </c>
+      <c r="O7" s="6">
+        <v>100</v>
+      </c>
+      <c r="P7" s="8">
+        <v>97</v>
+      </c>
+      <c r="Q7" s="16">
+        <v>100</v>
+      </c>
+      <c r="R7" s="16">
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1685,55 +1718,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>67</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>67</v>
+        <v>181</v>
       </c>
       <c r="L8" s="4">
-        <v>-49.9</v>
+        <v>-20.4</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O8" s="9">
-        <v>83</v>
-      </c>
-      <c r="P8" s="16">
-        <v>34</v>
-      </c>
-      <c r="Q8" s="13">
-        <v>5</v>
-      </c>
-      <c r="R8" s="17">
-        <v>55</v>
+        <v>192</v>
+      </c>
+      <c r="O8" s="6">
+        <v>93</v>
+      </c>
+      <c r="P8" s="11">
+        <v>81</v>
+      </c>
+      <c r="Q8" s="17">
+        <v>49</v>
+      </c>
+      <c r="R8" s="18">
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1741,55 +1774,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>68</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>183</v>
+        <v>68</v>
       </c>
       <c r="L9" s="4">
-        <v>-28.4</v>
+        <v>-35</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O9" s="9">
-        <v>100</v>
-      </c>
-      <c r="P9" s="18">
-        <v>98</v>
+        <v>191</v>
+      </c>
+      <c r="O9" s="6">
+        <v>96</v>
+      </c>
+      <c r="P9" s="8">
+        <v>95</v>
       </c>
       <c r="Q9" s="18">
-        <v>100</v>
-      </c>
-      <c r="R9" s="18">
-        <v>100</v>
+        <v>47</v>
+      </c>
+      <c r="R9" s="12">
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1797,55 +1830,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>69</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>69</v>
       </c>
       <c r="L10" s="4">
-        <v>-41.6</v>
+        <v>-46.3</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O10" s="9">
-        <v>100</v>
-      </c>
-      <c r="P10" s="18">
-        <v>98</v>
-      </c>
-      <c r="Q10" s="18">
-        <v>100</v>
-      </c>
-      <c r="R10" s="18">
-        <v>100</v>
+        <v>191</v>
+      </c>
+      <c r="O10" s="6">
+        <v>94</v>
+      </c>
+      <c r="P10" s="15">
+        <v>92</v>
+      </c>
+      <c r="Q10" s="19">
+        <v>24</v>
+      </c>
+      <c r="R10" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1853,55 +1886,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>70</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>70</v>
       </c>
       <c r="L11" s="4">
-        <v>-49.5</v>
+        <v>-50.7</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O11" s="9">
-        <v>100</v>
-      </c>
-      <c r="P11" s="19">
-        <v>92</v>
-      </c>
-      <c r="Q11" s="18">
-        <v>100</v>
-      </c>
-      <c r="R11" s="18">
-        <v>100</v>
+        <v>192</v>
+      </c>
+      <c r="O11" s="6">
+        <v>95</v>
+      </c>
+      <c r="P11" s="8">
+        <v>95</v>
+      </c>
+      <c r="Q11" s="10">
+        <v>31</v>
+      </c>
+      <c r="R11" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1909,55 +1942,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L12" s="4">
-        <v>-20.4</v>
+        <v>-27.3</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O12" s="6">
-        <v>44</v>
-      </c>
-      <c r="P12" s="8">
-        <v>2</v>
-      </c>
-      <c r="Q12" s="7">
-        <v>42</v>
-      </c>
-      <c r="R12" s="8">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="P12" s="20">
+        <v>58</v>
+      </c>
+      <c r="Q12" s="16">
+        <v>100</v>
+      </c>
+      <c r="R12" s="21">
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1965,55 +1998,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>72</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>72</v>
       </c>
       <c r="L13" s="4">
-        <v>-35</v>
+        <v>-40.9</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O13" s="9">
-        <v>64</v>
-      </c>
-      <c r="P13" s="13">
+        <v>191</v>
+      </c>
+      <c r="O13" s="6">
+        <v>100</v>
+      </c>
+      <c r="P13" s="12">
         <v>5</v>
       </c>
-      <c r="Q13" s="17">
-        <v>55</v>
-      </c>
-      <c r="R13" s="8">
-        <v>0</v>
+      <c r="Q13" s="16">
+        <v>100</v>
+      </c>
+      <c r="R13" s="7">
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2021,55 +2054,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>73</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>73</v>
       </c>
       <c r="L14" s="4">
-        <v>-46.3</v>
+        <v>-49.7</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O14" s="9">
-        <v>90</v>
-      </c>
-      <c r="P14" s="7">
-        <v>39</v>
-      </c>
-      <c r="Q14" s="17">
-        <v>54</v>
-      </c>
-      <c r="R14" s="8">
-        <v>0</v>
+        <v>191</v>
+      </c>
+      <c r="O14" s="6">
+        <v>100</v>
+      </c>
+      <c r="P14" s="12">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="16">
+        <v>100</v>
+      </c>
+      <c r="R14" s="12">
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2077,10 +2110,10 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>57</v>
@@ -2089,43 +2122,43 @@
         <v>74</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>74</v>
+        <v>183</v>
       </c>
       <c r="L15" s="4">
-        <v>-50.7</v>
+        <v>-19.3</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>190</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="O15" s="9">
-        <v>90</v>
-      </c>
-      <c r="P15" s="14">
-        <v>46</v>
-      </c>
-      <c r="Q15" s="17">
-        <v>55</v>
-      </c>
-      <c r="R15" s="8">
-        <v>0</v>
+        <v>193</v>
+      </c>
+      <c r="O15" s="22">
+        <v>22</v>
+      </c>
+      <c r="P15" s="7">
+        <v>18</v>
+      </c>
+      <c r="Q15" s="9">
+        <v>1</v>
+      </c>
+      <c r="R15" s="12">
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2133,55 +2166,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>75</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L16" s="4">
-        <v>-27.3</v>
+        <v>-33.9</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O16" s="9">
-        <v>53</v>
-      </c>
-      <c r="P16" s="16">
-        <v>35</v>
-      </c>
-      <c r="Q16" s="17">
-        <v>53</v>
-      </c>
-      <c r="R16" s="20">
-        <v>30</v>
+        <v>191</v>
+      </c>
+      <c r="O16" s="23">
+        <v>8</v>
+      </c>
+      <c r="P16" s="12">
+        <v>6</v>
+      </c>
+      <c r="Q16" s="9">
+        <v>1</v>
+      </c>
+      <c r="R16" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2189,55 +2222,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>76</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>76</v>
       </c>
       <c r="L17" s="4">
-        <v>-40.9</v>
+        <v>-46</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O17" s="9">
-        <v>92</v>
+        <v>191</v>
+      </c>
+      <c r="O17" s="22">
+        <v>30</v>
       </c>
       <c r="P17" s="10">
-        <v>52</v>
-      </c>
-      <c r="Q17" s="21">
-        <v>73</v>
-      </c>
-      <c r="R17" s="14">
-        <v>44</v>
+        <v>30</v>
+      </c>
+      <c r="Q17" s="9">
+        <v>1</v>
+      </c>
+      <c r="R17" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2248,34 +2281,34 @@
         <v>16</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>77</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>176</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>77</v>
+        <v>185</v>
       </c>
       <c r="L18" s="4">
-        <v>-49.7</v>
+        <v>-11.1</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>190</v>
@@ -2283,17 +2316,17 @@
       <c r="N18" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="O18" s="9">
+      <c r="O18" s="6">
+        <v>100</v>
+      </c>
+      <c r="P18" s="21">
+        <v>54</v>
+      </c>
+      <c r="Q18" s="24">
         <v>83</v>
       </c>
-      <c r="P18" s="16">
-        <v>35</v>
-      </c>
-      <c r="Q18" s="10">
-        <v>49</v>
-      </c>
-      <c r="R18" s="22">
-        <v>64</v>
+      <c r="R18" s="19">
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2301,55 +2334,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>78</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>186</v>
       </c>
       <c r="L19" s="4">
-        <v>-19.2</v>
+        <v>-26.2</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="O19" s="9">
-        <v>50</v>
-      </c>
-      <c r="P19" s="14">
-        <v>44</v>
-      </c>
-      <c r="Q19" s="20">
-        <v>29</v>
-      </c>
-      <c r="R19" s="8">
-        <v>0</v>
+        <v>193</v>
+      </c>
+      <c r="O19" s="6">
+        <v>100</v>
+      </c>
+      <c r="P19" s="16">
+        <v>100</v>
+      </c>
+      <c r="Q19" s="16">
+        <v>100</v>
+      </c>
+      <c r="R19" s="14">
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2357,55 +2390,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>79</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I20" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>177</v>
-      </c>
       <c r="K20" s="1" t="s">
-        <v>187</v>
+        <v>79</v>
       </c>
       <c r="L20" s="4">
-        <v>-33.9</v>
+        <v>-40.1</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="O20" s="6">
-        <v>14</v>
-      </c>
-      <c r="P20" s="15">
-        <v>14</v>
-      </c>
-      <c r="Q20" s="23">
-        <v>12</v>
-      </c>
-      <c r="R20" s="8">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="P20" s="25">
+        <v>76</v>
+      </c>
+      <c r="Q20" s="25">
+        <v>73</v>
+      </c>
+      <c r="R20" s="12">
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2413,37 +2446,37 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>80</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>80</v>
+        <v>187</v>
       </c>
       <c r="L21" s="4">
-        <v>-45.9</v>
+        <v>-18</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>190</v>
@@ -2451,17 +2484,17 @@
       <c r="N21" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="O21" s="9">
-        <v>48</v>
+      <c r="O21" s="6">
+        <v>95</v>
       </c>
       <c r="P21" s="10">
-        <v>48</v>
-      </c>
-      <c r="Q21" s="16">
-        <v>34</v>
-      </c>
-      <c r="R21" s="7">
-        <v>42</v>
+        <v>28</v>
+      </c>
+      <c r="Q21" s="26">
+        <v>68</v>
+      </c>
+      <c r="R21" s="13">
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2469,55 +2502,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>81</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>188</v>
       </c>
       <c r="L22" s="4">
-        <v>-11</v>
+        <v>-32.8</v>
       </c>
       <c r="M22" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="N22" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="N22" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="O22" s="9">
-        <v>100</v>
-      </c>
-      <c r="P22" s="22">
-        <v>65</v>
-      </c>
-      <c r="Q22" s="24">
-        <v>93</v>
-      </c>
-      <c r="R22" s="11">
-        <v>87</v>
+      <c r="O22" s="6">
+        <v>80</v>
+      </c>
+      <c r="P22" s="7">
+        <v>21</v>
+      </c>
+      <c r="Q22" s="26">
+        <v>70</v>
+      </c>
+      <c r="R22" s="27">
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2525,170 +2558,114 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K23" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L23" s="4">
+        <v>-45.4</v>
+      </c>
+      <c r="M23" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="L23" s="4">
-        <v>-26.1</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>191</v>
-      </c>
       <c r="N23" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="O23" s="9">
-        <v>100</v>
-      </c>
-      <c r="P23" s="19">
-        <v>89</v>
-      </c>
-      <c r="Q23" s="18">
-        <v>99</v>
-      </c>
-      <c r="R23" s="18">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18">
-      <c r="A24" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="2">
-        <v>24</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="L24" s="4">
-        <v>-40.1</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O24" s="9">
-        <v>100</v>
-      </c>
-      <c r="P24" s="11">
-        <v>86</v>
-      </c>
-      <c r="Q24" s="18">
-        <v>100</v>
-      </c>
-      <c r="R24" s="18">
-        <v>100</v>
+        <v>192</v>
+      </c>
+      <c r="O23" s="6">
+        <v>67</v>
+      </c>
+      <c r="P23" s="28">
+        <v>12</v>
+      </c>
+      <c r="Q23" s="20">
+        <v>59</v>
+      </c>
+      <c r="R23" s="14">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A24">
+  <conditionalFormatting sqref="A2:A23">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B24">
+  <conditionalFormatting sqref="B2:B23">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C24">
+  <conditionalFormatting sqref="C2:C23">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D24">
+  <conditionalFormatting sqref="D2:D23">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E24">
+  <conditionalFormatting sqref="E2:E23">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F24">
+  <conditionalFormatting sqref="F2:F23">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G24">
+  <conditionalFormatting sqref="G2:G23">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H24">
+  <conditionalFormatting sqref="H2:H23">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I24">
+  <conditionalFormatting sqref="I2:I23">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J24">
+  <conditionalFormatting sqref="J2:J23">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K24">
+  <conditionalFormatting sqref="K2:K23">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L24">
+  <conditionalFormatting sqref="L2:L23">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2707,12 +2684,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M24">
+  <conditionalFormatting sqref="M2:M23">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N24">
+  <conditionalFormatting sqref="N2:N23">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2729,22 +2706,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O24">
+  <conditionalFormatting sqref="O2:O23">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P24">
+  <conditionalFormatting sqref="P2:P23">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q24">
+  <conditionalFormatting sqref="Q2:Q23">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R24">
+  <conditionalFormatting sqref="R2:R23">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="198">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261020--01</t>
-  </si>
-  <si>
-    <t>20261020--02</t>
-  </si>
-  <si>
-    <t>20261020--03</t>
-  </si>
-  <si>
     <t>20261021--01</t>
   </si>
   <si>
@@ -136,51 +127,60 @@
     <t>20261026--03</t>
   </si>
   <si>
+    <t>20261027--01</t>
+  </si>
+  <si>
+    <t>20261027--02</t>
+  </si>
+  <si>
+    <t>20261027--03</t>
+  </si>
+  <si>
+    <t>04:34</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
     <t>05:10</t>
   </si>
   <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>04:34</t>
-  </si>
-  <si>
-    <t>03:26</t>
+    <t>03:27</t>
+  </si>
+  <si>
+    <t>05:37</t>
+  </si>
+  <si>
+    <t>05:31</t>
+  </si>
+  <si>
+    <t>02:23</t>
+  </si>
+  <si>
+    <t>05:22</t>
+  </si>
+  <si>
+    <t>05:42</t>
+  </si>
+  <si>
+    <t>04:04</t>
+  </si>
+  <si>
+    <t>04:55</t>
+  </si>
+  <si>
+    <t>04:54</t>
+  </si>
+  <si>
+    <t>04:06</t>
+  </si>
+  <si>
+    <t>05:32</t>
   </si>
   <si>
     <t>05:38</t>
   </si>
   <si>
-    <t>05:32</t>
-  </si>
-  <si>
-    <t>02:22</t>
-  </si>
-  <si>
-    <t>05:23</t>
-  </si>
-  <si>
-    <t>05:42</t>
-  </si>
-  <si>
-    <t>04:04</t>
-  </si>
-  <si>
-    <t>04:55</t>
-  </si>
-  <si>
-    <t>04:54</t>
-  </si>
-  <si>
-    <t>04:06</t>
-  </si>
-  <si>
-    <t>05:22</t>
-  </si>
-  <si>
-    <t>05:31</t>
-  </si>
-  <si>
     <t>03:25</t>
   </si>
   <si>
@@ -190,22 +190,16 @@
     <t>01:45</t>
   </si>
   <si>
-    <t>03:38</t>
+    <t>03:37</t>
   </si>
   <si>
     <t>00:38</t>
   </si>
   <si>
-    <t>02:50</t>
-  </si>
-  <si>
-    <t>19:46:09</t>
-  </si>
-  <si>
-    <t>21:22:27</t>
-  </si>
-  <si>
-    <t>22:59:10</t>
+    <t>02:51</t>
+  </si>
+  <si>
+    <t>01:19</t>
   </si>
   <si>
     <t>18:52:45</t>
@@ -214,7 +208,7 @@
     <t>20:28:51</t>
   </si>
   <si>
-    <t>22:05:27</t>
+    <t>22:05:28</t>
   </si>
   <si>
     <t>17:59:23</t>
@@ -235,13 +229,13 @@
     <t>20:17:51</t>
   </si>
   <si>
-    <t>21:54:36</t>
+    <t>21:54:37</t>
   </si>
   <si>
     <t>17:47:45</t>
   </si>
   <si>
-    <t>19:23:56</t>
+    <t>19:23:57</t>
   </si>
   <si>
     <t>21:00:35</t>
@@ -259,19 +253,19 @@
     <t>17:35:58</t>
   </si>
   <si>
-    <t>19:12:24</t>
-  </si>
-  <si>
-    <t>20:49:13</t>
-  </si>
-  <si>
-    <t>19:48:30</t>
-  </si>
-  <si>
-    <t>21:24:41</t>
-  </si>
-  <si>
-    <t>23:01:41</t>
+    <t>19:12:23</t>
+  </si>
+  <si>
+    <t>20:49:12</t>
+  </si>
+  <si>
+    <t>16:41:56</t>
+  </si>
+  <si>
+    <t>18:18:12</t>
+  </si>
+  <si>
+    <t>19:54:52</t>
   </si>
   <si>
     <t>18:55:15</t>
@@ -286,16 +280,16 @@
     <t>18:02:12</t>
   </si>
   <si>
-    <t>19:37:25</t>
-  </si>
-  <si>
-    <t>21:13:57</t>
+    <t>19:37:26</t>
+  </si>
+  <si>
+    <t>21:13:58</t>
   </si>
   <si>
     <t>22:51:48</t>
   </si>
   <si>
-    <t>18:43:46</t>
+    <t>18:43:47</t>
   </si>
   <si>
     <t>20:20:05</t>
@@ -322,25 +316,25 @@
     <t>20:08:50</t>
   </si>
   <si>
-    <t>17:38:15</t>
-  </si>
-  <si>
-    <t>19:14:39</t>
-  </si>
-  <si>
-    <t>20:52:03</t>
-  </si>
-  <si>
-    <t>19:51:05</t>
-  </si>
-  <si>
-    <t>21:27:33</t>
-  </si>
-  <si>
-    <t>23:03:58</t>
-  </si>
-  <si>
-    <t>18:57:31</t>
+    <t>17:38:14</t>
+  </si>
+  <si>
+    <t>19:14:38</t>
+  </si>
+  <si>
+    <t>20:52:02</t>
+  </si>
+  <si>
+    <t>16:44:17</t>
+  </si>
+  <si>
+    <t>18:20:25</t>
+  </si>
+  <si>
+    <t>19:57:23</t>
+  </si>
+  <si>
+    <t>18:57:32</t>
   </si>
   <si>
     <t>20:33:56</t>
@@ -373,7 +367,7 @@
     <t>17:52:37</t>
   </si>
   <si>
-    <t>19:29:02</t>
+    <t>19:29:03</t>
   </si>
   <si>
     <t>21:05:28</t>
@@ -391,19 +385,19 @@
     <t>17:41:00</t>
   </si>
   <si>
-    <t>19:17:28</t>
-  </si>
-  <si>
-    <t>20:53:46</t>
-  </si>
-  <si>
-    <t>19:53:40</t>
-  </si>
-  <si>
-    <t>21:30:26</t>
-  </si>
-  <si>
-    <t>23:06:15</t>
+    <t>19:17:27</t>
+  </si>
+  <si>
+    <t>20:53:45</t>
+  </si>
+  <si>
+    <t>16:46:52</t>
+  </si>
+  <si>
+    <t>18:23:17</t>
+  </si>
+  <si>
+    <t>19:59:40</t>
   </si>
   <si>
     <t>18:59:49</t>
@@ -415,7 +409,7 @@
     <t>22:12:59</t>
   </si>
   <si>
-    <t>18:05:38</t>
+    <t>18:05:39</t>
   </si>
   <si>
     <t>19:43:03</t>
@@ -424,7 +418,7 @@
     <t>21:19:29</t>
   </si>
   <si>
-    <t>22:54:10</t>
+    <t>22:54:11</t>
   </si>
   <si>
     <t>18:49:09</t>
@@ -457,25 +451,25 @@
     <t>17:43:46</t>
   </si>
   <si>
-    <t>19:20:17</t>
-  </si>
-  <si>
-    <t>20:55:28</t>
-  </si>
-  <si>
-    <t>19:56:02</t>
-  </si>
-  <si>
-    <t>21:32:39</t>
-  </si>
-  <si>
-    <t>23:08:46</t>
+    <t>19:20:16</t>
+  </si>
+  <si>
+    <t>20:55:27</t>
+  </si>
+  <si>
+    <t>16:49:27</t>
+  </si>
+  <si>
+    <t>18:26:10</t>
+  </si>
+  <si>
+    <t>20:01:57</t>
   </si>
   <si>
     <t>19:02:19</t>
   </si>
   <si>
-    <t>20:39:02</t>
+    <t>20:39:03</t>
   </si>
   <si>
     <t>22:15:21</t>
@@ -484,7 +478,7 @@
     <t>18:08:28</t>
   </si>
   <si>
-    <t>19:45:18</t>
+    <t>19:45:19</t>
   </si>
   <si>
     <t>21:21:45</t>
@@ -499,7 +493,7 @@
     <t>20:28:01</t>
   </si>
   <si>
-    <t>22:03:57</t>
+    <t>22:03:58</t>
   </si>
   <si>
     <t>17:57:30</t>
@@ -520,21 +514,30 @@
     <t>20:16:30</t>
   </si>
   <si>
-    <t>17:46:03</t>
+    <t>17:46:02</t>
   </si>
   <si>
     <t>19:22:31</t>
   </si>
   <si>
-    <t>20:58:18</t>
+    <t>20:58:17</t>
+  </si>
+  <si>
+    <t>16:51:49</t>
+  </si>
+  <si>
+    <t>18:28:23</t>
+  </si>
+  <si>
+    <t>20:04:27</t>
+  </si>
+  <si>
+    <t>2°</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>2°</t>
-  </si>
-  <si>
     <t>10°</t>
   </si>
   <si>
@@ -556,6 +559,9 @@
     <t>5°</t>
   </si>
   <si>
+    <t>11°</t>
+  </si>
+  <si>
     <t>18:53:16</t>
   </si>
   <si>
@@ -571,7 +577,7 @@
     <t>19:24:29</t>
   </si>
   <si>
-    <t>17:00:18</t>
+    <t>17:00:17</t>
   </si>
   <si>
     <t>18:32:51</t>
@@ -580,7 +586,13 @@
     <t>17:41:05</t>
   </si>
   <si>
-    <t>19:13:38</t>
+    <t>19:13:37</t>
+  </si>
+  <si>
+    <t>16:49:12</t>
+  </si>
+  <si>
+    <t>18:21:44</t>
   </si>
   <si>
     <t>B</t>
@@ -629,7 +641,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -650,7 +662,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -662,7 +686,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -674,7 +698,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -686,7 +752,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -698,85 +776,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -817,7 +817,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -895,12 +895,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1382,7 +1376,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>40</v>
@@ -1391,46 +1385,46 @@
         <v>56</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-28.4</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="O2" s="6">
+        <v>100</v>
+      </c>
+      <c r="P2" s="7">
         <v>83</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-35.9</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O2" s="6">
-        <v>98</v>
-      </c>
-      <c r="P2" s="7">
-        <v>19</v>
-      </c>
       <c r="Q2" s="8">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="R2" s="9">
-        <v>2</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1447,46 +1441,46 @@
         <v>56</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L3" s="4">
-        <v>-46.6</v>
+        <v>-41.6</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="O3" s="6">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="P3" s="10">
-        <v>28</v>
-      </c>
-      <c r="Q3" s="11">
-        <v>78</v>
-      </c>
-      <c r="R3" s="12">
-        <v>3</v>
+        <v>97</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>100</v>
+      </c>
+      <c r="R3" s="11">
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1494,7 +1488,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>42</v>
@@ -1503,46 +1497,46 @@
         <v>56</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L4" s="4">
-        <v>-49.9</v>
+        <v>-49.5</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="O4" s="6">
-        <v>78</v>
-      </c>
-      <c r="P4" s="7">
-        <v>19</v>
-      </c>
-      <c r="Q4" s="13">
-        <v>67</v>
-      </c>
-      <c r="R4" s="14">
-        <v>16</v>
+        <v>100</v>
+      </c>
+      <c r="P4" s="8">
+        <v>100</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>100</v>
+      </c>
+      <c r="R4" s="8">
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1550,55 +1544,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="L5" s="4">
-        <v>-28.4</v>
+        <v>-20.4</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="O5" s="6">
-        <v>100</v>
-      </c>
-      <c r="P5" s="15">
-        <v>90</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>95</v>
-      </c>
-      <c r="R5" s="16">
-        <v>100</v>
+        <v>49</v>
+      </c>
+      <c r="P5" s="12">
+        <v>30</v>
+      </c>
+      <c r="Q5" s="13">
+        <v>38</v>
+      </c>
+      <c r="R5" s="14">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1606,55 +1600,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L6" s="4">
-        <v>-41.6</v>
+        <v>-35</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="O6" s="6">
-        <v>100</v>
-      </c>
-      <c r="P6" s="16">
-        <v>100</v>
-      </c>
-      <c r="Q6" s="16">
-        <v>100</v>
-      </c>
-      <c r="R6" s="16">
-        <v>100</v>
+        <v>49</v>
+      </c>
+      <c r="P6" s="15">
+        <v>34</v>
+      </c>
+      <c r="Q6" s="13">
+        <v>39</v>
+      </c>
+      <c r="R6" s="14">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1662,55 +1656,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L7" s="4">
-        <v>-49.5</v>
+        <v>-46.3</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="O7" s="6">
-        <v>100</v>
-      </c>
-      <c r="P7" s="8">
-        <v>97</v>
-      </c>
-      <c r="Q7" s="16">
-        <v>100</v>
-      </c>
-      <c r="R7" s="16">
-        <v>100</v>
+        <v>83</v>
+      </c>
+      <c r="P7" s="16">
+        <v>80</v>
+      </c>
+      <c r="Q7" s="17">
+        <v>18</v>
+      </c>
+      <c r="R7" s="14">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1718,55 +1712,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>173</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>181</v>
+        <v>68</v>
       </c>
       <c r="L8" s="4">
-        <v>-20.4</v>
+        <v>-50.7</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="O8" s="6">
-        <v>93</v>
-      </c>
-      <c r="P8" s="11">
-        <v>81</v>
+        <v>84</v>
+      </c>
+      <c r="P8" s="18">
+        <v>77</v>
       </c>
       <c r="Q8" s="17">
-        <v>49</v>
-      </c>
-      <c r="R8" s="18">
-        <v>44</v>
+        <v>22</v>
+      </c>
+      <c r="R8" s="14">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1774,55 +1768,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>68</v>
+        <v>184</v>
       </c>
       <c r="L9" s="4">
-        <v>-35</v>
+        <v>-27.3</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="O9" s="6">
-        <v>96</v>
-      </c>
-      <c r="P9" s="8">
-        <v>95</v>
-      </c>
-      <c r="Q9" s="18">
-        <v>47</v>
-      </c>
-      <c r="R9" s="12">
-        <v>5</v>
+        <v>100</v>
+      </c>
+      <c r="P9" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>100</v>
+      </c>
+      <c r="R9" s="9">
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1830,55 +1824,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L10" s="4">
-        <v>-46.3</v>
+        <v>-40.9</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="O10" s="6">
-        <v>94</v>
-      </c>
-      <c r="P10" s="15">
-        <v>92</v>
-      </c>
-      <c r="Q10" s="19">
-        <v>24</v>
-      </c>
-      <c r="R10" s="9">
+        <v>100</v>
+      </c>
+      <c r="P10" s="14">
         <v>0</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>100</v>
+      </c>
+      <c r="R10" s="13">
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1886,55 +1880,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L11" s="4">
-        <v>-50.7</v>
+        <v>-49.7</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="O11" s="6">
-        <v>95</v>
-      </c>
-      <c r="P11" s="8">
-        <v>95</v>
-      </c>
-      <c r="Q11" s="10">
-        <v>31</v>
-      </c>
-      <c r="R11" s="9">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="P11" s="19">
+        <v>23</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>100</v>
+      </c>
+      <c r="R11" s="15">
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1942,55 +1936,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="L12" s="4">
-        <v>-27.3</v>
+        <v>-19.3</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="O12" s="6">
-        <v>100</v>
-      </c>
-      <c r="P12" s="20">
-        <v>58</v>
-      </c>
-      <c r="Q12" s="16">
-        <v>100</v>
-      </c>
-      <c r="R12" s="21">
-        <v>53</v>
+        <v>57</v>
+      </c>
+      <c r="P12" s="11">
+        <v>57</v>
+      </c>
+      <c r="Q12" s="14">
+        <v>2</v>
+      </c>
+      <c r="R12" s="14">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1998,55 +1992,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="L13" s="4">
-        <v>-40.9</v>
+        <v>-33.9</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O13" s="6">
-        <v>100</v>
-      </c>
-      <c r="P13" s="12">
-        <v>5</v>
-      </c>
-      <c r="Q13" s="16">
-        <v>100</v>
-      </c>
-      <c r="R13" s="7">
-        <v>21</v>
+        <v>195</v>
+      </c>
+      <c r="O13" s="20">
+        <v>6</v>
+      </c>
+      <c r="P13" s="21">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="21">
+        <v>4</v>
+      </c>
+      <c r="R13" s="14">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2054,55 +2048,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L14" s="4">
-        <v>-49.7</v>
+        <v>-46</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O14" s="6">
-        <v>100</v>
-      </c>
-      <c r="P14" s="12">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="16">
-        <v>100</v>
-      </c>
-      <c r="R14" s="12">
-        <v>6</v>
+        <v>195</v>
+      </c>
+      <c r="O14" s="20">
+        <v>1</v>
+      </c>
+      <c r="P14" s="14">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="14">
+        <v>0</v>
+      </c>
+      <c r="R14" s="14">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2110,55 +2104,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="L15" s="4">
-        <v>-19.3</v>
+        <v>-11.1</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O15" s="22">
-        <v>22</v>
-      </c>
-      <c r="P15" s="7">
-        <v>18</v>
+        <v>197</v>
+      </c>
+      <c r="O15" s="6">
+        <v>68</v>
+      </c>
+      <c r="P15" s="22">
+        <v>68</v>
       </c>
       <c r="Q15" s="9">
-        <v>1</v>
-      </c>
-      <c r="R15" s="12">
-        <v>3</v>
+        <v>46</v>
+      </c>
+      <c r="R15" s="14">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2166,55 +2160,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="L16" s="4">
-        <v>-33.9</v>
+        <v>-26.2</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O16" s="23">
-        <v>8</v>
-      </c>
-      <c r="P16" s="12">
-        <v>6</v>
+        <v>197</v>
+      </c>
+      <c r="O16" s="6">
+        <v>69</v>
+      </c>
+      <c r="P16" s="23">
+        <v>63</v>
       </c>
       <c r="Q16" s="9">
-        <v>1</v>
-      </c>
-      <c r="R16" s="9">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="R16" s="15">
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2222,55 +2216,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L17" s="4">
-        <v>-46</v>
+        <v>-40.1</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O17" s="22">
-        <v>30</v>
-      </c>
-      <c r="P17" s="10">
-        <v>30</v>
-      </c>
-      <c r="Q17" s="9">
-        <v>1</v>
-      </c>
-      <c r="R17" s="12">
-        <v>4</v>
+        <v>195</v>
+      </c>
+      <c r="O17" s="6">
+        <v>75</v>
+      </c>
+      <c r="P17" s="18">
+        <v>73</v>
+      </c>
+      <c r="Q17" s="24">
+        <v>49</v>
+      </c>
+      <c r="R17" s="19">
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2278,55 +2272,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="L18" s="4">
-        <v>-11.1</v>
+        <v>-18</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="O18" s="6">
-        <v>100</v>
-      </c>
-      <c r="P18" s="21">
-        <v>54</v>
-      </c>
-      <c r="Q18" s="24">
-        <v>83</v>
-      </c>
-      <c r="R18" s="19">
-        <v>25</v>
+        <v>81</v>
+      </c>
+      <c r="P18" s="17">
+        <v>20</v>
+      </c>
+      <c r="Q18" s="9">
+        <v>45</v>
+      </c>
+      <c r="R18" s="21">
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2334,55 +2328,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="L19" s="4">
-        <v>-26.2</v>
+        <v>-32.8</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O19" s="6">
-        <v>100</v>
-      </c>
-      <c r="P19" s="16">
-        <v>100</v>
-      </c>
-      <c r="Q19" s="16">
-        <v>100</v>
-      </c>
-      <c r="R19" s="14">
-        <v>15</v>
+        <v>94</v>
+      </c>
+      <c r="P19" s="25">
+        <v>14</v>
+      </c>
+      <c r="Q19" s="24">
+        <v>49</v>
+      </c>
+      <c r="R19" s="21">
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2390,55 +2384,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L20" s="4">
-        <v>-40.1</v>
+        <v>-45.4</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="O20" s="6">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="P20" s="25">
-        <v>76</v>
-      </c>
-      <c r="Q20" s="25">
-        <v>73</v>
-      </c>
-      <c r="R20" s="12">
-        <v>5</v>
+        <v>17</v>
+      </c>
+      <c r="Q20" s="11">
+        <v>57</v>
+      </c>
+      <c r="R20" s="21">
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2446,55 +2440,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="L21" s="4">
-        <v>-18</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="O21" s="6">
-        <v>95</v>
-      </c>
-      <c r="P21" s="10">
-        <v>28</v>
-      </c>
-      <c r="Q21" s="26">
-        <v>68</v>
-      </c>
-      <c r="R21" s="13">
-        <v>65</v>
+        <v>79</v>
+      </c>
+      <c r="P21" s="15">
+        <v>34</v>
+      </c>
+      <c r="Q21" s="25">
+        <v>13</v>
+      </c>
+      <c r="R21" s="21">
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2502,55 +2496,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="L22" s="4">
-        <v>-32.8</v>
+        <v>-24.9</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="O22" s="6">
-        <v>80</v>
-      </c>
-      <c r="P22" s="7">
-        <v>21</v>
-      </c>
-      <c r="Q22" s="26">
-        <v>70</v>
-      </c>
-      <c r="R22" s="27">
-        <v>35</v>
+        <v>74</v>
+      </c>
+      <c r="P22" s="26">
+        <v>58</v>
+      </c>
+      <c r="Q22" s="14">
+        <v>0</v>
+      </c>
+      <c r="R22" s="21">
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2558,55 +2552,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L23" s="4">
-        <v>-45.4</v>
+        <v>-39.2</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="O23" s="6">
-        <v>67</v>
-      </c>
-      <c r="P23" s="28">
-        <v>12</v>
-      </c>
-      <c r="Q23" s="20">
-        <v>59</v>
-      </c>
-      <c r="R23" s="14">
-        <v>17</v>
+        <v>51</v>
+      </c>
+      <c r="P23" s="13">
+        <v>39</v>
+      </c>
+      <c r="Q23" s="14">
+        <v>0</v>
+      </c>
+      <c r="R23" s="25">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="188">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261021--01</t>
-  </si>
-  <si>
-    <t>20261021--02</t>
-  </si>
-  <si>
-    <t>20261021--03</t>
-  </si>
-  <si>
     <t>20261022--01</t>
   </si>
   <si>
@@ -133,61 +124,64 @@
     <t>20261027--02</t>
   </si>
   <si>
-    <t>20261027--03</t>
+    <t>20261028--01</t>
+  </si>
+  <si>
+    <t>20261028--02</t>
+  </si>
+  <si>
+    <t>03:26</t>
+  </si>
+  <si>
+    <t>05:38</t>
+  </si>
+  <si>
+    <t>05:31</t>
+  </si>
+  <si>
+    <t>02:22</t>
+  </si>
+  <si>
+    <t>05:22</t>
+  </si>
+  <si>
+    <t>05:41</t>
+  </si>
+  <si>
+    <t>04:03</t>
+  </si>
+  <si>
+    <t>04:55</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>04:53</t>
+  </si>
+  <si>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>05:42</t>
+  </si>
+  <si>
+    <t>05:37</t>
+  </si>
+  <si>
+    <t>05:10</t>
   </si>
   <si>
     <t>04:34</t>
   </si>
   <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>05:10</t>
-  </si>
-  <si>
-    <t>03:27</t>
-  </si>
-  <si>
-    <t>05:37</t>
-  </si>
-  <si>
-    <t>05:31</t>
-  </si>
-  <si>
-    <t>02:23</t>
-  </si>
-  <si>
-    <t>05:22</t>
-  </si>
-  <si>
-    <t>05:42</t>
-  </si>
-  <si>
-    <t>04:04</t>
-  </si>
-  <si>
-    <t>04:55</t>
-  </si>
-  <si>
-    <t>04:54</t>
-  </si>
-  <si>
-    <t>04:06</t>
-  </si>
-  <si>
-    <t>05:32</t>
-  </si>
-  <si>
-    <t>05:38</t>
-  </si>
-  <si>
-    <t>03:25</t>
+    <t>05:11</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:45</t>
+    <t>01:46</t>
   </si>
   <si>
     <t>03:37</t>
@@ -199,148 +193,130 @@
     <t>02:51</t>
   </si>
   <si>
-    <t>01:19</t>
-  </si>
-  <si>
-    <t>18:52:45</t>
-  </si>
-  <si>
-    <t>20:28:51</t>
-  </si>
-  <si>
-    <t>22:05:28</t>
-  </si>
-  <si>
-    <t>17:59:23</t>
-  </si>
-  <si>
-    <t>19:35:11</t>
-  </si>
-  <si>
-    <t>21:11:41</t>
+    <t>04:56</t>
+  </si>
+  <si>
+    <t>03:36</t>
+  </si>
+  <si>
+    <t>17:59:22</t>
+  </si>
+  <si>
+    <t>19:35:10</t>
+  </si>
+  <si>
+    <t>21:11:40</t>
   </si>
   <si>
     <t>22:48:36</t>
   </si>
   <si>
-    <t>18:41:28</t>
-  </si>
-  <si>
-    <t>20:17:51</t>
-  </si>
-  <si>
-    <t>21:54:37</t>
-  </si>
-  <si>
-    <t>17:47:45</t>
-  </si>
-  <si>
-    <t>19:23:57</t>
-  </si>
-  <si>
-    <t>21:00:35</t>
-  </si>
-  <si>
-    <t>16:54:02</t>
-  </si>
-  <si>
-    <t>18:29:59</t>
-  </si>
-  <si>
-    <t>20:06:31</t>
-  </si>
-  <si>
-    <t>17:35:58</t>
-  </si>
-  <si>
-    <t>19:12:23</t>
-  </si>
-  <si>
-    <t>20:49:12</t>
-  </si>
-  <si>
-    <t>16:41:56</t>
-  </si>
-  <si>
-    <t>18:18:12</t>
-  </si>
-  <si>
-    <t>19:54:52</t>
-  </si>
-  <si>
-    <t>18:55:15</t>
-  </si>
-  <si>
-    <t>20:31:04</t>
-  </si>
-  <si>
-    <t>22:07:49</t>
+    <t>18:41:26</t>
+  </si>
+  <si>
+    <t>20:17:49</t>
+  </si>
+  <si>
+    <t>21:54:34</t>
+  </si>
+  <si>
+    <t>17:47:41</t>
+  </si>
+  <si>
+    <t>19:23:52</t>
+  </si>
+  <si>
+    <t>21:00:31</t>
+  </si>
+  <si>
+    <t>16:53:55</t>
+  </si>
+  <si>
+    <t>18:29:51</t>
+  </si>
+  <si>
+    <t>20:06:23</t>
+  </si>
+  <si>
+    <t>17:35:47</t>
+  </si>
+  <si>
+    <t>19:12:12</t>
+  </si>
+  <si>
+    <t>20:49:00</t>
+  </si>
+  <si>
+    <t>16:41:40</t>
+  </si>
+  <si>
+    <t>19:54:36</t>
+  </si>
+  <si>
+    <t>17:23:35</t>
+  </si>
+  <si>
+    <t>19:00:09</t>
   </si>
   <si>
     <t>18:02:12</t>
   </si>
   <si>
-    <t>19:37:26</t>
-  </si>
-  <si>
-    <t>21:13:58</t>
-  </si>
-  <si>
-    <t>22:51:48</t>
-  </si>
-  <si>
-    <t>18:43:47</t>
-  </si>
-  <si>
-    <t>20:20:05</t>
-  </si>
-  <si>
-    <t>21:57:15</t>
-  </si>
-  <si>
-    <t>17:50:10</t>
-  </si>
-  <si>
-    <t>19:26:10</t>
-  </si>
-  <si>
-    <t>21:03:01</t>
-  </si>
-  <si>
-    <t>16:56:40</t>
-  </si>
-  <si>
-    <t>18:32:13</t>
-  </si>
-  <si>
-    <t>20:08:50</t>
-  </si>
-  <si>
-    <t>17:38:14</t>
-  </si>
-  <si>
-    <t>19:14:38</t>
-  </si>
-  <si>
-    <t>20:52:02</t>
-  </si>
-  <si>
-    <t>16:44:17</t>
-  </si>
-  <si>
-    <t>18:20:25</t>
-  </si>
-  <si>
-    <t>19:57:23</t>
-  </si>
-  <si>
-    <t>18:57:32</t>
-  </si>
-  <si>
-    <t>20:33:56</t>
-  </si>
-  <si>
-    <t>22:10:24</t>
+    <t>19:37:25</t>
+  </si>
+  <si>
+    <t>21:13:57</t>
+  </si>
+  <si>
+    <t>22:51:47</t>
+  </si>
+  <si>
+    <t>18:43:45</t>
+  </si>
+  <si>
+    <t>20:20:03</t>
+  </si>
+  <si>
+    <t>21:57:13</t>
+  </si>
+  <si>
+    <t>17:50:05</t>
+  </si>
+  <si>
+    <t>19:26:05</t>
+  </si>
+  <si>
+    <t>21:02:56</t>
+  </si>
+  <si>
+    <t>16:56:33</t>
+  </si>
+  <si>
+    <t>18:32:05</t>
+  </si>
+  <si>
+    <t>20:08:42</t>
+  </si>
+  <si>
+    <t>17:38:03</t>
+  </si>
+  <si>
+    <t>19:14:27</t>
+  </si>
+  <si>
+    <t>20:51:50</t>
+  </si>
+  <si>
+    <t>16:44:01</t>
+  </si>
+  <si>
+    <t>19:57:06</t>
+  </si>
+  <si>
+    <t>17:25:48</t>
+  </si>
+  <si>
+    <t>19:02:30</t>
   </si>
   <si>
     <t>18:03:55</t>
@@ -349,204 +325,195 @@
     <t>19:40:14</t>
   </si>
   <si>
-    <t>21:16:43</t>
-  </si>
-  <si>
-    <t>22:52:59</t>
-  </si>
-  <si>
-    <t>18:46:28</t>
-  </si>
-  <si>
-    <t>20:22:56</t>
-  </si>
-  <si>
-    <t>21:59:17</t>
-  </si>
-  <si>
-    <t>17:52:37</t>
-  </si>
-  <si>
-    <t>19:29:03</t>
-  </si>
-  <si>
-    <t>21:05:28</t>
-  </si>
-  <si>
-    <t>16:58:43</t>
-  </si>
-  <si>
-    <t>18:35:04</t>
-  </si>
-  <si>
-    <t>20:11:31</t>
-  </si>
-  <si>
-    <t>17:41:00</t>
-  </si>
-  <si>
-    <t>19:17:27</t>
-  </si>
-  <si>
-    <t>20:53:45</t>
-  </si>
-  <si>
-    <t>16:46:52</t>
-  </si>
-  <si>
-    <t>18:23:17</t>
-  </si>
-  <si>
-    <t>19:59:40</t>
-  </si>
-  <si>
-    <t>18:59:49</t>
-  </si>
-  <si>
-    <t>20:36:49</t>
-  </si>
-  <si>
-    <t>22:12:59</t>
-  </si>
-  <si>
-    <t>18:05:39</t>
+    <t>21:16:42</t>
+  </si>
+  <si>
+    <t>22:52:58</t>
+  </si>
+  <si>
+    <t>18:46:26</t>
+  </si>
+  <si>
+    <t>20:22:53</t>
+  </si>
+  <si>
+    <t>21:59:14</t>
+  </si>
+  <si>
+    <t>17:52:33</t>
+  </si>
+  <si>
+    <t>19:28:58</t>
+  </si>
+  <si>
+    <t>21:05:23</t>
+  </si>
+  <si>
+    <t>16:58:35</t>
+  </si>
+  <si>
+    <t>18:34:56</t>
+  </si>
+  <si>
+    <t>20:11:23</t>
+  </si>
+  <si>
+    <t>17:40:48</t>
+  </si>
+  <si>
+    <t>19:17:15</t>
+  </si>
+  <si>
+    <t>20:53:33</t>
+  </si>
+  <si>
+    <t>16:46:36</t>
+  </si>
+  <si>
+    <t>19:59:23</t>
+  </si>
+  <si>
+    <t>17:28:41</t>
+  </si>
+  <si>
+    <t>19:05:06</t>
+  </si>
+  <si>
+    <t>18:05:38</t>
   </si>
   <si>
     <t>19:43:03</t>
   </si>
   <si>
-    <t>21:19:29</t>
-  </si>
-  <si>
-    <t>22:54:11</t>
-  </si>
-  <si>
-    <t>18:49:09</t>
-  </si>
-  <si>
-    <t>20:25:47</t>
-  </si>
-  <si>
-    <t>22:01:19</t>
-  </si>
-  <si>
-    <t>17:55:05</t>
-  </si>
-  <si>
-    <t>19:31:55</t>
-  </si>
-  <si>
-    <t>21:07:55</t>
-  </si>
-  <si>
-    <t>17:00:46</t>
-  </si>
-  <si>
-    <t>18:37:55</t>
-  </si>
-  <si>
-    <t>20:14:12</t>
-  </si>
-  <si>
-    <t>17:43:46</t>
-  </si>
-  <si>
-    <t>19:20:16</t>
-  </si>
-  <si>
-    <t>20:55:27</t>
-  </si>
-  <si>
-    <t>16:49:27</t>
-  </si>
-  <si>
-    <t>18:26:10</t>
-  </si>
-  <si>
-    <t>20:01:57</t>
-  </si>
-  <si>
-    <t>19:02:19</t>
-  </si>
-  <si>
-    <t>20:39:03</t>
-  </si>
-  <si>
-    <t>22:15:21</t>
+    <t>21:19:28</t>
+  </si>
+  <si>
+    <t>22:54:09</t>
+  </si>
+  <si>
+    <t>18:49:07</t>
+  </si>
+  <si>
+    <t>20:25:44</t>
+  </si>
+  <si>
+    <t>22:01:16</t>
+  </si>
+  <si>
+    <t>17:55:00</t>
+  </si>
+  <si>
+    <t>19:31:50</t>
+  </si>
+  <si>
+    <t>21:07:49</t>
+  </si>
+  <si>
+    <t>17:00:38</t>
+  </si>
+  <si>
+    <t>18:37:47</t>
+  </si>
+  <si>
+    <t>20:14:04</t>
+  </si>
+  <si>
+    <t>17:43:34</t>
+  </si>
+  <si>
+    <t>19:20:04</t>
+  </si>
+  <si>
+    <t>20:55:16</t>
+  </si>
+  <si>
+    <t>16:49:11</t>
+  </si>
+  <si>
+    <t>20:01:40</t>
+  </si>
+  <si>
+    <t>17:31:33</t>
+  </si>
+  <si>
+    <t>19:07:41</t>
   </si>
   <si>
     <t>18:08:28</t>
   </si>
   <si>
-    <t>19:45:19</t>
-  </si>
-  <si>
-    <t>21:21:45</t>
-  </si>
-  <si>
-    <t>22:57:22</t>
-  </si>
-  <si>
-    <t>18:51:28</t>
-  </si>
-  <si>
-    <t>20:28:01</t>
-  </si>
-  <si>
-    <t>22:03:58</t>
-  </si>
-  <si>
-    <t>17:57:30</t>
-  </si>
-  <si>
-    <t>19:34:09</t>
-  </si>
-  <si>
-    <t>21:10:20</t>
-  </si>
-  <si>
-    <t>17:03:24</t>
-  </si>
-  <si>
-    <t>18:40:09</t>
-  </si>
-  <si>
-    <t>20:16:30</t>
-  </si>
-  <si>
-    <t>17:46:02</t>
-  </si>
-  <si>
-    <t>19:22:31</t>
-  </si>
-  <si>
-    <t>20:58:17</t>
-  </si>
-  <si>
-    <t>16:51:49</t>
-  </si>
-  <si>
-    <t>18:28:23</t>
-  </si>
-  <si>
-    <t>20:04:27</t>
+    <t>19:45:18</t>
+  </si>
+  <si>
+    <t>21:21:44</t>
+  </si>
+  <si>
+    <t>22:57:21</t>
+  </si>
+  <si>
+    <t>18:51:25</t>
+  </si>
+  <si>
+    <t>20:27:58</t>
+  </si>
+  <si>
+    <t>22:03:55</t>
+  </si>
+  <si>
+    <t>17:57:25</t>
+  </si>
+  <si>
+    <t>19:34:04</t>
+  </si>
+  <si>
+    <t>21:10:14</t>
+  </si>
+  <si>
+    <t>17:03:16</t>
+  </si>
+  <si>
+    <t>18:40:01</t>
+  </si>
+  <si>
+    <t>20:16:22</t>
+  </si>
+  <si>
+    <t>17:45:51</t>
+  </si>
+  <si>
+    <t>19:22:19</t>
+  </si>
+  <si>
+    <t>20:58:05</t>
+  </si>
+  <si>
+    <t>16:51:32</t>
+  </si>
+  <si>
+    <t>20:04:10</t>
+  </si>
+  <si>
+    <t>17:33:46</t>
+  </si>
+  <si>
+    <t>19:10:02</t>
+  </si>
+  <si>
+    <t>10°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>8°</t>
+  </si>
+  <si>
+    <t>19°</t>
   </si>
   <si>
     <t>2°</t>
   </si>
   <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>10°</t>
-  </si>
-  <si>
-    <t>8°</t>
-  </si>
-  <si>
-    <t>19°</t>
-  </si>
-  <si>
     <t>12°</t>
   </si>
   <si>
@@ -562,37 +529,40 @@
     <t>11°</t>
   </si>
   <si>
-    <t>18:53:16</t>
-  </si>
-  <si>
-    <t>18:02:08</t>
-  </si>
-  <si>
-    <t>18:43:24</t>
-  </si>
-  <si>
-    <t>17:51:55</t>
-  </si>
-  <si>
-    <t>19:24:29</t>
-  </si>
-  <si>
-    <t>17:00:17</t>
-  </si>
-  <si>
-    <t>18:32:51</t>
-  </si>
-  <si>
-    <t>17:41:05</t>
-  </si>
-  <si>
-    <t>19:13:37</t>
-  </si>
-  <si>
-    <t>16:49:12</t>
-  </si>
-  <si>
-    <t>18:21:44</t>
+    <t>7°</t>
+  </si>
+  <si>
+    <t>18:02:07</t>
+  </si>
+  <si>
+    <t>18:43:22</t>
+  </si>
+  <si>
+    <t>17:51:51</t>
+  </si>
+  <si>
+    <t>19:24:24</t>
+  </si>
+  <si>
+    <t>17:00:10</t>
+  </si>
+  <si>
+    <t>18:32:43</t>
+  </si>
+  <si>
+    <t>17:40:54</t>
+  </si>
+  <si>
+    <t>19:13:26</t>
+  </si>
+  <si>
+    <t>16:48:57</t>
+  </si>
+  <si>
+    <t>17:29:24</t>
+  </si>
+  <si>
+    <t>19:01:56</t>
   </si>
   <si>
     <t>B</t>
@@ -601,10 +571,10 @@
     <t>A+B</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
   <si>
     <t>2</t>
@@ -641,7 +611,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -656,43 +626,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -710,13 +650,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -728,31 +710,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -764,19 +746,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -817,7 +793,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -895,6 +871,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1298,15 +1277,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" style="3" customWidth="1"/>
     <col min="4" max="4" width="16.5703125" style="1" customWidth="1"/>
-    <col min="5" max="8" width="14.28515625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" customWidth="1"/>
+    <col min="5" max="8" width="14.140625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" style="1" customWidth="1"/>
     <col min="10" max="10" width="13.28515625" style="3" customWidth="1"/>
     <col min="11" max="11" width="8.7109375" style="1" customWidth="1"/>
     <col min="12" max="12" width="12.7109375" style="4" customWidth="1"/>
@@ -1376,55 +1355,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-20.4</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="O2" s="6">
+        <v>44</v>
+      </c>
+      <c r="P2" s="7">
+        <v>5</v>
+      </c>
+      <c r="Q2" s="8">
         <v>40</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-28.4</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O2" s="6">
-        <v>100</v>
-      </c>
-      <c r="P2" s="7">
-        <v>83</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>99</v>
-      </c>
       <c r="R2" s="9">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1432,55 +1411,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L3" s="4">
-        <v>-41.6</v>
+        <v>-35</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="O3" s="6">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="P3" s="10">
-        <v>97</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>100</v>
-      </c>
-      <c r="R3" s="11">
-        <v>55</v>
+        <v>26</v>
+      </c>
+      <c r="Q3" s="11">
+        <v>33</v>
+      </c>
+      <c r="R3" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1488,55 +1467,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-46.3</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="O4" s="12">
+        <v>52</v>
+      </c>
+      <c r="P4" s="13">
+        <v>43</v>
+      </c>
+      <c r="Q4" s="8">
         <v>42</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-49.5</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O4" s="6">
-        <v>100</v>
-      </c>
-      <c r="P4" s="8">
-        <v>100</v>
-      </c>
-      <c r="Q4" s="8">
-        <v>100</v>
-      </c>
-      <c r="R4" s="8">
-        <v>100</v>
+      <c r="R4" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1544,54 +1523,54 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="K5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-50.7</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="L5" s="4">
-        <v>-20.4</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>193</v>
-      </c>
       <c r="N5" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O5" s="6">
-        <v>49</v>
-      </c>
-      <c r="P5" s="12">
-        <v>30</v>
-      </c>
-      <c r="Q5" s="13">
-        <v>38</v>
-      </c>
-      <c r="R5" s="14">
+        <v>185</v>
+      </c>
+      <c r="O5" s="12">
+        <v>77</v>
+      </c>
+      <c r="P5" s="11">
+        <v>34</v>
+      </c>
+      <c r="Q5" s="14">
+        <v>68</v>
+      </c>
+      <c r="R5" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1600,55 +1579,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="J6" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="L6" s="4">
-        <v>-35</v>
+        <v>-27.3</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O6" s="6">
-        <v>49</v>
+        <v>186</v>
+      </c>
+      <c r="O6" s="12">
+        <v>100</v>
       </c>
       <c r="P6" s="15">
-        <v>34</v>
-      </c>
-      <c r="Q6" s="13">
-        <v>39</v>
-      </c>
-      <c r="R6" s="14">
-        <v>0</v>
+        <v>61</v>
+      </c>
+      <c r="Q6" s="16">
+        <v>100</v>
+      </c>
+      <c r="R6" s="16">
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1656,55 +1635,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L7" s="4">
-        <v>-46.3</v>
+        <v>-40.9</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O7" s="6">
-        <v>83</v>
-      </c>
-      <c r="P7" s="16">
-        <v>80</v>
-      </c>
-      <c r="Q7" s="17">
-        <v>18</v>
-      </c>
-      <c r="R7" s="14">
-        <v>0</v>
+        <v>186</v>
+      </c>
+      <c r="O7" s="12">
+        <v>100</v>
+      </c>
+      <c r="P7" s="17">
+        <v>15</v>
+      </c>
+      <c r="Q7" s="16">
+        <v>100</v>
+      </c>
+      <c r="R7" s="18">
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1712,55 +1691,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L8" s="4">
-        <v>-50.7</v>
+        <v>-49.7</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O8" s="6">
-        <v>84</v>
-      </c>
-      <c r="P8" s="18">
-        <v>77</v>
-      </c>
-      <c r="Q8" s="17">
-        <v>22</v>
-      </c>
-      <c r="R8" s="14">
-        <v>0</v>
+        <v>186</v>
+      </c>
+      <c r="O8" s="12">
+        <v>100</v>
+      </c>
+      <c r="P8" s="19">
+        <v>18</v>
+      </c>
+      <c r="Q8" s="20">
+        <v>94</v>
+      </c>
+      <c r="R8" s="16">
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1768,55 +1747,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="K9" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="L9" s="4">
+        <v>-19.3</v>
+      </c>
+      <c r="M9" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="L9" s="4">
-        <v>-27.3</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>193</v>
-      </c>
       <c r="N9" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O9" s="6">
-        <v>100</v>
-      </c>
-      <c r="P9" s="14">
+        <v>187</v>
+      </c>
+      <c r="O9" s="12">
+        <v>87</v>
+      </c>
+      <c r="P9" s="21">
+        <v>85</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>26</v>
+      </c>
+      <c r="R9" s="9">
         <v>0</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>100</v>
-      </c>
-      <c r="R9" s="9">
-        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1824,55 +1803,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="L10" s="4">
+        <v>-33.9</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="O10" s="12">
         <v>56</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="L10" s="4">
-        <v>-40.9</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O10" s="6">
-        <v>100</v>
-      </c>
-      <c r="P10" s="14">
+      <c r="P10" s="22">
+        <v>55</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>3</v>
+      </c>
+      <c r="R10" s="9">
         <v>0</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>100</v>
-      </c>
-      <c r="R10" s="13">
-        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1880,55 +1859,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L11" s="4">
-        <v>-49.7</v>
+        <v>-46</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="O11" s="6">
-        <v>100</v>
-      </c>
-      <c r="P11" s="19">
-        <v>23</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>100</v>
-      </c>
-      <c r="R11" s="15">
-        <v>35</v>
+        <v>24</v>
+      </c>
+      <c r="P11" s="17">
+        <v>17</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>0</v>
+      </c>
+      <c r="R11" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1936,55 +1915,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="J12" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>185</v>
-      </c>
       <c r="L12" s="4">
-        <v>-19.3</v>
+        <v>-11.1</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O12" s="6">
-        <v>57</v>
-      </c>
-      <c r="P12" s="11">
-        <v>57</v>
-      </c>
-      <c r="Q12" s="14">
-        <v>2</v>
-      </c>
-      <c r="R12" s="14">
-        <v>0</v>
+        <v>187</v>
+      </c>
+      <c r="O12" s="12">
+        <v>77</v>
+      </c>
+      <c r="P12" s="23">
+        <v>77</v>
+      </c>
+      <c r="Q12" s="18">
+        <v>49</v>
+      </c>
+      <c r="R12" s="24">
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1992,55 +1971,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="L13" s="4">
-        <v>-33.9</v>
+        <v>-26.2</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O13" s="20">
-        <v>6</v>
-      </c>
-      <c r="P13" s="21">
-        <v>3</v>
-      </c>
-      <c r="Q13" s="21">
-        <v>4</v>
-      </c>
-      <c r="R13" s="14">
-        <v>0</v>
+        <v>187</v>
+      </c>
+      <c r="O13" s="12">
+        <v>66</v>
+      </c>
+      <c r="P13" s="25">
+        <v>66</v>
+      </c>
+      <c r="Q13" s="22">
+        <v>54</v>
+      </c>
+      <c r="R13" s="10">
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2048,54 +2027,54 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="I14" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="K14" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L14" s="4">
-        <v>-46</v>
+        <v>-40.1</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O14" s="20">
-        <v>1</v>
+        <v>186</v>
+      </c>
+      <c r="O14" s="12">
+        <v>85</v>
       </c>
       <c r="P14" s="14">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="14">
-        <v>0</v>
-      </c>
-      <c r="R14" s="14">
+        <v>69</v>
+      </c>
+      <c r="Q14" s="21">
+        <v>84</v>
+      </c>
+      <c r="R14" s="9">
         <v>0</v>
       </c>
     </row>
@@ -2104,55 +2083,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="K15" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="L15" s="4">
+        <v>-18</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="N15" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="L15" s="4">
-        <v>-11.1</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O15" s="6">
-        <v>68</v>
-      </c>
-      <c r="P15" s="22">
-        <v>68</v>
-      </c>
-      <c r="Q15" s="9">
-        <v>46</v>
-      </c>
-      <c r="R15" s="14">
-        <v>0</v>
+      <c r="O15" s="12">
+        <v>94</v>
+      </c>
+      <c r="P15" s="26">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="22">
+        <v>55</v>
+      </c>
+      <c r="R15" s="25">
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2160,55 +2139,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="L16" s="4">
-        <v>-26.2</v>
+        <v>-32.8</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O16" s="6">
-        <v>69</v>
-      </c>
-      <c r="P16" s="23">
-        <v>63</v>
-      </c>
-      <c r="Q16" s="9">
-        <v>43</v>
-      </c>
-      <c r="R16" s="15">
-        <v>35</v>
+        <v>186</v>
+      </c>
+      <c r="O16" s="12">
+        <v>99</v>
+      </c>
+      <c r="P16" s="26">
+        <v>9</v>
+      </c>
+      <c r="Q16" s="24">
+        <v>32</v>
+      </c>
+      <c r="R16" s="23">
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2216,55 +2195,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F17" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L17" s="4">
+        <v>-45.4</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="O17" s="12">
         <v>99</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="L17" s="4">
-        <v>-40.1</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O17" s="6">
-        <v>75</v>
-      </c>
-      <c r="P17" s="18">
-        <v>73</v>
-      </c>
-      <c r="Q17" s="24">
-        <v>49</v>
-      </c>
-      <c r="R17" s="19">
-        <v>25</v>
+      <c r="P17" s="7">
+        <v>6</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>40</v>
+      </c>
+      <c r="R17" s="25">
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2272,55 +2251,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="L18" s="4">
-        <v>-18</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O18" s="6">
-        <v>81</v>
-      </c>
-      <c r="P18" s="17">
-        <v>20</v>
+        <v>187</v>
+      </c>
+      <c r="O18" s="12">
+        <v>59</v>
+      </c>
+      <c r="P18" s="26">
+        <v>8</v>
       </c>
       <c r="Q18" s="9">
-        <v>45</v>
-      </c>
-      <c r="R18" s="21">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="R18" s="15">
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2328,55 +2307,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="E19" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="L19" s="4">
-        <v>-32.8</v>
+        <v>-39.1</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O19" s="6">
-        <v>94</v>
-      </c>
-      <c r="P19" s="25">
-        <v>14</v>
-      </c>
-      <c r="Q19" s="24">
-        <v>49</v>
-      </c>
-      <c r="R19" s="21">
-        <v>6</v>
+        <v>186</v>
+      </c>
+      <c r="O19" s="12">
+        <v>95</v>
+      </c>
+      <c r="P19" s="17">
+        <v>16</v>
+      </c>
+      <c r="Q19" s="26">
+        <v>12</v>
+      </c>
+      <c r="R19" s="14">
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2384,55 +2363,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I20" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="K20" s="1" t="s">
-        <v>80</v>
+        <v>181</v>
       </c>
       <c r="L20" s="4">
-        <v>-45.4</v>
+        <v>-16.6</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O20" s="6">
-        <v>98</v>
-      </c>
-      <c r="P20" s="25">
-        <v>17</v>
-      </c>
-      <c r="Q20" s="11">
-        <v>57</v>
-      </c>
-      <c r="R20" s="21">
-        <v>4</v>
+        <v>187</v>
+      </c>
+      <c r="O20" s="27">
+        <v>12</v>
+      </c>
+      <c r="P20" s="26">
+        <v>12</v>
+      </c>
+      <c r="Q20" s="9">
+        <v>0</v>
+      </c>
+      <c r="R20" s="26">
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2443,223 +2422,56 @@
         <v>22</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="L21" s="4">
-        <v>-9.800000000000001</v>
+        <v>-31.6</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="O21" s="6">
-        <v>79</v>
-      </c>
-      <c r="P21" s="15">
-        <v>34</v>
-      </c>
-      <c r="Q21" s="25">
-        <v>13</v>
-      </c>
-      <c r="R21" s="21">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:18">
-      <c r="A22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="2">
-        <v>29</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="L22" s="4">
-        <v>-24.9</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O22" s="6">
-        <v>74</v>
-      </c>
-      <c r="P22" s="26">
-        <v>58</v>
-      </c>
-      <c r="Q22" s="14">
-        <v>0</v>
-      </c>
-      <c r="R22" s="21">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18">
-      <c r="A23" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="2">
-        <v>18</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="L23" s="4">
-        <v>-39.2</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O23" s="6">
-        <v>51</v>
-      </c>
-      <c r="P23" s="13">
-        <v>39</v>
-      </c>
-      <c r="Q23" s="14">
-        <v>0</v>
-      </c>
-      <c r="R23" s="25">
-        <v>15</v>
+      <c r="P21" s="7">
+        <v>7</v>
+      </c>
+      <c r="Q21" s="9">
+        <v>1</v>
+      </c>
+      <c r="R21" s="7">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A23">
-    <cfRule type="expression" dxfId="8" priority="9">
-      <formula>RIGHT($A2,4)="--01"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B23">
-    <cfRule type="expression" dxfId="9" priority="10">
-      <formula>RIGHT($A2,4)="--01"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C23">
-    <cfRule type="expression" dxfId="9" priority="11">
-      <formula>RIGHT($A2,4)="--01"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D23">
-    <cfRule type="expression" dxfId="8" priority="12">
-      <formula>RIGHT($A2,4)="--01"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E23">
-    <cfRule type="expression" dxfId="9" priority="13">
-      <formula>RIGHT($A2,4)="--01"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F23">
-    <cfRule type="expression" dxfId="9" priority="14">
-      <formula>RIGHT($A2,4)="--01"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G23">
-    <cfRule type="expression" dxfId="9" priority="15">
-      <formula>RIGHT($A2,4)="--01"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H23">
-    <cfRule type="expression" dxfId="9" priority="16">
-      <formula>RIGHT($A2,4)="--01"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I23">
-    <cfRule type="expression" dxfId="8" priority="17">
-      <formula>RIGHT($A2,4)="--01"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J23">
-    <cfRule type="expression" dxfId="9" priority="18">
-      <formula>RIGHT($A2,4)="--01"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K23">
-    <cfRule type="expression" dxfId="8" priority="19">
-      <formula>RIGHT($A2,4)="--01"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L23">
+  <conditionalFormatting sqref="L2:L21">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2678,12 +2490,7 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M23">
-    <cfRule type="expression" dxfId="9" priority="21">
-      <formula>RIGHT($A2,4)="--01"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N23">
+  <conditionalFormatting sqref="N2:N21">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2700,22 +2507,82 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O23">
+  <conditionalFormatting sqref="A2:A21">
+    <cfRule type="expression" dxfId="8" priority="9">
+      <formula>RIGHT($A2,4)="--01"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B21">
+    <cfRule type="expression" dxfId="9" priority="10">
+      <formula>RIGHT($A2,4)="--01"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C21">
+    <cfRule type="expression" dxfId="9" priority="11">
+      <formula>RIGHT($A2,4)="--01"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D21">
+    <cfRule type="expression" dxfId="8" priority="12">
+      <formula>RIGHT($A2,4)="--01"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E21">
+    <cfRule type="expression" dxfId="9" priority="13">
+      <formula>RIGHT($A2,4)="--01"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F21">
+    <cfRule type="expression" dxfId="9" priority="14">
+      <formula>RIGHT($A2,4)="--01"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G21">
+    <cfRule type="expression" dxfId="9" priority="15">
+      <formula>RIGHT($A2,4)="--01"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H21">
+    <cfRule type="expression" dxfId="9" priority="16">
+      <formula>RIGHT($A2,4)="--01"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I21">
+    <cfRule type="expression" dxfId="8" priority="17">
+      <formula>RIGHT($A2,4)="--01"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J21">
+    <cfRule type="expression" dxfId="9" priority="18">
+      <formula>RIGHT($A2,4)="--01"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K21">
+    <cfRule type="expression" dxfId="8" priority="19">
+      <formula>RIGHT($A2,4)="--01"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M21">
+    <cfRule type="expression" dxfId="9" priority="21">
+      <formula>RIGHT($A2,4)="--01"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O2:O21">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P23">
+  <conditionalFormatting sqref="P2:P21">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q23">
+  <conditionalFormatting sqref="Q2:Q21">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R23">
+  <conditionalFormatting sqref="R2:R21">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="197">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261022--01</t>
-  </si>
-  <si>
-    <t>20261022--02</t>
-  </si>
-  <si>
-    <t>20261022--03</t>
-  </si>
-  <si>
-    <t>20261022--04</t>
-  </si>
-  <si>
     <t>20261023--01</t>
   </si>
   <si>
@@ -124,390 +112,408 @@
     <t>20261027--02</t>
   </si>
   <si>
+    <t>20261027--03</t>
+  </si>
+  <si>
     <t>20261028--01</t>
   </si>
   <si>
     <t>20261028--02</t>
   </si>
   <si>
+    <t>20261029--01</t>
+  </si>
+  <si>
+    <t>20261029--02</t>
+  </si>
+  <si>
+    <t>20261029--03</t>
+  </si>
+  <si>
+    <t>05:22</t>
+  </si>
+  <si>
+    <t>05:41</t>
+  </si>
+  <si>
+    <t>04:03</t>
+  </si>
+  <si>
+    <t>04:55</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>04:54</t>
+  </si>
+  <si>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>05:31</t>
+  </si>
+  <si>
+    <t>05:38</t>
+  </si>
+  <si>
     <t>03:26</t>
   </si>
   <si>
-    <t>05:38</t>
-  </si>
-  <si>
-    <t>05:31</t>
-  </si>
-  <si>
-    <t>02:22</t>
-  </si>
-  <si>
-    <t>05:22</t>
-  </si>
-  <si>
-    <t>05:41</t>
-  </si>
-  <si>
-    <t>04:03</t>
-  </si>
-  <si>
-    <t>04:55</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>04:53</t>
-  </si>
-  <si>
-    <t>04:05</t>
-  </si>
-  <si>
-    <t>05:42</t>
+    <t>05:09</t>
+  </si>
+  <si>
+    <t>05:44</t>
+  </si>
+  <si>
+    <t>04:34</t>
+  </si>
+  <si>
+    <t>05:12</t>
   </si>
   <si>
     <t>05:37</t>
   </si>
   <si>
-    <t>05:10</t>
-  </si>
-  <si>
-    <t>04:34</t>
-  </si>
-  <si>
-    <t>05:11</t>
+    <t>05:32</t>
+  </si>
+  <si>
+    <t>02:37</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:46</t>
+    <t>01:45</t>
+  </si>
+  <si>
+    <t>03:38</t>
+  </si>
+  <si>
+    <t>00:38</t>
+  </si>
+  <si>
+    <t>02:51</t>
+  </si>
+  <si>
+    <t>04:56</t>
+  </si>
+  <si>
+    <t>01:20</t>
   </si>
   <si>
     <t>03:37</t>
   </si>
   <si>
-    <t>00:38</t>
-  </si>
-  <si>
-    <t>02:51</t>
-  </si>
-  <si>
-    <t>04:56</t>
-  </si>
-  <si>
-    <t>03:36</t>
-  </si>
-  <si>
-    <t>17:59:22</t>
-  </si>
-  <si>
-    <t>19:35:10</t>
-  </si>
-  <si>
-    <t>21:11:40</t>
-  </si>
-  <si>
-    <t>22:48:36</t>
-  </si>
-  <si>
-    <t>18:41:26</t>
-  </si>
-  <si>
-    <t>20:17:49</t>
-  </si>
-  <si>
-    <t>21:54:34</t>
-  </si>
-  <si>
-    <t>17:47:41</t>
-  </si>
-  <si>
-    <t>19:23:52</t>
-  </si>
-  <si>
-    <t>21:00:31</t>
-  </si>
-  <si>
-    <t>16:53:55</t>
-  </si>
-  <si>
-    <t>18:29:51</t>
-  </si>
-  <si>
-    <t>20:06:23</t>
-  </si>
-  <si>
-    <t>17:35:47</t>
-  </si>
-  <si>
-    <t>19:12:12</t>
-  </si>
-  <si>
-    <t>20:49:00</t>
-  </si>
-  <si>
-    <t>16:41:40</t>
-  </si>
-  <si>
-    <t>19:54:36</t>
-  </si>
-  <si>
-    <t>17:23:35</t>
-  </si>
-  <si>
-    <t>19:00:09</t>
-  </si>
-  <si>
-    <t>18:02:12</t>
-  </si>
-  <si>
-    <t>19:37:25</t>
-  </si>
-  <si>
-    <t>21:13:57</t>
-  </si>
-  <si>
-    <t>22:51:47</t>
-  </si>
-  <si>
-    <t>18:43:45</t>
-  </si>
-  <si>
-    <t>20:20:03</t>
-  </si>
-  <si>
-    <t>21:57:13</t>
-  </si>
-  <si>
-    <t>17:50:05</t>
-  </si>
-  <si>
-    <t>19:26:05</t>
-  </si>
-  <si>
-    <t>21:02:56</t>
-  </si>
-  <si>
-    <t>16:56:33</t>
-  </si>
-  <si>
-    <t>18:32:05</t>
-  </si>
-  <si>
-    <t>20:08:42</t>
-  </si>
-  <si>
-    <t>17:38:03</t>
-  </si>
-  <si>
-    <t>19:14:27</t>
-  </si>
-  <si>
-    <t>20:51:50</t>
-  </si>
-  <si>
-    <t>16:44:01</t>
-  </si>
-  <si>
-    <t>19:57:06</t>
-  </si>
-  <si>
-    <t>17:25:48</t>
-  </si>
-  <si>
-    <t>19:02:30</t>
-  </si>
-  <si>
-    <t>18:03:55</t>
-  </si>
-  <si>
-    <t>19:40:14</t>
-  </si>
-  <si>
-    <t>21:16:42</t>
-  </si>
-  <si>
-    <t>22:52:58</t>
-  </si>
-  <si>
-    <t>18:46:26</t>
-  </si>
-  <si>
-    <t>20:22:53</t>
-  </si>
-  <si>
-    <t>21:59:14</t>
-  </si>
-  <si>
-    <t>17:52:33</t>
-  </si>
-  <si>
-    <t>19:28:58</t>
-  </si>
-  <si>
-    <t>21:05:23</t>
-  </si>
-  <si>
-    <t>16:58:35</t>
-  </si>
-  <si>
-    <t>18:34:56</t>
-  </si>
-  <si>
-    <t>20:11:23</t>
-  </si>
-  <si>
-    <t>17:40:48</t>
-  </si>
-  <si>
-    <t>19:17:15</t>
-  </si>
-  <si>
-    <t>20:53:33</t>
-  </si>
-  <si>
-    <t>16:46:36</t>
-  </si>
-  <si>
-    <t>19:59:23</t>
-  </si>
-  <si>
-    <t>17:28:41</t>
-  </si>
-  <si>
-    <t>19:05:06</t>
-  </si>
-  <si>
-    <t>18:05:38</t>
-  </si>
-  <si>
-    <t>19:43:03</t>
-  </si>
-  <si>
-    <t>21:19:28</t>
-  </si>
-  <si>
-    <t>22:54:09</t>
-  </si>
-  <si>
-    <t>18:49:07</t>
-  </si>
-  <si>
-    <t>20:25:44</t>
-  </si>
-  <si>
-    <t>22:01:16</t>
-  </si>
-  <si>
-    <t>17:55:00</t>
-  </si>
-  <si>
-    <t>19:31:50</t>
-  </si>
-  <si>
-    <t>21:07:49</t>
-  </si>
-  <si>
-    <t>17:00:38</t>
-  </si>
-  <si>
-    <t>18:37:47</t>
-  </si>
-  <si>
-    <t>20:14:04</t>
-  </si>
-  <si>
-    <t>17:43:34</t>
-  </si>
-  <si>
-    <t>19:20:04</t>
-  </si>
-  <si>
-    <t>20:55:16</t>
-  </si>
-  <si>
-    <t>16:49:11</t>
-  </si>
-  <si>
-    <t>20:01:40</t>
-  </si>
-  <si>
-    <t>17:31:33</t>
-  </si>
-  <si>
-    <t>19:07:41</t>
-  </si>
-  <si>
-    <t>18:08:28</t>
-  </si>
-  <si>
-    <t>19:45:18</t>
-  </si>
-  <si>
-    <t>21:21:44</t>
-  </si>
-  <si>
-    <t>22:57:21</t>
-  </si>
-  <si>
-    <t>18:51:25</t>
-  </si>
-  <si>
-    <t>20:27:58</t>
-  </si>
-  <si>
-    <t>22:03:55</t>
-  </si>
-  <si>
-    <t>17:57:25</t>
-  </si>
-  <si>
-    <t>19:34:04</t>
-  </si>
-  <si>
-    <t>21:10:14</t>
-  </si>
-  <si>
-    <t>17:03:16</t>
-  </si>
-  <si>
-    <t>18:40:01</t>
-  </si>
-  <si>
-    <t>20:16:22</t>
-  </si>
-  <si>
-    <t>17:45:51</t>
-  </si>
-  <si>
-    <t>19:22:19</t>
-  </si>
-  <si>
-    <t>20:58:05</t>
-  </si>
-  <si>
-    <t>16:51:32</t>
-  </si>
-  <si>
-    <t>20:04:10</t>
-  </si>
-  <si>
-    <t>17:33:46</t>
-  </si>
-  <si>
-    <t>19:10:02</t>
-  </si>
-  <si>
-    <t>10°</t>
+    <t>01:53</t>
+  </si>
+  <si>
+    <t>18:41:24</t>
+  </si>
+  <si>
+    <t>20:17:46</t>
+  </si>
+  <si>
+    <t>21:54:31</t>
+  </si>
+  <si>
+    <t>17:47:35</t>
+  </si>
+  <si>
+    <t>19:23:45</t>
+  </si>
+  <si>
+    <t>21:00:24</t>
+  </si>
+  <si>
+    <t>16:53:44</t>
+  </si>
+  <si>
+    <t>18:29:40</t>
+  </si>
+  <si>
+    <t>20:06:12</t>
+  </si>
+  <si>
+    <t>17:35:30</t>
+  </si>
+  <si>
+    <t>19:11:54</t>
+  </si>
+  <si>
+    <t>20:48:42</t>
+  </si>
+  <si>
+    <t>16:41:16</t>
+  </si>
+  <si>
+    <t>18:17:31</t>
+  </si>
+  <si>
+    <t>19:54:10</t>
+  </si>
+  <si>
+    <t>17:23:01</t>
+  </si>
+  <si>
+    <t>18:59:34</t>
+  </si>
+  <si>
+    <t>16:28:27</t>
+  </si>
+  <si>
+    <t>18:04:53</t>
+  </si>
+  <si>
+    <t>19:41:44</t>
+  </si>
+  <si>
+    <t>18:43:42</t>
+  </si>
+  <si>
+    <t>20:20:00</t>
+  </si>
+  <si>
+    <t>21:57:10</t>
+  </si>
+  <si>
+    <t>17:49:59</t>
+  </si>
+  <si>
+    <t>19:25:59</t>
+  </si>
+  <si>
+    <t>21:02:49</t>
+  </si>
+  <si>
+    <t>16:56:22</t>
+  </si>
+  <si>
+    <t>18:31:54</t>
+  </si>
+  <si>
+    <t>20:08:30</t>
+  </si>
+  <si>
+    <t>17:37:46</t>
+  </si>
+  <si>
+    <t>19:14:09</t>
+  </si>
+  <si>
+    <t>20:51:32</t>
+  </si>
+  <si>
+    <t>16:43:37</t>
+  </si>
+  <si>
+    <t>18:19:44</t>
+  </si>
+  <si>
+    <t>19:56:41</t>
+  </si>
+  <si>
+    <t>17:25:15</t>
+  </si>
+  <si>
+    <t>19:01:55</t>
+  </si>
+  <si>
+    <t>16:30:42</t>
+  </si>
+  <si>
+    <t>18:07:10</t>
+  </si>
+  <si>
+    <t>19:44:50</t>
+  </si>
+  <si>
+    <t>18:46:23</t>
+  </si>
+  <si>
+    <t>20:22:50</t>
+  </si>
+  <si>
+    <t>21:59:11</t>
+  </si>
+  <si>
+    <t>17:52:26</t>
+  </si>
+  <si>
+    <t>19:28:51</t>
+  </si>
+  <si>
+    <t>21:05:16</t>
+  </si>
+  <si>
+    <t>16:58:25</t>
+  </si>
+  <si>
+    <t>18:34:44</t>
+  </si>
+  <si>
+    <t>20:11:11</t>
+  </si>
+  <si>
+    <t>17:40:31</t>
+  </si>
+  <si>
+    <t>19:16:58</t>
+  </si>
+  <si>
+    <t>20:53:15</t>
+  </si>
+  <si>
+    <t>16:46:12</t>
+  </si>
+  <si>
+    <t>18:22:36</t>
+  </si>
+  <si>
+    <t>19:58:58</t>
+  </si>
+  <si>
+    <t>17:28:07</t>
+  </si>
+  <si>
+    <t>19:04:31</t>
+  </si>
+  <si>
+    <t>16:33:30</t>
+  </si>
+  <si>
+    <t>18:09:56</t>
+  </si>
+  <si>
+    <t>19:46:09</t>
+  </si>
+  <si>
+    <t>18:49:04</t>
+  </si>
+  <si>
+    <t>20:25:41</t>
+  </si>
+  <si>
+    <t>22:01:13</t>
+  </si>
+  <si>
+    <t>17:54:54</t>
+  </si>
+  <si>
+    <t>19:31:44</t>
+  </si>
+  <si>
+    <t>21:07:43</t>
+  </si>
+  <si>
+    <t>17:00:27</t>
+  </si>
+  <si>
+    <t>18:37:35</t>
+  </si>
+  <si>
+    <t>20:13:52</t>
+  </si>
+  <si>
+    <t>17:43:17</t>
+  </si>
+  <si>
+    <t>19:19:47</t>
+  </si>
+  <si>
+    <t>20:54:58</t>
+  </si>
+  <si>
+    <t>16:48:46</t>
+  </si>
+  <si>
+    <t>18:25:28</t>
+  </si>
+  <si>
+    <t>20:01:15</t>
+  </si>
+  <si>
+    <t>17:30:59</t>
+  </si>
+  <si>
+    <t>19:07:07</t>
+  </si>
+  <si>
+    <t>16:36:19</t>
+  </si>
+  <si>
+    <t>18:12:42</t>
+  </si>
+  <si>
+    <t>19:47:27</t>
+  </si>
+  <si>
+    <t>18:51:22</t>
+  </si>
+  <si>
+    <t>20:27:55</t>
+  </si>
+  <si>
+    <t>22:03:51</t>
+  </si>
+  <si>
+    <t>17:57:19</t>
+  </si>
+  <si>
+    <t>19:33:57</t>
+  </si>
+  <si>
+    <t>21:10:08</t>
+  </si>
+  <si>
+    <t>17:03:05</t>
+  </si>
+  <si>
+    <t>18:39:50</t>
+  </si>
+  <si>
+    <t>20:16:10</t>
+  </si>
+  <si>
+    <t>17:45:33</t>
+  </si>
+  <si>
+    <t>19:22:01</t>
+  </si>
+  <si>
+    <t>20:57:47</t>
+  </si>
+  <si>
+    <t>16:51:08</t>
+  </si>
+  <si>
+    <t>18:27:42</t>
+  </si>
+  <si>
+    <t>20:03:45</t>
+  </si>
+  <si>
+    <t>17:33:12</t>
+  </si>
+  <si>
+    <t>19:09:27</t>
+  </si>
+  <si>
+    <t>16:38:34</t>
+  </si>
+  <si>
+    <t>18:14:58</t>
+  </si>
+  <si>
+    <t>19:50:32</t>
+  </si>
+  <si>
+    <t>8°</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>8°</t>
-  </si>
-  <si>
     <t>19°</t>
   </si>
   <si>
@@ -529,40 +535,55 @@
     <t>11°</t>
   </si>
   <si>
+    <t>20°</t>
+  </si>
+  <si>
     <t>7°</t>
   </si>
   <si>
-    <t>18:02:07</t>
-  </si>
-  <si>
-    <t>18:43:22</t>
-  </si>
-  <si>
-    <t>17:51:51</t>
-  </si>
-  <si>
-    <t>19:24:24</t>
-  </si>
-  <si>
-    <t>17:00:10</t>
-  </si>
-  <si>
-    <t>18:32:43</t>
-  </si>
-  <si>
-    <t>17:40:54</t>
-  </si>
-  <si>
-    <t>19:13:26</t>
-  </si>
-  <si>
-    <t>16:48:57</t>
-  </si>
-  <si>
-    <t>17:29:24</t>
-  </si>
-  <si>
-    <t>19:01:56</t>
+    <t>9°</t>
+  </si>
+  <si>
+    <t>23°</t>
+  </si>
+  <si>
+    <t>18:43:19</t>
+  </si>
+  <si>
+    <t>17:51:44</t>
+  </si>
+  <si>
+    <t>19:24:18</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>18:32:32</t>
+  </si>
+  <si>
+    <t>17:40:37</t>
+  </si>
+  <si>
+    <t>19:13:09</t>
+  </si>
+  <si>
+    <t>16:48:33</t>
+  </si>
+  <si>
+    <t>18:21:04</t>
+  </si>
+  <si>
+    <t>17:28:52</t>
+  </si>
+  <si>
+    <t>19:01:23</t>
+  </si>
+  <si>
+    <t>16:36:33</t>
+  </si>
+  <si>
+    <t>18:09:03</t>
   </si>
   <si>
     <t>B</t>
@@ -571,13 +592,19 @@
     <t>A+B</t>
   </si>
   <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>4</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>1</t>
   </si>
 </sst>
 </file>
@@ -626,55 +653,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -692,7 +671,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -704,7 +731,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -716,25 +761,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FFEEF3F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -752,7 +779,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1355,55 +1382,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="L2" s="4">
-        <v>-20.4</v>
+        <v>-27.3</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="O2" s="6">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="P2" s="7">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="Q2" s="8">
-        <v>40</v>
-      </c>
-      <c r="R2" s="9">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="R2" s="8">
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1411,55 +1438,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>39</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="L3" s="4">
-        <v>-35</v>
+        <v>-40.9</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="O3" s="6">
-        <v>43</v>
-      </c>
-      <c r="P3" s="10">
-        <v>26</v>
-      </c>
-      <c r="Q3" s="11">
-        <v>33</v>
-      </c>
-      <c r="R3" s="9">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="P3" s="9">
+        <v>2</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>100</v>
+      </c>
+      <c r="R3" s="8">
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1467,55 +1494,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L4" s="4">
-        <v>-46.3</v>
+        <v>-49.7</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="O4" s="12">
-        <v>52</v>
-      </c>
-      <c r="P4" s="13">
-        <v>43</v>
+        <v>193</v>
+      </c>
+      <c r="O4" s="6">
+        <v>100</v>
+      </c>
+      <c r="P4" s="10">
+        <v>28</v>
       </c>
       <c r="Q4" s="8">
-        <v>42</v>
-      </c>
-      <c r="R4" s="9">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="R4" s="8">
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1523,52 +1550,52 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>41</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>64</v>
+        <v>178</v>
       </c>
       <c r="L5" s="4">
-        <v>-50.7</v>
+        <v>-19.3</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="O5" s="12">
-        <v>77</v>
+        <v>194</v>
+      </c>
+      <c r="O5" s="6">
+        <v>57</v>
       </c>
       <c r="P5" s="11">
-        <v>34</v>
-      </c>
-      <c r="Q5" s="14">
-        <v>68</v>
+        <v>35</v>
+      </c>
+      <c r="Q5" s="12">
+        <v>20</v>
       </c>
       <c r="R5" s="9">
         <v>0</v>
@@ -1579,55 +1606,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="L6" s="4">
-        <v>-27.3</v>
+        <v>-33.9</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="O6" s="12">
-        <v>100</v>
-      </c>
-      <c r="P6" s="15">
-        <v>61</v>
-      </c>
-      <c r="Q6" s="16">
-        <v>100</v>
-      </c>
-      <c r="R6" s="16">
-        <v>100</v>
+        <v>193</v>
+      </c>
+      <c r="O6" s="13">
+        <v>34</v>
+      </c>
+      <c r="P6" s="10">
+        <v>30</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>0</v>
+      </c>
+      <c r="R6" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1635,55 +1662,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="L7" s="4">
-        <v>-40.9</v>
+        <v>-46</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="O7" s="12">
-        <v>100</v>
-      </c>
-      <c r="P7" s="17">
-        <v>15</v>
-      </c>
-      <c r="Q7" s="16">
-        <v>100</v>
-      </c>
-      <c r="R7" s="18">
-        <v>50</v>
+        <v>193</v>
+      </c>
+      <c r="O7" s="14">
+        <v>3</v>
+      </c>
+      <c r="P7" s="15">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>0</v>
+      </c>
+      <c r="R7" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1697,49 +1724,49 @@
         <v>44</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>67</v>
+        <v>180</v>
       </c>
       <c r="L8" s="4">
-        <v>-49.7</v>
+        <v>-11</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="O8" s="12">
-        <v>100</v>
-      </c>
-      <c r="P8" s="19">
-        <v>18</v>
-      </c>
-      <c r="Q8" s="20">
-        <v>94</v>
-      </c>
-      <c r="R8" s="16">
-        <v>100</v>
+        <v>194</v>
+      </c>
+      <c r="O8" s="6">
+        <v>79</v>
+      </c>
+      <c r="P8" s="16">
+        <v>79</v>
+      </c>
+      <c r="Q8" s="17">
+        <v>40</v>
+      </c>
+      <c r="R8" s="18">
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1747,52 +1774,52 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="L9" s="4">
+        <v>-26.1</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="O9" s="6">
+        <v>52</v>
+      </c>
+      <c r="P9" s="18">
+        <v>52</v>
+      </c>
+      <c r="Q9" s="19">
         <v>45</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="L9" s="4">
-        <v>-19.3</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="O9" s="12">
-        <v>87</v>
-      </c>
-      <c r="P9" s="21">
-        <v>85</v>
-      </c>
-      <c r="Q9" s="10">
-        <v>26</v>
       </c>
       <c r="R9" s="9">
         <v>0</v>
@@ -1803,52 +1830,52 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>165</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>175</v>
+        <v>72</v>
       </c>
       <c r="L10" s="4">
-        <v>-33.9</v>
+        <v>-40.1</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="O10" s="12">
-        <v>56</v>
-      </c>
-      <c r="P10" s="22">
-        <v>55</v>
-      </c>
-      <c r="Q10" s="7">
-        <v>3</v>
+        <v>193</v>
+      </c>
+      <c r="O10" s="13">
+        <v>26</v>
+      </c>
+      <c r="P10" s="20">
+        <v>26</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>0</v>
       </c>
       <c r="R10" s="9">
         <v>0</v>
@@ -1859,55 +1886,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="L11" s="4">
+        <v>-17.9</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="O11" s="6">
+        <v>100</v>
+      </c>
+      <c r="P11" s="21">
+        <v>13</v>
+      </c>
+      <c r="Q11" s="22">
         <v>54</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="L11" s="4">
-        <v>-46</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="O11" s="6">
-        <v>24</v>
-      </c>
-      <c r="P11" s="17">
-        <v>17</v>
-      </c>
-      <c r="Q11" s="9">
-        <v>0</v>
-      </c>
-      <c r="R11" s="9">
-        <v>0</v>
+      <c r="R11" s="7">
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1915,55 +1942,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="L12" s="4">
-        <v>-11.1</v>
+        <v>-32.8</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="O12" s="12">
-        <v>77</v>
-      </c>
-      <c r="P12" s="23">
-        <v>77</v>
-      </c>
-      <c r="Q12" s="18">
-        <v>49</v>
-      </c>
-      <c r="R12" s="24">
-        <v>30</v>
+        <v>193</v>
+      </c>
+      <c r="O12" s="6">
+        <v>96</v>
+      </c>
+      <c r="P12" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="23">
+        <v>96</v>
+      </c>
+      <c r="R12" s="10">
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1971,55 +1998,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F13" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L13" s="4">
+        <v>-45.4</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="O13" s="6">
         <v>92</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L13" s="4">
-        <v>-26.2</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="O13" s="12">
-        <v>66</v>
-      </c>
-      <c r="P13" s="25">
-        <v>66</v>
-      </c>
-      <c r="Q13" s="22">
-        <v>54</v>
-      </c>
-      <c r="R13" s="10">
-        <v>25</v>
+      <c r="P13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="24">
+        <v>89</v>
+      </c>
+      <c r="R13" s="21">
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2027,55 +2054,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>73</v>
+        <v>184</v>
       </c>
       <c r="L14" s="4">
-        <v>-40.1</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="O14" s="12">
-        <v>85</v>
-      </c>
-      <c r="P14" s="14">
-        <v>69</v>
-      </c>
-      <c r="Q14" s="21">
-        <v>84</v>
-      </c>
-      <c r="R14" s="9">
+        <v>194</v>
+      </c>
+      <c r="O14" s="13">
+        <v>44</v>
+      </c>
+      <c r="P14" s="15">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="9">
         <v>0</v>
+      </c>
+      <c r="R14" s="11">
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2083,55 +2110,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="L15" s="4">
-        <v>-18</v>
+        <v>-24.8</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="O15" s="12">
-        <v>94</v>
-      </c>
-      <c r="P15" s="26">
-        <v>8</v>
-      </c>
-      <c r="Q15" s="22">
-        <v>55</v>
+        <v>194</v>
+      </c>
+      <c r="O15" s="6">
+        <v>71</v>
+      </c>
+      <c r="P15" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="9">
+        <v>0</v>
       </c>
       <c r="R15" s="25">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2139,55 +2166,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="L16" s="4">
-        <v>-32.8</v>
+        <v>-39.1</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="O16" s="12">
-        <v>99</v>
-      </c>
-      <c r="P16" s="26">
-        <v>9</v>
-      </c>
-      <c r="Q16" s="24">
-        <v>32</v>
-      </c>
-      <c r="R16" s="23">
-        <v>74</v>
+        <v>193</v>
+      </c>
+      <c r="O16" s="6">
+        <v>63</v>
+      </c>
+      <c r="P16" s="15">
+        <v>4</v>
+      </c>
+      <c r="Q16" s="26">
+        <v>11</v>
+      </c>
+      <c r="R16" s="7">
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2195,55 +2222,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>76</v>
+        <v>186</v>
       </c>
       <c r="L17" s="4">
-        <v>-45.4</v>
+        <v>-16.5</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="O17" s="12">
-        <v>99</v>
-      </c>
-      <c r="P17" s="7">
-        <v>6</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>40</v>
-      </c>
-      <c r="R17" s="25">
-        <v>63</v>
+        <v>194</v>
+      </c>
+      <c r="O17" s="6">
+        <v>55</v>
+      </c>
+      <c r="P17" s="10">
+        <v>31</v>
+      </c>
+      <c r="Q17" s="12">
+        <v>21</v>
+      </c>
+      <c r="R17" s="15">
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2257,49 +2284,49 @@
         <v>51</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="L18" s="4">
-        <v>-9.800000000000001</v>
+        <v>-31.5</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="O18" s="12">
-        <v>59</v>
+        <v>193</v>
+      </c>
+      <c r="O18" s="6">
+        <v>62</v>
       </c>
       <c r="P18" s="26">
-        <v>8</v>
-      </c>
-      <c r="Q18" s="9">
+        <v>12</v>
+      </c>
+      <c r="Q18" s="20">
+        <v>24</v>
+      </c>
+      <c r="R18" s="9">
         <v>0</v>
-      </c>
-      <c r="R18" s="15">
-        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2307,55 +2334,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>78</v>
+        <v>188</v>
       </c>
       <c r="L19" s="4">
-        <v>-39.1</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="O19" s="12">
-        <v>95</v>
-      </c>
-      <c r="P19" s="17">
-        <v>16</v>
-      </c>
-      <c r="Q19" s="26">
-        <v>12</v>
-      </c>
-      <c r="R19" s="14">
-        <v>68</v>
+        <v>196</v>
+      </c>
+      <c r="O19" s="6">
+        <v>97</v>
+      </c>
+      <c r="P19" s="27">
+        <v>87</v>
+      </c>
+      <c r="Q19" s="12">
+        <v>18</v>
+      </c>
+      <c r="R19" s="9">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2363,55 +2390,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="L20" s="4">
-        <v>-16.6</v>
+        <v>-23.4</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="O20" s="27">
-        <v>12</v>
-      </c>
-      <c r="P20" s="26">
-        <v>12</v>
+        <v>194</v>
+      </c>
+      <c r="O20" s="6">
+        <v>100</v>
+      </c>
+      <c r="P20" s="8">
+        <v>100</v>
       </c>
       <c r="Q20" s="9">
         <v>0</v>
       </c>
-      <c r="R20" s="26">
-        <v>12</v>
+      <c r="R20" s="9">
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2419,55 +2446,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>182</v>
+        <v>83</v>
       </c>
       <c r="L21" s="4">
-        <v>-31.6</v>
+        <v>-37.9</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="O21" s="6">
-        <v>7</v>
-      </c>
-      <c r="P21" s="7">
-        <v>7</v>
+        <v>97</v>
+      </c>
+      <c r="P21" s="23">
+        <v>97</v>
       </c>
       <c r="Q21" s="9">
-        <v>1</v>
-      </c>
-      <c r="R21" s="7">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="R21" s="15">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/output/HaP_Teplice.xlsx
+++ b/output/HaP_Teplice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="194">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20261023--01</t>
-  </si>
-  <si>
-    <t>20261023--02</t>
-  </si>
-  <si>
-    <t>20261023--03</t>
-  </si>
-  <si>
     <t>20261024--01</t>
   </si>
   <si>
@@ -130,396 +121,390 @@
     <t>20261029--03</t>
   </si>
   <si>
-    <t>05:22</t>
+    <t>20261030--01</t>
+  </si>
+  <si>
+    <t>20261030--02</t>
+  </si>
+  <si>
+    <t>04:54</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>04:53</t>
+  </si>
+  <si>
+    <t>04:04</t>
   </si>
   <si>
     <t>05:41</t>
   </si>
   <si>
-    <t>04:03</t>
+    <t>05:21</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>05:38</t>
+  </si>
+  <si>
+    <t>03:25</t>
+  </si>
+  <si>
+    <t>05:09</t>
+  </si>
+  <si>
+    <t>05:44</t>
+  </si>
+  <si>
+    <t>04:33</t>
+  </si>
+  <si>
+    <t>05:10</t>
+  </si>
+  <si>
+    <t>05:37</t>
+  </si>
+  <si>
+    <t>05:32</t>
+  </si>
+  <si>
+    <t>02:33</t>
+  </si>
+  <si>
+    <t>05:43</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>01:44</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>03:37</t>
+  </si>
+  <si>
+    <t>00:38</t>
+  </si>
+  <si>
+    <t>02:50</t>
   </si>
   <si>
     <t>04:55</t>
   </si>
   <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>04:54</t>
-  </si>
-  <si>
-    <t>04:05</t>
-  </si>
-  <si>
-    <t>05:31</t>
-  </si>
-  <si>
-    <t>05:38</t>
-  </si>
-  <si>
-    <t>03:26</t>
-  </si>
-  <si>
-    <t>05:09</t>
-  </si>
-  <si>
-    <t>05:44</t>
-  </si>
-  <si>
-    <t>04:34</t>
-  </si>
-  <si>
-    <t>05:12</t>
-  </si>
-  <si>
-    <t>05:37</t>
-  </si>
-  <si>
-    <t>05:32</t>
-  </si>
-  <si>
-    <t>02:37</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>01:45</t>
-  </si>
-  <si>
-    <t>03:38</t>
-  </si>
-  <si>
-    <t>00:38</t>
-  </si>
-  <si>
-    <t>02:51</t>
-  </si>
-  <si>
-    <t>04:56</t>
-  </si>
-  <si>
     <t>01:20</t>
   </si>
   <si>
-    <t>03:37</t>
-  </si>
-  <si>
-    <t>01:53</t>
-  </si>
-  <si>
-    <t>18:41:24</t>
-  </si>
-  <si>
-    <t>20:17:46</t>
-  </si>
-  <si>
-    <t>21:54:31</t>
-  </si>
-  <si>
-    <t>17:47:35</t>
-  </si>
-  <si>
-    <t>19:23:45</t>
-  </si>
-  <si>
-    <t>21:00:24</t>
-  </si>
-  <si>
-    <t>16:53:44</t>
-  </si>
-  <si>
-    <t>18:29:40</t>
-  </si>
-  <si>
-    <t>20:06:12</t>
-  </si>
-  <si>
-    <t>17:35:30</t>
-  </si>
-  <si>
-    <t>19:11:54</t>
-  </si>
-  <si>
-    <t>20:48:42</t>
-  </si>
-  <si>
-    <t>16:41:16</t>
-  </si>
-  <si>
-    <t>18:17:31</t>
-  </si>
-  <si>
-    <t>19:54:10</t>
-  </si>
-  <si>
-    <t>17:23:01</t>
-  </si>
-  <si>
-    <t>18:59:34</t>
-  </si>
-  <si>
-    <t>16:28:27</t>
-  </si>
-  <si>
-    <t>18:04:53</t>
-  </si>
-  <si>
-    <t>19:41:44</t>
-  </si>
-  <si>
-    <t>18:43:42</t>
-  </si>
-  <si>
-    <t>20:20:00</t>
-  </si>
-  <si>
-    <t>21:57:10</t>
-  </si>
-  <si>
-    <t>17:49:59</t>
-  </si>
-  <si>
-    <t>19:25:59</t>
-  </si>
-  <si>
-    <t>21:02:49</t>
-  </si>
-  <si>
-    <t>16:56:22</t>
-  </si>
-  <si>
-    <t>18:31:54</t>
-  </si>
-  <si>
-    <t>20:08:30</t>
-  </si>
-  <si>
-    <t>17:37:46</t>
-  </si>
-  <si>
-    <t>19:14:09</t>
-  </si>
-  <si>
-    <t>20:51:32</t>
-  </si>
-  <si>
-    <t>16:43:37</t>
-  </si>
-  <si>
-    <t>18:19:44</t>
-  </si>
-  <si>
-    <t>19:56:41</t>
-  </si>
-  <si>
-    <t>17:25:15</t>
-  </si>
-  <si>
-    <t>19:01:55</t>
-  </si>
-  <si>
-    <t>16:30:42</t>
-  </si>
-  <si>
-    <t>18:07:10</t>
-  </si>
-  <si>
-    <t>19:44:50</t>
-  </si>
-  <si>
-    <t>18:46:23</t>
-  </si>
-  <si>
-    <t>20:22:50</t>
-  </si>
-  <si>
-    <t>21:59:11</t>
-  </si>
-  <si>
-    <t>17:52:26</t>
-  </si>
-  <si>
-    <t>19:28:51</t>
-  </si>
-  <si>
-    <t>21:05:16</t>
-  </si>
-  <si>
-    <t>16:58:25</t>
-  </si>
-  <si>
-    <t>18:34:44</t>
-  </si>
-  <si>
-    <t>20:11:11</t>
-  </si>
-  <si>
-    <t>17:40:31</t>
-  </si>
-  <si>
-    <t>19:16:58</t>
-  </si>
-  <si>
-    <t>20:53:15</t>
-  </si>
-  <si>
-    <t>16:46:12</t>
-  </si>
-  <si>
-    <t>18:22:36</t>
-  </si>
-  <si>
-    <t>19:58:58</t>
-  </si>
-  <si>
-    <t>17:28:07</t>
-  </si>
-  <si>
-    <t>19:04:31</t>
-  </si>
-  <si>
-    <t>16:33:30</t>
-  </si>
-  <si>
-    <t>18:09:56</t>
-  </si>
-  <si>
-    <t>19:46:09</t>
-  </si>
-  <si>
-    <t>18:49:04</t>
-  </si>
-  <si>
-    <t>20:25:41</t>
-  </si>
-  <si>
-    <t>22:01:13</t>
-  </si>
-  <si>
-    <t>17:54:54</t>
-  </si>
-  <si>
-    <t>19:31:44</t>
-  </si>
-  <si>
-    <t>21:07:43</t>
-  </si>
-  <si>
-    <t>17:00:27</t>
-  </si>
-  <si>
-    <t>18:37:35</t>
-  </si>
-  <si>
-    <t>20:13:52</t>
-  </si>
-  <si>
-    <t>17:43:17</t>
-  </si>
-  <si>
-    <t>19:19:47</t>
-  </si>
-  <si>
-    <t>20:54:58</t>
-  </si>
-  <si>
-    <t>16:48:46</t>
-  </si>
-  <si>
-    <t>18:25:28</t>
-  </si>
-  <si>
-    <t>20:01:15</t>
-  </si>
-  <si>
-    <t>17:30:59</t>
-  </si>
-  <si>
-    <t>19:07:07</t>
-  </si>
-  <si>
-    <t>16:36:19</t>
-  </si>
-  <si>
-    <t>18:12:42</t>
-  </si>
-  <si>
-    <t>19:47:27</t>
-  </si>
-  <si>
-    <t>18:51:22</t>
-  </si>
-  <si>
-    <t>20:27:55</t>
-  </si>
-  <si>
-    <t>22:03:51</t>
-  </si>
-  <si>
-    <t>17:57:19</t>
-  </si>
-  <si>
-    <t>19:33:57</t>
-  </si>
-  <si>
-    <t>21:10:08</t>
-  </si>
-  <si>
-    <t>17:03:05</t>
-  </si>
-  <si>
-    <t>18:39:50</t>
-  </si>
-  <si>
-    <t>20:16:10</t>
-  </si>
-  <si>
-    <t>17:45:33</t>
-  </si>
-  <si>
-    <t>19:22:01</t>
-  </si>
-  <si>
-    <t>20:57:47</t>
-  </si>
-  <si>
-    <t>16:51:08</t>
-  </si>
-  <si>
-    <t>18:27:42</t>
-  </si>
-  <si>
-    <t>20:03:45</t>
-  </si>
-  <si>
-    <t>17:33:12</t>
-  </si>
-  <si>
-    <t>19:09:27</t>
-  </si>
-  <si>
-    <t>16:38:34</t>
-  </si>
-  <si>
-    <t>18:14:58</t>
-  </si>
-  <si>
-    <t>19:50:32</t>
-  </si>
-  <si>
-    <t>8°</t>
+    <t>03:36</t>
+  </si>
+  <si>
+    <t>01:52</t>
+  </si>
+  <si>
+    <t>04:15</t>
+  </si>
+  <si>
+    <t>17:47:39</t>
+  </si>
+  <si>
+    <t>19:23:50</t>
+  </si>
+  <si>
+    <t>21:00:28</t>
+  </si>
+  <si>
+    <t>16:53:52</t>
+  </si>
+  <si>
+    <t>18:29:48</t>
+  </si>
+  <si>
+    <t>20:06:20</t>
+  </si>
+  <si>
+    <t>17:35:42</t>
+  </si>
+  <si>
+    <t>19:12:07</t>
+  </si>
+  <si>
+    <t>20:48:56</t>
+  </si>
+  <si>
+    <t>16:41:34</t>
+  </si>
+  <si>
+    <t>18:17:50</t>
+  </si>
+  <si>
+    <t>19:54:30</t>
+  </si>
+  <si>
+    <t>17:23:28</t>
+  </si>
+  <si>
+    <t>19:00:02</t>
+  </si>
+  <si>
+    <t>16:29:02</t>
+  </si>
+  <si>
+    <t>18:05:29</t>
+  </si>
+  <si>
+    <t>19:42:20</t>
+  </si>
+  <si>
+    <t>17:10:51</t>
+  </si>
+  <si>
+    <t>18:47:33</t>
+  </si>
+  <si>
+    <t>17:50:04</t>
+  </si>
+  <si>
+    <t>19:26:03</t>
+  </si>
+  <si>
+    <t>21:02:54</t>
+  </si>
+  <si>
+    <t>16:56:30</t>
+  </si>
+  <si>
+    <t>18:32:02</t>
+  </si>
+  <si>
+    <t>20:08:39</t>
+  </si>
+  <si>
+    <t>17:37:59</t>
+  </si>
+  <si>
+    <t>19:14:22</t>
+  </si>
+  <si>
+    <t>20:51:46</t>
+  </si>
+  <si>
+    <t>16:43:56</t>
+  </si>
+  <si>
+    <t>18:20:03</t>
+  </si>
+  <si>
+    <t>19:57:01</t>
+  </si>
+  <si>
+    <t>17:25:41</t>
+  </si>
+  <si>
+    <t>19:02:23</t>
+  </si>
+  <si>
+    <t>16:31:17</t>
+  </si>
+  <si>
+    <t>18:07:45</t>
+  </si>
+  <si>
+    <t>19:45:28</t>
+  </si>
+  <si>
+    <t>17:13:05</t>
+  </si>
+  <si>
+    <t>18:50:10</t>
+  </si>
+  <si>
+    <t>17:52:30</t>
+  </si>
+  <si>
+    <t>19:28:55</t>
+  </si>
+  <si>
+    <t>21:05:20</t>
+  </si>
+  <si>
+    <t>16:58:32</t>
+  </si>
+  <si>
+    <t>18:34:53</t>
+  </si>
+  <si>
+    <t>20:11:19</t>
+  </si>
+  <si>
+    <t>17:40:44</t>
+  </si>
+  <si>
+    <t>19:17:11</t>
+  </si>
+  <si>
+    <t>20:53:28</t>
+  </si>
+  <si>
+    <t>16:46:30</t>
+  </si>
+  <si>
+    <t>18:22:55</t>
+  </si>
+  <si>
+    <t>19:59:17</t>
+  </si>
+  <si>
+    <t>17:28:33</t>
+  </si>
+  <si>
+    <t>19:04:58</t>
+  </si>
+  <si>
+    <t>16:34:05</t>
+  </si>
+  <si>
+    <t>18:10:31</t>
+  </si>
+  <si>
+    <t>19:46:44</t>
+  </si>
+  <si>
+    <t>17:15:56</t>
+  </si>
+  <si>
+    <t>18:52:15</t>
+  </si>
+  <si>
+    <t>17:54:58</t>
+  </si>
+  <si>
+    <t>19:31:48</t>
+  </si>
+  <si>
+    <t>21:07:47</t>
+  </si>
+  <si>
+    <t>17:00:34</t>
+  </si>
+  <si>
+    <t>18:37:43</t>
+  </si>
+  <si>
+    <t>20:14:00</t>
+  </si>
+  <si>
+    <t>17:43:29</t>
+  </si>
+  <si>
+    <t>19:20:00</t>
+  </si>
+  <si>
+    <t>20:55:11</t>
+  </si>
+  <si>
+    <t>16:49:05</t>
+  </si>
+  <si>
+    <t>18:25:47</t>
+  </si>
+  <si>
+    <t>20:01:34</t>
+  </si>
+  <si>
+    <t>17:31:25</t>
+  </si>
+  <si>
+    <t>19:07:33</t>
+  </si>
+  <si>
+    <t>16:36:54</t>
+  </si>
+  <si>
+    <t>18:13:17</t>
+  </si>
+  <si>
+    <t>19:48:01</t>
+  </si>
+  <si>
+    <t>17:18:48</t>
+  </si>
+  <si>
+    <t>18:54:20</t>
+  </si>
+  <si>
+    <t>17:57:23</t>
+  </si>
+  <si>
+    <t>19:34:01</t>
+  </si>
+  <si>
+    <t>21:10:12</t>
+  </si>
+  <si>
+    <t>17:03:13</t>
+  </si>
+  <si>
+    <t>18:39:57</t>
+  </si>
+  <si>
+    <t>20:16:18</t>
+  </si>
+  <si>
+    <t>17:45:46</t>
+  </si>
+  <si>
+    <t>19:22:14</t>
+  </si>
+  <si>
+    <t>20:58:00</t>
+  </si>
+  <si>
+    <t>16:51:27</t>
+  </si>
+  <si>
+    <t>18:28:01</t>
+  </si>
+  <si>
+    <t>20:04:04</t>
+  </si>
+  <si>
+    <t>17:33:39</t>
+  </si>
+  <si>
+    <t>19:09:54</t>
+  </si>
+  <si>
+    <t>16:39:09</t>
+  </si>
+  <si>
+    <t>18:15:33</t>
+  </si>
+  <si>
+    <t>19:51:08</t>
+  </si>
+  <si>
+    <t>17:21:01</t>
+  </si>
+  <si>
+    <t>18:56:56</t>
+  </si>
+  <si>
+    <t>19°</t>
+  </si>
+  <si>
+    <t>2°</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>19°</t>
-  </si>
-  <si>
-    <t>2°</t>
-  </si>
-  <si>
     <t>12°</t>
   </si>
   <si>
@@ -547,58 +532,64 @@
     <t>23°</t>
   </si>
   <si>
-    <t>18:43:19</t>
-  </si>
-  <si>
-    <t>17:51:44</t>
-  </si>
-  <si>
-    <t>19:24:18</t>
-  </si>
-  <si>
-    <t>17:00:00</t>
-  </si>
-  <si>
-    <t>18:32:32</t>
-  </si>
-  <si>
-    <t>17:40:37</t>
-  </si>
-  <si>
-    <t>19:13:09</t>
-  </si>
-  <si>
-    <t>16:48:33</t>
-  </si>
-  <si>
-    <t>18:21:04</t>
-  </si>
-  <si>
-    <t>17:28:52</t>
-  </si>
-  <si>
-    <t>19:01:23</t>
-  </si>
-  <si>
-    <t>16:36:33</t>
-  </si>
-  <si>
-    <t>18:09:03</t>
+    <t>21°</t>
+  </si>
+  <si>
+    <t>17:51:48</t>
+  </si>
+  <si>
+    <t>19:24:22</t>
+  </si>
+  <si>
+    <t>17:00:07</t>
+  </si>
+  <si>
+    <t>18:32:40</t>
+  </si>
+  <si>
+    <t>17:40:49</t>
+  </si>
+  <si>
+    <t>19:13:22</t>
+  </si>
+  <si>
+    <t>16:48:51</t>
+  </si>
+  <si>
+    <t>18:21:23</t>
+  </si>
+  <si>
+    <t>17:29:17</t>
+  </si>
+  <si>
+    <t>19:01:49</t>
+  </si>
+  <si>
+    <t>16:37:06</t>
+  </si>
+  <si>
+    <t>18:09:37</t>
+  </si>
+  <si>
+    <t>17:17:20</t>
+  </si>
+  <si>
+    <t>18:49:51</t>
+  </si>
+  <si>
+    <t>A+B</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>A+B</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>4</t>
@@ -638,7 +629,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -659,7 +650,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -671,31 +728,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF6F9FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -707,31 +740,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -743,43 +752,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -820,7 +799,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -895,12 +874,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1304,7 +1277,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.140625" style="1" customWidth="1"/>
@@ -1382,55 +1355,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>55</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>84</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="L2" s="4">
-        <v>-27.3</v>
+        <v>-19.3</v>
       </c>
       <c r="M2" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>193</v>
-      </c>
       <c r="O2" s="6">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="P2" s="7">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="Q2" s="8">
-        <v>100</v>
-      </c>
-      <c r="R2" s="8">
-        <v>100</v>
+        <v>28</v>
+      </c>
+      <c r="R2" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1438,55 +1411,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>85</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>65</v>
+        <v>174</v>
       </c>
       <c r="L3" s="4">
-        <v>-40.9</v>
+        <v>-33.9</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O3" s="6">
-        <v>100</v>
-      </c>
-      <c r="P3" s="9">
-        <v>2</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>100</v>
-      </c>
-      <c r="R3" s="8">
-        <v>100</v>
+        <v>191</v>
+      </c>
+      <c r="O3" s="10">
+        <v>21</v>
+      </c>
+      <c r="P3" s="11">
+        <v>16</v>
+      </c>
+      <c r="Q3" s="12">
+        <v>7</v>
+      </c>
+      <c r="R3" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1494,55 +1467,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>86</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L4" s="4">
-        <v>-49.7</v>
+        <v>-46</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O4" s="6">
-        <v>100</v>
-      </c>
-      <c r="P4" s="10">
-        <v>28</v>
-      </c>
-      <c r="Q4" s="8">
-        <v>100</v>
-      </c>
-      <c r="R4" s="8">
-        <v>100</v>
+        <v>191</v>
+      </c>
+      <c r="O4" s="10">
+        <v>21</v>
+      </c>
+      <c r="P4" s="9">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="13">
+        <v>18</v>
+      </c>
+      <c r="R4" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1550,52 +1523,52 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>87</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="L5" s="4">
-        <v>-19.3</v>
+        <v>-11</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="O5" s="6">
-        <v>57</v>
-      </c>
-      <c r="P5" s="11">
-        <v>35</v>
-      </c>
-      <c r="Q5" s="12">
-        <v>20</v>
+        <v>85</v>
+      </c>
+      <c r="P5" s="14">
+        <v>83</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>45</v>
       </c>
       <c r="R5" s="9">
         <v>0</v>
@@ -1606,52 +1579,52 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="L6" s="4">
-        <v>-33.9</v>
+        <v>-26.2</v>
       </c>
       <c r="M6" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="N6" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O6" s="13">
-        <v>34</v>
-      </c>
-      <c r="P6" s="10">
-        <v>30</v>
-      </c>
-      <c r="Q6" s="9">
-        <v>0</v>
+      <c r="O6" s="6">
+        <v>60</v>
+      </c>
+      <c r="P6" s="15">
+        <v>52</v>
+      </c>
+      <c r="Q6" s="16">
+        <v>55</v>
       </c>
       <c r="R6" s="9">
         <v>0</v>
@@ -1662,52 +1635,52 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>89</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L7" s="4">
-        <v>-46</v>
+        <v>-40.1</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O7" s="14">
-        <v>3</v>
-      </c>
-      <c r="P7" s="15">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="9">
-        <v>0</v>
+        <v>191</v>
+      </c>
+      <c r="O7" s="10">
+        <v>46</v>
+      </c>
+      <c r="P7" s="17">
+        <v>37</v>
+      </c>
+      <c r="Q7" s="11">
+        <v>15</v>
       </c>
       <c r="R7" s="9">
         <v>0</v>
@@ -1718,55 +1691,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>90</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="L8" s="4">
-        <v>-11</v>
+        <v>-18</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="O8" s="6">
-        <v>79</v>
-      </c>
-      <c r="P8" s="16">
-        <v>79</v>
-      </c>
-      <c r="Q8" s="17">
-        <v>40</v>
-      </c>
-      <c r="R8" s="18">
-        <v>50</v>
+        <v>100</v>
+      </c>
+      <c r="P8" s="13">
+        <v>18</v>
+      </c>
+      <c r="Q8" s="18">
+        <v>78</v>
+      </c>
+      <c r="R8" s="19">
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1774,55 +1747,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>91</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="L9" s="4">
-        <v>-26.1</v>
+        <v>-32.8</v>
       </c>
       <c r="M9" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="N9" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="N9" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="O9" s="6">
-        <v>52</v>
-      </c>
-      <c r="P9" s="18">
-        <v>52</v>
+        <v>100</v>
+      </c>
+      <c r="P9" s="9">
+        <v>0</v>
       </c>
       <c r="Q9" s="19">
-        <v>45</v>
-      </c>
-      <c r="R9" s="9">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="R9" s="19">
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1830,55 +1803,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>92</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L10" s="4">
-        <v>-40.1</v>
+        <v>-45.4</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O10" s="13">
-        <v>26</v>
-      </c>
-      <c r="P10" s="20">
-        <v>26</v>
-      </c>
-      <c r="Q10" s="9">
+        <v>192</v>
+      </c>
+      <c r="O10" s="6">
+        <v>100</v>
+      </c>
+      <c r="P10" s="9">
         <v>0</v>
       </c>
-      <c r="R10" s="9">
-        <v>0</v>
+      <c r="Q10" s="20">
+        <v>97</v>
+      </c>
+      <c r="R10" s="19">
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1886,55 +1859,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>93</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="L11" s="4">
-        <v>-17.9</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="O11" s="6">
-        <v>100</v>
-      </c>
-      <c r="P11" s="21">
-        <v>13</v>
-      </c>
-      <c r="Q11" s="22">
-        <v>54</v>
-      </c>
-      <c r="R11" s="7">
-        <v>61</v>
+        <v>190</v>
+      </c>
+      <c r="O11" s="21">
+        <v>16</v>
+      </c>
+      <c r="P11" s="22">
+        <v>8</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>0</v>
+      </c>
+      <c r="R11" s="22">
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1942,55 +1915,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>94</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="L12" s="4">
-        <v>-32.8</v>
+        <v>-24.9</v>
       </c>
       <c r="M12" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="N12" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="N12" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O12" s="6">
-        <v>96</v>
-      </c>
-      <c r="P12" s="9">
+      <c r="O12" s="10">
+        <v>29</v>
+      </c>
+      <c r="P12" s="22">
+        <v>9</v>
+      </c>
+      <c r="Q12" s="9">
         <v>0</v>
       </c>
-      <c r="Q12" s="23">
-        <v>96</v>
-      </c>
-      <c r="R12" s="10">
-        <v>31</v>
+      <c r="R12" s="23">
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1998,55 +1971,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>95</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L13" s="4">
-        <v>-45.4</v>
+        <v>-39.1</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O13" s="6">
-        <v>92</v>
-      </c>
-      <c r="P13" s="9">
+        <v>191</v>
+      </c>
+      <c r="O13" s="10">
+        <v>45</v>
+      </c>
+      <c r="P13" s="12">
+        <v>6</v>
+      </c>
+      <c r="Q13" s="9">
         <v>0</v>
       </c>
-      <c r="Q13" s="24">
-        <v>89</v>
-      </c>
-      <c r="R13" s="21">
-        <v>15</v>
+      <c r="R13" s="7">
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2054,55 +2027,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>96</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="L14" s="4">
-        <v>-9.699999999999999</v>
+        <v>-16.6</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="O14" s="13">
-        <v>44</v>
-      </c>
-      <c r="P14" s="15">
+        <v>190</v>
+      </c>
+      <c r="O14" s="10">
+        <v>20</v>
+      </c>
+      <c r="P14" s="13">
+        <v>20</v>
+      </c>
+      <c r="Q14" s="12">
         <v>3</v>
       </c>
-      <c r="Q14" s="9">
-        <v>0</v>
-      </c>
-      <c r="R14" s="11">
-        <v>37</v>
+      <c r="R14" s="9">
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2110,55 +2083,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>97</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="L15" s="4">
-        <v>-24.8</v>
+        <v>-31.6</v>
       </c>
       <c r="M15" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="N15" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="N15" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="O15" s="6">
-        <v>71</v>
-      </c>
-      <c r="P15" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="9">
-        <v>0</v>
-      </c>
-      <c r="R15" s="25">
-        <v>67</v>
+        <v>72</v>
+      </c>
+      <c r="P15" s="11">
+        <v>16</v>
+      </c>
+      <c r="Q15" s="22">
+        <v>9</v>
+      </c>
+      <c r="R15" s="24">
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2166,55 +2139,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>98</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="L16" s="4">
-        <v>-39.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N16" s="1" t="s">
         <v>193</v>
       </c>
       <c r="O16" s="6">
-        <v>63</v>
-      </c>
-      <c r="P16" s="15">
+        <v>64</v>
+      </c>
+      <c r="P16" s="24">
+        <v>59</v>
+      </c>
+      <c r="Q16" s="9">
+        <v>0</v>
+      </c>
+      <c r="R16" s="12">
         <v>4</v>
-      </c>
-      <c r="Q16" s="26">
-        <v>11</v>
-      </c>
-      <c r="R16" s="7">
-        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2222,55 +2195,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>99</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="L17" s="4">
-        <v>-16.5</v>
+        <v>-23.5</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="O17" s="6">
-        <v>55</v>
-      </c>
-      <c r="P17" s="10">
-        <v>31</v>
-      </c>
-      <c r="Q17" s="12">
-        <v>21</v>
-      </c>
-      <c r="R17" s="15">
-        <v>3</v>
+        <v>58</v>
+      </c>
+      <c r="P17" s="25">
+        <v>40</v>
+      </c>
+      <c r="Q17" s="9">
+        <v>0</v>
+      </c>
+      <c r="R17" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2278,55 +2251,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>100</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>187</v>
+        <v>81</v>
       </c>
       <c r="L18" s="4">
-        <v>-31.5</v>
+        <v>-38</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O18" s="6">
-        <v>62</v>
-      </c>
-      <c r="P18" s="26">
-        <v>12</v>
-      </c>
-      <c r="Q18" s="20">
-        <v>24</v>
-      </c>
-      <c r="R18" s="9">
+        <v>56</v>
+      </c>
+      <c r="P18" s="8">
+        <v>28</v>
+      </c>
+      <c r="Q18" s="9">
         <v>0</v>
+      </c>
+      <c r="R18" s="22">
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2334,55 +2307,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>101</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="L19" s="4">
-        <v>-8.199999999999999</v>
+        <v>-15.1</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="O19" s="6">
-        <v>97</v>
-      </c>
-      <c r="P19" s="27">
-        <v>87</v>
-      </c>
-      <c r="Q19" s="12">
+        <v>68</v>
+      </c>
+      <c r="P19" s="7">
+        <v>44</v>
+      </c>
+      <c r="Q19" s="9">
+        <v>2</v>
+      </c>
+      <c r="R19" s="13">
         <v>18</v>
-      </c>
-      <c r="R19" s="9">
-        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2390,115 +2363,59 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>102</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="L20" s="4">
-        <v>-23.4</v>
+        <v>-30.2</v>
       </c>
       <c r="M20" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="N20" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="N20" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="O20" s="6">
-        <v>100</v>
-      </c>
-      <c r="P20" s="8">
-        <v>100</v>
-      </c>
-      <c r="Q20" s="9">
-        <v>0</v>
-      </c>
-      <c r="R20" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18">
-      <c r="A21" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="2">
-        <v>12</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="L21" s="4">
-        <v>-37.9</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O21" s="6">
-        <v>97</v>
-      </c>
-      <c r="P21" s="23">
-        <v>97</v>
-      </c>
-      <c r="Q21" s="9">
-        <v>0</v>
-      </c>
-      <c r="R21" s="15">
+        <v>69</v>
+      </c>
+      <c r="P20" s="17">
+        <v>34</v>
+      </c>
+      <c r="Q20" s="12">
         <v>3</v>
+      </c>
+      <c r="R20" s="8">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="L2:L21">
+  <conditionalFormatting sqref="L2:L20">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2517,7 +2434,7 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N21">
+  <conditionalFormatting sqref="N2:N20">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2534,82 +2451,82 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A21">
+  <conditionalFormatting sqref="A2:A20">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B21">
+  <conditionalFormatting sqref="B2:B20">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C21">
+  <conditionalFormatting sqref="C2:C20">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D21">
+  <conditionalFormatting sqref="D2:D20">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E21">
+  <conditionalFormatting sqref="E2:E20">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F21">
+  <conditionalFormatting sqref="F2:F20">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G21">
+  <conditionalFormatting sqref="G2:G20">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H21">
+  <conditionalFormatting sqref="H2:H20">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I21">
+  <conditionalFormatting sqref="I2:I20">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J21">
+  <conditionalFormatting sqref="J2:J20">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K21">
+  <conditionalFormatting sqref="K2:K20">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M21">
+  <conditionalFormatting sqref="M2:M20">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O21">
+  <conditionalFormatting sqref="O2:O20">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P21">
+  <conditionalFormatting sqref="P2:P20">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
